--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-04-12 06:17</t>
+          <t>Run: 2026-04-13 07:30</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-04-19 06:56</t>
+          <t>Run: 2026-04-20 07:32</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-04-26 07:12</t>
+          <t>Run: 2026-04-27 09:32</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-05-03 07:34</t>
+          <t>Run: 2026-05-04 09:33</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$267</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$227</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W267"/>
+  <dimension ref="A1:W227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -705,49 +705,53 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>20260275580</t>
+          <t>20260277635</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Rebekah Tillian Celaya</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>U.S. Bank National Association Leonard J. McDonald</t>
-        </is>
-      </c>
+          <t>ESPERANZA LOPEZ</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr"/>
       <c r="H2" s="4" t="n">
-        <v>343660</v>
+        <v>190976</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>718 W Enid Ave</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>8820 W HEATHERBRAE DRIVE</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>85037</t>
+        </is>
+      </c>
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" s="3" t="inlineStr">
@@ -758,12 +762,12 @@
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>134-17-2538</t>
+          <t>102-19-5653</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>U.S. Bank National Association Leonard J. McDonald</t>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -798,49 +802,57 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>20260275587</t>
+          <t>20260277684</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Jaime Celado</t>
+          <t>Christopher Berzoza</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
+          <t>Freedom Mortgage Corporation</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>172975</v>
+        <v>368207</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>10337 W Atlantis Way</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>6649 WEST CYPRESS STREET</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>85035</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
@@ -851,12 +863,12 @@
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>101-28-4491</t>
+          <t>148-22-02882</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -891,45 +903,57 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>20260275600</t>
+          <t>20260277721</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Stephanie C. Gosztola</t>
+          <t>HUSSEIN AL TAMEEMI AND RAHMA HATEM</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>U.S. Bank National Association, as Trustee for</t>
+          <t>Freedom Mortgage Corporation</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>416000</v>
+        <v>324021</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>18639 E Raven Dr</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>4247 W Culver Street</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>85009</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr">
@@ -940,12 +964,12 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>314-05-3051</t>
+          <t>106-29-04262</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Pass-Through Certificates, Series 2006-BNC2 Leonard J. McDonald</t>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -980,45 +1004,45 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>20260275611</t>
+          <t>20260277723</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>DIANE HOAG</t>
+          <t>TRENTON JAMES BEATTY AND AMBER LEANNE BEATTY</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>CROSSCOUNTRY MORTGAGE LLC</t>
+          <t>Freedom Mortgage Corporation</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>157700</v>
+        <v>451658</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>920 E DEVONSHIRE AVE #A206</t>
+          <t>1813 S 83RD DR</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>PHOENIX</t>
+          <t>TOLLESON</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -1028,7 +1052,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>85014</t>
+          <t>85353</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr"/>
@@ -1039,10 +1063,14 @@
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr"/>
-      <c r="S5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>504-44-38062</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Prime Recon LLC</t>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1077,45 +1105,57 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>20260275647</t>
+          <t>20260277732</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Karan Armstrong-Friedrich</t>
+          <t>Joshua Apodaca</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>U.S. Bank Trust National Association, not in its Current Trustee:</t>
+          <t>Freedom Mortgage Corporation</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>150000</v>
+        <v>396196</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>10571 W Rancho Dr</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>7146 W Bluefield Ave</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
@@ -1126,12 +1166,12 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>102-16-5507</t>
+          <t>200-44-25472</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>individual capacity but solely as owner trustee for Leonard J. McDonald</t>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1166,30 +1206,30 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>20260275665</t>
+          <t>20260277870</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>SCOTT BANKS</t>
+          <t>PAUL DAVIS JR, AMARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>NewRez LLC</t>
+          <t>Freedom Mortgage Corporation</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>452218</v>
+        <v>419826</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1199,24 +1239,16 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>2132 W HIDDEN TREASURE WAY</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
+          <t>24330 W JONES AVE</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>85086</t>
-        </is>
-      </c>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
@@ -1227,12 +1259,12 @@
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>203-06-2781</t>
+          <t>504-24-8005</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Michelle R. Ghidotti, Esq.</t>
+          <t>(</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1267,49 +1299,57 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>20260275671</t>
+          <t>20260278853</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>JOSE FRANCISCO CASTANEDA</t>
+          <t>JAN VOOLSTRA, UNMARRIED MAN</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>AMERIHOME MORTGAGE COMPANY, LLC</t>
+          <t>Lakeview Loan Servicing, LLC</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>544350</v>
+        <v>366660</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building. Maricopa County Courthouse</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>12799 S 183RD DR</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>6601 WEST POINSETTIA DRIVE</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>85304</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
@@ -1320,12 +1360,12 @@
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>400-80-802</t>
+          <t>143-04-441</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Michelle R. Ghidotti, Esq.</t>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1360,36 +1400,36 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>20260276180</t>
+          <t>20260279520</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Mohammed K Ghori and Sabiha Hussain</t>
+          <t>Mohamed A. Muglad</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>Arvest Bank, Successor in Interest by Merger to Current Trustee:</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>345000</v>
+        <v>198617</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr"/>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>1010 E Kaibab PI</t>
+          <t>3437 West Saint Catherine Avenue</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -1409,12 +1449,12 @@
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>303-91-0308</t>
+          <t>105-85-5221</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>Arvest Central Mortgage Company F/K/A Central Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1449,30 +1489,26 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>20260276197</t>
+          <t>20260279537</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>RAUL GARCIA ANDAVERDE JR, AND MICHELLE ROSE ANDAVERDE</t>
-        </is>
-      </c>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing, LLC</t>
+          <t>HFG Income , LLC</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>726200</v>
+        <v>707000</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1482,12 +1518,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>22930 S 204TH PL</t>
+          <t>5514 W Michigan Ave</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>QUEEN CREEK</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1497,7 +1533,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>85142</t>
+          <t>85308</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr"/>
@@ -1510,12 +1546,12 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>314-16-255</t>
+          <t>200-49-298</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>MTC Financial Inc. dba Trustee Corps</t>
+          <t>Robert A. Riether, Esq</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1550,45 +1586,57 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>20260276205</t>
+          <t>20260279710</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>Jabril Abdou and L. Elaine Rodriguez</t>
+          <t>MANUEL ALFREDO GUERRERO</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>MidFirst Bank</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>166840</v>
+        <v>392480</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr"/>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>law firm of Folks Hess</t>
+        </is>
+      </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>5501 E Emelita Ave</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+          <t>6836 N 33rd Dr</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr"/>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>85017</t>
+        </is>
+      </c>
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr"/>
       <c r="Q11" s="3" t="inlineStr">
@@ -1599,12 +1647,12 @@
       <c r="R11" s="3" t="inlineStr"/>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>141-83-6990</t>
+          <t>152-21-014</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>Larry O. Folks</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1639,49 +1687,57 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>20260276224</t>
+          <t>20260279714</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>Emer Alejandro Moreno Ortiz</t>
+          <t>JOSE LUIS RODRIGUEZ HERNANDEZ AND SOLEDAD AYALA RODRIGUEZ</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>U.S. Bank National Association Leonard J. McDonald</t>
+          <t>MidFirst Bank</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>230373</v>
+        <v>344350</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
+          <t>law firm of Folks Hess</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>4401 N 77th Ave</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
+          <t>6909 W San Juan Ave</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>85303</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr"/>
       <c r="Q12" s="3" t="inlineStr">
@@ -1692,12 +1748,12 @@
       <c r="R12" s="3" t="inlineStr"/>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t>102-20-9195</t>
+          <t>144-21-204</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>U.S. Bank National Association Leonard J. McDonald</t>
+          <t>Larry O. Folks</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1732,45 +1788,37 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>20260276515</t>
+          <t>20260279719</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>JONAS RIGGINS, MARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>U.S. BANK TRUST COMPANY, NATIONAL ASSOCIATION, NOT IN ITS INDIVIDUAL</t>
-        </is>
-      </c>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr"/>
+      <c r="G13" s="3" t="inlineStr"/>
       <c r="H13" s="4" t="n">
-        <v>670000</v>
+        <v>170000</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>7611 S 9TH WAY</t>
+          <t>2836 W. Portland St.</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>PHOENIX</t>
+          <t>Phoenix</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1780,7 +1828,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>85042</t>
+          <t>85009</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr"/>
@@ -1791,12 +1839,12 @@
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr"/>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t>Prime Recon LLC</t>
-        </is>
-      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>109-15-104</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr"/>
       <c r="U13" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -1829,30 +1877,30 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>20260276555</t>
+          <t>20260279801</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>ANDREW MICHAEL NIEMER</t>
+          <t>Christopher Nielsen</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing, LLC</t>
+          <t>HFG Income, LLC</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>254409</v>
+        <v>707000</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1862,12 +1910,12 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>7801 N 44TH DR UNIT 1116</t>
+          <t>17469 N. 54th Ave</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>GLENDALE</t>
+          <t>Glendale</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
@@ -1877,7 +1925,7 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>85301</t>
+          <t>85308</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr"/>
@@ -1888,335 +1936,399 @@
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>147-01-0707</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
+      <c r="S14" s="3" t="inlineStr"/>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>20260279810</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>WILLIAM G DELISLE</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>AmeriHome Mortgage Company, LLC</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>300000</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>5810 W. ASTER DR.</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>85304</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>200-39-525</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr"/>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>20260279854</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>as stated in the Deed of Trust:</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+      <c r="H16" s="4" t="n">
+        <v>305000</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr"/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>2230 North 15"" Avenue</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr"/>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr"/>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>111-06-016</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>20260280018</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>ANDREW J. GARCIA</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>PennyMac Loan Services, LLC</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>225000</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>2041 N 38TH WAY</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>85008</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>120-10-0525</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
         <is>
           <t>MTC Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="U17" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V14" s="3" t="inlineStr">
+      <c r="V17" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" s="5" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="W17" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C15" s="7" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>20260276218</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Joseph F. DeLeon</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>71500</v>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr"/>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>1434 E Hatcher Rd</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr"/>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr"/>
-      <c r="O15" s="7" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr"/>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>159-32-0133</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>20260280022</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>DONIKA R SMITH</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>PennyMac Loan Services, LLC</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>273946</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>13926 N 156TH LN</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>SURPRISE</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>85379</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>501-97-548</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V15" s="7" t="inlineStr">
+      <c r="V18" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>20260276237</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="8" t="n">
-        <v>400000</v>
-      </c>
-      <c r="I16" s="7" t="inlineStr"/>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Superior Courts Building. Maricopa County</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr"/>
-      <c r="L16" s="7" t="inlineStr"/>
-      <c r="M16" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N16" s="7" t="inlineStr"/>
-      <c r="O16" s="7" t="inlineStr"/>
-      <c r="P16" s="7" t="inlineStr"/>
-      <c r="Q16" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R16" s="7" t="inlineStr"/>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>313-11-291</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr"/>
-      <c r="U16" s="7" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V16" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="26" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>63</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="C17" s="7" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="D17" s="7" t="inlineStr">
-        <is>
-          <t>20260276784</t>
-        </is>
-      </c>
-      <c r="E17" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>C/O Bank of America, N.A.</t>
-        </is>
-      </c>
-      <c r="H17" s="8" t="n">
-        <v>58600</v>
-      </c>
-      <c r="I17" s="7" t="inlineStr"/>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Superior Courts Building. Maricopa County</t>
-        </is>
-      </c>
-      <c r="K17" s="7" t="inlineStr"/>
-      <c r="L17" s="7" t="inlineStr"/>
-      <c r="M17" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N17" s="7" t="inlineStr"/>
-      <c r="O17" s="7" t="inlineStr"/>
-      <c r="P17" s="7" t="inlineStr"/>
-      <c r="Q17" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R17" s="7" t="inlineStr"/>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>208-01-162</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr"/>
-      <c r="U17" s="7" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V17" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="26" customHeight="1">
-      <c r="A18" s="6" t="n">
-        <v>61</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Mechanic Lien</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>ML</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>20260275915</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="8" t="n">
-        <v>4816020.17</v>
-      </c>
-      <c r="I18" s="7" t="inlineStr"/>
-      <c r="J18" s="7" t="inlineStr"/>
-      <c r="K18" s="7" t="inlineStr"/>
-      <c r="L18" s="7" t="inlineStr"/>
-      <c r="M18" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N18" s="7" t="inlineStr"/>
-      <c r="O18" s="7" t="inlineStr"/>
-      <c r="P18" s="7" t="inlineStr"/>
-      <c r="Q18" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R18" s="7" t="inlineStr"/>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>210-07-171</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr"/>
-      <c r="U18" s="7" t="inlineStr">
-        <is>
-          <t>Mechanic lien; New this week</t>
-        </is>
-      </c>
-      <c r="V18" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -2224,7 +2336,7 @@
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -2238,38 +2350,30 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>20260276184</t>
+          <t>20260277622</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Jonathan Ribeiro</t>
-        </is>
-      </c>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>Name and Address of Original Truster: Maci Davis AND Hannah Davis, 12887 West Virginia Avenue, Avondale, AZ</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>40500</v>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr"/>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>8104 E Impala Ave</t>
-        </is>
-      </c>
+        <v>413000</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr"/>
       <c r="L19" s="7" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr">
         <is>
@@ -2287,12 +2391,12 @@
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>218-63-1701</t>
+          <t>501-89-7369</t>
         </is>
       </c>
       <c r="T19" s="7" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>1253, Phoenix, AZ 85016, (602) 222-5711 C</t>
         </is>
       </c>
       <c r="U19" s="7" t="inlineStr">
@@ -2313,7 +2417,7 @@
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -2327,38 +2431,38 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>20260276195</t>
+          <t>20260277769</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Cesar Borquez Felix</t>
+          <t>ERIN L BOULTER AND CRAIG H BOULTER, WIFE AND HUSBAND</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>Freedom Mortgage Corporation</t>
         </is>
       </c>
       <c r="H20" s="8" t="n">
-        <v>45360</v>
+        <v>692000</v>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr"/>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>602 E Euclid Ave</t>
-        </is>
-      </c>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr"/>
       <c r="L20" s="7" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr">
         <is>
@@ -2376,12 +2480,12 @@
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>300-45-0477</t>
+          <t>501-63-328202</t>
         </is>
       </c>
       <c r="T20" s="7" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
         </is>
       </c>
       <c r="U20" s="7" t="inlineStr">
@@ -2401,201 +2505,275 @@
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Lis Pendens</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>20260274477</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr"/>
-      <c r="G21" s="11" t="inlineStr"/>
-      <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr"/>
-      <c r="L21" s="11" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N21" s="11" t="inlineStr"/>
-      <c r="O21" s="11" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr"/>
-      <c r="Q21" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R21" s="11" t="inlineStr"/>
-      <c r="S21" s="11" t="inlineStr"/>
-      <c r="T21" s="11" t="inlineStr"/>
-      <c r="U21" s="11" t="inlineStr">
-        <is>
-          <t>Lis pendens; New this week</t>
-        </is>
-      </c>
-      <c r="V21" s="11" t="inlineStr">
+      <c r="A21" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>20260279024</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>Efrain Barranco and Kim Barranco</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>Government Loan Securitization Trust 2011-FV1,</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>78288</v>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>8630 North 32nd Avenue</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>150-10-0883</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>individual capacity but solely as Delaware trustee and Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W21" s="12" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Lis Pendens</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>20260274479</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr"/>
-      <c r="G22" s="11" t="inlineStr"/>
-      <c r="H22" s="11" t="inlineStr"/>
-      <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr"/>
-      <c r="L22" s="11" t="inlineStr"/>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr"/>
-      <c r="O22" s="11" t="inlineStr"/>
-      <c r="P22" s="11" t="inlineStr"/>
-      <c r="Q22" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R22" s="11" t="inlineStr"/>
-      <c r="S22" s="11" t="inlineStr"/>
-      <c r="T22" s="11" t="inlineStr"/>
-      <c r="U22" s="11" t="inlineStr">
-        <is>
-          <t>Lis pendens; New this week</t>
-        </is>
-      </c>
-      <c r="V22" s="11" t="inlineStr">
+      <c r="A22" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>20260279519</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>Ronald H. Swanson</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Village Capital &amp; Investment LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>78844</v>
+      </c>
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>4371 W Ocotillo Rd</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr"/>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr"/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>146-27-104</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr">
+        <is>
+          <t>Village Capital &amp; Investment LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W22" s="12" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Lis Pendens</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>20260274480</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr"/>
-      <c r="G23" s="11" t="inlineStr"/>
-      <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr"/>
-      <c r="L23" s="11" t="inlineStr"/>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N23" s="11" t="inlineStr"/>
-      <c r="O23" s="11" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr"/>
-      <c r="Q23" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R23" s="11" t="inlineStr"/>
-      <c r="S23" s="11" t="inlineStr"/>
-      <c r="T23" s="11" t="inlineStr"/>
-      <c r="U23" s="11" t="inlineStr">
-        <is>
-          <t>Lis pendens; New this week</t>
-        </is>
-      </c>
-      <c r="V23" s="11" t="inlineStr">
+      <c r="A23" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>20260279712</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="8" t="n">
+        <v>50000</v>
+      </c>
+      <c r="I23" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>law firm of Folks Hess</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>1722 East Citation Lane</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr">
+        <is>
+          <t>Tempe</t>
+        </is>
+      </c>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>85284</t>
+        </is>
+      </c>
+      <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="7" t="inlineStr"/>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr"/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>301-51-232</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr"/>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W23" s="12" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -2617,12 +2795,12 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>20260274481</t>
+          <t>20260278118</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr"/>
@@ -2650,7 +2828,11 @@
         </is>
       </c>
       <c r="R24" s="11" t="inlineStr"/>
-      <c r="S24" s="11" t="inlineStr"/>
+      <c r="S24" s="11" t="inlineStr">
+        <is>
+          <t>103-47-083</t>
+        </is>
+      </c>
       <c r="T24" s="11" t="inlineStr"/>
       <c r="U24" s="11" t="inlineStr">
         <is>
@@ -2684,12 +2866,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>20260274482</t>
+          <t>20260278615</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr"/>
@@ -2717,7 +2899,11 @@
         </is>
       </c>
       <c r="R25" s="11" t="inlineStr"/>
-      <c r="S25" s="11" t="inlineStr"/>
+      <c r="S25" s="11" t="inlineStr">
+        <is>
+          <t>203-27-748</t>
+        </is>
+      </c>
       <c r="T25" s="11" t="inlineStr"/>
       <c r="U25" s="11" t="inlineStr">
         <is>
@@ -2751,12 +2937,12 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>20260274712</t>
+          <t>20260279273</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr"/>
@@ -2784,7 +2970,11 @@
         </is>
       </c>
       <c r="R26" s="11" t="inlineStr"/>
-      <c r="S26" s="11" t="inlineStr"/>
+      <c r="S26" s="11" t="inlineStr">
+        <is>
+          <t>501-36-040</t>
+        </is>
+      </c>
       <c r="T26" s="11" t="inlineStr"/>
       <c r="U26" s="11" t="inlineStr">
         <is>
@@ -2818,12 +3008,12 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>20260275005</t>
+          <t>20260279523</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr"/>
@@ -2851,11 +3041,7 @@
         </is>
       </c>
       <c r="R27" s="11" t="inlineStr"/>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>155-08-155</t>
-        </is>
-      </c>
+      <c r="S27" s="11" t="inlineStr"/>
       <c r="T27" s="11" t="inlineStr"/>
       <c r="U27" s="11" t="inlineStr">
         <is>
@@ -2889,12 +3075,12 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>20260276252</t>
+          <t>20260279573</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
@@ -2922,7 +3108,11 @@
         </is>
       </c>
       <c r="R28" s="11" t="inlineStr"/>
-      <c r="S28" s="11" t="inlineStr"/>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>113-63-001</t>
+        </is>
+      </c>
       <c r="T28" s="11" t="inlineStr"/>
       <c r="U28" s="11" t="inlineStr">
         <is>
@@ -2946,22 +3136,22 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>20260274219</t>
+          <t>20260279844</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr"/>
@@ -2970,7 +3160,7 @@
       <c r="I29" s="11" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr"/>
@@ -2989,11 +3179,15 @@
         </is>
       </c>
       <c r="R29" s="11" t="inlineStr"/>
-      <c r="S29" s="11" t="inlineStr"/>
+      <c r="S29" s="11" t="inlineStr">
+        <is>
+          <t>202-22-179</t>
+        </is>
+      </c>
       <c r="T29" s="11" t="inlineStr"/>
       <c r="U29" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V29" s="11" t="inlineStr">
@@ -3023,12 +3217,12 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>20260274260</t>
+          <t>20260277085</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr"/>
@@ -3090,12 +3284,12 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>20260274262</t>
+          <t>20260277086</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
@@ -3104,7 +3298,7 @@
       <c r="I31" s="11" t="inlineStr"/>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr"/>
@@ -3157,12 +3351,12 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>20260274406</t>
+          <t>20260277087</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
@@ -3224,12 +3418,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>20260274425</t>
+          <t>20260277382</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
@@ -3287,23 +3481,19 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>20260274478</t>
+          <t>20260277733</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
       <c r="G34" s="11" t="inlineStr"/>
       <c r="H34" s="11" t="inlineStr"/>
       <c r="I34" s="11" t="inlineStr"/>
-      <c r="J34" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court Cause No. CV2024-034986</t>
-        </is>
-      </c>
+      <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="11" t="inlineStr"/>
       <c r="L34" s="11" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr">
@@ -3354,23 +3544,19 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>20260274835</t>
+          <t>20260277756</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
       <c r="G35" s="11" t="inlineStr"/>
       <c r="H35" s="11" t="inlineStr"/>
       <c r="I35" s="11" t="inlineStr"/>
-      <c r="J35" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J35" s="11" t="inlineStr"/>
       <c r="K35" s="11" t="inlineStr"/>
       <c r="L35" s="11" t="inlineStr"/>
       <c r="M35" s="11" t="inlineStr">
@@ -3421,19 +3607,23 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>20260274838</t>
+          <t>20260277796</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
       <c r="G36" s="11" t="inlineStr"/>
       <c r="H36" s="11" t="inlineStr"/>
       <c r="I36" s="11" t="inlineStr"/>
-      <c r="J36" s="11" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
       <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
       <c r="M36" s="11" t="inlineStr">
@@ -3484,12 +3674,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>20260274839</t>
+          <t>20260277798</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
@@ -3551,12 +3741,12 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>20260274840</t>
+          <t>20260277799</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr"/>
@@ -3565,7 +3755,7 @@
       <c r="I38" s="11" t="inlineStr"/>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr"/>
@@ -3618,19 +3808,23 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>20260274841</t>
+          <t>20260277800</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
       <c r="G39" s="11" t="inlineStr"/>
       <c r="H39" s="11" t="inlineStr"/>
       <c r="I39" s="11" t="inlineStr"/>
-      <c r="J39" s="11" t="inlineStr"/>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K39" s="11" t="inlineStr"/>
       <c r="L39" s="11" t="inlineStr"/>
       <c r="M39" s="11" t="inlineStr">
@@ -3681,23 +3875,19 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>20260274842</t>
+          <t>20260277806</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
       <c r="G40" s="11" t="inlineStr"/>
       <c r="H40" s="11" t="inlineStr"/>
       <c r="I40" s="11" t="inlineStr"/>
-      <c r="J40" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J40" s="11" t="inlineStr"/>
       <c r="K40" s="11" t="inlineStr"/>
       <c r="L40" s="11" t="inlineStr"/>
       <c r="M40" s="11" t="inlineStr">
@@ -3748,12 +3938,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>20260274843</t>
+          <t>20260277807</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
@@ -3762,7 +3952,7 @@
       <c r="I41" s="11" t="inlineStr"/>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>Superior Court i</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -3815,19 +4005,23 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>20260274844</t>
+          <t>20260277809</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
       <c r="G42" s="11" t="inlineStr"/>
       <c r="H42" s="11" t="inlineStr"/>
       <c r="I42" s="11" t="inlineStr"/>
-      <c r="J42" s="11" t="inlineStr"/>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K42" s="11" t="inlineStr"/>
       <c r="L42" s="11" t="inlineStr"/>
       <c r="M42" s="11" t="inlineStr">
@@ -3878,19 +4072,23 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>20260274847</t>
+          <t>20260277810</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr"/>
       <c r="H43" s="11" t="inlineStr"/>
       <c r="I43" s="11" t="inlineStr"/>
-      <c r="J43" s="11" t="inlineStr"/>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K43" s="11" t="inlineStr"/>
       <c r="L43" s="11" t="inlineStr"/>
       <c r="M43" s="11" t="inlineStr">
@@ -3941,23 +4139,19 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>20260275037</t>
+          <t>20260277811</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="11" t="inlineStr"/>
       <c r="H44" s="11" t="inlineStr"/>
       <c r="I44" s="11" t="inlineStr"/>
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J44" s="11" t="inlineStr"/>
       <c r="K44" s="11" t="inlineStr"/>
       <c r="L44" s="11" t="inlineStr"/>
       <c r="M44" s="11" t="inlineStr">
@@ -4008,23 +4202,19 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>20260275039</t>
+          <t>20260277813</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
       <c r="G45" s="11" t="inlineStr"/>
       <c r="H45" s="11" t="inlineStr"/>
       <c r="I45" s="11" t="inlineStr"/>
-      <c r="J45" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J45" s="11" t="inlineStr"/>
       <c r="K45" s="11" t="inlineStr"/>
       <c r="L45" s="11" t="inlineStr"/>
       <c r="M45" s="11" t="inlineStr">
@@ -4075,12 +4265,12 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>20260275152</t>
+          <t>20260277836</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
@@ -4089,7 +4279,7 @@
       <c r="I46" s="11" t="inlineStr"/>
       <c r="J46" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr"/>
@@ -4142,19 +4332,23 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>20260275440</t>
+          <t>20260277841</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
       <c r="G47" s="11" t="inlineStr"/>
       <c r="H47" s="11" t="inlineStr"/>
       <c r="I47" s="11" t="inlineStr"/>
-      <c r="J47" s="11" t="inlineStr"/>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
       <c r="K47" s="11" t="inlineStr"/>
       <c r="L47" s="11" t="inlineStr"/>
       <c r="M47" s="11" t="inlineStr">
@@ -4205,19 +4399,23 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>20260275441</t>
+          <t>20260277918</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
       <c r="G48" s="11" t="inlineStr"/>
       <c r="H48" s="11" t="inlineStr"/>
       <c r="I48" s="11" t="inlineStr"/>
-      <c r="J48" s="11" t="inlineStr"/>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K48" s="11" t="inlineStr"/>
       <c r="L48" s="11" t="inlineStr"/>
       <c r="M48" s="11" t="inlineStr">
@@ -4268,12 +4466,12 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>20260275590</t>
+          <t>20260277924</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
@@ -4282,7 +4480,7 @@
       <c r="I49" s="11" t="inlineStr"/>
       <c r="J49" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr"/>
@@ -4335,12 +4533,12 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>20260275764</t>
+          <t>20260277978</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr"/>
@@ -4349,7 +4547,7 @@
       <c r="I50" s="11" t="inlineStr"/>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>Superior Court Case No. CV2025-062290</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr"/>
@@ -4402,19 +4600,23 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>20260275789</t>
+          <t>20260278091</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
       <c r="G51" s="11" t="inlineStr"/>
       <c r="H51" s="11" t="inlineStr"/>
       <c r="I51" s="11" t="inlineStr"/>
-      <c r="J51" s="11" t="inlineStr"/>
+      <c r="J51" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K51" s="11" t="inlineStr"/>
       <c r="L51" s="11" t="inlineStr"/>
       <c r="M51" s="11" t="inlineStr">
@@ -4465,12 +4667,12 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>20260275916</t>
+          <t>20260278226</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
@@ -4479,7 +4681,7 @@
       <c r="I52" s="11" t="inlineStr"/>
       <c r="J52" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>Superior Court Case No._T J £1) 26-000517</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr"/>
@@ -4532,19 +4734,23 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>20260276231</t>
+          <t>20260278308</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
       <c r="G53" s="11" t="inlineStr"/>
       <c r="H53" s="11" t="inlineStr"/>
       <c r="I53" s="11" t="inlineStr"/>
-      <c r="J53" s="11" t="inlineStr"/>
+      <c r="J53" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
       <c r="K53" s="11" t="inlineStr"/>
       <c r="L53" s="11" t="inlineStr"/>
       <c r="M53" s="11" t="inlineStr">
@@ -4595,12 +4801,12 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>20260276287</t>
+          <t>20260279689</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
@@ -4658,12 +4864,12 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>20260276359</t>
+          <t>20260279692</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
@@ -4672,7 +4878,7 @@
       <c r="I55" s="11" t="inlineStr"/>
       <c r="J55" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>Superior Court in Maricopa County.</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr"/>
@@ -4725,19 +4931,23 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>20260276459</t>
+          <t>20260279746</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr"/>
       <c r="H56" s="11" t="inlineStr"/>
       <c r="I56" s="11" t="inlineStr"/>
-      <c r="J56" s="11" t="inlineStr"/>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K56" s="11" t="inlineStr"/>
       <c r="L56" s="11" t="inlineStr"/>
       <c r="M56" s="11" t="inlineStr">
@@ -4788,19 +4998,23 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>20260276474</t>
+          <t>20260279989</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr"/>
       <c r="G57" s="11" t="inlineStr"/>
       <c r="H57" s="11" t="inlineStr"/>
       <c r="I57" s="11" t="inlineStr"/>
-      <c r="J57" s="11" t="inlineStr"/>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K57" s="11" t="inlineStr"/>
       <c r="L57" s="11" t="inlineStr"/>
       <c r="M57" s="11" t="inlineStr">
@@ -4851,12 +5065,12 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>20260276551</t>
+          <t>20260280037</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr"/>
@@ -4865,7 +5079,7 @@
       <c r="I58" s="11" t="inlineStr"/>
       <c r="J58" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr"/>
@@ -4918,12 +5132,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>20260276682</t>
+          <t>20260280082</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
@@ -4985,19 +5199,23 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>20260276758</t>
+          <t>20260280106</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
       <c r="G60" s="11" t="inlineStr"/>
       <c r="H60" s="11" t="inlineStr"/>
       <c r="I60" s="11" t="inlineStr"/>
-      <c r="J60" s="11" t="inlineStr"/>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
       <c r="K60" s="11" t="inlineStr"/>
       <c r="L60" s="11" t="inlineStr"/>
       <c r="M60" s="11" t="inlineStr">
@@ -5038,29 +5256,33 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>20260276759</t>
+          <t>20260279044</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
       <c r="G61" s="11" t="inlineStr"/>
       <c r="H61" s="11" t="inlineStr"/>
       <c r="I61" s="11" t="inlineStr"/>
-      <c r="J61" s="11" t="inlineStr"/>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K61" s="11" t="inlineStr"/>
       <c r="L61" s="11" t="inlineStr"/>
       <c r="M61" s="11" t="inlineStr">
@@ -5081,7 +5303,7 @@
       <c r="T61" s="11" t="inlineStr"/>
       <c r="U61" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V61" s="11" t="inlineStr">
@@ -5101,29 +5323,33 @@
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>20260276760</t>
+          <t>20260279490</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
       <c r="G62" s="11" t="inlineStr"/>
       <c r="H62" s="11" t="inlineStr"/>
       <c r="I62" s="11" t="inlineStr"/>
-      <c r="J62" s="11" t="inlineStr"/>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K62" s="11" t="inlineStr"/>
       <c r="L62" s="11" t="inlineStr"/>
       <c r="M62" s="11" t="inlineStr">
@@ -5144,7 +5370,7 @@
       <c r="T62" s="11" t="inlineStr"/>
       <c r="U62" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V62" s="11" t="inlineStr">
@@ -5160,26 +5386,26 @@
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>20260276761</t>
+          <t>20260277740</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
@@ -5203,11 +5429,15 @@
         </is>
       </c>
       <c r="R63" s="11" t="inlineStr"/>
-      <c r="S63" s="11" t="inlineStr"/>
+      <c r="S63" s="11" t="inlineStr">
+        <is>
+          <t>301-53-316</t>
+        </is>
+      </c>
       <c r="T63" s="11" t="inlineStr"/>
       <c r="U63" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V63" s="11" t="inlineStr">
@@ -5223,26 +5453,26 @@
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>20260276762</t>
+          <t>20260277871</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
@@ -5270,7 +5500,7 @@
       <c r="T64" s="11" t="inlineStr"/>
       <c r="U64" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V64" s="11" t="inlineStr">
@@ -5286,26 +5516,26 @@
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>20260276764</t>
+          <t>20260278202</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
@@ -5329,11 +5559,15 @@
         </is>
       </c>
       <c r="R65" s="11" t="inlineStr"/>
-      <c r="S65" s="11" t="inlineStr"/>
+      <c r="S65" s="11" t="inlineStr">
+        <is>
+          <t>144-70-086</t>
+        </is>
+      </c>
       <c r="T65" s="11" t="inlineStr"/>
       <c r="U65" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V65" s="11" t="inlineStr">
@@ -5349,26 +5583,26 @@
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>20260276765</t>
+          <t>20260278635</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
@@ -5392,11 +5626,15 @@
         </is>
       </c>
       <c r="R66" s="11" t="inlineStr"/>
-      <c r="S66" s="11" t="inlineStr"/>
+      <c r="S66" s="11" t="inlineStr">
+        <is>
+          <t>149-17-154</t>
+        </is>
+      </c>
       <c r="T66" s="11" t="inlineStr"/>
       <c r="U66" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V66" s="11" t="inlineStr">
@@ -5412,26 +5650,26 @@
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>20260276766</t>
+          <t>20260278742</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
@@ -5459,7 +5697,7 @@
       <c r="T67" s="11" t="inlineStr"/>
       <c r="U67" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V67" s="11" t="inlineStr">
@@ -5475,26 +5713,26 @@
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>20260276767</t>
+          <t>20260278792</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
@@ -5522,7 +5760,7 @@
       <c r="T68" s="11" t="inlineStr"/>
       <c r="U68" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V68" s="11" t="inlineStr">
@@ -5538,37 +5776,33 @@
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>20260276811</t>
+          <t>20260279449</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
       <c r="G69" s="11" t="inlineStr"/>
       <c r="H69" s="11" t="inlineStr"/>
       <c r="I69" s="11" t="inlineStr"/>
-      <c r="J69" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court Case No. TJ2025-000161</t>
-        </is>
-      </c>
+      <c r="J69" s="11" t="inlineStr"/>
       <c r="K69" s="11" t="inlineStr"/>
       <c r="L69" s="11" t="inlineStr"/>
       <c r="M69" s="11" t="inlineStr">
@@ -5585,11 +5819,15 @@
         </is>
       </c>
       <c r="R69" s="11" t="inlineStr"/>
-      <c r="S69" s="11" t="inlineStr"/>
+      <c r="S69" s="11" t="inlineStr">
+        <is>
+          <t>314-13-242</t>
+        </is>
+      </c>
       <c r="T69" s="11" t="inlineStr"/>
       <c r="U69" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V69" s="11" t="inlineStr">
@@ -5605,37 +5843,33 @@
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>20260276825</t>
+          <t>20260280025</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
       <c r="G70" s="11" t="inlineStr"/>
       <c r="H70" s="11" t="inlineStr"/>
       <c r="I70" s="11" t="inlineStr"/>
-      <c r="J70" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court/Case No. CV2025-064652</t>
-        </is>
-      </c>
+      <c r="J70" s="11" t="inlineStr"/>
       <c r="K70" s="11" t="inlineStr"/>
       <c r="L70" s="11" t="inlineStr"/>
       <c r="M70" s="11" t="inlineStr">
@@ -5652,11 +5886,15 @@
         </is>
       </c>
       <c r="R70" s="11" t="inlineStr"/>
-      <c r="S70" s="11" t="inlineStr"/>
+      <c r="S70" s="11" t="inlineStr">
+        <is>
+          <t>304-64-9975</t>
+        </is>
+      </c>
       <c r="T70" s="11" t="inlineStr"/>
       <c r="U70" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V70" s="11" t="inlineStr">
@@ -5672,37 +5910,33 @@
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>20260276828</t>
+          <t>20260276994</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr"/>
       <c r="H71" s="11" t="inlineStr"/>
       <c r="I71" s="11" t="inlineStr"/>
-      <c r="J71" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court Case No. J 2026-000314</t>
-        </is>
-      </c>
+      <c r="J71" s="11" t="inlineStr"/>
       <c r="K71" s="11" t="inlineStr"/>
       <c r="L71" s="11" t="inlineStr"/>
       <c r="M71" s="11" t="inlineStr">
@@ -5723,7 +5957,7 @@
       <c r="T71" s="11" t="inlineStr"/>
       <c r="U71" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V71" s="11" t="inlineStr">
@@ -5739,37 +5973,33 @@
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>20260275031</t>
+          <t>20260276996</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="11" t="inlineStr"/>
       <c r="H72" s="11" t="inlineStr"/>
       <c r="I72" s="11" t="inlineStr"/>
-      <c r="J72" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE-STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J72" s="11" t="inlineStr"/>
       <c r="K72" s="11" t="inlineStr"/>
       <c r="L72" s="11" t="inlineStr"/>
       <c r="M72" s="11" t="inlineStr">
@@ -5790,7 +6020,7 @@
       <c r="T72" s="11" t="inlineStr"/>
       <c r="U72" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V72" s="11" t="inlineStr">
@@ -5806,37 +6036,33 @@
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>20260276100</t>
+          <t>20260276997</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
       <c r="G73" s="11" t="inlineStr"/>
       <c r="H73" s="11" t="inlineStr"/>
       <c r="I73" s="11" t="inlineStr"/>
-      <c r="J73" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J73" s="11" t="inlineStr"/>
       <c r="K73" s="11" t="inlineStr"/>
       <c r="L73" s="11" t="inlineStr"/>
       <c r="M73" s="11" t="inlineStr">
@@ -5857,7 +6083,7 @@
       <c r="T73" s="11" t="inlineStr"/>
       <c r="U73" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V73" s="11" t="inlineStr">
@@ -5873,37 +6099,33 @@
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>20260276726</t>
+          <t>20260276998</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
       <c r="G74" s="11" t="inlineStr"/>
       <c r="H74" s="11" t="inlineStr"/>
       <c r="I74" s="11" t="inlineStr"/>
-      <c r="J74" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J74" s="11" t="inlineStr"/>
       <c r="K74" s="11" t="inlineStr"/>
       <c r="L74" s="11" t="inlineStr"/>
       <c r="M74" s="11" t="inlineStr">
@@ -5924,7 +6146,7 @@
       <c r="T74" s="11" t="inlineStr"/>
       <c r="U74" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V74" s="11" t="inlineStr">
@@ -5940,37 +6162,33 @@
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>20260275029</t>
+          <t>20260276999</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
       <c r="G75" s="11" t="inlineStr"/>
       <c r="H75" s="11" t="inlineStr"/>
       <c r="I75" s="11" t="inlineStr"/>
-      <c r="J75" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court q</t>
-        </is>
-      </c>
+      <c r="J75" s="11" t="inlineStr"/>
       <c r="K75" s="11" t="inlineStr"/>
       <c r="L75" s="11" t="inlineStr"/>
       <c r="M75" s="11" t="inlineStr">
@@ -5991,7 +6209,7 @@
       <c r="T75" s="11" t="inlineStr"/>
       <c r="U75" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V75" s="11" t="inlineStr">
@@ -6007,26 +6225,26 @@
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>20260275853</t>
+          <t>20260277000</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
@@ -6054,7 +6272,7 @@
       <c r="T76" s="11" t="inlineStr"/>
       <c r="U76" s="11" t="inlineStr">
         <is>
-          <t>Mechanic lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V76" s="11" t="inlineStr">
@@ -6070,26 +6288,26 @@
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>20260276004</t>
+          <t>20260277001</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr"/>
@@ -6113,15 +6331,11 @@
         </is>
       </c>
       <c r="R77" s="11" t="inlineStr"/>
-      <c r="S77" s="11" t="inlineStr">
-        <is>
-          <t>118-25-121</t>
-        </is>
-      </c>
+      <c r="S77" s="11" t="inlineStr"/>
       <c r="T77" s="11" t="inlineStr"/>
       <c r="U77" s="11" t="inlineStr">
         <is>
-          <t>Mechanic lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V77" s="11" t="inlineStr">
@@ -6137,26 +6351,26 @@
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>20260276364</t>
+          <t>20260277002</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
@@ -6180,15 +6394,11 @@
         </is>
       </c>
       <c r="R78" s="11" t="inlineStr"/>
-      <c r="S78" s="11" t="inlineStr">
-        <is>
-          <t>118-37-021</t>
-        </is>
-      </c>
+      <c r="S78" s="11" t="inlineStr"/>
       <c r="T78" s="11" t="inlineStr"/>
       <c r="U78" s="11" t="inlineStr">
         <is>
-          <t>Mechanic lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V78" s="11" t="inlineStr">
@@ -6218,12 +6428,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>20260274186</t>
+          <t>20260277003</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr"/>
@@ -6281,12 +6491,12 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>20260274187</t>
+          <t>20260277004</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
@@ -6344,12 +6554,12 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>20260274193</t>
+          <t>20260277005</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr"/>
@@ -6407,12 +6617,12 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>20260274194</t>
+          <t>20260277006</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr"/>
@@ -6470,12 +6680,12 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>20260274195</t>
+          <t>20260277008</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
@@ -6533,12 +6743,12 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>20260274196</t>
+          <t>20260277009</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr"/>
@@ -6596,12 +6806,12 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>20260274197</t>
+          <t>20260277010</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr"/>
@@ -6659,12 +6869,12 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>20260274198</t>
+          <t>20260277011</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr"/>
@@ -6722,12 +6932,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>20260274199</t>
+          <t>20260277012</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr"/>
@@ -6785,12 +6995,12 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>20260274200</t>
+          <t>20260277013</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr"/>
@@ -6848,12 +7058,12 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>20260274201</t>
+          <t>20260277014</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
@@ -6911,12 +7121,12 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>20260274202</t>
+          <t>20260277016</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
@@ -6974,12 +7184,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>20260274203</t>
+          <t>20260277024</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr"/>
@@ -7037,12 +7247,12 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>20260274204</t>
+          <t>20260277110</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr"/>
@@ -7100,12 +7310,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>20260274205</t>
+          <t>20260277111</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
@@ -7163,12 +7373,12 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>20260274206</t>
+          <t>20260277112</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr"/>
@@ -7226,12 +7436,12 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>20260274207</t>
+          <t>20260277250</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr"/>
@@ -7289,12 +7499,12 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>20260274799</t>
+          <t>20260277317</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr"/>
@@ -7352,12 +7562,12 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>20260274807</t>
+          <t>20260277865</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr"/>
@@ -7415,12 +7625,12 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>20260274818</t>
+          <t>20260277866</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr"/>
@@ -7478,12 +7688,12 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>20260274819</t>
+          <t>20260277867</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr"/>
@@ -7541,12 +7751,12 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>20260274821</t>
+          <t>20260278330</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr"/>
@@ -7604,12 +7814,12 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>20260274854</t>
+          <t>20260278332</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr"/>
@@ -7667,12 +7877,12 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>20260274866</t>
+          <t>20260278442</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr"/>
@@ -7730,12 +7940,12 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>20260274869</t>
+          <t>20260278463</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr"/>
@@ -7793,12 +8003,12 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>20260274871</t>
+          <t>20260278482</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr"/>
@@ -7856,12 +8066,12 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>20260274876</t>
+          <t>20260278483</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr"/>
@@ -7919,12 +8129,12 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>20260274913</t>
+          <t>20260278484</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr"/>
@@ -7972,22 +8182,22 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>20260274217</t>
+          <t>20260278485</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr"/>
@@ -8015,12 +8225,12 @@
       <c r="T107" s="11" t="inlineStr"/>
       <c r="U107" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V107" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W107" s="12" t="inlineStr">
@@ -8035,22 +8245,22 @@
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>20260274218</t>
+          <t>20260278648</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr"/>
@@ -8078,12 +8288,12 @@
       <c r="T108" s="11" t="inlineStr"/>
       <c r="U108" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V108" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W108" s="12" t="inlineStr">
@@ -8108,12 +8318,12 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>20260274554</t>
+          <t>20260277161</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr"/>
@@ -8171,12 +8381,12 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>20260275511</t>
+          <t>20260277679</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr"/>
@@ -8234,12 +8444,12 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>20260275610</t>
+          <t>20260277906</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr"/>
@@ -8297,12 +8507,12 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>20260275717</t>
+          <t>20260278256</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr"/>
@@ -8360,12 +8570,12 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>20260275785</t>
+          <t>20260278259</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr"/>
@@ -8423,12 +8633,12 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>20260276063</t>
+          <t>20260279205</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr"/>
@@ -8476,22 +8686,22 @@
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>20260275373</t>
+          <t>20260279499</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr"/>
@@ -8519,7 +8729,7 @@
       <c r="T115" s="11" t="inlineStr"/>
       <c r="U115" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V115" s="11" t="inlineStr">
@@ -8549,12 +8759,12 @@
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>20260275537</t>
+          <t>20260277714</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr"/>
@@ -8612,12 +8822,12 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>20260276099</t>
+          <t>20260278200</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr"/>
@@ -8675,12 +8885,12 @@
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>20260276188</t>
+          <t>20260278404</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr"/>
@@ -8738,12 +8948,12 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>20260276274</t>
+          <t>20260279054</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr"/>
@@ -8801,12 +9011,12 @@
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>20260276517</t>
+          <t>20260279280</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr"/>
@@ -8864,12 +9074,12 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>20260276637</t>
+          <t>20260279433</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr"/>
@@ -8927,12 +9137,12 @@
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>20260276678</t>
+          <t>20260279461</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr"/>
@@ -8976,26 +9186,26 @@
     </row>
     <row r="123" ht="26" customHeight="1">
       <c r="A123" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>20260274432</t>
+          <t>20260279568</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr"/>
@@ -9023,12 +9233,12 @@
       <c r="T123" s="11" t="inlineStr"/>
       <c r="U123" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V123" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W123" s="12" t="inlineStr">
@@ -9039,26 +9249,26 @@
     </row>
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>20260274459</t>
+          <t>20260279684</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr"/>
@@ -9086,12 +9296,12 @@
       <c r="T124" s="11" t="inlineStr"/>
       <c r="U124" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V124" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W124" s="12" t="inlineStr">
@@ -9102,26 +9312,26 @@
     </row>
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>20260274460</t>
+          <t>20260279685</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr"/>
@@ -9149,12 +9359,12 @@
       <c r="T125" s="11" t="inlineStr"/>
       <c r="U125" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V125" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W125" s="12" t="inlineStr">
@@ -9165,26 +9375,26 @@
     </row>
     <row r="126" ht="26" customHeight="1">
       <c r="A126" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>20260274461</t>
+          <t>20260279781</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr"/>
@@ -9212,12 +9422,12 @@
       <c r="T126" s="11" t="inlineStr"/>
       <c r="U126" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V126" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W126" s="12" t="inlineStr">
@@ -9228,26 +9438,26 @@
     </row>
     <row r="127" ht="26" customHeight="1">
       <c r="A127" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>20260274462</t>
+          <t>20260279977</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr"/>
@@ -9275,12 +9485,12 @@
       <c r="T127" s="11" t="inlineStr"/>
       <c r="U127" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V127" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W127" s="12" t="inlineStr">
@@ -9291,26 +9501,26 @@
     </row>
     <row r="128" ht="26" customHeight="1">
       <c r="A128" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>20260274463</t>
+          <t>20260280005</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr"/>
@@ -9338,12 +9548,12 @@
       <c r="T128" s="11" t="inlineStr"/>
       <c r="U128" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V128" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W128" s="12" t="inlineStr">
@@ -9368,12 +9578,12 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>20260274464</t>
+          <t>20260278793</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr"/>
@@ -9431,12 +9641,12 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>20260274465</t>
+          <t>20260278794</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr"/>
@@ -9494,12 +9704,12 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>20260274466</t>
+          <t>20260278798</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr"/>
@@ -9557,12 +9767,12 @@
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>20260274467</t>
+          <t>20260278799</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr"/>
@@ -9620,12 +9830,12 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>20260274468</t>
+          <t>20260278804</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr"/>
@@ -9683,12 +9893,12 @@
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>20260274774</t>
+          <t>20260278805</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr"/>
@@ -9746,12 +9956,12 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>20260274829</t>
+          <t>20260278806</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr"/>
@@ -9809,12 +10019,12 @@
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>20260274862</t>
+          <t>20260278807</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr"/>
@@ -9872,12 +10082,12 @@
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>20260274912</t>
+          <t>20260278808</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr"/>
@@ -9935,12 +10145,12 @@
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>20260274914</t>
+          <t>20260278809</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr"/>
@@ -9998,12 +10208,12 @@
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>20260274918</t>
+          <t>20260278810</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr"/>
@@ -10061,12 +10271,12 @@
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>20260274920</t>
+          <t>20260278811</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr"/>
@@ -10124,12 +10334,12 @@
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>20260275002</t>
+          <t>20260278812</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr"/>
@@ -10187,12 +10397,12 @@
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>20260275710</t>
+          <t>20260278813</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr"/>
@@ -10250,12 +10460,12 @@
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>20260275714</t>
+          <t>20260278814</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr"/>
@@ -10313,12 +10523,12 @@
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>20260275832</t>
+          <t>20260278815</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr"/>
@@ -10376,12 +10586,12 @@
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>20260275833</t>
+          <t>20260278816</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr"/>
@@ -10439,12 +10649,12 @@
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>20260275834</t>
+          <t>20260278817</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr"/>
@@ -10468,7 +10678,11 @@
         </is>
       </c>
       <c r="R146" s="11" t="inlineStr"/>
-      <c r="S146" s="11" t="inlineStr"/>
+      <c r="S146" s="11" t="inlineStr">
+        <is>
+          <t>501-96-414</t>
+        </is>
+      </c>
       <c r="T146" s="11" t="inlineStr"/>
       <c r="U146" s="11" t="inlineStr">
         <is>
@@ -10502,12 +10716,12 @@
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>20260275841</t>
+          <t>20260278818</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr"/>
@@ -10565,12 +10779,12 @@
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>20260275844</t>
+          <t>20260278820</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr"/>
@@ -10628,12 +10842,12 @@
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>20260275845</t>
+          <t>20260278821</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr"/>
@@ -10691,12 +10905,12 @@
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>20260275847</t>
+          <t>20260278822</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr"/>
@@ -10754,12 +10968,12 @@
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>20260275848</t>
+          <t>20260278823</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr"/>
@@ -10817,12 +11031,12 @@
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>20260275849</t>
+          <t>20260279185</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr"/>
@@ -10880,12 +11094,12 @@
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>20260275850</t>
+          <t>20260279330</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr"/>
@@ -10943,12 +11157,12 @@
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>20260275851</t>
+          <t>20260279337</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr"/>
@@ -11006,12 +11220,12 @@
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>20260275852</t>
+          <t>20260279338</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr"/>
@@ -11069,12 +11283,12 @@
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>20260276084</t>
+          <t>20260279339</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr"/>
@@ -11132,12 +11346,12 @@
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>20260276091</t>
+          <t>20260279527</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr"/>
@@ -11195,12 +11409,12 @@
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>20260276094</t>
+          <t>20260279528</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr"/>
@@ -11258,12 +11472,12 @@
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>20260276109</t>
+          <t>20260279529</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr"/>
@@ -11307,26 +11521,26 @@
     </row>
     <row r="160" ht="26" customHeight="1">
       <c r="A160" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>20260276281</t>
+          <t>20260278662</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr"/>
@@ -11354,12 +11568,12 @@
       <c r="T160" s="11" t="inlineStr"/>
       <c r="U160" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V160" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W160" s="12" t="inlineStr">
@@ -11370,26 +11584,26 @@
     </row>
     <row r="161" ht="26" customHeight="1">
       <c r="A161" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>20260276306</t>
+          <t>20260278663</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr"/>
@@ -11417,12 +11631,12 @@
       <c r="T161" s="11" t="inlineStr"/>
       <c r="U161" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V161" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W161" s="12" t="inlineStr">
@@ -11433,26 +11647,26 @@
     </row>
     <row r="162" ht="26" customHeight="1">
       <c r="A162" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>20260276556</t>
+          <t>20260278664</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F162" s="11" t="inlineStr"/>
@@ -11480,12 +11694,12 @@
       <c r="T162" s="11" t="inlineStr"/>
       <c r="U162" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V162" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W162" s="12" t="inlineStr">
@@ -11496,26 +11710,26 @@
     </row>
     <row r="163" ht="26" customHeight="1">
       <c r="A163" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>20260276557</t>
+          <t>20260278665</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr"/>
@@ -11543,12 +11757,12 @@
       <c r="T163" s="11" t="inlineStr"/>
       <c r="U163" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V163" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W163" s="12" t="inlineStr">
@@ -11559,26 +11773,26 @@
     </row>
     <row r="164" ht="26" customHeight="1">
       <c r="A164" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>20260276558</t>
+          <t>20260278666</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr"/>
@@ -11606,12 +11820,12 @@
       <c r="T164" s="11" t="inlineStr"/>
       <c r="U164" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V164" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W164" s="12" t="inlineStr">
@@ -11622,26 +11836,26 @@
     </row>
     <row r="165" ht="26" customHeight="1">
       <c r="A165" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>20260276559</t>
+          <t>20260278667</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr"/>
@@ -11669,12 +11883,12 @@
       <c r="T165" s="11" t="inlineStr"/>
       <c r="U165" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V165" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W165" s="12" t="inlineStr">
@@ -11685,26 +11899,26 @@
     </row>
     <row r="166" ht="26" customHeight="1">
       <c r="A166" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>20260276560</t>
+          <t>20260278668</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F166" s="11" t="inlineStr"/>
@@ -11732,12 +11946,12 @@
       <c r="T166" s="11" t="inlineStr"/>
       <c r="U166" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V166" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W166" s="12" t="inlineStr">
@@ -11748,26 +11962,26 @@
     </row>
     <row r="167" ht="26" customHeight="1">
       <c r="A167" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>20260276561</t>
+          <t>20260278669</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F167" s="11" t="inlineStr"/>
@@ -11795,12 +12009,12 @@
       <c r="T167" s="11" t="inlineStr"/>
       <c r="U167" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V167" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W167" s="12" t="inlineStr">
@@ -11825,12 +12039,12 @@
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>20260274815</t>
+          <t>20260278670</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F168" s="11" t="inlineStr"/>
@@ -11888,12 +12102,12 @@
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>20260274816</t>
+          <t>20260278672</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr"/>
@@ -11951,12 +12165,12 @@
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>20260274820</t>
+          <t>20260278674</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr"/>
@@ -12014,12 +12228,12 @@
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>20260274823</t>
+          <t>20260278675</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr"/>
@@ -12077,12 +12291,12 @@
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>20260274851</t>
+          <t>20260278676</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr"/>
@@ -12140,12 +12354,12 @@
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>20260274856</t>
+          <t>20260278677</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr"/>
@@ -12203,12 +12417,12 @@
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>20260274867</t>
+          <t>20260278678</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr"/>
@@ -12266,12 +12480,12 @@
       </c>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>20260274868</t>
+          <t>20260278679</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F175" s="11" t="inlineStr"/>
@@ -12329,12 +12543,12 @@
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>20260274870</t>
+          <t>20260278680</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F176" s="11" t="inlineStr"/>
@@ -12392,12 +12606,12 @@
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>20260274874</t>
+          <t>20260278682</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F177" s="11" t="inlineStr"/>
@@ -12455,12 +12669,12 @@
       </c>
       <c r="D178" s="11" t="inlineStr">
         <is>
-          <t>20260274875</t>
+          <t>20260278715</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F178" s="11" t="inlineStr"/>
@@ -12518,12 +12732,12 @@
       </c>
       <c r="D179" s="11" t="inlineStr">
         <is>
-          <t>20260274907</t>
+          <t>20260278718</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F179" s="11" t="inlineStr"/>
@@ -12581,12 +12795,12 @@
       </c>
       <c r="D180" s="11" t="inlineStr">
         <is>
-          <t>20260275038</t>
+          <t>20260278758</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F180" s="11" t="inlineStr"/>
@@ -12644,12 +12858,12 @@
       </c>
       <c r="D181" s="11" t="inlineStr">
         <is>
-          <t>20260275054</t>
+          <t>20260278759</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F181" s="11" t="inlineStr"/>
@@ -12707,12 +12921,12 @@
       </c>
       <c r="D182" s="11" t="inlineStr">
         <is>
-          <t>20260275280</t>
+          <t>20260278760</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr"/>
@@ -12770,12 +12984,12 @@
       </c>
       <c r="D183" s="11" t="inlineStr">
         <is>
-          <t>20260275392</t>
+          <t>20260278768</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F183" s="11" t="inlineStr"/>
@@ -12833,12 +13047,12 @@
       </c>
       <c r="D184" s="11" t="inlineStr">
         <is>
-          <t>20260275394</t>
+          <t>20260278972</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr"/>
@@ -12896,12 +13110,12 @@
       </c>
       <c r="D185" s="11" t="inlineStr">
         <is>
-          <t>20260275395</t>
+          <t>20260278983</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F185" s="11" t="inlineStr"/>
@@ -12959,12 +13173,12 @@
       </c>
       <c r="D186" s="11" t="inlineStr">
         <is>
-          <t>20260275396</t>
+          <t>20260278984</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr"/>
@@ -13022,12 +13236,12 @@
       </c>
       <c r="D187" s="11" t="inlineStr">
         <is>
-          <t>20260275397</t>
+          <t>20260278985</t>
         </is>
       </c>
       <c r="E187" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F187" s="11" t="inlineStr"/>
@@ -13085,12 +13299,12 @@
       </c>
       <c r="D188" s="11" t="inlineStr">
         <is>
-          <t>20260275398</t>
+          <t>20260279005</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F188" s="11" t="inlineStr"/>
@@ -13148,12 +13362,12 @@
       </c>
       <c r="D189" s="11" t="inlineStr">
         <is>
-          <t>20260275399</t>
+          <t>20260279006</t>
         </is>
       </c>
       <c r="E189" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F189" s="11" t="inlineStr"/>
@@ -13211,12 +13425,12 @@
       </c>
       <c r="D190" s="11" t="inlineStr">
         <is>
-          <t>20260275400</t>
+          <t>20260279007</t>
         </is>
       </c>
       <c r="E190" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F190" s="11" t="inlineStr"/>
@@ -13274,12 +13488,12 @@
       </c>
       <c r="D191" s="11" t="inlineStr">
         <is>
-          <t>20260275401</t>
+          <t>20260279008</t>
         </is>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr"/>
@@ -13337,12 +13551,12 @@
       </c>
       <c r="D192" s="11" t="inlineStr">
         <is>
-          <t>20260275402</t>
+          <t>20260279009</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F192" s="11" t="inlineStr"/>
@@ -13400,12 +13614,12 @@
       </c>
       <c r="D193" s="11" t="inlineStr">
         <is>
-          <t>20260275403</t>
+          <t>20260279010</t>
         </is>
       </c>
       <c r="E193" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F193" s="11" t="inlineStr"/>
@@ -13463,12 +13677,12 @@
       </c>
       <c r="D194" s="11" t="inlineStr">
         <is>
-          <t>20260275408</t>
+          <t>20260279011</t>
         </is>
       </c>
       <c r="E194" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F194" s="11" t="inlineStr"/>
@@ -13526,12 +13740,12 @@
       </c>
       <c r="D195" s="11" t="inlineStr">
         <is>
-          <t>20260275410</t>
+          <t>20260279012</t>
         </is>
       </c>
       <c r="E195" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F195" s="11" t="inlineStr"/>
@@ -13589,12 +13803,12 @@
       </c>
       <c r="D196" s="11" t="inlineStr">
         <is>
-          <t>20260275526</t>
+          <t>20260279013</t>
         </is>
       </c>
       <c r="E196" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F196" s="11" t="inlineStr"/>
@@ -13652,12 +13866,12 @@
       </c>
       <c r="D197" s="11" t="inlineStr">
         <is>
-          <t>20260275565</t>
+          <t>20260279014</t>
         </is>
       </c>
       <c r="E197" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F197" s="11" t="inlineStr"/>
@@ -13715,12 +13929,12 @@
       </c>
       <c r="D198" s="11" t="inlineStr">
         <is>
-          <t>20260275623</t>
+          <t>20260279147</t>
         </is>
       </c>
       <c r="E198" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F198" s="11" t="inlineStr"/>
@@ -13778,12 +13992,12 @@
       </c>
       <c r="D199" s="11" t="inlineStr">
         <is>
-          <t>20260275624</t>
+          <t>20260279199</t>
         </is>
       </c>
       <c r="E199" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F199" s="11" t="inlineStr"/>
@@ -13841,12 +14055,12 @@
       </c>
       <c r="D200" s="11" t="inlineStr">
         <is>
-          <t>20260275625</t>
+          <t>20260279240</t>
         </is>
       </c>
       <c r="E200" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F200" s="11" t="inlineStr"/>
@@ -13904,12 +14118,12 @@
       </c>
       <c r="D201" s="11" t="inlineStr">
         <is>
-          <t>20260275626</t>
+          <t>20260279564</t>
         </is>
       </c>
       <c r="E201" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F201" s="11" t="inlineStr"/>
@@ -13967,12 +14181,12 @@
       </c>
       <c r="D202" s="11" t="inlineStr">
         <is>
-          <t>20260275627</t>
+          <t>20260279567</t>
         </is>
       </c>
       <c r="E202" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F202" s="11" t="inlineStr"/>
@@ -14030,12 +14244,12 @@
       </c>
       <c r="D203" s="11" t="inlineStr">
         <is>
-          <t>20260275742</t>
+          <t>20260279571</t>
         </is>
       </c>
       <c r="E203" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F203" s="11" t="inlineStr"/>
@@ -14093,12 +14307,12 @@
       </c>
       <c r="D204" s="11" t="inlineStr">
         <is>
-          <t>20260275754</t>
+          <t>20260279574</t>
         </is>
       </c>
       <c r="E204" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F204" s="11" t="inlineStr"/>
@@ -14156,12 +14370,12 @@
       </c>
       <c r="D205" s="11" t="inlineStr">
         <is>
-          <t>20260275756</t>
+          <t>20260279578</t>
         </is>
       </c>
       <c r="E205" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F205" s="11" t="inlineStr"/>
@@ -14219,12 +14433,12 @@
       </c>
       <c r="D206" s="11" t="inlineStr">
         <is>
-          <t>20260275856</t>
+          <t>20260279581</t>
         </is>
       </c>
       <c r="E206" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F206" s="11" t="inlineStr"/>
@@ -14282,12 +14496,12 @@
       </c>
       <c r="D207" s="11" t="inlineStr">
         <is>
-          <t>20260275857</t>
+          <t>20260279582</t>
         </is>
       </c>
       <c r="E207" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F207" s="11" t="inlineStr"/>
@@ -14345,12 +14559,12 @@
       </c>
       <c r="D208" s="11" t="inlineStr">
         <is>
-          <t>20260276083</t>
+          <t>20260279583</t>
         </is>
       </c>
       <c r="E208" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F208" s="11" t="inlineStr"/>
@@ -14408,12 +14622,12 @@
       </c>
       <c r="D209" s="11" t="inlineStr">
         <is>
-          <t>20260276368</t>
+          <t>20260279585</t>
         </is>
       </c>
       <c r="E209" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F209" s="11" t="inlineStr"/>
@@ -14471,12 +14685,12 @@
       </c>
       <c r="D210" s="11" t="inlineStr">
         <is>
-          <t>20260276407</t>
+          <t>20260279587</t>
         </is>
       </c>
       <c r="E210" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F210" s="11" t="inlineStr"/>
@@ -14534,12 +14748,12 @@
       </c>
       <c r="D211" s="11" t="inlineStr">
         <is>
-          <t>20260276408</t>
+          <t>20260279588</t>
         </is>
       </c>
       <c r="E211" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F211" s="11" t="inlineStr"/>
@@ -14597,12 +14811,12 @@
       </c>
       <c r="D212" s="11" t="inlineStr">
         <is>
-          <t>20260276409</t>
+          <t>20260279591</t>
         </is>
       </c>
       <c r="E212" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F212" s="11" t="inlineStr"/>
@@ -14660,12 +14874,12 @@
       </c>
       <c r="D213" s="11" t="inlineStr">
         <is>
-          <t>20260276410</t>
+          <t>20260279592</t>
         </is>
       </c>
       <c r="E213" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F213" s="11" t="inlineStr"/>
@@ -14723,12 +14937,12 @@
       </c>
       <c r="D214" s="11" t="inlineStr">
         <is>
-          <t>20260276411</t>
+          <t>20260279593</t>
         </is>
       </c>
       <c r="E214" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F214" s="11" t="inlineStr"/>
@@ -14786,12 +15000,12 @@
       </c>
       <c r="D215" s="11" t="inlineStr">
         <is>
-          <t>20260276412</t>
+          <t>20260279608</t>
         </is>
       </c>
       <c r="E215" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F215" s="11" t="inlineStr"/>
@@ -14849,12 +15063,12 @@
       </c>
       <c r="D216" s="11" t="inlineStr">
         <is>
-          <t>20260276414</t>
+          <t>20260279609</t>
         </is>
       </c>
       <c r="E216" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F216" s="11" t="inlineStr"/>
@@ -14912,12 +15126,12 @@
       </c>
       <c r="D217" s="11" t="inlineStr">
         <is>
-          <t>20260276415</t>
+          <t>20260279661</t>
         </is>
       </c>
       <c r="E217" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F217" s="11" t="inlineStr"/>
@@ -14975,12 +15189,12 @@
       </c>
       <c r="D218" s="11" t="inlineStr">
         <is>
-          <t>20260276416</t>
+          <t>20260279667</t>
         </is>
       </c>
       <c r="E218" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F218" s="11" t="inlineStr"/>
@@ -15038,12 +15252,12 @@
       </c>
       <c r="D219" s="11" t="inlineStr">
         <is>
-          <t>20260276417</t>
+          <t>20260279743</t>
         </is>
       </c>
       <c r="E219" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F219" s="11" t="inlineStr"/>
@@ -15101,12 +15315,12 @@
       </c>
       <c r="D220" s="11" t="inlineStr">
         <is>
-          <t>20260276418</t>
+          <t>20260280008</t>
         </is>
       </c>
       <c r="E220" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F220" s="11" t="inlineStr"/>
@@ -15164,12 +15378,12 @@
       </c>
       <c r="D221" s="11" t="inlineStr">
         <is>
-          <t>20260276419</t>
+          <t>20260280011</t>
         </is>
       </c>
       <c r="E221" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F221" s="11" t="inlineStr"/>
@@ -15227,12 +15441,12 @@
       </c>
       <c r="D222" s="11" t="inlineStr">
         <is>
-          <t>20260276420</t>
+          <t>20260280012</t>
         </is>
       </c>
       <c r="E222" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F222" s="11" t="inlineStr"/>
@@ -15290,12 +15504,12 @@
       </c>
       <c r="D223" s="11" t="inlineStr">
         <is>
-          <t>20260276421</t>
+          <t>20260280013</t>
         </is>
       </c>
       <c r="E223" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F223" s="11" t="inlineStr"/>
@@ -15353,12 +15567,12 @@
       </c>
       <c r="D224" s="11" t="inlineStr">
         <is>
-          <t>20260276422</t>
+          <t>20260280014</t>
         </is>
       </c>
       <c r="E224" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F224" s="11" t="inlineStr"/>
@@ -15416,12 +15630,12 @@
       </c>
       <c r="D225" s="11" t="inlineStr">
         <is>
-          <t>20260276423</t>
+          <t>20260280015</t>
         </is>
       </c>
       <c r="E225" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F225" s="11" t="inlineStr"/>
@@ -15479,12 +15693,12 @@
       </c>
       <c r="D226" s="11" t="inlineStr">
         <is>
-          <t>20260276424</t>
+          <t>20260280016</t>
         </is>
       </c>
       <c r="E226" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F226" s="11" t="inlineStr"/>
@@ -15542,12 +15756,12 @@
       </c>
       <c r="D227" s="11" t="inlineStr">
         <is>
-          <t>20260276425</t>
+          <t>20260280089</t>
         </is>
       </c>
       <c r="E227" s="11" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F227" s="11" t="inlineStr"/>
@@ -15589,2528 +15803,8 @@
         </is>
       </c>
     </row>
-    <row r="228" ht="26" customHeight="1">
-      <c r="A228" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B228" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C228" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D228" s="11" t="inlineStr">
-        <is>
-          <t>20260276426</t>
-        </is>
-      </c>
-      <c r="E228" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F228" s="11" t="inlineStr"/>
-      <c r="G228" s="11" t="inlineStr"/>
-      <c r="H228" s="11" t="inlineStr"/>
-      <c r="I228" s="11" t="inlineStr"/>
-      <c r="J228" s="11" t="inlineStr"/>
-      <c r="K228" s="11" t="inlineStr"/>
-      <c r="L228" s="11" t="inlineStr"/>
-      <c r="M228" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N228" s="11" t="inlineStr"/>
-      <c r="O228" s="11" t="inlineStr"/>
-      <c r="P228" s="11" t="inlineStr"/>
-      <c r="Q228" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R228" s="11" t="inlineStr"/>
-      <c r="S228" s="11" t="inlineStr"/>
-      <c r="T228" s="11" t="inlineStr"/>
-      <c r="U228" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V228" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W228" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="229" ht="26" customHeight="1">
-      <c r="A229" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B229" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C229" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D229" s="11" t="inlineStr">
-        <is>
-          <t>20260276427</t>
-        </is>
-      </c>
-      <c r="E229" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F229" s="11" t="inlineStr"/>
-      <c r="G229" s="11" t="inlineStr"/>
-      <c r="H229" s="11" t="inlineStr"/>
-      <c r="I229" s="11" t="inlineStr"/>
-      <c r="J229" s="11" t="inlineStr"/>
-      <c r="K229" s="11" t="inlineStr"/>
-      <c r="L229" s="11" t="inlineStr"/>
-      <c r="M229" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N229" s="11" t="inlineStr"/>
-      <c r="O229" s="11" t="inlineStr"/>
-      <c r="P229" s="11" t="inlineStr"/>
-      <c r="Q229" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R229" s="11" t="inlineStr"/>
-      <c r="S229" s="11" t="inlineStr"/>
-      <c r="T229" s="11" t="inlineStr"/>
-      <c r="U229" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V229" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W229" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="230" ht="26" customHeight="1">
-      <c r="A230" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B230" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C230" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D230" s="11" t="inlineStr">
-        <is>
-          <t>20260276428</t>
-        </is>
-      </c>
-      <c r="E230" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F230" s="11" t="inlineStr"/>
-      <c r="G230" s="11" t="inlineStr"/>
-      <c r="H230" s="11" t="inlineStr"/>
-      <c r="I230" s="11" t="inlineStr"/>
-      <c r="J230" s="11" t="inlineStr"/>
-      <c r="K230" s="11" t="inlineStr"/>
-      <c r="L230" s="11" t="inlineStr"/>
-      <c r="M230" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N230" s="11" t="inlineStr"/>
-      <c r="O230" s="11" t="inlineStr"/>
-      <c r="P230" s="11" t="inlineStr"/>
-      <c r="Q230" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R230" s="11" t="inlineStr"/>
-      <c r="S230" s="11" t="inlineStr"/>
-      <c r="T230" s="11" t="inlineStr"/>
-      <c r="U230" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V230" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W230" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="231" ht="26" customHeight="1">
-      <c r="A231" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B231" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C231" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D231" s="11" t="inlineStr">
-        <is>
-          <t>20260276429</t>
-        </is>
-      </c>
-      <c r="E231" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F231" s="11" t="inlineStr"/>
-      <c r="G231" s="11" t="inlineStr"/>
-      <c r="H231" s="11" t="inlineStr"/>
-      <c r="I231" s="11" t="inlineStr"/>
-      <c r="J231" s="11" t="inlineStr"/>
-      <c r="K231" s="11" t="inlineStr"/>
-      <c r="L231" s="11" t="inlineStr"/>
-      <c r="M231" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N231" s="11" t="inlineStr"/>
-      <c r="O231" s="11" t="inlineStr"/>
-      <c r="P231" s="11" t="inlineStr"/>
-      <c r="Q231" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R231" s="11" t="inlineStr"/>
-      <c r="S231" s="11" t="inlineStr"/>
-      <c r="T231" s="11" t="inlineStr"/>
-      <c r="U231" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V231" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W231" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="232" ht="26" customHeight="1">
-      <c r="A232" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B232" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C232" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D232" s="11" t="inlineStr">
-        <is>
-          <t>20260276430</t>
-        </is>
-      </c>
-      <c r="E232" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F232" s="11" t="inlineStr"/>
-      <c r="G232" s="11" t="inlineStr"/>
-      <c r="H232" s="11" t="inlineStr"/>
-      <c r="I232" s="11" t="inlineStr"/>
-      <c r="J232" s="11" t="inlineStr"/>
-      <c r="K232" s="11" t="inlineStr"/>
-      <c r="L232" s="11" t="inlineStr"/>
-      <c r="M232" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N232" s="11" t="inlineStr"/>
-      <c r="O232" s="11" t="inlineStr"/>
-      <c r="P232" s="11" t="inlineStr"/>
-      <c r="Q232" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R232" s="11" t="inlineStr"/>
-      <c r="S232" s="11" t="inlineStr"/>
-      <c r="T232" s="11" t="inlineStr"/>
-      <c r="U232" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V232" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W232" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="233" ht="26" customHeight="1">
-      <c r="A233" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B233" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C233" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D233" s="11" t="inlineStr">
-        <is>
-          <t>20260276431</t>
-        </is>
-      </c>
-      <c r="E233" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F233" s="11" t="inlineStr"/>
-      <c r="G233" s="11" t="inlineStr"/>
-      <c r="H233" s="11" t="inlineStr"/>
-      <c r="I233" s="11" t="inlineStr"/>
-      <c r="J233" s="11" t="inlineStr"/>
-      <c r="K233" s="11" t="inlineStr"/>
-      <c r="L233" s="11" t="inlineStr"/>
-      <c r="M233" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N233" s="11" t="inlineStr"/>
-      <c r="O233" s="11" t="inlineStr"/>
-      <c r="P233" s="11" t="inlineStr"/>
-      <c r="Q233" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R233" s="11" t="inlineStr"/>
-      <c r="S233" s="11" t="inlineStr"/>
-      <c r="T233" s="11" t="inlineStr"/>
-      <c r="U233" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V233" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W233" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="234" ht="26" customHeight="1">
-      <c r="A234" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B234" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C234" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D234" s="11" t="inlineStr">
-        <is>
-          <t>20260276432</t>
-        </is>
-      </c>
-      <c r="E234" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F234" s="11" t="inlineStr"/>
-      <c r="G234" s="11" t="inlineStr"/>
-      <c r="H234" s="11" t="inlineStr"/>
-      <c r="I234" s="11" t="inlineStr"/>
-      <c r="J234" s="11" t="inlineStr"/>
-      <c r="K234" s="11" t="inlineStr"/>
-      <c r="L234" s="11" t="inlineStr"/>
-      <c r="M234" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N234" s="11" t="inlineStr"/>
-      <c r="O234" s="11" t="inlineStr"/>
-      <c r="P234" s="11" t="inlineStr"/>
-      <c r="Q234" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R234" s="11" t="inlineStr"/>
-      <c r="S234" s="11" t="inlineStr"/>
-      <c r="T234" s="11" t="inlineStr"/>
-      <c r="U234" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V234" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W234" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="235" ht="26" customHeight="1">
-      <c r="A235" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B235" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C235" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D235" s="11" t="inlineStr">
-        <is>
-          <t>20260276434</t>
-        </is>
-      </c>
-      <c r="E235" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F235" s="11" t="inlineStr"/>
-      <c r="G235" s="11" t="inlineStr"/>
-      <c r="H235" s="11" t="inlineStr"/>
-      <c r="I235" s="11" t="inlineStr"/>
-      <c r="J235" s="11" t="inlineStr"/>
-      <c r="K235" s="11" t="inlineStr"/>
-      <c r="L235" s="11" t="inlineStr"/>
-      <c r="M235" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N235" s="11" t="inlineStr"/>
-      <c r="O235" s="11" t="inlineStr"/>
-      <c r="P235" s="11" t="inlineStr"/>
-      <c r="Q235" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R235" s="11" t="inlineStr"/>
-      <c r="S235" s="11" t="inlineStr"/>
-      <c r="T235" s="11" t="inlineStr"/>
-      <c r="U235" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V235" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W235" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="236" ht="26" customHeight="1">
-      <c r="A236" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B236" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C236" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D236" s="11" t="inlineStr">
-        <is>
-          <t>20260276435</t>
-        </is>
-      </c>
-      <c r="E236" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F236" s="11" t="inlineStr"/>
-      <c r="G236" s="11" t="inlineStr"/>
-      <c r="H236" s="11" t="inlineStr"/>
-      <c r="I236" s="11" t="inlineStr"/>
-      <c r="J236" s="11" t="inlineStr"/>
-      <c r="K236" s="11" t="inlineStr"/>
-      <c r="L236" s="11" t="inlineStr"/>
-      <c r="M236" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N236" s="11" t="inlineStr"/>
-      <c r="O236" s="11" t="inlineStr"/>
-      <c r="P236" s="11" t="inlineStr"/>
-      <c r="Q236" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R236" s="11" t="inlineStr"/>
-      <c r="S236" s="11" t="inlineStr"/>
-      <c r="T236" s="11" t="inlineStr"/>
-      <c r="U236" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V236" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W236" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="237" ht="26" customHeight="1">
-      <c r="A237" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B237" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C237" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D237" s="11" t="inlineStr">
-        <is>
-          <t>20260276436</t>
-        </is>
-      </c>
-      <c r="E237" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F237" s="11" t="inlineStr"/>
-      <c r="G237" s="11" t="inlineStr"/>
-      <c r="H237" s="11" t="inlineStr"/>
-      <c r="I237" s="11" t="inlineStr"/>
-      <c r="J237" s="11" t="inlineStr"/>
-      <c r="K237" s="11" t="inlineStr"/>
-      <c r="L237" s="11" t="inlineStr"/>
-      <c r="M237" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N237" s="11" t="inlineStr"/>
-      <c r="O237" s="11" t="inlineStr"/>
-      <c r="P237" s="11" t="inlineStr"/>
-      <c r="Q237" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R237" s="11" t="inlineStr"/>
-      <c r="S237" s="11" t="inlineStr"/>
-      <c r="T237" s="11" t="inlineStr"/>
-      <c r="U237" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V237" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W237" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="238" ht="26" customHeight="1">
-      <c r="A238" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B238" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C238" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D238" s="11" t="inlineStr">
-        <is>
-          <t>20260276437</t>
-        </is>
-      </c>
-      <c r="E238" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F238" s="11" t="inlineStr"/>
-      <c r="G238" s="11" t="inlineStr"/>
-      <c r="H238" s="11" t="inlineStr"/>
-      <c r="I238" s="11" t="inlineStr"/>
-      <c r="J238" s="11" t="inlineStr"/>
-      <c r="K238" s="11" t="inlineStr"/>
-      <c r="L238" s="11" t="inlineStr"/>
-      <c r="M238" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N238" s="11" t="inlineStr"/>
-      <c r="O238" s="11" t="inlineStr"/>
-      <c r="P238" s="11" t="inlineStr"/>
-      <c r="Q238" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R238" s="11" t="inlineStr"/>
-      <c r="S238" s="11" t="inlineStr"/>
-      <c r="T238" s="11" t="inlineStr"/>
-      <c r="U238" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V238" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W238" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="239" ht="26" customHeight="1">
-      <c r="A239" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B239" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C239" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D239" s="11" t="inlineStr">
-        <is>
-          <t>20260276438</t>
-        </is>
-      </c>
-      <c r="E239" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F239" s="11" t="inlineStr"/>
-      <c r="G239" s="11" t="inlineStr"/>
-      <c r="H239" s="11" t="inlineStr"/>
-      <c r="I239" s="11" t="inlineStr"/>
-      <c r="J239" s="11" t="inlineStr"/>
-      <c r="K239" s="11" t="inlineStr"/>
-      <c r="L239" s="11" t="inlineStr"/>
-      <c r="M239" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N239" s="11" t="inlineStr"/>
-      <c r="O239" s="11" t="inlineStr"/>
-      <c r="P239" s="11" t="inlineStr"/>
-      <c r="Q239" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R239" s="11" t="inlineStr"/>
-      <c r="S239" s="11" t="inlineStr"/>
-      <c r="T239" s="11" t="inlineStr"/>
-      <c r="U239" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V239" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W239" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="240" ht="26" customHeight="1">
-      <c r="A240" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B240" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C240" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D240" s="11" t="inlineStr">
-        <is>
-          <t>20260276439</t>
-        </is>
-      </c>
-      <c r="E240" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F240" s="11" t="inlineStr"/>
-      <c r="G240" s="11" t="inlineStr"/>
-      <c r="H240" s="11" t="inlineStr"/>
-      <c r="I240" s="11" t="inlineStr"/>
-      <c r="J240" s="11" t="inlineStr"/>
-      <c r="K240" s="11" t="inlineStr"/>
-      <c r="L240" s="11" t="inlineStr"/>
-      <c r="M240" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N240" s="11" t="inlineStr"/>
-      <c r="O240" s="11" t="inlineStr"/>
-      <c r="P240" s="11" t="inlineStr"/>
-      <c r="Q240" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R240" s="11" t="inlineStr"/>
-      <c r="S240" s="11" t="inlineStr"/>
-      <c r="T240" s="11" t="inlineStr"/>
-      <c r="U240" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V240" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W240" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="241" ht="26" customHeight="1">
-      <c r="A241" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B241" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C241" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D241" s="11" t="inlineStr">
-        <is>
-          <t>20260276440</t>
-        </is>
-      </c>
-      <c r="E241" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F241" s="11" t="inlineStr"/>
-      <c r="G241" s="11" t="inlineStr"/>
-      <c r="H241" s="11" t="inlineStr"/>
-      <c r="I241" s="11" t="inlineStr"/>
-      <c r="J241" s="11" t="inlineStr"/>
-      <c r="K241" s="11" t="inlineStr"/>
-      <c r="L241" s="11" t="inlineStr"/>
-      <c r="M241" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N241" s="11" t="inlineStr"/>
-      <c r="O241" s="11" t="inlineStr"/>
-      <c r="P241" s="11" t="inlineStr"/>
-      <c r="Q241" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R241" s="11" t="inlineStr"/>
-      <c r="S241" s="11" t="inlineStr"/>
-      <c r="T241" s="11" t="inlineStr"/>
-      <c r="U241" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V241" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W241" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="242" ht="26" customHeight="1">
-      <c r="A242" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B242" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C242" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D242" s="11" t="inlineStr">
-        <is>
-          <t>20260276441</t>
-        </is>
-      </c>
-      <c r="E242" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F242" s="11" t="inlineStr"/>
-      <c r="G242" s="11" t="inlineStr"/>
-      <c r="H242" s="11" t="inlineStr"/>
-      <c r="I242" s="11" t="inlineStr"/>
-      <c r="J242" s="11" t="inlineStr"/>
-      <c r="K242" s="11" t="inlineStr"/>
-      <c r="L242" s="11" t="inlineStr"/>
-      <c r="M242" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N242" s="11" t="inlineStr"/>
-      <c r="O242" s="11" t="inlineStr"/>
-      <c r="P242" s="11" t="inlineStr"/>
-      <c r="Q242" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R242" s="11" t="inlineStr"/>
-      <c r="S242" s="11" t="inlineStr"/>
-      <c r="T242" s="11" t="inlineStr"/>
-      <c r="U242" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V242" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W242" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="243" ht="26" customHeight="1">
-      <c r="A243" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B243" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C243" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D243" s="11" t="inlineStr">
-        <is>
-          <t>20260276442</t>
-        </is>
-      </c>
-      <c r="E243" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F243" s="11" t="inlineStr"/>
-      <c r="G243" s="11" t="inlineStr"/>
-      <c r="H243" s="11" t="inlineStr"/>
-      <c r="I243" s="11" t="inlineStr"/>
-      <c r="J243" s="11" t="inlineStr"/>
-      <c r="K243" s="11" t="inlineStr"/>
-      <c r="L243" s="11" t="inlineStr"/>
-      <c r="M243" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N243" s="11" t="inlineStr"/>
-      <c r="O243" s="11" t="inlineStr"/>
-      <c r="P243" s="11" t="inlineStr"/>
-      <c r="Q243" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R243" s="11" t="inlineStr"/>
-      <c r="S243" s="11" t="inlineStr"/>
-      <c r="T243" s="11" t="inlineStr"/>
-      <c r="U243" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V243" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W243" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="244" ht="26" customHeight="1">
-      <c r="A244" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B244" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C244" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D244" s="11" t="inlineStr">
-        <is>
-          <t>20260276443</t>
-        </is>
-      </c>
-      <c r="E244" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F244" s="11" t="inlineStr"/>
-      <c r="G244" s="11" t="inlineStr"/>
-      <c r="H244" s="11" t="inlineStr"/>
-      <c r="I244" s="11" t="inlineStr"/>
-      <c r="J244" s="11" t="inlineStr"/>
-      <c r="K244" s="11" t="inlineStr"/>
-      <c r="L244" s="11" t="inlineStr"/>
-      <c r="M244" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N244" s="11" t="inlineStr"/>
-      <c r="O244" s="11" t="inlineStr"/>
-      <c r="P244" s="11" t="inlineStr"/>
-      <c r="Q244" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R244" s="11" t="inlineStr"/>
-      <c r="S244" s="11" t="inlineStr"/>
-      <c r="T244" s="11" t="inlineStr"/>
-      <c r="U244" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V244" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W244" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="245" ht="26" customHeight="1">
-      <c r="A245" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B245" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C245" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D245" s="11" t="inlineStr">
-        <is>
-          <t>20260276444</t>
-        </is>
-      </c>
-      <c r="E245" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F245" s="11" t="inlineStr"/>
-      <c r="G245" s="11" t="inlineStr"/>
-      <c r="H245" s="11" t="inlineStr"/>
-      <c r="I245" s="11" t="inlineStr"/>
-      <c r="J245" s="11" t="inlineStr"/>
-      <c r="K245" s="11" t="inlineStr"/>
-      <c r="L245" s="11" t="inlineStr"/>
-      <c r="M245" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N245" s="11" t="inlineStr"/>
-      <c r="O245" s="11" t="inlineStr"/>
-      <c r="P245" s="11" t="inlineStr"/>
-      <c r="Q245" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R245" s="11" t="inlineStr"/>
-      <c r="S245" s="11" t="inlineStr"/>
-      <c r="T245" s="11" t="inlineStr"/>
-      <c r="U245" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V245" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W245" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="246" ht="26" customHeight="1">
-      <c r="A246" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B246" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C246" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D246" s="11" t="inlineStr">
-        <is>
-          <t>20260276687</t>
-        </is>
-      </c>
-      <c r="E246" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F246" s="11" t="inlineStr"/>
-      <c r="G246" s="11" t="inlineStr"/>
-      <c r="H246" s="11" t="inlineStr"/>
-      <c r="I246" s="11" t="inlineStr"/>
-      <c r="J246" s="11" t="inlineStr"/>
-      <c r="K246" s="11" t="inlineStr"/>
-      <c r="L246" s="11" t="inlineStr"/>
-      <c r="M246" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N246" s="11" t="inlineStr"/>
-      <c r="O246" s="11" t="inlineStr"/>
-      <c r="P246" s="11" t="inlineStr"/>
-      <c r="Q246" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R246" s="11" t="inlineStr"/>
-      <c r="S246" s="11" t="inlineStr"/>
-      <c r="T246" s="11" t="inlineStr"/>
-      <c r="U246" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V246" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W246" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="247" ht="26" customHeight="1">
-      <c r="A247" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B247" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C247" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D247" s="11" t="inlineStr">
-        <is>
-          <t>20260276688</t>
-        </is>
-      </c>
-      <c r="E247" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F247" s="11" t="inlineStr"/>
-      <c r="G247" s="11" t="inlineStr"/>
-      <c r="H247" s="11" t="inlineStr"/>
-      <c r="I247" s="11" t="inlineStr"/>
-      <c r="J247" s="11" t="inlineStr"/>
-      <c r="K247" s="11" t="inlineStr"/>
-      <c r="L247" s="11" t="inlineStr"/>
-      <c r="M247" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N247" s="11" t="inlineStr"/>
-      <c r="O247" s="11" t="inlineStr"/>
-      <c r="P247" s="11" t="inlineStr"/>
-      <c r="Q247" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R247" s="11" t="inlineStr"/>
-      <c r="S247" s="11" t="inlineStr"/>
-      <c r="T247" s="11" t="inlineStr"/>
-      <c r="U247" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V247" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W247" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="248" ht="26" customHeight="1">
-      <c r="A248" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B248" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C248" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D248" s="11" t="inlineStr">
-        <is>
-          <t>20260276689</t>
-        </is>
-      </c>
-      <c r="E248" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F248" s="11" t="inlineStr"/>
-      <c r="G248" s="11" t="inlineStr"/>
-      <c r="H248" s="11" t="inlineStr"/>
-      <c r="I248" s="11" t="inlineStr"/>
-      <c r="J248" s="11" t="inlineStr"/>
-      <c r="K248" s="11" t="inlineStr"/>
-      <c r="L248" s="11" t="inlineStr"/>
-      <c r="M248" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N248" s="11" t="inlineStr"/>
-      <c r="O248" s="11" t="inlineStr"/>
-      <c r="P248" s="11" t="inlineStr"/>
-      <c r="Q248" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R248" s="11" t="inlineStr"/>
-      <c r="S248" s="11" t="inlineStr"/>
-      <c r="T248" s="11" t="inlineStr"/>
-      <c r="U248" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V248" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W248" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="249" ht="26" customHeight="1">
-      <c r="A249" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B249" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C249" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D249" s="11" t="inlineStr">
-        <is>
-          <t>20260276690</t>
-        </is>
-      </c>
-      <c r="E249" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F249" s="11" t="inlineStr"/>
-      <c r="G249" s="11" t="inlineStr"/>
-      <c r="H249" s="11" t="inlineStr"/>
-      <c r="I249" s="11" t="inlineStr"/>
-      <c r="J249" s="11" t="inlineStr"/>
-      <c r="K249" s="11" t="inlineStr"/>
-      <c r="L249" s="11" t="inlineStr"/>
-      <c r="M249" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N249" s="11" t="inlineStr"/>
-      <c r="O249" s="11" t="inlineStr"/>
-      <c r="P249" s="11" t="inlineStr"/>
-      <c r="Q249" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R249" s="11" t="inlineStr"/>
-      <c r="S249" s="11" t="inlineStr"/>
-      <c r="T249" s="11" t="inlineStr"/>
-      <c r="U249" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V249" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W249" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="250" ht="26" customHeight="1">
-      <c r="A250" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B250" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C250" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D250" s="11" t="inlineStr">
-        <is>
-          <t>20260276692</t>
-        </is>
-      </c>
-      <c r="E250" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F250" s="11" t="inlineStr"/>
-      <c r="G250" s="11" t="inlineStr"/>
-      <c r="H250" s="11" t="inlineStr"/>
-      <c r="I250" s="11" t="inlineStr"/>
-      <c r="J250" s="11" t="inlineStr"/>
-      <c r="K250" s="11" t="inlineStr"/>
-      <c r="L250" s="11" t="inlineStr"/>
-      <c r="M250" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N250" s="11" t="inlineStr"/>
-      <c r="O250" s="11" t="inlineStr"/>
-      <c r="P250" s="11" t="inlineStr"/>
-      <c r="Q250" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R250" s="11" t="inlineStr"/>
-      <c r="S250" s="11" t="inlineStr"/>
-      <c r="T250" s="11" t="inlineStr"/>
-      <c r="U250" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V250" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W250" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="251" ht="26" customHeight="1">
-      <c r="A251" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B251" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C251" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D251" s="11" t="inlineStr">
-        <is>
-          <t>20260276696</t>
-        </is>
-      </c>
-      <c r="E251" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F251" s="11" t="inlineStr"/>
-      <c r="G251" s="11" t="inlineStr"/>
-      <c r="H251" s="11" t="inlineStr"/>
-      <c r="I251" s="11" t="inlineStr"/>
-      <c r="J251" s="11" t="inlineStr"/>
-      <c r="K251" s="11" t="inlineStr"/>
-      <c r="L251" s="11" t="inlineStr"/>
-      <c r="M251" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N251" s="11" t="inlineStr"/>
-      <c r="O251" s="11" t="inlineStr"/>
-      <c r="P251" s="11" t="inlineStr"/>
-      <c r="Q251" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R251" s="11" t="inlineStr"/>
-      <c r="S251" s="11" t="inlineStr"/>
-      <c r="T251" s="11" t="inlineStr"/>
-      <c r="U251" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V251" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W251" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="252" ht="26" customHeight="1">
-      <c r="A252" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B252" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C252" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D252" s="11" t="inlineStr">
-        <is>
-          <t>20260276697</t>
-        </is>
-      </c>
-      <c r="E252" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F252" s="11" t="inlineStr"/>
-      <c r="G252" s="11" t="inlineStr"/>
-      <c r="H252" s="11" t="inlineStr"/>
-      <c r="I252" s="11" t="inlineStr"/>
-      <c r="J252" s="11" t="inlineStr"/>
-      <c r="K252" s="11" t="inlineStr"/>
-      <c r="L252" s="11" t="inlineStr"/>
-      <c r="M252" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N252" s="11" t="inlineStr"/>
-      <c r="O252" s="11" t="inlineStr"/>
-      <c r="P252" s="11" t="inlineStr"/>
-      <c r="Q252" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R252" s="11" t="inlineStr"/>
-      <c r="S252" s="11" t="inlineStr"/>
-      <c r="T252" s="11" t="inlineStr"/>
-      <c r="U252" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V252" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W252" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="253" ht="26" customHeight="1">
-      <c r="A253" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B253" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C253" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D253" s="11" t="inlineStr">
-        <is>
-          <t>20260276698</t>
-        </is>
-      </c>
-      <c r="E253" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F253" s="11" t="inlineStr"/>
-      <c r="G253" s="11" t="inlineStr"/>
-      <c r="H253" s="11" t="inlineStr"/>
-      <c r="I253" s="11" t="inlineStr"/>
-      <c r="J253" s="11" t="inlineStr"/>
-      <c r="K253" s="11" t="inlineStr"/>
-      <c r="L253" s="11" t="inlineStr"/>
-      <c r="M253" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N253" s="11" t="inlineStr"/>
-      <c r="O253" s="11" t="inlineStr"/>
-      <c r="P253" s="11" t="inlineStr"/>
-      <c r="Q253" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R253" s="11" t="inlineStr"/>
-      <c r="S253" s="11" t="inlineStr"/>
-      <c r="T253" s="11" t="inlineStr"/>
-      <c r="U253" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V253" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W253" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="254" ht="26" customHeight="1">
-      <c r="A254" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B254" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C254" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D254" s="11" t="inlineStr">
-        <is>
-          <t>20260276700</t>
-        </is>
-      </c>
-      <c r="E254" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F254" s="11" t="inlineStr"/>
-      <c r="G254" s="11" t="inlineStr"/>
-      <c r="H254" s="11" t="inlineStr"/>
-      <c r="I254" s="11" t="inlineStr"/>
-      <c r="J254" s="11" t="inlineStr"/>
-      <c r="K254" s="11" t="inlineStr"/>
-      <c r="L254" s="11" t="inlineStr"/>
-      <c r="M254" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N254" s="11" t="inlineStr"/>
-      <c r="O254" s="11" t="inlineStr"/>
-      <c r="P254" s="11" t="inlineStr"/>
-      <c r="Q254" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R254" s="11" t="inlineStr"/>
-      <c r="S254" s="11" t="inlineStr"/>
-      <c r="T254" s="11" t="inlineStr"/>
-      <c r="U254" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V254" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W254" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="255" ht="26" customHeight="1">
-      <c r="A255" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B255" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C255" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D255" s="11" t="inlineStr">
-        <is>
-          <t>20260276701</t>
-        </is>
-      </c>
-      <c r="E255" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F255" s="11" t="inlineStr"/>
-      <c r="G255" s="11" t="inlineStr"/>
-      <c r="H255" s="11" t="inlineStr"/>
-      <c r="I255" s="11" t="inlineStr"/>
-      <c r="J255" s="11" t="inlineStr"/>
-      <c r="K255" s="11" t="inlineStr"/>
-      <c r="L255" s="11" t="inlineStr"/>
-      <c r="M255" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N255" s="11" t="inlineStr"/>
-      <c r="O255" s="11" t="inlineStr"/>
-      <c r="P255" s="11" t="inlineStr"/>
-      <c r="Q255" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R255" s="11" t="inlineStr"/>
-      <c r="S255" s="11" t="inlineStr"/>
-      <c r="T255" s="11" t="inlineStr"/>
-      <c r="U255" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V255" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W255" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="256" ht="26" customHeight="1">
-      <c r="A256" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B256" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C256" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D256" s="11" t="inlineStr">
-        <is>
-          <t>20260276702</t>
-        </is>
-      </c>
-      <c r="E256" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F256" s="11" t="inlineStr"/>
-      <c r="G256" s="11" t="inlineStr"/>
-      <c r="H256" s="11" t="inlineStr"/>
-      <c r="I256" s="11" t="inlineStr"/>
-      <c r="J256" s="11" t="inlineStr"/>
-      <c r="K256" s="11" t="inlineStr"/>
-      <c r="L256" s="11" t="inlineStr"/>
-      <c r="M256" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N256" s="11" t="inlineStr"/>
-      <c r="O256" s="11" t="inlineStr"/>
-      <c r="P256" s="11" t="inlineStr"/>
-      <c r="Q256" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R256" s="11" t="inlineStr"/>
-      <c r="S256" s="11" t="inlineStr"/>
-      <c r="T256" s="11" t="inlineStr"/>
-      <c r="U256" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V256" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W256" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="26" customHeight="1">
-      <c r="A257" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B257" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C257" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D257" s="11" t="inlineStr">
-        <is>
-          <t>20260276703</t>
-        </is>
-      </c>
-      <c r="E257" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F257" s="11" t="inlineStr"/>
-      <c r="G257" s="11" t="inlineStr"/>
-      <c r="H257" s="11" t="inlineStr"/>
-      <c r="I257" s="11" t="inlineStr"/>
-      <c r="J257" s="11" t="inlineStr"/>
-      <c r="K257" s="11" t="inlineStr"/>
-      <c r="L257" s="11" t="inlineStr"/>
-      <c r="M257" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N257" s="11" t="inlineStr"/>
-      <c r="O257" s="11" t="inlineStr"/>
-      <c r="P257" s="11" t="inlineStr"/>
-      <c r="Q257" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R257" s="11" t="inlineStr"/>
-      <c r="S257" s="11" t="inlineStr"/>
-      <c r="T257" s="11" t="inlineStr"/>
-      <c r="U257" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V257" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W257" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="258" ht="26" customHeight="1">
-      <c r="A258" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B258" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C258" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D258" s="11" t="inlineStr">
-        <is>
-          <t>20260276704</t>
-        </is>
-      </c>
-      <c r="E258" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F258" s="11" t="inlineStr"/>
-      <c r="G258" s="11" t="inlineStr"/>
-      <c r="H258" s="11" t="inlineStr"/>
-      <c r="I258" s="11" t="inlineStr"/>
-      <c r="J258" s="11" t="inlineStr"/>
-      <c r="K258" s="11" t="inlineStr"/>
-      <c r="L258" s="11" t="inlineStr"/>
-      <c r="M258" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N258" s="11" t="inlineStr"/>
-      <c r="O258" s="11" t="inlineStr"/>
-      <c r="P258" s="11" t="inlineStr"/>
-      <c r="Q258" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R258" s="11" t="inlineStr"/>
-      <c r="S258" s="11" t="inlineStr"/>
-      <c r="T258" s="11" t="inlineStr"/>
-      <c r="U258" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V258" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W258" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="259" ht="26" customHeight="1">
-      <c r="A259" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B259" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C259" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D259" s="11" t="inlineStr">
-        <is>
-          <t>20260276705</t>
-        </is>
-      </c>
-      <c r="E259" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F259" s="11" t="inlineStr"/>
-      <c r="G259" s="11" t="inlineStr"/>
-      <c r="H259" s="11" t="inlineStr"/>
-      <c r="I259" s="11" t="inlineStr"/>
-      <c r="J259" s="11" t="inlineStr"/>
-      <c r="K259" s="11" t="inlineStr"/>
-      <c r="L259" s="11" t="inlineStr"/>
-      <c r="M259" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N259" s="11" t="inlineStr"/>
-      <c r="O259" s="11" t="inlineStr"/>
-      <c r="P259" s="11" t="inlineStr"/>
-      <c r="Q259" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R259" s="11" t="inlineStr"/>
-      <c r="S259" s="11" t="inlineStr"/>
-      <c r="T259" s="11" t="inlineStr"/>
-      <c r="U259" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V259" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W259" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="260" ht="26" customHeight="1">
-      <c r="A260" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B260" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C260" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D260" s="11" t="inlineStr">
-        <is>
-          <t>20260276706</t>
-        </is>
-      </c>
-      <c r="E260" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F260" s="11" t="inlineStr"/>
-      <c r="G260" s="11" t="inlineStr"/>
-      <c r="H260" s="11" t="inlineStr"/>
-      <c r="I260" s="11" t="inlineStr"/>
-      <c r="J260" s="11" t="inlineStr"/>
-      <c r="K260" s="11" t="inlineStr"/>
-      <c r="L260" s="11" t="inlineStr"/>
-      <c r="M260" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N260" s="11" t="inlineStr"/>
-      <c r="O260" s="11" t="inlineStr"/>
-      <c r="P260" s="11" t="inlineStr"/>
-      <c r="Q260" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R260" s="11" t="inlineStr"/>
-      <c r="S260" s="11" t="inlineStr"/>
-      <c r="T260" s="11" t="inlineStr"/>
-      <c r="U260" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V260" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W260" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="261" ht="26" customHeight="1">
-      <c r="A261" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B261" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C261" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D261" s="11" t="inlineStr">
-        <is>
-          <t>20260276709</t>
-        </is>
-      </c>
-      <c r="E261" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F261" s="11" t="inlineStr"/>
-      <c r="G261" s="11" t="inlineStr"/>
-      <c r="H261" s="11" t="inlineStr"/>
-      <c r="I261" s="11" t="inlineStr"/>
-      <c r="J261" s="11" t="inlineStr"/>
-      <c r="K261" s="11" t="inlineStr"/>
-      <c r="L261" s="11" t="inlineStr"/>
-      <c r="M261" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N261" s="11" t="inlineStr"/>
-      <c r="O261" s="11" t="inlineStr"/>
-      <c r="P261" s="11" t="inlineStr"/>
-      <c r="Q261" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R261" s="11" t="inlineStr"/>
-      <c r="S261" s="11" t="inlineStr"/>
-      <c r="T261" s="11" t="inlineStr"/>
-      <c r="U261" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V261" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W261" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="262" ht="26" customHeight="1">
-      <c r="A262" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B262" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C262" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D262" s="11" t="inlineStr">
-        <is>
-          <t>20260276710</t>
-        </is>
-      </c>
-      <c r="E262" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F262" s="11" t="inlineStr"/>
-      <c r="G262" s="11" t="inlineStr"/>
-      <c r="H262" s="11" t="inlineStr"/>
-      <c r="I262" s="11" t="inlineStr"/>
-      <c r="J262" s="11" t="inlineStr"/>
-      <c r="K262" s="11" t="inlineStr"/>
-      <c r="L262" s="11" t="inlineStr"/>
-      <c r="M262" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N262" s="11" t="inlineStr"/>
-      <c r="O262" s="11" t="inlineStr"/>
-      <c r="P262" s="11" t="inlineStr"/>
-      <c r="Q262" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R262" s="11" t="inlineStr"/>
-      <c r="S262" s="11" t="inlineStr"/>
-      <c r="T262" s="11" t="inlineStr"/>
-      <c r="U262" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V262" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W262" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="263" ht="26" customHeight="1">
-      <c r="A263" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B263" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C263" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D263" s="11" t="inlineStr">
-        <is>
-          <t>20260276711</t>
-        </is>
-      </c>
-      <c r="E263" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F263" s="11" t="inlineStr"/>
-      <c r="G263" s="11" t="inlineStr"/>
-      <c r="H263" s="11" t="inlineStr"/>
-      <c r="I263" s="11" t="inlineStr"/>
-      <c r="J263" s="11" t="inlineStr"/>
-      <c r="K263" s="11" t="inlineStr"/>
-      <c r="L263" s="11" t="inlineStr"/>
-      <c r="M263" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N263" s="11" t="inlineStr"/>
-      <c r="O263" s="11" t="inlineStr"/>
-      <c r="P263" s="11" t="inlineStr"/>
-      <c r="Q263" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R263" s="11" t="inlineStr"/>
-      <c r="S263" s="11" t="inlineStr"/>
-      <c r="T263" s="11" t="inlineStr"/>
-      <c r="U263" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V263" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W263" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="264" ht="26" customHeight="1">
-      <c r="A264" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B264" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C264" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D264" s="11" t="inlineStr">
-        <is>
-          <t>20260276712</t>
-        </is>
-      </c>
-      <c r="E264" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F264" s="11" t="inlineStr"/>
-      <c r="G264" s="11" t="inlineStr"/>
-      <c r="H264" s="11" t="inlineStr"/>
-      <c r="I264" s="11" t="inlineStr"/>
-      <c r="J264" s="11" t="inlineStr"/>
-      <c r="K264" s="11" t="inlineStr"/>
-      <c r="L264" s="11" t="inlineStr"/>
-      <c r="M264" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N264" s="11" t="inlineStr"/>
-      <c r="O264" s="11" t="inlineStr"/>
-      <c r="P264" s="11" t="inlineStr"/>
-      <c r="Q264" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R264" s="11" t="inlineStr"/>
-      <c r="S264" s="11" t="inlineStr"/>
-      <c r="T264" s="11" t="inlineStr"/>
-      <c r="U264" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V264" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W264" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="265" ht="26" customHeight="1">
-      <c r="A265" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B265" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C265" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D265" s="11" t="inlineStr">
-        <is>
-          <t>20260276770</t>
-        </is>
-      </c>
-      <c r="E265" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F265" s="11" t="inlineStr"/>
-      <c r="G265" s="11" t="inlineStr"/>
-      <c r="H265" s="11" t="inlineStr"/>
-      <c r="I265" s="11" t="inlineStr"/>
-      <c r="J265" s="11" t="inlineStr"/>
-      <c r="K265" s="11" t="inlineStr"/>
-      <c r="L265" s="11" t="inlineStr"/>
-      <c r="M265" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N265" s="11" t="inlineStr"/>
-      <c r="O265" s="11" t="inlineStr"/>
-      <c r="P265" s="11" t="inlineStr"/>
-      <c r="Q265" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R265" s="11" t="inlineStr"/>
-      <c r="S265" s="11" t="inlineStr"/>
-      <c r="T265" s="11" t="inlineStr"/>
-      <c r="U265" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V265" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W265" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="266" ht="26" customHeight="1">
-      <c r="A266" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B266" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C266" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D266" s="11" t="inlineStr">
-        <is>
-          <t>20260276797</t>
-        </is>
-      </c>
-      <c r="E266" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F266" s="11" t="inlineStr"/>
-      <c r="G266" s="11" t="inlineStr"/>
-      <c r="H266" s="11" t="inlineStr"/>
-      <c r="I266" s="11" t="inlineStr"/>
-      <c r="J266" s="11" t="inlineStr"/>
-      <c r="K266" s="11" t="inlineStr"/>
-      <c r="L266" s="11" t="inlineStr"/>
-      <c r="M266" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N266" s="11" t="inlineStr"/>
-      <c r="O266" s="11" t="inlineStr"/>
-      <c r="P266" s="11" t="inlineStr"/>
-      <c r="Q266" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R266" s="11" t="inlineStr"/>
-      <c r="S266" s="11" t="inlineStr"/>
-      <c r="T266" s="11" t="inlineStr"/>
-      <c r="U266" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V266" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W266" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="267" ht="26" customHeight="1">
-      <c r="A267" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B267" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C267" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D267" s="11" t="inlineStr">
-        <is>
-          <t>20260276827</t>
-        </is>
-      </c>
-      <c r="E267" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-07</t>
-        </is>
-      </c>
-      <c r="F267" s="11" t="inlineStr"/>
-      <c r="G267" s="11" t="inlineStr"/>
-      <c r="H267" s="11" t="inlineStr"/>
-      <c r="I267" s="11" t="inlineStr"/>
-      <c r="J267" s="11" t="inlineStr"/>
-      <c r="K267" s="11" t="inlineStr"/>
-      <c r="L267" s="11" t="inlineStr"/>
-      <c r="M267" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N267" s="11" t="inlineStr"/>
-      <c r="O267" s="11" t="inlineStr"/>
-      <c r="P267" s="11" t="inlineStr"/>
-      <c r="Q267" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R267" s="11" t="inlineStr"/>
-      <c r="S267" s="11" t="inlineStr"/>
-      <c r="T267" s="11" t="inlineStr"/>
-      <c r="U267" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V267" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W267" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W267"/>
+  <autoFilter ref="A1:W227"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
@@ -18338,46 +16032,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W225" r:id="rId224"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W226" r:id="rId225"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W227" r:id="rId226"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W228" r:id="rId227"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W229" r:id="rId228"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W230" r:id="rId229"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W231" r:id="rId230"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W232" r:id="rId231"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W233" r:id="rId232"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W234" r:id="rId233"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W235" r:id="rId234"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W236" r:id="rId235"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W237" r:id="rId236"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W238" r:id="rId237"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W239" r:id="rId238"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W240" r:id="rId239"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W241" r:id="rId240"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W242" r:id="rId241"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W243" r:id="rId242"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W244" r:id="rId243"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W245" r:id="rId244"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W246" r:id="rId245"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W247" r:id="rId246"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W248" r:id="rId247"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W249" r:id="rId248"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W250" r:id="rId249"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W251" r:id="rId250"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W252" r:id="rId251"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W253" r:id="rId252"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W254" r:id="rId253"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W255" r:id="rId254"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W256" r:id="rId255"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W257" r:id="rId256"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W258" r:id="rId257"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W259" r:id="rId258"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W260" r:id="rId259"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W261" r:id="rId260"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W262" r:id="rId261"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W263" r:id="rId262"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W264" r:id="rId263"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W265" r:id="rId264"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W266" r:id="rId265"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W267" r:id="rId266"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18406,7 +16060,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-05-08 07:12</t>
+          <t>Run: 2026-05-09 04:29</t>
         </is>
       </c>
     </row>
@@ -18421,7 +16075,7 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>266</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5">
@@ -18431,7 +16085,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -18451,7 +16105,7 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="8">
@@ -18461,7 +16115,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -18471,7 +16125,7 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -18497,7 +16151,7 @@
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>128</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -18507,7 +16161,7 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -18517,7 +16171,7 @@
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15">
@@ -18527,7 +16181,7 @@
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -18537,13 +16191,13 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="B17" s="14" t="n">
@@ -18557,17 +16211,17 @@
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-05-10 04:43</t>
+          <t>Run: 2026-05-11 04:57</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$193</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$223</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -174,6 +174,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -544,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W193"/>
+  <dimension ref="A1:W223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -705,26 +708,26 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>20260290801</t>
+          <t>20260292422</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>DAVID ANDRAE DE LA O AND VALERIE P DE LA O</t>
+          <t>STEVEN M. TIERNO</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>MidFirst Bank</t>
+          <t>ROCKET MORTGAGE, LLC S/B/M TO NATIONSTAR MORTGAGE LLC</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>466396</v>
+        <v>143355</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -738,12 +741,12 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>12614 W ALEGRE DR</t>
+          <t>1605 WEST HAZELWOOD STREET</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>LITCHFIELD PARK</t>
+          <t>PHOENIX</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -753,7 +756,7 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>85340</t>
+          <t>85015</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
@@ -764,14 +767,10 @@
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>508-07-495</t>
-        </is>
-      </c>
+      <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>Larry O. Folks</t>
+          <t>America West Lender Services, LLC</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -806,45 +805,57 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>20260290803</t>
+          <t>20260292825</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Fred Lembo and Sylvana Lembo</t>
+          <t>PHILLIP ANDREW SUCHOCKI</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Chase Bank, NA as successor by merger to Leonard J. McDonald</t>
+          <t>Freedom Mortgage Corporation</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>484350</v>
+        <v>493436</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>4430 N 22nd St Apt 5</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>3935 EAST GREENWAY ROAD APARTMENT 250</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>85032</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
@@ -855,12 +866,12 @@
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>163-31-2313</t>
+          <t>143-26-33612</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>JPMorgan Chase Bank, NA as successor by merger to Leonard J. McDonald</t>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -895,40 +906,40 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>20260290818</t>
+          <t>20260293166</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>April E Alvarez and Travis Clem</t>
+          <t>ROY CARINO, SINGLE MAN</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>U.S. Bank National Association Leonard J. McDonald</t>
+          <t>Freedom Mortgage Corporation</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>319113</v>
+        <v>263415</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2766 S Arroyo Ln</t>
+          <t>14300 W BELL RD UNIT 310</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
@@ -948,12 +959,12 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>309-29-5100</t>
+          <t>503-98-800</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>U.S. Bank National Association Leonard J. McDonald</t>
+          <t>(</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -988,30 +999,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>20260291258</t>
+          <t>20260293563</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>ARON RAMIREZ</t>
+          <t>Dancor Investment Holdings, LLC, an Arizona limited liability company</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>PennyMac Loan Services, LLC</t>
+          <t>Kayak Capital, LLC, an Arizona limited liability company</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>381900</v>
+        <v>250000</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1021,12 +1032,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>11570 W LEVI DR</t>
+          <t>16150 N. Arrowhead Fountain Centers Dr. #283</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>AVONDALE</t>
+          <t>Peoria</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -1036,7 +1047,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>85323</t>
+          <t>85382</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr"/>
@@ -1049,17 +1060,17 @@
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>500-67-135</t>
+          <t>153-15-096</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>MTC Financial Inc. dba Trustee Corps</t>
+          <t>Tolesoaz Corp. d/b/a Total Lender Solutions, an AZ Corp.</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
@@ -1089,36 +1100,40 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>20260291578</t>
+          <t>20260294316</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Realty</t>
+          <t>AARON COLLINS</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Credit Union West Leonard J. McDonald</t>
+          <t>Planet Home Lending, LLC</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>108000</v>
+        <v>315000</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr"/>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>4743 South 36th Dr</t>
+          <t>10947 EAST SYLVAN AVENUE</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr"/>
@@ -1138,14 +1153,10 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>105-69-0474</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
-        <is>
-          <t>Credit Union West Leonard J. McDonald</t>
-        </is>
-      </c>
+          <t>312-08-367</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr"/>
       <c r="U6" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -1178,40 +1189,36 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>20260291588</t>
+          <t>20260294428</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Edgar Hernandez</t>
+          <t>Robin R. Roberts and Debra L. Roberts</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Rocket Mortgage, LLC f/k/a Quicken Loans, LLC Leonard J. McDonald</t>
+          <t>Federal Home Loan Mortgage Corporation as Trustee Current Trustee:</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>195000</v>
+        <v>205000</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
-        </is>
-      </c>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>16631 W Taylor St</t>
+          <t>3810 W Sunnyside Ave</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
@@ -1231,12 +1238,12 @@
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>500-89-0998</t>
+          <t>149-33-0307</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Rocket Mortgage, LLC f/k/a Quicken Loans, LLC Leonard J. McDonald</t>
+          <t>for Freddie Mac Seasoned Credit Risk Transfer Trust, Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1271,30 +1278,30 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>20260291606</t>
+          <t>20260294509</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Keegan James McManus</t>
+          <t>MICHAEL BEASLEY AND AMBER BEASLEY</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Village Capital &amp; Investment LLC Leonard J. McDonald</t>
+          <t>New American Funding, LLC FKA Broker Solutions Inc. dba New American Funding</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>383368</v>
+        <v>412392</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1304,7 +1311,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>814 West Temple Street</t>
+          <t>5310 W BECKER LN</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
@@ -1324,12 +1331,12 @@
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>302-42-2793</t>
+          <t>148-26-0418</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Village Capital &amp; Investment LLC Leonard J. McDonald</t>
+          <t>Bradford E. Klein, a member of the State Bar of</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1364,40 +1371,40 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>20260291616</t>
+          <t>20260294633</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>Juan Rivera Jimenez</t>
+          <t>EVELIO R. MARTIN CHAVEZ, A UNMARRIED MAN AND IBET HORTA CLAVEL</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Lakeview Loan Servicing, LLC</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>279837</v>
+        <v>392755</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>Superior Court Building. Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>415 W GROVE ST</t>
+          <t>1412 S 120Th Dr</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr"/>
@@ -1417,12 +1424,12 @@
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>113-38-019</t>
+          <t>500-31-490</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Vylla Solutions, LLC</t>
+          <t>Michelle R. Ghidotti, Esq.</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1457,45 +1464,57 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>20260291628</t>
+          <t>20260294658</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Mare Gootman</t>
+          <t>CLAUDIA I. PADILLA</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>Lakeview Loan Servicing, LLC, By LoanCare, LLC, As Attorney In Fact Under A Limited Power of</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>119000</v>
+        <v>256810</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr"/>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>6735 E Juniper St</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>2017 EELMWOOD ST</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N10" s="3" t="inlineStr"/>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>85213</t>
+        </is>
+      </c>
       <c r="O10" s="3" t="inlineStr"/>
       <c r="P10" s="3" t="inlineStr"/>
       <c r="Q10" s="3" t="inlineStr">
@@ -1506,12 +1525,12 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>141-65-9279</t>
+          <t>140-08-0440</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>Erin K. Sweeney, a member of the State Bar of</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1546,57 +1565,49 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>20260291808</t>
+          <t>20260294938</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>KELLY N. COLE, TRUSTEE OF THE KELLY N. COLE TRUST UNDER AGREEMENT</t>
+          <t>Marieze Z Cole, and Danielle D Cole</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>NEWREZ LLC</t>
+          <t>Freedom Mortgage Corporation</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>151000</v>
+        <v>348392</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>4406 N 126TH DRIVE</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>LITCHFIELD PARK</t>
-        </is>
-      </c>
+          <t>18157 W. DIANA AVENUE</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>85340</t>
-        </is>
-      </c>
+      <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr"/>
       <c r="Q11" s="3" t="inlineStr">
@@ -1605,11 +1616,19 @@
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
-      <c r="T11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>502-09-8756</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>(</t>
+        </is>
+      </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
@@ -1639,45 +1658,45 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>20260291896</t>
+          <t>20260295362</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>REBECCA ANN STEWART AND CHARLES SPENCER FAHERTY, WIFE AND HUSBAND AS</t>
+          <t>CINDY M CORRAL</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>NEWREZ LLC</t>
+          <t>Freedom Mortgage Corporation</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>447700</v>
+        <v>473259</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>10416 E EDGEWOOD AVE</t>
+          <t>12540 W TRUMBULL RD</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>MESA</t>
+          <t>AVONDALE</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1687,7 +1706,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>85208</t>
+          <t>85323</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr"/>
@@ -1698,10 +1717,14 @@
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>500-72-13512</t>
+        </is>
+      </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Prime Recon LLC</t>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1721,231 +1744,291 @@
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="A13" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>20260291073</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>dated September 1, 2004</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>an Arizona limited liability company</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>1375000</v>
-      </c>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr"/>
-      <c r="O13" s="7" t="inlineStr"/>
-      <c r="P13" s="7" t="inlineStr"/>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr"/>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>173-46-062</t>
-        </is>
-      </c>
-      <c r="T13" s="7" t="inlineStr"/>
-      <c r="U13" s="7" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>20260295385</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>JOSE SCOTT AND TRACE R SCOTT</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Rocket Mortgage, LLC sbm Nationstar Mortgage LLC</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>539000</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>17941 WALICE AVE</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>WADDELL</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>85355</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>502-10-4999</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V13" s="7" t="inlineStr">
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="A14" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C14" s="7" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>20260291347</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>limited liability company, 8753 E Bell Rd. Ste 110, Scottsdale, AZ 85260.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>775000</v>
-      </c>
-      <c r="I14" s="7" t="inlineStr"/>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT BUILDING</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr"/>
-      <c r="L14" s="7" t="inlineStr"/>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr"/>
-      <c r="O14" s="7" t="inlineStr"/>
-      <c r="P14" s="7" t="inlineStr"/>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R14" s="7" t="inlineStr"/>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>118-17-365</t>
-        </is>
-      </c>
-      <c r="T14" s="7" t="inlineStr"/>
-      <c r="U14" s="7" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>20260296159</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>GEORGE PRESTON THOMAS AND PATRICIA ANN THOMAS, CO-TRUSTEES OF THE FAMILY</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Planet Home Lending LLC</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>292000</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>10981 W CIMARRON DR</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>200-35-538</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr"/>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>20260296342</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>ERNEST CLARK, JR</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>WaFd Bank</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>1198351</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>law firm of Folks Hess</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>25220 S Pyrenees Ct</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Queen Creek</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>304-88-1304</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>Larry O. Folks</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V14" s="7" t="inlineStr">
+      <c r="V15" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>20260291568</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>C/O LoanCare, LLC</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>100783</v>
-      </c>
-      <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Superior Courts Building. Maricopa County</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr"/>
-      <c r="L15" s="7" t="inlineStr"/>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr"/>
-      <c r="O15" s="7" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr"/>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>144-28-227</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr"/>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V15" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -1967,30 +2050,38 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>20260291573</t>
+          <t>20260292499</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr"/>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Alberto Garcia Jr and Estela Garcia</t>
+        </is>
+      </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Trustee, successor in interest to U.S. Bank National</t>
+          <t>U.S. Bank National Association, as Trustee for Current Trustee:</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>205600</v>
-      </c>
-      <c r="I16" s="7" t="inlineStr"/>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>Superior Courts Building. Maricopa County</t>
-        </is>
-      </c>
-      <c r="K16" s="7" t="inlineStr"/>
+        <v>80500</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J16" s="7" t="inlineStr"/>
+      <c r="K16" s="7" t="inlineStr">
+        <is>
+          <t>4820 West Catalina Drive, Unit 1</t>
+        </is>
+      </c>
       <c r="L16" s="7" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr">
         <is>
@@ -2008,10 +2099,14 @@
       <c r="R16" s="7" t="inlineStr"/>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>145-01-3050</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr"/>
+          <t>107-47-0531</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>Structured Asset Securities Corporation Mortgage Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="U16" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2044,27 +2139,27 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>20260291579</t>
+          <t>20260293700</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>C/O Wells Fargo Bank, N.A. -</t>
+          <t>solely as Trustee for Morgan Stanley Residential</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
-        <v>286862</v>
+        <v>262500</v>
       </c>
       <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Superior Courts Building. Maricopa County</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr"/>
@@ -2085,7 +2180,7 @@
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>304-70-167</t>
+          <t>112-37-104</t>
         </is>
       </c>
       <c r="T17" s="7" t="inlineStr"/>
@@ -2121,30 +2216,42 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>20260291582</t>
+          <t>20260294495</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr"/>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Holly Kanavy</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>C/O Wells Fargo Bank, N.A.</t>
+          <t>U.S. Bank National Association Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>170940</v>
-      </c>
-      <c r="I18" s="7" t="inlineStr"/>
+        <v>96214</v>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Superior Courts Building. Maricopa County</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr"/>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>903 S Casitas Dr, Unit C</t>
+        </is>
+      </c>
       <c r="L18" s="7" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr">
         <is>
@@ -2162,10 +2269,14 @@
       <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>143-04-2935</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr"/>
+          <t>132-63-1416</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>U.S. Bank National Association Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="U18" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2184,7 +2295,7 @@
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -2198,32 +2309,24 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>20260290799</t>
+          <t>20260295847</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>Reginald P. Allen and Cheryl C. Allen</t>
-        </is>
-      </c>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>Balboa LLC, a California Limited Liability Company, ISAOA</t>
+          <t>C/O Fay Servicing, LLC</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>75000</v>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
-        </is>
-      </c>
+        <v>848400</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
           <t>Superior Court Building</t>
@@ -2247,7 +2350,7 @@
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>309-05-147</t>
+          <t>136-27-065</t>
         </is>
       </c>
       <c r="T19" s="7" t="inlineStr"/>
@@ -2269,7 +2372,7 @@
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -2283,36 +2386,30 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>20260292036</t>
+          <t>20260296504</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>JAMAL PARKER</t>
-        </is>
-      </c>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>CROSSCOUNTRY MORTGAGE, LLC</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
+          <t>C/O Freedom Mortgage Corporation .</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>266000</v>
+      </c>
       <c r="I20" s="7" t="inlineStr"/>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>845 N LOS ALAMOS DR</t>
-        </is>
-      </c>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr"/>
       <c r="L20" s="7" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr">
         <is>
@@ -2330,506 +2427,564 @@
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>500-11-067</t>
-        </is>
-      </c>
-      <c r="T20" s="7" t="inlineStr">
+          <t>159-32-035</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr"/>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>20260294313</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>C/O MidFirst Bank</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>86418</v>
+      </c>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>111-28-0622</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr"/>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>20260293780</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>PATRICK M FITZGERALD</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>PennyMac Loan Services, LLC</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>1214 W SAND HILLS COURT</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr"/>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr"/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>302-96-579</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr">
         <is>
           <t>Clear Recon Corp</t>
         </is>
       </c>
-      <c r="U20" s="7" t="inlineStr">
+      <c r="U22" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V20" s="7" t="inlineStr">
+      <c r="V22" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="10" t="n">
-        <v>49</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>20260290308</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr"/>
-      <c r="G21" s="11" t="inlineStr"/>
-      <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="11" t="inlineStr">
-        <is>
-          <t>19631 N 132ND AVE</t>
-        </is>
-      </c>
-      <c r="L21" s="11" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N21" s="11" t="inlineStr"/>
-      <c r="O21" s="11" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr"/>
-      <c r="Q21" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R21" s="11" t="inlineStr"/>
-      <c r="S21" s="11" t="inlineStr"/>
-      <c r="T21" s="11" t="inlineStr"/>
-      <c r="U21" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V21" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>20260296205</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>FREDY MORALES</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>NewRez LLC D/B/A Shellpoint Mortgage Servicing</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>8621 S 48TH ST, UNIT #3</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="7" t="inlineStr"/>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr"/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>301-13-146</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W21" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Lis Pendens</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>20260290005</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr"/>
-      <c r="G22" s="11" t="inlineStr"/>
-      <c r="H22" s="11" t="inlineStr"/>
-      <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>20260293574</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="8" t="n">
+        <v>55712.83</v>
+      </c>
+      <c r="I24" s="7" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr"/>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr"/>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R24" s="7" t="inlineStr"/>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>105-75-451</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr"/>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V24" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="6" t="n">
+        <v>56</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>20260294266</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="8" t="n">
+        <v>63678</v>
+      </c>
+      <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr"/>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr"/>
+      <c r="O25" s="7" t="inlineStr"/>
+      <c r="P25" s="7" t="inlineStr"/>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr"/>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>210-07-171</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr"/>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V25" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>20260295850</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>C/O Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr"/>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr"/>
+      <c r="O26" s="7" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr"/>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr"/>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>149-28-056</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr"/>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>20260295862</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr">
         <is>
           <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
-      <c r="K22" s="11" t="inlineStr"/>
-      <c r="L22" s="11" t="inlineStr"/>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr"/>
-      <c r="O22" s="11" t="inlineStr"/>
-      <c r="P22" s="11" t="inlineStr"/>
-      <c r="Q22" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R22" s="11" t="inlineStr"/>
-      <c r="S22" s="11" t="inlineStr">
-        <is>
-          <t>176-08-934</t>
-        </is>
-      </c>
-      <c r="T22" s="11" t="inlineStr"/>
-      <c r="U22" s="11" t="inlineStr">
-        <is>
-          <t>Lis pendens; New this week</t>
-        </is>
-      </c>
-      <c r="V22" s="11" t="inlineStr">
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>3150 West Matthew Drive</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>85027</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr"/>
+      <c r="P27" s="7" t="inlineStr"/>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr"/>
+      <c r="S27" s="7" t="inlineStr"/>
+      <c r="T27" s="7" t="inlineStr"/>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W22" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Lis Pendens</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>20260290200</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr"/>
-      <c r="G23" s="11" t="inlineStr"/>
-      <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr"/>
-      <c r="L23" s="11" t="inlineStr"/>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N23" s="11" t="inlineStr"/>
-      <c r="O23" s="11" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr"/>
-      <c r="Q23" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R23" s="11" t="inlineStr"/>
-      <c r="S23" s="11" t="inlineStr">
-        <is>
-          <t>216-88-048</t>
-        </is>
-      </c>
-      <c r="T23" s="11" t="inlineStr"/>
-      <c r="U23" s="11" t="inlineStr">
-        <is>
-          <t>Lis pendens; New this week</t>
-        </is>
-      </c>
-      <c r="V23" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W23" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="26" customHeight="1">
-      <c r="A24" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B24" s="11" t="inlineStr">
-        <is>
-          <t>Lis Pendens</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="D24" s="11" t="inlineStr">
-        <is>
-          <t>20260290384</t>
-        </is>
-      </c>
-      <c r="E24" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F24" s="11" t="inlineStr"/>
-      <c r="G24" s="11" t="inlineStr"/>
-      <c r="H24" s="11" t="inlineStr"/>
-      <c r="I24" s="11" t="inlineStr"/>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K24" s="11" t="inlineStr"/>
-      <c r="L24" s="11" t="inlineStr"/>
-      <c r="M24" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N24" s="11" t="inlineStr"/>
-      <c r="O24" s="11" t="inlineStr"/>
-      <c r="P24" s="11" t="inlineStr"/>
-      <c r="Q24" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R24" s="11" t="inlineStr"/>
-      <c r="S24" s="11" t="inlineStr"/>
-      <c r="T24" s="11" t="inlineStr"/>
-      <c r="U24" s="11" t="inlineStr">
-        <is>
-          <t>Lis pendens; New this week</t>
-        </is>
-      </c>
-      <c r="V24" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W24" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="26" customHeight="1">
-      <c r="A25" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
-        <is>
-          <t>Lis Pendens</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="D25" s="11" t="inlineStr">
-        <is>
-          <t>20260290556</t>
-        </is>
-      </c>
-      <c r="E25" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F25" s="11" t="inlineStr"/>
-      <c r="G25" s="11" t="inlineStr"/>
-      <c r="H25" s="11" t="inlineStr"/>
-      <c r="I25" s="11" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K25" s="11" t="inlineStr"/>
-      <c r="L25" s="11" t="inlineStr"/>
-      <c r="M25" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N25" s="11" t="inlineStr"/>
-      <c r="O25" s="11" t="inlineStr"/>
-      <c r="P25" s="11" t="inlineStr"/>
-      <c r="Q25" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R25" s="11" t="inlineStr"/>
-      <c r="S25" s="11" t="inlineStr"/>
-      <c r="T25" s="11" t="inlineStr"/>
-      <c r="U25" s="11" t="inlineStr">
-        <is>
-          <t>Lis pendens; New this week</t>
-        </is>
-      </c>
-      <c r="V25" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W25" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B26" s="11" t="inlineStr">
-        <is>
-          <t>Lis Pendens</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="D26" s="11" t="inlineStr">
-        <is>
-          <t>20260290840</t>
-        </is>
-      </c>
-      <c r="E26" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F26" s="11" t="inlineStr"/>
-      <c r="G26" s="11" t="inlineStr"/>
-      <c r="H26" s="11" t="inlineStr"/>
-      <c r="I26" s="11" t="inlineStr"/>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K26" s="11" t="inlineStr"/>
-      <c r="L26" s="11" t="inlineStr"/>
-      <c r="M26" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N26" s="11" t="inlineStr"/>
-      <c r="O26" s="11" t="inlineStr"/>
-      <c r="P26" s="11" t="inlineStr"/>
-      <c r="Q26" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R26" s="11" t="inlineStr"/>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>502-29-032</t>
-        </is>
-      </c>
-      <c r="T26" s="11" t="inlineStr"/>
-      <c r="U26" s="11" t="inlineStr">
-        <is>
-          <t>Lis pendens; New this week</t>
-        </is>
-      </c>
-      <c r="V26" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W26" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="A27" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B27" s="11" t="inlineStr">
-        <is>
-          <t>Lis Pendens</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
-        <is>
-          <t>LP</t>
-        </is>
-      </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>20260290952</t>
-        </is>
-      </c>
-      <c r="E27" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="F27" s="11" t="inlineStr"/>
-      <c r="G27" s="11" t="inlineStr"/>
-      <c r="H27" s="11" t="inlineStr"/>
-      <c r="I27" s="11" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K27" s="11" t="inlineStr"/>
-      <c r="L27" s="11" t="inlineStr"/>
-      <c r="M27" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N27" s="11" t="inlineStr"/>
-      <c r="O27" s="11" t="inlineStr"/>
-      <c r="P27" s="11" t="inlineStr"/>
-      <c r="Q27" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R27" s="11" t="inlineStr"/>
-      <c r="S27" s="11" t="inlineStr"/>
-      <c r="T27" s="11" t="inlineStr"/>
-      <c r="U27" s="11" t="inlineStr">
-        <is>
-          <t>Lis pendens; New this week</t>
-        </is>
-      </c>
-      <c r="V27" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W27" s="12" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -2851,12 +3006,12 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>20260291917</t>
+          <t>20260296134</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
@@ -2918,12 +3073,12 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>20260292038</t>
+          <t>20260296193</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr"/>
@@ -2932,7 +3087,7 @@
       <c r="I29" s="11" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>SUPERIOR COURT OF ARIZONA</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr"/>
@@ -2985,12 +3140,12 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>20260289941</t>
+          <t>20260293218</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr"/>
@@ -2999,7 +3154,7 @@
       <c r="I30" s="11" t="inlineStr"/>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr"/>
@@ -3052,12 +3207,12 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>20260289942</t>
+          <t>20260293219</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
@@ -3066,7 +3221,7 @@
       <c r="I31" s="11" t="inlineStr"/>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr"/>
@@ -3119,12 +3274,12 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>20260290079</t>
+          <t>20260293220</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
@@ -3133,7 +3288,7 @@
       <c r="I32" s="11" t="inlineStr"/>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>Superior Court in Maricopa County.</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr"/>
@@ -3186,19 +3341,23 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>20260290115</t>
+          <t>20260293223</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
       <c r="G33" s="11" t="inlineStr"/>
       <c r="H33" s="11" t="inlineStr"/>
       <c r="I33" s="11" t="inlineStr"/>
-      <c r="J33" s="11" t="inlineStr"/>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K33" s="11" t="inlineStr"/>
       <c r="L33" s="11" t="inlineStr"/>
       <c r="M33" s="11" t="inlineStr">
@@ -3249,12 +3408,12 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>20260290222</t>
+          <t>20260293224</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
@@ -3263,7 +3422,7 @@
       <c r="I34" s="11" t="inlineStr"/>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
@@ -3316,19 +3475,23 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>20260290223</t>
+          <t>20260293225</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
       <c r="G35" s="11" t="inlineStr"/>
       <c r="H35" s="11" t="inlineStr"/>
       <c r="I35" s="11" t="inlineStr"/>
-      <c r="J35" s="11" t="inlineStr"/>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court :</t>
+        </is>
+      </c>
       <c r="K35" s="11" t="inlineStr"/>
       <c r="L35" s="11" t="inlineStr"/>
       <c r="M35" s="11" t="inlineStr">
@@ -3379,12 +3542,12 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>20260290225</t>
+          <t>20260293226</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
@@ -3393,7 +3556,7 @@
       <c r="I36" s="11" t="inlineStr"/>
       <c r="J36" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT OF ARIZONA i</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr"/>
@@ -3446,12 +3609,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>20260290226</t>
+          <t>20260293227</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
@@ -3460,7 +3623,7 @@
       <c r="I37" s="11" t="inlineStr"/>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>Superior Court |</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr"/>
@@ -3513,12 +3676,12 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>20260290227</t>
+          <t>20260293228</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr"/>
@@ -3580,12 +3743,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>20260290228</t>
+          <t>20260293229</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
@@ -3647,12 +3810,12 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>20260290229</t>
+          <t>20260293234</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
@@ -3661,7 +3824,7 @@
       <c r="I40" s="11" t="inlineStr"/>
       <c r="J40" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr"/>
@@ -3714,12 +3877,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>20260290230</t>
+          <t>20260293274</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
@@ -3728,7 +3891,7 @@
       <c r="I41" s="11" t="inlineStr"/>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT .</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -3781,12 +3944,12 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>20260290231</t>
+          <t>20260293777</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
@@ -3848,19 +4011,23 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>20260290232</t>
+          <t>20260293778</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr"/>
       <c r="H43" s="11" t="inlineStr"/>
       <c r="I43" s="11" t="inlineStr"/>
-      <c r="J43" s="11" t="inlineStr"/>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K43" s="11" t="inlineStr"/>
       <c r="L43" s="11" t="inlineStr"/>
       <c r="M43" s="11" t="inlineStr">
@@ -3911,12 +4078,12 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>20260290455</t>
+          <t>20260293779</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
@@ -3925,7 +4092,7 @@
       <c r="I44" s="11" t="inlineStr"/>
       <c r="J44" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr"/>
@@ -3978,12 +4145,12 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>20260290456</t>
+          <t>20260294070</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
@@ -3992,7 +4159,7 @@
       <c r="I45" s="11" t="inlineStr"/>
       <c r="J45" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT OF ARIZONA</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr"/>
@@ -4045,12 +4212,12 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>20260290461</t>
+          <t>20260294071</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
@@ -4059,7 +4226,7 @@
       <c r="I46" s="11" t="inlineStr"/>
       <c r="J46" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>Superior Court .</t>
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr"/>
@@ -4112,12 +4279,12 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>20260290462</t>
+          <t>20260294078</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
@@ -4179,12 +4346,12 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>20260290463</t>
+          <t>20260294079</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
@@ -4193,7 +4360,7 @@
       <c r="I48" s="11" t="inlineStr"/>
       <c r="J48" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr"/>
@@ -4246,12 +4413,12 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>20260290465</t>
+          <t>20260294362</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
@@ -4313,12 +4480,12 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>20260290466</t>
+          <t>20260294399</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr"/>
@@ -4327,7 +4494,7 @@
       <c r="I50" s="11" t="inlineStr"/>
       <c r="J50" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>Superior Court in Maricopa County.</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr"/>
@@ -4380,23 +4547,19 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>20260290470</t>
+          <t>20260295019</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
       <c r="G51" s="11" t="inlineStr"/>
       <c r="H51" s="11" t="inlineStr"/>
       <c r="I51" s="11" t="inlineStr"/>
-      <c r="J51" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J51" s="11" t="inlineStr"/>
       <c r="K51" s="11" t="inlineStr"/>
       <c r="L51" s="11" t="inlineStr"/>
       <c r="M51" s="11" t="inlineStr">
@@ -4447,23 +4610,19 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>20260290486</t>
+          <t>20260295020</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr"/>
       <c r="H52" s="11" t="inlineStr"/>
       <c r="I52" s="11" t="inlineStr"/>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court in Maricopa County.</t>
-        </is>
-      </c>
+      <c r="J52" s="11" t="inlineStr"/>
       <c r="K52" s="11" t="inlineStr"/>
       <c r="L52" s="11" t="inlineStr"/>
       <c r="M52" s="11" t="inlineStr">
@@ -4514,23 +4673,19 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>20260290489</t>
+          <t>20260295021</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
       <c r="G53" s="11" t="inlineStr"/>
       <c r="H53" s="11" t="inlineStr"/>
       <c r="I53" s="11" t="inlineStr"/>
-      <c r="J53" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court in Maricopa County.</t>
-        </is>
-      </c>
+      <c r="J53" s="11" t="inlineStr"/>
       <c r="K53" s="11" t="inlineStr"/>
       <c r="L53" s="11" t="inlineStr"/>
       <c r="M53" s="11" t="inlineStr">
@@ -4581,23 +4736,19 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>20260290596</t>
+          <t>20260295022</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
       <c r="G54" s="11" t="inlineStr"/>
       <c r="H54" s="11" t="inlineStr"/>
       <c r="I54" s="11" t="inlineStr"/>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr"/>
       <c r="L54" s="11" t="inlineStr"/>
       <c r="M54" s="11" t="inlineStr">
@@ -4648,23 +4799,19 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>20260290601</t>
+          <t>20260295023</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr"/>
       <c r="H55" s="11" t="inlineStr"/>
       <c r="I55" s="11" t="inlineStr"/>
-      <c r="J55" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J55" s="11" t="inlineStr"/>
       <c r="K55" s="11" t="inlineStr"/>
       <c r="L55" s="11" t="inlineStr"/>
       <c r="M55" s="11" t="inlineStr">
@@ -4715,12 +4862,12 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>20260290681</t>
+          <t>20260295360</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
@@ -4729,7 +4876,7 @@
       <c r="I56" s="11" t="inlineStr"/>
       <c r="J56" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr"/>
@@ -4782,12 +4929,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>20260290682</t>
+          <t>20260295650</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr"/>
@@ -4849,12 +4996,12 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>20260290718</t>
+          <t>20260295732</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr"/>
@@ -4916,12 +5063,12 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>20260290927</t>
+          <t>20260295759</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
@@ -4930,7 +5077,7 @@
       <c r="I59" s="11" t="inlineStr"/>
       <c r="J59" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K59" s="11" t="inlineStr"/>
@@ -4983,12 +5130,12 @@
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>20260291117</t>
+          <t>20260295760</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
@@ -4997,7 +5144,7 @@
       <c r="I60" s="11" t="inlineStr"/>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr"/>
@@ -5050,12 +5197,12 @@
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>20260291130</t>
+          <t>20260295766</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
@@ -5064,7 +5211,7 @@
       <c r="I61" s="11" t="inlineStr"/>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr"/>
@@ -5117,12 +5264,12 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>20260291635</t>
+          <t>20260295889</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
@@ -5131,7 +5278,7 @@
       <c r="I62" s="11" t="inlineStr"/>
       <c r="J62" s="11" t="inlineStr">
         <is>
-          <t>Superior Court of Arizona in Maricopa County</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr"/>
@@ -5184,23 +5331,19 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>20260291655</t>
+          <t>20260296282</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr"/>
       <c r="H63" s="11" t="inlineStr"/>
       <c r="I63" s="11" t="inlineStr"/>
-      <c r="J63" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J63" s="11" t="inlineStr"/>
       <c r="K63" s="11" t="inlineStr"/>
       <c r="L63" s="11" t="inlineStr"/>
       <c r="M63" s="11" t="inlineStr">
@@ -5251,12 +5394,12 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>20260291802</t>
+          <t>20260296295</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
@@ -5265,7 +5408,7 @@
       <c r="I64" s="11" t="inlineStr"/>
       <c r="J64" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr"/>
@@ -5308,22 +5451,22 @@
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>20260290491</t>
+          <t>20260296394</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
@@ -5332,7 +5475,7 @@
       <c r="I65" s="11" t="inlineStr"/>
       <c r="J65" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr"/>
@@ -5355,7 +5498,7 @@
       <c r="T65" s="11" t="inlineStr"/>
       <c r="U65" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V65" s="11" t="inlineStr">
@@ -5375,33 +5518,29 @@
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>20260290796</t>
+          <t>20260296401</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
       <c r="G66" s="11" t="inlineStr"/>
       <c r="H66" s="11" t="inlineStr"/>
       <c r="I66" s="11" t="inlineStr"/>
-      <c r="J66" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J66" s="11" t="inlineStr"/>
       <c r="K66" s="11" t="inlineStr"/>
       <c r="L66" s="11" t="inlineStr"/>
       <c r="M66" s="11" t="inlineStr">
@@ -5422,7 +5561,7 @@
       <c r="T66" s="11" t="inlineStr"/>
       <c r="U66" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V66" s="11" t="inlineStr">
@@ -5442,33 +5581,29 @@
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>20260291292</t>
+          <t>20260296402</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
       <c r="G67" s="11" t="inlineStr"/>
       <c r="H67" s="11" t="inlineStr"/>
       <c r="I67" s="11" t="inlineStr"/>
-      <c r="J67" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J67" s="11" t="inlineStr"/>
       <c r="K67" s="11" t="inlineStr"/>
       <c r="L67" s="11" t="inlineStr"/>
       <c r="M67" s="11" t="inlineStr">
@@ -5489,7 +5624,7 @@
       <c r="T67" s="11" t="inlineStr"/>
       <c r="U67" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V67" s="11" t="inlineStr">
@@ -5505,26 +5640,26 @@
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>20260290613</t>
+          <t>20260296404</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
@@ -5552,7 +5687,7 @@
       <c r="T68" s="11" t="inlineStr"/>
       <c r="U68" s="11" t="inlineStr">
         <is>
-          <t>Mechanic lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V68" s="11" t="inlineStr">
@@ -5568,33 +5703,37 @@
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>20260291075</t>
+          <t>20260293393</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
       <c r="G69" s="11" t="inlineStr"/>
       <c r="H69" s="11" t="inlineStr"/>
       <c r="I69" s="11" t="inlineStr"/>
-      <c r="J69" s="11" t="inlineStr"/>
+      <c r="J69" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K69" s="11" t="inlineStr"/>
       <c r="L69" s="11" t="inlineStr"/>
       <c r="M69" s="11" t="inlineStr">
@@ -5611,15 +5750,11 @@
         </is>
       </c>
       <c r="R69" s="11" t="inlineStr"/>
-      <c r="S69" s="11" t="inlineStr">
-        <is>
-          <t>149-23-028</t>
-        </is>
-      </c>
+      <c r="S69" s="11" t="inlineStr"/>
       <c r="T69" s="11" t="inlineStr"/>
       <c r="U69" s="11" t="inlineStr">
         <is>
-          <t>Mechanic lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V69" s="11" t="inlineStr">
@@ -5635,33 +5770,37 @@
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>20260291156</t>
+          <t>20260293636</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
       <c r="G70" s="11" t="inlineStr"/>
       <c r="H70" s="11" t="inlineStr"/>
       <c r="I70" s="11" t="inlineStr"/>
-      <c r="J70" s="11" t="inlineStr"/>
+      <c r="J70" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K70" s="11" t="inlineStr"/>
       <c r="L70" s="11" t="inlineStr"/>
       <c r="M70" s="11" t="inlineStr">
@@ -5678,15 +5817,11 @@
         </is>
       </c>
       <c r="R70" s="11" t="inlineStr"/>
-      <c r="S70" s="11" t="inlineStr">
-        <is>
-          <t>501-61-014</t>
-        </is>
-      </c>
+      <c r="S70" s="11" t="inlineStr"/>
       <c r="T70" s="11" t="inlineStr"/>
       <c r="U70" s="11" t="inlineStr">
         <is>
-          <t>Mechanic lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V70" s="11" t="inlineStr">
@@ -5702,33 +5837,37 @@
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>20260291167</t>
+          <t>20260295147</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
       <c r="G71" s="11" t="inlineStr"/>
       <c r="H71" s="11" t="inlineStr"/>
       <c r="I71" s="11" t="inlineStr"/>
-      <c r="J71" s="11" t="inlineStr"/>
+      <c r="J71" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court Case No. PB2025-002503</t>
+        </is>
+      </c>
       <c r="K71" s="11" t="inlineStr"/>
       <c r="L71" s="11" t="inlineStr"/>
       <c r="M71" s="11" t="inlineStr">
@@ -5745,15 +5884,11 @@
         </is>
       </c>
       <c r="R71" s="11" t="inlineStr"/>
-      <c r="S71" s="11" t="inlineStr">
-        <is>
-          <t>304-12-990</t>
-        </is>
-      </c>
+      <c r="S71" s="11" t="inlineStr"/>
       <c r="T71" s="11" t="inlineStr"/>
       <c r="U71" s="11" t="inlineStr">
         <is>
-          <t>Mechanic lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V71" s="11" t="inlineStr">
@@ -5769,31 +5904,33 @@
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>20260289194</t>
+          <t>20260293572</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
       <c r="G72" s="11" t="inlineStr"/>
-      <c r="H72" s="11" t="inlineStr"/>
+      <c r="H72" s="13" t="n">
+        <v>30058.51</v>
+      </c>
       <c r="I72" s="11" t="inlineStr"/>
       <c r="J72" s="11" t="inlineStr"/>
       <c r="K72" s="11" t="inlineStr"/>
@@ -5812,11 +5949,15 @@
         </is>
       </c>
       <c r="R72" s="11" t="inlineStr"/>
-      <c r="S72" s="11" t="inlineStr"/>
+      <c r="S72" s="11" t="inlineStr">
+        <is>
+          <t>204-09-005</t>
+        </is>
+      </c>
       <c r="T72" s="11" t="inlineStr"/>
       <c r="U72" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V72" s="11" t="inlineStr">
@@ -5832,26 +5973,26 @@
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>20260289195</t>
+          <t>20260293812</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
@@ -5875,11 +6016,15 @@
         </is>
       </c>
       <c r="R73" s="11" t="inlineStr"/>
-      <c r="S73" s="11" t="inlineStr"/>
+      <c r="S73" s="11" t="inlineStr">
+        <is>
+          <t>164-22-124</t>
+        </is>
+      </c>
       <c r="T73" s="11" t="inlineStr"/>
       <c r="U73" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V73" s="11" t="inlineStr">
@@ -5895,26 +6040,26 @@
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="10" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>20260289196</t>
+          <t>20260295861</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
@@ -5938,11 +6083,15 @@
         </is>
       </c>
       <c r="R74" s="11" t="inlineStr"/>
-      <c r="S74" s="11" t="inlineStr"/>
+      <c r="S74" s="11" t="inlineStr">
+        <is>
+          <t>304-61-001</t>
+        </is>
+      </c>
       <c r="T74" s="11" t="inlineStr"/>
       <c r="U74" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V74" s="11" t="inlineStr">
@@ -5972,12 +6121,12 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>20260289197</t>
+          <t>20260292066</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
@@ -6035,12 +6184,12 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>20260289199</t>
+          <t>20260292067</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
@@ -6098,12 +6247,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>20260289200</t>
+          <t>20260292068</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr"/>
@@ -6161,12 +6310,12 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>20260289205</t>
+          <t>20260292069</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
@@ -6224,12 +6373,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>20260289206</t>
+          <t>20260292070</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr"/>
@@ -6287,12 +6436,12 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>20260289207</t>
+          <t>20260292071</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
@@ -6350,12 +6499,12 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>20260289208</t>
+          <t>20260292072</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr"/>
@@ -6413,12 +6562,12 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>20260289209</t>
+          <t>20260292073</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr"/>
@@ -6476,12 +6625,12 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>20260289210</t>
+          <t>20260292074</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
@@ -6539,12 +6688,12 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>20260289211</t>
+          <t>20260292075</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr"/>
@@ -6602,12 +6751,12 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>20260289212</t>
+          <t>20260292076</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr"/>
@@ -6665,12 +6814,12 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>20260289213</t>
+          <t>20260292077</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr"/>
@@ -6728,12 +6877,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>20260289214</t>
+          <t>20260292078</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr"/>
@@ -6791,12 +6940,12 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>20260289215</t>
+          <t>20260292079</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr"/>
@@ -6854,12 +7003,12 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>20260289216</t>
+          <t>20260292080</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
@@ -6917,12 +7066,12 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>20260289217</t>
+          <t>20260292081</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
@@ -6980,12 +7129,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>20260289219</t>
+          <t>20260292082</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr"/>
@@ -7043,12 +7192,12 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>20260289220</t>
+          <t>20260292083</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr"/>
@@ -7106,12 +7255,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>20260289221</t>
+          <t>20260292084</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
@@ -7169,12 +7318,12 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>20260289222</t>
+          <t>20260292086</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr"/>
@@ -7232,12 +7381,12 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>20260289223</t>
+          <t>20260292743</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr"/>
@@ -7295,12 +7444,12 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>20260289224</t>
+          <t>20260292744</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr"/>
@@ -7358,12 +7507,12 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>20260289225</t>
+          <t>20260292750</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr"/>
@@ -7421,12 +7570,12 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>20260289226</t>
+          <t>20260292800</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr"/>
@@ -7484,12 +7633,12 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>20260289227</t>
+          <t>20260293328</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr"/>
@@ -7547,12 +7696,12 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>20260289256</t>
+          <t>20260294162</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr"/>
@@ -7610,12 +7759,12 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>20260289257</t>
+          <t>20260294301</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr"/>
@@ -7663,22 +7812,22 @@
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>20260290136</t>
+          <t>20260294333</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr"/>
@@ -7706,12 +7855,12 @@
       <c r="T102" s="11" t="inlineStr"/>
       <c r="U102" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V102" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W102" s="12" t="inlineStr">
@@ -7726,22 +7875,22 @@
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>20260290645</t>
+          <t>20260294334</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr"/>
@@ -7769,12 +7918,12 @@
       <c r="T103" s="11" t="inlineStr"/>
       <c r="U103" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V103" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W103" s="12" t="inlineStr">
@@ -7789,22 +7938,22 @@
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>20260291111</t>
+          <t>20260294335</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr"/>
@@ -7832,12 +7981,12 @@
       <c r="T104" s="11" t="inlineStr"/>
       <c r="U104" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V104" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W104" s="12" t="inlineStr">
@@ -7852,22 +8001,22 @@
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>20260291338</t>
+          <t>20260294336</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr"/>
@@ -7895,12 +8044,12 @@
       <c r="T105" s="11" t="inlineStr"/>
       <c r="U105" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V105" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W105" s="12" t="inlineStr">
@@ -7915,22 +8064,22 @@
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>20260291837</t>
+          <t>20260294337</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr"/>
@@ -7958,12 +8107,12 @@
       <c r="T106" s="11" t="inlineStr"/>
       <c r="U106" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V106" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W106" s="12" t="inlineStr">
@@ -7978,22 +8127,22 @@
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>20260291839</t>
+          <t>20260294398</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr"/>
@@ -8021,12 +8170,12 @@
       <c r="T107" s="11" t="inlineStr"/>
       <c r="U107" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V107" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W107" s="12" t="inlineStr">
@@ -8051,12 +8200,12 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>20260291841</t>
+          <t>20260294434</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr"/>
@@ -8114,12 +8263,12 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>20260291842</t>
+          <t>20260295063</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr"/>
@@ -8177,12 +8326,12 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>20260291843</t>
+          <t>20260295375</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr"/>
@@ -8240,12 +8389,12 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>20260291844</t>
+          <t>20260295773</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr"/>
@@ -8293,22 +8442,22 @@
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>20260291847</t>
+          <t>20260292783</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr"/>
@@ -8336,7 +8485,7 @@
       <c r="T112" s="11" t="inlineStr"/>
       <c r="U112" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V112" s="11" t="inlineStr">
@@ -8352,26 +8501,26 @@
     </row>
     <row r="113" ht="26" customHeight="1">
       <c r="A113" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>20260289961</t>
+          <t>20260292844</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr"/>
@@ -8399,12 +8548,12 @@
       <c r="T113" s="11" t="inlineStr"/>
       <c r="U113" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V113" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W113" s="12" t="inlineStr">
@@ -8415,26 +8564,26 @@
     </row>
     <row r="114" ht="26" customHeight="1">
       <c r="A114" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>20260289962</t>
+          <t>20260293422</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr"/>
@@ -8462,12 +8611,12 @@
       <c r="T114" s="11" t="inlineStr"/>
       <c r="U114" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V114" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W114" s="12" t="inlineStr">
@@ -8478,26 +8627,26 @@
     </row>
     <row r="115" ht="26" customHeight="1">
       <c r="A115" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>20260289964</t>
+          <t>20260293635</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr"/>
@@ -8525,12 +8674,12 @@
       <c r="T115" s="11" t="inlineStr"/>
       <c r="U115" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V115" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W115" s="12" t="inlineStr">
@@ -8541,26 +8690,26 @@
     </row>
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>20260289969</t>
+          <t>20260294092</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr"/>
@@ -8588,12 +8737,12 @@
       <c r="T116" s="11" t="inlineStr"/>
       <c r="U116" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V116" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W116" s="12" t="inlineStr">
@@ -8604,26 +8753,26 @@
     </row>
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>20260291354</t>
+          <t>20260294102</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr"/>
@@ -8651,12 +8800,12 @@
       <c r="T117" s="11" t="inlineStr"/>
       <c r="U117" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V117" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W117" s="12" t="inlineStr">
@@ -8667,26 +8816,26 @@
     </row>
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>20260291389</t>
+          <t>20260294394</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr"/>
@@ -8714,12 +8863,12 @@
       <c r="T118" s="11" t="inlineStr"/>
       <c r="U118" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V118" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W118" s="12" t="inlineStr">
@@ -8730,26 +8879,26 @@
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>20260291390</t>
+          <t>20260294990</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr"/>
@@ -8777,12 +8926,12 @@
       <c r="T119" s="11" t="inlineStr"/>
       <c r="U119" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V119" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W119" s="12" t="inlineStr">
@@ -8793,26 +8942,26 @@
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>20260291391</t>
+          <t>20260295357</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr"/>
@@ -8840,12 +8989,12 @@
       <c r="T120" s="11" t="inlineStr"/>
       <c r="U120" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V120" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W120" s="12" t="inlineStr">
@@ -8856,26 +9005,26 @@
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>20260291392</t>
+          <t>20260295762</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr"/>
@@ -8903,12 +9052,12 @@
       <c r="T121" s="11" t="inlineStr"/>
       <c r="U121" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V121" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W121" s="12" t="inlineStr">
@@ -8919,26 +9068,26 @@
     </row>
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>20260291393</t>
+          <t>20260295763</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr"/>
@@ -8966,12 +9115,12 @@
       <c r="T122" s="11" t="inlineStr"/>
       <c r="U122" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V122" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W122" s="12" t="inlineStr">
@@ -8982,26 +9131,26 @@
     </row>
     <row r="123" ht="26" customHeight="1">
       <c r="A123" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>20260291394</t>
+          <t>20260296088</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr"/>
@@ -9029,12 +9178,12 @@
       <c r="T123" s="11" t="inlineStr"/>
       <c r="U123" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V123" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W123" s="12" t="inlineStr">
@@ -9045,26 +9194,26 @@
     </row>
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="10" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>20260291395</t>
+          <t>20260296089</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr"/>
@@ -9092,12 +9241,12 @@
       <c r="T124" s="11" t="inlineStr"/>
       <c r="U124" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V124" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W124" s="12" t="inlineStr">
@@ -9122,12 +9271,12 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>20260291396</t>
+          <t>20260292704</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr"/>
@@ -9185,12 +9334,12 @@
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>20260291401</t>
+          <t>20260292705</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr"/>
@@ -9248,12 +9397,12 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>20260291402</t>
+          <t>20260292706</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr"/>
@@ -9311,12 +9460,12 @@
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>20260291403</t>
+          <t>20260292707</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr"/>
@@ -9374,12 +9523,12 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>20260291404</t>
+          <t>20260292708</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr"/>
@@ -9437,12 +9586,12 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>20260291405</t>
+          <t>20260292709</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr"/>
@@ -9500,12 +9649,12 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>20260291772</t>
+          <t>20260292710</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr"/>
@@ -9563,12 +9712,12 @@
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>20260291773</t>
+          <t>20260292713</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr"/>
@@ -9626,12 +9775,12 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>20260291774</t>
+          <t>20260292714</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr"/>
@@ -9675,33 +9824,33 @@
     </row>
     <row r="134" ht="26" customHeight="1">
       <c r="A134" s="10" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>20260289900</t>
-        </is>
-      </c>
-      <c r="E134" s="11" t="inlineStr"/>
+          <t>20260292715</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
       <c r="F134" s="11" t="inlineStr"/>
       <c r="G134" s="11" t="inlineStr"/>
       <c r="H134" s="11" t="inlineStr"/>
       <c r="I134" s="11" t="inlineStr"/>
-      <c r="J134" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court Case</t>
-        </is>
-      </c>
+      <c r="J134" s="11" t="inlineStr"/>
       <c r="K134" s="11" t="inlineStr"/>
       <c r="L134" s="11" t="inlineStr"/>
       <c r="M134" s="11" t="inlineStr">
@@ -9722,7 +9871,7 @@
       <c r="T134" s="11" t="inlineStr"/>
       <c r="U134" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V134" s="11" t="inlineStr">
@@ -9738,26 +9887,26 @@
     </row>
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>20260289573</t>
+          <t>20260292717</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr"/>
@@ -9785,12 +9934,12 @@
       <c r="T135" s="11" t="inlineStr"/>
       <c r="U135" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V135" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W135" s="12" t="inlineStr">
@@ -9801,26 +9950,26 @@
     </row>
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>20260289968</t>
+          <t>20260292718</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr"/>
@@ -9848,12 +9997,12 @@
       <c r="T136" s="11" t="inlineStr"/>
       <c r="U136" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V136" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W136" s="12" t="inlineStr">
@@ -9864,26 +10013,26 @@
     </row>
     <row r="137" ht="26" customHeight="1">
       <c r="A137" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>20260290468</t>
+          <t>20260292719</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr"/>
@@ -9911,12 +10060,12 @@
       <c r="T137" s="11" t="inlineStr"/>
       <c r="U137" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V137" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W137" s="12" t="inlineStr">
@@ -9927,26 +10076,26 @@
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>20260290472</t>
+          <t>20260292722</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr"/>
@@ -9974,12 +10123,12 @@
       <c r="T138" s="11" t="inlineStr"/>
       <c r="U138" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V138" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W138" s="12" t="inlineStr">
@@ -9990,26 +10139,26 @@
     </row>
     <row r="139" ht="26" customHeight="1">
       <c r="A139" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>20260290473</t>
+          <t>20260292723</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr"/>
@@ -10037,12 +10186,12 @@
       <c r="T139" s="11" t="inlineStr"/>
       <c r="U139" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V139" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W139" s="12" t="inlineStr">
@@ -10053,26 +10202,26 @@
     </row>
     <row r="140" ht="26" customHeight="1">
       <c r="A140" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>20260290475</t>
+          <t>20260292724</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr"/>
@@ -10100,12 +10249,12 @@
       <c r="T140" s="11" t="inlineStr"/>
       <c r="U140" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V140" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W140" s="12" t="inlineStr">
@@ -10116,26 +10265,26 @@
     </row>
     <row r="141" ht="26" customHeight="1">
       <c r="A141" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>20260290522</t>
+          <t>20260292725</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr"/>
@@ -10163,12 +10312,12 @@
       <c r="T141" s="11" t="inlineStr"/>
       <c r="U141" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V141" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W141" s="12" t="inlineStr">
@@ -10179,26 +10328,26 @@
     </row>
     <row r="142" ht="26" customHeight="1">
       <c r="A142" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>20260290559</t>
+          <t>20260292730</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr"/>
@@ -10226,12 +10375,12 @@
       <c r="T142" s="11" t="inlineStr"/>
       <c r="U142" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V142" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W142" s="12" t="inlineStr">
@@ -10242,26 +10391,26 @@
     </row>
     <row r="143" ht="26" customHeight="1">
       <c r="A143" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>20260290561</t>
+          <t>20260292731</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr"/>
@@ -10289,12 +10438,12 @@
       <c r="T143" s="11" t="inlineStr"/>
       <c r="U143" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V143" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W143" s="12" t="inlineStr">
@@ -10305,26 +10454,26 @@
     </row>
     <row r="144" ht="26" customHeight="1">
       <c r="A144" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>20260290562</t>
+          <t>20260293247</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr"/>
@@ -10352,12 +10501,12 @@
       <c r="T144" s="11" t="inlineStr"/>
       <c r="U144" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V144" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W144" s="12" t="inlineStr">
@@ -10368,26 +10517,26 @@
     </row>
     <row r="145" ht="26" customHeight="1">
       <c r="A145" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>20260290563</t>
+          <t>20260293365</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr"/>
@@ -10415,12 +10564,12 @@
       <c r="T145" s="11" t="inlineStr"/>
       <c r="U145" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V145" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W145" s="12" t="inlineStr">
@@ -10431,26 +10580,26 @@
     </row>
     <row r="146" ht="26" customHeight="1">
       <c r="A146" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>20260290564</t>
+          <t>20260293369</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr"/>
@@ -10478,12 +10627,12 @@
       <c r="T146" s="11" t="inlineStr"/>
       <c r="U146" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V146" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W146" s="12" t="inlineStr">
@@ -10494,26 +10643,26 @@
     </row>
     <row r="147" ht="26" customHeight="1">
       <c r="A147" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>20260290565</t>
+          <t>20260293371</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr"/>
@@ -10541,12 +10690,12 @@
       <c r="T147" s="11" t="inlineStr"/>
       <c r="U147" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V147" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W147" s="12" t="inlineStr">
@@ -10557,26 +10706,26 @@
     </row>
     <row r="148" ht="26" customHeight="1">
       <c r="A148" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>20260290566</t>
+          <t>20260293372</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr"/>
@@ -10604,12 +10753,12 @@
       <c r="T148" s="11" t="inlineStr"/>
       <c r="U148" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V148" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W148" s="12" t="inlineStr">
@@ -10620,26 +10769,26 @@
     </row>
     <row r="149" ht="26" customHeight="1">
       <c r="A149" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>20260290567</t>
+          <t>20260293376</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr"/>
@@ -10667,12 +10816,12 @@
       <c r="T149" s="11" t="inlineStr"/>
       <c r="U149" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V149" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W149" s="12" t="inlineStr">
@@ -10683,26 +10832,26 @@
     </row>
     <row r="150" ht="26" customHeight="1">
       <c r="A150" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>20260290568</t>
+          <t>20260293377</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr"/>
@@ -10730,12 +10879,12 @@
       <c r="T150" s="11" t="inlineStr"/>
       <c r="U150" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V150" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W150" s="12" t="inlineStr">
@@ -10746,26 +10895,26 @@
     </row>
     <row r="151" ht="26" customHeight="1">
       <c r="A151" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>20260290569</t>
+          <t>20260293378</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr"/>
@@ -10793,12 +10942,12 @@
       <c r="T151" s="11" t="inlineStr"/>
       <c r="U151" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V151" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W151" s="12" t="inlineStr">
@@ -10809,26 +10958,26 @@
     </row>
     <row r="152" ht="26" customHeight="1">
       <c r="A152" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>20260290570</t>
+          <t>20260293379</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr"/>
@@ -10856,12 +11005,12 @@
       <c r="T152" s="11" t="inlineStr"/>
       <c r="U152" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V152" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W152" s="12" t="inlineStr">
@@ -10872,26 +11021,26 @@
     </row>
     <row r="153" ht="26" customHeight="1">
       <c r="A153" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>20260290571</t>
+          <t>20260293380</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr"/>
@@ -10919,12 +11068,12 @@
       <c r="T153" s="11" t="inlineStr"/>
       <c r="U153" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V153" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W153" s="12" t="inlineStr">
@@ -10935,26 +11084,26 @@
     </row>
     <row r="154" ht="26" customHeight="1">
       <c r="A154" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>20260290572</t>
+          <t>20260293381</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr"/>
@@ -10982,12 +11131,12 @@
       <c r="T154" s="11" t="inlineStr"/>
       <c r="U154" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V154" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W154" s="12" t="inlineStr">
@@ -10998,26 +11147,26 @@
     </row>
     <row r="155" ht="26" customHeight="1">
       <c r="A155" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>20260290573</t>
+          <t>20260293389</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr"/>
@@ -11045,12 +11194,12 @@
       <c r="T155" s="11" t="inlineStr"/>
       <c r="U155" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V155" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W155" s="12" t="inlineStr">
@@ -11061,26 +11210,26 @@
     </row>
     <row r="156" ht="26" customHeight="1">
       <c r="A156" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>20260290574</t>
+          <t>20260293438</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr"/>
@@ -11108,12 +11257,12 @@
       <c r="T156" s="11" t="inlineStr"/>
       <c r="U156" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V156" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W156" s="12" t="inlineStr">
@@ -11124,26 +11273,26 @@
     </row>
     <row r="157" ht="26" customHeight="1">
       <c r="A157" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>20260290575</t>
+          <t>20260294946</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr"/>
@@ -11171,12 +11320,12 @@
       <c r="T157" s="11" t="inlineStr"/>
       <c r="U157" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V157" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W157" s="12" t="inlineStr">
@@ -11187,26 +11336,26 @@
     </row>
     <row r="158" ht="26" customHeight="1">
       <c r="A158" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>20260290576</t>
+          <t>20260295290</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr"/>
@@ -11234,12 +11383,12 @@
       <c r="T158" s="11" t="inlineStr"/>
       <c r="U158" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V158" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W158" s="12" t="inlineStr">
@@ -11250,26 +11399,26 @@
     </row>
     <row r="159" ht="26" customHeight="1">
       <c r="A159" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>20260290577</t>
+          <t>20260296107</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr"/>
@@ -11297,12 +11446,12 @@
       <c r="T159" s="11" t="inlineStr"/>
       <c r="U159" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V159" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W159" s="12" t="inlineStr">
@@ -11313,26 +11462,26 @@
     </row>
     <row r="160" ht="26" customHeight="1">
       <c r="A160" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>20260290578</t>
+          <t>20260296110</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr"/>
@@ -11360,12 +11509,12 @@
       <c r="T160" s="11" t="inlineStr"/>
       <c r="U160" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V160" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W160" s="12" t="inlineStr">
@@ -11376,26 +11525,26 @@
     </row>
     <row r="161" ht="26" customHeight="1">
       <c r="A161" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>20260290622</t>
+          <t>20260296112</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr"/>
@@ -11423,12 +11572,12 @@
       <c r="T161" s="11" t="inlineStr"/>
       <c r="U161" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V161" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W161" s="12" t="inlineStr">
@@ -11439,26 +11588,26 @@
     </row>
     <row r="162" ht="26" customHeight="1">
       <c r="A162" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>20260290656</t>
+          <t>20260296114</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F162" s="11" t="inlineStr"/>
@@ -11486,12 +11635,12 @@
       <c r="T162" s="11" t="inlineStr"/>
       <c r="U162" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V162" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W162" s="12" t="inlineStr">
@@ -11502,26 +11651,26 @@
     </row>
     <row r="163" ht="26" customHeight="1">
       <c r="A163" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>20260290657</t>
+          <t>20260296119</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr"/>
@@ -11549,12 +11698,12 @@
       <c r="T163" s="11" t="inlineStr"/>
       <c r="U163" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V163" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W163" s="12" t="inlineStr">
@@ -11565,26 +11714,26 @@
     </row>
     <row r="164" ht="26" customHeight="1">
       <c r="A164" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>20260290720</t>
+          <t>20260296120</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr"/>
@@ -11612,12 +11761,12 @@
       <c r="T164" s="11" t="inlineStr"/>
       <c r="U164" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V164" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W164" s="12" t="inlineStr">
@@ -11628,26 +11777,26 @@
     </row>
     <row r="165" ht="26" customHeight="1">
       <c r="A165" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>20260290738</t>
+          <t>20260296121</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr"/>
@@ -11675,12 +11824,12 @@
       <c r="T165" s="11" t="inlineStr"/>
       <c r="U165" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V165" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W165" s="12" t="inlineStr">
@@ -11691,26 +11840,26 @@
     </row>
     <row r="166" ht="26" customHeight="1">
       <c r="A166" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>20260290739</t>
+          <t>20260296124</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F166" s="11" t="inlineStr"/>
@@ -11738,12 +11887,12 @@
       <c r="T166" s="11" t="inlineStr"/>
       <c r="U166" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V166" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W166" s="12" t="inlineStr">
@@ -11754,26 +11903,26 @@
     </row>
     <row r="167" ht="26" customHeight="1">
       <c r="A167" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>20260290754</t>
+          <t>20260296125</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F167" s="11" t="inlineStr"/>
@@ -11801,12 +11950,12 @@
       <c r="T167" s="11" t="inlineStr"/>
       <c r="U167" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V167" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W167" s="12" t="inlineStr">
@@ -11817,26 +11966,26 @@
     </row>
     <row r="168" ht="26" customHeight="1">
       <c r="A168" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>20260290755</t>
+          <t>20260296138</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F168" s="11" t="inlineStr"/>
@@ -11864,12 +12013,12 @@
       <c r="T168" s="11" t="inlineStr"/>
       <c r="U168" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V168" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W168" s="12" t="inlineStr">
@@ -11880,26 +12029,26 @@
     </row>
     <row r="169" ht="26" customHeight="1">
       <c r="A169" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B169" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C169" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>20260290828</t>
+          <t>20260296140</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr"/>
@@ -11927,12 +12076,12 @@
       <c r="T169" s="11" t="inlineStr"/>
       <c r="U169" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V169" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W169" s="12" t="inlineStr">
@@ -11943,26 +12092,26 @@
     </row>
     <row r="170" ht="26" customHeight="1">
       <c r="A170" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B170" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C170" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>20260290859</t>
+          <t>20260296253</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr"/>
@@ -11990,12 +12139,12 @@
       <c r="T170" s="11" t="inlineStr"/>
       <c r="U170" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V170" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W170" s="12" t="inlineStr">
@@ -12020,12 +12169,12 @@
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>20260290860</t>
+          <t>20260294942</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr"/>
@@ -12083,12 +12232,12 @@
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>20260290861</t>
+          <t>20260294954</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr"/>
@@ -12146,12 +12295,12 @@
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>20260290862</t>
+          <t>20260294955</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr"/>
@@ -12209,12 +12358,12 @@
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>20260290863</t>
+          <t>20260294956</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr"/>
@@ -12272,12 +12421,12 @@
       </c>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>20260290864</t>
+          <t>20260294957</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F175" s="11" t="inlineStr"/>
@@ -12335,12 +12484,12 @@
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>20260290865</t>
+          <t>20260294959</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F176" s="11" t="inlineStr"/>
@@ -12398,12 +12547,12 @@
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>20260290866</t>
+          <t>20260294960</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F177" s="11" t="inlineStr"/>
@@ -12461,12 +12610,12 @@
       </c>
       <c r="D178" s="11" t="inlineStr">
         <is>
-          <t>20260290867</t>
+          <t>20260294961</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F178" s="11" t="inlineStr"/>
@@ -12524,12 +12673,12 @@
       </c>
       <c r="D179" s="11" t="inlineStr">
         <is>
-          <t>20260291332</t>
+          <t>20260294962</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F179" s="11" t="inlineStr"/>
@@ -12587,12 +12736,12 @@
       </c>
       <c r="D180" s="11" t="inlineStr">
         <is>
-          <t>20260291333</t>
+          <t>20260294963</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F180" s="11" t="inlineStr"/>
@@ -12650,12 +12799,12 @@
       </c>
       <c r="D181" s="11" t="inlineStr">
         <is>
-          <t>20260291337</t>
+          <t>20260294964</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F181" s="11" t="inlineStr"/>
@@ -12713,12 +12862,12 @@
       </c>
       <c r="D182" s="11" t="inlineStr">
         <is>
-          <t>20260291340</t>
+          <t>20260294965</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr"/>
@@ -12776,12 +12925,12 @@
       </c>
       <c r="D183" s="11" t="inlineStr">
         <is>
-          <t>20260291723</t>
+          <t>20260294966</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F183" s="11" t="inlineStr"/>
@@ -12839,12 +12988,12 @@
       </c>
       <c r="D184" s="11" t="inlineStr">
         <is>
-          <t>20260291746</t>
+          <t>20260294967</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr"/>
@@ -12902,12 +13051,12 @@
       </c>
       <c r="D185" s="11" t="inlineStr">
         <is>
-          <t>20260291761</t>
+          <t>20260294968</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F185" s="11" t="inlineStr"/>
@@ -12965,12 +13114,12 @@
       </c>
       <c r="D186" s="11" t="inlineStr">
         <is>
-          <t>20260291762</t>
+          <t>20260294969</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr"/>
@@ -13028,12 +13177,12 @@
       </c>
       <c r="D187" s="11" t="inlineStr">
         <is>
-          <t>20260291763</t>
+          <t>20260294970</t>
         </is>
       </c>
       <c r="E187" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F187" s="11" t="inlineStr"/>
@@ -13091,12 +13240,12 @@
       </c>
       <c r="D188" s="11" t="inlineStr">
         <is>
-          <t>20260291831</t>
+          <t>20260294971</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F188" s="11" t="inlineStr"/>
@@ -13154,12 +13303,12 @@
       </c>
       <c r="D189" s="11" t="inlineStr">
         <is>
-          <t>20260291833</t>
+          <t>20260294972</t>
         </is>
       </c>
       <c r="E189" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F189" s="11" t="inlineStr"/>
@@ -13217,12 +13366,12 @@
       </c>
       <c r="D190" s="11" t="inlineStr">
         <is>
-          <t>20260291834</t>
+          <t>20260294973</t>
         </is>
       </c>
       <c r="E190" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F190" s="11" t="inlineStr"/>
@@ -13280,12 +13429,12 @@
       </c>
       <c r="D191" s="11" t="inlineStr">
         <is>
-          <t>20260291835</t>
+          <t>20260294974</t>
         </is>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr"/>
@@ -13343,12 +13492,12 @@
       </c>
       <c r="D192" s="11" t="inlineStr">
         <is>
-          <t>20260291890</t>
+          <t>20260294975</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F192" s="11" t="inlineStr"/>
@@ -13406,12 +13555,12 @@
       </c>
       <c r="D193" s="11" t="inlineStr">
         <is>
-          <t>20260292022</t>
+          <t>20260294976</t>
         </is>
       </c>
       <c r="E193" s="11" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="F193" s="11" t="inlineStr"/>
@@ -13453,8 +13602,1898 @@
         </is>
       </c>
     </row>
+    <row r="194" ht="26" customHeight="1">
+      <c r="A194" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B194" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C194" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D194" s="11" t="inlineStr">
+        <is>
+          <t>20260294977</t>
+        </is>
+      </c>
+      <c r="E194" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F194" s="11" t="inlineStr"/>
+      <c r="G194" s="11" t="inlineStr"/>
+      <c r="H194" s="11" t="inlineStr"/>
+      <c r="I194" s="11" t="inlineStr"/>
+      <c r="J194" s="11" t="inlineStr"/>
+      <c r="K194" s="11" t="inlineStr"/>
+      <c r="L194" s="11" t="inlineStr"/>
+      <c r="M194" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N194" s="11" t="inlineStr"/>
+      <c r="O194" s="11" t="inlineStr"/>
+      <c r="P194" s="11" t="inlineStr"/>
+      <c r="Q194" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R194" s="11" t="inlineStr"/>
+      <c r="S194" s="11" t="inlineStr"/>
+      <c r="T194" s="11" t="inlineStr"/>
+      <c r="U194" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V194" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W194" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="26" customHeight="1">
+      <c r="A195" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B195" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C195" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D195" s="11" t="inlineStr">
+        <is>
+          <t>20260294979</t>
+        </is>
+      </c>
+      <c r="E195" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F195" s="11" t="inlineStr"/>
+      <c r="G195" s="11" t="inlineStr"/>
+      <c r="H195" s="11" t="inlineStr"/>
+      <c r="I195" s="11" t="inlineStr"/>
+      <c r="J195" s="11" t="inlineStr"/>
+      <c r="K195" s="11" t="inlineStr"/>
+      <c r="L195" s="11" t="inlineStr"/>
+      <c r="M195" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N195" s="11" t="inlineStr"/>
+      <c r="O195" s="11" t="inlineStr"/>
+      <c r="P195" s="11" t="inlineStr"/>
+      <c r="Q195" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R195" s="11" t="inlineStr"/>
+      <c r="S195" s="11" t="inlineStr"/>
+      <c r="T195" s="11" t="inlineStr"/>
+      <c r="U195" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V195" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W195" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="26" customHeight="1">
+      <c r="A196" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B196" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C196" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D196" s="11" t="inlineStr">
+        <is>
+          <t>20260294980</t>
+        </is>
+      </c>
+      <c r="E196" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F196" s="11" t="inlineStr"/>
+      <c r="G196" s="11" t="inlineStr"/>
+      <c r="H196" s="11" t="inlineStr"/>
+      <c r="I196" s="11" t="inlineStr"/>
+      <c r="J196" s="11" t="inlineStr"/>
+      <c r="K196" s="11" t="inlineStr"/>
+      <c r="L196" s="11" t="inlineStr"/>
+      <c r="M196" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N196" s="11" t="inlineStr"/>
+      <c r="O196" s="11" t="inlineStr"/>
+      <c r="P196" s="11" t="inlineStr"/>
+      <c r="Q196" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R196" s="11" t="inlineStr"/>
+      <c r="S196" s="11" t="inlineStr"/>
+      <c r="T196" s="11" t="inlineStr"/>
+      <c r="U196" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V196" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W196" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="26" customHeight="1">
+      <c r="A197" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B197" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C197" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D197" s="11" t="inlineStr">
+        <is>
+          <t>20260294981</t>
+        </is>
+      </c>
+      <c r="E197" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F197" s="11" t="inlineStr"/>
+      <c r="G197" s="11" t="inlineStr"/>
+      <c r="H197" s="11" t="inlineStr"/>
+      <c r="I197" s="11" t="inlineStr"/>
+      <c r="J197" s="11" t="inlineStr"/>
+      <c r="K197" s="11" t="inlineStr"/>
+      <c r="L197" s="11" t="inlineStr"/>
+      <c r="M197" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N197" s="11" t="inlineStr"/>
+      <c r="O197" s="11" t="inlineStr"/>
+      <c r="P197" s="11" t="inlineStr"/>
+      <c r="Q197" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R197" s="11" t="inlineStr"/>
+      <c r="S197" s="11" t="inlineStr"/>
+      <c r="T197" s="11" t="inlineStr"/>
+      <c r="U197" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V197" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W197" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="198" ht="26" customHeight="1">
+      <c r="A198" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B198" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C198" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D198" s="11" t="inlineStr">
+        <is>
+          <t>20260294982</t>
+        </is>
+      </c>
+      <c r="E198" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F198" s="11" t="inlineStr"/>
+      <c r="G198" s="11" t="inlineStr"/>
+      <c r="H198" s="11" t="inlineStr"/>
+      <c r="I198" s="11" t="inlineStr"/>
+      <c r="J198" s="11" t="inlineStr"/>
+      <c r="K198" s="11" t="inlineStr"/>
+      <c r="L198" s="11" t="inlineStr"/>
+      <c r="M198" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N198" s="11" t="inlineStr"/>
+      <c r="O198" s="11" t="inlineStr"/>
+      <c r="P198" s="11" t="inlineStr"/>
+      <c r="Q198" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R198" s="11" t="inlineStr"/>
+      <c r="S198" s="11" t="inlineStr"/>
+      <c r="T198" s="11" t="inlineStr"/>
+      <c r="U198" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V198" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W198" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="26" customHeight="1">
+      <c r="A199" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B199" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C199" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D199" s="11" t="inlineStr">
+        <is>
+          <t>20260294983</t>
+        </is>
+      </c>
+      <c r="E199" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F199" s="11" t="inlineStr"/>
+      <c r="G199" s="11" t="inlineStr"/>
+      <c r="H199" s="11" t="inlineStr"/>
+      <c r="I199" s="11" t="inlineStr"/>
+      <c r="J199" s="11" t="inlineStr"/>
+      <c r="K199" s="11" t="inlineStr"/>
+      <c r="L199" s="11" t="inlineStr"/>
+      <c r="M199" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N199" s="11" t="inlineStr"/>
+      <c r="O199" s="11" t="inlineStr"/>
+      <c r="P199" s="11" t="inlineStr"/>
+      <c r="Q199" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R199" s="11" t="inlineStr"/>
+      <c r="S199" s="11" t="inlineStr"/>
+      <c r="T199" s="11" t="inlineStr"/>
+      <c r="U199" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V199" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W199" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="26" customHeight="1">
+      <c r="A200" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B200" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C200" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D200" s="11" t="inlineStr">
+        <is>
+          <t>20260294984</t>
+        </is>
+      </c>
+      <c r="E200" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F200" s="11" t="inlineStr"/>
+      <c r="G200" s="11" t="inlineStr"/>
+      <c r="H200" s="11" t="inlineStr"/>
+      <c r="I200" s="11" t="inlineStr"/>
+      <c r="J200" s="11" t="inlineStr"/>
+      <c r="K200" s="11" t="inlineStr"/>
+      <c r="L200" s="11" t="inlineStr"/>
+      <c r="M200" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N200" s="11" t="inlineStr"/>
+      <c r="O200" s="11" t="inlineStr"/>
+      <c r="P200" s="11" t="inlineStr"/>
+      <c r="Q200" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R200" s="11" t="inlineStr"/>
+      <c r="S200" s="11" t="inlineStr"/>
+      <c r="T200" s="11" t="inlineStr"/>
+      <c r="U200" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V200" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W200" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="26" customHeight="1">
+      <c r="A201" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B201" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C201" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D201" s="11" t="inlineStr">
+        <is>
+          <t>20260294985</t>
+        </is>
+      </c>
+      <c r="E201" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F201" s="11" t="inlineStr"/>
+      <c r="G201" s="11" t="inlineStr"/>
+      <c r="H201" s="11" t="inlineStr"/>
+      <c r="I201" s="11" t="inlineStr"/>
+      <c r="J201" s="11" t="inlineStr"/>
+      <c r="K201" s="11" t="inlineStr"/>
+      <c r="L201" s="11" t="inlineStr"/>
+      <c r="M201" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N201" s="11" t="inlineStr"/>
+      <c r="O201" s="11" t="inlineStr"/>
+      <c r="P201" s="11" t="inlineStr"/>
+      <c r="Q201" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R201" s="11" t="inlineStr"/>
+      <c r="S201" s="11" t="inlineStr"/>
+      <c r="T201" s="11" t="inlineStr"/>
+      <c r="U201" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V201" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W201" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="26" customHeight="1">
+      <c r="A202" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B202" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C202" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D202" s="11" t="inlineStr">
+        <is>
+          <t>20260294986</t>
+        </is>
+      </c>
+      <c r="E202" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F202" s="11" t="inlineStr"/>
+      <c r="G202" s="11" t="inlineStr"/>
+      <c r="H202" s="11" t="inlineStr"/>
+      <c r="I202" s="11" t="inlineStr"/>
+      <c r="J202" s="11" t="inlineStr"/>
+      <c r="K202" s="11" t="inlineStr"/>
+      <c r="L202" s="11" t="inlineStr"/>
+      <c r="M202" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N202" s="11" t="inlineStr"/>
+      <c r="O202" s="11" t="inlineStr"/>
+      <c r="P202" s="11" t="inlineStr"/>
+      <c r="Q202" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R202" s="11" t="inlineStr"/>
+      <c r="S202" s="11" t="inlineStr"/>
+      <c r="T202" s="11" t="inlineStr"/>
+      <c r="U202" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V202" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W202" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="26" customHeight="1">
+      <c r="A203" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B203" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C203" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D203" s="11" t="inlineStr">
+        <is>
+          <t>20260294987</t>
+        </is>
+      </c>
+      <c r="E203" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F203" s="11" t="inlineStr"/>
+      <c r="G203" s="11" t="inlineStr"/>
+      <c r="H203" s="11" t="inlineStr"/>
+      <c r="I203" s="11" t="inlineStr"/>
+      <c r="J203" s="11" t="inlineStr"/>
+      <c r="K203" s="11" t="inlineStr"/>
+      <c r="L203" s="11" t="inlineStr"/>
+      <c r="M203" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N203" s="11" t="inlineStr"/>
+      <c r="O203" s="11" t="inlineStr"/>
+      <c r="P203" s="11" t="inlineStr"/>
+      <c r="Q203" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R203" s="11" t="inlineStr"/>
+      <c r="S203" s="11" t="inlineStr"/>
+      <c r="T203" s="11" t="inlineStr"/>
+      <c r="U203" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V203" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W203" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="26" customHeight="1">
+      <c r="A204" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B204" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C204" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D204" s="11" t="inlineStr">
+        <is>
+          <t>20260294988</t>
+        </is>
+      </c>
+      <c r="E204" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F204" s="11" t="inlineStr"/>
+      <c r="G204" s="11" t="inlineStr"/>
+      <c r="H204" s="11" t="inlineStr"/>
+      <c r="I204" s="11" t="inlineStr"/>
+      <c r="J204" s="11" t="inlineStr"/>
+      <c r="K204" s="11" t="inlineStr"/>
+      <c r="L204" s="11" t="inlineStr"/>
+      <c r="M204" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N204" s="11" t="inlineStr"/>
+      <c r="O204" s="11" t="inlineStr"/>
+      <c r="P204" s="11" t="inlineStr"/>
+      <c r="Q204" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R204" s="11" t="inlineStr"/>
+      <c r="S204" s="11" t="inlineStr"/>
+      <c r="T204" s="11" t="inlineStr"/>
+      <c r="U204" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V204" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W204" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="26" customHeight="1">
+      <c r="A205" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B205" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C205" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D205" s="11" t="inlineStr">
+        <is>
+          <t>20260294989</t>
+        </is>
+      </c>
+      <c r="E205" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F205" s="11" t="inlineStr"/>
+      <c r="G205" s="11" t="inlineStr"/>
+      <c r="H205" s="11" t="inlineStr"/>
+      <c r="I205" s="11" t="inlineStr"/>
+      <c r="J205" s="11" t="inlineStr"/>
+      <c r="K205" s="11" t="inlineStr"/>
+      <c r="L205" s="11" t="inlineStr"/>
+      <c r="M205" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N205" s="11" t="inlineStr"/>
+      <c r="O205" s="11" t="inlineStr"/>
+      <c r="P205" s="11" t="inlineStr"/>
+      <c r="Q205" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R205" s="11" t="inlineStr"/>
+      <c r="S205" s="11" t="inlineStr"/>
+      <c r="T205" s="11" t="inlineStr"/>
+      <c r="U205" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V205" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W205" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="26" customHeight="1">
+      <c r="A206" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B206" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C206" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D206" s="11" t="inlineStr">
+        <is>
+          <t>20260294996</t>
+        </is>
+      </c>
+      <c r="E206" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F206" s="11" t="inlineStr"/>
+      <c r="G206" s="11" t="inlineStr"/>
+      <c r="H206" s="11" t="inlineStr"/>
+      <c r="I206" s="11" t="inlineStr"/>
+      <c r="J206" s="11" t="inlineStr"/>
+      <c r="K206" s="11" t="inlineStr"/>
+      <c r="L206" s="11" t="inlineStr"/>
+      <c r="M206" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N206" s="11" t="inlineStr"/>
+      <c r="O206" s="11" t="inlineStr"/>
+      <c r="P206" s="11" t="inlineStr"/>
+      <c r="Q206" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R206" s="11" t="inlineStr"/>
+      <c r="S206" s="11" t="inlineStr"/>
+      <c r="T206" s="11" t="inlineStr"/>
+      <c r="U206" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V206" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W206" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="26" customHeight="1">
+      <c r="A207" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B207" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C207" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D207" s="11" t="inlineStr">
+        <is>
+          <t>20260295050</t>
+        </is>
+      </c>
+      <c r="E207" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F207" s="11" t="inlineStr"/>
+      <c r="G207" s="11" t="inlineStr"/>
+      <c r="H207" s="11" t="inlineStr"/>
+      <c r="I207" s="11" t="inlineStr"/>
+      <c r="J207" s="11" t="inlineStr"/>
+      <c r="K207" s="11" t="inlineStr"/>
+      <c r="L207" s="11" t="inlineStr"/>
+      <c r="M207" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N207" s="11" t="inlineStr"/>
+      <c r="O207" s="11" t="inlineStr"/>
+      <c r="P207" s="11" t="inlineStr"/>
+      <c r="Q207" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R207" s="11" t="inlineStr"/>
+      <c r="S207" s="11" t="inlineStr"/>
+      <c r="T207" s="11" t="inlineStr"/>
+      <c r="U207" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V207" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W207" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="26" customHeight="1">
+      <c r="A208" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B208" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C208" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D208" s="11" t="inlineStr">
+        <is>
+          <t>20260295053</t>
+        </is>
+      </c>
+      <c r="E208" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F208" s="11" t="inlineStr"/>
+      <c r="G208" s="11" t="inlineStr"/>
+      <c r="H208" s="11" t="inlineStr"/>
+      <c r="I208" s="11" t="inlineStr"/>
+      <c r="J208" s="11" t="inlineStr"/>
+      <c r="K208" s="11" t="inlineStr"/>
+      <c r="L208" s="11" t="inlineStr"/>
+      <c r="M208" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N208" s="11" t="inlineStr"/>
+      <c r="O208" s="11" t="inlineStr"/>
+      <c r="P208" s="11" t="inlineStr"/>
+      <c r="Q208" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R208" s="11" t="inlineStr"/>
+      <c r="S208" s="11" t="inlineStr"/>
+      <c r="T208" s="11" t="inlineStr"/>
+      <c r="U208" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V208" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W208" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="209" ht="26" customHeight="1">
+      <c r="A209" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B209" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C209" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D209" s="11" t="inlineStr">
+        <is>
+          <t>20260295287</t>
+        </is>
+      </c>
+      <c r="E209" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F209" s="11" t="inlineStr"/>
+      <c r="G209" s="11" t="inlineStr"/>
+      <c r="H209" s="11" t="inlineStr"/>
+      <c r="I209" s="11" t="inlineStr"/>
+      <c r="J209" s="11" t="inlineStr"/>
+      <c r="K209" s="11" t="inlineStr"/>
+      <c r="L209" s="11" t="inlineStr"/>
+      <c r="M209" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N209" s="11" t="inlineStr"/>
+      <c r="O209" s="11" t="inlineStr"/>
+      <c r="P209" s="11" t="inlineStr"/>
+      <c r="Q209" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R209" s="11" t="inlineStr"/>
+      <c r="S209" s="11" t="inlineStr"/>
+      <c r="T209" s="11" t="inlineStr"/>
+      <c r="U209" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V209" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W209" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="26" customHeight="1">
+      <c r="A210" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B210" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C210" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D210" s="11" t="inlineStr">
+        <is>
+          <t>20260295289</t>
+        </is>
+      </c>
+      <c r="E210" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F210" s="11" t="inlineStr"/>
+      <c r="G210" s="11" t="inlineStr"/>
+      <c r="H210" s="11" t="inlineStr"/>
+      <c r="I210" s="11" t="inlineStr"/>
+      <c r="J210" s="11" t="inlineStr"/>
+      <c r="K210" s="11" t="inlineStr"/>
+      <c r="L210" s="11" t="inlineStr"/>
+      <c r="M210" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N210" s="11" t="inlineStr"/>
+      <c r="O210" s="11" t="inlineStr"/>
+      <c r="P210" s="11" t="inlineStr"/>
+      <c r="Q210" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R210" s="11" t="inlineStr"/>
+      <c r="S210" s="11" t="inlineStr"/>
+      <c r="T210" s="11" t="inlineStr"/>
+      <c r="U210" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V210" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W210" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="26" customHeight="1">
+      <c r="A211" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B211" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C211" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D211" s="11" t="inlineStr">
+        <is>
+          <t>20260295292</t>
+        </is>
+      </c>
+      <c r="E211" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F211" s="11" t="inlineStr"/>
+      <c r="G211" s="11" t="inlineStr"/>
+      <c r="H211" s="11" t="inlineStr"/>
+      <c r="I211" s="11" t="inlineStr"/>
+      <c r="J211" s="11" t="inlineStr"/>
+      <c r="K211" s="11" t="inlineStr"/>
+      <c r="L211" s="11" t="inlineStr"/>
+      <c r="M211" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N211" s="11" t="inlineStr"/>
+      <c r="O211" s="11" t="inlineStr"/>
+      <c r="P211" s="11" t="inlineStr"/>
+      <c r="Q211" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R211" s="11" t="inlineStr"/>
+      <c r="S211" s="11" t="inlineStr"/>
+      <c r="T211" s="11" t="inlineStr"/>
+      <c r="U211" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V211" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W211" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="26" customHeight="1">
+      <c r="A212" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B212" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C212" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D212" s="11" t="inlineStr">
+        <is>
+          <t>20260295352</t>
+        </is>
+      </c>
+      <c r="E212" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F212" s="11" t="inlineStr"/>
+      <c r="G212" s="11" t="inlineStr"/>
+      <c r="H212" s="11" t="inlineStr"/>
+      <c r="I212" s="11" t="inlineStr"/>
+      <c r="J212" s="11" t="inlineStr"/>
+      <c r="K212" s="11" t="inlineStr"/>
+      <c r="L212" s="11" t="inlineStr"/>
+      <c r="M212" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N212" s="11" t="inlineStr"/>
+      <c r="O212" s="11" t="inlineStr"/>
+      <c r="P212" s="11" t="inlineStr"/>
+      <c r="Q212" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R212" s="11" t="inlineStr"/>
+      <c r="S212" s="11" t="inlineStr"/>
+      <c r="T212" s="11" t="inlineStr"/>
+      <c r="U212" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V212" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W212" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="26" customHeight="1">
+      <c r="A213" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B213" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C213" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D213" s="11" t="inlineStr">
+        <is>
+          <t>20260295705</t>
+        </is>
+      </c>
+      <c r="E213" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F213" s="11" t="inlineStr"/>
+      <c r="G213" s="11" t="inlineStr"/>
+      <c r="H213" s="11" t="inlineStr"/>
+      <c r="I213" s="11" t="inlineStr"/>
+      <c r="J213" s="11" t="inlineStr"/>
+      <c r="K213" s="11" t="inlineStr"/>
+      <c r="L213" s="11" t="inlineStr"/>
+      <c r="M213" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N213" s="11" t="inlineStr"/>
+      <c r="O213" s="11" t="inlineStr"/>
+      <c r="P213" s="11" t="inlineStr"/>
+      <c r="Q213" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R213" s="11" t="inlineStr"/>
+      <c r="S213" s="11" t="inlineStr"/>
+      <c r="T213" s="11" t="inlineStr"/>
+      <c r="U213" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V213" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W213" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="26" customHeight="1">
+      <c r="A214" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B214" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C214" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D214" s="11" t="inlineStr">
+        <is>
+          <t>20260296214</t>
+        </is>
+      </c>
+      <c r="E214" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F214" s="11" t="inlineStr"/>
+      <c r="G214" s="11" t="inlineStr"/>
+      <c r="H214" s="11" t="inlineStr"/>
+      <c r="I214" s="11" t="inlineStr"/>
+      <c r="J214" s="11" t="inlineStr"/>
+      <c r="K214" s="11" t="inlineStr"/>
+      <c r="L214" s="11" t="inlineStr"/>
+      <c r="M214" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N214" s="11" t="inlineStr"/>
+      <c r="O214" s="11" t="inlineStr"/>
+      <c r="P214" s="11" t="inlineStr"/>
+      <c r="Q214" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R214" s="11" t="inlineStr"/>
+      <c r="S214" s="11" t="inlineStr"/>
+      <c r="T214" s="11" t="inlineStr"/>
+      <c r="U214" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V214" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W214" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="26" customHeight="1">
+      <c r="A215" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B215" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C215" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D215" s="11" t="inlineStr">
+        <is>
+          <t>20260296217</t>
+        </is>
+      </c>
+      <c r="E215" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F215" s="11" t="inlineStr"/>
+      <c r="G215" s="11" t="inlineStr"/>
+      <c r="H215" s="11" t="inlineStr"/>
+      <c r="I215" s="11" t="inlineStr"/>
+      <c r="J215" s="11" t="inlineStr"/>
+      <c r="K215" s="11" t="inlineStr"/>
+      <c r="L215" s="11" t="inlineStr"/>
+      <c r="M215" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N215" s="11" t="inlineStr"/>
+      <c r="O215" s="11" t="inlineStr"/>
+      <c r="P215" s="11" t="inlineStr"/>
+      <c r="Q215" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R215" s="11" t="inlineStr"/>
+      <c r="S215" s="11" t="inlineStr"/>
+      <c r="T215" s="11" t="inlineStr"/>
+      <c r="U215" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V215" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W215" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="26" customHeight="1">
+      <c r="A216" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B216" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C216" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D216" s="11" t="inlineStr">
+        <is>
+          <t>20260296230</t>
+        </is>
+      </c>
+      <c r="E216" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F216" s="11" t="inlineStr"/>
+      <c r="G216" s="11" t="inlineStr"/>
+      <c r="H216" s="11" t="inlineStr"/>
+      <c r="I216" s="11" t="inlineStr"/>
+      <c r="J216" s="11" t="inlineStr"/>
+      <c r="K216" s="11" t="inlineStr"/>
+      <c r="L216" s="11" t="inlineStr"/>
+      <c r="M216" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N216" s="11" t="inlineStr"/>
+      <c r="O216" s="11" t="inlineStr"/>
+      <c r="P216" s="11" t="inlineStr"/>
+      <c r="Q216" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R216" s="11" t="inlineStr"/>
+      <c r="S216" s="11" t="inlineStr"/>
+      <c r="T216" s="11" t="inlineStr"/>
+      <c r="U216" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V216" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W216" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="26" customHeight="1">
+      <c r="A217" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B217" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C217" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D217" s="11" t="inlineStr">
+        <is>
+          <t>20260296231</t>
+        </is>
+      </c>
+      <c r="E217" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F217" s="11" t="inlineStr"/>
+      <c r="G217" s="11" t="inlineStr"/>
+      <c r="H217" s="11" t="inlineStr"/>
+      <c r="I217" s="11" t="inlineStr"/>
+      <c r="J217" s="11" t="inlineStr"/>
+      <c r="K217" s="11" t="inlineStr"/>
+      <c r="L217" s="11" t="inlineStr"/>
+      <c r="M217" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N217" s="11" t="inlineStr"/>
+      <c r="O217" s="11" t="inlineStr"/>
+      <c r="P217" s="11" t="inlineStr"/>
+      <c r="Q217" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R217" s="11" t="inlineStr"/>
+      <c r="S217" s="11" t="inlineStr"/>
+      <c r="T217" s="11" t="inlineStr"/>
+      <c r="U217" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V217" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W217" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="26" customHeight="1">
+      <c r="A218" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B218" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C218" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D218" s="11" t="inlineStr">
+        <is>
+          <t>20260296235</t>
+        </is>
+      </c>
+      <c r="E218" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F218" s="11" t="inlineStr"/>
+      <c r="G218" s="11" t="inlineStr"/>
+      <c r="H218" s="11" t="inlineStr"/>
+      <c r="I218" s="11" t="inlineStr"/>
+      <c r="J218" s="11" t="inlineStr"/>
+      <c r="K218" s="11" t="inlineStr"/>
+      <c r="L218" s="11" t="inlineStr"/>
+      <c r="M218" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N218" s="11" t="inlineStr"/>
+      <c r="O218" s="11" t="inlineStr"/>
+      <c r="P218" s="11" t="inlineStr"/>
+      <c r="Q218" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R218" s="11" t="inlineStr"/>
+      <c r="S218" s="11" t="inlineStr"/>
+      <c r="T218" s="11" t="inlineStr"/>
+      <c r="U218" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V218" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W218" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="26" customHeight="1">
+      <c r="A219" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B219" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C219" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D219" s="11" t="inlineStr">
+        <is>
+          <t>20260296239</t>
+        </is>
+      </c>
+      <c r="E219" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F219" s="11" t="inlineStr"/>
+      <c r="G219" s="11" t="inlineStr"/>
+      <c r="H219" s="11" t="inlineStr"/>
+      <c r="I219" s="11" t="inlineStr"/>
+      <c r="J219" s="11" t="inlineStr"/>
+      <c r="K219" s="11" t="inlineStr"/>
+      <c r="L219" s="11" t="inlineStr"/>
+      <c r="M219" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N219" s="11" t="inlineStr"/>
+      <c r="O219" s="11" t="inlineStr"/>
+      <c r="P219" s="11" t="inlineStr"/>
+      <c r="Q219" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R219" s="11" t="inlineStr"/>
+      <c r="S219" s="11" t="inlineStr"/>
+      <c r="T219" s="11" t="inlineStr"/>
+      <c r="U219" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V219" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W219" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="220" ht="26" customHeight="1">
+      <c r="A220" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B220" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C220" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D220" s="11" t="inlineStr">
+        <is>
+          <t>20260296266</t>
+        </is>
+      </c>
+      <c r="E220" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F220" s="11" t="inlineStr"/>
+      <c r="G220" s="11" t="inlineStr"/>
+      <c r="H220" s="11" t="inlineStr"/>
+      <c r="I220" s="11" t="inlineStr"/>
+      <c r="J220" s="11" t="inlineStr"/>
+      <c r="K220" s="11" t="inlineStr"/>
+      <c r="L220" s="11" t="inlineStr"/>
+      <c r="M220" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N220" s="11" t="inlineStr"/>
+      <c r="O220" s="11" t="inlineStr"/>
+      <c r="P220" s="11" t="inlineStr"/>
+      <c r="Q220" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R220" s="11" t="inlineStr"/>
+      <c r="S220" s="11" t="inlineStr"/>
+      <c r="T220" s="11" t="inlineStr"/>
+      <c r="U220" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V220" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W220" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="26" customHeight="1">
+      <c r="A221" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B221" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C221" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D221" s="11" t="inlineStr">
+        <is>
+          <t>20260296270</t>
+        </is>
+      </c>
+      <c r="E221" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F221" s="11" t="inlineStr"/>
+      <c r="G221" s="11" t="inlineStr"/>
+      <c r="H221" s="11" t="inlineStr"/>
+      <c r="I221" s="11" t="inlineStr"/>
+      <c r="J221" s="11" t="inlineStr"/>
+      <c r="K221" s="11" t="inlineStr"/>
+      <c r="L221" s="11" t="inlineStr"/>
+      <c r="M221" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N221" s="11" t="inlineStr"/>
+      <c r="O221" s="11" t="inlineStr"/>
+      <c r="P221" s="11" t="inlineStr"/>
+      <c r="Q221" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R221" s="11" t="inlineStr"/>
+      <c r="S221" s="11" t="inlineStr"/>
+      <c r="T221" s="11" t="inlineStr"/>
+      <c r="U221" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V221" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W221" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="26" customHeight="1">
+      <c r="A222" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B222" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C222" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D222" s="11" t="inlineStr">
+        <is>
+          <t>20260296272</t>
+        </is>
+      </c>
+      <c r="E222" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F222" s="11" t="inlineStr"/>
+      <c r="G222" s="11" t="inlineStr"/>
+      <c r="H222" s="11" t="inlineStr"/>
+      <c r="I222" s="11" t="inlineStr"/>
+      <c r="J222" s="11" t="inlineStr"/>
+      <c r="K222" s="11" t="inlineStr"/>
+      <c r="L222" s="11" t="inlineStr"/>
+      <c r="M222" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N222" s="11" t="inlineStr"/>
+      <c r="O222" s="11" t="inlineStr"/>
+      <c r="P222" s="11" t="inlineStr"/>
+      <c r="Q222" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R222" s="11" t="inlineStr"/>
+      <c r="S222" s="11" t="inlineStr"/>
+      <c r="T222" s="11" t="inlineStr"/>
+      <c r="U222" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V222" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W222" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="26" customHeight="1">
+      <c r="A223" s="10" t="n">
+        <v>42</v>
+      </c>
+      <c r="B223" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C223" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D223" s="11" t="inlineStr">
+        <is>
+          <t>20260296376</t>
+        </is>
+      </c>
+      <c r="E223" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="F223" s="11" t="inlineStr"/>
+      <c r="G223" s="11" t="inlineStr"/>
+      <c r="H223" s="11" t="inlineStr"/>
+      <c r="I223" s="11" t="inlineStr"/>
+      <c r="J223" s="11" t="inlineStr"/>
+      <c r="K223" s="11" t="inlineStr"/>
+      <c r="L223" s="11" t="inlineStr"/>
+      <c r="M223" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N223" s="11" t="inlineStr"/>
+      <c r="O223" s="11" t="inlineStr"/>
+      <c r="P223" s="11" t="inlineStr"/>
+      <c r="Q223" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R223" s="11" t="inlineStr"/>
+      <c r="S223" s="11" t="inlineStr"/>
+      <c r="T223" s="11" t="inlineStr"/>
+      <c r="U223" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V223" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W223" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W193"/>
+  <autoFilter ref="A1:W223"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
@@ -13648,6 +15687,36 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W191" r:id="rId190"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W192" r:id="rId191"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W223" r:id="rId222"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13667,7 +15736,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Maricopa County Motivated Seller Leads</t>
         </is>
@@ -13676,168 +15745,168 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-05-15 04:53</t>
+          <t>Run: 2026-05-16 04:34</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr"/>
-      <c r="B3" s="14" t="inlineStr"/>
+      <c r="A3" s="15" t="inlineStr"/>
+      <c r="B3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Total Leads</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
-        <v>192</v>
+      <c r="B4" s="15" t="n">
+        <v>222</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>With Property Address</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
-        <v>13</v>
+      <c r="B5" s="15" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>With Mailing Address</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>PDF Parsed</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
-        <v>122</v>
+      <c r="B7" s="15" t="n">
+        <v>152</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Score 70+ (Hot)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
-        <v>11</v>
+      <c r="B8" s="15" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Score 50-69 (Warm)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
-        <v>8</v>
+      <c r="B9" s="15" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="inlineStr"/>
-      <c r="B10" s="14" t="inlineStr"/>
+      <c r="A10" s="15" t="inlineStr"/>
+      <c r="B10" s="15" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="inlineStr">
+      <c r="A11" s="16" t="inlineStr">
         <is>
           <t>By Category</t>
         </is>
       </c>
-      <c r="B11" s="14" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>Medical Lien</t>
         </is>
       </c>
-      <c r="B12" s="14" t="n">
-        <v>89</v>
+      <c r="B12" s="15" t="n">
+        <v>86</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="inlineStr">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
         <is>
           <t>Judgment</t>
         </is>
       </c>
-      <c r="B13" s="14" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>22</v>
+      <c r="B14" s="15" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="inlineStr">
+      <c r="A15" s="16" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="B15" s="14" t="n">
-        <v>19</v>
+      <c r="B15" s="15" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Tax Deed</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="B18" s="15" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>Lis Pendens</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Probate Document</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Mechanic Lien</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="n">
-        <v>4</v>
+      <c r="B19" s="15" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-05-17 04:56</t>
+          <t>Run: 2026-05-18 05:05</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$195</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$159</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W195"/>
+  <dimension ref="A1:W159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -705,22 +705,26 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>20260300812</t>
+          <t>20260303938</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>SHAWN CARROLL</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr"/>
+          <t>IFEANYI WILLSON</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>LAKEVIEW LOAN SERVICING, LLC</t>
+        </is>
+      </c>
       <c r="H2" s="4" t="n">
-        <v>234025</v>
+        <v>144000</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -729,17 +733,17 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building Maricopa County Courthouse</t>
+          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2024 S BALDWIN Unit 36</t>
+          <t>2225 E. VISTA DR</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>MESA</t>
+          <t>PHOENIX</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -749,7 +753,7 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>85209</t>
+          <t>85022</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
@@ -760,14 +764,10 @@
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>312-10-362</t>
-        </is>
-      </c>
+      <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>America West Lender Services, LLC .</t>
+          <t>Prime Recon LLC</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -802,57 +802,45 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>20260300865</t>
+          <t>20260305019</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>JEFFREY TODD DOUGLAS AND JENNIFER A. DOUGLAS</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>ROCKET MORTGAGE, LLC S/B/M NATIONSTAR MORTGAGE LLC D/B/A MR. COOPER</t>
-        </is>
-      </c>
+          <t>Vivek Kumar Srivastava and Shika Srivastava</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
       <c r="H3" s="4" t="n">
-        <v>312957</v>
+        <v>320336</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>12646 W PALMAIRE AVE</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>GLENDALE</t>
-        </is>
-      </c>
+          <t>7821 SOUTH 23RD WAY</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr"/>
       <c r="M3" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>85307</t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="inlineStr"/>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
@@ -861,10 +849,14 @@
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>301-30-381</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>America West Lender Services, LLC</t>
+          <t>Entra Default Solutions, LLC</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -899,30 +891,30 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>20260301245</t>
+          <t>20260305058</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MICHAEL JAMES MALONE</t>
+          <t>Corbin Gary Matthews and Amy Elizabeth Matthews</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Freedom Mortgage Corporation</t>
+          <t>(as of recording of Notice of Sale)</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>332220</v>
+        <v>150000</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -932,24 +924,16 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2028 W MEDLOCK DR</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
+          <t>2980 EAST BOOT TRACK TRAIL</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>85015</t>
-        </is>
-      </c>
+      <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr">
@@ -960,12 +944,12 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>153-23-1126</t>
+          <t>304-20-481</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Kim Quam, a member of the State Bar of Arizona</t>
+          <t>Entra Default Solutions, LLC</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -1000,57 +984,45 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>20260301274</t>
+          <t>20260305239</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CHRISTOPHER BOYD and VANIA BOYD</t>
+          <t>Robert J Newman</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Freedom Mortgage Corporation</t>
+          <t>U.S. Bank TrustNational Association, not in its Current Trustee:</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>570000</v>
+        <v>256000</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr"/>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>18225 W PIERSON ST</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>GOODYEAR</t>
-        </is>
-      </c>
+          <t>2651 E Los Alamos Ct</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>85395</t>
-        </is>
-      </c>
+      <c r="N5" s="3" t="inlineStr"/>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr">
@@ -1061,12 +1033,12 @@
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>502-93-51402</t>
+          <t>304-40-6631</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Kim Quam, a member of the State Bar of Arizona</t>
+          <t>individual capacity, but solely in its capacity as trustee Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1101,57 +1073,45 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>20260301376</t>
+          <t>20260305338</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>JOEL FELIX IRIBE, AMARRIED MAN AS HIS SOLE AND SEPARATE PROPERTY</t>
+          <t>Eugene Rushing and Brenda Rushing</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Freedom Mortgage Corporation</t>
+          <t>Metropolitan Life Insurance Company Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>363399</v>
+        <v>452000</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr"/>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>822 E Calle Bolo Ln</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
-        <is>
-          <t>Goodyear</t>
-        </is>
-      </c>
+          <t>13227 W Annika Dr</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>85338</t>
-        </is>
-      </c>
+      <c r="N6" s="3" t="inlineStr"/>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
@@ -1162,12 +1122,12 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>500-03-10432</t>
+          <t>508-08-0569</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Kim Quam, a member of the State Bar of Arizona</t>
+          <t>Metropolitan Life Insurance Company Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1202,57 +1162,49 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>20260301539</t>
+          <t>20260305345</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>ELIZABETH SASSE</t>
+          <t>Abbey Adams</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Freedom Mortgage Corporation</t>
+          <t>NewRez LLC Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>325600</v>
+        <v>204232</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>895 SOUTH NEWPORT STREET</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr">
-        <is>
-          <t>CHANDLER</t>
-        </is>
-      </c>
+          <t>20268 N. 64th Ave</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr">
-        <is>
-          <t>85225</t>
-        </is>
-      </c>
+      <c r="N7" s="3" t="inlineStr"/>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
@@ -1263,12 +1215,12 @@
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>303-82-15462</t>
+          <t>231-16-3660</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Kim Quam, a member of the State Bar of Arizona</t>
+          <t>NewRez LLC Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1303,57 +1255,49 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>20260301725</t>
+          <t>20260305366</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>CARMENAMANDA JULIE MAESTAS, UNMARRIED WOMAN</t>
+          <t>Martin C Reyes and Marcella A Reyes</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Freedom Mortgage Corporation</t>
+          <t>U.S. Bank National Association Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>242526</v>
+        <v>389448</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>3810 West Harrison Street</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Chandler</t>
-        </is>
-      </c>
+          <t>16340 W Moreland St</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>85226</t>
-        </is>
-      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
@@ -1364,12 +1308,12 @@
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>301-64-5359</t>
+          <t>500-09-1962</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Kim Quam, a member of the State Bar of Arizona</t>
+          <t>U.S. Bank National Association Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1404,26 +1348,26 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>20260301900</t>
+          <t>20260305404</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>DONALD I PEREZ GUTIERREZ</t>
+          <t>PAUL HORTON, UNMARRIED MAN</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>Planet Home Lending, LLC</t>
+          <t>Lakeview Loan Servicing, LLC, By LoanCare, LLC, As Attorney In Fact Under A Limited Power of</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>296530</v>
+        <v>196840</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
@@ -1437,24 +1381,16 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>5625 SOUTH 19TH PLACE</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
+          <t>695 S 93RD WAY</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>85040</t>
-        </is>
-      </c>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr">
@@ -1465,12 +1401,12 @@
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>122-50-085</t>
+          <t>220-70-5614</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>Erin K. Sweeney, a member of the State Bar of</t>
+          <t>Erin K. Sweeney, a member of the State Bar of Arizona</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1505,36 +1441,40 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>20260302088</t>
+          <t>20260305410</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>Timothy D Haverluck</t>
+          <t>DULCE A MENDEZ-TIRADO</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>U.S. Bank/PRET/2024-RPL2 Leonard J. McDonald</t>
+          <t>Lakeview Loan Servicing, LLC, By LoanCare, LLC, As Attorney In Fact Under A Limited Power of</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>163100</v>
+        <v>245217</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr"/>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>7431 W Sanna St</t>
+          <t>9026 W MULBERRY DR</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr"/>
@@ -1554,12 +1494,12 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>143-10-5823</t>
+          <t>102-23-7419</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>U.S. Bank/PRET/2024-RPL2 Leonard J. McDonald</t>
+          <t>Erin K. Sweeney, a member of the State Bar of Arizona</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1594,40 +1534,40 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>20260302120</t>
+          <t>20260305925</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>BLAKE JOHNSON</t>
+          <t>Araceli Martinez Franco</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>loanDepot.com, LLC</t>
+          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>330000</v>
+        <v>352000</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>2780 N. ACACIA WAY</t>
+          <t>6313 N 29th Ave</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr"/>
@@ -1647,12 +1587,12 @@
       <c r="R11" s="3" t="inlineStr"/>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>502-86-1657</t>
+          <t>152-14-008</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>Erin K. Sweeney, a member of the State Bar of Arizona</t>
+          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1687,49 +1627,45 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>20260302151</t>
+          <t>20260306600</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Douglas Summit Brown and Barbara Sue Mackerman</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Carrington Mortgage Services, LLC</t>
-        </is>
-      </c>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr"/>
+      <c r="G12" s="3" t="inlineStr"/>
       <c r="H12" s="4" t="n">
-        <v>1010100</v>
+        <v>2362500</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Superior Court Building located at 201 West Jefferson</t>
-        </is>
-      </c>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>7503 EAST TORREY POINT CIRCLE</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
+          <t>33011 North 141 Street</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr"/>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>85262</t>
+        </is>
+      </c>
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr"/>
       <c r="Q12" s="3" t="inlineStr">
@@ -1738,12 +1674,12 @@
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>Vylla Solutions, LLC</t>
-        </is>
-      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>219-36-148</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr"/>
       <c r="U12" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -1761,174 +1697,158 @@
       </c>
     </row>
     <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="A13" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>20260302396</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr"/>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Trust, dated May 3, 2022, and any amendments thereto.</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>316200</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>714.N. 96" St.</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>Mesa</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>85207</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr"/>
-      <c r="P13" s="3" t="inlineStr"/>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr"/>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t>220-21-052</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr"/>
-      <c r="U13" s="3" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>20260304021</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>ROCKET MORTGAGE, LLC</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>417000</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr"/>
+      <c r="S13" s="7" t="inlineStr"/>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>Prime Recon LLC</t>
+        </is>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V13" s="3" t="inlineStr">
+      <c r="V13" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" s="5" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="A14" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>20260303137</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr"/>
-      <c r="G14" s="3" t="inlineStr"/>
-      <c r="H14" s="4" t="n">
-        <v>92750000</v>
-      </c>
-      <c r="I14" s="3" t="inlineStr"/>
-      <c r="J14" s="3" t="inlineStr"/>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>3600 W. Ray Road</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>Chandler</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>85226</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr"/>
-      <c r="P14" s="3" t="inlineStr"/>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr"/>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>308-06-9833</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr"/>
-      <c r="U14" s="3" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>20260305710</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>C/O Wells Fargo Bank, N.A.</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>194930</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr"/>
+      <c r="P14" s="7" t="inlineStr"/>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr"/>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>313-01-5700</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr"/>
+      <c r="U14" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V14" s="3" t="inlineStr">
+      <c r="V14" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W14" s="5" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -1950,22 +1870,26 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>20260301225</t>
+          <t>20260305837</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Ave #612, Phoenix, Arizona 85003</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr"/>
+          <t>Jacqueline I. Rita</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>21t Mortgage Corporation</t>
+        </is>
+      </c>
       <c r="H15" s="8" t="n">
-        <v>612000</v>
+        <v>586000</v>
       </c>
       <c r="I15" s="7" t="inlineStr"/>
       <c r="J15" s="7" t="inlineStr"/>
@@ -1987,10 +1911,14 @@
       <c r="R15" s="7" t="inlineStr"/>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>118-48-209</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr"/>
+          <t>217-47-324</t>
+        </is>
+      </c>
+      <c r="T15" s="7" t="inlineStr">
+        <is>
+          <t>Tyler S. Stine, Esq.</t>
+        </is>
+      </c>
       <c r="U15" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2023,27 +1951,27 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>20260301898</t>
+          <t>20260306081</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>C/O M&amp;T Bank</t>
+          <t>Trustee, as successor-in-interest to U.S. Bank</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>343660</v>
+        <v>138700</v>
       </c>
       <c r="I16" s="7" t="inlineStr"/>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Superior Courts Building. Maricopa County</t>
+          <t>Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr"/>
@@ -2064,7 +1992,7 @@
       <c r="R16" s="7" t="inlineStr"/>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>101-39-5291</t>
+          <t>218-36-0082</t>
         </is>
       </c>
       <c r="T16" s="7" t="inlineStr"/>
@@ -2100,22 +2028,22 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>20260301910</t>
+          <t>20260306094</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>C/O M&amp;T Bank</t>
+          <t>C/O Onity Mortgage</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
-        <v>417203</v>
+        <v>277359</v>
       </c>
       <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr">
@@ -2141,7 +2069,7 @@
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>503-78-4473</t>
+          <t>135-68-020</t>
         </is>
       </c>
       <c r="T17" s="7" t="inlineStr"/>
@@ -2163,7 +2091,7 @@
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="6" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -2177,30 +2105,36 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>20260302896</t>
+          <t>20260305391</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr"/>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>ALEX RODRIGUEZ AND VIKKI D BARNES</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>C/O Freedom Northwest Credit Union</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>335000</v>
-      </c>
+          <t>CROSSCOUNTRY MORTGAGE, LLC</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="7" t="inlineStr"/>
       <c r="J18" s="7" t="inlineStr">
         <is>
           <t>Superior Court Building</t>
         </is>
       </c>
-      <c r="K18" s="7" t="inlineStr"/>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>17477 W WOODROW LN</t>
+        </is>
+      </c>
       <c r="L18" s="7" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr">
         <is>
@@ -2216,8 +2150,16 @@
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr"/>
-      <c r="S18" s="7" t="inlineStr"/>
-      <c r="T18" s="7" t="inlineStr"/>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>502-88-870</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
       <c r="U18" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2235,245 +2177,205 @@
       </c>
     </row>
     <row r="19" ht="26" customHeight="1">
-      <c r="A19" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>20260301908</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>ERNESTO LUCIO ZERMENO AND ANA TERESA SEVILLANO ARRIAGA</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>SELECT PORTFOLIO SERVICING, INC.</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
-      <c r="J19" s="7" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT BUILDING</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr">
-        <is>
-          <t>6917 W SHUMWAY FARM RD</t>
-        </is>
-      </c>
-      <c r="L19" s="7" t="inlineStr"/>
-      <c r="M19" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N19" s="7" t="inlineStr"/>
-      <c r="O19" s="7" t="inlineStr"/>
-      <c r="P19" s="7" t="inlineStr"/>
-      <c r="Q19" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R19" s="7" t="inlineStr"/>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>104-83-862</t>
-        </is>
-      </c>
-      <c r="T19" s="7" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
-      <c r="U19" s="7" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V19" s="7" t="inlineStr">
+      <c r="A19" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Lis Pendens</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>20260304040</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F19" s="11" t="inlineStr"/>
+      <c r="G19" s="11" t="inlineStr"/>
+      <c r="H19" s="11" t="inlineStr"/>
+      <c r="I19" s="11" t="inlineStr"/>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr"/>
+      <c r="L19" s="11" t="inlineStr"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N19" s="11" t="inlineStr"/>
+      <c r="O19" s="11" t="inlineStr"/>
+      <c r="P19" s="11" t="inlineStr"/>
+      <c r="Q19" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R19" s="11" t="inlineStr"/>
+      <c r="S19" s="11" t="inlineStr"/>
+      <c r="T19" s="11" t="inlineStr"/>
+      <c r="U19" s="11" t="inlineStr">
+        <is>
+          <t>Lis pendens; New this week</t>
+        </is>
+      </c>
+      <c r="V19" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="12" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26" customHeight="1">
-      <c r="A20" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>20260302960</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>LUCIO TINOCO TOLEDO</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>SELECT PORTFOLIO SERVICING, INC.</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT BUILDING</t>
-        </is>
-      </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>9028 W CLARENDON AVE</t>
-        </is>
-      </c>
-      <c r="L20" s="7" t="inlineStr"/>
-      <c r="M20" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N20" s="7" t="inlineStr"/>
-      <c r="O20" s="7" t="inlineStr"/>
-      <c r="P20" s="7" t="inlineStr"/>
-      <c r="Q20" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R20" s="7" t="inlineStr"/>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>102-24-088</t>
-        </is>
-      </c>
-      <c r="T20" s="7" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
-      <c r="U20" s="7" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V20" s="7" t="inlineStr">
+      <c r="A20" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B20" s="11" t="inlineStr">
+        <is>
+          <t>Lis Pendens</t>
+        </is>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="D20" s="11" t="inlineStr">
+        <is>
+          <t>20260304045</t>
+        </is>
+      </c>
+      <c r="E20" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F20" s="11" t="inlineStr"/>
+      <c r="G20" s="11" t="inlineStr"/>
+      <c r="H20" s="11" t="inlineStr"/>
+      <c r="I20" s="11" t="inlineStr"/>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr"/>
+      <c r="L20" s="11" t="inlineStr"/>
+      <c r="M20" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N20" s="11" t="inlineStr"/>
+      <c r="O20" s="11" t="inlineStr"/>
+      <c r="P20" s="11" t="inlineStr"/>
+      <c r="Q20" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R20" s="11" t="inlineStr"/>
+      <c r="S20" s="11" t="inlineStr"/>
+      <c r="T20" s="11" t="inlineStr"/>
+      <c r="U20" s="11" t="inlineStr">
+        <is>
+          <t>Lis pendens; New this week</t>
+        </is>
+      </c>
+      <c r="V20" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="12" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="6" t="n">
-        <v>53</v>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Probate Document</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>PD</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>20260302900</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
-      <c r="I21" s="7" t="inlineStr"/>
-      <c r="J21" s="7" t="inlineStr">
+      <c r="A21" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B21" s="11" t="inlineStr">
+        <is>
+          <t>Lis Pendens</t>
+        </is>
+      </c>
+      <c r="C21" s="11" t="inlineStr">
+        <is>
+          <t>LP</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="inlineStr">
+        <is>
+          <t>20260305320</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="F21" s="11" t="inlineStr"/>
+      <c r="G21" s="11" t="inlineStr"/>
+      <c r="H21" s="11" t="inlineStr"/>
+      <c r="I21" s="11" t="inlineStr"/>
+      <c r="J21" s="11" t="inlineStr">
         <is>
           <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
-      <c r="K21" s="7" t="inlineStr">
-        <is>
-          <t>10186 E. Joy Ranch Road</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr"/>
-      <c r="M21" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N21" s="7" t="inlineStr"/>
-      <c r="O21" s="7" t="inlineStr"/>
-      <c r="P21" s="7" t="inlineStr"/>
-      <c r="Q21" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R21" s="7" t="inlineStr"/>
-      <c r="S21" s="7" t="inlineStr"/>
-      <c r="T21" s="7" t="inlineStr"/>
-      <c r="U21" s="7" t="inlineStr">
-        <is>
-          <t>Probate / estate; New this week</t>
-        </is>
-      </c>
-      <c r="V21" s="7" t="inlineStr">
+      <c r="K21" s="11" t="inlineStr"/>
+      <c r="L21" s="11" t="inlineStr"/>
+      <c r="M21" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="11" t="inlineStr"/>
+      <c r="O21" s="11" t="inlineStr"/>
+      <c r="P21" s="11" t="inlineStr"/>
+      <c r="Q21" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="11" t="inlineStr"/>
+      <c r="S21" s="11" t="inlineStr">
+        <is>
+          <t>501-74-1277</t>
+        </is>
+      </c>
+      <c r="T21" s="11" t="inlineStr"/>
+      <c r="U21" s="11" t="inlineStr">
+        <is>
+          <t>Lis pendens; New this week</t>
+        </is>
+      </c>
+      <c r="V21" s="11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="12" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -2481,38 +2383,38 @@
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>20260302366</t>
+          <t>20260305614</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr"/>
       <c r="G22" s="11" t="inlineStr"/>
       <c r="H22" s="11" t="inlineStr"/>
       <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr"/>
-      <c r="K22" s="11" t="inlineStr">
-        <is>
-          <t>18206 N 129TH DR</t>
-        </is>
-      </c>
+      <c r="J22" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr"/>
       <c r="L22" s="11" t="inlineStr"/>
       <c r="M22" s="11" t="inlineStr">
         <is>
@@ -2532,7 +2434,7 @@
       <c r="T22" s="11" t="inlineStr"/>
       <c r="U22" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V22" s="11" t="inlineStr">
@@ -2548,38 +2450,38 @@
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>20260302400</t>
+          <t>20260305708</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr"/>
       <c r="G23" s="11" t="inlineStr"/>
       <c r="H23" s="11" t="inlineStr"/>
       <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>12842 W BALLAD DR</t>
-        </is>
-      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr"/>
       <c r="L23" s="11" t="inlineStr"/>
       <c r="M23" s="11" t="inlineStr">
         <is>
@@ -2599,7 +2501,7 @@
       <c r="T23" s="11" t="inlineStr"/>
       <c r="U23" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr">
@@ -2629,12 +2531,12 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>20260301856</t>
+          <t>20260306513</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr"/>
@@ -2662,11 +2564,7 @@
         </is>
       </c>
       <c r="R24" s="11" t="inlineStr"/>
-      <c r="S24" s="11" t="inlineStr">
-        <is>
-          <t>119-32-098</t>
-        </is>
-      </c>
+      <c r="S24" s="11" t="inlineStr"/>
       <c r="T24" s="11" t="inlineStr"/>
       <c r="U24" s="11" t="inlineStr">
         <is>
@@ -2700,12 +2598,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>20260302092</t>
+          <t>20260306580</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr"/>
@@ -2733,11 +2631,7 @@
         </is>
       </c>
       <c r="R25" s="11" t="inlineStr"/>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>505-35-002</t>
-        </is>
-      </c>
+      <c r="S25" s="11" t="inlineStr"/>
       <c r="T25" s="11" t="inlineStr"/>
       <c r="U25" s="11" t="inlineStr">
         <is>
@@ -2761,33 +2655,29 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>20260302121</t>
+          <t>20260305791</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr"/>
       <c r="G26" s="11" t="inlineStr"/>
       <c r="H26" s="11" t="inlineStr"/>
       <c r="I26" s="11" t="inlineStr"/>
-      <c r="J26" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J26" s="11" t="inlineStr"/>
       <c r="K26" s="11" t="inlineStr"/>
       <c r="L26" s="11" t="inlineStr"/>
       <c r="M26" s="11" t="inlineStr">
@@ -2808,7 +2698,7 @@
       <c r="T26" s="11" t="inlineStr"/>
       <c r="U26" s="11" t="inlineStr">
         <is>
-          <t>Lis pendens; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V26" s="11" t="inlineStr">
@@ -2828,33 +2718,29 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>20260302267</t>
+          <t>20260305792</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr"/>
       <c r="G27" s="11" t="inlineStr"/>
       <c r="H27" s="11" t="inlineStr"/>
       <c r="I27" s="11" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J27" s="11" t="inlineStr"/>
       <c r="K27" s="11" t="inlineStr"/>
       <c r="L27" s="11" t="inlineStr"/>
       <c r="M27" s="11" t="inlineStr">
@@ -2875,7 +2761,7 @@
       <c r="T27" s="11" t="inlineStr"/>
       <c r="U27" s="11" t="inlineStr">
         <is>
-          <t>Lis pendens; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr">
@@ -2895,33 +2781,29 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>20260302307</t>
+          <t>20260305793</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
       <c r="G28" s="11" t="inlineStr"/>
       <c r="H28" s="11" t="inlineStr"/>
       <c r="I28" s="11" t="inlineStr"/>
-      <c r="J28" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J28" s="11" t="inlineStr"/>
       <c r="K28" s="11" t="inlineStr"/>
       <c r="L28" s="11" t="inlineStr"/>
       <c r="M28" s="11" t="inlineStr">
@@ -2942,7 +2824,7 @@
       <c r="T28" s="11" t="inlineStr"/>
       <c r="U28" s="11" t="inlineStr">
         <is>
-          <t>Lis pendens; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V28" s="11" t="inlineStr">
@@ -2962,33 +2844,29 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>20260302581</t>
+          <t>20260305794</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr"/>
       <c r="G29" s="11" t="inlineStr"/>
       <c r="H29" s="11" t="inlineStr"/>
       <c r="I29" s="11" t="inlineStr"/>
-      <c r="J29" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J29" s="11" t="inlineStr"/>
       <c r="K29" s="11" t="inlineStr"/>
       <c r="L29" s="11" t="inlineStr"/>
       <c r="M29" s="11" t="inlineStr">
@@ -3009,7 +2887,7 @@
       <c r="T29" s="11" t="inlineStr"/>
       <c r="U29" s="11" t="inlineStr">
         <is>
-          <t>Lis pendens; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V29" s="11" t="inlineStr">
@@ -3029,33 +2907,29 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>20260303164</t>
+          <t>20260305795</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr"/>
       <c r="G30" s="11" t="inlineStr"/>
       <c r="H30" s="11" t="inlineStr"/>
       <c r="I30" s="11" t="inlineStr"/>
-      <c r="J30" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J30" s="11" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr"/>
       <c r="L30" s="11" t="inlineStr"/>
       <c r="M30" s="11" t="inlineStr">
@@ -3076,7 +2950,7 @@
       <c r="T30" s="11" t="inlineStr"/>
       <c r="U30" s="11" t="inlineStr">
         <is>
-          <t>Lis pendens; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V30" s="11" t="inlineStr">
@@ -3096,33 +2970,29 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>20260300935</t>
+          <t>20260305796</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr"/>
       <c r="H31" s="11" t="inlineStr"/>
       <c r="I31" s="11" t="inlineStr"/>
-      <c r="J31" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J31" s="11" t="inlineStr"/>
       <c r="K31" s="11" t="inlineStr"/>
       <c r="L31" s="11" t="inlineStr"/>
       <c r="M31" s="11" t="inlineStr">
@@ -3143,7 +3013,7 @@
       <c r="T31" s="11" t="inlineStr"/>
       <c r="U31" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V31" s="11" t="inlineStr">
@@ -3163,33 +3033,29 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>20260301000</t>
+          <t>20260305797</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
       <c r="G32" s="11" t="inlineStr"/>
       <c r="H32" s="11" t="inlineStr"/>
       <c r="I32" s="11" t="inlineStr"/>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J32" s="11" t="inlineStr"/>
       <c r="K32" s="11" t="inlineStr"/>
       <c r="L32" s="11" t="inlineStr"/>
       <c r="M32" s="11" t="inlineStr">
@@ -3210,7 +3076,7 @@
       <c r="T32" s="11" t="inlineStr"/>
       <c r="U32" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V32" s="11" t="inlineStr">
@@ -3230,22 +3096,22 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>20260301001</t>
+          <t>20260305798</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
@@ -3273,7 +3139,7 @@
       <c r="T33" s="11" t="inlineStr"/>
       <c r="U33" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V33" s="11" t="inlineStr">
@@ -3293,22 +3159,22 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>20260301621</t>
+          <t>20260305799</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
@@ -3336,7 +3202,7 @@
       <c r="T34" s="11" t="inlineStr"/>
       <c r="U34" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V34" s="11" t="inlineStr">
@@ -3356,22 +3222,22 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>20260301622</t>
+          <t>20260305800</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
@@ -3399,7 +3265,7 @@
       <c r="T35" s="11" t="inlineStr"/>
       <c r="U35" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V35" s="11" t="inlineStr">
@@ -3419,22 +3285,22 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>20260301623</t>
+          <t>20260305801</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
@@ -3462,7 +3328,7 @@
       <c r="T36" s="11" t="inlineStr"/>
       <c r="U36" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V36" s="11" t="inlineStr">
@@ -3482,33 +3348,29 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>20260301745</t>
+          <t>20260305802</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
       <c r="G37" s="11" t="inlineStr"/>
       <c r="H37" s="11" t="inlineStr"/>
       <c r="I37" s="11" t="inlineStr"/>
-      <c r="J37" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J37" s="11" t="inlineStr"/>
       <c r="K37" s="11" t="inlineStr"/>
       <c r="L37" s="11" t="inlineStr"/>
       <c r="M37" s="11" t="inlineStr">
@@ -3529,7 +3391,7 @@
       <c r="T37" s="11" t="inlineStr"/>
       <c r="U37" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V37" s="11" t="inlineStr">
@@ -3549,22 +3411,22 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>20260301789</t>
+          <t>20260305803</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr"/>
@@ -3592,7 +3454,7 @@
       <c r="T38" s="11" t="inlineStr"/>
       <c r="U38" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V38" s="11" t="inlineStr">
@@ -3612,22 +3474,22 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>20260301815</t>
+          <t>20260305804</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
@@ -3655,7 +3517,7 @@
       <c r="T39" s="11" t="inlineStr"/>
       <c r="U39" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V39" s="11" t="inlineStr">
@@ -3675,22 +3537,22 @@
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>20260301847</t>
+          <t>20260305805</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
@@ -3718,7 +3580,7 @@
       <c r="T40" s="11" t="inlineStr"/>
       <c r="U40" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V40" s="11" t="inlineStr">
@@ -3738,22 +3600,22 @@
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>20260301859</t>
+          <t>20260305806</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
@@ -3781,7 +3643,7 @@
       <c r="T41" s="11" t="inlineStr"/>
       <c r="U41" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V41" s="11" t="inlineStr">
@@ -3801,33 +3663,29 @@
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>20260302434</t>
+          <t>20260305807</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
       <c r="G42" s="11" t="inlineStr"/>
       <c r="H42" s="11" t="inlineStr"/>
       <c r="I42" s="11" t="inlineStr"/>
-      <c r="J42" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J42" s="11" t="inlineStr"/>
       <c r="K42" s="11" t="inlineStr"/>
       <c r="L42" s="11" t="inlineStr"/>
       <c r="M42" s="11" t="inlineStr">
@@ -3848,7 +3706,7 @@
       <c r="T42" s="11" t="inlineStr"/>
       <c r="U42" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V42" s="11" t="inlineStr">
@@ -3868,33 +3726,29 @@
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>20260302787</t>
+          <t>20260305808</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr"/>
       <c r="H43" s="11" t="inlineStr"/>
       <c r="I43" s="11" t="inlineStr"/>
-      <c r="J43" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court Case No. CV2026-000170</t>
-        </is>
-      </c>
+      <c r="J43" s="11" t="inlineStr"/>
       <c r="K43" s="11" t="inlineStr"/>
       <c r="L43" s="11" t="inlineStr"/>
       <c r="M43" s="11" t="inlineStr">
@@ -3915,7 +3769,7 @@
       <c r="T43" s="11" t="inlineStr"/>
       <c r="U43" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Gov/Tax lien; New this week</t>
         </is>
       </c>
       <c r="V43" s="11" t="inlineStr">
@@ -3935,29 +3789,33 @@
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>20260302827</t>
+          <t>20260305787</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="11" t="inlineStr"/>
       <c r="H44" s="11" t="inlineStr"/>
       <c r="I44" s="11" t="inlineStr"/>
-      <c r="J44" s="11" t="inlineStr"/>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA |</t>
+        </is>
+      </c>
       <c r="K44" s="11" t="inlineStr"/>
       <c r="L44" s="11" t="inlineStr"/>
       <c r="M44" s="11" t="inlineStr">
@@ -3978,7 +3836,7 @@
       <c r="T44" s="11" t="inlineStr"/>
       <c r="U44" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V44" s="11" t="inlineStr">
@@ -3998,29 +3856,33 @@
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>20260302904</t>
+          <t>20260305993</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
       <c r="G45" s="11" t="inlineStr"/>
       <c r="H45" s="11" t="inlineStr"/>
       <c r="I45" s="11" t="inlineStr"/>
-      <c r="J45" s="11" t="inlineStr"/>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
       <c r="K45" s="11" t="inlineStr"/>
       <c r="L45" s="11" t="inlineStr"/>
       <c r="M45" s="11" t="inlineStr">
@@ -4041,7 +3903,7 @@
       <c r="T45" s="11" t="inlineStr"/>
       <c r="U45" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V45" s="11" t="inlineStr">
@@ -4057,37 +3919,33 @@
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>20260303053</t>
+          <t>20260303350</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
       <c r="G46" s="11" t="inlineStr"/>
       <c r="H46" s="11" t="inlineStr"/>
       <c r="I46" s="11" t="inlineStr"/>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr"/>
       <c r="L46" s="11" t="inlineStr"/>
       <c r="M46" s="11" t="inlineStr">
@@ -4108,7 +3966,7 @@
       <c r="T46" s="11" t="inlineStr"/>
       <c r="U46" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V46" s="11" t="inlineStr">
@@ -4124,37 +3982,33 @@
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>20260303055</t>
+          <t>20260303351</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
       <c r="G47" s="11" t="inlineStr"/>
       <c r="H47" s="11" t="inlineStr"/>
       <c r="I47" s="11" t="inlineStr"/>
-      <c r="J47" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J47" s="11" t="inlineStr"/>
       <c r="K47" s="11" t="inlineStr"/>
       <c r="L47" s="11" t="inlineStr"/>
       <c r="M47" s="11" t="inlineStr">
@@ -4175,7 +4029,7 @@
       <c r="T47" s="11" t="inlineStr"/>
       <c r="U47" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V47" s="11" t="inlineStr">
@@ -4191,37 +4045,33 @@
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>20260303221</t>
+          <t>20260303352</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
       <c r="G48" s="11" t="inlineStr"/>
       <c r="H48" s="11" t="inlineStr"/>
       <c r="I48" s="11" t="inlineStr"/>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court Case No. C20242507</t>
-        </is>
-      </c>
+      <c r="J48" s="11" t="inlineStr"/>
       <c r="K48" s="11" t="inlineStr"/>
       <c r="L48" s="11" t="inlineStr"/>
       <c r="M48" s="11" t="inlineStr">
@@ -4242,7 +4092,7 @@
       <c r="T48" s="11" t="inlineStr"/>
       <c r="U48" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V48" s="11" t="inlineStr">
@@ -4258,37 +4108,33 @@
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>20260303222</t>
+          <t>20260303353</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
       <c r="G49" s="11" t="inlineStr"/>
       <c r="H49" s="11" t="inlineStr"/>
       <c r="I49" s="11" t="inlineStr"/>
-      <c r="J49" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J49" s="11" t="inlineStr"/>
       <c r="K49" s="11" t="inlineStr"/>
       <c r="L49" s="11" t="inlineStr"/>
       <c r="M49" s="11" t="inlineStr">
@@ -4309,7 +4155,7 @@
       <c r="T49" s="11" t="inlineStr"/>
       <c r="U49" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V49" s="11" t="inlineStr">
@@ -4325,26 +4171,26 @@
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>20260303234</t>
+          <t>20260303354</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr"/>
@@ -4372,7 +4218,7 @@
       <c r="T50" s="11" t="inlineStr"/>
       <c r="U50" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V50" s="11" t="inlineStr">
@@ -4388,26 +4234,26 @@
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>20260303235</t>
+          <t>20260303355</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
@@ -4435,7 +4281,7 @@
       <c r="T51" s="11" t="inlineStr"/>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
@@ -4451,26 +4297,26 @@
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>20260303236</t>
+          <t>20260303356</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
@@ -4498,7 +4344,7 @@
       <c r="T52" s="11" t="inlineStr"/>
       <c r="U52" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V52" s="11" t="inlineStr">
@@ -4514,26 +4360,26 @@
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>20260303237</t>
+          <t>20260303357</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
@@ -4561,7 +4407,7 @@
       <c r="T53" s="11" t="inlineStr"/>
       <c r="U53" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V53" s="11" t="inlineStr">
@@ -4577,37 +4423,33 @@
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>20260301476</t>
+          <t>20260303358</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
       <c r="G54" s="11" t="inlineStr"/>
       <c r="H54" s="11" t="inlineStr"/>
       <c r="I54" s="11" t="inlineStr"/>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr"/>
       <c r="L54" s="11" t="inlineStr"/>
       <c r="M54" s="11" t="inlineStr">
@@ -4628,7 +4470,7 @@
       <c r="T54" s="11" t="inlineStr"/>
       <c r="U54" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V54" s="11" t="inlineStr">
@@ -4644,37 +4486,33 @@
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>20260302546</t>
+          <t>20260303359</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr"/>
       <c r="H55" s="11" t="inlineStr"/>
       <c r="I55" s="11" t="inlineStr"/>
-      <c r="J55" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J55" s="11" t="inlineStr"/>
       <c r="K55" s="11" t="inlineStr"/>
       <c r="L55" s="11" t="inlineStr"/>
       <c r="M55" s="11" t="inlineStr">
@@ -4695,7 +4533,7 @@
       <c r="T55" s="11" t="inlineStr"/>
       <c r="U55" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V55" s="11" t="inlineStr">
@@ -4711,37 +4549,33 @@
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>20260302812</t>
+          <t>20260303360</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr"/>
       <c r="H56" s="11" t="inlineStr"/>
       <c r="I56" s="11" t="inlineStr"/>
-      <c r="J56" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J56" s="11" t="inlineStr"/>
       <c r="K56" s="11" t="inlineStr"/>
       <c r="L56" s="11" t="inlineStr"/>
       <c r="M56" s="11" t="inlineStr">
@@ -4762,7 +4596,7 @@
       <c r="T56" s="11" t="inlineStr"/>
       <c r="U56" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V56" s="11" t="inlineStr">
@@ -4778,37 +4612,33 @@
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>20260300491</t>
+          <t>20260303361</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr"/>
       <c r="G57" s="11" t="inlineStr"/>
       <c r="H57" s="11" t="inlineStr"/>
       <c r="I57" s="11" t="inlineStr"/>
-      <c r="J57" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J57" s="11" t="inlineStr"/>
       <c r="K57" s="11" t="inlineStr"/>
       <c r="L57" s="11" t="inlineStr"/>
       <c r="M57" s="11" t="inlineStr">
@@ -4829,7 +4659,7 @@
       <c r="T57" s="11" t="inlineStr"/>
       <c r="U57" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V57" s="11" t="inlineStr">
@@ -4845,37 +4675,33 @@
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>20260301470</t>
+          <t>20260303363</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr"/>
       <c r="G58" s="11" t="inlineStr"/>
       <c r="H58" s="11" t="inlineStr"/>
       <c r="I58" s="11" t="inlineStr"/>
-      <c r="J58" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr"/>
       <c r="L58" s="11" t="inlineStr"/>
       <c r="M58" s="11" t="inlineStr">
@@ -4896,7 +4722,7 @@
       <c r="T58" s="11" t="inlineStr"/>
       <c r="U58" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V58" s="11" t="inlineStr">
@@ -4912,37 +4738,33 @@
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>20260302164</t>
+          <t>20260303364</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
       <c r="G59" s="11" t="inlineStr"/>
       <c r="H59" s="11" t="inlineStr"/>
       <c r="I59" s="11" t="inlineStr"/>
-      <c r="J59" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J59" s="11" t="inlineStr"/>
       <c r="K59" s="11" t="inlineStr"/>
       <c r="L59" s="11" t="inlineStr"/>
       <c r="M59" s="11" t="inlineStr">
@@ -4963,7 +4785,7 @@
       <c r="T59" s="11" t="inlineStr"/>
       <c r="U59" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V59" s="11" t="inlineStr">
@@ -4979,37 +4801,33 @@
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>20260302344</t>
+          <t>20260303365</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
       <c r="G60" s="11" t="inlineStr"/>
       <c r="H60" s="11" t="inlineStr"/>
       <c r="I60" s="11" t="inlineStr"/>
-      <c r="J60" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT ] CLERK’S CERTIFICATION</t>
-        </is>
-      </c>
+      <c r="J60" s="11" t="inlineStr"/>
       <c r="K60" s="11" t="inlineStr"/>
       <c r="L60" s="11" t="inlineStr"/>
       <c r="M60" s="11" t="inlineStr">
@@ -5030,7 +4848,7 @@
       <c r="T60" s="11" t="inlineStr"/>
       <c r="U60" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V60" s="11" t="inlineStr">
@@ -5046,37 +4864,33 @@
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>20260302545</t>
+          <t>20260303366</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
       <c r="G61" s="11" t="inlineStr"/>
       <c r="H61" s="11" t="inlineStr"/>
       <c r="I61" s="11" t="inlineStr"/>
-      <c r="J61" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA :</t>
-        </is>
-      </c>
+      <c r="J61" s="11" t="inlineStr"/>
       <c r="K61" s="11" t="inlineStr"/>
       <c r="L61" s="11" t="inlineStr"/>
       <c r="M61" s="11" t="inlineStr">
@@ -5097,7 +4911,7 @@
       <c r="T61" s="11" t="inlineStr"/>
       <c r="U61" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V61" s="11" t="inlineStr">
@@ -5113,37 +4927,33 @@
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>20260302811</t>
+          <t>20260303367</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
       <c r="G62" s="11" t="inlineStr"/>
       <c r="H62" s="11" t="inlineStr"/>
       <c r="I62" s="11" t="inlineStr"/>
-      <c r="J62" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J62" s="11" t="inlineStr"/>
       <c r="K62" s="11" t="inlineStr"/>
       <c r="L62" s="11" t="inlineStr"/>
       <c r="M62" s="11" t="inlineStr">
@@ -5164,7 +4974,7 @@
       <c r="T62" s="11" t="inlineStr"/>
       <c r="U62" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V62" s="11" t="inlineStr">
@@ -5180,37 +4990,33 @@
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>20260303089</t>
+          <t>20260303368</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
       <c r="G63" s="11" t="inlineStr"/>
       <c r="H63" s="11" t="inlineStr"/>
       <c r="I63" s="11" t="inlineStr"/>
-      <c r="J63" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J63" s="11" t="inlineStr"/>
       <c r="K63" s="11" t="inlineStr"/>
       <c r="L63" s="11" t="inlineStr"/>
       <c r="M63" s="11" t="inlineStr">
@@ -5231,7 +5037,7 @@
       <c r="T63" s="11" t="inlineStr"/>
       <c r="U63" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V63" s="11" t="inlineStr">
@@ -5247,26 +5053,26 @@
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>20260301488</t>
+          <t>20260303369</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
@@ -5290,15 +5096,11 @@
         </is>
       </c>
       <c r="R64" s="11" t="inlineStr"/>
-      <c r="S64" s="11" t="inlineStr">
-        <is>
-          <t>130-23-206</t>
-        </is>
-      </c>
+      <c r="S64" s="11" t="inlineStr"/>
       <c r="T64" s="11" t="inlineStr"/>
       <c r="U64" s="11" t="inlineStr">
         <is>
-          <t>Mechanic lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V64" s="11" t="inlineStr">
@@ -5328,12 +5130,12 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>20260300395</t>
+          <t>20260303430</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
@@ -5391,12 +5193,12 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>20260300397</t>
+          <t>20260303591</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
@@ -5454,12 +5256,12 @@
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>20260300398</t>
+          <t>20260303592</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
@@ -5517,12 +5319,12 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>20260300399</t>
+          <t>20260303752</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
@@ -5580,12 +5382,12 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>20260300400</t>
+          <t>20260303755</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
@@ -5643,12 +5445,12 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>20260300401</t>
+          <t>20260303760</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
@@ -5706,12 +5508,12 @@
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>20260300402</t>
+          <t>20260303763</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
@@ -5769,12 +5571,12 @@
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>20260300403</t>
+          <t>20260303943</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
@@ -5832,12 +5634,12 @@
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>20260300404</t>
+          <t>20260303944</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
@@ -5895,12 +5697,12 @@
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>20260300405</t>
+          <t>20260303945</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
@@ -5958,12 +5760,12 @@
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>20260300406</t>
+          <t>20260303946</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
@@ -6021,12 +5823,12 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>20260300407</t>
+          <t>20260303947</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
@@ -6084,12 +5886,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>20260300408</t>
+          <t>20260303948</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr"/>
@@ -6147,12 +5949,12 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>20260300409</t>
+          <t>20260303949</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
@@ -6210,12 +6012,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>20260300410</t>
+          <t>20260303950</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr"/>
@@ -6273,12 +6075,12 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>20260300411</t>
+          <t>20260303951</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
@@ -6336,12 +6138,12 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>20260300412</t>
+          <t>20260304060</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr"/>
@@ -6399,12 +6201,12 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>20260300413</t>
+          <t>20260304061</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr"/>
@@ -6462,12 +6264,12 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>20260300414</t>
+          <t>20260304236</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
@@ -6525,12 +6327,12 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>20260300416</t>
+          <t>20260304238</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr"/>
@@ -6588,12 +6390,12 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>20260300417</t>
+          <t>20260304239</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr"/>
@@ -6651,12 +6453,12 @@
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>20260300418</t>
+          <t>20260304240</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr"/>
@@ -6714,12 +6516,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>20260300419</t>
+          <t>20260304241</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr"/>
@@ -6777,12 +6579,12 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>20260300420</t>
+          <t>20260304314</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr"/>
@@ -6840,12 +6642,12 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>20260300421</t>
+          <t>20260304315</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
@@ -6903,12 +6705,12 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>20260300422</t>
+          <t>20260304375</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
@@ -6966,12 +6768,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>20260300423</t>
+          <t>20260304376</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr"/>
@@ -7015,7 +6817,7 @@
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
@@ -7029,12 +6831,12 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>20260300424</t>
+          <t>20260304523</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr"/>
@@ -7067,7 +6869,7 @@
       </c>
       <c r="V92" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W92" s="12" t="inlineStr">
@@ -7078,7 +6880,7 @@
     </row>
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
@@ -7092,12 +6894,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>20260300425</t>
+          <t>20260304656</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
@@ -7130,7 +6932,7 @@
       </c>
       <c r="V93" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W93" s="12" t="inlineStr">
@@ -7141,7 +6943,7 @@
     </row>
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
@@ -7155,12 +6957,12 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>20260300426</t>
+          <t>20260304658</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr"/>
@@ -7193,7 +6995,7 @@
       </c>
       <c r="V94" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W94" s="12" t="inlineStr">
@@ -7204,7 +7006,7 @@
     </row>
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
@@ -7218,12 +7020,12 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>20260300427</t>
+          <t>20260304679</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr"/>
@@ -7256,7 +7058,7 @@
       </c>
       <c r="V95" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W95" s="12" t="inlineStr">
@@ -7267,7 +7069,7 @@
     </row>
     <row r="96" ht="26" customHeight="1">
       <c r="A96" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
@@ -7281,12 +7083,12 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>20260300428</t>
+          <t>20260304680</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr"/>
@@ -7319,7 +7121,7 @@
       </c>
       <c r="V96" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W96" s="12" t="inlineStr">
@@ -7330,7 +7132,7 @@
     </row>
     <row r="97" ht="26" customHeight="1">
       <c r="A97" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
@@ -7344,12 +7146,12 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>20260300429</t>
+          <t>20260304681</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr"/>
@@ -7382,7 +7184,7 @@
       </c>
       <c r="V97" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W97" s="12" t="inlineStr">
@@ -7393,7 +7195,7 @@
     </row>
     <row r="98" ht="26" customHeight="1">
       <c r="A98" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
@@ -7407,12 +7209,12 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>20260301291</t>
+          <t>20260304682</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr"/>
@@ -7445,7 +7247,7 @@
       </c>
       <c r="V98" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W98" s="12" t="inlineStr">
@@ -7456,7 +7258,7 @@
     </row>
     <row r="99" ht="26" customHeight="1">
       <c r="A99" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
@@ -7470,12 +7272,12 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>20260301540</t>
+          <t>20260304683</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr"/>
@@ -7508,7 +7310,7 @@
       </c>
       <c r="V99" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W99" s="12" t="inlineStr">
@@ -7519,7 +7321,7 @@
     </row>
     <row r="100" ht="26" customHeight="1">
       <c r="A100" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
@@ -7533,12 +7335,12 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>20260301729</t>
+          <t>20260304684</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr"/>
@@ -7571,7 +7373,7 @@
       </c>
       <c r="V100" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W100" s="12" t="inlineStr">
@@ -7582,26 +7384,26 @@
     </row>
     <row r="101" ht="26" customHeight="1">
       <c r="A101" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>20260302614</t>
+          <t>20260304685</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr"/>
@@ -7629,7 +7431,7 @@
       <c r="T101" s="11" t="inlineStr"/>
       <c r="U101" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V101" s="11" t="inlineStr">
@@ -7645,26 +7447,26 @@
     </row>
     <row r="102" ht="26" customHeight="1">
       <c r="A102" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C102" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>20260303051</t>
+          <t>20260304686</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr"/>
@@ -7692,7 +7494,7 @@
       <c r="T102" s="11" t="inlineStr"/>
       <c r="U102" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V102" s="11" t="inlineStr">
@@ -7708,26 +7510,26 @@
     </row>
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C103" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>20260303215</t>
+          <t>20260304688</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr"/>
@@ -7755,7 +7557,7 @@
       <c r="T103" s="11" t="inlineStr"/>
       <c r="U103" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V103" s="11" t="inlineStr">
@@ -7771,26 +7573,26 @@
     </row>
     <row r="104" ht="26" customHeight="1">
       <c r="A104" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C104" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>20260303217</t>
+          <t>20260304689</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr"/>
@@ -7818,7 +7620,7 @@
       <c r="T104" s="11" t="inlineStr"/>
       <c r="U104" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V104" s="11" t="inlineStr">
@@ -7834,26 +7636,26 @@
     </row>
     <row r="105" ht="26" customHeight="1">
       <c r="A105" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C105" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>20260303218</t>
+          <t>20260304690</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr"/>
@@ -7881,7 +7683,7 @@
       <c r="T105" s="11" t="inlineStr"/>
       <c r="U105" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V105" s="11" t="inlineStr">
@@ -7897,26 +7699,26 @@
     </row>
     <row r="106" ht="26" customHeight="1">
       <c r="A106" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>20260303107</t>
+          <t>20260304691</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr"/>
@@ -7944,7 +7746,7 @@
       <c r="T106" s="11" t="inlineStr"/>
       <c r="U106" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V106" s="11" t="inlineStr">
@@ -7960,26 +7762,26 @@
     </row>
     <row r="107" ht="26" customHeight="1">
       <c r="A107" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>20260303133</t>
+          <t>20260304692</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr"/>
@@ -8007,7 +7809,7 @@
       <c r="T107" s="11" t="inlineStr"/>
       <c r="U107" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V107" s="11" t="inlineStr">
@@ -8023,26 +7825,26 @@
     </row>
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>20260303174</t>
+          <t>20260304693</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr"/>
@@ -8070,7 +7872,7 @@
       <c r="T108" s="11" t="inlineStr"/>
       <c r="U108" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V108" s="11" t="inlineStr">
@@ -8086,26 +7888,26 @@
     </row>
     <row r="109" ht="26" customHeight="1">
       <c r="A109" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>20260301429</t>
+          <t>20260304694</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr"/>
@@ -8133,12 +7935,12 @@
       <c r="T109" s="11" t="inlineStr"/>
       <c r="U109" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V109" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W109" s="12" t="inlineStr">
@@ -8149,26 +7951,26 @@
     </row>
     <row r="110" ht="26" customHeight="1">
       <c r="A110" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>20260301478</t>
+          <t>20260304695</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr"/>
@@ -8196,12 +7998,12 @@
       <c r="T110" s="11" t="inlineStr"/>
       <c r="U110" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V110" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W110" s="12" t="inlineStr">
@@ -8212,26 +8014,26 @@
     </row>
     <row r="111" ht="26" customHeight="1">
       <c r="A111" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C111" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>20260301479</t>
+          <t>20260304696</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr"/>
@@ -8259,12 +8061,12 @@
       <c r="T111" s="11" t="inlineStr"/>
       <c r="U111" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V111" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W111" s="12" t="inlineStr">
@@ -8275,26 +8077,26 @@
     </row>
     <row r="112" ht="26" customHeight="1">
       <c r="A112" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C112" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>20260301497</t>
+          <t>20260304697</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr"/>
@@ -8322,12 +8124,12 @@
       <c r="T112" s="11" t="inlineStr"/>
       <c r="U112" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V112" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W112" s="12" t="inlineStr">
@@ -8338,26 +8140,26 @@
     </row>
     <row r="113" ht="26" customHeight="1">
       <c r="A113" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C113" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>20260301664</t>
+          <t>20260304698</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr"/>
@@ -8385,12 +8187,12 @@
       <c r="T113" s="11" t="inlineStr"/>
       <c r="U113" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V113" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W113" s="12" t="inlineStr">
@@ -8401,26 +8203,26 @@
     </row>
     <row r="114" ht="26" customHeight="1">
       <c r="A114" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C114" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>20260301665</t>
+          <t>20260304699</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr"/>
@@ -8448,12 +8250,12 @@
       <c r="T114" s="11" t="inlineStr"/>
       <c r="U114" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V114" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W114" s="12" t="inlineStr">
@@ -8464,26 +8266,26 @@
     </row>
     <row r="115" ht="26" customHeight="1">
       <c r="A115" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>20260301666</t>
+          <t>20260304700</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr"/>
@@ -8511,12 +8313,12 @@
       <c r="T115" s="11" t="inlineStr"/>
       <c r="U115" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V115" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W115" s="12" t="inlineStr">
@@ -8527,26 +8329,26 @@
     </row>
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>20260301766</t>
+          <t>20260304701</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr"/>
@@ -8574,12 +8376,12 @@
       <c r="T116" s="11" t="inlineStr"/>
       <c r="U116" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V116" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W116" s="12" t="inlineStr">
@@ -8590,26 +8392,26 @@
     </row>
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>20260301767</t>
+          <t>20260304702</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr"/>
@@ -8637,12 +8439,12 @@
       <c r="T117" s="11" t="inlineStr"/>
       <c r="U117" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V117" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W117" s="12" t="inlineStr">
@@ -8653,26 +8455,26 @@
     </row>
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>20260301768</t>
+          <t>20260304703</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr"/>
@@ -8700,12 +8502,12 @@
       <c r="T118" s="11" t="inlineStr"/>
       <c r="U118" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V118" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W118" s="12" t="inlineStr">
@@ -8716,26 +8518,26 @@
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>20260301770</t>
+          <t>20260304704</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr"/>
@@ -8763,12 +8565,12 @@
       <c r="T119" s="11" t="inlineStr"/>
       <c r="U119" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V119" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W119" s="12" t="inlineStr">
@@ -8779,26 +8581,26 @@
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>20260301771</t>
+          <t>20260304771</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr"/>
@@ -8826,12 +8628,12 @@
       <c r="T120" s="11" t="inlineStr"/>
       <c r="U120" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V120" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W120" s="12" t="inlineStr">
@@ -8842,26 +8644,26 @@
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>20260301772</t>
+          <t>20260304808</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr"/>
@@ -8889,12 +8691,12 @@
       <c r="T121" s="11" t="inlineStr"/>
       <c r="U121" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V121" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W121" s="12" t="inlineStr">
@@ -8905,26 +8707,26 @@
     </row>
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>20260301773</t>
+          <t>20260304810</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr"/>
@@ -8952,12 +8754,12 @@
       <c r="T122" s="11" t="inlineStr"/>
       <c r="U122" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V122" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W122" s="12" t="inlineStr">
@@ -8968,26 +8770,26 @@
     </row>
     <row r="123" ht="26" customHeight="1">
       <c r="A123" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>20260301774</t>
+          <t>20260304811</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr"/>
@@ -9015,12 +8817,12 @@
       <c r="T123" s="11" t="inlineStr"/>
       <c r="U123" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V123" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W123" s="12" t="inlineStr">
@@ -9031,26 +8833,26 @@
     </row>
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>20260301776</t>
+          <t>20260304907</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr"/>
@@ -9078,12 +8880,12 @@
       <c r="T124" s="11" t="inlineStr"/>
       <c r="U124" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V124" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W124" s="12" t="inlineStr">
@@ -9094,26 +8896,26 @@
     </row>
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>20260301778</t>
+          <t>20260304908</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr"/>
@@ -9141,12 +8943,12 @@
       <c r="T125" s="11" t="inlineStr"/>
       <c r="U125" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V125" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W125" s="12" t="inlineStr">
@@ -9157,26 +8959,26 @@
     </row>
     <row r="126" ht="26" customHeight="1">
       <c r="A126" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>20260301779</t>
+          <t>20260305252</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr"/>
@@ -9204,12 +9006,12 @@
       <c r="T126" s="11" t="inlineStr"/>
       <c r="U126" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V126" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W126" s="12" t="inlineStr">
@@ -9220,26 +9022,26 @@
     </row>
     <row r="127" ht="26" customHeight="1">
       <c r="A127" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>20260301780</t>
+          <t>20260305259</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr"/>
@@ -9267,12 +9069,12 @@
       <c r="T127" s="11" t="inlineStr"/>
       <c r="U127" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V127" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W127" s="12" t="inlineStr">
@@ -9283,26 +9085,26 @@
     </row>
     <row r="128" ht="26" customHeight="1">
       <c r="A128" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>20260301782</t>
+          <t>20260305683</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr"/>
@@ -9330,12 +9132,12 @@
       <c r="T128" s="11" t="inlineStr"/>
       <c r="U128" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V128" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W128" s="12" t="inlineStr">
@@ -9346,26 +9148,26 @@
     </row>
     <row r="129" ht="26" customHeight="1">
       <c r="A129" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>20260301783</t>
+          <t>20260305690</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr"/>
@@ -9393,12 +9195,12 @@
       <c r="T129" s="11" t="inlineStr"/>
       <c r="U129" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V129" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W129" s="12" t="inlineStr">
@@ -9409,26 +9211,26 @@
     </row>
     <row r="130" ht="26" customHeight="1">
       <c r="A130" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>20260301784</t>
+          <t>20260305692</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr"/>
@@ -9456,12 +9258,12 @@
       <c r="T130" s="11" t="inlineStr"/>
       <c r="U130" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V130" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W130" s="12" t="inlineStr">
@@ -9472,26 +9274,26 @@
     </row>
     <row r="131" ht="26" customHeight="1">
       <c r="A131" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>20260301785</t>
+          <t>20260305693</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr"/>
@@ -9519,12 +9321,12 @@
       <c r="T131" s="11" t="inlineStr"/>
       <c r="U131" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V131" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W131" s="12" t="inlineStr">
@@ -9535,26 +9337,26 @@
     </row>
     <row r="132" ht="26" customHeight="1">
       <c r="A132" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>20260301786</t>
+          <t>20260305695</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr"/>
@@ -9582,12 +9384,12 @@
       <c r="T132" s="11" t="inlineStr"/>
       <c r="U132" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V132" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W132" s="12" t="inlineStr">
@@ -9598,26 +9400,26 @@
     </row>
     <row r="133" ht="26" customHeight="1">
       <c r="A133" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>20260301787</t>
+          <t>20260305696</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr"/>
@@ -9645,12 +9447,12 @@
       <c r="T133" s="11" t="inlineStr"/>
       <c r="U133" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V133" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W133" s="12" t="inlineStr">
@@ -9661,26 +9463,26 @@
     </row>
     <row r="134" ht="26" customHeight="1">
       <c r="A134" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>20260301788</t>
+          <t>20260305702</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr"/>
@@ -9708,12 +9510,12 @@
       <c r="T134" s="11" t="inlineStr"/>
       <c r="U134" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V134" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W134" s="12" t="inlineStr">
@@ -9724,26 +9526,26 @@
     </row>
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>20260301790</t>
+          <t>20260305703</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr"/>
@@ -9771,12 +9573,12 @@
       <c r="T135" s="11" t="inlineStr"/>
       <c r="U135" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V135" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W135" s="12" t="inlineStr">
@@ -9787,26 +9589,26 @@
     </row>
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>20260301791</t>
+          <t>20260305841</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr"/>
@@ -9834,12 +9636,12 @@
       <c r="T136" s="11" t="inlineStr"/>
       <c r="U136" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V136" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W136" s="12" t="inlineStr">
@@ -9850,26 +9652,26 @@
     </row>
     <row r="137" ht="26" customHeight="1">
       <c r="A137" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>20260301792</t>
+          <t>20260305842</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr"/>
@@ -9897,12 +9699,12 @@
       <c r="T137" s="11" t="inlineStr"/>
       <c r="U137" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V137" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W137" s="12" t="inlineStr">
@@ -9913,26 +9715,26 @@
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>20260301793</t>
+          <t>20260305843</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr"/>
@@ -9960,12 +9762,12 @@
       <c r="T138" s="11" t="inlineStr"/>
       <c r="U138" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V138" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W138" s="12" t="inlineStr">
@@ -9976,26 +9778,26 @@
     </row>
     <row r="139" ht="26" customHeight="1">
       <c r="A139" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>20260301794</t>
+          <t>20260305845</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr"/>
@@ -10023,12 +9825,12 @@
       <c r="T139" s="11" t="inlineStr"/>
       <c r="U139" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V139" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W139" s="12" t="inlineStr">
@@ -10039,26 +9841,26 @@
     </row>
     <row r="140" ht="26" customHeight="1">
       <c r="A140" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>20260302183</t>
+          <t>20260305846</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr"/>
@@ -10086,12 +9888,12 @@
       <c r="T140" s="11" t="inlineStr"/>
       <c r="U140" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V140" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W140" s="12" t="inlineStr">
@@ -10102,26 +9904,26 @@
     </row>
     <row r="141" ht="26" customHeight="1">
       <c r="A141" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>20260302205</t>
+          <t>20260305848</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr"/>
@@ -10149,12 +9951,12 @@
       <c r="T141" s="11" t="inlineStr"/>
       <c r="U141" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V141" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W141" s="12" t="inlineStr">
@@ -10165,26 +9967,26 @@
     </row>
     <row r="142" ht="26" customHeight="1">
       <c r="A142" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>20260302206</t>
+          <t>20260305849</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr"/>
@@ -10212,12 +10014,12 @@
       <c r="T142" s="11" t="inlineStr"/>
       <c r="U142" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V142" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W142" s="12" t="inlineStr">
@@ -10228,26 +10030,26 @@
     </row>
     <row r="143" ht="26" customHeight="1">
       <c r="A143" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>20260302211</t>
+          <t>20260305850</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr"/>
@@ -10275,12 +10077,12 @@
       <c r="T143" s="11" t="inlineStr"/>
       <c r="U143" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V143" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W143" s="12" t="inlineStr">
@@ -10291,26 +10093,26 @@
     </row>
     <row r="144" ht="26" customHeight="1">
       <c r="A144" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>20260302212</t>
+          <t>20260305851</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr"/>
@@ -10338,12 +10140,12 @@
       <c r="T144" s="11" t="inlineStr"/>
       <c r="U144" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V144" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W144" s="12" t="inlineStr">
@@ -10354,26 +10156,26 @@
     </row>
     <row r="145" ht="26" customHeight="1">
       <c r="A145" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>20260302213</t>
+          <t>20260305852</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr"/>
@@ -10401,12 +10203,12 @@
       <c r="T145" s="11" t="inlineStr"/>
       <c r="U145" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V145" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W145" s="12" t="inlineStr">
@@ -10417,26 +10219,26 @@
     </row>
     <row r="146" ht="26" customHeight="1">
       <c r="A146" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>20260302215</t>
+          <t>20260305853</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr"/>
@@ -10464,12 +10266,12 @@
       <c r="T146" s="11" t="inlineStr"/>
       <c r="U146" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V146" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W146" s="12" t="inlineStr">
@@ -10480,26 +10282,26 @@
     </row>
     <row r="147" ht="26" customHeight="1">
       <c r="A147" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>20260302522</t>
+          <t>20260306104</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr"/>
@@ -10527,12 +10329,12 @@
       <c r="T147" s="11" t="inlineStr"/>
       <c r="U147" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V147" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W147" s="12" t="inlineStr">
@@ -10543,26 +10345,26 @@
     </row>
     <row r="148" ht="26" customHeight="1">
       <c r="A148" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>20260302524</t>
+          <t>20260306105</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr"/>
@@ -10590,12 +10392,12 @@
       <c r="T148" s="11" t="inlineStr"/>
       <c r="U148" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V148" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W148" s="12" t="inlineStr">
@@ -10606,26 +10408,26 @@
     </row>
     <row r="149" ht="26" customHeight="1">
       <c r="A149" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>20260302606</t>
+          <t>20260306106</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr"/>
@@ -10653,12 +10455,12 @@
       <c r="T149" s="11" t="inlineStr"/>
       <c r="U149" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V149" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W149" s="12" t="inlineStr">
@@ -10669,26 +10471,26 @@
     </row>
     <row r="150" ht="26" customHeight="1">
       <c r="A150" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>20260302607</t>
+          <t>20260306107</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr"/>
@@ -10716,12 +10518,12 @@
       <c r="T150" s="11" t="inlineStr"/>
       <c r="U150" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V150" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W150" s="12" t="inlineStr">
@@ -10732,26 +10534,26 @@
     </row>
     <row r="151" ht="26" customHeight="1">
       <c r="A151" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>20260302611</t>
+          <t>20260306108</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr"/>
@@ -10779,12 +10581,12 @@
       <c r="T151" s="11" t="inlineStr"/>
       <c r="U151" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V151" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W151" s="12" t="inlineStr">
@@ -10795,26 +10597,26 @@
     </row>
     <row r="152" ht="26" customHeight="1">
       <c r="A152" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>20260302615</t>
+          <t>20260306109</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr"/>
@@ -10842,12 +10644,12 @@
       <c r="T152" s="11" t="inlineStr"/>
       <c r="U152" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V152" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W152" s="12" t="inlineStr">
@@ -10858,26 +10660,26 @@
     </row>
     <row r="153" ht="26" customHeight="1">
       <c r="A153" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>20260303161</t>
+          <t>20260306112</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr"/>
@@ -10905,12 +10707,12 @@
       <c r="T153" s="11" t="inlineStr"/>
       <c r="U153" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V153" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W153" s="12" t="inlineStr">
@@ -10921,26 +10723,26 @@
     </row>
     <row r="154" ht="26" customHeight="1">
       <c r="A154" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>20260303194</t>
+          <t>20260306113</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr"/>
@@ -10968,12 +10770,12 @@
       <c r="T154" s="11" t="inlineStr"/>
       <c r="U154" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V154" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W154" s="12" t="inlineStr">
@@ -10984,26 +10786,26 @@
     </row>
     <row r="155" ht="26" customHeight="1">
       <c r="A155" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>20260303195</t>
+          <t>20260306430</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr"/>
@@ -11031,12 +10833,12 @@
       <c r="T155" s="11" t="inlineStr"/>
       <c r="U155" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V155" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W155" s="12" t="inlineStr">
@@ -11047,26 +10849,26 @@
     </row>
     <row r="156" ht="26" customHeight="1">
       <c r="A156" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>20260303196</t>
+          <t>20260306591</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr"/>
@@ -11094,12 +10896,12 @@
       <c r="T156" s="11" t="inlineStr"/>
       <c r="U156" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V156" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W156" s="12" t="inlineStr">
@@ -11110,26 +10912,26 @@
     </row>
     <row r="157" ht="26" customHeight="1">
       <c r="A157" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>20260303197</t>
+          <t>20260306594</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr"/>
@@ -11157,12 +10959,12 @@
       <c r="T157" s="11" t="inlineStr"/>
       <c r="U157" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V157" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W157" s="12" t="inlineStr">
@@ -11173,26 +10975,26 @@
     </row>
     <row r="158" ht="26" customHeight="1">
       <c r="A158" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>20260303198</t>
+          <t>20260306595</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr"/>
@@ -11220,12 +11022,12 @@
       <c r="T158" s="11" t="inlineStr"/>
       <c r="U158" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V158" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W158" s="12" t="inlineStr">
@@ -11236,26 +11038,26 @@
     </row>
     <row r="159" ht="26" customHeight="1">
       <c r="A159" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>20260303199</t>
+          <t>20260306596</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr"/>
@@ -11283,12 +11085,12 @@
       <c r="T159" s="11" t="inlineStr"/>
       <c r="U159" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V159" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W159" s="12" t="inlineStr">
@@ -11297,2276 +11099,8 @@
         </is>
       </c>
     </row>
-    <row r="160" ht="26" customHeight="1">
-      <c r="A160" s="10" t="n">
-        <v>44</v>
-      </c>
-      <c r="B160" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C160" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D160" s="11" t="inlineStr">
-        <is>
-          <t>20260303200</t>
-        </is>
-      </c>
-      <c r="E160" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F160" s="11" t="inlineStr"/>
-      <c r="G160" s="11" t="inlineStr"/>
-      <c r="H160" s="11" t="inlineStr"/>
-      <c r="I160" s="11" t="inlineStr"/>
-      <c r="J160" s="11" t="inlineStr"/>
-      <c r="K160" s="11" t="inlineStr"/>
-      <c r="L160" s="11" t="inlineStr"/>
-      <c r="M160" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N160" s="11" t="inlineStr"/>
-      <c r="O160" s="11" t="inlineStr"/>
-      <c r="P160" s="11" t="inlineStr"/>
-      <c r="Q160" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R160" s="11" t="inlineStr"/>
-      <c r="S160" s="11" t="inlineStr"/>
-      <c r="T160" s="11" t="inlineStr"/>
-      <c r="U160" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V160" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W160" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="26" customHeight="1">
-      <c r="A161" s="10" t="n">
-        <v>44</v>
-      </c>
-      <c r="B161" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C161" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D161" s="11" t="inlineStr">
-        <is>
-          <t>20260303252</t>
-        </is>
-      </c>
-      <c r="E161" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F161" s="11" t="inlineStr"/>
-      <c r="G161" s="11" t="inlineStr"/>
-      <c r="H161" s="11" t="inlineStr"/>
-      <c r="I161" s="11" t="inlineStr"/>
-      <c r="J161" s="11" t="inlineStr"/>
-      <c r="K161" s="11" t="inlineStr"/>
-      <c r="L161" s="11" t="inlineStr"/>
-      <c r="M161" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N161" s="11" t="inlineStr"/>
-      <c r="O161" s="11" t="inlineStr"/>
-      <c r="P161" s="11" t="inlineStr"/>
-      <c r="Q161" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R161" s="11" t="inlineStr"/>
-      <c r="S161" s="11" t="inlineStr"/>
-      <c r="T161" s="11" t="inlineStr"/>
-      <c r="U161" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V161" s="11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W161" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="26" customHeight="1">
-      <c r="A162" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B162" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C162" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D162" s="11" t="inlineStr">
-        <is>
-          <t>20260301917</t>
-        </is>
-      </c>
-      <c r="E162" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F162" s="11" t="inlineStr"/>
-      <c r="G162" s="11" t="inlineStr"/>
-      <c r="H162" s="11" t="inlineStr"/>
-      <c r="I162" s="11" t="inlineStr"/>
-      <c r="J162" s="11" t="inlineStr"/>
-      <c r="K162" s="11" t="inlineStr"/>
-      <c r="L162" s="11" t="inlineStr"/>
-      <c r="M162" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N162" s="11" t="inlineStr"/>
-      <c r="O162" s="11" t="inlineStr"/>
-      <c r="P162" s="11" t="inlineStr"/>
-      <c r="Q162" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R162" s="11" t="inlineStr"/>
-      <c r="S162" s="11" t="inlineStr"/>
-      <c r="T162" s="11" t="inlineStr"/>
-      <c r="U162" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V162" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W162" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="26" customHeight="1">
-      <c r="A163" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B163" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C163" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D163" s="11" t="inlineStr">
-        <is>
-          <t>20260301999</t>
-        </is>
-      </c>
-      <c r="E163" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F163" s="11" t="inlineStr"/>
-      <c r="G163" s="11" t="inlineStr"/>
-      <c r="H163" s="11" t="inlineStr"/>
-      <c r="I163" s="11" t="inlineStr"/>
-      <c r="J163" s="11" t="inlineStr"/>
-      <c r="K163" s="11" t="inlineStr"/>
-      <c r="L163" s="11" t="inlineStr"/>
-      <c r="M163" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N163" s="11" t="inlineStr"/>
-      <c r="O163" s="11" t="inlineStr"/>
-      <c r="P163" s="11" t="inlineStr"/>
-      <c r="Q163" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R163" s="11" t="inlineStr"/>
-      <c r="S163" s="11" t="inlineStr"/>
-      <c r="T163" s="11" t="inlineStr"/>
-      <c r="U163" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V163" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W163" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="26" customHeight="1">
-      <c r="A164" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B164" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C164" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D164" s="11" t="inlineStr">
-        <is>
-          <t>20260302033</t>
-        </is>
-      </c>
-      <c r="E164" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F164" s="11" t="inlineStr"/>
-      <c r="G164" s="11" t="inlineStr"/>
-      <c r="H164" s="11" t="inlineStr"/>
-      <c r="I164" s="11" t="inlineStr"/>
-      <c r="J164" s="11" t="inlineStr"/>
-      <c r="K164" s="11" t="inlineStr"/>
-      <c r="L164" s="11" t="inlineStr"/>
-      <c r="M164" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N164" s="11" t="inlineStr"/>
-      <c r="O164" s="11" t="inlineStr"/>
-      <c r="P164" s="11" t="inlineStr"/>
-      <c r="Q164" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R164" s="11" t="inlineStr"/>
-      <c r="S164" s="11" t="inlineStr"/>
-      <c r="T164" s="11" t="inlineStr"/>
-      <c r="U164" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V164" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W164" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="26" customHeight="1">
-      <c r="A165" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B165" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C165" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D165" s="11" t="inlineStr">
-        <is>
-          <t>20260302048</t>
-        </is>
-      </c>
-      <c r="E165" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F165" s="11" t="inlineStr"/>
-      <c r="G165" s="11" t="inlineStr"/>
-      <c r="H165" s="11" t="inlineStr"/>
-      <c r="I165" s="11" t="inlineStr"/>
-      <c r="J165" s="11" t="inlineStr"/>
-      <c r="K165" s="11" t="inlineStr"/>
-      <c r="L165" s="11" t="inlineStr"/>
-      <c r="M165" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N165" s="11" t="inlineStr"/>
-      <c r="O165" s="11" t="inlineStr"/>
-      <c r="P165" s="11" t="inlineStr"/>
-      <c r="Q165" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R165" s="11" t="inlineStr"/>
-      <c r="S165" s="11" t="inlineStr"/>
-      <c r="T165" s="11" t="inlineStr"/>
-      <c r="U165" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V165" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W165" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="26" customHeight="1">
-      <c r="A166" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B166" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C166" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D166" s="11" t="inlineStr">
-        <is>
-          <t>20260302072</t>
-        </is>
-      </c>
-      <c r="E166" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F166" s="11" t="inlineStr"/>
-      <c r="G166" s="11" t="inlineStr"/>
-      <c r="H166" s="11" t="inlineStr"/>
-      <c r="I166" s="11" t="inlineStr"/>
-      <c r="J166" s="11" t="inlineStr"/>
-      <c r="K166" s="11" t="inlineStr"/>
-      <c r="L166" s="11" t="inlineStr"/>
-      <c r="M166" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N166" s="11" t="inlineStr"/>
-      <c r="O166" s="11" t="inlineStr"/>
-      <c r="P166" s="11" t="inlineStr"/>
-      <c r="Q166" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R166" s="11" t="inlineStr"/>
-      <c r="S166" s="11" t="inlineStr"/>
-      <c r="T166" s="11" t="inlineStr"/>
-      <c r="U166" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V166" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W166" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="26" customHeight="1">
-      <c r="A167" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C167" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D167" s="11" t="inlineStr">
-        <is>
-          <t>20260302282</t>
-        </is>
-      </c>
-      <c r="E167" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F167" s="11" t="inlineStr"/>
-      <c r="G167" s="11" t="inlineStr"/>
-      <c r="H167" s="11" t="inlineStr"/>
-      <c r="I167" s="11" t="inlineStr"/>
-      <c r="J167" s="11" t="inlineStr"/>
-      <c r="K167" s="11" t="inlineStr"/>
-      <c r="L167" s="11" t="inlineStr"/>
-      <c r="M167" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N167" s="11" t="inlineStr"/>
-      <c r="O167" s="11" t="inlineStr"/>
-      <c r="P167" s="11" t="inlineStr"/>
-      <c r="Q167" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R167" s="11" t="inlineStr"/>
-      <c r="S167" s="11" t="inlineStr"/>
-      <c r="T167" s="11" t="inlineStr"/>
-      <c r="U167" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V167" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W167" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="26" customHeight="1">
-      <c r="A168" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B168" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C168" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D168" s="11" t="inlineStr">
-        <is>
-          <t>20260302605</t>
-        </is>
-      </c>
-      <c r="E168" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F168" s="11" t="inlineStr"/>
-      <c r="G168" s="11" t="inlineStr"/>
-      <c r="H168" s="11" t="inlineStr"/>
-      <c r="I168" s="11" t="inlineStr"/>
-      <c r="J168" s="11" t="inlineStr"/>
-      <c r="K168" s="11" t="inlineStr"/>
-      <c r="L168" s="11" t="inlineStr"/>
-      <c r="M168" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N168" s="11" t="inlineStr"/>
-      <c r="O168" s="11" t="inlineStr"/>
-      <c r="P168" s="11" t="inlineStr"/>
-      <c r="Q168" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R168" s="11" t="inlineStr"/>
-      <c r="S168" s="11" t="inlineStr"/>
-      <c r="T168" s="11" t="inlineStr"/>
-      <c r="U168" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V168" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W168" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="26" customHeight="1">
-      <c r="A169" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B169" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C169" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D169" s="11" t="inlineStr">
-        <is>
-          <t>20260302759</t>
-        </is>
-      </c>
-      <c r="E169" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F169" s="11" t="inlineStr"/>
-      <c r="G169" s="11" t="inlineStr"/>
-      <c r="H169" s="11" t="inlineStr"/>
-      <c r="I169" s="11" t="inlineStr"/>
-      <c r="J169" s="11" t="inlineStr"/>
-      <c r="K169" s="11" t="inlineStr"/>
-      <c r="L169" s="11" t="inlineStr"/>
-      <c r="M169" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N169" s="11" t="inlineStr"/>
-      <c r="O169" s="11" t="inlineStr"/>
-      <c r="P169" s="11" t="inlineStr"/>
-      <c r="Q169" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R169" s="11" t="inlineStr"/>
-      <c r="S169" s="11" t="inlineStr"/>
-      <c r="T169" s="11" t="inlineStr"/>
-      <c r="U169" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V169" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W169" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="26" customHeight="1">
-      <c r="A170" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B170" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C170" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D170" s="11" t="inlineStr">
-        <is>
-          <t>20260302760</t>
-        </is>
-      </c>
-      <c r="E170" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F170" s="11" t="inlineStr"/>
-      <c r="G170" s="11" t="inlineStr"/>
-      <c r="H170" s="11" t="inlineStr"/>
-      <c r="I170" s="11" t="inlineStr"/>
-      <c r="J170" s="11" t="inlineStr"/>
-      <c r="K170" s="11" t="inlineStr"/>
-      <c r="L170" s="11" t="inlineStr"/>
-      <c r="M170" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N170" s="11" t="inlineStr"/>
-      <c r="O170" s="11" t="inlineStr"/>
-      <c r="P170" s="11" t="inlineStr"/>
-      <c r="Q170" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R170" s="11" t="inlineStr"/>
-      <c r="S170" s="11" t="inlineStr"/>
-      <c r="T170" s="11" t="inlineStr"/>
-      <c r="U170" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V170" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W170" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="26" customHeight="1">
-      <c r="A171" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B171" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C171" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D171" s="11" t="inlineStr">
-        <is>
-          <t>20260302761</t>
-        </is>
-      </c>
-      <c r="E171" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F171" s="11" t="inlineStr"/>
-      <c r="G171" s="11" t="inlineStr"/>
-      <c r="H171" s="11" t="inlineStr"/>
-      <c r="I171" s="11" t="inlineStr"/>
-      <c r="J171" s="11" t="inlineStr"/>
-      <c r="K171" s="11" t="inlineStr"/>
-      <c r="L171" s="11" t="inlineStr"/>
-      <c r="M171" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N171" s="11" t="inlineStr"/>
-      <c r="O171" s="11" t="inlineStr"/>
-      <c r="P171" s="11" t="inlineStr"/>
-      <c r="Q171" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R171" s="11" t="inlineStr"/>
-      <c r="S171" s="11" t="inlineStr"/>
-      <c r="T171" s="11" t="inlineStr"/>
-      <c r="U171" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V171" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W171" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="26" customHeight="1">
-      <c r="A172" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B172" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C172" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D172" s="11" t="inlineStr">
-        <is>
-          <t>20260302762</t>
-        </is>
-      </c>
-      <c r="E172" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F172" s="11" t="inlineStr"/>
-      <c r="G172" s="11" t="inlineStr"/>
-      <c r="H172" s="11" t="inlineStr"/>
-      <c r="I172" s="11" t="inlineStr"/>
-      <c r="J172" s="11" t="inlineStr"/>
-      <c r="K172" s="11" t="inlineStr"/>
-      <c r="L172" s="11" t="inlineStr"/>
-      <c r="M172" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N172" s="11" t="inlineStr"/>
-      <c r="O172" s="11" t="inlineStr"/>
-      <c r="P172" s="11" t="inlineStr"/>
-      <c r="Q172" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R172" s="11" t="inlineStr"/>
-      <c r="S172" s="11" t="inlineStr"/>
-      <c r="T172" s="11" t="inlineStr"/>
-      <c r="U172" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V172" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W172" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="26" customHeight="1">
-      <c r="A173" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B173" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C173" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D173" s="11" t="inlineStr">
-        <is>
-          <t>20260302763</t>
-        </is>
-      </c>
-      <c r="E173" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F173" s="11" t="inlineStr"/>
-      <c r="G173" s="11" t="inlineStr"/>
-      <c r="H173" s="11" t="inlineStr"/>
-      <c r="I173" s="11" t="inlineStr"/>
-      <c r="J173" s="11" t="inlineStr"/>
-      <c r="K173" s="11" t="inlineStr"/>
-      <c r="L173" s="11" t="inlineStr"/>
-      <c r="M173" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N173" s="11" t="inlineStr"/>
-      <c r="O173" s="11" t="inlineStr"/>
-      <c r="P173" s="11" t="inlineStr"/>
-      <c r="Q173" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R173" s="11" t="inlineStr"/>
-      <c r="S173" s="11" t="inlineStr"/>
-      <c r="T173" s="11" t="inlineStr"/>
-      <c r="U173" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V173" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W173" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="26" customHeight="1">
-      <c r="A174" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B174" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C174" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D174" s="11" t="inlineStr">
-        <is>
-          <t>20260302764</t>
-        </is>
-      </c>
-      <c r="E174" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F174" s="11" t="inlineStr"/>
-      <c r="G174" s="11" t="inlineStr"/>
-      <c r="H174" s="11" t="inlineStr"/>
-      <c r="I174" s="11" t="inlineStr"/>
-      <c r="J174" s="11" t="inlineStr"/>
-      <c r="K174" s="11" t="inlineStr"/>
-      <c r="L174" s="11" t="inlineStr"/>
-      <c r="M174" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N174" s="11" t="inlineStr"/>
-      <c r="O174" s="11" t="inlineStr"/>
-      <c r="P174" s="11" t="inlineStr"/>
-      <c r="Q174" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R174" s="11" t="inlineStr"/>
-      <c r="S174" s="11" t="inlineStr"/>
-      <c r="T174" s="11" t="inlineStr"/>
-      <c r="U174" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V174" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W174" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="26" customHeight="1">
-      <c r="A175" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B175" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C175" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D175" s="11" t="inlineStr">
-        <is>
-          <t>20260302765</t>
-        </is>
-      </c>
-      <c r="E175" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F175" s="11" t="inlineStr"/>
-      <c r="G175" s="11" t="inlineStr"/>
-      <c r="H175" s="11" t="inlineStr"/>
-      <c r="I175" s="11" t="inlineStr"/>
-      <c r="J175" s="11" t="inlineStr"/>
-      <c r="K175" s="11" t="inlineStr"/>
-      <c r="L175" s="11" t="inlineStr"/>
-      <c r="M175" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N175" s="11" t="inlineStr"/>
-      <c r="O175" s="11" t="inlineStr"/>
-      <c r="P175" s="11" t="inlineStr"/>
-      <c r="Q175" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R175" s="11" t="inlineStr"/>
-      <c r="S175" s="11" t="inlineStr"/>
-      <c r="T175" s="11" t="inlineStr"/>
-      <c r="U175" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V175" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W175" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="26" customHeight="1">
-      <c r="A176" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B176" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C176" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D176" s="11" t="inlineStr">
-        <is>
-          <t>20260302766</t>
-        </is>
-      </c>
-      <c r="E176" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F176" s="11" t="inlineStr"/>
-      <c r="G176" s="11" t="inlineStr"/>
-      <c r="H176" s="11" t="inlineStr"/>
-      <c r="I176" s="11" t="inlineStr"/>
-      <c r="J176" s="11" t="inlineStr"/>
-      <c r="K176" s="11" t="inlineStr"/>
-      <c r="L176" s="11" t="inlineStr"/>
-      <c r="M176" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N176" s="11" t="inlineStr"/>
-      <c r="O176" s="11" t="inlineStr"/>
-      <c r="P176" s="11" t="inlineStr"/>
-      <c r="Q176" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R176" s="11" t="inlineStr"/>
-      <c r="S176" s="11" t="inlineStr"/>
-      <c r="T176" s="11" t="inlineStr"/>
-      <c r="U176" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V176" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W176" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="26" customHeight="1">
-      <c r="A177" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B177" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C177" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D177" s="11" t="inlineStr">
-        <is>
-          <t>20260302767</t>
-        </is>
-      </c>
-      <c r="E177" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F177" s="11" t="inlineStr"/>
-      <c r="G177" s="11" t="inlineStr"/>
-      <c r="H177" s="11" t="inlineStr"/>
-      <c r="I177" s="11" t="inlineStr"/>
-      <c r="J177" s="11" t="inlineStr"/>
-      <c r="K177" s="11" t="inlineStr"/>
-      <c r="L177" s="11" t="inlineStr"/>
-      <c r="M177" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N177" s="11" t="inlineStr"/>
-      <c r="O177" s="11" t="inlineStr"/>
-      <c r="P177" s="11" t="inlineStr"/>
-      <c r="Q177" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R177" s="11" t="inlineStr"/>
-      <c r="S177" s="11" t="inlineStr"/>
-      <c r="T177" s="11" t="inlineStr"/>
-      <c r="U177" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V177" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W177" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="26" customHeight="1">
-      <c r="A178" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B178" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C178" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D178" s="11" t="inlineStr">
-        <is>
-          <t>20260302768</t>
-        </is>
-      </c>
-      <c r="E178" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F178" s="11" t="inlineStr"/>
-      <c r="G178" s="11" t="inlineStr"/>
-      <c r="H178" s="11" t="inlineStr"/>
-      <c r="I178" s="11" t="inlineStr"/>
-      <c r="J178" s="11" t="inlineStr"/>
-      <c r="K178" s="11" t="inlineStr"/>
-      <c r="L178" s="11" t="inlineStr"/>
-      <c r="M178" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N178" s="11" t="inlineStr"/>
-      <c r="O178" s="11" t="inlineStr"/>
-      <c r="P178" s="11" t="inlineStr"/>
-      <c r="Q178" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R178" s="11" t="inlineStr"/>
-      <c r="S178" s="11" t="inlineStr"/>
-      <c r="T178" s="11" t="inlineStr"/>
-      <c r="U178" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V178" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W178" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="179" ht="26" customHeight="1">
-      <c r="A179" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B179" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C179" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D179" s="11" t="inlineStr">
-        <is>
-          <t>20260302769</t>
-        </is>
-      </c>
-      <c r="E179" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F179" s="11" t="inlineStr"/>
-      <c r="G179" s="11" t="inlineStr"/>
-      <c r="H179" s="11" t="inlineStr"/>
-      <c r="I179" s="11" t="inlineStr"/>
-      <c r="J179" s="11" t="inlineStr"/>
-      <c r="K179" s="11" t="inlineStr"/>
-      <c r="L179" s="11" t="inlineStr"/>
-      <c r="M179" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N179" s="11" t="inlineStr"/>
-      <c r="O179" s="11" t="inlineStr"/>
-      <c r="P179" s="11" t="inlineStr"/>
-      <c r="Q179" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R179" s="11" t="inlineStr"/>
-      <c r="S179" s="11" t="inlineStr"/>
-      <c r="T179" s="11" t="inlineStr"/>
-      <c r="U179" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V179" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W179" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="180" ht="26" customHeight="1">
-      <c r="A180" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B180" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C180" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D180" s="11" t="inlineStr">
-        <is>
-          <t>20260302770</t>
-        </is>
-      </c>
-      <c r="E180" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F180" s="11" t="inlineStr"/>
-      <c r="G180" s="11" t="inlineStr"/>
-      <c r="H180" s="11" t="inlineStr"/>
-      <c r="I180" s="11" t="inlineStr"/>
-      <c r="J180" s="11" t="inlineStr"/>
-      <c r="K180" s="11" t="inlineStr"/>
-      <c r="L180" s="11" t="inlineStr"/>
-      <c r="M180" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N180" s="11" t="inlineStr"/>
-      <c r="O180" s="11" t="inlineStr"/>
-      <c r="P180" s="11" t="inlineStr"/>
-      <c r="Q180" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R180" s="11" t="inlineStr"/>
-      <c r="S180" s="11" t="inlineStr"/>
-      <c r="T180" s="11" t="inlineStr"/>
-      <c r="U180" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V180" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W180" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="181" ht="26" customHeight="1">
-      <c r="A181" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B181" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C181" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D181" s="11" t="inlineStr">
-        <is>
-          <t>20260302771</t>
-        </is>
-      </c>
-      <c r="E181" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F181" s="11" t="inlineStr"/>
-      <c r="G181" s="11" t="inlineStr"/>
-      <c r="H181" s="11" t="inlineStr"/>
-      <c r="I181" s="11" t="inlineStr"/>
-      <c r="J181" s="11" t="inlineStr"/>
-      <c r="K181" s="11" t="inlineStr"/>
-      <c r="L181" s="11" t="inlineStr"/>
-      <c r="M181" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N181" s="11" t="inlineStr"/>
-      <c r="O181" s="11" t="inlineStr"/>
-      <c r="P181" s="11" t="inlineStr"/>
-      <c r="Q181" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R181" s="11" t="inlineStr"/>
-      <c r="S181" s="11" t="inlineStr"/>
-      <c r="T181" s="11" t="inlineStr"/>
-      <c r="U181" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V181" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W181" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="182" ht="26" customHeight="1">
-      <c r="A182" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B182" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C182" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D182" s="11" t="inlineStr">
-        <is>
-          <t>20260302772</t>
-        </is>
-      </c>
-      <c r="E182" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F182" s="11" t="inlineStr"/>
-      <c r="G182" s="11" t="inlineStr"/>
-      <c r="H182" s="11" t="inlineStr"/>
-      <c r="I182" s="11" t="inlineStr"/>
-      <c r="J182" s="11" t="inlineStr"/>
-      <c r="K182" s="11" t="inlineStr"/>
-      <c r="L182" s="11" t="inlineStr"/>
-      <c r="M182" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N182" s="11" t="inlineStr"/>
-      <c r="O182" s="11" t="inlineStr"/>
-      <c r="P182" s="11" t="inlineStr"/>
-      <c r="Q182" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R182" s="11" t="inlineStr"/>
-      <c r="S182" s="11" t="inlineStr"/>
-      <c r="T182" s="11" t="inlineStr"/>
-      <c r="U182" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V182" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W182" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="183" ht="26" customHeight="1">
-      <c r="A183" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B183" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C183" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D183" s="11" t="inlineStr">
-        <is>
-          <t>20260302774</t>
-        </is>
-      </c>
-      <c r="E183" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F183" s="11" t="inlineStr"/>
-      <c r="G183" s="11" t="inlineStr"/>
-      <c r="H183" s="11" t="inlineStr"/>
-      <c r="I183" s="11" t="inlineStr"/>
-      <c r="J183" s="11" t="inlineStr"/>
-      <c r="K183" s="11" t="inlineStr"/>
-      <c r="L183" s="11" t="inlineStr"/>
-      <c r="M183" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N183" s="11" t="inlineStr"/>
-      <c r="O183" s="11" t="inlineStr"/>
-      <c r="P183" s="11" t="inlineStr"/>
-      <c r="Q183" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R183" s="11" t="inlineStr"/>
-      <c r="S183" s="11" t="inlineStr"/>
-      <c r="T183" s="11" t="inlineStr"/>
-      <c r="U183" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V183" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W183" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="184" ht="26" customHeight="1">
-      <c r="A184" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B184" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C184" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D184" s="11" t="inlineStr">
-        <is>
-          <t>20260302775</t>
-        </is>
-      </c>
-      <c r="E184" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F184" s="11" t="inlineStr"/>
-      <c r="G184" s="11" t="inlineStr"/>
-      <c r="H184" s="11" t="inlineStr"/>
-      <c r="I184" s="11" t="inlineStr"/>
-      <c r="J184" s="11" t="inlineStr"/>
-      <c r="K184" s="11" t="inlineStr"/>
-      <c r="L184" s="11" t="inlineStr"/>
-      <c r="M184" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N184" s="11" t="inlineStr"/>
-      <c r="O184" s="11" t="inlineStr"/>
-      <c r="P184" s="11" t="inlineStr"/>
-      <c r="Q184" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R184" s="11" t="inlineStr"/>
-      <c r="S184" s="11" t="inlineStr"/>
-      <c r="T184" s="11" t="inlineStr"/>
-      <c r="U184" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V184" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W184" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="185" ht="26" customHeight="1">
-      <c r="A185" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B185" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C185" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D185" s="11" t="inlineStr">
-        <is>
-          <t>20260302776</t>
-        </is>
-      </c>
-      <c r="E185" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F185" s="11" t="inlineStr"/>
-      <c r="G185" s="11" t="inlineStr"/>
-      <c r="H185" s="11" t="inlineStr"/>
-      <c r="I185" s="11" t="inlineStr"/>
-      <c r="J185" s="11" t="inlineStr"/>
-      <c r="K185" s="11" t="inlineStr"/>
-      <c r="L185" s="11" t="inlineStr"/>
-      <c r="M185" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N185" s="11" t="inlineStr"/>
-      <c r="O185" s="11" t="inlineStr"/>
-      <c r="P185" s="11" t="inlineStr"/>
-      <c r="Q185" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R185" s="11" t="inlineStr"/>
-      <c r="S185" s="11" t="inlineStr"/>
-      <c r="T185" s="11" t="inlineStr"/>
-      <c r="U185" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V185" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W185" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="26" customHeight="1">
-      <c r="A186" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B186" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C186" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D186" s="11" t="inlineStr">
-        <is>
-          <t>20260302777</t>
-        </is>
-      </c>
-      <c r="E186" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F186" s="11" t="inlineStr"/>
-      <c r="G186" s="11" t="inlineStr"/>
-      <c r="H186" s="11" t="inlineStr"/>
-      <c r="I186" s="11" t="inlineStr"/>
-      <c r="J186" s="11" t="inlineStr"/>
-      <c r="K186" s="11" t="inlineStr"/>
-      <c r="L186" s="11" t="inlineStr"/>
-      <c r="M186" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N186" s="11" t="inlineStr"/>
-      <c r="O186" s="11" t="inlineStr"/>
-      <c r="P186" s="11" t="inlineStr"/>
-      <c r="Q186" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R186" s="11" t="inlineStr"/>
-      <c r="S186" s="11" t="inlineStr"/>
-      <c r="T186" s="11" t="inlineStr"/>
-      <c r="U186" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V186" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W186" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="187" ht="26" customHeight="1">
-      <c r="A187" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B187" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C187" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D187" s="11" t="inlineStr">
-        <is>
-          <t>20260302778</t>
-        </is>
-      </c>
-      <c r="E187" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F187" s="11" t="inlineStr"/>
-      <c r="G187" s="11" t="inlineStr"/>
-      <c r="H187" s="11" t="inlineStr"/>
-      <c r="I187" s="11" t="inlineStr"/>
-      <c r="J187" s="11" t="inlineStr"/>
-      <c r="K187" s="11" t="inlineStr"/>
-      <c r="L187" s="11" t="inlineStr"/>
-      <c r="M187" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N187" s="11" t="inlineStr"/>
-      <c r="O187" s="11" t="inlineStr"/>
-      <c r="P187" s="11" t="inlineStr"/>
-      <c r="Q187" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R187" s="11" t="inlineStr"/>
-      <c r="S187" s="11" t="inlineStr"/>
-      <c r="T187" s="11" t="inlineStr"/>
-      <c r="U187" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V187" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W187" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="188" ht="26" customHeight="1">
-      <c r="A188" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B188" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C188" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D188" s="11" t="inlineStr">
-        <is>
-          <t>20260302779</t>
-        </is>
-      </c>
-      <c r="E188" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F188" s="11" t="inlineStr"/>
-      <c r="G188" s="11" t="inlineStr"/>
-      <c r="H188" s="11" t="inlineStr"/>
-      <c r="I188" s="11" t="inlineStr"/>
-      <c r="J188" s="11" t="inlineStr"/>
-      <c r="K188" s="11" t="inlineStr"/>
-      <c r="L188" s="11" t="inlineStr"/>
-      <c r="M188" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N188" s="11" t="inlineStr"/>
-      <c r="O188" s="11" t="inlineStr"/>
-      <c r="P188" s="11" t="inlineStr"/>
-      <c r="Q188" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R188" s="11" t="inlineStr"/>
-      <c r="S188" s="11" t="inlineStr"/>
-      <c r="T188" s="11" t="inlineStr"/>
-      <c r="U188" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V188" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W188" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="189" ht="26" customHeight="1">
-      <c r="A189" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B189" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C189" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D189" s="11" t="inlineStr">
-        <is>
-          <t>20260302780</t>
-        </is>
-      </c>
-      <c r="E189" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F189" s="11" t="inlineStr"/>
-      <c r="G189" s="11" t="inlineStr"/>
-      <c r="H189" s="11" t="inlineStr"/>
-      <c r="I189" s="11" t="inlineStr"/>
-      <c r="J189" s="11" t="inlineStr"/>
-      <c r="K189" s="11" t="inlineStr"/>
-      <c r="L189" s="11" t="inlineStr"/>
-      <c r="M189" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N189" s="11" t="inlineStr"/>
-      <c r="O189" s="11" t="inlineStr"/>
-      <c r="P189" s="11" t="inlineStr"/>
-      <c r="Q189" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R189" s="11" t="inlineStr"/>
-      <c r="S189" s="11" t="inlineStr"/>
-      <c r="T189" s="11" t="inlineStr"/>
-      <c r="U189" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V189" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W189" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="190" ht="26" customHeight="1">
-      <c r="A190" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B190" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C190" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D190" s="11" t="inlineStr">
-        <is>
-          <t>20260302781</t>
-        </is>
-      </c>
-      <c r="E190" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F190" s="11" t="inlineStr"/>
-      <c r="G190" s="11" t="inlineStr"/>
-      <c r="H190" s="11" t="inlineStr"/>
-      <c r="I190" s="11" t="inlineStr"/>
-      <c r="J190" s="11" t="inlineStr"/>
-      <c r="K190" s="11" t="inlineStr"/>
-      <c r="L190" s="11" t="inlineStr"/>
-      <c r="M190" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N190" s="11" t="inlineStr"/>
-      <c r="O190" s="11" t="inlineStr"/>
-      <c r="P190" s="11" t="inlineStr"/>
-      <c r="Q190" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R190" s="11" t="inlineStr"/>
-      <c r="S190" s="11" t="inlineStr"/>
-      <c r="T190" s="11" t="inlineStr"/>
-      <c r="U190" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V190" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W190" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="191" ht="26" customHeight="1">
-      <c r="A191" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B191" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C191" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D191" s="11" t="inlineStr">
-        <is>
-          <t>20260302782</t>
-        </is>
-      </c>
-      <c r="E191" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F191" s="11" t="inlineStr"/>
-      <c r="G191" s="11" t="inlineStr"/>
-      <c r="H191" s="11" t="inlineStr"/>
-      <c r="I191" s="11" t="inlineStr"/>
-      <c r="J191" s="11" t="inlineStr"/>
-      <c r="K191" s="11" t="inlineStr"/>
-      <c r="L191" s="11" t="inlineStr"/>
-      <c r="M191" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N191" s="11" t="inlineStr"/>
-      <c r="O191" s="11" t="inlineStr"/>
-      <c r="P191" s="11" t="inlineStr"/>
-      <c r="Q191" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R191" s="11" t="inlineStr"/>
-      <c r="S191" s="11" t="inlineStr"/>
-      <c r="T191" s="11" t="inlineStr"/>
-      <c r="U191" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V191" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W191" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="192" ht="26" customHeight="1">
-      <c r="A192" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B192" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C192" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D192" s="11" t="inlineStr">
-        <is>
-          <t>20260302783</t>
-        </is>
-      </c>
-      <c r="E192" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F192" s="11" t="inlineStr"/>
-      <c r="G192" s="11" t="inlineStr"/>
-      <c r="H192" s="11" t="inlineStr"/>
-      <c r="I192" s="11" t="inlineStr"/>
-      <c r="J192" s="11" t="inlineStr"/>
-      <c r="K192" s="11" t="inlineStr"/>
-      <c r="L192" s="11" t="inlineStr"/>
-      <c r="M192" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N192" s="11" t="inlineStr"/>
-      <c r="O192" s="11" t="inlineStr"/>
-      <c r="P192" s="11" t="inlineStr"/>
-      <c r="Q192" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R192" s="11" t="inlineStr"/>
-      <c r="S192" s="11" t="inlineStr"/>
-      <c r="T192" s="11" t="inlineStr"/>
-      <c r="U192" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V192" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W192" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="193" ht="26" customHeight="1">
-      <c r="A193" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B193" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C193" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D193" s="11" t="inlineStr">
-        <is>
-          <t>20260302885</t>
-        </is>
-      </c>
-      <c r="E193" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F193" s="11" t="inlineStr"/>
-      <c r="G193" s="11" t="inlineStr"/>
-      <c r="H193" s="11" t="inlineStr"/>
-      <c r="I193" s="11" t="inlineStr"/>
-      <c r="J193" s="11" t="inlineStr"/>
-      <c r="K193" s="11" t="inlineStr"/>
-      <c r="L193" s="11" t="inlineStr"/>
-      <c r="M193" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N193" s="11" t="inlineStr"/>
-      <c r="O193" s="11" t="inlineStr"/>
-      <c r="P193" s="11" t="inlineStr"/>
-      <c r="Q193" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R193" s="11" t="inlineStr"/>
-      <c r="S193" s="11" t="inlineStr"/>
-      <c r="T193" s="11" t="inlineStr"/>
-      <c r="U193" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V193" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W193" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="194" ht="26" customHeight="1">
-      <c r="A194" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B194" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C194" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D194" s="11" t="inlineStr">
-        <is>
-          <t>20260303168</t>
-        </is>
-      </c>
-      <c r="E194" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F194" s="11" t="inlineStr"/>
-      <c r="G194" s="11" t="inlineStr"/>
-      <c r="H194" s="11" t="inlineStr"/>
-      <c r="I194" s="11" t="inlineStr"/>
-      <c r="J194" s="11" t="inlineStr"/>
-      <c r="K194" s="11" t="inlineStr"/>
-      <c r="L194" s="11" t="inlineStr"/>
-      <c r="M194" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N194" s="11" t="inlineStr"/>
-      <c r="O194" s="11" t="inlineStr"/>
-      <c r="P194" s="11" t="inlineStr"/>
-      <c r="Q194" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R194" s="11" t="inlineStr"/>
-      <c r="S194" s="11" t="inlineStr"/>
-      <c r="T194" s="11" t="inlineStr"/>
-      <c r="U194" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V194" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W194" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="195" ht="26" customHeight="1">
-      <c r="A195" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B195" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C195" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D195" s="11" t="inlineStr">
-        <is>
-          <t>20260303171</t>
-        </is>
-      </c>
-      <c r="E195" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="F195" s="11" t="inlineStr"/>
-      <c r="G195" s="11" t="inlineStr"/>
-      <c r="H195" s="11" t="inlineStr"/>
-      <c r="I195" s="11" t="inlineStr"/>
-      <c r="J195" s="11" t="inlineStr"/>
-      <c r="K195" s="11" t="inlineStr"/>
-      <c r="L195" s="11" t="inlineStr"/>
-      <c r="M195" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N195" s="11" t="inlineStr"/>
-      <c r="O195" s="11" t="inlineStr"/>
-      <c r="P195" s="11" t="inlineStr"/>
-      <c r="Q195" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R195" s="11" t="inlineStr"/>
-      <c r="S195" s="11" t="inlineStr"/>
-      <c r="T195" s="11" t="inlineStr"/>
-      <c r="U195" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V195" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W195" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W195"/>
+  <autoFilter ref="A1:W159"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
@@ -13726,42 +11260,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W157" r:id="rId156"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W158" r:id="rId157"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W159" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W160" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W161" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W162" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W168" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W170" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W171" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W172" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W173" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W174" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W175" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W176" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W177" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W178" r:id="rId177"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W179" r:id="rId178"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W180" r:id="rId179"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W181" r:id="rId180"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W182" r:id="rId181"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W183" r:id="rId182"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W184" r:id="rId183"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W185" r:id="rId184"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W186" r:id="rId185"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W187" r:id="rId186"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W188" r:id="rId187"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W189" r:id="rId188"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W190" r:id="rId189"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W191" r:id="rId190"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W192" r:id="rId191"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W193" r:id="rId192"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W194" r:id="rId193"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W195" r:id="rId194"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -13773,7 +11271,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -13790,7 +11288,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-05-20 05:09</t>
+          <t>Run: 2026-05-21 05:16</t>
         </is>
       </c>
     </row>
@@ -13805,7 +11303,7 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>194</v>
+        <v>158</v>
       </c>
     </row>
     <row r="5">
@@ -13815,7 +11313,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>18</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6">
@@ -13835,7 +11333,7 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>152</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8">
@@ -13845,7 +11343,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -13855,7 +11353,7 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
@@ -13881,37 +11379,37 @@
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>70</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Federal Tax Lien</t>
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>55</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Notice of Trustee Sale</t>
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Notice of Trustee Sale</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -13921,37 +11419,7 @@
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
-        <is>
-          <t>Lis Pendens</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="inlineStr">
-        <is>
-          <t>Tax Deed</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Mechanic Lien</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$222</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$205</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W222"/>
+  <dimension ref="A1:W205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -705,45 +705,57 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>20260308486</t>
+          <t>20260309936</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>Cornelius Donald Scott II</t>
+          <t>MARGARET ANN HALL</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo Bank, N.A. Leonard J. McDonald</t>
+          <t>PennyMac Loan Services, LLC</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>219500</v>
+        <v>357200</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr"/>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>12345 West Campbell Avenue</t>
-        </is>
-      </c>
-      <c r="L2" s="3" t="inlineStr"/>
+          <t>9834 N 34TH AVE</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
       <c r="M2" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>85051</t>
+        </is>
+      </c>
       <c r="O2" s="3" t="inlineStr"/>
       <c r="P2" s="3" t="inlineStr"/>
       <c r="Q2" s="3" t="inlineStr">
@@ -754,12 +766,12 @@
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>501-63-4756</t>
+          <t>149-15-026</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo Bank, N.A. Leonard J. McDonald</t>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -794,45 +806,57 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>20260308507</t>
+          <t>20260309944</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Noe M Carranza</t>
+          <t>KENNETH J. BACKER AND LESLIE A. BACKER</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Wilmington Trust, National Association as trustee for Current Trustee:</t>
+          <t>PennyMac Loan Services, LLC</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>409000</v>
+        <v>357000</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr"/>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>19919 W Rustler Rd</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>19270 N 62ND DR</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>85308</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
@@ -843,12 +867,12 @@
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>400-76-1739</t>
+          <t>200-28-5050</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>Tryon Street Acquisition Trust I Leonard J. McDonald</t>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -883,49 +907,57 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>20260308519</t>
+          <t>20260310184</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Joseph A Errante and Britney D Errante</t>
+          <t>LINDA A. KLEIN</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
+          <t>Finance of America Reverse LLC</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>208650</v>
+        <v>450000</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>201 West Jefferson</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>292 South 230th Lane</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>5877 N GRANITE REEF ROAD #1107</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>SCOTTSDALE</t>
+        </is>
+      </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr"/>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>85250</t>
+        </is>
+      </c>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr">
@@ -936,12 +968,12 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>504-21-6694</t>
+          <t>173-75-2760</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -976,49 +1008,57 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>20260308535</t>
+          <t>20260310222</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Binh Truong</t>
+          <t>KENTON DURKEE, UNMARRIED MAN</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Selene Finance, LP Leonard J. McDonald</t>
+          <t>Rocket Mortgage, LLC sbm Nationstar Mortgage LLC</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>234500</v>
+        <v>188000</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>983 W Morelos St</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr"/>
+          <t>1860 E CONCORDA DR</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>TEMPE</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N5" s="3" t="inlineStr"/>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>85282</t>
+        </is>
+      </c>
       <c r="O5" s="3" t="inlineStr"/>
       <c r="P5" s="3" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr">
@@ -1029,12 +1069,12 @@
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>303-21-3227</t>
+          <t>133-44-048</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>Selene Finance, LP Leonard J. McDonald</t>
+          <t>MTC Financial inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1069,26 +1109,30 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>20260308566</t>
+          <t>20260310277</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>PAUL B. BLAND AND MARILYN Y. BLAND</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr"/>
+          <t>LINDA SCOTT ARROYO AND RENE MARKUS ARROYO, WIFE AND HUSBAND</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Rocket Mortgage, LLC sbm Nationstar Mortgage LLC</t>
+        </is>
+      </c>
       <c r="H6" s="4" t="n">
-        <v>408000</v>
+        <v>482576</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -1098,16 +1142,24 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>9134 N 95TH LN</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>7530 W JONES AVENUE</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>85043</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
@@ -1118,10 +1170,14 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>142-90-647</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr"/>
+          <t>104-52-760</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -1154,30 +1210,30 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>20260308585</t>
+          <t>20260310296</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>ANAPALANI GAYLENE HARTZELL</t>
+          <t>SHERRY MAJEWSKI</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Wilmington Savings Fund Society, FSB, not in its individual capacity but solely as owner trustee for Verus</t>
+          <t>Nova Financial &amp; Investment Corporation</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>220800</v>
+        <v>274550</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1187,16 +1243,24 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>5676 W EVERGREEN RD</t>
-        </is>
-      </c>
-      <c r="L7" s="3" t="inlineStr"/>
+          <t>1456 W LA JOLLA DR</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>TEMPE</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N7" s="3" t="inlineStr"/>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
+          <t>85282</t>
+        </is>
+      </c>
       <c r="O7" s="3" t="inlineStr"/>
       <c r="P7" s="3" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
@@ -1207,12 +1271,12 @@
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>148-14-154</t>
+          <t>123-27-7445</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Michelle R. Ghidotti, Esq.</t>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1247,49 +1311,57 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>20260308645</t>
+          <t>20260310477</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Paul Andrew Proulx Jr and Briann Cyrus Holguin</t>
+          <t>HAILEY MICHELLE RIVERO AND ADAM DEL RIVERO III, WIFE AND HUSBAND</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>United Wholesale Mortgage, LLC Leonard J, McDonald</t>
+          <t>NEWREZ LLC</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>274928</v>
+        <v>475000</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
+          <t>SUPERIOR COURT BUILDING</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>11223 West Missouri Avenue</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr"/>
+          <t>11227 E SHERIDAN AVE</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr"/>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>85212</t>
+        </is>
+      </c>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
@@ -1298,14 +1370,10 @@
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr"/>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>142-64-1622</t>
-        </is>
-      </c>
+      <c r="S8" s="3" t="inlineStr"/>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>United Wholesale Mortgage, LLC Leonard J, McDonald</t>
+          <t>Prime Recon LLC</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1340,49 +1408,49 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>20260309138</t>
+          <t>20260311118</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Eduardo Gaspar Cervantes</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>NewRez LLC Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="H9" s="4" t="n">
-        <v>247000</v>
+        <v>328932</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>7835 W. Alvarado Rd.</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
+          <t>4231 West Krall Street</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>85035</t>
-        </is>
-      </c>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr">
@@ -1393,10 +1461,14 @@
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>102-38-542</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr"/>
+          <t>152-31-1085</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>NewRez LLC Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -1429,30 +1501,30 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>20260309293</t>
+          <t>20260311123</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>STARR MARIE SECOR</t>
+          <t>Dena M. Scott</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>SERVIS ONE, INC. DBA BSI FINANCIAL SERVICES</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>252103</v>
+        <v>339845</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1462,7 +1534,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>921 W UNIVERSITY DR</t>
+          <t>8900 W GREER AVE</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr"/>
@@ -1482,12 +1554,12 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>135-55-233</t>
+          <t>142-45-173</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Michelle R. Ghidotti, Esq.</t>
+          <t>Vylla Solutions, LLC</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1507,469 +1579,465 @@
       </c>
     </row>
     <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="A11" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>20260308258</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>LISA M. BODINE</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>SANDRA KAY MILLAR</t>
-        </is>
-      </c>
-      <c r="H11" s="8" t="n">
-        <v>60000</v>
-      </c>
-      <c r="I11" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="J11" s="7" t="inlineStr">
-        <is>
-          <t>201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K11" s="7" t="inlineStr">
-        <is>
-          <t>5445 EAST MCKELLIPS RD #45</t>
-        </is>
-      </c>
-      <c r="L11" s="7" t="inlineStr">
-        <is>
-          <t>MESA</t>
-        </is>
-      </c>
-      <c r="M11" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N11" s="7" t="inlineStr">
-        <is>
-          <t>85215</t>
-        </is>
-      </c>
-      <c r="O11" s="7" t="inlineStr"/>
-      <c r="P11" s="7" t="inlineStr"/>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R11" s="7" t="inlineStr"/>
-      <c r="S11" s="7" t="inlineStr"/>
-      <c r="T11" s="7" t="inlineStr">
-        <is>
-          <t>MTC FINANCIAL INC. dba Trustee Corps</t>
-        </is>
-      </c>
-      <c r="U11" s="7" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>20260311156</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Phillip A Dawson</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>US Bank Trust National Association, not in its Current Trustee:</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>403200</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>8014 S 225th Ave</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>400-12-016</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>individual capacity, but solely as Delaware trustee for Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V11" s="7" t="inlineStr">
+      <c r="V11" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="A12" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>20260309089</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>Fred M. Hill</t>
-        </is>
-      </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>20260311212</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>Jorge Antonio Leon Lazcano</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>ROCKET MORTGAGE LLC S/B/M TO NATIONSTAR MORTGAGE LLC</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>377886</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>6002 N 62ND LN</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>144-68-0047</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>America West Lender Services, LLC</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>20260311884</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>David R. Pineda</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
         </is>
       </c>
-      <c r="H12" s="8" t="n">
-        <v>62100</v>
-      </c>
-      <c r="I12" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="J12" s="7" t="inlineStr">
+      <c r="H13" s="4" t="n">
+        <v>162700</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>Superior Court Building of the Maricopa County Courthouse</t>
         </is>
       </c>
-      <c r="K12" s="7" t="inlineStr">
-        <is>
-          <t>1207 E Georgia Ave</t>
-        </is>
-      </c>
-      <c r="L12" s="7" t="inlineStr"/>
-      <c r="M12" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N12" s="7" t="inlineStr"/>
-      <c r="O12" s="7" t="inlineStr"/>
-      <c r="P12" s="7" t="inlineStr"/>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R12" s="7" t="inlineStr"/>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>162-09-0023</t>
-        </is>
-      </c>
-      <c r="T12" s="7" t="inlineStr">
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>10617 W Raymond St</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>101-25-7575</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
         <is>
           <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
         </is>
       </c>
-      <c r="U12" s="7" t="inlineStr">
+      <c r="U13" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V12" s="7" t="inlineStr">
+      <c r="V13" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="W13" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C13" s="7" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
-        <is>
-          <t>20260309100</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Joshua E. Johnson and</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr">
-        <is>
-          <t>| 545 E. Horseshoe Avenue</t>
-        </is>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>350000</v>
-      </c>
-      <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="7" t="inlineStr"/>
-      <c r="K13" s="7" t="inlineStr"/>
-      <c r="L13" s="7" t="inlineStr"/>
-      <c r="M13" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N13" s="7" t="inlineStr"/>
-      <c r="O13" s="7" t="inlineStr"/>
-      <c r="P13" s="7" t="inlineStr"/>
-      <c r="Q13" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R13" s="7" t="inlineStr"/>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>503-34-043202</t>
-        </is>
-      </c>
-      <c r="T13" s="7" t="inlineStr">
-        <is>
-          <t>Christopher J. Charles, Esq.</t>
-        </is>
-      </c>
-      <c r="U13" s="7" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>20260311941</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Real Estate Finance Corporation</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Guardian III Limited Partnership Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>450000</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr"/>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>9270 E Thompson Peak Pkwy Lot 354</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>217-62-9409</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>Guardian III Limited Partnership Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>20260311952</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>Adelaida Nunez-Rodriguez</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>NewRez LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>128250</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>4520 W Maryland Ave</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr"/>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr"/>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>146-27-3947</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>NewRez LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V13" s="7" t="inlineStr">
+      <c r="V15" s="3" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="D14" s="7" t="inlineStr">
-        <is>
-          <t>20260309156</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>JEFFREY J. ROEDIGER AND M.K. ROEDIGER</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>BANK OF AMERICA, N.A.</t>
-        </is>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>58698</v>
-      </c>
-      <c r="I14" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="J14" s="7" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>2014 N 55TH AVE</t>
-        </is>
-      </c>
-      <c r="L14" s="7" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
-      <c r="M14" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>85035</t>
-        </is>
-      </c>
-      <c r="O14" s="7" t="inlineStr"/>
-      <c r="P14" s="7" t="inlineStr"/>
-      <c r="Q14" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R14" s="7" t="inlineStr"/>
-      <c r="S14" s="7" t="inlineStr"/>
-      <c r="T14" s="7" t="inlineStr">
-        <is>
-          <t>Prime Recon LLC</t>
-        </is>
-      </c>
-      <c r="U14" s="7" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V14" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>20260309362</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>BARRY SM LUM</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Rocket Mortgage, LLC sbm Nationstar Mortgage LLC</t>
-        </is>
-      </c>
-      <c r="H15" s="8" t="n">
-        <v>91550</v>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="J15" s="7" t="inlineStr">
-        <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>16269 W MORNING GLORY ST</t>
-        </is>
-      </c>
-      <c r="L15" s="7" t="inlineStr">
-        <is>
-          <t>GOODYEAR</t>
-        </is>
-      </c>
-      <c r="M15" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>85338</t>
-        </is>
-      </c>
-      <c r="O15" s="7" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr"/>
-      <c r="Q15" s="7" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>500-05-596</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>MTC Financial Inc. dba Trustee Corps</t>
-        </is>
-      </c>
-      <c r="U15" s="7" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V15" s="7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="5" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -1991,27 +2059,35 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>20260309460</t>
+          <t>20260309954</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Daniel Ortiz Parra</t>
+        </is>
+      </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>C/O Freedom Morigage Corporation</t>
+          <t>NewRez LLC d/b/a Shellpoint Mortgage Servicing Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>357750</v>
-      </c>
-      <c r="I16" s="7" t="inlineStr"/>
+        <v>355000</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Superior Courts Building. Maricopa County</t>
+          <t>Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr"/>
@@ -2032,10 +2108,14 @@
       <c r="R16" s="7" t="inlineStr"/>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>205-07-204</t>
-        </is>
-      </c>
-      <c r="T16" s="7" t="inlineStr"/>
+          <t>301-67-0412</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
+        <is>
+          <t>NewRez LLC d/b/a Shellpoint Mortgage Servicing Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="U16" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2054,7 +2134,7 @@
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -2068,35 +2148,35 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>20260309229</t>
+          <t>20260310082</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>MARY M. GALVAN UNMARRIED WOMAN, WHO ACQUIRED TITLE AS MARY M</t>
+          <t>SAM YASSA</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>NEWREZ LLC D/B/A SHELLPOINT MORTGAGE SERVICING</t>
+          <t>The Bank of New York Mellon f/k/a The Bank of New York as successor to JPMorgan Chase Bank, National</t>
         </is>
       </c>
       <c r="H17" s="8" t="n">
-        <v>90000</v>
+        <v>163900</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr"/>
@@ -2115,10 +2195,14 @@
         </is>
       </c>
       <c r="R17" s="7" t="inlineStr"/>
-      <c r="S17" s="7" t="inlineStr"/>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>141-69-914</t>
+        </is>
+      </c>
       <c r="T17" s="7" t="inlineStr">
         <is>
-          <t>Prime Recon LLC</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="U17" s="7" t="inlineStr">
@@ -2139,7 +2223,7 @@
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -2153,26 +2237,26 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>20260309288</t>
+          <t>20260310668</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>SAMUEL MCCOWN</t>
+          <t>GARY D BARNETT</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>NEWREZ LLC DBA SHELLPOINT MORTGAGE SERVICING</t>
+          <t>Deutsche Bank National Trust Company, as Trustee for Soundview Home Loan Trust 2006-NLC1, Asset-Back</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>53176.96</v>
+        <v>144750</v>
       </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
@@ -2181,7 +2265,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
+          <t>Superior Court Building Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr"/>
@@ -2200,10 +2284,14 @@
         </is>
       </c>
       <c r="R18" s="7" t="inlineStr"/>
-      <c r="S18" s="7" t="inlineStr"/>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>145-19-034</t>
+        </is>
+      </c>
       <c r="T18" s="7" t="inlineStr">
         <is>
-          <t>Prime Recon LLC</t>
+          <t>Western Progressive — Arizona, Inc.</t>
         </is>
       </c>
       <c r="U18" s="7" t="inlineStr">
@@ -2224,40 +2312,54 @@
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Notice of Trustee Sale</t>
         </is>
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>20260309464</t>
+          <t>20260311865</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
-      <c r="I19" s="7" t="inlineStr"/>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Sripan T. Roemer</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Rocket Mortgage, LLC f/k/a Quicken Loans, LLC Current Trustee:</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>80300</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr">
         <is>
-          <t>1323 W. Morrow Drive, Phoenix, AZ</t>
+          <t>17704 W Maricopa St</t>
         </is>
       </c>
       <c r="L19" s="7" t="inlineStr"/>
@@ -2277,13 +2379,17 @@
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>209-13-22425</t>
-        </is>
-      </c>
-      <c r="T19" s="7" t="inlineStr"/>
+          <t>502-39-6368</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr">
+        <is>
+          <t>f/k/a Quicken Loans Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="U19" s="7" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
       <c r="V19" s="7" t="inlineStr">
@@ -2299,40 +2405,50 @@
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="6" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Notice of Trustee Sale</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>NS</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>20260309465</t>
+          <t>20260311915</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr"/>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="7" t="inlineStr"/>
-      <c r="J20" s="7" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Vivek Kumar Srivastava and Shikha Srivastava</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr"/>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>1348 W. Rosemonte Drive, Phoenix, AZ</t>
+          <t>7821 S 23rd Way</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr"/>
@@ -2352,13 +2468,17 @@
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>209-13-243</t>
-        </is>
-      </c>
-      <c r="T20" s="7" t="inlineStr"/>
+          <t>301-30-3811</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr">
+        <is>
+          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="U20" s="7" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
       <c r="V20" s="7" t="inlineStr">
@@ -2373,201 +2493,261 @@
       </c>
     </row>
     <row r="21" ht="26" customHeight="1">
-      <c r="A21" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B21" s="11" t="inlineStr">
-        <is>
-          <t>Judgment</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>20260306994</t>
-        </is>
-      </c>
-      <c r="E21" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F21" s="11" t="inlineStr"/>
-      <c r="G21" s="11" t="inlineStr"/>
-      <c r="H21" s="11" t="inlineStr"/>
-      <c r="I21" s="11" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
-      <c r="K21" s="11" t="inlineStr"/>
-      <c r="L21" s="11" t="inlineStr"/>
-      <c r="M21" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N21" s="11" t="inlineStr"/>
-      <c r="O21" s="11" t="inlineStr"/>
-      <c r="P21" s="11" t="inlineStr"/>
-      <c r="Q21" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R21" s="11" t="inlineStr"/>
-      <c r="S21" s="11" t="inlineStr"/>
-      <c r="T21" s="11" t="inlineStr"/>
-      <c r="U21" s="11" t="inlineStr">
-        <is>
-          <t>Judgment lien; New this week</t>
-        </is>
-      </c>
-      <c r="V21" s="11" t="inlineStr">
+      <c r="A21" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>20260310953</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>VICTOR JETT CONTRERAS</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>TRUIST BANK</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr">
+        <is>
+          <t>2801 W AUGUSTA AVE</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>151-01-026</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W21" s="12" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26" customHeight="1">
-      <c r="A22" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B22" s="11" t="inlineStr">
-        <is>
-          <t>Judgment</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>20260307129</t>
-        </is>
-      </c>
-      <c r="E22" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F22" s="11" t="inlineStr"/>
-      <c r="G22" s="11" t="inlineStr"/>
-      <c r="H22" s="11" t="inlineStr"/>
-      <c r="I22" s="11" t="inlineStr"/>
-      <c r="J22" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court/Case No. CV2025-027524</t>
-        </is>
-      </c>
-      <c r="K22" s="11" t="inlineStr"/>
-      <c r="L22" s="11" t="inlineStr"/>
-      <c r="M22" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N22" s="11" t="inlineStr"/>
-      <c r="O22" s="11" t="inlineStr"/>
-      <c r="P22" s="11" t="inlineStr"/>
-      <c r="Q22" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R22" s="11" t="inlineStr"/>
-      <c r="S22" s="11" t="inlineStr"/>
-      <c r="T22" s="11" t="inlineStr"/>
-      <c r="U22" s="11" t="inlineStr">
-        <is>
-          <t>Judgment lien; New this week</t>
-        </is>
-      </c>
-      <c r="V22" s="11" t="inlineStr">
+      <c r="A22" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>20260311173</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>MARCO A SALAS AND HEIDY DEL CARMEN SALAS</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>Fifth Third Bank, N.A.</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>12011 WEST BLOOMFIELD ROAD</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr"/>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr"/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>509-05-381</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W22" s="12" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="23" ht="26" customHeight="1">
-      <c r="A23" s="10" t="n">
-        <v>48</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
-        <is>
-          <t>Judgment</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="D23" s="11" t="inlineStr">
-        <is>
-          <t>20260307144</t>
-        </is>
-      </c>
-      <c r="E23" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F23" s="11" t="inlineStr"/>
-      <c r="G23" s="11" t="inlineStr"/>
-      <c r="H23" s="11" t="inlineStr"/>
-      <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court/Case No. CV2025-027524</t>
-        </is>
-      </c>
-      <c r="K23" s="11" t="inlineStr"/>
-      <c r="L23" s="11" t="inlineStr"/>
-      <c r="M23" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N23" s="11" t="inlineStr"/>
-      <c r="O23" s="11" t="inlineStr"/>
-      <c r="P23" s="11" t="inlineStr"/>
-      <c r="Q23" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R23" s="11" t="inlineStr"/>
-      <c r="S23" s="11" t="inlineStr"/>
-      <c r="T23" s="11" t="inlineStr"/>
-      <c r="U23" s="11" t="inlineStr">
-        <is>
-          <t>Judgment lien; New this week</t>
-        </is>
-      </c>
-      <c r="V23" s="11" t="inlineStr">
+      <c r="A23" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>20260311192</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>PATRICK J. MALLON AND ANNE ELYSE MALLON</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>USAA FEDERAL SAVINGS BANK</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>10740 E BALMORAL AVE</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="7" t="inlineStr"/>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr"/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>220-53-278</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="W23" s="12" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -2589,19 +2769,23 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>20260307345</t>
+          <t>20260309875</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr"/>
       <c r="G24" s="11" t="inlineStr"/>
       <c r="H24" s="11" t="inlineStr"/>
       <c r="I24" s="11" t="inlineStr"/>
-      <c r="J24" s="11" t="inlineStr"/>
+      <c r="J24" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="11" t="inlineStr">
@@ -2652,12 +2836,12 @@
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>20260307346</t>
+          <t>20260310130</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr"/>
@@ -2715,19 +2899,23 @@
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>20260307347</t>
+          <t>20260310189</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr"/>
       <c r="G26" s="11" t="inlineStr"/>
       <c r="H26" s="11" t="inlineStr"/>
       <c r="I26" s="11" t="inlineStr"/>
-      <c r="J26" s="11" t="inlineStr"/>
+      <c r="J26" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
       <c r="K26" s="11" t="inlineStr"/>
       <c r="L26" s="11" t="inlineStr"/>
       <c r="M26" s="11" t="inlineStr">
@@ -2778,19 +2966,23 @@
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>20260307348</t>
+          <t>20260310204</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr"/>
       <c r="G27" s="11" t="inlineStr"/>
       <c r="H27" s="11" t="inlineStr"/>
       <c r="I27" s="11" t="inlineStr"/>
-      <c r="J27" s="11" t="inlineStr"/>
+      <c r="J27" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K27" s="11" t="inlineStr"/>
       <c r="L27" s="11" t="inlineStr"/>
       <c r="M27" s="11" t="inlineStr">
@@ -2841,19 +3033,23 @@
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>20260307349</t>
+          <t>20260310458</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
       <c r="G28" s="11" t="inlineStr"/>
       <c r="H28" s="11" t="inlineStr"/>
       <c r="I28" s="11" t="inlineStr"/>
-      <c r="J28" s="11" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K28" s="11" t="inlineStr"/>
       <c r="L28" s="11" t="inlineStr"/>
       <c r="M28" s="11" t="inlineStr">
@@ -2904,19 +3100,23 @@
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>20260307350</t>
+          <t>20260310496</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr"/>
       <c r="G29" s="11" t="inlineStr"/>
       <c r="H29" s="11" t="inlineStr"/>
       <c r="I29" s="11" t="inlineStr"/>
-      <c r="J29" s="11" t="inlineStr"/>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
       <c r="K29" s="11" t="inlineStr"/>
       <c r="L29" s="11" t="inlineStr"/>
       <c r="M29" s="11" t="inlineStr">
@@ -2967,19 +3167,23 @@
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>20260307351</t>
+          <t>20260310746</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr"/>
       <c r="G30" s="11" t="inlineStr"/>
       <c r="H30" s="11" t="inlineStr"/>
       <c r="I30" s="11" t="inlineStr"/>
-      <c r="J30" s="11" t="inlineStr"/>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K30" s="11" t="inlineStr"/>
       <c r="L30" s="11" t="inlineStr"/>
       <c r="M30" s="11" t="inlineStr">
@@ -3030,19 +3234,23 @@
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>20260307352</t>
+          <t>20260310755</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr"/>
       <c r="H31" s="11" t="inlineStr"/>
       <c r="I31" s="11" t="inlineStr"/>
-      <c r="J31" s="11" t="inlineStr"/>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K31" s="11" t="inlineStr"/>
       <c r="L31" s="11" t="inlineStr"/>
       <c r="M31" s="11" t="inlineStr">
@@ -3093,19 +3301,23 @@
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>20260307353</t>
+          <t>20260310783</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
       <c r="G32" s="11" t="inlineStr"/>
       <c r="H32" s="11" t="inlineStr"/>
       <c r="I32" s="11" t="inlineStr"/>
-      <c r="J32" s="11" t="inlineStr"/>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court Case No. CV2023-020284</t>
+        </is>
+      </c>
       <c r="K32" s="11" t="inlineStr"/>
       <c r="L32" s="11" t="inlineStr"/>
       <c r="M32" s="11" t="inlineStr">
@@ -3156,19 +3368,23 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>20260307741</t>
+          <t>20260310801</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
       <c r="G33" s="11" t="inlineStr"/>
       <c r="H33" s="11" t="inlineStr"/>
       <c r="I33" s="11" t="inlineStr"/>
-      <c r="J33" s="11" t="inlineStr"/>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K33" s="11" t="inlineStr"/>
       <c r="L33" s="11" t="inlineStr"/>
       <c r="M33" s="11" t="inlineStr">
@@ -3219,19 +3435,23 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>20260307742</t>
+          <t>20260310812</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
       <c r="G34" s="11" t="inlineStr"/>
       <c r="H34" s="11" t="inlineStr"/>
       <c r="I34" s="11" t="inlineStr"/>
-      <c r="J34" s="11" t="inlineStr"/>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K34" s="11" t="inlineStr"/>
       <c r="L34" s="11" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr">
@@ -3282,19 +3502,23 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>20260307743</t>
+          <t>20260310862</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
       <c r="G35" s="11" t="inlineStr"/>
       <c r="H35" s="11" t="inlineStr"/>
       <c r="I35" s="11" t="inlineStr"/>
-      <c r="J35" s="11" t="inlineStr"/>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K35" s="11" t="inlineStr"/>
       <c r="L35" s="11" t="inlineStr"/>
       <c r="M35" s="11" t="inlineStr">
@@ -3345,19 +3569,23 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>20260307744</t>
+          <t>20260311029</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
       <c r="G36" s="11" t="inlineStr"/>
       <c r="H36" s="11" t="inlineStr"/>
       <c r="I36" s="11" t="inlineStr"/>
-      <c r="J36" s="11" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
       <c r="M36" s="11" t="inlineStr">
@@ -3408,12 +3636,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>20260307745</t>
+          <t>20260311299</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
@@ -3471,19 +3699,23 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>20260307746</t>
+          <t>20260311316</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr"/>
       <c r="G38" s="11" t="inlineStr"/>
       <c r="H38" s="11" t="inlineStr"/>
       <c r="I38" s="11" t="inlineStr"/>
-      <c r="J38" s="11" t="inlineStr"/>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
       <c r="K38" s="11" t="inlineStr"/>
       <c r="L38" s="11" t="inlineStr"/>
       <c r="M38" s="11" t="inlineStr">
@@ -3534,19 +3766,23 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>20260307747</t>
+          <t>20260311376</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
       <c r="G39" s="11" t="inlineStr"/>
       <c r="H39" s="11" t="inlineStr"/>
       <c r="I39" s="11" t="inlineStr"/>
-      <c r="J39" s="11" t="inlineStr"/>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K39" s="11" t="inlineStr"/>
       <c r="L39" s="11" t="inlineStr"/>
       <c r="M39" s="11" t="inlineStr">
@@ -3597,19 +3833,23 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>20260307749</t>
+          <t>20260311379</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
       <c r="G40" s="11" t="inlineStr"/>
       <c r="H40" s="11" t="inlineStr"/>
       <c r="I40" s="11" t="inlineStr"/>
-      <c r="J40" s="11" t="inlineStr"/>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K40" s="11" t="inlineStr"/>
       <c r="L40" s="11" t="inlineStr"/>
       <c r="M40" s="11" t="inlineStr">
@@ -3660,12 +3900,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>20260307750</t>
+          <t>20260311627</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
@@ -3674,7 +3914,7 @@
       <c r="I41" s="11" t="inlineStr"/>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -3727,12 +3967,12 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>20260307751</t>
+          <t>20260311628</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
@@ -3741,7 +3981,7 @@
       <c r="I42" s="11" t="inlineStr"/>
       <c r="J42" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr"/>
@@ -3794,23 +4034,19 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>20260307752</t>
+          <t>20260312262</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr"/>
       <c r="H43" s="11" t="inlineStr"/>
       <c r="I43" s="11" t="inlineStr"/>
-      <c r="J43" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J43" s="11" t="inlineStr"/>
       <c r="K43" s="11" t="inlineStr"/>
       <c r="L43" s="11" t="inlineStr"/>
       <c r="M43" s="11" t="inlineStr">
@@ -3861,23 +4097,19 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>20260307753</t>
+          <t>20260312263</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="11" t="inlineStr"/>
       <c r="H44" s="11" t="inlineStr"/>
       <c r="I44" s="11" t="inlineStr"/>
-      <c r="J44" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J44" s="11" t="inlineStr"/>
       <c r="K44" s="11" t="inlineStr"/>
       <c r="L44" s="11" t="inlineStr"/>
       <c r="M44" s="11" t="inlineStr">
@@ -3928,23 +4160,19 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>20260307754</t>
+          <t>20260312264</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
       <c r="G45" s="11" t="inlineStr"/>
       <c r="H45" s="11" t="inlineStr"/>
       <c r="I45" s="11" t="inlineStr"/>
-      <c r="J45" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J45" s="11" t="inlineStr"/>
       <c r="K45" s="11" t="inlineStr"/>
       <c r="L45" s="11" t="inlineStr"/>
       <c r="M45" s="11" t="inlineStr">
@@ -3995,23 +4223,19 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>20260307755</t>
+          <t>20260312265</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
       <c r="G46" s="11" t="inlineStr"/>
       <c r="H46" s="11" t="inlineStr"/>
       <c r="I46" s="11" t="inlineStr"/>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr"/>
       <c r="L46" s="11" t="inlineStr"/>
       <c r="M46" s="11" t="inlineStr">
@@ -4062,23 +4286,19 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>20260307756</t>
+          <t>20260312266</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
       <c r="G47" s="11" t="inlineStr"/>
       <c r="H47" s="11" t="inlineStr"/>
       <c r="I47" s="11" t="inlineStr"/>
-      <c r="J47" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J47" s="11" t="inlineStr"/>
       <c r="K47" s="11" t="inlineStr"/>
       <c r="L47" s="11" t="inlineStr"/>
       <c r="M47" s="11" t="inlineStr">
@@ -4129,23 +4349,19 @@
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>20260307757</t>
+          <t>20260312267</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
       <c r="G48" s="11" t="inlineStr"/>
       <c r="H48" s="11" t="inlineStr"/>
       <c r="I48" s="11" t="inlineStr"/>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J48" s="11" t="inlineStr"/>
       <c r="K48" s="11" t="inlineStr"/>
       <c r="L48" s="11" t="inlineStr"/>
       <c r="M48" s="11" t="inlineStr">
@@ -4196,23 +4412,19 @@
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>20260307758</t>
+          <t>20260312268</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
       <c r="G49" s="11" t="inlineStr"/>
       <c r="H49" s="11" t="inlineStr"/>
       <c r="I49" s="11" t="inlineStr"/>
-      <c r="J49" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J49" s="11" t="inlineStr"/>
       <c r="K49" s="11" t="inlineStr"/>
       <c r="L49" s="11" t="inlineStr"/>
       <c r="M49" s="11" t="inlineStr">
@@ -4263,23 +4475,19 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>20260308024</t>
+          <t>20260312269</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr"/>
       <c r="G50" s="11" t="inlineStr"/>
       <c r="H50" s="11" t="inlineStr"/>
       <c r="I50" s="11" t="inlineStr"/>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court Case No. S-0300-CV-2025 00753</t>
-        </is>
-      </c>
+      <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr"/>
       <c r="L50" s="11" t="inlineStr"/>
       <c r="M50" s="11" t="inlineStr">
@@ -4330,23 +4538,19 @@
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>20260308141</t>
+          <t>20260312270</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
       <c r="G51" s="11" t="inlineStr"/>
       <c r="H51" s="11" t="inlineStr"/>
       <c r="I51" s="11" t="inlineStr"/>
-      <c r="J51" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J51" s="11" t="inlineStr"/>
       <c r="K51" s="11" t="inlineStr"/>
       <c r="L51" s="11" t="inlineStr"/>
       <c r="M51" s="11" t="inlineStr">
@@ -4397,23 +4601,19 @@
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>20260308484</t>
+          <t>20260312271</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
       <c r="G52" s="11" t="inlineStr"/>
       <c r="H52" s="11" t="inlineStr"/>
       <c r="I52" s="11" t="inlineStr"/>
-      <c r="J52" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J52" s="11" t="inlineStr"/>
       <c r="K52" s="11" t="inlineStr"/>
       <c r="L52" s="11" t="inlineStr"/>
       <c r="M52" s="11" t="inlineStr">
@@ -4464,23 +4664,19 @@
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>20260308488</t>
+          <t>20260312272</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
       <c r="G53" s="11" t="inlineStr"/>
       <c r="H53" s="11" t="inlineStr"/>
       <c r="I53" s="11" t="inlineStr"/>
-      <c r="J53" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J53" s="11" t="inlineStr"/>
       <c r="K53" s="11" t="inlineStr"/>
       <c r="L53" s="11" t="inlineStr"/>
       <c r="M53" s="11" t="inlineStr">
@@ -4531,23 +4727,19 @@
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>20260308490</t>
+          <t>20260312273</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
       <c r="G54" s="11" t="inlineStr"/>
       <c r="H54" s="11" t="inlineStr"/>
       <c r="I54" s="11" t="inlineStr"/>
-      <c r="J54" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J54" s="11" t="inlineStr"/>
       <c r="K54" s="11" t="inlineStr"/>
       <c r="L54" s="11" t="inlineStr"/>
       <c r="M54" s="11" t="inlineStr">
@@ -4598,23 +4790,19 @@
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>20260308606</t>
+          <t>20260312274</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
       <c r="G55" s="11" t="inlineStr"/>
       <c r="H55" s="11" t="inlineStr"/>
       <c r="I55" s="11" t="inlineStr"/>
-      <c r="J55" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J55" s="11" t="inlineStr"/>
       <c r="K55" s="11" t="inlineStr"/>
       <c r="L55" s="11" t="inlineStr"/>
       <c r="M55" s="11" t="inlineStr">
@@ -4665,23 +4853,19 @@
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>20260308863</t>
+          <t>20260312275</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
       <c r="G56" s="11" t="inlineStr"/>
       <c r="H56" s="11" t="inlineStr"/>
       <c r="I56" s="11" t="inlineStr"/>
-      <c r="J56" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J56" s="11" t="inlineStr"/>
       <c r="K56" s="11" t="inlineStr"/>
       <c r="L56" s="11" t="inlineStr"/>
       <c r="M56" s="11" t="inlineStr">
@@ -4732,12 +4916,12 @@
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>20260309158</t>
+          <t>20260312276</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr"/>
@@ -4795,23 +4979,19 @@
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>20260309357</t>
+          <t>20260312277</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr"/>
       <c r="G58" s="11" t="inlineStr"/>
       <c r="H58" s="11" t="inlineStr"/>
       <c r="I58" s="11" t="inlineStr"/>
-      <c r="J58" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr"/>
       <c r="L58" s="11" t="inlineStr"/>
       <c r="M58" s="11" t="inlineStr">
@@ -4862,19 +5042,23 @@
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>20260309480</t>
+          <t>20260312355</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
       <c r="G59" s="11" t="inlineStr"/>
       <c r="H59" s="11" t="inlineStr"/>
       <c r="I59" s="11" t="inlineStr"/>
-      <c r="J59" s="11" t="inlineStr"/>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K59" s="11" t="inlineStr"/>
       <c r="L59" s="11" t="inlineStr"/>
       <c r="M59" s="11" t="inlineStr">
@@ -4915,22 +5099,22 @@
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>20260309514</t>
+          <t>20260310846</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
@@ -4939,7 +5123,7 @@
       <c r="I60" s="11" t="inlineStr"/>
       <c r="J60" s="11" t="inlineStr">
         <is>
-          <t>Superior Court in Maricopa County.</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr"/>
@@ -4958,11 +5142,15 @@
         </is>
       </c>
       <c r="R60" s="11" t="inlineStr"/>
-      <c r="S60" s="11" t="inlineStr"/>
+      <c r="S60" s="11" t="inlineStr">
+        <is>
+          <t>176-22-238</t>
+        </is>
+      </c>
       <c r="T60" s="11" t="inlineStr"/>
       <c r="U60" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V60" s="11" t="inlineStr">
@@ -4982,22 +5170,22 @@
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>20260309549</t>
+          <t>20260310852</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
@@ -5006,7 +5194,7 @@
       <c r="I61" s="11" t="inlineStr"/>
       <c r="J61" s="11" t="inlineStr">
         <is>
-          <t>Superior Court in Maricopa County.</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr"/>
@@ -5025,11 +5213,15 @@
         </is>
       </c>
       <c r="R61" s="11" t="inlineStr"/>
-      <c r="S61" s="11" t="inlineStr"/>
+      <c r="S61" s="11" t="inlineStr">
+        <is>
+          <t>132-68-069</t>
+        </is>
+      </c>
       <c r="T61" s="11" t="inlineStr"/>
       <c r="U61" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V61" s="11" t="inlineStr">
@@ -5059,12 +5251,12 @@
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>20260306645</t>
+          <t>20260310920</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
@@ -5126,12 +5318,12 @@
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>20260307441</t>
+          <t>20260312578</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
@@ -5140,7 +5332,7 @@
       <c r="I63" s="11" t="inlineStr"/>
       <c r="J63" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K63" s="11" t="inlineStr"/>
@@ -5159,7 +5351,11 @@
         </is>
       </c>
       <c r="R63" s="11" t="inlineStr"/>
-      <c r="S63" s="11" t="inlineStr"/>
+      <c r="S63" s="11" t="inlineStr">
+        <is>
+          <t>173-70-11189</t>
+        </is>
+      </c>
       <c r="T63" s="11" t="inlineStr"/>
       <c r="U63" s="11" t="inlineStr">
         <is>
@@ -5193,12 +5389,12 @@
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>20260307657</t>
+          <t>20260311182</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
@@ -5222,7 +5418,11 @@
         </is>
       </c>
       <c r="R64" s="11" t="inlineStr"/>
-      <c r="S64" s="11" t="inlineStr"/>
+      <c r="S64" s="11" t="inlineStr">
+        <is>
+          <t>220-81-989</t>
+        </is>
+      </c>
       <c r="T64" s="11" t="inlineStr"/>
       <c r="U64" s="11" t="inlineStr">
         <is>
@@ -5256,12 +5456,12 @@
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>20260307886</t>
+          <t>20260311819</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
@@ -5285,7 +5485,11 @@
         </is>
       </c>
       <c r="R65" s="11" t="inlineStr"/>
-      <c r="S65" s="11" t="inlineStr"/>
+      <c r="S65" s="11" t="inlineStr">
+        <is>
+          <t>201-13-351</t>
+        </is>
+      </c>
       <c r="T65" s="11" t="inlineStr"/>
       <c r="U65" s="11" t="inlineStr">
         <is>
@@ -5319,12 +5523,12 @@
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>20260308542</t>
+          <t>20260312117</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
@@ -5350,7 +5554,7 @@
       <c r="R66" s="11" t="inlineStr"/>
       <c r="S66" s="11" t="inlineStr">
         <is>
-          <t>302-26-887</t>
+          <t>132-32-020</t>
         </is>
       </c>
       <c r="T66" s="11" t="inlineStr"/>
@@ -5372,26 +5576,26 @@
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>20260308574</t>
+          <t>20260309613</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
@@ -5415,15 +5619,11 @@
         </is>
       </c>
       <c r="R67" s="11" t="inlineStr"/>
-      <c r="S67" s="11" t="inlineStr">
-        <is>
-          <t>502-09-062</t>
-        </is>
-      </c>
+      <c r="S67" s="11" t="inlineStr"/>
       <c r="T67" s="11" t="inlineStr"/>
       <c r="U67" s="11" t="inlineStr">
         <is>
-          <t>Mechanic lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V67" s="11" t="inlineStr">
@@ -5439,26 +5639,26 @@
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>20260308683</t>
+          <t>20260309614</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
@@ -5486,7 +5686,7 @@
       <c r="T68" s="11" t="inlineStr"/>
       <c r="U68" s="11" t="inlineStr">
         <is>
-          <t>Mechanic lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V68" s="11" t="inlineStr">
@@ -5502,26 +5702,26 @@
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="10" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>ML</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>20260309360</t>
+          <t>20260309616</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
@@ -5545,15 +5745,11 @@
         </is>
       </c>
       <c r="R69" s="11" t="inlineStr"/>
-      <c r="S69" s="11" t="inlineStr">
-        <is>
-          <t>111-36-022</t>
-        </is>
-      </c>
+      <c r="S69" s="11" t="inlineStr"/>
       <c r="T69" s="11" t="inlineStr"/>
       <c r="U69" s="11" t="inlineStr">
         <is>
-          <t>Mechanic lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V69" s="11" t="inlineStr">
@@ -5573,22 +5769,22 @@
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>State Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>20260309547</t>
+          <t>20260309617</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
@@ -5616,12 +5812,12 @@
       <c r="T70" s="11" t="inlineStr"/>
       <c r="U70" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V70" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W70" s="12" t="inlineStr">
@@ -5636,22 +5832,22 @@
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>State Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>20260309548</t>
+          <t>20260309618</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
@@ -5679,12 +5875,12 @@
       <c r="T71" s="11" t="inlineStr"/>
       <c r="U71" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V71" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W71" s="12" t="inlineStr">
@@ -5699,22 +5895,22 @@
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>State Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>20260309553</t>
+          <t>20260309619</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
@@ -5742,12 +5938,12 @@
       <c r="T72" s="11" t="inlineStr"/>
       <c r="U72" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V72" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W72" s="12" t="inlineStr">
@@ -5762,22 +5958,22 @@
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>State Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>20260309562</t>
+          <t>20260309620</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
@@ -5805,12 +6001,12 @@
       <c r="T73" s="11" t="inlineStr"/>
       <c r="U73" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V73" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W73" s="12" t="inlineStr">
@@ -5825,22 +6021,22 @@
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>State Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>20260309568</t>
+          <t>20260309621</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
@@ -5868,12 +6064,12 @@
       <c r="T74" s="11" t="inlineStr"/>
       <c r="U74" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V74" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W74" s="12" t="inlineStr">
@@ -5888,22 +6084,22 @@
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>State Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>20260309569</t>
+          <t>20260309622</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
@@ -5931,12 +6127,12 @@
       <c r="T75" s="11" t="inlineStr"/>
       <c r="U75" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V75" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W75" s="12" t="inlineStr">
@@ -5961,12 +6157,12 @@
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>20260306647</t>
+          <t>20260309623</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
@@ -6024,12 +6220,12 @@
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>20260306649</t>
+          <t>20260309624</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr"/>
@@ -6087,12 +6283,12 @@
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>20260306650</t>
+          <t>20260309625</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
@@ -6150,12 +6346,12 @@
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>20260306651</t>
+          <t>20260309626</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr"/>
@@ -6213,12 +6409,12 @@
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>20260306652</t>
+          <t>20260309627</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
@@ -6276,12 +6472,12 @@
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>20260306653</t>
+          <t>20260309628</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr"/>
@@ -6339,12 +6535,12 @@
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>20260306654</t>
+          <t>20260309652</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr"/>
@@ -6402,12 +6598,12 @@
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>20260306655</t>
+          <t>20260310179</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
@@ -6465,12 +6661,12 @@
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>20260306656</t>
+          <t>20260310207</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr"/>
@@ -6528,12 +6724,12 @@
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>20260306657</t>
+          <t>20260310684</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr"/>
@@ -6581,22 +6777,22 @@
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>20260306658</t>
+          <t>20260310748</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr"/>
@@ -6624,12 +6820,12 @@
       <c r="T86" s="11" t="inlineStr"/>
       <c r="U86" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V86" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W86" s="12" t="inlineStr">
@@ -6644,22 +6840,22 @@
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>20260306659</t>
+          <t>20260312147</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr"/>
@@ -6687,12 +6883,12 @@
       <c r="T87" s="11" t="inlineStr"/>
       <c r="U87" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V87" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W87" s="12" t="inlineStr">
@@ -6707,22 +6903,22 @@
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>20260306660</t>
+          <t>20260312299</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr"/>
@@ -6750,12 +6946,12 @@
       <c r="T88" s="11" t="inlineStr"/>
       <c r="U88" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V88" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W88" s="12" t="inlineStr">
@@ -6770,22 +6966,22 @@
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>20260306661</t>
+          <t>20260312304</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
@@ -6813,12 +7009,12 @@
       <c r="T89" s="11" t="inlineStr"/>
       <c r="U89" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V89" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W89" s="12" t="inlineStr">
@@ -6833,22 +7029,22 @@
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>20260306662</t>
+          <t>20260312305</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
@@ -6876,12 +7072,12 @@
       <c r="T90" s="11" t="inlineStr"/>
       <c r="U90" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V90" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W90" s="12" t="inlineStr">
@@ -6896,22 +7092,22 @@
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>20260306663</t>
+          <t>20260312306</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr"/>
@@ -6939,12 +7135,12 @@
       <c r="T91" s="11" t="inlineStr"/>
       <c r="U91" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V91" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W91" s="12" t="inlineStr">
@@ -6959,22 +7155,22 @@
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>20260306664</t>
+          <t>20260312307</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr"/>
@@ -7002,12 +7198,12 @@
       <c r="T92" s="11" t="inlineStr"/>
       <c r="U92" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V92" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W92" s="12" t="inlineStr">
@@ -7022,22 +7218,22 @@
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>20260306665</t>
+          <t>20260309950</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
@@ -7065,12 +7261,12 @@
       <c r="T93" s="11" t="inlineStr"/>
       <c r="U93" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V93" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W93" s="12" t="inlineStr">
@@ -7085,22 +7281,22 @@
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>20260306666</t>
+          <t>20260310504</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr"/>
@@ -7128,12 +7324,12 @@
       <c r="T94" s="11" t="inlineStr"/>
       <c r="U94" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V94" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W94" s="12" t="inlineStr">
@@ -7148,22 +7344,22 @@
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>20260306908</t>
+          <t>20260310800</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr"/>
@@ -7191,12 +7387,12 @@
       <c r="T95" s="11" t="inlineStr"/>
       <c r="U95" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V95" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W95" s="12" t="inlineStr">
@@ -7211,22 +7407,22 @@
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>20260307792</t>
+          <t>20260310919</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr"/>
@@ -7254,7 +7450,7 @@
       <c r="T96" s="11" t="inlineStr"/>
       <c r="U96" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V96" s="11" t="inlineStr">
@@ -7274,22 +7470,22 @@
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>20260308345</t>
+          <t>20260310946</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr"/>
@@ -7317,7 +7513,7 @@
       <c r="T97" s="11" t="inlineStr"/>
       <c r="U97" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V97" s="11" t="inlineStr">
@@ -7337,22 +7533,22 @@
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>20260309122</t>
+          <t>20260311504</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr"/>
@@ -7380,7 +7576,7 @@
       <c r="T98" s="11" t="inlineStr"/>
       <c r="U98" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V98" s="11" t="inlineStr">
@@ -7400,22 +7596,22 @@
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>20260309123</t>
+          <t>20260311521</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr"/>
@@ -7443,7 +7639,7 @@
       <c r="T99" s="11" t="inlineStr"/>
       <c r="U99" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V99" s="11" t="inlineStr">
@@ -7463,22 +7659,22 @@
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C100" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>20260309513</t>
+          <t>20260311693</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr"/>
@@ -7506,7 +7702,7 @@
       <c r="T100" s="11" t="inlineStr"/>
       <c r="U100" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V100" s="11" t="inlineStr">
@@ -7526,22 +7722,22 @@
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C101" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>20260309551</t>
+          <t>20260311719</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr"/>
@@ -7569,7 +7765,7 @@
       <c r="T101" s="11" t="inlineStr"/>
       <c r="U101" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V101" s="11" t="inlineStr">
@@ -7599,12 +7795,12 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>20260306644</t>
+          <t>20260311774</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr"/>
@@ -7662,12 +7858,12 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>20260308148</t>
+          <t>20260311961</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr"/>
@@ -7725,12 +7921,12 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>20260308417</t>
+          <t>20260312317</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr"/>
@@ -7788,12 +7984,12 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>20260308532</t>
+          <t>20260312602</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr"/>
@@ -7837,26 +8033,26 @@
     </row>
     <row r="106" ht="26" customHeight="1">
       <c r="A106" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C106" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>20260308678</t>
+          <t>20260310101</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr"/>
@@ -7884,12 +8080,12 @@
       <c r="T106" s="11" t="inlineStr"/>
       <c r="U106" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V106" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W106" s="12" t="inlineStr">
@@ -7900,26 +8096,26 @@
     </row>
     <row r="107" ht="26" customHeight="1">
       <c r="A107" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C107" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>20260308795</t>
+          <t>20260310103</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr"/>
@@ -7947,12 +8143,12 @@
       <c r="T107" s="11" t="inlineStr"/>
       <c r="U107" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V107" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W107" s="12" t="inlineStr">
@@ -7963,26 +8159,26 @@
     </row>
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C108" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>20260308931</t>
+          <t>20260310105</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr"/>
@@ -8010,12 +8206,12 @@
       <c r="T108" s="11" t="inlineStr"/>
       <c r="U108" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V108" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W108" s="12" t="inlineStr">
@@ -8026,26 +8222,26 @@
     </row>
     <row r="109" ht="26" customHeight="1">
       <c r="A109" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C109" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>20260309475</t>
+          <t>20260310108</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr"/>
@@ -8073,12 +8269,12 @@
       <c r="T109" s="11" t="inlineStr"/>
       <c r="U109" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V109" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W109" s="12" t="inlineStr">
@@ -8089,26 +8285,26 @@
     </row>
     <row r="110" ht="26" customHeight="1">
       <c r="A110" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C110" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>20260309504</t>
+          <t>20260310123</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr"/>
@@ -8136,12 +8332,12 @@
       <c r="T110" s="11" t="inlineStr"/>
       <c r="U110" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V110" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W110" s="12" t="inlineStr">
@@ -8166,12 +8362,12 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>20260307498</t>
+          <t>20260311148</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr"/>
@@ -8229,12 +8425,12 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>20260307501</t>
+          <t>20260311149</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr"/>
@@ -8292,12 +8488,12 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>20260307520</t>
+          <t>20260311836</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr"/>
@@ -8355,12 +8551,12 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>20260308032</t>
+          <t>20260312186</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr"/>
@@ -8404,26 +8600,26 @@
     </row>
     <row r="115" ht="26" customHeight="1">
       <c r="A115" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>20260308138</t>
+          <t>20260310924</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr"/>
@@ -8451,12 +8647,12 @@
       <c r="T115" s="11" t="inlineStr"/>
       <c r="U115" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V115" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W115" s="12" t="inlineStr">
@@ -8467,26 +8663,26 @@
     </row>
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>20260308140</t>
+          <t>20260310926</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr"/>
@@ -8514,12 +8710,12 @@
       <c r="T116" s="11" t="inlineStr"/>
       <c r="U116" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V116" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W116" s="12" t="inlineStr">
@@ -8530,26 +8726,26 @@
     </row>
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>20260308144</t>
+          <t>20260310927</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr"/>
@@ -8577,12 +8773,12 @@
       <c r="T117" s="11" t="inlineStr"/>
       <c r="U117" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V117" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W117" s="12" t="inlineStr">
@@ -8593,26 +8789,26 @@
     </row>
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>20260308358</t>
+          <t>20260310928</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr"/>
@@ -8640,12 +8836,12 @@
       <c r="T118" s="11" t="inlineStr"/>
       <c r="U118" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V118" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W118" s="12" t="inlineStr">
@@ -8656,26 +8852,26 @@
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>20260308403</t>
+          <t>20260310929</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr"/>
@@ -8703,12 +8899,12 @@
       <c r="T119" s="11" t="inlineStr"/>
       <c r="U119" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V119" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W119" s="12" t="inlineStr">
@@ -8719,26 +8915,26 @@
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>20260308404</t>
+          <t>20260310930</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr"/>
@@ -8766,12 +8962,12 @@
       <c r="T120" s="11" t="inlineStr"/>
       <c r="U120" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V120" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W120" s="12" t="inlineStr">
@@ -8782,26 +8978,26 @@
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>20260308405</t>
+          <t>20260311051</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr"/>
@@ -8829,12 +9025,12 @@
       <c r="T121" s="11" t="inlineStr"/>
       <c r="U121" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V121" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W121" s="12" t="inlineStr">
@@ -8845,26 +9041,26 @@
     </row>
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>20260308406</t>
+          <t>20260311134</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr"/>
@@ -8892,12 +9088,12 @@
       <c r="T122" s="11" t="inlineStr"/>
       <c r="U122" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V122" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W122" s="12" t="inlineStr">
@@ -8908,26 +9104,26 @@
     </row>
     <row r="123" ht="26" customHeight="1">
       <c r="A123" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>20260308438</t>
+          <t>20260311207</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr"/>
@@ -8955,12 +9151,12 @@
       <c r="T123" s="11" t="inlineStr"/>
       <c r="U123" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V123" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W123" s="12" t="inlineStr">
@@ -8971,26 +9167,26 @@
     </row>
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>20260308447</t>
+          <t>20260311567</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr"/>
@@ -9018,12 +9214,12 @@
       <c r="T124" s="11" t="inlineStr"/>
       <c r="U124" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V124" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W124" s="12" t="inlineStr">
@@ -9034,26 +9230,26 @@
     </row>
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>20260308448</t>
+          <t>20260311568</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr"/>
@@ -9081,12 +9277,12 @@
       <c r="T125" s="11" t="inlineStr"/>
       <c r="U125" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V125" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W125" s="12" t="inlineStr">
@@ -9097,26 +9293,26 @@
     </row>
     <row r="126" ht="26" customHeight="1">
       <c r="A126" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>20260308459</t>
+          <t>20260311569</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr"/>
@@ -9144,12 +9340,12 @@
       <c r="T126" s="11" t="inlineStr"/>
       <c r="U126" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V126" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W126" s="12" t="inlineStr">
@@ -9160,26 +9356,26 @@
     </row>
     <row r="127" ht="26" customHeight="1">
       <c r="A127" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>20260308475</t>
+          <t>20260311570</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr"/>
@@ -9207,12 +9403,12 @@
       <c r="T127" s="11" t="inlineStr"/>
       <c r="U127" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V127" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W127" s="12" t="inlineStr">
@@ -9223,26 +9419,26 @@
     </row>
     <row r="128" ht="26" customHeight="1">
       <c r="A128" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>20260308483</t>
+          <t>20260311571</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr"/>
@@ -9270,12 +9466,12 @@
       <c r="T128" s="11" t="inlineStr"/>
       <c r="U128" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V128" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W128" s="12" t="inlineStr">
@@ -9286,26 +9482,26 @@
     </row>
     <row r="129" ht="26" customHeight="1">
       <c r="A129" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>20260308789</t>
+          <t>20260311572</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr"/>
@@ -9333,12 +9529,12 @@
       <c r="T129" s="11" t="inlineStr"/>
       <c r="U129" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V129" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W129" s="12" t="inlineStr">
@@ -9349,26 +9545,26 @@
     </row>
     <row r="130" ht="26" customHeight="1">
       <c r="A130" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>20260309027</t>
+          <t>20260311573</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr"/>
@@ -9396,12 +9592,12 @@
       <c r="T130" s="11" t="inlineStr"/>
       <c r="U130" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V130" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W130" s="12" t="inlineStr">
@@ -9412,26 +9608,26 @@
     </row>
     <row r="131" ht="26" customHeight="1">
       <c r="A131" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>20260309028</t>
+          <t>20260311574</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr"/>
@@ -9459,12 +9655,12 @@
       <c r="T131" s="11" t="inlineStr"/>
       <c r="U131" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V131" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W131" s="12" t="inlineStr">
@@ -9475,26 +9671,26 @@
     </row>
     <row r="132" ht="26" customHeight="1">
       <c r="A132" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>20260309086</t>
+          <t>20260311577</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr"/>
@@ -9522,12 +9718,12 @@
       <c r="T132" s="11" t="inlineStr"/>
       <c r="U132" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V132" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W132" s="12" t="inlineStr">
@@ -9538,26 +9734,26 @@
     </row>
     <row r="133" ht="26" customHeight="1">
       <c r="A133" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>20260309386</t>
+          <t>20260311578</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr"/>
@@ -9585,12 +9781,12 @@
       <c r="T133" s="11" t="inlineStr"/>
       <c r="U133" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V133" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W133" s="12" t="inlineStr">
@@ -9601,26 +9797,26 @@
     </row>
     <row r="134" ht="26" customHeight="1">
       <c r="A134" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>20260309387</t>
+          <t>20260311581</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr"/>
@@ -9648,12 +9844,12 @@
       <c r="T134" s="11" t="inlineStr"/>
       <c r="U134" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V134" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W134" s="12" t="inlineStr">
@@ -9664,26 +9860,26 @@
     </row>
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>20260309401</t>
+          <t>20260311582</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr"/>
@@ -9711,12 +9907,12 @@
       <c r="T135" s="11" t="inlineStr"/>
       <c r="U135" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V135" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W135" s="12" t="inlineStr">
@@ -9727,26 +9923,26 @@
     </row>
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>20260309402</t>
+          <t>20260311583</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr"/>
@@ -9774,12 +9970,12 @@
       <c r="T136" s="11" t="inlineStr"/>
       <c r="U136" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V136" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W136" s="12" t="inlineStr">
@@ -9790,26 +9986,26 @@
     </row>
     <row r="137" ht="26" customHeight="1">
       <c r="A137" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>20260309405</t>
+          <t>20260311584</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr"/>
@@ -9837,12 +10033,12 @@
       <c r="T137" s="11" t="inlineStr"/>
       <c r="U137" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V137" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W137" s="12" t="inlineStr">
@@ -9853,26 +10049,26 @@
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>20260309406</t>
+          <t>20260311585</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr"/>
@@ -9900,12 +10096,12 @@
       <c r="T138" s="11" t="inlineStr"/>
       <c r="U138" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V138" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W138" s="12" t="inlineStr">
@@ -9916,26 +10112,26 @@
     </row>
     <row r="139" ht="26" customHeight="1">
       <c r="A139" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>20260309407</t>
+          <t>20260311586</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr"/>
@@ -9963,12 +10159,12 @@
       <c r="T139" s="11" t="inlineStr"/>
       <c r="U139" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V139" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W139" s="12" t="inlineStr">
@@ -9979,26 +10175,26 @@
     </row>
     <row r="140" ht="26" customHeight="1">
       <c r="A140" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>20260309408</t>
+          <t>20260311587</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr"/>
@@ -10026,12 +10222,12 @@
       <c r="T140" s="11" t="inlineStr"/>
       <c r="U140" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V140" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W140" s="12" t="inlineStr">
@@ -10042,26 +10238,26 @@
     </row>
     <row r="141" ht="26" customHeight="1">
       <c r="A141" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>20260309534</t>
+          <t>20260311588</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr"/>
@@ -10089,12 +10285,12 @@
       <c r="T141" s="11" t="inlineStr"/>
       <c r="U141" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V141" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W141" s="12" t="inlineStr">
@@ -10105,26 +10301,26 @@
     </row>
     <row r="142" ht="26" customHeight="1">
       <c r="A142" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>20260309535</t>
+          <t>20260311589</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr"/>
@@ -10152,12 +10348,12 @@
       <c r="T142" s="11" t="inlineStr"/>
       <c r="U142" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V142" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W142" s="12" t="inlineStr">
@@ -10168,26 +10364,26 @@
     </row>
     <row r="143" ht="26" customHeight="1">
       <c r="A143" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>20260309536</t>
+          <t>20260311590</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr"/>
@@ -10215,12 +10411,12 @@
       <c r="T143" s="11" t="inlineStr"/>
       <c r="U143" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V143" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W143" s="12" t="inlineStr">
@@ -10231,26 +10427,26 @@
     </row>
     <row r="144" ht="26" customHeight="1">
       <c r="A144" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>20260309537</t>
+          <t>20260311591</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr"/>
@@ -10278,12 +10474,12 @@
       <c r="T144" s="11" t="inlineStr"/>
       <c r="U144" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V144" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W144" s="12" t="inlineStr">
@@ -10294,26 +10490,26 @@
     </row>
     <row r="145" ht="26" customHeight="1">
       <c r="A145" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>20260309538</t>
+          <t>20260311592</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr"/>
@@ -10341,12 +10537,12 @@
       <c r="T145" s="11" t="inlineStr"/>
       <c r="U145" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V145" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W145" s="12" t="inlineStr">
@@ -10371,12 +10567,12 @@
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>20260307272</t>
+          <t>20260311593</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr"/>
@@ -10434,12 +10630,12 @@
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>20260307273</t>
+          <t>20260311594</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr"/>
@@ -10497,12 +10693,12 @@
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>20260307366</t>
+          <t>20260311595</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr"/>
@@ -10560,12 +10756,12 @@
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>20260307593</t>
+          <t>20260311596</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr"/>
@@ -10623,12 +10819,12 @@
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>20260307594</t>
+          <t>20260311597</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr"/>
@@ -10686,12 +10882,12 @@
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>20260307595</t>
+          <t>20260311598</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr"/>
@@ -10749,12 +10945,12 @@
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>20260307596</t>
+          <t>20260311599</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr"/>
@@ -10812,12 +11008,12 @@
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>20260307597</t>
+          <t>20260311601</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr"/>
@@ -10875,12 +11071,12 @@
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>20260307598</t>
+          <t>20260311602</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr"/>
@@ -10938,12 +11134,12 @@
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>20260307599</t>
+          <t>20260311603</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr"/>
@@ -11001,12 +11197,12 @@
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>20260307600</t>
+          <t>20260311604</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr"/>
@@ -11064,12 +11260,12 @@
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>20260307601</t>
+          <t>20260311606</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr"/>
@@ -11127,12 +11323,12 @@
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>20260307602</t>
+          <t>20260311987</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr"/>
@@ -11190,12 +11386,12 @@
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>20260307603</t>
+          <t>20260311988</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr"/>
@@ -11253,12 +11449,12 @@
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>20260307604</t>
+          <t>20260311989</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr"/>
@@ -11316,12 +11512,12 @@
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>20260307605</t>
+          <t>20260311990</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr"/>
@@ -11379,12 +11575,12 @@
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>20260307606</t>
+          <t>20260311991</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F162" s="11" t="inlineStr"/>
@@ -11442,12 +11638,12 @@
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>20260307607</t>
+          <t>20260311992</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr"/>
@@ -11505,12 +11701,12 @@
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>20260307609</t>
+          <t>20260311993</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr"/>
@@ -11568,12 +11764,12 @@
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>20260307610</t>
+          <t>20260311994</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr"/>
@@ -11631,12 +11827,12 @@
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>20260307611</t>
+          <t>20260311995</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F166" s="11" t="inlineStr"/>
@@ -11694,12 +11890,12 @@
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>20260307612</t>
+          <t>20260311996</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F167" s="11" t="inlineStr"/>
@@ -11757,12 +11953,12 @@
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>20260307613</t>
+          <t>20260312089</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F168" s="11" t="inlineStr"/>
@@ -11820,12 +12016,12 @@
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>20260307614</t>
+          <t>20260312090</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr"/>
@@ -11883,12 +12079,12 @@
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>20260307615</t>
+          <t>20260312091</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr"/>
@@ -11946,12 +12142,12 @@
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>20260307616</t>
+          <t>20260312092</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr"/>
@@ -12009,12 +12205,12 @@
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>20260307617</t>
+          <t>20260312094</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr"/>
@@ -12072,12 +12268,12 @@
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>20260307618</t>
+          <t>20260312095</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr"/>
@@ -12135,12 +12331,12 @@
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>20260307619</t>
+          <t>20260312096</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr"/>
@@ -12198,12 +12394,12 @@
       </c>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>20260307620</t>
+          <t>20260312097</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F175" s="11" t="inlineStr"/>
@@ -12261,12 +12457,12 @@
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>20260307621</t>
+          <t>20260312098</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F176" s="11" t="inlineStr"/>
@@ -12324,12 +12520,12 @@
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>20260307622</t>
+          <t>20260312099</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F177" s="11" t="inlineStr"/>
@@ -12387,12 +12583,12 @@
       </c>
       <c r="D178" s="11" t="inlineStr">
         <is>
-          <t>20260307623</t>
+          <t>20260312100</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F178" s="11" t="inlineStr"/>
@@ -12450,12 +12646,12 @@
       </c>
       <c r="D179" s="11" t="inlineStr">
         <is>
-          <t>20260307624</t>
+          <t>20260312101</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F179" s="11" t="inlineStr"/>
@@ -12513,12 +12709,12 @@
       </c>
       <c r="D180" s="11" t="inlineStr">
         <is>
-          <t>20260307625</t>
+          <t>20260312102</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F180" s="11" t="inlineStr"/>
@@ -12576,12 +12772,12 @@
       </c>
       <c r="D181" s="11" t="inlineStr">
         <is>
-          <t>20260307626</t>
+          <t>20260312103</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F181" s="11" t="inlineStr"/>
@@ -12639,12 +12835,12 @@
       </c>
       <c r="D182" s="11" t="inlineStr">
         <is>
-          <t>20260307627</t>
+          <t>20260312104</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr"/>
@@ -12702,12 +12898,12 @@
       </c>
       <c r="D183" s="11" t="inlineStr">
         <is>
-          <t>20260307629</t>
+          <t>20260312105</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F183" s="11" t="inlineStr"/>
@@ -12765,12 +12961,12 @@
       </c>
       <c r="D184" s="11" t="inlineStr">
         <is>
-          <t>20260307630</t>
+          <t>20260312106</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr"/>
@@ -12828,12 +13024,12 @@
       </c>
       <c r="D185" s="11" t="inlineStr">
         <is>
-          <t>20260307631</t>
+          <t>20260312107</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F185" s="11" t="inlineStr"/>
@@ -12891,12 +13087,12 @@
       </c>
       <c r="D186" s="11" t="inlineStr">
         <is>
-          <t>20260307632</t>
+          <t>20260312108</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr"/>
@@ -12954,12 +13150,12 @@
       </c>
       <c r="D187" s="11" t="inlineStr">
         <is>
-          <t>20260307633</t>
+          <t>20260312109</t>
         </is>
       </c>
       <c r="E187" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F187" s="11" t="inlineStr"/>
@@ -13017,12 +13213,12 @@
       </c>
       <c r="D188" s="11" t="inlineStr">
         <is>
-          <t>20260307634</t>
+          <t>20260312110</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F188" s="11" t="inlineStr"/>
@@ -13080,12 +13276,12 @@
       </c>
       <c r="D189" s="11" t="inlineStr">
         <is>
-          <t>20260307635</t>
+          <t>20260312111</t>
         </is>
       </c>
       <c r="E189" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F189" s="11" t="inlineStr"/>
@@ -13143,12 +13339,12 @@
       </c>
       <c r="D190" s="11" t="inlineStr">
         <is>
-          <t>20260307816</t>
+          <t>20260312112</t>
         </is>
       </c>
       <c r="E190" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F190" s="11" t="inlineStr"/>
@@ -13206,12 +13402,12 @@
       </c>
       <c r="D191" s="11" t="inlineStr">
         <is>
-          <t>20260307817</t>
+          <t>20260312114</t>
         </is>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr"/>
@@ -13269,12 +13465,12 @@
       </c>
       <c r="D192" s="11" t="inlineStr">
         <is>
-          <t>20260307818</t>
+          <t>20260312115</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F192" s="11" t="inlineStr"/>
@@ -13332,12 +13528,12 @@
       </c>
       <c r="D193" s="11" t="inlineStr">
         <is>
-          <t>20260307819</t>
+          <t>20260312333</t>
         </is>
       </c>
       <c r="E193" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F193" s="11" t="inlineStr"/>
@@ -13395,12 +13591,12 @@
       </c>
       <c r="D194" s="11" t="inlineStr">
         <is>
-          <t>20260307820</t>
+          <t>20260312334</t>
         </is>
       </c>
       <c r="E194" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F194" s="11" t="inlineStr"/>
@@ -13458,12 +13654,12 @@
       </c>
       <c r="D195" s="11" t="inlineStr">
         <is>
-          <t>20260307821</t>
+          <t>20260312335</t>
         </is>
       </c>
       <c r="E195" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F195" s="11" t="inlineStr"/>
@@ -13521,12 +13717,12 @@
       </c>
       <c r="D196" s="11" t="inlineStr">
         <is>
-          <t>20260307998</t>
+          <t>20260312336</t>
         </is>
       </c>
       <c r="E196" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F196" s="11" t="inlineStr"/>
@@ -13584,12 +13780,12 @@
       </c>
       <c r="D197" s="11" t="inlineStr">
         <is>
-          <t>20260308027</t>
+          <t>20260312337</t>
         </is>
       </c>
       <c r="E197" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F197" s="11" t="inlineStr"/>
@@ -13647,12 +13843,12 @@
       </c>
       <c r="D198" s="11" t="inlineStr">
         <is>
-          <t>20260308028</t>
+          <t>20260312338</t>
         </is>
       </c>
       <c r="E198" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F198" s="11" t="inlineStr"/>
@@ -13710,12 +13906,12 @@
       </c>
       <c r="D199" s="11" t="inlineStr">
         <is>
-          <t>20260308029</t>
+          <t>20260312339</t>
         </is>
       </c>
       <c r="E199" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F199" s="11" t="inlineStr"/>
@@ -13773,12 +13969,12 @@
       </c>
       <c r="D200" s="11" t="inlineStr">
         <is>
-          <t>20260308031</t>
+          <t>20260312417</t>
         </is>
       </c>
       <c r="E200" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F200" s="11" t="inlineStr"/>
@@ -13836,12 +14032,12 @@
       </c>
       <c r="D201" s="11" t="inlineStr">
         <is>
-          <t>20260308033</t>
+          <t>20260312423</t>
         </is>
       </c>
       <c r="E201" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F201" s="11" t="inlineStr"/>
@@ -13899,12 +14095,12 @@
       </c>
       <c r="D202" s="11" t="inlineStr">
         <is>
-          <t>20260308078</t>
+          <t>20260312424</t>
         </is>
       </c>
       <c r="E202" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F202" s="11" t="inlineStr"/>
@@ -13962,12 +14158,12 @@
       </c>
       <c r="D203" s="11" t="inlineStr">
         <is>
-          <t>20260308603</t>
+          <t>20260312425</t>
         </is>
       </c>
       <c r="E203" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F203" s="11" t="inlineStr"/>
@@ -14025,12 +14221,12 @@
       </c>
       <c r="D204" s="11" t="inlineStr">
         <is>
-          <t>20260308605</t>
+          <t>20260312426</t>
         </is>
       </c>
       <c r="E204" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F204" s="11" t="inlineStr"/>
@@ -14088,12 +14284,12 @@
       </c>
       <c r="D205" s="11" t="inlineStr">
         <is>
-          <t>20260308717</t>
+          <t>20260312427</t>
         </is>
       </c>
       <c r="E205" s="11" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F205" s="11" t="inlineStr"/>
@@ -14135,1079 +14331,8 @@
         </is>
       </c>
     </row>
-    <row r="206" ht="26" customHeight="1">
-      <c r="A206" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B206" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C206" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D206" s="11" t="inlineStr">
-        <is>
-          <t>20260308743</t>
-        </is>
-      </c>
-      <c r="E206" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F206" s="11" t="inlineStr"/>
-      <c r="G206" s="11" t="inlineStr"/>
-      <c r="H206" s="11" t="inlineStr"/>
-      <c r="I206" s="11" t="inlineStr"/>
-      <c r="J206" s="11" t="inlineStr"/>
-      <c r="K206" s="11" t="inlineStr"/>
-      <c r="L206" s="11" t="inlineStr"/>
-      <c r="M206" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N206" s="11" t="inlineStr"/>
-      <c r="O206" s="11" t="inlineStr"/>
-      <c r="P206" s="11" t="inlineStr"/>
-      <c r="Q206" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R206" s="11" t="inlineStr"/>
-      <c r="S206" s="11" t="inlineStr"/>
-      <c r="T206" s="11" t="inlineStr"/>
-      <c r="U206" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V206" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W206" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="26" customHeight="1">
-      <c r="A207" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B207" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C207" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D207" s="11" t="inlineStr">
-        <is>
-          <t>20260308764</t>
-        </is>
-      </c>
-      <c r="E207" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F207" s="11" t="inlineStr"/>
-      <c r="G207" s="11" t="inlineStr"/>
-      <c r="H207" s="11" t="inlineStr"/>
-      <c r="I207" s="11" t="inlineStr"/>
-      <c r="J207" s="11" t="inlineStr"/>
-      <c r="K207" s="11" t="inlineStr"/>
-      <c r="L207" s="11" t="inlineStr"/>
-      <c r="M207" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N207" s="11" t="inlineStr"/>
-      <c r="O207" s="11" t="inlineStr"/>
-      <c r="P207" s="11" t="inlineStr"/>
-      <c r="Q207" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R207" s="11" t="inlineStr"/>
-      <c r="S207" s="11" t="inlineStr"/>
-      <c r="T207" s="11" t="inlineStr"/>
-      <c r="U207" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V207" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W207" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="26" customHeight="1">
-      <c r="A208" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B208" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C208" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D208" s="11" t="inlineStr">
-        <is>
-          <t>20260308868</t>
-        </is>
-      </c>
-      <c r="E208" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F208" s="11" t="inlineStr"/>
-      <c r="G208" s="11" t="inlineStr"/>
-      <c r="H208" s="11" t="inlineStr"/>
-      <c r="I208" s="11" t="inlineStr"/>
-      <c r="J208" s="11" t="inlineStr"/>
-      <c r="K208" s="11" t="inlineStr"/>
-      <c r="L208" s="11" t="inlineStr"/>
-      <c r="M208" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N208" s="11" t="inlineStr"/>
-      <c r="O208" s="11" t="inlineStr"/>
-      <c r="P208" s="11" t="inlineStr"/>
-      <c r="Q208" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R208" s="11" t="inlineStr"/>
-      <c r="S208" s="11" t="inlineStr"/>
-      <c r="T208" s="11" t="inlineStr"/>
-      <c r="U208" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V208" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W208" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="26" customHeight="1">
-      <c r="A209" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B209" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C209" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D209" s="11" t="inlineStr">
-        <is>
-          <t>20260308924</t>
-        </is>
-      </c>
-      <c r="E209" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F209" s="11" t="inlineStr"/>
-      <c r="G209" s="11" t="inlineStr"/>
-      <c r="H209" s="11" t="inlineStr"/>
-      <c r="I209" s="11" t="inlineStr"/>
-      <c r="J209" s="11" t="inlineStr"/>
-      <c r="K209" s="11" t="inlineStr"/>
-      <c r="L209" s="11" t="inlineStr"/>
-      <c r="M209" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N209" s="11" t="inlineStr"/>
-      <c r="O209" s="11" t="inlineStr"/>
-      <c r="P209" s="11" t="inlineStr"/>
-      <c r="Q209" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R209" s="11" t="inlineStr"/>
-      <c r="S209" s="11" t="inlineStr"/>
-      <c r="T209" s="11" t="inlineStr"/>
-      <c r="U209" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V209" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W209" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="26" customHeight="1">
-      <c r="A210" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B210" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C210" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D210" s="11" t="inlineStr">
-        <is>
-          <t>20260308954</t>
-        </is>
-      </c>
-      <c r="E210" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F210" s="11" t="inlineStr"/>
-      <c r="G210" s="11" t="inlineStr"/>
-      <c r="H210" s="11" t="inlineStr"/>
-      <c r="I210" s="11" t="inlineStr"/>
-      <c r="J210" s="11" t="inlineStr"/>
-      <c r="K210" s="11" t="inlineStr"/>
-      <c r="L210" s="11" t="inlineStr"/>
-      <c r="M210" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N210" s="11" t="inlineStr"/>
-      <c r="O210" s="11" t="inlineStr"/>
-      <c r="P210" s="11" t="inlineStr"/>
-      <c r="Q210" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R210" s="11" t="inlineStr"/>
-      <c r="S210" s="11" t="inlineStr"/>
-      <c r="T210" s="11" t="inlineStr"/>
-      <c r="U210" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V210" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W210" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="26" customHeight="1">
-      <c r="A211" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B211" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C211" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D211" s="11" t="inlineStr">
-        <is>
-          <t>20260309062</t>
-        </is>
-      </c>
-      <c r="E211" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F211" s="11" t="inlineStr"/>
-      <c r="G211" s="11" t="inlineStr"/>
-      <c r="H211" s="11" t="inlineStr"/>
-      <c r="I211" s="11" t="inlineStr"/>
-      <c r="J211" s="11" t="inlineStr"/>
-      <c r="K211" s="11" t="inlineStr"/>
-      <c r="L211" s="11" t="inlineStr"/>
-      <c r="M211" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N211" s="11" t="inlineStr"/>
-      <c r="O211" s="11" t="inlineStr"/>
-      <c r="P211" s="11" t="inlineStr"/>
-      <c r="Q211" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R211" s="11" t="inlineStr"/>
-      <c r="S211" s="11" t="inlineStr"/>
-      <c r="T211" s="11" t="inlineStr"/>
-      <c r="U211" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V211" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W211" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="26" customHeight="1">
-      <c r="A212" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B212" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C212" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D212" s="11" t="inlineStr">
-        <is>
-          <t>20260309063</t>
-        </is>
-      </c>
-      <c r="E212" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F212" s="11" t="inlineStr"/>
-      <c r="G212" s="11" t="inlineStr"/>
-      <c r="H212" s="11" t="inlineStr"/>
-      <c r="I212" s="11" t="inlineStr"/>
-      <c r="J212" s="11" t="inlineStr"/>
-      <c r="K212" s="11" t="inlineStr"/>
-      <c r="L212" s="11" t="inlineStr"/>
-      <c r="M212" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N212" s="11" t="inlineStr"/>
-      <c r="O212" s="11" t="inlineStr"/>
-      <c r="P212" s="11" t="inlineStr"/>
-      <c r="Q212" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R212" s="11" t="inlineStr"/>
-      <c r="S212" s="11" t="inlineStr"/>
-      <c r="T212" s="11" t="inlineStr"/>
-      <c r="U212" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V212" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W212" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="26" customHeight="1">
-      <c r="A213" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B213" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C213" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D213" s="11" t="inlineStr">
-        <is>
-          <t>20260309068</t>
-        </is>
-      </c>
-      <c r="E213" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F213" s="11" t="inlineStr"/>
-      <c r="G213" s="11" t="inlineStr"/>
-      <c r="H213" s="11" t="inlineStr"/>
-      <c r="I213" s="11" t="inlineStr"/>
-      <c r="J213" s="11" t="inlineStr"/>
-      <c r="K213" s="11" t="inlineStr"/>
-      <c r="L213" s="11" t="inlineStr"/>
-      <c r="M213" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N213" s="11" t="inlineStr"/>
-      <c r="O213" s="11" t="inlineStr"/>
-      <c r="P213" s="11" t="inlineStr"/>
-      <c r="Q213" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R213" s="11" t="inlineStr"/>
-      <c r="S213" s="11" t="inlineStr"/>
-      <c r="T213" s="11" t="inlineStr"/>
-      <c r="U213" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V213" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W213" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="26" customHeight="1">
-      <c r="A214" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B214" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C214" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D214" s="11" t="inlineStr">
-        <is>
-          <t>20260309074</t>
-        </is>
-      </c>
-      <c r="E214" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F214" s="11" t="inlineStr"/>
-      <c r="G214" s="11" t="inlineStr"/>
-      <c r="H214" s="11" t="inlineStr"/>
-      <c r="I214" s="11" t="inlineStr"/>
-      <c r="J214" s="11" t="inlineStr"/>
-      <c r="K214" s="11" t="inlineStr"/>
-      <c r="L214" s="11" t="inlineStr"/>
-      <c r="M214" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N214" s="11" t="inlineStr"/>
-      <c r="O214" s="11" t="inlineStr"/>
-      <c r="P214" s="11" t="inlineStr"/>
-      <c r="Q214" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R214" s="11" t="inlineStr"/>
-      <c r="S214" s="11" t="inlineStr"/>
-      <c r="T214" s="11" t="inlineStr"/>
-      <c r="U214" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V214" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W214" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="26" customHeight="1">
-      <c r="A215" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B215" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C215" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D215" s="11" t="inlineStr">
-        <is>
-          <t>20260309076</t>
-        </is>
-      </c>
-      <c r="E215" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F215" s="11" t="inlineStr"/>
-      <c r="G215" s="11" t="inlineStr"/>
-      <c r="H215" s="11" t="inlineStr"/>
-      <c r="I215" s="11" t="inlineStr"/>
-      <c r="J215" s="11" t="inlineStr"/>
-      <c r="K215" s="11" t="inlineStr"/>
-      <c r="L215" s="11" t="inlineStr"/>
-      <c r="M215" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N215" s="11" t="inlineStr"/>
-      <c r="O215" s="11" t="inlineStr"/>
-      <c r="P215" s="11" t="inlineStr"/>
-      <c r="Q215" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R215" s="11" t="inlineStr"/>
-      <c r="S215" s="11" t="inlineStr"/>
-      <c r="T215" s="11" t="inlineStr"/>
-      <c r="U215" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V215" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W215" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="26" customHeight="1">
-      <c r="A216" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B216" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C216" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D216" s="11" t="inlineStr">
-        <is>
-          <t>20260309077</t>
-        </is>
-      </c>
-      <c r="E216" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F216" s="11" t="inlineStr"/>
-      <c r="G216" s="11" t="inlineStr"/>
-      <c r="H216" s="11" t="inlineStr"/>
-      <c r="I216" s="11" t="inlineStr"/>
-      <c r="J216" s="11" t="inlineStr"/>
-      <c r="K216" s="11" t="inlineStr"/>
-      <c r="L216" s="11" t="inlineStr"/>
-      <c r="M216" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N216" s="11" t="inlineStr"/>
-      <c r="O216" s="11" t="inlineStr"/>
-      <c r="P216" s="11" t="inlineStr"/>
-      <c r="Q216" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R216" s="11" t="inlineStr"/>
-      <c r="S216" s="11" t="inlineStr"/>
-      <c r="T216" s="11" t="inlineStr"/>
-      <c r="U216" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V216" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W216" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="217" ht="26" customHeight="1">
-      <c r="A217" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B217" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C217" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D217" s="11" t="inlineStr">
-        <is>
-          <t>20260309166</t>
-        </is>
-      </c>
-      <c r="E217" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F217" s="11" t="inlineStr"/>
-      <c r="G217" s="11" t="inlineStr"/>
-      <c r="H217" s="11" t="inlineStr"/>
-      <c r="I217" s="11" t="inlineStr"/>
-      <c r="J217" s="11" t="inlineStr"/>
-      <c r="K217" s="11" t="inlineStr"/>
-      <c r="L217" s="11" t="inlineStr"/>
-      <c r="M217" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N217" s="11" t="inlineStr"/>
-      <c r="O217" s="11" t="inlineStr"/>
-      <c r="P217" s="11" t="inlineStr"/>
-      <c r="Q217" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R217" s="11" t="inlineStr"/>
-      <c r="S217" s="11" t="inlineStr"/>
-      <c r="T217" s="11" t="inlineStr"/>
-      <c r="U217" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V217" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W217" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="218" ht="26" customHeight="1">
-      <c r="A218" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B218" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C218" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D218" s="11" t="inlineStr">
-        <is>
-          <t>20260309172</t>
-        </is>
-      </c>
-      <c r="E218" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F218" s="11" t="inlineStr"/>
-      <c r="G218" s="11" t="inlineStr"/>
-      <c r="H218" s="11" t="inlineStr"/>
-      <c r="I218" s="11" t="inlineStr"/>
-      <c r="J218" s="11" t="inlineStr"/>
-      <c r="K218" s="11" t="inlineStr"/>
-      <c r="L218" s="11" t="inlineStr"/>
-      <c r="M218" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N218" s="11" t="inlineStr"/>
-      <c r="O218" s="11" t="inlineStr"/>
-      <c r="P218" s="11" t="inlineStr"/>
-      <c r="Q218" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R218" s="11" t="inlineStr"/>
-      <c r="S218" s="11" t="inlineStr"/>
-      <c r="T218" s="11" t="inlineStr"/>
-      <c r="U218" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V218" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W218" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="219" ht="26" customHeight="1">
-      <c r="A219" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B219" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C219" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D219" s="11" t="inlineStr">
-        <is>
-          <t>20260309199</t>
-        </is>
-      </c>
-      <c r="E219" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F219" s="11" t="inlineStr"/>
-      <c r="G219" s="11" t="inlineStr"/>
-      <c r="H219" s="11" t="inlineStr"/>
-      <c r="I219" s="11" t="inlineStr"/>
-      <c r="J219" s="11" t="inlineStr"/>
-      <c r="K219" s="11" t="inlineStr"/>
-      <c r="L219" s="11" t="inlineStr"/>
-      <c r="M219" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N219" s="11" t="inlineStr"/>
-      <c r="O219" s="11" t="inlineStr"/>
-      <c r="P219" s="11" t="inlineStr"/>
-      <c r="Q219" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R219" s="11" t="inlineStr"/>
-      <c r="S219" s="11" t="inlineStr"/>
-      <c r="T219" s="11" t="inlineStr"/>
-      <c r="U219" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V219" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W219" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="220" ht="26" customHeight="1">
-      <c r="A220" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B220" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C220" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D220" s="11" t="inlineStr">
-        <is>
-          <t>20260309255</t>
-        </is>
-      </c>
-      <c r="E220" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F220" s="11" t="inlineStr"/>
-      <c r="G220" s="11" t="inlineStr"/>
-      <c r="H220" s="11" t="inlineStr"/>
-      <c r="I220" s="11" t="inlineStr"/>
-      <c r="J220" s="11" t="inlineStr"/>
-      <c r="K220" s="11" t="inlineStr"/>
-      <c r="L220" s="11" t="inlineStr"/>
-      <c r="M220" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N220" s="11" t="inlineStr"/>
-      <c r="O220" s="11" t="inlineStr"/>
-      <c r="P220" s="11" t="inlineStr"/>
-      <c r="Q220" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R220" s="11" t="inlineStr"/>
-      <c r="S220" s="11" t="inlineStr"/>
-      <c r="T220" s="11" t="inlineStr"/>
-      <c r="U220" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V220" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W220" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="221" ht="26" customHeight="1">
-      <c r="A221" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B221" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C221" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D221" s="11" t="inlineStr">
-        <is>
-          <t>20260309343</t>
-        </is>
-      </c>
-      <c r="E221" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F221" s="11" t="inlineStr"/>
-      <c r="G221" s="11" t="inlineStr"/>
-      <c r="H221" s="11" t="inlineStr"/>
-      <c r="I221" s="11" t="inlineStr"/>
-      <c r="J221" s="11" t="inlineStr"/>
-      <c r="K221" s="11" t="inlineStr"/>
-      <c r="L221" s="11" t="inlineStr"/>
-      <c r="M221" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N221" s="11" t="inlineStr"/>
-      <c r="O221" s="11" t="inlineStr"/>
-      <c r="P221" s="11" t="inlineStr"/>
-      <c r="Q221" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R221" s="11" t="inlineStr"/>
-      <c r="S221" s="11" t="inlineStr"/>
-      <c r="T221" s="11" t="inlineStr"/>
-      <c r="U221" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V221" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W221" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="222" ht="26" customHeight="1">
-      <c r="A222" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B222" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C222" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D222" s="11" t="inlineStr">
-        <is>
-          <t>20260309434</t>
-        </is>
-      </c>
-      <c r="E222" s="11" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="F222" s="11" t="inlineStr"/>
-      <c r="G222" s="11" t="inlineStr"/>
-      <c r="H222" s="11" t="inlineStr"/>
-      <c r="I222" s="11" t="inlineStr"/>
-      <c r="J222" s="11" t="inlineStr"/>
-      <c r="K222" s="11" t="inlineStr"/>
-      <c r="L222" s="11" t="inlineStr"/>
-      <c r="M222" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N222" s="11" t="inlineStr"/>
-      <c r="O222" s="11" t="inlineStr"/>
-      <c r="P222" s="11" t="inlineStr"/>
-      <c r="Q222" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R222" s="11" t="inlineStr"/>
-      <c r="S222" s="11" t="inlineStr"/>
-      <c r="T222" s="11" t="inlineStr"/>
-      <c r="U222" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V222" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W222" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W222"/>
+  <autoFilter ref="A1:W205"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
@@ -15413,23 +14538,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W203" r:id="rId202"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W204" r:id="rId203"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W205" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W206" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W207" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W208" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W209" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W210" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W211" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W212" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W213" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W214" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W215" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W216" r:id="rId215"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W217" r:id="rId216"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W218" r:id="rId217"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W219" r:id="rId218"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W220" r:id="rId219"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W221" r:id="rId220"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W222" r:id="rId221"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15441,7 +14549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15458,7 +14566,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-05-22 05:07</t>
+          <t>Run: 2026-05-23 04:43</t>
         </is>
       </c>
     </row>
@@ -15473,7 +14581,7 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>221</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
@@ -15483,7 +14591,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
@@ -15503,7 +14611,7 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>123</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
@@ -15513,7 +14621,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -15523,7 +14631,7 @@
         </is>
       </c>
       <c r="B9" s="14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10">
@@ -15549,7 +14657,7 @@
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13">
@@ -15559,23 +14667,23 @@
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Notice of Trustee Sale</t>
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>35</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Notice of Trustee Sale</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
@@ -15585,41 +14693,31 @@
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Mechanic Lien</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>State Tax Lien</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="inlineStr">
-        <is>
-          <t>Tax Deed</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-05-24 05:04</t>
+          <t>Run: 2026-05-25 05:18</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-05-25 05:18</t>
+          <t>Run: 2026-05-26 05:00</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$87</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +34,39 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00374151"/>
       <sz val="10"/>
     </font>
     <font>
@@ -49,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +94,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E2433"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,14 +138,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -606,8 +689,6334 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>20260313572</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>Gannon Nikolich</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>U.S. Bank Trust Company, National Association, not in its individual capacity, but solely as</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>236250</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr"/>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>155 North Pasadena Mesa, AZ 85201-6727</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>138-31-013</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>20260313859</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>REBECCA LYNN DAVIS, SINGLE WOMAN</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>U.S. Bank Trust National Association as Trustee for Igloo Annex Series VI Trust</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>354900</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>11331 WALABAMAAVE</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>YOUNGTOWN</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>85363</t>
+        </is>
+      </c>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>142-66-0074</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>20260313892</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>SCOTT K. GARCIAAND ELYSE GARCIA</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Lakeview Loan Servicing, LLC</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>514892</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2902 EAST DIAMOND AVENUE</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>85204</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>140-40-1646</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>20260313920</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>ROBERT L COUCH</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Finance of America Reverse LLC</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>642000</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>201 West Jefferson</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>258 N SANDAL</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>85205</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>141-49-5820</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>20260314798</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Kelvin Garcia</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>U.S. Bank National Association Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>168785</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>8723 West Magnolia Street</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>101-57-5251</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>U.S. Bank National Association Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>20260314824</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Jeffrey Alan Christian and Rene Kristina Christian</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>U.S. Bank National Association Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>313222</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>16910 S 16th Ln</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>300-97-3926</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>U.S. Bank National Association Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>20260314848</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Aubrey Mitchell and Antwain Mitchell</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>American Financial Network, Inc. Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>397664</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>3141 W Desert Cove Ave</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>149-18-1404</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>American Financial Network, Inc. Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>20260314921</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>GI DC GLENDALE, LLC, a Delaware limited liability company</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>U.S. Bank National Association, as Trustee for the benefit of the Holders of CFCRE 2016-C4 Mortgage Trust</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>19700000</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr"/>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>5353 West Bell Road</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>200-50-212</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>John Craiger</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>20260314959</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>TERRENCE A. JACKSON</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>loanDepot.com, LLC</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>255375</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>4040 EAST SIDEWINDER COURT</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>313-02-0155</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>Bradford E. Klein, a member of the State Bar of</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>20260314977</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>BEAU MUNHOLLON AND TRACY L. WOOLGAR</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>loanDepot.com, LLC</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>411300</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>5659 N 195TH DR</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr"/>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>502-34-7524</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>Bradford E. Klein, a member of the State Bar of</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>20260315021</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>CRYSTAL RIDDELL</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>MidFirst Bank</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>282380</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>22043 S 211TH ST</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>QUEEN CREEK</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>314-06-751</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>Larry O. Folks</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>20260315202</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>MARY JANE HEREDIA</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>TH MSR Holdings LLC</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>292540</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>7168 W DREYFUS DR</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>PEORIA</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>85381</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>200-98-619</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>20260315257</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Henry Marquez</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Sailfish Servicing, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>205000</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>11545 West Wethersfield Road</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr"/>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr"/>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>509-06-9084</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>Sailfish Servicing, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>20260315625</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>WILHELMINA M. BUFORD, SINGLE WOMAN</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>358428</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>4214 S 58TH LN</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>85043</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>104-58-4525</t>
+        </is>
+      </c>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>20260315780</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr"/>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>923 E. Mary Lane, Gilbert, AZ 85295</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>374000</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>3800 S. Cantabria Cir., Unit 1087</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>Chandler</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>88248</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>303-80-087</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr"/>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>20260316003</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>DANIEL BRUCE BURNS AND APRIL BURNS</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>CrossCountry Mortgage, LLC</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>484350</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>10005 E SUPERNOVA DR</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
+          <t>85212</t>
+        </is>
+      </c>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>312-15-804</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>20260314595</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Qnity Mortgage Corporation F/K/A PHH Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>422211</v>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr"/>
+      <c r="L18" s="7" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr"/>
+      <c r="O18" s="7" t="inlineStr"/>
+      <c r="P18" s="7" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr"/>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>501-17-343</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>Western Progressive — Arizona, Inc.</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>20260315019</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>Pedro Cano</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Arizona Financial Credit Union f/k/a Arizona Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>60000</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>law firm of Folks Hess</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>8839 W Golden Ln</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr">
+        <is>
+          <t>Peoria</t>
+        </is>
+      </c>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>85345</t>
+        </is>
+      </c>
+      <c r="O19" s="7" t="inlineStr"/>
+      <c r="P19" s="7" t="inlineStr"/>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr"/>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>142-35-231</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr">
+        <is>
+          <t>Larry O. Folks</t>
+        </is>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>20260315025</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>CHRISTOPHER L WOODS</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>MidFirst Bank</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>51656</v>
+      </c>
+      <c r="I20" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr">
+        <is>
+          <t>630 E JENSEN ST UNIT 156</t>
+        </is>
+      </c>
+      <c r="L20" s="7" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>85203</t>
+        </is>
+      </c>
+      <c r="O20" s="7" t="inlineStr"/>
+      <c r="P20" s="7" t="inlineStr"/>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr"/>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>136-24-290</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr">
+        <is>
+          <t>Larry O. Folks</t>
+        </is>
+      </c>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>20260315727</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>C/O NewRez LLC, d/b/a Shellpoint Mortgage</t>
+        </is>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>155000</v>
+      </c>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>110-16-0560</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr"/>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>20260315739</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>C/O NewRez LLC, d/b/a Shellpoint Mortgage</t>
+        </is>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>531960</v>
+      </c>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr"/>
+      <c r="L22" s="7" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr"/>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr"/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>300-23-1686</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr"/>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>20260316133</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>C/O Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>118750</v>
+      </c>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr"/>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="7" t="inlineStr"/>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr"/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>102-82-416</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr"/>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>20260316134</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>C/O Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>313430</v>
+      </c>
+      <c r="I24" s="7" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr"/>
+      <c r="L24" s="7" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr"/>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R24" s="7" t="inlineStr"/>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>501-15-155</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr"/>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V24" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>20260316137</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>C/O Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>334579</v>
+      </c>
+      <c r="I25" s="7" t="inlineStr"/>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr"/>
+      <c r="O25" s="7" t="inlineStr"/>
+      <c r="P25" s="7" t="inlineStr"/>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr"/>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>503-82-697</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr"/>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V25" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>20260313547</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>Thomas J. Long and Beirget M. Long</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>Wells Fargo Bank, N.A. Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>100000</v>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr"/>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr"/>
+      <c r="O26" s="7" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr"/>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr"/>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>211-20-057</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr">
+        <is>
+          <t>Wells Fargo Bank, N.A. Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>20260313847</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr"/>
+      <c r="G27" s="7" t="inlineStr"/>
+      <c r="H27" s="7" t="inlineStr"/>
+      <c r="I27" s="7" t="inlineStr"/>
+      <c r="J27" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>17700 North Hayden Road</t>
+        </is>
+      </c>
+      <c r="L27" s="7" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
+      <c r="M27" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>85255</t>
+        </is>
+      </c>
+      <c r="O27" s="7" t="inlineStr"/>
+      <c r="P27" s="7" t="inlineStr"/>
+      <c r="Q27" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R27" s="7" t="inlineStr"/>
+      <c r="S27" s="7" t="inlineStr"/>
+      <c r="T27" s="7" t="inlineStr"/>
+      <c r="U27" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V27" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>20260315733</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr"/>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>C/O NewRez LLC, d/b/a Shellpoint Mortgage</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>49533.3</v>
+      </c>
+      <c r="I28" s="7" t="inlineStr"/>
+      <c r="J28" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K28" s="7" t="inlineStr"/>
+      <c r="L28" s="7" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr"/>
+      <c r="O28" s="7" t="inlineStr"/>
+      <c r="P28" s="7" t="inlineStr"/>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R28" s="7" t="inlineStr"/>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>155-28-038</t>
+        </is>
+      </c>
+      <c r="T28" s="7" t="inlineStr"/>
+      <c r="U28" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V28" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>20260315564</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr"/>
+      <c r="G29" s="7" t="inlineStr"/>
+      <c r="H29" s="7" t="inlineStr"/>
+      <c r="I29" s="7" t="inlineStr"/>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr">
+        <is>
+          <t>4730 W Northern Ave #1108</t>
+        </is>
+      </c>
+      <c r="L29" s="7" t="inlineStr">
+        <is>
+          <t>Glendale</t>
+        </is>
+      </c>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
+      <c r="O29" s="7" t="inlineStr"/>
+      <c r="P29" s="7" t="inlineStr"/>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr"/>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>148-12-697</t>
+        </is>
+      </c>
+      <c r="T29" s="7" t="inlineStr"/>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V29" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>20260312640</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr"/>
+      <c r="G30" s="11" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr"/>
+      <c r="I30" s="11" t="inlineStr"/>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr"/>
+      <c r="L30" s="11" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr"/>
+      <c r="O30" s="11" t="inlineStr"/>
+      <c r="P30" s="11" t="inlineStr"/>
+      <c r="Q30" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R30" s="11" t="inlineStr"/>
+      <c r="S30" s="11" t="inlineStr"/>
+      <c r="T30" s="11" t="inlineStr"/>
+      <c r="U30" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V30" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W30" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>20260312650</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr"/>
+      <c r="G31" s="11" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr"/>
+      <c r="I31" s="11" t="inlineStr"/>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K31" s="11" t="inlineStr"/>
+      <c r="L31" s="11" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr"/>
+      <c r="O31" s="11" t="inlineStr"/>
+      <c r="P31" s="11" t="inlineStr"/>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R31" s="11" t="inlineStr"/>
+      <c r="S31" s="11" t="inlineStr"/>
+      <c r="T31" s="11" t="inlineStr"/>
+      <c r="U31" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W31" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>20260312717</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr"/>
+      <c r="G32" s="11" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr"/>
+      <c r="I32" s="11" t="inlineStr"/>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr"/>
+      <c r="L32" s="11" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N32" s="11" t="inlineStr"/>
+      <c r="O32" s="11" t="inlineStr"/>
+      <c r="P32" s="11" t="inlineStr"/>
+      <c r="Q32" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R32" s="11" t="inlineStr"/>
+      <c r="S32" s="11" t="inlineStr"/>
+      <c r="T32" s="11" t="inlineStr"/>
+      <c r="U32" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V32" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W32" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>20260312754</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr"/>
+      <c r="G33" s="11" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr"/>
+      <c r="I33" s="11" t="inlineStr"/>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr"/>
+      <c r="L33" s="11" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr"/>
+      <c r="O33" s="11" t="inlineStr"/>
+      <c r="P33" s="11" t="inlineStr"/>
+      <c r="Q33" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R33" s="11" t="inlineStr"/>
+      <c r="S33" s="11" t="inlineStr"/>
+      <c r="T33" s="11" t="inlineStr"/>
+      <c r="U33" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W33" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>20260312756</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr"/>
+      <c r="G34" s="11" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="11" t="inlineStr"/>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr"/>
+      <c r="L34" s="11" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N34" s="11" t="inlineStr"/>
+      <c r="O34" s="11" t="inlineStr"/>
+      <c r="P34" s="11" t="inlineStr"/>
+      <c r="Q34" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R34" s="11" t="inlineStr"/>
+      <c r="S34" s="11" t="inlineStr"/>
+      <c r="T34" s="11" t="inlineStr"/>
+      <c r="U34" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V34" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>20260312762</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr"/>
+      <c r="G35" s="11" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr"/>
+      <c r="I35" s="11" t="inlineStr"/>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr"/>
+      <c r="L35" s="11" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr"/>
+      <c r="O35" s="11" t="inlineStr"/>
+      <c r="P35" s="11" t="inlineStr"/>
+      <c r="Q35" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R35" s="11" t="inlineStr"/>
+      <c r="S35" s="11" t="inlineStr"/>
+      <c r="T35" s="11" t="inlineStr"/>
+      <c r="U35" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V35" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>20260312804</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr"/>
+      <c r="G36" s="11" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr"/>
+      <c r="I36" s="11" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr"/>
+      <c r="K36" s="11" t="inlineStr"/>
+      <c r="L36" s="11" t="inlineStr"/>
+      <c r="M36" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N36" s="11" t="inlineStr"/>
+      <c r="O36" s="11" t="inlineStr"/>
+      <c r="P36" s="11" t="inlineStr"/>
+      <c r="Q36" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R36" s="11" t="inlineStr"/>
+      <c r="S36" s="11" t="inlineStr"/>
+      <c r="T36" s="11" t="inlineStr"/>
+      <c r="U36" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V36" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W36" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>20260312810</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr"/>
+      <c r="G37" s="11" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr"/>
+      <c r="I37" s="11" t="inlineStr"/>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr"/>
+      <c r="L37" s="11" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr"/>
+      <c r="O37" s="11" t="inlineStr"/>
+      <c r="P37" s="11" t="inlineStr"/>
+      <c r="Q37" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R37" s="11" t="inlineStr"/>
+      <c r="S37" s="11" t="inlineStr"/>
+      <c r="T37" s="11" t="inlineStr"/>
+      <c r="U37" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V37" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W37" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>20260312848</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr"/>
+      <c r="G38" s="11" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr"/>
+      <c r="I38" s="11" t="inlineStr"/>
+      <c r="J38" s="11" t="inlineStr"/>
+      <c r="K38" s="11" t="inlineStr"/>
+      <c r="L38" s="11" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N38" s="11" t="inlineStr"/>
+      <c r="O38" s="11" t="inlineStr"/>
+      <c r="P38" s="11" t="inlineStr"/>
+      <c r="Q38" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R38" s="11" t="inlineStr"/>
+      <c r="S38" s="11" t="inlineStr"/>
+      <c r="T38" s="11" t="inlineStr"/>
+      <c r="U38" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V38" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W38" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>20260313870</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr"/>
+      <c r="G39" s="11" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr"/>
+      <c r="I39" s="11" t="inlineStr"/>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr"/>
+      <c r="L39" s="11" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr"/>
+      <c r="O39" s="11" t="inlineStr"/>
+      <c r="P39" s="11" t="inlineStr"/>
+      <c r="Q39" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R39" s="11" t="inlineStr"/>
+      <c r="S39" s="11" t="inlineStr"/>
+      <c r="T39" s="11" t="inlineStr"/>
+      <c r="U39" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V39" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W39" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>20260313881</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr"/>
+      <c r="G40" s="11" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr"/>
+      <c r="I40" s="11" t="inlineStr"/>
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr"/>
+      <c r="L40" s="11" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N40" s="11" t="inlineStr"/>
+      <c r="O40" s="11" t="inlineStr"/>
+      <c r="P40" s="11" t="inlineStr"/>
+      <c r="Q40" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R40" s="11" t="inlineStr"/>
+      <c r="S40" s="11" t="inlineStr"/>
+      <c r="T40" s="11" t="inlineStr"/>
+      <c r="U40" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V40" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W40" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>20260313915</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr"/>
+      <c r="G41" s="11" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr"/>
+      <c r="I41" s="11" t="inlineStr"/>
+      <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr"/>
+      <c r="L41" s="11" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr"/>
+      <c r="O41" s="11" t="inlineStr"/>
+      <c r="P41" s="11" t="inlineStr"/>
+      <c r="Q41" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R41" s="11" t="inlineStr"/>
+      <c r="S41" s="11" t="inlineStr"/>
+      <c r="T41" s="11" t="inlineStr"/>
+      <c r="U41" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V41" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W41" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>20260314246</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr"/>
+      <c r="G42" s="11" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr"/>
+      <c r="I42" s="11" t="inlineStr"/>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr"/>
+      <c r="L42" s="11" t="inlineStr"/>
+      <c r="M42" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N42" s="11" t="inlineStr"/>
+      <c r="O42" s="11" t="inlineStr"/>
+      <c r="P42" s="11" t="inlineStr"/>
+      <c r="Q42" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R42" s="11" t="inlineStr"/>
+      <c r="S42" s="11" t="inlineStr"/>
+      <c r="T42" s="11" t="inlineStr"/>
+      <c r="U42" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V42" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W42" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>20260314523</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr"/>
+      <c r="G43" s="11" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr"/>
+      <c r="I43" s="11" t="inlineStr"/>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr"/>
+      <c r="L43" s="11" t="inlineStr"/>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr"/>
+      <c r="O43" s="11" t="inlineStr"/>
+      <c r="P43" s="11" t="inlineStr"/>
+      <c r="Q43" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R43" s="11" t="inlineStr"/>
+      <c r="S43" s="11" t="inlineStr"/>
+      <c r="T43" s="11" t="inlineStr"/>
+      <c r="U43" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V43" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W43" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>20260314861</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr"/>
+      <c r="G44" s="11" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr"/>
+      <c r="I44" s="11" t="inlineStr"/>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="inlineStr"/>
+      <c r="L44" s="11" t="inlineStr"/>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr"/>
+      <c r="O44" s="11" t="inlineStr"/>
+      <c r="P44" s="11" t="inlineStr"/>
+      <c r="Q44" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R44" s="11" t="inlineStr"/>
+      <c r="S44" s="11" t="inlineStr"/>
+      <c r="T44" s="11" t="inlineStr"/>
+      <c r="U44" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V44" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W44" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>20260315489</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr"/>
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr"/>
+      <c r="I45" s="11" t="inlineStr"/>
+      <c r="J45" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr"/>
+      <c r="L45" s="11" t="inlineStr"/>
+      <c r="M45" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N45" s="11" t="inlineStr"/>
+      <c r="O45" s="11" t="inlineStr"/>
+      <c r="P45" s="11" t="inlineStr"/>
+      <c r="Q45" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R45" s="11" t="inlineStr"/>
+      <c r="S45" s="11" t="inlineStr"/>
+      <c r="T45" s="11" t="inlineStr"/>
+      <c r="U45" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V45" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W45" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>20260315688</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr"/>
+      <c r="G46" s="11" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr"/>
+      <c r="I46" s="11" t="inlineStr"/>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>201 W JEFFERSON ST</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr"/>
+      <c r="L46" s="11" t="inlineStr"/>
+      <c r="M46" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N46" s="11" t="inlineStr"/>
+      <c r="O46" s="11" t="inlineStr"/>
+      <c r="P46" s="11" t="inlineStr"/>
+      <c r="Q46" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R46" s="11" t="inlineStr"/>
+      <c r="S46" s="11" t="inlineStr"/>
+      <c r="T46" s="11" t="inlineStr"/>
+      <c r="U46" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V46" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W46" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>20260315948</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr"/>
+      <c r="G47" s="11" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr"/>
+      <c r="I47" s="11" t="inlineStr"/>
+      <c r="J47" s="11" t="inlineStr"/>
+      <c r="K47" s="11" t="inlineStr"/>
+      <c r="L47" s="11" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N47" s="11" t="inlineStr"/>
+      <c r="O47" s="11" t="inlineStr"/>
+      <c r="P47" s="11" t="inlineStr"/>
+      <c r="Q47" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R47" s="11" t="inlineStr"/>
+      <c r="S47" s="11" t="inlineStr"/>
+      <c r="T47" s="11" t="inlineStr"/>
+      <c r="U47" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V47" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W47" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>20260315949</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr"/>
+      <c r="G48" s="11" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr"/>
+      <c r="I48" s="11" t="inlineStr"/>
+      <c r="J48" s="11" t="inlineStr"/>
+      <c r="K48" s="11" t="inlineStr"/>
+      <c r="L48" s="11" t="inlineStr"/>
+      <c r="M48" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N48" s="11" t="inlineStr"/>
+      <c r="O48" s="11" t="inlineStr"/>
+      <c r="P48" s="11" t="inlineStr"/>
+      <c r="Q48" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R48" s="11" t="inlineStr"/>
+      <c r="S48" s="11" t="inlineStr"/>
+      <c r="T48" s="11" t="inlineStr"/>
+      <c r="U48" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V48" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W48" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>20260315951</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr"/>
+      <c r="G49" s="11" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr"/>
+      <c r="I49" s="11" t="inlineStr"/>
+      <c r="J49" s="11" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr"/>
+      <c r="L49" s="11" t="inlineStr"/>
+      <c r="M49" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N49" s="11" t="inlineStr"/>
+      <c r="O49" s="11" t="inlineStr"/>
+      <c r="P49" s="11" t="inlineStr"/>
+      <c r="Q49" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R49" s="11" t="inlineStr"/>
+      <c r="S49" s="11" t="inlineStr"/>
+      <c r="T49" s="11" t="inlineStr"/>
+      <c r="U49" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V49" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W49" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>20260315952</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr"/>
+      <c r="G50" s="11" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr"/>
+      <c r="I50" s="11" t="inlineStr"/>
+      <c r="J50" s="11" t="inlineStr"/>
+      <c r="K50" s="11" t="inlineStr"/>
+      <c r="L50" s="11" t="inlineStr"/>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N50" s="11" t="inlineStr"/>
+      <c r="O50" s="11" t="inlineStr"/>
+      <c r="P50" s="11" t="inlineStr"/>
+      <c r="Q50" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R50" s="11" t="inlineStr"/>
+      <c r="S50" s="11" t="inlineStr"/>
+      <c r="T50" s="11" t="inlineStr"/>
+      <c r="U50" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V50" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W50" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>20260315953</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr"/>
+      <c r="H51" s="11" t="inlineStr"/>
+      <c r="I51" s="11" t="inlineStr"/>
+      <c r="J51" s="11" t="inlineStr"/>
+      <c r="K51" s="11" t="inlineStr"/>
+      <c r="L51" s="11" t="inlineStr"/>
+      <c r="M51" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N51" s="11" t="inlineStr"/>
+      <c r="O51" s="11" t="inlineStr"/>
+      <c r="P51" s="11" t="inlineStr"/>
+      <c r="Q51" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R51" s="11" t="inlineStr"/>
+      <c r="S51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr"/>
+      <c r="U51" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W51" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>20260315954</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr"/>
+      <c r="G52" s="11" t="inlineStr"/>
+      <c r="H52" s="11" t="inlineStr"/>
+      <c r="I52" s="11" t="inlineStr"/>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
+      <c r="L52" s="11" t="inlineStr"/>
+      <c r="M52" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N52" s="11" t="inlineStr"/>
+      <c r="O52" s="11" t="inlineStr"/>
+      <c r="P52" s="11" t="inlineStr"/>
+      <c r="Q52" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R52" s="11" t="inlineStr"/>
+      <c r="S52" s="11" t="inlineStr"/>
+      <c r="T52" s="11" t="inlineStr"/>
+      <c r="U52" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V52" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W52" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>20260315955</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr"/>
+      <c r="G53" s="11" t="inlineStr"/>
+      <c r="H53" s="11" t="inlineStr"/>
+      <c r="I53" s="11" t="inlineStr"/>
+      <c r="J53" s="11" t="inlineStr"/>
+      <c r="K53" s="11" t="inlineStr"/>
+      <c r="L53" s="11" t="inlineStr"/>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N53" s="11" t="inlineStr"/>
+      <c r="O53" s="11" t="inlineStr"/>
+      <c r="P53" s="11" t="inlineStr"/>
+      <c r="Q53" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R53" s="11" t="inlineStr"/>
+      <c r="S53" s="11" t="inlineStr"/>
+      <c r="T53" s="11" t="inlineStr"/>
+      <c r="U53" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V53" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W53" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>20260315956</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr"/>
+      <c r="G54" s="11" t="inlineStr"/>
+      <c r="H54" s="11" t="inlineStr"/>
+      <c r="I54" s="11" t="inlineStr"/>
+      <c r="J54" s="11" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr"/>
+      <c r="L54" s="11" t="inlineStr"/>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N54" s="11" t="inlineStr"/>
+      <c r="O54" s="11" t="inlineStr"/>
+      <c r="P54" s="11" t="inlineStr"/>
+      <c r="Q54" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R54" s="11" t="inlineStr"/>
+      <c r="S54" s="11" t="inlineStr"/>
+      <c r="T54" s="11" t="inlineStr"/>
+      <c r="U54" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V54" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W54" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>20260315957</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr"/>
+      <c r="G55" s="11" t="inlineStr"/>
+      <c r="H55" s="11" t="inlineStr"/>
+      <c r="I55" s="11" t="inlineStr"/>
+      <c r="J55" s="11" t="inlineStr"/>
+      <c r="K55" s="11" t="inlineStr"/>
+      <c r="L55" s="11" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N55" s="11" t="inlineStr"/>
+      <c r="O55" s="11" t="inlineStr"/>
+      <c r="P55" s="11" t="inlineStr"/>
+      <c r="Q55" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R55" s="11" t="inlineStr"/>
+      <c r="S55" s="11" t="inlineStr"/>
+      <c r="T55" s="11" t="inlineStr"/>
+      <c r="U55" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V55" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W55" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>20260315958</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr"/>
+      <c r="G56" s="11" t="inlineStr"/>
+      <c r="H56" s="11" t="inlineStr"/>
+      <c r="I56" s="11" t="inlineStr"/>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr"/>
+      <c r="L56" s="11" t="inlineStr"/>
+      <c r="M56" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N56" s="11" t="inlineStr"/>
+      <c r="O56" s="11" t="inlineStr"/>
+      <c r="P56" s="11" t="inlineStr"/>
+      <c r="Q56" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R56" s="11" t="inlineStr"/>
+      <c r="S56" s="11" t="inlineStr"/>
+      <c r="T56" s="11" t="inlineStr"/>
+      <c r="U56" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V56" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W56" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>20260315959</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr"/>
+      <c r="G57" s="11" t="inlineStr"/>
+      <c r="H57" s="11" t="inlineStr"/>
+      <c r="I57" s="11" t="inlineStr"/>
+      <c r="J57" s="11" t="inlineStr"/>
+      <c r="K57" s="11" t="inlineStr"/>
+      <c r="L57" s="11" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N57" s="11" t="inlineStr"/>
+      <c r="O57" s="11" t="inlineStr"/>
+      <c r="P57" s="11" t="inlineStr"/>
+      <c r="Q57" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R57" s="11" t="inlineStr"/>
+      <c r="S57" s="11" t="inlineStr"/>
+      <c r="T57" s="11" t="inlineStr"/>
+      <c r="U57" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V57" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W57" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>20260315960</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr"/>
+      <c r="G58" s="11" t="inlineStr"/>
+      <c r="H58" s="11" t="inlineStr"/>
+      <c r="I58" s="11" t="inlineStr"/>
+      <c r="J58" s="11" t="inlineStr"/>
+      <c r="K58" s="11" t="inlineStr"/>
+      <c r="L58" s="11" t="inlineStr"/>
+      <c r="M58" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N58" s="11" t="inlineStr"/>
+      <c r="O58" s="11" t="inlineStr"/>
+      <c r="P58" s="11" t="inlineStr"/>
+      <c r="Q58" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R58" s="11" t="inlineStr"/>
+      <c r="S58" s="11" t="inlineStr"/>
+      <c r="T58" s="11" t="inlineStr"/>
+      <c r="U58" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V58" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W58" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>20260316014</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr"/>
+      <c r="G59" s="11" t="inlineStr"/>
+      <c r="H59" s="11" t="inlineStr"/>
+      <c r="I59" s="11" t="inlineStr"/>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="inlineStr"/>
+      <c r="L59" s="11" t="inlineStr"/>
+      <c r="M59" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N59" s="11" t="inlineStr"/>
+      <c r="O59" s="11" t="inlineStr"/>
+      <c r="P59" s="11" t="inlineStr"/>
+      <c r="Q59" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R59" s="11" t="inlineStr"/>
+      <c r="S59" s="11" t="inlineStr"/>
+      <c r="T59" s="11" t="inlineStr"/>
+      <c r="U59" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V59" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W59" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>20260316152</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr"/>
+      <c r="G60" s="11" t="inlineStr"/>
+      <c r="H60" s="11" t="inlineStr"/>
+      <c r="I60" s="11" t="inlineStr"/>
+      <c r="J60" s="11" t="inlineStr"/>
+      <c r="K60" s="11" t="inlineStr"/>
+      <c r="L60" s="11" t="inlineStr"/>
+      <c r="M60" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N60" s="11" t="inlineStr"/>
+      <c r="O60" s="11" t="inlineStr"/>
+      <c r="P60" s="11" t="inlineStr"/>
+      <c r="Q60" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R60" s="11" t="inlineStr"/>
+      <c r="S60" s="11" t="inlineStr"/>
+      <c r="T60" s="11" t="inlineStr"/>
+      <c r="U60" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V60" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W60" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>20260316153</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr"/>
+      <c r="G61" s="11" t="inlineStr"/>
+      <c r="H61" s="11" t="inlineStr"/>
+      <c r="I61" s="11" t="inlineStr"/>
+      <c r="J61" s="11" t="inlineStr"/>
+      <c r="K61" s="11" t="inlineStr"/>
+      <c r="L61" s="11" t="inlineStr"/>
+      <c r="M61" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N61" s="11" t="inlineStr"/>
+      <c r="O61" s="11" t="inlineStr"/>
+      <c r="P61" s="11" t="inlineStr"/>
+      <c r="Q61" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R61" s="11" t="inlineStr"/>
+      <c r="S61" s="11" t="inlineStr"/>
+      <c r="T61" s="11" t="inlineStr"/>
+      <c r="U61" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V61" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W61" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>20260316154</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr"/>
+      <c r="G62" s="11" t="inlineStr"/>
+      <c r="H62" s="11" t="inlineStr"/>
+      <c r="I62" s="11" t="inlineStr"/>
+      <c r="J62" s="11" t="inlineStr"/>
+      <c r="K62" s="11" t="inlineStr"/>
+      <c r="L62" s="11" t="inlineStr"/>
+      <c r="M62" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N62" s="11" t="inlineStr"/>
+      <c r="O62" s="11" t="inlineStr"/>
+      <c r="P62" s="11" t="inlineStr"/>
+      <c r="Q62" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R62" s="11" t="inlineStr"/>
+      <c r="S62" s="11" t="inlineStr"/>
+      <c r="T62" s="11" t="inlineStr"/>
+      <c r="U62" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V62" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W62" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>20260316155</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr"/>
+      <c r="G63" s="11" t="inlineStr"/>
+      <c r="H63" s="11" t="inlineStr"/>
+      <c r="I63" s="11" t="inlineStr"/>
+      <c r="J63" s="11" t="inlineStr"/>
+      <c r="K63" s="11" t="inlineStr"/>
+      <c r="L63" s="11" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N63" s="11" t="inlineStr"/>
+      <c r="O63" s="11" t="inlineStr"/>
+      <c r="P63" s="11" t="inlineStr"/>
+      <c r="Q63" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R63" s="11" t="inlineStr"/>
+      <c r="S63" s="11" t="inlineStr"/>
+      <c r="T63" s="11" t="inlineStr"/>
+      <c r="U63" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V63" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W63" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>20260316156</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr"/>
+      <c r="G64" s="11" t="inlineStr"/>
+      <c r="H64" s="11" t="inlineStr"/>
+      <c r="I64" s="11" t="inlineStr"/>
+      <c r="J64" s="11" t="inlineStr"/>
+      <c r="K64" s="11" t="inlineStr"/>
+      <c r="L64" s="11" t="inlineStr"/>
+      <c r="M64" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N64" s="11" t="inlineStr"/>
+      <c r="O64" s="11" t="inlineStr"/>
+      <c r="P64" s="11" t="inlineStr"/>
+      <c r="Q64" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R64" s="11" t="inlineStr"/>
+      <c r="S64" s="11" t="inlineStr"/>
+      <c r="T64" s="11" t="inlineStr"/>
+      <c r="U64" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V64" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W64" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>20260316157</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr"/>
+      <c r="G65" s="11" t="inlineStr"/>
+      <c r="H65" s="11" t="inlineStr"/>
+      <c r="I65" s="11" t="inlineStr"/>
+      <c r="J65" s="11" t="inlineStr"/>
+      <c r="K65" s="11" t="inlineStr"/>
+      <c r="L65" s="11" t="inlineStr"/>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N65" s="11" t="inlineStr"/>
+      <c r="O65" s="11" t="inlineStr"/>
+      <c r="P65" s="11" t="inlineStr"/>
+      <c r="Q65" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R65" s="11" t="inlineStr"/>
+      <c r="S65" s="11" t="inlineStr"/>
+      <c r="T65" s="11" t="inlineStr"/>
+      <c r="U65" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V65" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W65" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>20260316158</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr"/>
+      <c r="G66" s="11" t="inlineStr"/>
+      <c r="H66" s="11" t="inlineStr"/>
+      <c r="I66" s="11" t="inlineStr"/>
+      <c r="J66" s="11" t="inlineStr"/>
+      <c r="K66" s="11" t="inlineStr"/>
+      <c r="L66" s="11" t="inlineStr"/>
+      <c r="M66" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N66" s="11" t="inlineStr"/>
+      <c r="O66" s="11" t="inlineStr"/>
+      <c r="P66" s="11" t="inlineStr"/>
+      <c r="Q66" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R66" s="11" t="inlineStr"/>
+      <c r="S66" s="11" t="inlineStr"/>
+      <c r="T66" s="11" t="inlineStr"/>
+      <c r="U66" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V66" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W66" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>20260316159</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr"/>
+      <c r="G67" s="11" t="inlineStr"/>
+      <c r="H67" s="11" t="inlineStr"/>
+      <c r="I67" s="11" t="inlineStr"/>
+      <c r="J67" s="11" t="inlineStr"/>
+      <c r="K67" s="11" t="inlineStr"/>
+      <c r="L67" s="11" t="inlineStr"/>
+      <c r="M67" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N67" s="11" t="inlineStr"/>
+      <c r="O67" s="11" t="inlineStr"/>
+      <c r="P67" s="11" t="inlineStr"/>
+      <c r="Q67" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R67" s="11" t="inlineStr"/>
+      <c r="S67" s="11" t="inlineStr"/>
+      <c r="T67" s="11" t="inlineStr"/>
+      <c r="U67" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V67" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W67" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>20260313833</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr"/>
+      <c r="G68" s="11" t="inlineStr"/>
+      <c r="H68" s="11" t="inlineStr"/>
+      <c r="I68" s="11" t="inlineStr"/>
+      <c r="J68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr"/>
+      <c r="L68" s="11" t="inlineStr"/>
+      <c r="M68" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N68" s="11" t="inlineStr"/>
+      <c r="O68" s="11" t="inlineStr"/>
+      <c r="P68" s="11" t="inlineStr"/>
+      <c r="Q68" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R68" s="11" t="inlineStr"/>
+      <c r="S68" s="11" t="inlineStr"/>
+      <c r="T68" s="11" t="inlineStr"/>
+      <c r="U68" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V68" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W68" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>20260314965</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr"/>
+      <c r="G69" s="11" t="inlineStr"/>
+      <c r="H69" s="11" t="inlineStr"/>
+      <c r="I69" s="11" t="inlineStr"/>
+      <c r="J69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr"/>
+      <c r="L69" s="11" t="inlineStr"/>
+      <c r="M69" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N69" s="11" t="inlineStr"/>
+      <c r="O69" s="11" t="inlineStr"/>
+      <c r="P69" s="11" t="inlineStr"/>
+      <c r="Q69" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R69" s="11" t="inlineStr"/>
+      <c r="S69" s="11" t="inlineStr">
+        <is>
+          <t>162-16-138</t>
+        </is>
+      </c>
+      <c r="T69" s="11" t="inlineStr"/>
+      <c r="U69" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V69" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W69" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>20260313672</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr"/>
+      <c r="G70" s="11" t="inlineStr"/>
+      <c r="H70" s="11" t="inlineStr"/>
+      <c r="I70" s="11" t="inlineStr"/>
+      <c r="J70" s="11" t="inlineStr"/>
+      <c r="K70" s="11" t="inlineStr"/>
+      <c r="L70" s="11" t="inlineStr"/>
+      <c r="M70" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N70" s="11" t="inlineStr"/>
+      <c r="O70" s="11" t="inlineStr"/>
+      <c r="P70" s="11" t="inlineStr"/>
+      <c r="Q70" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R70" s="11" t="inlineStr"/>
+      <c r="S70" s="11" t="inlineStr"/>
+      <c r="T70" s="11" t="inlineStr"/>
+      <c r="U70" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V70" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W70" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>20260313716</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr"/>
+      <c r="G71" s="11" t="inlineStr"/>
+      <c r="H71" s="11" t="inlineStr"/>
+      <c r="I71" s="11" t="inlineStr"/>
+      <c r="J71" s="11" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr"/>
+      <c r="L71" s="11" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N71" s="11" t="inlineStr"/>
+      <c r="O71" s="11" t="inlineStr"/>
+      <c r="P71" s="11" t="inlineStr"/>
+      <c r="Q71" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R71" s="11" t="inlineStr"/>
+      <c r="S71" s="11" t="inlineStr"/>
+      <c r="T71" s="11" t="inlineStr"/>
+      <c r="U71" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V71" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W71" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>20260314331</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr"/>
+      <c r="G72" s="11" t="inlineStr"/>
+      <c r="H72" s="11" t="inlineStr"/>
+      <c r="I72" s="11" t="inlineStr"/>
+      <c r="J72" s="11" t="inlineStr"/>
+      <c r="K72" s="11" t="inlineStr"/>
+      <c r="L72" s="11" t="inlineStr"/>
+      <c r="M72" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N72" s="11" t="inlineStr"/>
+      <c r="O72" s="11" t="inlineStr"/>
+      <c r="P72" s="11" t="inlineStr"/>
+      <c r="Q72" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R72" s="11" t="inlineStr"/>
+      <c r="S72" s="11" t="inlineStr"/>
+      <c r="T72" s="11" t="inlineStr"/>
+      <c r="U72" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V72" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W72" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>20260314420</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr"/>
+      <c r="G73" s="11" t="inlineStr"/>
+      <c r="H73" s="11" t="inlineStr"/>
+      <c r="I73" s="11" t="inlineStr"/>
+      <c r="J73" s="11" t="inlineStr"/>
+      <c r="K73" s="11" t="inlineStr"/>
+      <c r="L73" s="11" t="inlineStr"/>
+      <c r="M73" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N73" s="11" t="inlineStr"/>
+      <c r="O73" s="11" t="inlineStr"/>
+      <c r="P73" s="11" t="inlineStr"/>
+      <c r="Q73" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R73" s="11" t="inlineStr"/>
+      <c r="S73" s="11" t="inlineStr"/>
+      <c r="T73" s="11" t="inlineStr"/>
+      <c r="U73" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V73" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W73" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>20260314656</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr"/>
+      <c r="G74" s="11" t="inlineStr"/>
+      <c r="H74" s="11" t="inlineStr"/>
+      <c r="I74" s="11" t="inlineStr"/>
+      <c r="J74" s="11" t="inlineStr"/>
+      <c r="K74" s="11" t="inlineStr"/>
+      <c r="L74" s="11" t="inlineStr"/>
+      <c r="M74" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N74" s="11" t="inlineStr"/>
+      <c r="O74" s="11" t="inlineStr"/>
+      <c r="P74" s="11" t="inlineStr"/>
+      <c r="Q74" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R74" s="11" t="inlineStr"/>
+      <c r="S74" s="11" t="inlineStr"/>
+      <c r="T74" s="11" t="inlineStr"/>
+      <c r="U74" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V74" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W74" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
+      <c r="A75" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>20260314976</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr"/>
+      <c r="G75" s="11" t="inlineStr"/>
+      <c r="H75" s="11" t="inlineStr"/>
+      <c r="I75" s="11" t="inlineStr"/>
+      <c r="J75" s="11" t="inlineStr"/>
+      <c r="K75" s="11" t="inlineStr"/>
+      <c r="L75" s="11" t="inlineStr"/>
+      <c r="M75" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N75" s="11" t="inlineStr"/>
+      <c r="O75" s="11" t="inlineStr"/>
+      <c r="P75" s="11" t="inlineStr"/>
+      <c r="Q75" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R75" s="11" t="inlineStr"/>
+      <c r="S75" s="11" t="inlineStr"/>
+      <c r="T75" s="11" t="inlineStr"/>
+      <c r="U75" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V75" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W75" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>20260315450</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr"/>
+      <c r="G76" s="11" t="inlineStr"/>
+      <c r="H76" s="11" t="inlineStr"/>
+      <c r="I76" s="11" t="inlineStr"/>
+      <c r="J76" s="11" t="inlineStr"/>
+      <c r="K76" s="11" t="inlineStr"/>
+      <c r="L76" s="11" t="inlineStr"/>
+      <c r="M76" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N76" s="11" t="inlineStr"/>
+      <c r="O76" s="11" t="inlineStr"/>
+      <c r="P76" s="11" t="inlineStr"/>
+      <c r="Q76" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R76" s="11" t="inlineStr"/>
+      <c r="S76" s="11" t="inlineStr"/>
+      <c r="T76" s="11" t="inlineStr"/>
+      <c r="U76" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V76" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W76" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>20260315612</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr"/>
+      <c r="G77" s="11" t="inlineStr"/>
+      <c r="H77" s="11" t="inlineStr"/>
+      <c r="I77" s="11" t="inlineStr"/>
+      <c r="J77" s="11" t="inlineStr"/>
+      <c r="K77" s="11" t="inlineStr"/>
+      <c r="L77" s="11" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N77" s="11" t="inlineStr"/>
+      <c r="O77" s="11" t="inlineStr"/>
+      <c r="P77" s="11" t="inlineStr"/>
+      <c r="Q77" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R77" s="11" t="inlineStr"/>
+      <c r="S77" s="11" t="inlineStr"/>
+      <c r="T77" s="11" t="inlineStr"/>
+      <c r="U77" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V77" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W77" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>20260314111</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr"/>
+      <c r="G78" s="11" t="inlineStr"/>
+      <c r="H78" s="11" t="inlineStr"/>
+      <c r="I78" s="11" t="inlineStr"/>
+      <c r="J78" s="11" t="inlineStr"/>
+      <c r="K78" s="11" t="inlineStr"/>
+      <c r="L78" s="11" t="inlineStr"/>
+      <c r="M78" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N78" s="11" t="inlineStr"/>
+      <c r="O78" s="11" t="inlineStr"/>
+      <c r="P78" s="11" t="inlineStr"/>
+      <c r="Q78" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R78" s="11" t="inlineStr"/>
+      <c r="S78" s="11" t="inlineStr"/>
+      <c r="T78" s="11" t="inlineStr"/>
+      <c r="U78" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V78" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W78" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="26" customHeight="1">
+      <c r="A79" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>20260314571</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr"/>
+      <c r="G79" s="11" t="inlineStr"/>
+      <c r="H79" s="11" t="inlineStr"/>
+      <c r="I79" s="11" t="inlineStr"/>
+      <c r="J79" s="11" t="inlineStr"/>
+      <c r="K79" s="11" t="inlineStr"/>
+      <c r="L79" s="11" t="inlineStr"/>
+      <c r="M79" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N79" s="11" t="inlineStr"/>
+      <c r="O79" s="11" t="inlineStr"/>
+      <c r="P79" s="11" t="inlineStr"/>
+      <c r="Q79" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R79" s="11" t="inlineStr"/>
+      <c r="S79" s="11" t="inlineStr"/>
+      <c r="T79" s="11" t="inlineStr"/>
+      <c r="U79" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V79" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W79" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="26" customHeight="1">
+      <c r="A80" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>20260314615</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr"/>
+      <c r="G80" s="11" t="inlineStr"/>
+      <c r="H80" s="11" t="inlineStr"/>
+      <c r="I80" s="11" t="inlineStr"/>
+      <c r="J80" s="11" t="inlineStr"/>
+      <c r="K80" s="11" t="inlineStr"/>
+      <c r="L80" s="11" t="inlineStr"/>
+      <c r="M80" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N80" s="11" t="inlineStr"/>
+      <c r="O80" s="11" t="inlineStr"/>
+      <c r="P80" s="11" t="inlineStr"/>
+      <c r="Q80" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R80" s="11" t="inlineStr"/>
+      <c r="S80" s="11" t="inlineStr"/>
+      <c r="T80" s="11" t="inlineStr"/>
+      <c r="U80" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V80" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W80" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>20260314803</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr"/>
+      <c r="G81" s="11" t="inlineStr"/>
+      <c r="H81" s="11" t="inlineStr"/>
+      <c r="I81" s="11" t="inlineStr"/>
+      <c r="J81" s="11" t="inlineStr"/>
+      <c r="K81" s="11" t="inlineStr"/>
+      <c r="L81" s="11" t="inlineStr"/>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N81" s="11" t="inlineStr"/>
+      <c r="O81" s="11" t="inlineStr"/>
+      <c r="P81" s="11" t="inlineStr"/>
+      <c r="Q81" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R81" s="11" t="inlineStr"/>
+      <c r="S81" s="11" t="inlineStr"/>
+      <c r="T81" s="11" t="inlineStr"/>
+      <c r="U81" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V81" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W81" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="26" customHeight="1">
+      <c r="A82" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>20260314895</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="inlineStr"/>
+      <c r="G82" s="11" t="inlineStr"/>
+      <c r="H82" s="11" t="inlineStr"/>
+      <c r="I82" s="11" t="inlineStr"/>
+      <c r="J82" s="11" t="inlineStr"/>
+      <c r="K82" s="11" t="inlineStr"/>
+      <c r="L82" s="11" t="inlineStr"/>
+      <c r="M82" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N82" s="11" t="inlineStr"/>
+      <c r="O82" s="11" t="inlineStr"/>
+      <c r="P82" s="11" t="inlineStr"/>
+      <c r="Q82" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R82" s="11" t="inlineStr"/>
+      <c r="S82" s="11" t="inlineStr"/>
+      <c r="T82" s="11" t="inlineStr"/>
+      <c r="U82" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V82" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W82" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>20260315053</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr"/>
+      <c r="G83" s="11" t="inlineStr"/>
+      <c r="H83" s="11" t="inlineStr"/>
+      <c r="I83" s="11" t="inlineStr"/>
+      <c r="J83" s="11" t="inlineStr"/>
+      <c r="K83" s="11" t="inlineStr"/>
+      <c r="L83" s="11" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N83" s="11" t="inlineStr"/>
+      <c r="O83" s="11" t="inlineStr"/>
+      <c r="P83" s="11" t="inlineStr"/>
+      <c r="Q83" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R83" s="11" t="inlineStr"/>
+      <c r="S83" s="11" t="inlineStr"/>
+      <c r="T83" s="11" t="inlineStr"/>
+      <c r="U83" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V83" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W83" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>20260315563</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="inlineStr"/>
+      <c r="G84" s="11" t="inlineStr"/>
+      <c r="H84" s="11" t="inlineStr"/>
+      <c r="I84" s="11" t="inlineStr"/>
+      <c r="J84" s="11" t="inlineStr"/>
+      <c r="K84" s="11" t="inlineStr"/>
+      <c r="L84" s="11" t="inlineStr"/>
+      <c r="M84" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N84" s="11" t="inlineStr"/>
+      <c r="O84" s="11" t="inlineStr"/>
+      <c r="P84" s="11" t="inlineStr"/>
+      <c r="Q84" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R84" s="11" t="inlineStr"/>
+      <c r="S84" s="11" t="inlineStr"/>
+      <c r="T84" s="11" t="inlineStr"/>
+      <c r="U84" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V84" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W84" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>20260315728</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr"/>
+      <c r="G85" s="11" t="inlineStr"/>
+      <c r="H85" s="11" t="inlineStr"/>
+      <c r="I85" s="11" t="inlineStr"/>
+      <c r="J85" s="11" t="inlineStr"/>
+      <c r="K85" s="11" t="inlineStr"/>
+      <c r="L85" s="11" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N85" s="11" t="inlineStr"/>
+      <c r="O85" s="11" t="inlineStr"/>
+      <c r="P85" s="11" t="inlineStr"/>
+      <c r="Q85" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R85" s="11" t="inlineStr"/>
+      <c r="S85" s="11" t="inlineStr"/>
+      <c r="T85" s="11" t="inlineStr"/>
+      <c r="U85" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V85" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W85" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>20260316183</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>2026-05-26</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="inlineStr"/>
+      <c r="G86" s="11" t="inlineStr"/>
+      <c r="H86" s="11" t="inlineStr"/>
+      <c r="I86" s="11" t="inlineStr"/>
+      <c r="J86" s="11" t="inlineStr"/>
+      <c r="K86" s="11" t="inlineStr"/>
+      <c r="L86" s="11" t="inlineStr"/>
+      <c r="M86" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N86" s="11" t="inlineStr"/>
+      <c r="O86" s="11" t="inlineStr"/>
+      <c r="P86" s="11" t="inlineStr"/>
+      <c r="Q86" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R86" s="11" t="inlineStr"/>
+      <c r="S86" s="11" t="inlineStr"/>
+      <c r="T86" s="11" t="inlineStr"/>
+      <c r="U86" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V86" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W86" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="26" customHeight="1">
+      <c r="A87" s="10" t="n">
+        <v>43</v>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>20260316160</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr"/>
+      <c r="F87" s="11" t="inlineStr"/>
+      <c r="G87" s="11" t="inlineStr"/>
+      <c r="H87" s="11" t="inlineStr"/>
+      <c r="I87" s="11" t="inlineStr"/>
+      <c r="J87" s="11" t="inlineStr"/>
+      <c r="K87" s="11" t="inlineStr"/>
+      <c r="L87" s="11" t="inlineStr"/>
+      <c r="M87" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N87" s="11" t="inlineStr"/>
+      <c r="O87" s="11" t="inlineStr"/>
+      <c r="P87" s="11" t="inlineStr"/>
+      <c r="Q87" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R87" s="11" t="inlineStr"/>
+      <c r="S87" s="11" t="inlineStr"/>
+      <c r="T87" s="11" t="inlineStr"/>
+      <c r="U87" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien</t>
+        </is>
+      </c>
+      <c r="V87" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W87" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:W87"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W87" r:id="rId86"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -618,7 +7027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -626,7 +7035,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Maricopa County Motivated Seller Leads</t>
         </is>
@@ -635,88 +7044,138 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-05-26 05:00</t>
+          <t>Run: 2026-05-27 05:20</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="A3" s="14" t="inlineStr"/>
+      <c r="B3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Total Leads</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="14" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>With Property Address</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>With Mailing Address</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>With Property Address</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>With Mailing Address</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>PDF Parsed</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
+      <c r="B7" s="14" t="n">
+        <v>69</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Score 70+ (Hot)</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
+      <c r="B8" s="14" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Score 50-69 (Warm)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
+      <c r="B9" s="14" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="A10" s="14" t="inlineStr"/>
+      <c r="B10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>By Category</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-05-31 05:20</t>
+          <t>Run: 2026-06-01 05:58</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$216</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$203</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W216"/>
+  <dimension ref="A1:W203"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -705,40 +705,40 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>20260337972</t>
+          <t>20260340026</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>LAP TAN TRAN AKA LAP T TRAN</t>
+          <t>TRATERRIAOR GENENND ELAM</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>BANK OF AMERICA, N.A.</t>
+          <t>SALUDA GRADE INCOME FUND I</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>189900</v>
+        <v>400000</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>SUPERIOR COURT BUILDING</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>3732 E DEL RIO ST</t>
+          <t>4543 S ROY ROGERS WAY</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>85295</t>
+          <t>85297</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
@@ -764,14 +764,10 @@
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr"/>
-      <c r="S2" s="3" t="inlineStr">
-        <is>
-          <t>304-39-323</t>
-        </is>
-      </c>
+      <c r="S2" s="3" t="inlineStr"/>
       <c r="T2" s="3" t="inlineStr">
         <is>
-          <t>MTC Financial Inc. dba Trustee Corps</t>
+          <t>Prime Recon LLC</t>
         </is>
       </c>
       <c r="U2" s="3" t="inlineStr">
@@ -806,49 +802,57 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>20260338309</t>
+          <t>20260340288</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>Hector Arturo Arzaga</t>
+          <t>EMMETT H. SPENCER, JR., AND UNMARRIED MAN</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>U.S. Bank National Association Leonard J. McDonald</t>
+          <t>ROCKET MORTGAGE, LLC</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>176739</v>
+        <v>204517</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>1942 South Emerson Unit 119</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>9428 S LEILA LN</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N3" s="3" t="inlineStr"/>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
+          <t>85041</t>
+        </is>
+      </c>
       <c r="O3" s="3" t="inlineStr"/>
       <c r="P3" s="3" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
@@ -859,12 +863,12 @@
       <c r="R3" s="3" t="inlineStr"/>
       <c r="S3" s="3" t="inlineStr">
         <is>
-          <t>134-26-547</t>
+          <t>300-62-0762</t>
         </is>
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>U.S. Bank National Association Leonard J. McDonald</t>
+          <t>America West Lender Services, LLC</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -899,32 +903,40 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>20260338555</t>
+          <t>20260341371</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Danino Capital Properties LLC</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr"/>
+          <t>Rosa Alcantar-Gastelum</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>U.S. Bank National Association Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="H4" s="4" t="n">
-        <v>317500</v>
-      </c>
-      <c r="I4" s="3" t="inlineStr"/>
+        <v>183612</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>25611 W Satellite Ln</t>
+          <t>6412 S. Montezuma St</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr"/>
@@ -944,17 +956,17 @@
       <c r="R4" s="3" t="inlineStr"/>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t>504-40-198</t>
+          <t>114-05-1582</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Joseph G. Urtuzuastegui III</t>
+          <t>U.S. Bank National Association Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
@@ -984,36 +996,40 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>20260338963</t>
+          <t>20260341405</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>Aarette LLC, an Arizona limited liability company</t>
+          <t>Angela V Davis</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Arizona Capital Source</t>
+          <t>V.I.P. Mortgage, Inc. Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>305500</v>
+        <v>441849</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr"/>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>3022 North 17" Avenue</t>
+          <t>17497 W Hadley St</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr"/>
@@ -1033,13 +1049,17 @@
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>110-33-025</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr"/>
+          <t>502-39-6821</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>V.I.P. Mortgage, Inc. Leonard J. McDonald</t>
+        </is>
+      </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
@@ -1069,49 +1089,57 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>20260339183</t>
+          <t>20260341410</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Kelly Shoemaker</t>
+          <t>Sanjiv Mehra</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Rocket Mortgage, LLC f/k/a Quicken Loans, LLC Leonard J. McDonald</t>
+          <t>Stonegate Management, LLC, a Delaware limited liability company</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>208180</v>
+        <v>1015000</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>4509 W Cochise Dr</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>5329 E. Grovers Avenue</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>Scottsdale</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>85254</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
@@ -1122,12 +1150,12 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>148-06-0734</t>
+          <t>215-11-155</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Rocket Mortgage, LLC f/k/a Quicken Loans, LLC Leonard J. McDonald</t>
+          <t>Christopher R. Perry, Esq.</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1162,26 +1190,26 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>20260339194</t>
+          <t>20260341451</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Shawn C. Souza and Amy T. Souza</t>
+          <t>Ben C. Valenzuela and Josefina C. Valenzuela</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Rocket Mortgage, LLC f/k/a Quicken Loans, LLC Leonard J. McDonald</t>
+          <t>Wells Fargo 2007-OSI Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>297000</v>
+        <v>225000</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -1195,7 +1223,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>9594 W Quail Ave</t>
+          <t>1816 N 68th Dr</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
@@ -1215,12 +1243,12 @@
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>200-12-8589</t>
+          <t>102-76-4019</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Rocket Mortgage, LLC f/k/a Quicken Loans, LLC Leonard J. McDonald</t>
+          <t>Wells Fargo 2007-OSI Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1255,30 +1283,30 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>20260339343</t>
+          <t>20260341629</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>FRANCISCO J DORAME LOPEZ AND ANGELIA A VALLE</t>
+          <t>OSVALDO A QUINTERO COTA AND LEONDRA S ROJAS</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Freedom Mortgage Corporation</t>
+          <t>Lakeview Loan Servicing, LLC, By LoanCare, LLC, As Attorney In Fact Under A Limited Power of</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>387845</v>
+        <v>280328</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1288,24 +1316,16 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>3511 W Portland St</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
+          <t>6024 S 20TH AVENUE</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
       <c r="M8" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>85009</t>
-        </is>
-      </c>
+      <c r="N8" s="3" t="inlineStr"/>
       <c r="O8" s="3" t="inlineStr"/>
       <c r="P8" s="3" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
@@ -1316,12 +1336,12 @@
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>153-12-15092</t>
+          <t>105-85-273</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Kim Quam, a member of the State Bar of Arizona</t>
+          <t>Erin K. Sweeney, a member of the State Bar of Arizona</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1356,57 +1376,49 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>20260339389</t>
+          <t>20260341838</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>CHAD EWART</t>
+          <t>Megan Astraus and Nicholas Astraus</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>PennyMac Loan Services, LLC</t>
+          <t>Rocket Mortgage, LLC Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>342000</v>
+        <v>378000</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>8531 EAST CHAPARRAL ROAD</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>SCOTTSDALE</t>
-        </is>
-      </c>
+          <t>29633 N 120th Ln</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
       <c r="M9" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>85250</t>
-        </is>
-      </c>
+      <c r="N9" s="3" t="inlineStr"/>
       <c r="O9" s="3" t="inlineStr"/>
       <c r="P9" s="3" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr">
@@ -1417,12 +1429,12 @@
       <c r="R9" s="3" t="inlineStr"/>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t>173-62-117</t>
+          <t>501-01-4875</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>MTC Financial Inc. dba Trustee Corps</t>
+          <t>Rocket Mortgage, LLC Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1457,40 +1469,40 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>20260339435</t>
+          <t>20260342253</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>KIERSTYN C. HUNT</t>
+          <t>Frank L. Iversen</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>Planet Home Lending LLC</t>
+          <t>Desert Financial Credit Union Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>384615</v>
+        <v>130950</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>14830 W WATSON LN</t>
+          <t>3065 West Sunnyside Drive</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr"/>
@@ -1510,12 +1522,12 @@
       <c r="R10" s="3" t="inlineStr"/>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t>509-02-3165</t>
+          <t>149-20-1465</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>Erin K. Sweeney, a member of the State Bar of Arizona</t>
+          <t>Desert Financial Credit Union Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1550,57 +1562,45 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>20260339556</t>
+          <t>20260342260</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>SAUL H. RODRIGUEZ</t>
+          <t>Kim Cam Tu Nguyen and Loc Huu Nguyen</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>U.S. BANK NATIONAL ASSOCIATION, AS TRUSTEE FOR STRUCTURED ASSET</t>
+          <t>Desert Financial Credit Union Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>139500</v>
+        <v>147400</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
-        </is>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr"/>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>12018 N 113TH DR</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>YOUNGTOWN</t>
-        </is>
-      </c>
+          <t>7655 N 23rd Ave</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr"/>
       <c r="M11" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t>85363</t>
-        </is>
-      </c>
+      <c r="N11" s="3" t="inlineStr"/>
       <c r="O11" s="3" t="inlineStr"/>
       <c r="P11" s="3" t="inlineStr"/>
       <c r="Q11" s="3" t="inlineStr">
@@ -1609,10 +1609,14 @@
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>157-22-001</t>
+        </is>
+      </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>Prime Recon LLC</t>
+          <t>Desert Financial Credit Union Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
@@ -1647,57 +1651,45 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>20260339569</t>
+          <t>20260342288</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>SCOTT ALAN DUNCAN AND CHRISTY ELAINE DUNCAN</t>
+          <t>Nicholas Cameron</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>NEWREZ LLC</t>
+          <t>Sunflower Bank, N.A. Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>723238</v>
+        <v>286150</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT BUILDING</t>
-        </is>
-      </c>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr"/>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>13473 W ROY ROGERS RD</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t>PEORIA</t>
-        </is>
-      </c>
+          <t>8424 N 33rd Dr</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr"/>
       <c r="M12" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t>85383</t>
-        </is>
-      </c>
+      <c r="N12" s="3" t="inlineStr"/>
       <c r="O12" s="3" t="inlineStr"/>
       <c r="P12" s="3" t="inlineStr"/>
       <c r="Q12" s="3" t="inlineStr">
@@ -1706,10 +1698,14 @@
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>150-09-0706</t>
+        </is>
+      </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>Prime Recon LLC</t>
+          <t>Sunflower Bank, N.A. Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
@@ -1744,57 +1740,45 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>20260339601</t>
+          <t>20260342471</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>EVELYN MARTINEZ</t>
+          <t>Georgina Saldana</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>PennyMac Loan Services, LLC</t>
+          <t>Desert Financial Credit Union Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>216750</v>
+        <v>156000</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr"/>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>4027 W RUTH AVE</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
+          <t>1828 E Alicia Dr</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
       <c r="M13" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>85051</t>
-        </is>
-      </c>
+      <c r="N13" s="3" t="inlineStr"/>
       <c r="O13" s="3" t="inlineStr"/>
       <c r="P13" s="3" t="inlineStr"/>
       <c r="Q13" s="3" t="inlineStr">
@@ -1805,12 +1789,12 @@
       <c r="R13" s="3" t="inlineStr"/>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t>150-14-227</t>
+          <t>301-33-1935</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>MTC Financial Inc. dba Trustee Corps</t>
+          <t>Desert Financial Credit Union Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
@@ -1845,27 +1829,35 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>20260338719</t>
+          <t>20260340030</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr"/>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>SYDNEY JANE HILL</t>
+        </is>
+      </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>C/O loanDepot.com, LLC</t>
+          <t>U.S. BANK NATIONAL ASSOCIATION</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>113500</v>
-      </c>
-      <c r="I14" s="7" t="inlineStr"/>
+        <v>421722</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Superior Courts Building. Maricopa County</t>
+          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
         </is>
       </c>
       <c r="K14" s="7" t="inlineStr"/>
@@ -1884,12 +1876,12 @@
         </is>
       </c>
       <c r="R14" s="7" t="inlineStr"/>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>136-26-743</t>
-        </is>
-      </c>
-      <c r="T14" s="7" t="inlineStr"/>
+      <c r="S14" s="7" t="inlineStr"/>
+      <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>Prime Recon LLC</t>
+        </is>
+      </c>
       <c r="U14" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -1922,27 +1914,31 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>20260338721</t>
+          <t>20260340031</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>C/O M&amp;T Bank</t>
+          <t>U.S. BANK NATIONAL ASSOCIATION</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>281840</v>
-      </c>
-      <c r="I15" s="7" t="inlineStr"/>
+        <v>375457</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Superior Courts Building. Maricopa County</t>
+          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY</t>
         </is>
       </c>
       <c r="K15" s="7" t="inlineStr"/>
@@ -1961,12 +1957,12 @@
         </is>
       </c>
       <c r="R15" s="7" t="inlineStr"/>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>104-55-7179</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr"/>
+      <c r="S15" s="7" t="inlineStr"/>
+      <c r="T15" s="7" t="inlineStr">
+        <is>
+          <t>Prime Recon LLC</t>
+        </is>
+      </c>
       <c r="U15" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -1999,38 +1995,38 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>20260339196</t>
+          <t>20260340055</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>Jordan L. Delgadillo</t>
+          <t>Patricia Soule</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>PennyMac Loan Services, LLC Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>83500</v>
+        <v>275500</v>
       </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="J16" s="7" t="inlineStr"/>
-      <c r="K16" s="7" t="inlineStr">
-        <is>
-          <t>1196 E Julian Dr</t>
-        </is>
-      </c>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr"/>
       <c r="L16" s="7" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr">
         <is>
@@ -2048,12 +2044,12 @@
       <c r="R16" s="7" t="inlineStr"/>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>304-46-0757</t>
+          <t>200-94-2602</t>
         </is>
       </c>
       <c r="T16" s="7" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>PennyMac Loan Services, LLC Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U16" s="7" t="inlineStr">
@@ -2074,7 +2070,7 @@
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -2088,49 +2084,43 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>20260339394</t>
+          <t>20260341486</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="8" t="n">
-        <v>60000</v>
-      </c>
-      <c r="I17" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>JONATHAN THOMPSON AND LEKEISHA THOMPSON</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>SAILFISH SERVICING, LLC</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr"/>
+      <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>SUPERIOR COURT BUILDING</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
         <is>
-          <t>1913 W. Georgia Ave.</t>
-        </is>
-      </c>
-      <c r="L17" s="7" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
+          <t>6030 N 15TH ST 9</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N17" s="7" t="inlineStr">
-        <is>
-          <t>85015</t>
-        </is>
-      </c>
+      <c r="N17" s="7" t="inlineStr"/>
       <c r="O17" s="7" t="inlineStr"/>
       <c r="P17" s="7" t="inlineStr"/>
       <c r="Q17" s="7" t="inlineStr">
@@ -2141,10 +2131,14 @@
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>153-23-063</t>
-        </is>
-      </c>
-      <c r="T17" s="7" t="inlineStr"/>
+          <t>161-10-123</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
       <c r="U17" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2163,7 +2157,7 @@
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="6" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -2177,30 +2171,36 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>20260339557</t>
+          <t>20260341503</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr"/>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>THOMAS C. MCGRATH</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>C/O Onity Mortgage</t>
-        </is>
-      </c>
-      <c r="H18" s="8" t="n">
-        <v>287900</v>
-      </c>
+          <t>ROCKET MORTGAGE, LLC</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="7" t="inlineStr"/>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Superior Courts Building. Maricopa County</t>
-        </is>
-      </c>
-      <c r="K18" s="7" t="inlineStr"/>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>3518 W BERYL AVE</t>
+        </is>
+      </c>
       <c r="L18" s="7" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr">
         <is>
@@ -2218,10 +2218,14 @@
       <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>312-08-704</t>
-        </is>
-      </c>
-      <c r="T18" s="7" t="inlineStr"/>
+          <t>149-36-038</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
       <c r="U18" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2240,7 +2244,7 @@
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -2254,26 +2258,36 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>20260339725</t>
+          <t>20260341523</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="8" t="n">
-        <v>1198500</v>
-      </c>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>MATTHEW ADICKES AND CHRISTINE ADICKES</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>PNC BANK, NATIONAL ASSOCIATION</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING AT 201 W JEFFERSON</t>
-        </is>
-      </c>
-      <c r="K19" s="7" t="inlineStr"/>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>3012 W HORSHAM DR</t>
+        </is>
+      </c>
       <c r="L19" s="7" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr">
         <is>
@@ -2291,10 +2305,14 @@
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>167-03-181</t>
-        </is>
-      </c>
-      <c r="T19" s="7" t="inlineStr"/>
+          <t>206-41-245</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
       <c r="U19" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2327,34 +2345,34 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>20260338688</t>
+          <t>20260341650</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>DAWN ALISA MILLER</t>
+          <t>SALLY KILLEEN</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>ROCKET MORTGAGE, LLC</t>
+          <t>FINANCE OF AMERICA REVERSE LLC</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr"/>
       <c r="I20" s="7" t="inlineStr"/>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Maricopa County Courthouse</t>
+          <t>SUPERIOR COURT BUILDING</t>
         </is>
       </c>
       <c r="K20" s="7" t="inlineStr">
         <is>
-          <t>15833 W DURANGO ST</t>
+          <t>2006 S PLAYA</t>
         </is>
       </c>
       <c r="L20" s="7" t="inlineStr"/>
@@ -2374,7 +2392,7 @@
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>500-06-376</t>
+          <t>305-10-032</t>
         </is>
       </c>
       <c r="T20" s="7" t="inlineStr">
@@ -2414,40 +2432,34 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>20260339278</t>
+          <t>20260341717</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Thomas Duke and Sarah Hernandez aka Sarah F. Duke</t>
+          <t>KIMBERLY PANTASTICO</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>20000</v>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
+          <t>LENNAR MORTGAGE, LLC</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>SUPERIOR COURT BUILDING</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>43790 W Cahill Dr</t>
+          <t>21004 E ESTRELLA RD</t>
         </is>
       </c>
       <c r="L21" s="7" t="inlineStr"/>
@@ -2467,12 +2479,12 @@
       <c r="R21" s="7" t="inlineStr"/>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>512-22-15006</t>
+          <t>304-62-518</t>
         </is>
       </c>
       <c r="T21" s="7" t="inlineStr">
         <is>
-          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+          <t>Clear Recon Corp</t>
         </is>
       </c>
       <c r="U21" s="7" t="inlineStr">
@@ -2507,12 +2519,12 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>20260336844</t>
+          <t>20260341428</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F22" s="11" t="inlineStr"/>
@@ -2521,7 +2533,7 @@
       <c r="I22" s="11" t="inlineStr"/>
       <c r="J22" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr"/>
@@ -2540,11 +2552,7 @@
         </is>
       </c>
       <c r="R22" s="11" t="inlineStr"/>
-      <c r="S22" s="11" t="inlineStr">
-        <is>
-          <t>301-84-210</t>
-        </is>
-      </c>
+      <c r="S22" s="11" t="inlineStr"/>
       <c r="T22" s="11" t="inlineStr"/>
       <c r="U22" s="11" t="inlineStr">
         <is>
@@ -2578,12 +2586,12 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>20260337784</t>
+          <t>20260341439</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr"/>
@@ -2592,7 +2600,7 @@
       <c r="I23" s="11" t="inlineStr"/>
       <c r="J23" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr"/>
@@ -2635,33 +2643,29 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>20260338512</t>
+          <t>20260342048</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr"/>
       <c r="G24" s="11" t="inlineStr"/>
       <c r="H24" s="11" t="inlineStr"/>
       <c r="I24" s="11" t="inlineStr"/>
-      <c r="J24" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J24" s="11" t="inlineStr"/>
       <c r="K24" s="11" t="inlineStr"/>
       <c r="L24" s="11" t="inlineStr"/>
       <c r="M24" s="11" t="inlineStr">
@@ -2682,7 +2686,7 @@
       <c r="T24" s="11" t="inlineStr"/>
       <c r="U24" s="11" t="inlineStr">
         <is>
-          <t>Lis pendens; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V24" s="11" t="inlineStr">
@@ -2702,22 +2706,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>20260338691</t>
+          <t>20260342307</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr"/>
@@ -2726,7 +2730,7 @@
       <c r="I25" s="11" t="inlineStr"/>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>SUPERIOR COURT OF ARIZONA</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr"/>
@@ -2749,7 +2753,7 @@
       <c r="T25" s="11" t="inlineStr"/>
       <c r="U25" s="11" t="inlineStr">
         <is>
-          <t>Lis pendens; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V25" s="11" t="inlineStr">
@@ -2769,22 +2773,22 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>20260338982</t>
+          <t>20260342308</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr"/>
@@ -2793,7 +2797,7 @@
       <c r="I26" s="11" t="inlineStr"/>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>SUPERIOR COURT OF ARIZONA</t>
         </is>
       </c>
       <c r="K26" s="11" t="inlineStr"/>
@@ -2816,7 +2820,7 @@
       <c r="T26" s="11" t="inlineStr"/>
       <c r="U26" s="11" t="inlineStr">
         <is>
-          <t>Lis pendens; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V26" s="11" t="inlineStr">
@@ -2836,22 +2840,22 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>LP</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>20260339726</t>
+          <t>20260342309</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr"/>
@@ -2860,7 +2864,7 @@
       <c r="I27" s="11" t="inlineStr"/>
       <c r="J27" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>SUPERIOR COURT OF ARIZONA</t>
         </is>
       </c>
       <c r="K27" s="11" t="inlineStr"/>
@@ -2883,7 +2887,7 @@
       <c r="T27" s="11" t="inlineStr"/>
       <c r="U27" s="11" t="inlineStr">
         <is>
-          <t>Lis pendens; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr">
@@ -2903,29 +2907,33 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>20260338362</t>
+          <t>20260342310</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
       <c r="G28" s="11" t="inlineStr"/>
       <c r="H28" s="11" t="inlineStr"/>
       <c r="I28" s="11" t="inlineStr"/>
-      <c r="J28" s="11" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K28" s="11" t="inlineStr"/>
       <c r="L28" s="11" t="inlineStr"/>
       <c r="M28" s="11" t="inlineStr">
@@ -2946,7 +2954,7 @@
       <c r="T28" s="11" t="inlineStr"/>
       <c r="U28" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V28" s="11" t="inlineStr">
@@ -2966,29 +2974,33 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>20260338363</t>
+          <t>20260342311</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr"/>
       <c r="G29" s="11" t="inlineStr"/>
       <c r="H29" s="11" t="inlineStr"/>
       <c r="I29" s="11" t="inlineStr"/>
-      <c r="J29" s="11" t="inlineStr"/>
+      <c r="J29" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K29" s="11" t="inlineStr"/>
       <c r="L29" s="11" t="inlineStr"/>
       <c r="M29" s="11" t="inlineStr">
@@ -3009,7 +3021,7 @@
       <c r="T29" s="11" t="inlineStr"/>
       <c r="U29" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V29" s="11" t="inlineStr">
@@ -3029,29 +3041,33 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>20260338364</t>
+          <t>20260342312</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr"/>
       <c r="G30" s="11" t="inlineStr"/>
       <c r="H30" s="11" t="inlineStr"/>
       <c r="I30" s="11" t="inlineStr"/>
-      <c r="J30" s="11" t="inlineStr"/>
+      <c r="J30" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
       <c r="K30" s="11" t="inlineStr"/>
       <c r="L30" s="11" t="inlineStr"/>
       <c r="M30" s="11" t="inlineStr">
@@ -3072,7 +3088,7 @@
       <c r="T30" s="11" t="inlineStr"/>
       <c r="U30" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V30" s="11" t="inlineStr">
@@ -3092,29 +3108,33 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>20260338365</t>
+          <t>20260342313</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
       <c r="G31" s="11" t="inlineStr"/>
       <c r="H31" s="11" t="inlineStr"/>
       <c r="I31" s="11" t="inlineStr"/>
-      <c r="J31" s="11" t="inlineStr"/>
+      <c r="J31" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
       <c r="K31" s="11" t="inlineStr"/>
       <c r="L31" s="11" t="inlineStr"/>
       <c r="M31" s="11" t="inlineStr">
@@ -3135,7 +3155,7 @@
       <c r="T31" s="11" t="inlineStr"/>
       <c r="U31" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V31" s="11" t="inlineStr">
@@ -3155,29 +3175,33 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>20260338366</t>
+          <t>20260342314</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
       <c r="G32" s="11" t="inlineStr"/>
       <c r="H32" s="11" t="inlineStr"/>
       <c r="I32" s="11" t="inlineStr"/>
-      <c r="J32" s="11" t="inlineStr"/>
+      <c r="J32" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
       <c r="K32" s="11" t="inlineStr"/>
       <c r="L32" s="11" t="inlineStr"/>
       <c r="M32" s="11" t="inlineStr">
@@ -3198,7 +3222,7 @@
       <c r="T32" s="11" t="inlineStr"/>
       <c r="U32" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V32" s="11" t="inlineStr">
@@ -3218,29 +3242,33 @@
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C33" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>20260338367</t>
+          <t>20260342315</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
       <c r="G33" s="11" t="inlineStr"/>
       <c r="H33" s="11" t="inlineStr"/>
       <c r="I33" s="11" t="inlineStr"/>
-      <c r="J33" s="11" t="inlineStr"/>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
       <c r="K33" s="11" t="inlineStr"/>
       <c r="L33" s="11" t="inlineStr"/>
       <c r="M33" s="11" t="inlineStr">
@@ -3261,7 +3289,7 @@
       <c r="T33" s="11" t="inlineStr"/>
       <c r="U33" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V33" s="11" t="inlineStr">
@@ -3281,29 +3309,33 @@
       </c>
       <c r="B34" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C34" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>20260338368</t>
+          <t>20260342316</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
       <c r="G34" s="11" t="inlineStr"/>
       <c r="H34" s="11" t="inlineStr"/>
       <c r="I34" s="11" t="inlineStr"/>
-      <c r="J34" s="11" t="inlineStr"/>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
       <c r="K34" s="11" t="inlineStr"/>
       <c r="L34" s="11" t="inlineStr"/>
       <c r="M34" s="11" t="inlineStr">
@@ -3324,7 +3356,7 @@
       <c r="T34" s="11" t="inlineStr"/>
       <c r="U34" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V34" s="11" t="inlineStr">
@@ -3344,29 +3376,33 @@
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C35" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>20260338369</t>
+          <t>20260342353</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
       <c r="G35" s="11" t="inlineStr"/>
       <c r="H35" s="11" t="inlineStr"/>
       <c r="I35" s="11" t="inlineStr"/>
-      <c r="J35" s="11" t="inlineStr"/>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT CASE NO. C20252649)</t>
+        </is>
+      </c>
       <c r="K35" s="11" t="inlineStr"/>
       <c r="L35" s="11" t="inlineStr"/>
       <c r="M35" s="11" t="inlineStr">
@@ -3387,7 +3423,7 @@
       <c r="T35" s="11" t="inlineStr"/>
       <c r="U35" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V35" s="11" t="inlineStr">
@@ -3407,29 +3443,33 @@
       </c>
       <c r="B36" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C36" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>20260338370</t>
+          <t>20260342429</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
       <c r="G36" s="11" t="inlineStr"/>
       <c r="H36" s="11" t="inlineStr"/>
       <c r="I36" s="11" t="inlineStr"/>
-      <c r="J36" s="11" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
       <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
       <c r="M36" s="11" t="inlineStr">
@@ -3450,7 +3490,7 @@
       <c r="T36" s="11" t="inlineStr"/>
       <c r="U36" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V36" s="11" t="inlineStr">
@@ -3470,29 +3510,33 @@
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>20260338371</t>
+          <t>20260342782</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
       <c r="G37" s="11" t="inlineStr"/>
       <c r="H37" s="11" t="inlineStr"/>
       <c r="I37" s="11" t="inlineStr"/>
-      <c r="J37" s="11" t="inlineStr"/>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
       <c r="K37" s="11" t="inlineStr"/>
       <c r="L37" s="11" t="inlineStr"/>
       <c r="M37" s="11" t="inlineStr">
@@ -3513,7 +3557,7 @@
       <c r="T37" s="11" t="inlineStr"/>
       <c r="U37" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V37" s="11" t="inlineStr">
@@ -3533,29 +3577,33 @@
       </c>
       <c r="B38" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>20260338372</t>
+          <t>20260342914</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr"/>
       <c r="G38" s="11" t="inlineStr"/>
       <c r="H38" s="11" t="inlineStr"/>
       <c r="I38" s="11" t="inlineStr"/>
-      <c r="J38" s="11" t="inlineStr"/>
+      <c r="J38" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K38" s="11" t="inlineStr"/>
       <c r="L38" s="11" t="inlineStr"/>
       <c r="M38" s="11" t="inlineStr">
@@ -3576,7 +3624,7 @@
       <c r="T38" s="11" t="inlineStr"/>
       <c r="U38" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V38" s="11" t="inlineStr">
@@ -3596,37 +3644,49 @@
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C39" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>PD</t>
         </is>
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>20260338373</t>
-        </is>
-      </c>
-      <c r="E39" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
+          <t>20260340981</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr"/>
       <c r="F39" s="11" t="inlineStr"/>
       <c r="G39" s="11" t="inlineStr"/>
       <c r="H39" s="11" t="inlineStr"/>
       <c r="I39" s="11" t="inlineStr"/>
-      <c r="J39" s="11" t="inlineStr"/>
-      <c r="K39" s="11" t="inlineStr"/>
-      <c r="L39" s="11" t="inlineStr"/>
+      <c r="J39" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
+        <is>
+          <t>10139 W. Cumberland Drive</t>
+        </is>
+      </c>
+      <c r="L39" s="11" t="inlineStr">
+        <is>
+          <t>Sun City</t>
+        </is>
+      </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N39" s="11" t="inlineStr"/>
+      <c r="N39" s="11" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
       <c r="O39" s="11" t="inlineStr"/>
       <c r="P39" s="11" t="inlineStr"/>
       <c r="Q39" s="11" t="inlineStr">
@@ -3639,7 +3699,7 @@
       <c r="T39" s="11" t="inlineStr"/>
       <c r="U39" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Probate / estate</t>
         </is>
       </c>
       <c r="V39" s="11" t="inlineStr">
@@ -3655,26 +3715,26 @@
     </row>
     <row r="40" ht="26" customHeight="1">
       <c r="A40" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B40" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C40" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>20260338374</t>
+          <t>20260341307</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
@@ -3702,7 +3762,7 @@
       <c r="T40" s="11" t="inlineStr"/>
       <c r="U40" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V40" s="11" t="inlineStr">
@@ -3718,26 +3778,26 @@
     </row>
     <row r="41" ht="26" customHeight="1">
       <c r="A41" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C41" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>20260338375</t>
+          <t>20260341446</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
@@ -3761,11 +3821,15 @@
         </is>
       </c>
       <c r="R41" s="11" t="inlineStr"/>
-      <c r="S41" s="11" t="inlineStr"/>
+      <c r="S41" s="11" t="inlineStr">
+        <is>
+          <t>300-96-568</t>
+        </is>
+      </c>
       <c r="T41" s="11" t="inlineStr"/>
       <c r="U41" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V41" s="11" t="inlineStr">
@@ -3781,26 +3845,26 @@
     </row>
     <row r="42" ht="26" customHeight="1">
       <c r="A42" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B42" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C42" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>20260338376</t>
+          <t>20260341447</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
@@ -3824,11 +3888,15 @@
         </is>
       </c>
       <c r="R42" s="11" t="inlineStr"/>
-      <c r="S42" s="11" t="inlineStr"/>
+      <c r="S42" s="11" t="inlineStr">
+        <is>
+          <t>104-40-005</t>
+        </is>
+      </c>
       <c r="T42" s="11" t="inlineStr"/>
       <c r="U42" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V42" s="11" t="inlineStr">
@@ -3844,26 +3912,26 @@
     </row>
     <row r="43" ht="26" customHeight="1">
       <c r="A43" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C43" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>20260338377</t>
+          <t>20260341462</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
@@ -3891,7 +3959,7 @@
       <c r="T43" s="11" t="inlineStr"/>
       <c r="U43" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V43" s="11" t="inlineStr">
@@ -3907,26 +3975,26 @@
     </row>
     <row r="44" ht="26" customHeight="1">
       <c r="A44" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B44" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C44" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>20260338378</t>
+          <t>20260342522</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
@@ -3950,11 +4018,15 @@
         </is>
       </c>
       <c r="R44" s="11" t="inlineStr"/>
-      <c r="S44" s="11" t="inlineStr"/>
+      <c r="S44" s="11" t="inlineStr">
+        <is>
+          <t>201-13-351</t>
+        </is>
+      </c>
       <c r="T44" s="11" t="inlineStr"/>
       <c r="U44" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V44" s="11" t="inlineStr">
@@ -3970,26 +4042,26 @@
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>20260338379</t>
+          <t>20260339756</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
@@ -4017,7 +4089,7 @@
       <c r="T45" s="11" t="inlineStr"/>
       <c r="U45" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V45" s="11" t="inlineStr">
@@ -4033,26 +4105,26 @@
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>20260338380</t>
+          <t>20260339757</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
@@ -4080,7 +4152,7 @@
       <c r="T46" s="11" t="inlineStr"/>
       <c r="U46" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V46" s="11" t="inlineStr">
@@ -4096,26 +4168,26 @@
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>20260338382</t>
+          <t>20260339758</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
@@ -4143,7 +4215,7 @@
       <c r="T47" s="11" t="inlineStr"/>
       <c r="U47" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V47" s="11" t="inlineStr">
@@ -4159,26 +4231,26 @@
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>20260338383</t>
+          <t>20260339759</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
@@ -4206,7 +4278,7 @@
       <c r="T48" s="11" t="inlineStr"/>
       <c r="U48" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V48" s="11" t="inlineStr">
@@ -4222,26 +4294,26 @@
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>20260338384</t>
+          <t>20260339760</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
@@ -4269,7 +4341,7 @@
       <c r="T49" s="11" t="inlineStr"/>
       <c r="U49" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V49" s="11" t="inlineStr">
@@ -4285,26 +4357,26 @@
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>20260338385</t>
+          <t>20260339761</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr"/>
@@ -4332,7 +4404,7 @@
       <c r="T50" s="11" t="inlineStr"/>
       <c r="U50" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V50" s="11" t="inlineStr">
@@ -4348,26 +4420,26 @@
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>20260338386</t>
+          <t>20260339762</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
@@ -4395,7 +4467,7 @@
       <c r="T51" s="11" t="inlineStr"/>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
@@ -4411,26 +4483,26 @@
     </row>
     <row r="52" ht="26" customHeight="1">
       <c r="A52" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>20260338387</t>
+          <t>20260339763</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
@@ -4458,7 +4530,7 @@
       <c r="T52" s="11" t="inlineStr"/>
       <c r="U52" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V52" s="11" t="inlineStr">
@@ -4474,26 +4546,26 @@
     </row>
     <row r="53" ht="26" customHeight="1">
       <c r="A53" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>20260338388</t>
+          <t>20260339764</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
@@ -4521,7 +4593,7 @@
       <c r="T53" s="11" t="inlineStr"/>
       <c r="U53" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V53" s="11" t="inlineStr">
@@ -4537,26 +4609,26 @@
     </row>
     <row r="54" ht="26" customHeight="1">
       <c r="A54" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>20260338389</t>
+          <t>20260339765</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
@@ -4584,7 +4656,7 @@
       <c r="T54" s="11" t="inlineStr"/>
       <c r="U54" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V54" s="11" t="inlineStr">
@@ -4600,26 +4672,26 @@
     </row>
     <row r="55" ht="26" customHeight="1">
       <c r="A55" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>20260338390</t>
+          <t>20260339766</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
@@ -4647,7 +4719,7 @@
       <c r="T55" s="11" t="inlineStr"/>
       <c r="U55" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V55" s="11" t="inlineStr">
@@ -4663,26 +4735,26 @@
     </row>
     <row r="56" ht="26" customHeight="1">
       <c r="A56" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>20260338391</t>
+          <t>20260339767</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
@@ -4710,7 +4782,7 @@
       <c r="T56" s="11" t="inlineStr"/>
       <c r="U56" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V56" s="11" t="inlineStr">
@@ -4726,26 +4798,26 @@
     </row>
     <row r="57" ht="26" customHeight="1">
       <c r="A57" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>20260338392</t>
+          <t>20260339768</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr"/>
@@ -4773,7 +4845,7 @@
       <c r="T57" s="11" t="inlineStr"/>
       <c r="U57" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V57" s="11" t="inlineStr">
@@ -4789,26 +4861,26 @@
     </row>
     <row r="58" ht="26" customHeight="1">
       <c r="A58" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>20260338393</t>
+          <t>20260339769</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr"/>
@@ -4836,7 +4908,7 @@
       <c r="T58" s="11" t="inlineStr"/>
       <c r="U58" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V58" s="11" t="inlineStr">
@@ -4852,26 +4924,26 @@
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>20260338394</t>
+          <t>20260339770</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
@@ -4899,7 +4971,7 @@
       <c r="T59" s="11" t="inlineStr"/>
       <c r="U59" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V59" s="11" t="inlineStr">
@@ -4915,26 +4987,26 @@
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>20260338395</t>
+          <t>20260339772</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
@@ -4962,7 +5034,7 @@
       <c r="T60" s="11" t="inlineStr"/>
       <c r="U60" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V60" s="11" t="inlineStr">
@@ -4978,26 +5050,26 @@
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>20260338396</t>
+          <t>20260339821</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
@@ -5025,7 +5097,7 @@
       <c r="T61" s="11" t="inlineStr"/>
       <c r="U61" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V61" s="11" t="inlineStr">
@@ -5041,26 +5113,26 @@
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>20260338397</t>
+          <t>20260339822</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
@@ -5088,7 +5160,7 @@
       <c r="T62" s="11" t="inlineStr"/>
       <c r="U62" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V62" s="11" t="inlineStr">
@@ -5104,26 +5176,26 @@
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>20260338398</t>
+          <t>20260339826</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
@@ -5151,7 +5223,7 @@
       <c r="T63" s="11" t="inlineStr"/>
       <c r="U63" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V63" s="11" t="inlineStr">
@@ -5167,26 +5239,26 @@
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>FL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>20260338399</t>
+          <t>20260340145</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
@@ -5214,7 +5286,7 @@
       <c r="T64" s="11" t="inlineStr"/>
       <c r="U64" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V64" s="11" t="inlineStr">
@@ -5230,26 +5302,26 @@
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>State Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>20260338004</t>
+          <t>20260340326</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
@@ -5277,7 +5349,7 @@
       <c r="T65" s="11" t="inlineStr"/>
       <c r="U65" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V65" s="11" t="inlineStr">
@@ -5293,26 +5365,26 @@
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>State Tax Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>20260338005</t>
+          <t>20260340332</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
@@ -5340,7 +5412,7 @@
       <c r="T66" s="11" t="inlineStr"/>
       <c r="U66" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V66" s="11" t="inlineStr">
@@ -5356,26 +5428,26 @@
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>State Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>20260338006</t>
+          <t>20260340819</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
@@ -5403,12 +5475,12 @@
       <c r="T67" s="11" t="inlineStr"/>
       <c r="U67" s="11" t="inlineStr">
         <is>
-          <t>Gov/Tax lien; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V67" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W67" s="12" t="inlineStr">
@@ -5419,7 +5491,7 @@
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
@@ -5433,12 +5505,12 @@
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>20260336754</t>
+          <t>20260340959</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
@@ -5471,7 +5543,7 @@
       </c>
       <c r="V68" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W68" s="12" t="inlineStr">
@@ -5482,7 +5554,7 @@
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
@@ -5496,12 +5568,12 @@
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>20260336864</t>
+          <t>20260341634</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
@@ -5534,7 +5606,7 @@
       </c>
       <c r="V69" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W69" s="12" t="inlineStr">
@@ -5545,7 +5617,7 @@
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
@@ -5559,12 +5631,12 @@
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>20260336866</t>
+          <t>20260342043</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
@@ -5597,7 +5669,7 @@
       </c>
       <c r="V70" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W70" s="12" t="inlineStr">
@@ -5608,26 +5680,26 @@
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>20260336946</t>
+          <t>20260342442</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
@@ -5655,12 +5727,12 @@
       <c r="T71" s="11" t="inlineStr"/>
       <c r="U71" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V71" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W71" s="12" t="inlineStr">
@@ -5671,26 +5743,26 @@
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>20260336947</t>
+          <t>20260342638</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
@@ -5718,12 +5790,12 @@
       <c r="T72" s="11" t="inlineStr"/>
       <c r="U72" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V72" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W72" s="12" t="inlineStr">
@@ -5734,26 +5806,26 @@
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>20260336948</t>
+          <t>20260342803</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
@@ -5781,12 +5853,12 @@
       <c r="T73" s="11" t="inlineStr"/>
       <c r="U73" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V73" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W73" s="12" t="inlineStr">
@@ -5797,26 +5869,26 @@
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>20260336949</t>
+          <t>20260342942</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
@@ -5844,12 +5916,12 @@
       <c r="T74" s="11" t="inlineStr"/>
       <c r="U74" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V74" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W74" s="12" t="inlineStr">
@@ -5860,26 +5932,26 @@
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>20260336951</t>
+          <t>20260341876</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
@@ -5907,12 +5979,12 @@
       <c r="T75" s="11" t="inlineStr"/>
       <c r="U75" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V75" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W75" s="12" t="inlineStr">
@@ -5923,37 +5995,33 @@
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>20260336956</t>
+          <t>20260341893</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
       <c r="G76" s="11" t="inlineStr"/>
       <c r="H76" s="11" t="inlineStr"/>
       <c r="I76" s="11" t="inlineStr"/>
-      <c r="J76" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J76" s="11" t="inlineStr"/>
       <c r="K76" s="11" t="inlineStr"/>
       <c r="L76" s="11" t="inlineStr"/>
       <c r="M76" s="11" t="inlineStr">
@@ -5974,12 +6042,12 @@
       <c r="T76" s="11" t="inlineStr"/>
       <c r="U76" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V76" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W76" s="12" t="inlineStr">
@@ -5990,26 +6058,26 @@
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>20260336957</t>
+          <t>20260341918</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr"/>
@@ -6037,12 +6105,12 @@
       <c r="T77" s="11" t="inlineStr"/>
       <c r="U77" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V77" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W77" s="12" t="inlineStr">
@@ -6053,26 +6121,26 @@
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>20260336958</t>
+          <t>20260342181</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
@@ -6100,12 +6168,12 @@
       <c r="T78" s="11" t="inlineStr"/>
       <c r="U78" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V78" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W78" s="12" t="inlineStr">
@@ -6116,26 +6184,26 @@
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>20260336959</t>
+          <t>20260342432</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr"/>
@@ -6163,12 +6231,12 @@
       <c r="T79" s="11" t="inlineStr"/>
       <c r="U79" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V79" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W79" s="12" t="inlineStr">
@@ -6179,26 +6247,26 @@
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>20260336963</t>
+          <t>20260342466</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
@@ -6226,12 +6294,12 @@
       <c r="T80" s="11" t="inlineStr"/>
       <c r="U80" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V80" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W80" s="12" t="inlineStr">
@@ -6242,26 +6310,26 @@
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>20260336965</t>
+          <t>20260342801</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr"/>
@@ -6289,12 +6357,12 @@
       <c r="T81" s="11" t="inlineStr"/>
       <c r="U81" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V81" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W81" s="12" t="inlineStr">
@@ -6305,26 +6373,26 @@
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="10" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>20260336970</t>
+          <t>20260342895</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr"/>
@@ -6352,12 +6420,12 @@
       <c r="T82" s="11" t="inlineStr"/>
       <c r="U82" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V82" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W82" s="12" t="inlineStr">
@@ -6368,26 +6436,26 @@
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>20260336973</t>
+          <t>20260341311</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
@@ -6415,7 +6483,7 @@
       <c r="T83" s="11" t="inlineStr"/>
       <c r="U83" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V83" s="11" t="inlineStr">
@@ -6431,26 +6499,26 @@
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>20260336974</t>
+          <t>20260341326</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr"/>
@@ -6478,7 +6546,7 @@
       <c r="T84" s="11" t="inlineStr"/>
       <c r="U84" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V84" s="11" t="inlineStr">
@@ -6494,26 +6562,26 @@
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>20260336977</t>
+          <t>20260342063</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr"/>
@@ -6541,7 +6609,7 @@
       <c r="T85" s="11" t="inlineStr"/>
       <c r="U85" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V85" s="11" t="inlineStr">
@@ -6557,37 +6625,33 @@
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="10" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>20260336985</t>
+          <t>20260342064</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr"/>
       <c r="G86" s="11" t="inlineStr"/>
       <c r="H86" s="11" t="inlineStr"/>
       <c r="I86" s="11" t="inlineStr"/>
-      <c r="J86" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J86" s="11" t="inlineStr"/>
       <c r="K86" s="11" t="inlineStr"/>
       <c r="L86" s="11" t="inlineStr"/>
       <c r="M86" s="11" t="inlineStr">
@@ -6608,7 +6672,7 @@
       <c r="T86" s="11" t="inlineStr"/>
       <c r="U86" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V86" s="11" t="inlineStr">
@@ -6624,37 +6688,33 @@
     </row>
     <row r="87" ht="26" customHeight="1">
       <c r="A87" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B87" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C87" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>20260337001</t>
+          <t>20260340720</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr"/>
       <c r="G87" s="11" t="inlineStr"/>
       <c r="H87" s="11" t="inlineStr"/>
       <c r="I87" s="11" t="inlineStr"/>
-      <c r="J87" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J87" s="11" t="inlineStr"/>
       <c r="K87" s="11" t="inlineStr"/>
       <c r="L87" s="11" t="inlineStr"/>
       <c r="M87" s="11" t="inlineStr">
@@ -6675,12 +6735,12 @@
       <c r="T87" s="11" t="inlineStr"/>
       <c r="U87" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V87" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W87" s="12" t="inlineStr">
@@ -6691,37 +6751,33 @@
     </row>
     <row r="88" ht="26" customHeight="1">
       <c r="A88" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B88" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C88" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>20260337780</t>
+          <t>20260341094</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr"/>
       <c r="G88" s="11" t="inlineStr"/>
       <c r="H88" s="11" t="inlineStr"/>
       <c r="I88" s="11" t="inlineStr"/>
-      <c r="J88" s="11" t="inlineStr">
-        <is>
-          <t>201 W JEFFERSON ST</t>
-        </is>
-      </c>
+      <c r="J88" s="11" t="inlineStr"/>
       <c r="K88" s="11" t="inlineStr"/>
       <c r="L88" s="11" t="inlineStr"/>
       <c r="M88" s="11" t="inlineStr">
@@ -6742,12 +6798,12 @@
       <c r="T88" s="11" t="inlineStr"/>
       <c r="U88" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V88" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W88" s="12" t="inlineStr">
@@ -6758,37 +6814,33 @@
     </row>
     <row r="89" ht="26" customHeight="1">
       <c r="A89" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B89" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C89" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>20260337781</t>
+          <t>20260341189</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
       <c r="G89" s="11" t="inlineStr"/>
       <c r="H89" s="11" t="inlineStr"/>
       <c r="I89" s="11" t="inlineStr"/>
-      <c r="J89" s="11" t="inlineStr">
-        <is>
-          <t>201 W JEFFERSON ST</t>
-        </is>
-      </c>
+      <c r="J89" s="11" t="inlineStr"/>
       <c r="K89" s="11" t="inlineStr"/>
       <c r="L89" s="11" t="inlineStr"/>
       <c r="M89" s="11" t="inlineStr">
@@ -6809,12 +6861,12 @@
       <c r="T89" s="11" t="inlineStr"/>
       <c r="U89" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V89" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W89" s="12" t="inlineStr">
@@ -6825,26 +6877,26 @@
     </row>
     <row r="90" ht="26" customHeight="1">
       <c r="A90" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B90" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C90" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>20260337805</t>
+          <t>20260341277</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
@@ -6872,12 +6924,12 @@
       <c r="T90" s="11" t="inlineStr"/>
       <c r="U90" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V90" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W90" s="12" t="inlineStr">
@@ -6888,37 +6940,33 @@
     </row>
     <row r="91" ht="26" customHeight="1">
       <c r="A91" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B91" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C91" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>20260338049</t>
+          <t>20260341278</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr"/>
       <c r="G91" s="11" t="inlineStr"/>
       <c r="H91" s="11" t="inlineStr"/>
       <c r="I91" s="11" t="inlineStr"/>
-      <c r="J91" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court in Maricopa County.</t>
-        </is>
-      </c>
+      <c r="J91" s="11" t="inlineStr"/>
       <c r="K91" s="11" t="inlineStr"/>
       <c r="L91" s="11" t="inlineStr"/>
       <c r="M91" s="11" t="inlineStr">
@@ -6939,12 +6987,12 @@
       <c r="T91" s="11" t="inlineStr"/>
       <c r="U91" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V91" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W91" s="12" t="inlineStr">
@@ -6955,26 +7003,26 @@
     </row>
     <row r="92" ht="26" customHeight="1">
       <c r="A92" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B92" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>20260338170</t>
+          <t>20260341279</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr"/>
@@ -7002,12 +7050,12 @@
       <c r="T92" s="11" t="inlineStr"/>
       <c r="U92" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V92" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W92" s="12" t="inlineStr">
@@ -7018,26 +7066,26 @@
     </row>
     <row r="93" ht="26" customHeight="1">
       <c r="A93" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B93" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C93" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>20260338215</t>
+          <t>20260341280</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
@@ -7065,12 +7113,12 @@
       <c r="T93" s="11" t="inlineStr"/>
       <c r="U93" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V93" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W93" s="12" t="inlineStr">
@@ -7081,26 +7129,26 @@
     </row>
     <row r="94" ht="26" customHeight="1">
       <c r="A94" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B94" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C94" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>20260338823</t>
+          <t>20260341281</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr"/>
@@ -7128,12 +7176,12 @@
       <c r="T94" s="11" t="inlineStr"/>
       <c r="U94" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V94" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W94" s="12" t="inlineStr">
@@ -7144,26 +7192,26 @@
     </row>
     <row r="95" ht="26" customHeight="1">
       <c r="A95" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B95" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C95" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>20260338978</t>
+          <t>20260341282</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr"/>
@@ -7191,12 +7239,12 @@
       <c r="T95" s="11" t="inlineStr"/>
       <c r="U95" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V95" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W95" s="12" t="inlineStr">
@@ -7207,26 +7255,26 @@
     </row>
     <row r="96" ht="26" customHeight="1">
       <c r="A96" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B96" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C96" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>20260338979</t>
+          <t>20260341283</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr"/>
@@ -7254,12 +7302,12 @@
       <c r="T96" s="11" t="inlineStr"/>
       <c r="U96" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V96" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W96" s="12" t="inlineStr">
@@ -7270,26 +7318,26 @@
     </row>
     <row r="97" ht="26" customHeight="1">
       <c r="A97" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B97" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C97" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>20260338980</t>
+          <t>20260341284</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr"/>
@@ -7317,12 +7365,12 @@
       <c r="T97" s="11" t="inlineStr"/>
       <c r="U97" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V97" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W97" s="12" t="inlineStr">
@@ -7333,37 +7381,33 @@
     </row>
     <row r="98" ht="26" customHeight="1">
       <c r="A98" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B98" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C98" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>20260338921</t>
+          <t>20260341285</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr"/>
       <c r="G98" s="11" t="inlineStr"/>
       <c r="H98" s="11" t="inlineStr"/>
       <c r="I98" s="11" t="inlineStr"/>
-      <c r="J98" s="11" t="inlineStr">
-        <is>
-          <t>Superior Court Case No.: PB2024-050471</t>
-        </is>
-      </c>
+      <c r="J98" s="11" t="inlineStr"/>
       <c r="K98" s="11" t="inlineStr"/>
       <c r="L98" s="11" t="inlineStr"/>
       <c r="M98" s="11" t="inlineStr">
@@ -7384,12 +7428,12 @@
       <c r="T98" s="11" t="inlineStr"/>
       <c r="U98" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V98" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W98" s="12" t="inlineStr">
@@ -7400,37 +7444,33 @@
     </row>
     <row r="99" ht="26" customHeight="1">
       <c r="A99" s="10" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B99" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C99" s="11" t="inlineStr">
         <is>
-          <t>PD</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>20260339122</t>
+          <t>20260341286</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr"/>
       <c r="G99" s="11" t="inlineStr"/>
       <c r="H99" s="11" t="inlineStr"/>
       <c r="I99" s="11" t="inlineStr"/>
-      <c r="J99" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J99" s="11" t="inlineStr"/>
       <c r="K99" s="11" t="inlineStr"/>
       <c r="L99" s="11" t="inlineStr"/>
       <c r="M99" s="11" t="inlineStr">
@@ -7451,12 +7491,12 @@
       <c r="T99" s="11" t="inlineStr"/>
       <c r="U99" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V99" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W99" s="12" t="inlineStr">
@@ -7467,7 +7507,7 @@
     </row>
     <row r="100" ht="26" customHeight="1">
       <c r="A100" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B100" s="11" t="inlineStr">
         <is>
@@ -7481,12 +7521,12 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>20260336732</t>
+          <t>20260341287</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr"/>
@@ -7519,7 +7559,7 @@
       </c>
       <c r="V100" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W100" s="12" t="inlineStr">
@@ -7530,7 +7570,7 @@
     </row>
     <row r="101" ht="26" customHeight="1">
       <c r="A101" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B101" s="11" t="inlineStr">
         <is>
@@ -7544,12 +7584,12 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>20260336733</t>
+          <t>20260341288</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr"/>
@@ -7582,7 +7622,7 @@
       </c>
       <c r="V101" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W101" s="12" t="inlineStr">
@@ -7593,7 +7633,7 @@
     </row>
     <row r="102" ht="26" customHeight="1">
       <c r="A102" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B102" s="11" t="inlineStr">
         <is>
@@ -7607,12 +7647,12 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>20260336736</t>
+          <t>20260341289</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr"/>
@@ -7645,7 +7685,7 @@
       </c>
       <c r="V102" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W102" s="12" t="inlineStr">
@@ -7656,7 +7696,7 @@
     </row>
     <row r="103" ht="26" customHeight="1">
       <c r="A103" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B103" s="11" t="inlineStr">
         <is>
@@ -7670,12 +7710,12 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>20260336737</t>
+          <t>20260341291</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr"/>
@@ -7708,7 +7748,7 @@
       </c>
       <c r="V103" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W103" s="12" t="inlineStr">
@@ -7719,7 +7759,7 @@
     </row>
     <row r="104" ht="26" customHeight="1">
       <c r="A104" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B104" s="11" t="inlineStr">
         <is>
@@ -7733,12 +7773,12 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>20260336738</t>
+          <t>20260341292</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr"/>
@@ -7771,7 +7811,7 @@
       </c>
       <c r="V104" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W104" s="12" t="inlineStr">
@@ -7782,7 +7822,7 @@
     </row>
     <row r="105" ht="26" customHeight="1">
       <c r="A105" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B105" s="11" t="inlineStr">
         <is>
@@ -7796,12 +7836,12 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>20260336739</t>
+          <t>20260341293</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr"/>
@@ -7834,7 +7874,7 @@
       </c>
       <c r="V105" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W105" s="12" t="inlineStr">
@@ -7845,7 +7885,7 @@
     </row>
     <row r="106" ht="26" customHeight="1">
       <c r="A106" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B106" s="11" t="inlineStr">
         <is>
@@ -7859,12 +7899,12 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>20260336740</t>
+          <t>20260341294</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr"/>
@@ -7897,7 +7937,7 @@
       </c>
       <c r="V106" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W106" s="12" t="inlineStr">
@@ -7908,7 +7948,7 @@
     </row>
     <row r="107" ht="26" customHeight="1">
       <c r="A107" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B107" s="11" t="inlineStr">
         <is>
@@ -7922,12 +7962,12 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>20260336741</t>
+          <t>20260341295</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr"/>
@@ -7960,7 +8000,7 @@
       </c>
       <c r="V107" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W107" s="12" t="inlineStr">
@@ -7971,7 +8011,7 @@
     </row>
     <row r="108" ht="26" customHeight="1">
       <c r="A108" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B108" s="11" t="inlineStr">
         <is>
@@ -7985,12 +8025,12 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>20260336743</t>
+          <t>20260341296</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr"/>
@@ -8023,7 +8063,7 @@
       </c>
       <c r="V108" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W108" s="12" t="inlineStr">
@@ -8034,7 +8074,7 @@
     </row>
     <row r="109" ht="26" customHeight="1">
       <c r="A109" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B109" s="11" t="inlineStr">
         <is>
@@ -8048,12 +8088,12 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>20260336744</t>
+          <t>20260341297</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr"/>
@@ -8086,7 +8126,7 @@
       </c>
       <c r="V109" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W109" s="12" t="inlineStr">
@@ -8097,7 +8137,7 @@
     </row>
     <row r="110" ht="26" customHeight="1">
       <c r="A110" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B110" s="11" t="inlineStr">
         <is>
@@ -8111,12 +8151,12 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>20260336745</t>
+          <t>20260341298</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr"/>
@@ -8149,7 +8189,7 @@
       </c>
       <c r="V110" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W110" s="12" t="inlineStr">
@@ -8160,7 +8200,7 @@
     </row>
     <row r="111" ht="26" customHeight="1">
       <c r="A111" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B111" s="11" t="inlineStr">
         <is>
@@ -8174,12 +8214,12 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>20260336746</t>
+          <t>20260341299</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr"/>
@@ -8212,7 +8252,7 @@
       </c>
       <c r="V111" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W111" s="12" t="inlineStr">
@@ -8223,7 +8263,7 @@
     </row>
     <row r="112" ht="26" customHeight="1">
       <c r="A112" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B112" s="11" t="inlineStr">
         <is>
@@ -8237,12 +8277,12 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>20260336748</t>
+          <t>20260341300</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr"/>
@@ -8275,7 +8315,7 @@
       </c>
       <c r="V112" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W112" s="12" t="inlineStr">
@@ -8286,7 +8326,7 @@
     </row>
     <row r="113" ht="26" customHeight="1">
       <c r="A113" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B113" s="11" t="inlineStr">
         <is>
@@ -8300,12 +8340,12 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>20260336749</t>
+          <t>20260341301</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr"/>
@@ -8338,7 +8378,7 @@
       </c>
       <c r="V113" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W113" s="12" t="inlineStr">
@@ -8349,7 +8389,7 @@
     </row>
     <row r="114" ht="26" customHeight="1">
       <c r="A114" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B114" s="11" t="inlineStr">
         <is>
@@ -8363,12 +8403,12 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>20260336750</t>
+          <t>20260341302</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr"/>
@@ -8401,7 +8441,7 @@
       </c>
       <c r="V114" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W114" s="12" t="inlineStr">
@@ -8412,7 +8452,7 @@
     </row>
     <row r="115" ht="26" customHeight="1">
       <c r="A115" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
@@ -8426,12 +8466,12 @@
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>20260336751</t>
+          <t>20260341329</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr"/>
@@ -8464,7 +8504,7 @@
       </c>
       <c r="V115" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W115" s="12" t="inlineStr">
@@ -8475,7 +8515,7 @@
     </row>
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
@@ -8489,12 +8529,12 @@
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>20260336752</t>
+          <t>20260341664</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr"/>
@@ -8527,7 +8567,7 @@
       </c>
       <c r="V116" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W116" s="12" t="inlineStr">
@@ -8538,7 +8578,7 @@
     </row>
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
@@ -8552,12 +8592,12 @@
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>20260336753</t>
+          <t>20260341671</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr"/>
@@ -8590,7 +8630,7 @@
       </c>
       <c r="V117" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W117" s="12" t="inlineStr">
@@ -8601,7 +8641,7 @@
     </row>
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
@@ -8615,12 +8655,12 @@
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>20260337191</t>
+          <t>20260341675</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr"/>
@@ -8653,7 +8693,7 @@
       </c>
       <c r="V118" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W118" s="12" t="inlineStr">
@@ -8664,7 +8704,7 @@
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
@@ -8678,12 +8718,12 @@
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>20260337740</t>
+          <t>20260341676</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr"/>
@@ -8716,7 +8756,7 @@
       </c>
       <c r="V119" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W119" s="12" t="inlineStr">
@@ -8727,7 +8767,7 @@
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
@@ -8741,12 +8781,12 @@
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>20260337748</t>
+          <t>20260341683</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr"/>
@@ -8779,7 +8819,7 @@
       </c>
       <c r="V120" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W120" s="12" t="inlineStr">
@@ -8790,7 +8830,7 @@
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
@@ -8804,12 +8844,12 @@
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>20260337783</t>
+          <t>20260341686</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr"/>
@@ -8842,7 +8882,7 @@
       </c>
       <c r="V121" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W121" s="12" t="inlineStr">
@@ -8853,7 +8893,7 @@
     </row>
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
@@ -8867,12 +8907,12 @@
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>20260337785</t>
+          <t>20260341688</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr"/>
@@ -8905,7 +8945,7 @@
       </c>
       <c r="V122" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W122" s="12" t="inlineStr">
@@ -8916,7 +8956,7 @@
     </row>
     <row r="123" ht="26" customHeight="1">
       <c r="A123" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
@@ -8930,12 +8970,12 @@
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>20260337786</t>
+          <t>20260341689</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr"/>
@@ -8968,7 +9008,7 @@
       </c>
       <c r="V123" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W123" s="12" t="inlineStr">
@@ -8979,7 +9019,7 @@
     </row>
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
@@ -8993,12 +9033,12 @@
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>20260337787</t>
+          <t>20260341690</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr"/>
@@ -9031,7 +9071,7 @@
       </c>
       <c r="V124" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W124" s="12" t="inlineStr">
@@ -9042,7 +9082,7 @@
     </row>
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
@@ -9056,12 +9096,12 @@
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>20260337788</t>
+          <t>20260341693</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr"/>
@@ -9094,7 +9134,7 @@
       </c>
       <c r="V125" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W125" s="12" t="inlineStr">
@@ -9105,7 +9145,7 @@
     </row>
     <row r="126" ht="26" customHeight="1">
       <c r="A126" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
@@ -9119,12 +9159,12 @@
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>20260337789</t>
+          <t>20260341694</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr"/>
@@ -9157,7 +9197,7 @@
       </c>
       <c r="V126" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W126" s="12" t="inlineStr">
@@ -9168,7 +9208,7 @@
     </row>
     <row r="127" ht="26" customHeight="1">
       <c r="A127" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
@@ -9182,12 +9222,12 @@
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>20260337790</t>
+          <t>20260341699</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr"/>
@@ -9220,7 +9260,7 @@
       </c>
       <c r="V127" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W127" s="12" t="inlineStr">
@@ -9231,7 +9271,7 @@
     </row>
     <row r="128" ht="26" customHeight="1">
       <c r="A128" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
@@ -9245,12 +9285,12 @@
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>20260337791</t>
+          <t>20260341702</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr"/>
@@ -9283,7 +9323,7 @@
       </c>
       <c r="V128" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W128" s="12" t="inlineStr">
@@ -9294,7 +9334,7 @@
     </row>
     <row r="129" ht="26" customHeight="1">
       <c r="A129" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
@@ -9308,12 +9348,12 @@
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>20260337792</t>
+          <t>20260341706</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr"/>
@@ -9346,7 +9386,7 @@
       </c>
       <c r="V129" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W129" s="12" t="inlineStr">
@@ -9357,7 +9397,7 @@
     </row>
     <row r="130" ht="26" customHeight="1">
       <c r="A130" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
@@ -9371,12 +9411,12 @@
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>20260337794</t>
+          <t>20260341714</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr"/>
@@ -9409,7 +9449,7 @@
       </c>
       <c r="V130" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W130" s="12" t="inlineStr">
@@ -9420,7 +9460,7 @@
     </row>
     <row r="131" ht="26" customHeight="1">
       <c r="A131" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
@@ -9434,12 +9474,12 @@
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>20260337795</t>
+          <t>20260341718</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr"/>
@@ -9472,7 +9512,7 @@
       </c>
       <c r="V131" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W131" s="12" t="inlineStr">
@@ -9483,7 +9523,7 @@
     </row>
     <row r="132" ht="26" customHeight="1">
       <c r="A132" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
@@ -9497,12 +9537,12 @@
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>20260337798</t>
+          <t>20260341753</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr"/>
@@ -9535,7 +9575,7 @@
       </c>
       <c r="V132" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W132" s="12" t="inlineStr">
@@ -9546,7 +9586,7 @@
     </row>
     <row r="133" ht="26" customHeight="1">
       <c r="A133" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
@@ -9560,12 +9600,12 @@
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>20260337799</t>
+          <t>20260341759</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr"/>
@@ -9598,7 +9638,7 @@
       </c>
       <c r="V133" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W133" s="12" t="inlineStr">
@@ -9609,7 +9649,7 @@
     </row>
     <row r="134" ht="26" customHeight="1">
       <c r="A134" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
@@ -9623,12 +9663,12 @@
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>20260337800</t>
+          <t>20260341767</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr"/>
@@ -9661,7 +9701,7 @@
       </c>
       <c r="V134" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W134" s="12" t="inlineStr">
@@ -9672,7 +9712,7 @@
     </row>
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
@@ -9686,12 +9726,12 @@
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>20260337801</t>
+          <t>20260341768</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr"/>
@@ -9724,7 +9764,7 @@
       </c>
       <c r="V135" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W135" s="12" t="inlineStr">
@@ -9735,7 +9775,7 @@
     </row>
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
@@ -9749,12 +9789,12 @@
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>20260337803</t>
+          <t>20260341779</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr"/>
@@ -9787,7 +9827,7 @@
       </c>
       <c r="V136" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W136" s="12" t="inlineStr">
@@ -9798,26 +9838,26 @@
     </row>
     <row r="137" ht="26" customHeight="1">
       <c r="A137" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>20260338981</t>
+          <t>20260341886</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr"/>
@@ -9845,7 +9885,7 @@
       <c r="T137" s="11" t="inlineStr"/>
       <c r="U137" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V137" s="11" t="inlineStr">
@@ -9861,26 +9901,26 @@
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>20260338986</t>
+          <t>20260341892</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr"/>
@@ -9908,7 +9948,7 @@
       <c r="T138" s="11" t="inlineStr"/>
       <c r="U138" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V138" s="11" t="inlineStr">
@@ -9924,26 +9964,26 @@
     </row>
     <row r="139" ht="26" customHeight="1">
       <c r="A139" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>20260339090</t>
+          <t>20260341894</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr"/>
@@ -9971,7 +10011,7 @@
       <c r="T139" s="11" t="inlineStr"/>
       <c r="U139" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V139" s="11" t="inlineStr">
@@ -9987,26 +10027,26 @@
     </row>
     <row r="140" ht="26" customHeight="1">
       <c r="A140" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>20260339211</t>
+          <t>20260341898</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr"/>
@@ -10034,7 +10074,7 @@
       <c r="T140" s="11" t="inlineStr"/>
       <c r="U140" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V140" s="11" t="inlineStr">
@@ -10050,26 +10090,26 @@
     </row>
     <row r="141" ht="26" customHeight="1">
       <c r="A141" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>20260339444</t>
+          <t>20260341905</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr"/>
@@ -10097,7 +10137,7 @@
       <c r="T141" s="11" t="inlineStr"/>
       <c r="U141" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V141" s="11" t="inlineStr">
@@ -10113,26 +10153,26 @@
     </row>
     <row r="142" ht="26" customHeight="1">
       <c r="A142" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>20260338185</t>
+          <t>20260341907</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr"/>
@@ -10160,7 +10200,7 @@
       <c r="T142" s="11" t="inlineStr"/>
       <c r="U142" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V142" s="11" t="inlineStr">
@@ -10176,26 +10216,26 @@
     </row>
     <row r="143" ht="26" customHeight="1">
       <c r="A143" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>20260338504</t>
+          <t>20260341908</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr"/>
@@ -10223,7 +10263,7 @@
       <c r="T143" s="11" t="inlineStr"/>
       <c r="U143" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V143" s="11" t="inlineStr">
@@ -10239,26 +10279,26 @@
     </row>
     <row r="144" ht="26" customHeight="1">
       <c r="A144" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>20260337735</t>
+          <t>20260341909</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr"/>
@@ -10286,7 +10326,7 @@
       <c r="T144" s="11" t="inlineStr"/>
       <c r="U144" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V144" s="11" t="inlineStr">
@@ -10302,26 +10342,26 @@
     </row>
     <row r="145" ht="26" customHeight="1">
       <c r="A145" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B145" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C145" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D145" s="11" t="inlineStr">
         <is>
-          <t>20260339314</t>
+          <t>20260341913</t>
         </is>
       </c>
       <c r="E145" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F145" s="11" t="inlineStr"/>
@@ -10349,7 +10389,7 @@
       <c r="T145" s="11" t="inlineStr"/>
       <c r="U145" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V145" s="11" t="inlineStr">
@@ -10365,26 +10405,26 @@
     </row>
     <row r="146" ht="26" customHeight="1">
       <c r="A146" s="10" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B146" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C146" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D146" s="11" t="inlineStr">
         <is>
-          <t>20260339326</t>
+          <t>20260341916</t>
         </is>
       </c>
       <c r="E146" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F146" s="11" t="inlineStr"/>
@@ -10412,7 +10452,7 @@
       <c r="T146" s="11" t="inlineStr"/>
       <c r="U146" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V146" s="11" t="inlineStr">
@@ -10428,26 +10468,26 @@
     </row>
     <row r="147" ht="26" customHeight="1">
       <c r="A147" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B147" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C147" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D147" s="11" t="inlineStr">
         <is>
-          <t>20260337438</t>
+          <t>20260341921</t>
         </is>
       </c>
       <c r="E147" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F147" s="11" t="inlineStr"/>
@@ -10475,12 +10515,12 @@
       <c r="T147" s="11" t="inlineStr"/>
       <c r="U147" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V147" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W147" s="12" t="inlineStr">
@@ -10491,26 +10531,26 @@
     </row>
     <row r="148" ht="26" customHeight="1">
       <c r="A148" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B148" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C148" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D148" s="11" t="inlineStr">
         <is>
-          <t>20260337471</t>
+          <t>20260341967</t>
         </is>
       </c>
       <c r="E148" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F148" s="11" t="inlineStr"/>
@@ -10538,12 +10578,12 @@
       <c r="T148" s="11" t="inlineStr"/>
       <c r="U148" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V148" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W148" s="12" t="inlineStr">
@@ -10554,26 +10594,26 @@
     </row>
     <row r="149" ht="26" customHeight="1">
       <c r="A149" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B149" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C149" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D149" s="11" t="inlineStr">
         <is>
-          <t>20260337472</t>
+          <t>20260342077</t>
         </is>
       </c>
       <c r="E149" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F149" s="11" t="inlineStr"/>
@@ -10601,12 +10641,12 @@
       <c r="T149" s="11" t="inlineStr"/>
       <c r="U149" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V149" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W149" s="12" t="inlineStr">
@@ -10617,26 +10657,26 @@
     </row>
     <row r="150" ht="26" customHeight="1">
       <c r="A150" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B150" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C150" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D150" s="11" t="inlineStr">
         <is>
-          <t>20260337473</t>
+          <t>20260342078</t>
         </is>
       </c>
       <c r="E150" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F150" s="11" t="inlineStr"/>
@@ -10664,12 +10704,12 @@
       <c r="T150" s="11" t="inlineStr"/>
       <c r="U150" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V150" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W150" s="12" t="inlineStr">
@@ -10680,26 +10720,26 @@
     </row>
     <row r="151" ht="26" customHeight="1">
       <c r="A151" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B151" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C151" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D151" s="11" t="inlineStr">
         <is>
-          <t>20260337474</t>
+          <t>20260342079</t>
         </is>
       </c>
       <c r="E151" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F151" s="11" t="inlineStr"/>
@@ -10727,12 +10767,12 @@
       <c r="T151" s="11" t="inlineStr"/>
       <c r="U151" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V151" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W151" s="12" t="inlineStr">
@@ -10743,26 +10783,26 @@
     </row>
     <row r="152" ht="26" customHeight="1">
       <c r="A152" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B152" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C152" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D152" s="11" t="inlineStr">
         <is>
-          <t>20260337475</t>
+          <t>20260342080</t>
         </is>
       </c>
       <c r="E152" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F152" s="11" t="inlineStr"/>
@@ -10790,12 +10830,12 @@
       <c r="T152" s="11" t="inlineStr"/>
       <c r="U152" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V152" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W152" s="12" t="inlineStr">
@@ -10806,26 +10846,26 @@
     </row>
     <row r="153" ht="26" customHeight="1">
       <c r="A153" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B153" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C153" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D153" s="11" t="inlineStr">
         <is>
-          <t>20260337476</t>
+          <t>20260342083</t>
         </is>
       </c>
       <c r="E153" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F153" s="11" t="inlineStr"/>
@@ -10853,12 +10893,12 @@
       <c r="T153" s="11" t="inlineStr"/>
       <c r="U153" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V153" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W153" s="12" t="inlineStr">
@@ -10869,26 +10909,26 @@
     </row>
     <row r="154" ht="26" customHeight="1">
       <c r="A154" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B154" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C154" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D154" s="11" t="inlineStr">
         <is>
-          <t>20260337477</t>
+          <t>20260342084</t>
         </is>
       </c>
       <c r="E154" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F154" s="11" t="inlineStr"/>
@@ -10916,12 +10956,12 @@
       <c r="T154" s="11" t="inlineStr"/>
       <c r="U154" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V154" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W154" s="12" t="inlineStr">
@@ -10932,26 +10972,26 @@
     </row>
     <row r="155" ht="26" customHeight="1">
       <c r="A155" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B155" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C155" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D155" s="11" t="inlineStr">
         <is>
-          <t>20260337478</t>
+          <t>20260342085</t>
         </is>
       </c>
       <c r="E155" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F155" s="11" t="inlineStr"/>
@@ -10979,12 +11019,12 @@
       <c r="T155" s="11" t="inlineStr"/>
       <c r="U155" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V155" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W155" s="12" t="inlineStr">
@@ -10995,26 +11035,26 @@
     </row>
     <row r="156" ht="26" customHeight="1">
       <c r="A156" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B156" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C156" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D156" s="11" t="inlineStr">
         <is>
-          <t>20260337481</t>
+          <t>20260342086</t>
         </is>
       </c>
       <c r="E156" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F156" s="11" t="inlineStr"/>
@@ -11042,12 +11082,12 @@
       <c r="T156" s="11" t="inlineStr"/>
       <c r="U156" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V156" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W156" s="12" t="inlineStr">
@@ -11058,26 +11098,26 @@
     </row>
     <row r="157" ht="26" customHeight="1">
       <c r="A157" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B157" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C157" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D157" s="11" t="inlineStr">
         <is>
-          <t>20260337482</t>
+          <t>20260342087</t>
         </is>
       </c>
       <c r="E157" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F157" s="11" t="inlineStr"/>
@@ -11105,12 +11145,12 @@
       <c r="T157" s="11" t="inlineStr"/>
       <c r="U157" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V157" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W157" s="12" t="inlineStr">
@@ -11121,26 +11161,26 @@
     </row>
     <row r="158" ht="26" customHeight="1">
       <c r="A158" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B158" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C158" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D158" s="11" t="inlineStr">
         <is>
-          <t>20260337483</t>
+          <t>20260342099</t>
         </is>
       </c>
       <c r="E158" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F158" s="11" t="inlineStr"/>
@@ -11168,12 +11208,12 @@
       <c r="T158" s="11" t="inlineStr"/>
       <c r="U158" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V158" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W158" s="12" t="inlineStr">
@@ -11184,26 +11224,26 @@
     </row>
     <row r="159" ht="26" customHeight="1">
       <c r="A159" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B159" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C159" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D159" s="11" t="inlineStr">
         <is>
-          <t>20260337484</t>
+          <t>20260342100</t>
         </is>
       </c>
       <c r="E159" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F159" s="11" t="inlineStr"/>
@@ -11231,12 +11271,12 @@
       <c r="T159" s="11" t="inlineStr"/>
       <c r="U159" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V159" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W159" s="12" t="inlineStr">
@@ -11247,26 +11287,26 @@
     </row>
     <row r="160" ht="26" customHeight="1">
       <c r="A160" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B160" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C160" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D160" s="11" t="inlineStr">
         <is>
-          <t>20260337486</t>
+          <t>20260342102</t>
         </is>
       </c>
       <c r="E160" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F160" s="11" t="inlineStr"/>
@@ -11294,12 +11334,12 @@
       <c r="T160" s="11" t="inlineStr"/>
       <c r="U160" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V160" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W160" s="12" t="inlineStr">
@@ -11310,26 +11350,26 @@
     </row>
     <row r="161" ht="26" customHeight="1">
       <c r="A161" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B161" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C161" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D161" s="11" t="inlineStr">
         <is>
-          <t>20260337882</t>
+          <t>20260342103</t>
         </is>
       </c>
       <c r="E161" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F161" s="11" t="inlineStr"/>
@@ -11357,12 +11397,12 @@
       <c r="T161" s="11" t="inlineStr"/>
       <c r="U161" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V161" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W161" s="12" t="inlineStr">
@@ -11373,26 +11413,26 @@
     </row>
     <row r="162" ht="26" customHeight="1">
       <c r="A162" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B162" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C162" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D162" s="11" t="inlineStr">
         <is>
-          <t>20260337884</t>
+          <t>20260342105</t>
         </is>
       </c>
       <c r="E162" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F162" s="11" t="inlineStr"/>
@@ -11420,12 +11460,12 @@
       <c r="T162" s="11" t="inlineStr"/>
       <c r="U162" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V162" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W162" s="12" t="inlineStr">
@@ -11436,26 +11476,26 @@
     </row>
     <row r="163" ht="26" customHeight="1">
       <c r="A163" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B163" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C163" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D163" s="11" t="inlineStr">
         <is>
-          <t>20260337890</t>
+          <t>20260342108</t>
         </is>
       </c>
       <c r="E163" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F163" s="11" t="inlineStr"/>
@@ -11483,12 +11523,12 @@
       <c r="T163" s="11" t="inlineStr"/>
       <c r="U163" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V163" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W163" s="12" t="inlineStr">
@@ -11499,26 +11539,26 @@
     </row>
     <row r="164" ht="26" customHeight="1">
       <c r="A164" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B164" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C164" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D164" s="11" t="inlineStr">
         <is>
-          <t>20260338456</t>
+          <t>20260342110</t>
         </is>
       </c>
       <c r="E164" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F164" s="11" t="inlineStr"/>
@@ -11546,12 +11586,12 @@
       <c r="T164" s="11" t="inlineStr"/>
       <c r="U164" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V164" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W164" s="12" t="inlineStr">
@@ -11562,26 +11602,26 @@
     </row>
     <row r="165" ht="26" customHeight="1">
       <c r="A165" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B165" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C165" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D165" s="11" t="inlineStr">
         <is>
-          <t>20260338457</t>
+          <t>20260342113</t>
         </is>
       </c>
       <c r="E165" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F165" s="11" t="inlineStr"/>
@@ -11609,12 +11649,12 @@
       <c r="T165" s="11" t="inlineStr"/>
       <c r="U165" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V165" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W165" s="12" t="inlineStr">
@@ -11625,26 +11665,26 @@
     </row>
     <row r="166" ht="26" customHeight="1">
       <c r="A166" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B166" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C166" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D166" s="11" t="inlineStr">
         <is>
-          <t>20260338460</t>
+          <t>20260342117</t>
         </is>
       </c>
       <c r="E166" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F166" s="11" t="inlineStr"/>
@@ -11672,12 +11712,12 @@
       <c r="T166" s="11" t="inlineStr"/>
       <c r="U166" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V166" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W166" s="12" t="inlineStr">
@@ -11688,26 +11728,26 @@
     </row>
     <row r="167" ht="26" customHeight="1">
       <c r="A167" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B167" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C167" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D167" s="11" t="inlineStr">
         <is>
-          <t>20260338465</t>
+          <t>20260342120</t>
         </is>
       </c>
       <c r="E167" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F167" s="11" t="inlineStr"/>
@@ -11735,12 +11775,12 @@
       <c r="T167" s="11" t="inlineStr"/>
       <c r="U167" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V167" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W167" s="12" t="inlineStr">
@@ -11751,26 +11791,26 @@
     </row>
     <row r="168" ht="26" customHeight="1">
       <c r="A168" s="10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B168" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C168" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D168" s="11" t="inlineStr">
         <is>
-          <t>20260338780</t>
+          <t>20260342122</t>
         </is>
       </c>
       <c r="E168" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F168" s="11" t="inlineStr"/>
@@ -11798,12 +11838,12 @@
       <c r="T168" s="11" t="inlineStr"/>
       <c r="U168" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V168" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W168" s="12" t="inlineStr">
@@ -11828,12 +11868,12 @@
       </c>
       <c r="D169" s="11" t="inlineStr">
         <is>
-          <t>20260337742</t>
+          <t>20260342127</t>
         </is>
       </c>
       <c r="E169" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F169" s="11" t="inlineStr"/>
@@ -11891,12 +11931,12 @@
       </c>
       <c r="D170" s="11" t="inlineStr">
         <is>
-          <t>20260337744</t>
+          <t>20260342128</t>
         </is>
       </c>
       <c r="E170" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F170" s="11" t="inlineStr"/>
@@ -11954,12 +11994,12 @@
       </c>
       <c r="D171" s="11" t="inlineStr">
         <is>
-          <t>20260337745</t>
+          <t>20260342129</t>
         </is>
       </c>
       <c r="E171" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F171" s="11" t="inlineStr"/>
@@ -12017,12 +12057,12 @@
       </c>
       <c r="D172" s="11" t="inlineStr">
         <is>
-          <t>20260337746</t>
+          <t>20260342135</t>
         </is>
       </c>
       <c r="E172" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F172" s="11" t="inlineStr"/>
@@ -12080,12 +12120,12 @@
       </c>
       <c r="D173" s="11" t="inlineStr">
         <is>
-          <t>20260337747</t>
+          <t>20260342142</t>
         </is>
       </c>
       <c r="E173" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F173" s="11" t="inlineStr"/>
@@ -12143,12 +12183,12 @@
       </c>
       <c r="D174" s="11" t="inlineStr">
         <is>
-          <t>20260337782</t>
+          <t>20260342147</t>
         </is>
       </c>
       <c r="E174" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F174" s="11" t="inlineStr"/>
@@ -12206,12 +12246,12 @@
       </c>
       <c r="D175" s="11" t="inlineStr">
         <is>
-          <t>20260337904</t>
+          <t>20260342150</t>
         </is>
       </c>
       <c r="E175" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F175" s="11" t="inlineStr"/>
@@ -12269,12 +12309,12 @@
       </c>
       <c r="D176" s="11" t="inlineStr">
         <is>
-          <t>20260337916</t>
+          <t>20260342151</t>
         </is>
       </c>
       <c r="E176" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F176" s="11" t="inlineStr"/>
@@ -12332,12 +12372,12 @@
       </c>
       <c r="D177" s="11" t="inlineStr">
         <is>
-          <t>20260337917</t>
+          <t>20260342154</t>
         </is>
       </c>
       <c r="E177" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F177" s="11" t="inlineStr"/>
@@ -12395,12 +12435,12 @@
       </c>
       <c r="D178" s="11" t="inlineStr">
         <is>
-          <t>20260337918</t>
+          <t>20260342155</t>
         </is>
       </c>
       <c r="E178" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F178" s="11" t="inlineStr"/>
@@ -12458,12 +12498,12 @@
       </c>
       <c r="D179" s="11" t="inlineStr">
         <is>
-          <t>20260337919</t>
+          <t>20260342163</t>
         </is>
       </c>
       <c r="E179" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F179" s="11" t="inlineStr"/>
@@ -12521,12 +12561,12 @@
       </c>
       <c r="D180" s="11" t="inlineStr">
         <is>
-          <t>20260337920</t>
+          <t>20260342166</t>
         </is>
       </c>
       <c r="E180" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F180" s="11" t="inlineStr"/>
@@ -12584,12 +12624,12 @@
       </c>
       <c r="D181" s="11" t="inlineStr">
         <is>
-          <t>20260337985</t>
+          <t>20260342294</t>
         </is>
       </c>
       <c r="E181" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F181" s="11" t="inlineStr"/>
@@ -12647,12 +12687,12 @@
       </c>
       <c r="D182" s="11" t="inlineStr">
         <is>
-          <t>20260338431</t>
+          <t>20260342296</t>
         </is>
       </c>
       <c r="E182" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F182" s="11" t="inlineStr"/>
@@ -12710,12 +12750,12 @@
       </c>
       <c r="D183" s="11" t="inlineStr">
         <is>
-          <t>20260338684</t>
+          <t>20260342346</t>
         </is>
       </c>
       <c r="E183" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F183" s="11" t="inlineStr"/>
@@ -12773,12 +12813,12 @@
       </c>
       <c r="D184" s="11" t="inlineStr">
         <is>
-          <t>20260338723</t>
+          <t>20260342351</t>
         </is>
       </c>
       <c r="E184" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F184" s="11" t="inlineStr"/>
@@ -12836,12 +12876,12 @@
       </c>
       <c r="D185" s="11" t="inlineStr">
         <is>
-          <t>20260339021</t>
+          <t>20260342364</t>
         </is>
       </c>
       <c r="E185" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F185" s="11" t="inlineStr"/>
@@ -12899,12 +12939,12 @@
       </c>
       <c r="D186" s="11" t="inlineStr">
         <is>
-          <t>20260339022</t>
+          <t>20260342408</t>
         </is>
       </c>
       <c r="E186" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F186" s="11" t="inlineStr"/>
@@ -12962,12 +13002,12 @@
       </c>
       <c r="D187" s="11" t="inlineStr">
         <is>
-          <t>20260339023</t>
+          <t>20260342415</t>
         </is>
       </c>
       <c r="E187" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F187" s="11" t="inlineStr"/>
@@ -13025,12 +13065,12 @@
       </c>
       <c r="D188" s="11" t="inlineStr">
         <is>
-          <t>20260339024</t>
+          <t>20260342443</t>
         </is>
       </c>
       <c r="E188" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F188" s="11" t="inlineStr"/>
@@ -13088,12 +13128,12 @@
       </c>
       <c r="D189" s="11" t="inlineStr">
         <is>
-          <t>20260339028</t>
+          <t>20260342444</t>
         </is>
       </c>
       <c r="E189" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F189" s="11" t="inlineStr"/>
@@ -13151,12 +13191,12 @@
       </c>
       <c r="D190" s="11" t="inlineStr">
         <is>
-          <t>20260339029</t>
+          <t>20260342446</t>
         </is>
       </c>
       <c r="E190" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F190" s="11" t="inlineStr"/>
@@ -13214,12 +13254,12 @@
       </c>
       <c r="D191" s="11" t="inlineStr">
         <is>
-          <t>20260339030</t>
+          <t>20260342447</t>
         </is>
       </c>
       <c r="E191" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F191" s="11" t="inlineStr"/>
@@ -13277,12 +13317,12 @@
       </c>
       <c r="D192" s="11" t="inlineStr">
         <is>
-          <t>20260339044</t>
+          <t>20260342450</t>
         </is>
       </c>
       <c r="E192" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F192" s="11" t="inlineStr"/>
@@ -13326,26 +13366,26 @@
     </row>
     <row r="193" ht="26" customHeight="1">
       <c r="A193" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B193" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C193" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D193" s="11" t="inlineStr">
         <is>
-          <t>20260338785</t>
+          <t>20260342451</t>
         </is>
       </c>
       <c r="E193" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F193" s="11" t="inlineStr"/>
@@ -13373,7 +13413,7 @@
       <c r="T193" s="11" t="inlineStr"/>
       <c r="U193" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V193" s="11" t="inlineStr">
@@ -13389,26 +13429,26 @@
     </row>
     <row r="194" ht="26" customHeight="1">
       <c r="A194" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B194" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C194" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D194" s="11" t="inlineStr">
         <is>
-          <t>20260338792</t>
+          <t>20260342465</t>
         </is>
       </c>
       <c r="E194" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F194" s="11" t="inlineStr"/>
@@ -13436,7 +13476,7 @@
       <c r="T194" s="11" t="inlineStr"/>
       <c r="U194" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V194" s="11" t="inlineStr">
@@ -13452,26 +13492,26 @@
     </row>
     <row r="195" ht="26" customHeight="1">
       <c r="A195" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B195" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C195" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D195" s="11" t="inlineStr">
         <is>
-          <t>20260338793</t>
+          <t>20260342468</t>
         </is>
       </c>
       <c r="E195" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F195" s="11" t="inlineStr"/>
@@ -13499,7 +13539,7 @@
       <c r="T195" s="11" t="inlineStr"/>
       <c r="U195" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V195" s="11" t="inlineStr">
@@ -13515,26 +13555,26 @@
     </row>
     <row r="196" ht="26" customHeight="1">
       <c r="A196" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B196" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C196" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D196" s="11" t="inlineStr">
         <is>
-          <t>20260338794</t>
+          <t>20260342469</t>
         </is>
       </c>
       <c r="E196" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F196" s="11" t="inlineStr"/>
@@ -13562,7 +13602,7 @@
       <c r="T196" s="11" t="inlineStr"/>
       <c r="U196" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V196" s="11" t="inlineStr">
@@ -13578,26 +13618,26 @@
     </row>
     <row r="197" ht="26" customHeight="1">
       <c r="A197" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B197" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C197" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D197" s="11" t="inlineStr">
         <is>
-          <t>20260338796</t>
+          <t>20260342473</t>
         </is>
       </c>
       <c r="E197" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F197" s="11" t="inlineStr"/>
@@ -13625,7 +13665,7 @@
       <c r="T197" s="11" t="inlineStr"/>
       <c r="U197" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V197" s="11" t="inlineStr">
@@ -13641,26 +13681,26 @@
     </row>
     <row r="198" ht="26" customHeight="1">
       <c r="A198" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B198" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C198" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D198" s="11" t="inlineStr">
         <is>
-          <t>20260338800</t>
+          <t>20260342530</t>
         </is>
       </c>
       <c r="E198" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F198" s="11" t="inlineStr"/>
@@ -13688,7 +13728,7 @@
       <c r="T198" s="11" t="inlineStr"/>
       <c r="U198" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V198" s="11" t="inlineStr">
@@ -13704,26 +13744,26 @@
     </row>
     <row r="199" ht="26" customHeight="1">
       <c r="A199" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B199" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C199" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D199" s="11" t="inlineStr">
         <is>
-          <t>20260338803</t>
+          <t>20260342531</t>
         </is>
       </c>
       <c r="E199" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F199" s="11" t="inlineStr"/>
@@ -13751,7 +13791,7 @@
       <c r="T199" s="11" t="inlineStr"/>
       <c r="U199" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V199" s="11" t="inlineStr">
@@ -13767,26 +13807,26 @@
     </row>
     <row r="200" ht="26" customHeight="1">
       <c r="A200" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B200" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C200" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D200" s="11" t="inlineStr">
         <is>
-          <t>20260338812</t>
+          <t>20260342550</t>
         </is>
       </c>
       <c r="E200" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F200" s="11" t="inlineStr"/>
@@ -13814,7 +13854,7 @@
       <c r="T200" s="11" t="inlineStr"/>
       <c r="U200" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V200" s="11" t="inlineStr">
@@ -13830,26 +13870,26 @@
     </row>
     <row r="201" ht="26" customHeight="1">
       <c r="A201" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B201" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C201" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D201" s="11" t="inlineStr">
         <is>
-          <t>20260338817</t>
+          <t>20260342632</t>
         </is>
       </c>
       <c r="E201" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F201" s="11" t="inlineStr"/>
@@ -13877,7 +13917,7 @@
       <c r="T201" s="11" t="inlineStr"/>
       <c r="U201" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V201" s="11" t="inlineStr">
@@ -13893,26 +13933,26 @@
     </row>
     <row r="202" ht="26" customHeight="1">
       <c r="A202" s="10" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B202" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Medical Lien</t>
         </is>
       </c>
       <c r="C202" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>HL</t>
         </is>
       </c>
       <c r="D202" s="11" t="inlineStr">
         <is>
-          <t>20260338822</t>
+          <t>20260342679</t>
         </is>
       </c>
       <c r="E202" s="11" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="F202" s="11" t="inlineStr"/>
@@ -13940,7 +13980,7 @@
       <c r="T202" s="11" t="inlineStr"/>
       <c r="U202" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Medical lien; New this week</t>
         </is>
       </c>
       <c r="V202" s="11" t="inlineStr">
@@ -13956,28 +13996,24 @@
     </row>
     <row r="203" ht="26" customHeight="1">
       <c r="A203" s="10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B203" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C203" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>SJ</t>
         </is>
       </c>
       <c r="D203" s="11" t="inlineStr">
         <is>
-          <t>20260338833</t>
-        </is>
-      </c>
-      <c r="E203" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
+          <t>20260339944</t>
+        </is>
+      </c>
+      <c r="E203" s="11" t="inlineStr"/>
       <c r="F203" s="11" t="inlineStr"/>
       <c r="G203" s="11" t="inlineStr"/>
       <c r="H203" s="11" t="inlineStr"/>
@@ -14003,7 +14039,7 @@
       <c r="T203" s="11" t="inlineStr"/>
       <c r="U203" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Judgment lien</t>
         </is>
       </c>
       <c r="V203" s="11" t="inlineStr">
@@ -14017,827 +14053,8 @@
         </is>
       </c>
     </row>
-    <row r="204" ht="26" customHeight="1">
-      <c r="A204" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B204" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C204" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D204" s="11" t="inlineStr">
-        <is>
-          <t>20260338838</t>
-        </is>
-      </c>
-      <c r="E204" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F204" s="11" t="inlineStr"/>
-      <c r="G204" s="11" t="inlineStr"/>
-      <c r="H204" s="11" t="inlineStr"/>
-      <c r="I204" s="11" t="inlineStr"/>
-      <c r="J204" s="11" t="inlineStr"/>
-      <c r="K204" s="11" t="inlineStr"/>
-      <c r="L204" s="11" t="inlineStr"/>
-      <c r="M204" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N204" s="11" t="inlineStr"/>
-      <c r="O204" s="11" t="inlineStr"/>
-      <c r="P204" s="11" t="inlineStr"/>
-      <c r="Q204" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R204" s="11" t="inlineStr"/>
-      <c r="S204" s="11" t="inlineStr"/>
-      <c r="T204" s="11" t="inlineStr"/>
-      <c r="U204" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V204" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W204" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="205" ht="26" customHeight="1">
-      <c r="A205" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B205" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C205" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D205" s="11" t="inlineStr">
-        <is>
-          <t>20260338840</t>
-        </is>
-      </c>
-      <c r="E205" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F205" s="11" t="inlineStr"/>
-      <c r="G205" s="11" t="inlineStr"/>
-      <c r="H205" s="11" t="inlineStr"/>
-      <c r="I205" s="11" t="inlineStr"/>
-      <c r="J205" s="11" t="inlineStr"/>
-      <c r="K205" s="11" t="inlineStr"/>
-      <c r="L205" s="11" t="inlineStr"/>
-      <c r="M205" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N205" s="11" t="inlineStr"/>
-      <c r="O205" s="11" t="inlineStr"/>
-      <c r="P205" s="11" t="inlineStr"/>
-      <c r="Q205" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R205" s="11" t="inlineStr"/>
-      <c r="S205" s="11" t="inlineStr"/>
-      <c r="T205" s="11" t="inlineStr"/>
-      <c r="U205" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V205" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W205" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="206" ht="26" customHeight="1">
-      <c r="A206" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B206" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C206" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D206" s="11" t="inlineStr">
-        <is>
-          <t>20260338841</t>
-        </is>
-      </c>
-      <c r="E206" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F206" s="11" t="inlineStr"/>
-      <c r="G206" s="11" t="inlineStr"/>
-      <c r="H206" s="11" t="inlineStr"/>
-      <c r="I206" s="11" t="inlineStr"/>
-      <c r="J206" s="11" t="inlineStr"/>
-      <c r="K206" s="11" t="inlineStr"/>
-      <c r="L206" s="11" t="inlineStr"/>
-      <c r="M206" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N206" s="11" t="inlineStr"/>
-      <c r="O206" s="11" t="inlineStr"/>
-      <c r="P206" s="11" t="inlineStr"/>
-      <c r="Q206" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R206" s="11" t="inlineStr"/>
-      <c r="S206" s="11" t="inlineStr"/>
-      <c r="T206" s="11" t="inlineStr"/>
-      <c r="U206" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V206" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W206" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="207" ht="26" customHeight="1">
-      <c r="A207" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B207" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C207" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D207" s="11" t="inlineStr">
-        <is>
-          <t>20260338842</t>
-        </is>
-      </c>
-      <c r="E207" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F207" s="11" t="inlineStr"/>
-      <c r="G207" s="11" t="inlineStr"/>
-      <c r="H207" s="11" t="inlineStr"/>
-      <c r="I207" s="11" t="inlineStr"/>
-      <c r="J207" s="11" t="inlineStr"/>
-      <c r="K207" s="11" t="inlineStr"/>
-      <c r="L207" s="11" t="inlineStr"/>
-      <c r="M207" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N207" s="11" t="inlineStr"/>
-      <c r="O207" s="11" t="inlineStr"/>
-      <c r="P207" s="11" t="inlineStr"/>
-      <c r="Q207" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R207" s="11" t="inlineStr"/>
-      <c r="S207" s="11" t="inlineStr"/>
-      <c r="T207" s="11" t="inlineStr"/>
-      <c r="U207" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V207" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W207" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="208" ht="26" customHeight="1">
-      <c r="A208" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B208" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C208" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D208" s="11" t="inlineStr">
-        <is>
-          <t>20260338844</t>
-        </is>
-      </c>
-      <c r="E208" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F208" s="11" t="inlineStr"/>
-      <c r="G208" s="11" t="inlineStr"/>
-      <c r="H208" s="11" t="inlineStr"/>
-      <c r="I208" s="11" t="inlineStr"/>
-      <c r="J208" s="11" t="inlineStr"/>
-      <c r="K208" s="11" t="inlineStr"/>
-      <c r="L208" s="11" t="inlineStr"/>
-      <c r="M208" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N208" s="11" t="inlineStr"/>
-      <c r="O208" s="11" t="inlineStr"/>
-      <c r="P208" s="11" t="inlineStr"/>
-      <c r="Q208" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R208" s="11" t="inlineStr"/>
-      <c r="S208" s="11" t="inlineStr"/>
-      <c r="T208" s="11" t="inlineStr"/>
-      <c r="U208" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V208" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W208" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="209" ht="26" customHeight="1">
-      <c r="A209" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B209" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C209" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D209" s="11" t="inlineStr">
-        <is>
-          <t>20260339014</t>
-        </is>
-      </c>
-      <c r="E209" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F209" s="11" t="inlineStr"/>
-      <c r="G209" s="11" t="inlineStr"/>
-      <c r="H209" s="11" t="inlineStr"/>
-      <c r="I209" s="11" t="inlineStr"/>
-      <c r="J209" s="11" t="inlineStr"/>
-      <c r="K209" s="11" t="inlineStr"/>
-      <c r="L209" s="11" t="inlineStr"/>
-      <c r="M209" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N209" s="11" t="inlineStr"/>
-      <c r="O209" s="11" t="inlineStr"/>
-      <c r="P209" s="11" t="inlineStr"/>
-      <c r="Q209" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R209" s="11" t="inlineStr"/>
-      <c r="S209" s="11" t="inlineStr"/>
-      <c r="T209" s="11" t="inlineStr"/>
-      <c r="U209" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V209" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W209" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="210" ht="26" customHeight="1">
-      <c r="A210" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B210" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C210" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D210" s="11" t="inlineStr">
-        <is>
-          <t>20260339015</t>
-        </is>
-      </c>
-      <c r="E210" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F210" s="11" t="inlineStr"/>
-      <c r="G210" s="11" t="inlineStr"/>
-      <c r="H210" s="11" t="inlineStr"/>
-      <c r="I210" s="11" t="inlineStr"/>
-      <c r="J210" s="11" t="inlineStr"/>
-      <c r="K210" s="11" t="inlineStr"/>
-      <c r="L210" s="11" t="inlineStr"/>
-      <c r="M210" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N210" s="11" t="inlineStr"/>
-      <c r="O210" s="11" t="inlineStr"/>
-      <c r="P210" s="11" t="inlineStr"/>
-      <c r="Q210" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R210" s="11" t="inlineStr"/>
-      <c r="S210" s="11" t="inlineStr"/>
-      <c r="T210" s="11" t="inlineStr"/>
-      <c r="U210" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V210" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W210" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="211" ht="26" customHeight="1">
-      <c r="A211" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B211" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C211" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D211" s="11" t="inlineStr">
-        <is>
-          <t>20260339016</t>
-        </is>
-      </c>
-      <c r="E211" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F211" s="11" t="inlineStr"/>
-      <c r="G211" s="11" t="inlineStr"/>
-      <c r="H211" s="11" t="inlineStr"/>
-      <c r="I211" s="11" t="inlineStr"/>
-      <c r="J211" s="11" t="inlineStr"/>
-      <c r="K211" s="11" t="inlineStr"/>
-      <c r="L211" s="11" t="inlineStr"/>
-      <c r="M211" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N211" s="11" t="inlineStr"/>
-      <c r="O211" s="11" t="inlineStr"/>
-      <c r="P211" s="11" t="inlineStr"/>
-      <c r="Q211" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R211" s="11" t="inlineStr"/>
-      <c r="S211" s="11" t="inlineStr"/>
-      <c r="T211" s="11" t="inlineStr"/>
-      <c r="U211" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V211" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W211" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="212" ht="26" customHeight="1">
-      <c r="A212" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B212" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C212" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D212" s="11" t="inlineStr">
-        <is>
-          <t>20260339017</t>
-        </is>
-      </c>
-      <c r="E212" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F212" s="11" t="inlineStr"/>
-      <c r="G212" s="11" t="inlineStr"/>
-      <c r="H212" s="11" t="inlineStr"/>
-      <c r="I212" s="11" t="inlineStr"/>
-      <c r="J212" s="11" t="inlineStr"/>
-      <c r="K212" s="11" t="inlineStr"/>
-      <c r="L212" s="11" t="inlineStr"/>
-      <c r="M212" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N212" s="11" t="inlineStr"/>
-      <c r="O212" s="11" t="inlineStr"/>
-      <c r="P212" s="11" t="inlineStr"/>
-      <c r="Q212" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R212" s="11" t="inlineStr"/>
-      <c r="S212" s="11" t="inlineStr"/>
-      <c r="T212" s="11" t="inlineStr"/>
-      <c r="U212" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V212" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W212" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="213" ht="26" customHeight="1">
-      <c r="A213" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B213" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C213" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D213" s="11" t="inlineStr">
-        <is>
-          <t>20260339018</t>
-        </is>
-      </c>
-      <c r="E213" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F213" s="11" t="inlineStr"/>
-      <c r="G213" s="11" t="inlineStr"/>
-      <c r="H213" s="11" t="inlineStr"/>
-      <c r="I213" s="11" t="inlineStr"/>
-      <c r="J213" s="11" t="inlineStr"/>
-      <c r="K213" s="11" t="inlineStr"/>
-      <c r="L213" s="11" t="inlineStr"/>
-      <c r="M213" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N213" s="11" t="inlineStr"/>
-      <c r="O213" s="11" t="inlineStr"/>
-      <c r="P213" s="11" t="inlineStr"/>
-      <c r="Q213" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R213" s="11" t="inlineStr"/>
-      <c r="S213" s="11" t="inlineStr"/>
-      <c r="T213" s="11" t="inlineStr"/>
-      <c r="U213" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V213" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W213" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="214" ht="26" customHeight="1">
-      <c r="A214" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B214" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C214" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D214" s="11" t="inlineStr">
-        <is>
-          <t>20260339019</t>
-        </is>
-      </c>
-      <c r="E214" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F214" s="11" t="inlineStr"/>
-      <c r="G214" s="11" t="inlineStr"/>
-      <c r="H214" s="11" t="inlineStr"/>
-      <c r="I214" s="11" t="inlineStr"/>
-      <c r="J214" s="11" t="inlineStr"/>
-      <c r="K214" s="11" t="inlineStr"/>
-      <c r="L214" s="11" t="inlineStr"/>
-      <c r="M214" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N214" s="11" t="inlineStr"/>
-      <c r="O214" s="11" t="inlineStr"/>
-      <c r="P214" s="11" t="inlineStr"/>
-      <c r="Q214" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R214" s="11" t="inlineStr"/>
-      <c r="S214" s="11" t="inlineStr"/>
-      <c r="T214" s="11" t="inlineStr"/>
-      <c r="U214" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V214" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W214" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="215" ht="26" customHeight="1">
-      <c r="A215" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B215" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C215" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D215" s="11" t="inlineStr">
-        <is>
-          <t>20260339292</t>
-        </is>
-      </c>
-      <c r="E215" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F215" s="11" t="inlineStr"/>
-      <c r="G215" s="11" t="inlineStr"/>
-      <c r="H215" s="11" t="inlineStr"/>
-      <c r="I215" s="11" t="inlineStr"/>
-      <c r="J215" s="11" t="inlineStr"/>
-      <c r="K215" s="11" t="inlineStr"/>
-      <c r="L215" s="11" t="inlineStr"/>
-      <c r="M215" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N215" s="11" t="inlineStr"/>
-      <c r="O215" s="11" t="inlineStr"/>
-      <c r="P215" s="11" t="inlineStr"/>
-      <c r="Q215" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R215" s="11" t="inlineStr"/>
-      <c r="S215" s="11" t="inlineStr"/>
-      <c r="T215" s="11" t="inlineStr"/>
-      <c r="U215" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V215" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W215" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="216" ht="26" customHeight="1">
-      <c r="A216" s="10" t="n">
-        <v>41</v>
-      </c>
-      <c r="B216" s="11" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="C216" s="11" t="inlineStr">
-        <is>
-          <t>LN</t>
-        </is>
-      </c>
-      <c r="D216" s="11" t="inlineStr">
-        <is>
-          <t>20260339552</t>
-        </is>
-      </c>
-      <c r="E216" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="F216" s="11" t="inlineStr"/>
-      <c r="G216" s="11" t="inlineStr"/>
-      <c r="H216" s="11" t="inlineStr"/>
-      <c r="I216" s="11" t="inlineStr"/>
-      <c r="J216" s="11" t="inlineStr"/>
-      <c r="K216" s="11" t="inlineStr"/>
-      <c r="L216" s="11" t="inlineStr"/>
-      <c r="M216" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N216" s="11" t="inlineStr"/>
-      <c r="O216" s="11" t="inlineStr"/>
-      <c r="P216" s="11" t="inlineStr"/>
-      <c r="Q216" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R216" s="11" t="inlineStr"/>
-      <c r="S216" s="11" t="inlineStr"/>
-      <c r="T216" s="11" t="inlineStr"/>
-      <c r="U216" s="11" t="inlineStr">
-        <is>
-          <t>Lien; New this week</t>
-        </is>
-      </c>
-      <c r="V216" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W216" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W216"/>
+  <autoFilter ref="A1:W203"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
@@ -15041,19 +14258,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W201" r:id="rId200"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W202" r:id="rId201"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W203" r:id="rId202"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W204" r:id="rId203"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W205" r:id="rId204"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W206" r:id="rId205"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W207" r:id="rId206"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W208" r:id="rId207"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W209" r:id="rId208"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W210" r:id="rId209"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W211" r:id="rId210"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W212" r:id="rId211"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W213" r:id="rId212"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W214" r:id="rId213"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W215" r:id="rId214"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W216" r:id="rId215"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15065,7 +14269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15082,7 +14286,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-06-05 05:22</t>
+          <t>Run: 2026-06-06 04:57</t>
         </is>
       </c>
     </row>
@@ -15097,7 +14301,7 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>215</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5">
@@ -15107,7 +14311,7 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
@@ -15127,7 +14331,7 @@
         </is>
       </c>
       <c r="B7" s="14" t="n">
-        <v>157</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
@@ -15173,86 +14377,76 @@
         </is>
       </c>
       <c r="B12" s="14" t="n">
-        <v>61</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Notice of Trustee Sale</t>
         </is>
       </c>
       <c r="B13" s="14" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>Federal Tax Lien</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="B14" s="14" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="B15" s="14" t="n">
-        <v>35</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="15" t="inlineStr">
         <is>
-          <t>Notice of Trustee Sale</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="B16" s="14" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>Lis Pendens</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="B17" s="14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="15" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="B18" s="14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>State Tax Lien</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="B19" s="14" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>Tax Deed</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="n">
         <v>2</v>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-06-07 05:24</t>
+          <t>Run: 2026-06-08 05:27</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-06-14 05:36</t>
+          <t>Run: 2026-06-15 06:22</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -138,7 +138,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -174,6 +174,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -544,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W178"/>
+  <dimension ref="A1:W144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -705,26 +708,26 @@
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>20260357799</t>
+          <t>20260360864</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>JESSICA JOHANNES AND MATHEW JOHANNES, WIFE AND HUSBAND</t>
+          <t>ABBIE MCDONALD</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>TH MSR Holdings LLC</t>
+          <t>PennyMac Loan Services, LLC</t>
         </is>
       </c>
       <c r="H2" s="4" t="n">
-        <v>641700</v>
+        <v>206196</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
@@ -738,12 +741,12 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>39720 N CENTRAL AVE</t>
+          <t>10027 W ODEUM LN</t>
         </is>
       </c>
       <c r="L2" s="3" t="inlineStr">
         <is>
-          <t>PHOENIX</t>
+          <t>TOLLESON</t>
         </is>
       </c>
       <c r="M2" s="3" t="inlineStr">
@@ -753,7 +756,7 @@
       </c>
       <c r="N2" s="3" t="inlineStr">
         <is>
-          <t>85086</t>
+          <t>85353</t>
         </is>
       </c>
       <c r="O2" s="3" t="inlineStr"/>
@@ -766,7 +769,7 @@
       <c r="R2" s="3" t="inlineStr"/>
       <c r="S2" s="3" t="inlineStr">
         <is>
-          <t>211-73-126</t>
+          <t>101-28-5959</t>
         </is>
       </c>
       <c r="T2" s="3" t="inlineStr">
@@ -806,45 +809,45 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>20260358767</t>
+          <t>20260361172</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>NOAH M ST GEORGE</t>
+          <t>BABAJIDE AJAYI AND GBEMISOLA AJAYI</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>ROUNDPOINT MORTGAGE SERVICING LLC</t>
+          <t>MLD MORTGAGE, INC. DBA THE MONEY STORE</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>142590</v>
+        <v>210000</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
+          <t>Superior Court Building Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>4030 W READE AVE</t>
+          <t>13963 NORTH 132ND LANE</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>PHOENIX</t>
+          <t>SURPRISE</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
@@ -854,7 +857,7 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>85019</t>
+          <t>85379</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr"/>
@@ -865,12 +868,12 @@
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr"/>
-      <c r="S3" s="3" t="inlineStr"/>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>Prime Recon LLC</t>
-        </is>
-      </c>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>501-94-588</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr"/>
       <c r="U3" s="3" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -903,57 +906,49 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>20260359013</t>
+          <t>20260361963</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>ROBERT THOMPSON</t>
+          <t>Conde Rogers</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>WILMINGTON SAVINGS FUND SOCIETY, FSB, NOT IN ITS INDIVIDUAL CAPACITY BUT</t>
+          <t>PrimeLending, a PlainsCapital Company Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>355500</v>
+        <v>468360</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2214 W PARADISE DR</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>PHOENIX</t>
-        </is>
-      </c>
+          <t>4549 E Wescott Dr</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
       <c r="M4" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>85029</t>
-        </is>
-      </c>
+      <c r="N4" s="3" t="inlineStr"/>
       <c r="O4" s="3" t="inlineStr"/>
       <c r="P4" s="3" t="inlineStr"/>
       <c r="Q4" s="3" t="inlineStr">
@@ -962,10 +957,14 @@
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr"/>
-      <c r="S4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>215-01-2583</t>
+        </is>
+      </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>Prime Recon LLC</t>
+          <t>PrimeLending, a PlainsCapital Company Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
@@ -1000,30 +999,30 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>20260359018</t>
+          <t>20260361990</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>JEFFREY A. KIRKLAND AND SHERRY A. KIRKLAND</t>
+          <t>Casandra Cronk</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>AmeriHome Mortgage Company, LLC</t>
+          <t>MidFirst Bank, a federally chartered savings association</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>284000</v>
+        <v>217393</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -1033,12 +1032,12 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>600 SOUTH 9TH STREET</t>
+          <t>6611 W ALTADENA AVE</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>AVONDALE</t>
+          <t>GLENDALE</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
@@ -1048,7 +1047,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>85323</t>
+          <t>85304</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr"/>
@@ -1061,12 +1060,12 @@
       <c r="R5" s="3" t="inlineStr"/>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>500-41-221</t>
+          <t>143-04-196</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>MTC Financial Inc. dba Trustee Corps</t>
+          <t>Larry O. Folks</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -1101,49 +1100,57 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>20260359823</t>
+          <t>20260361993</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Victor Manuel Hernandez and Jesus Ofelia Juarez</t>
+          <t>BRITTAN HOSNER AND KADEN HOSNER, WIFE AND HUSBAND</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>Truist Bank Leonard J. McDonald</t>
+          <t>Lakeview Loan Servicing, LLC</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>247920</v>
+        <v>532000</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>3208 N 109th Dr</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr"/>
+          <t>20408 E ROSA RD</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>QUEEN CREEK</t>
+        </is>
+      </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N6" s="3" t="inlineStr"/>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>85142</t>
+        </is>
+      </c>
       <c r="O6" s="3" t="inlineStr"/>
       <c r="P6" s="3" t="inlineStr"/>
       <c r="Q6" s="3" t="inlineStr">
@@ -1154,12 +1161,12 @@
       <c r="R6" s="3" t="inlineStr"/>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t>102-28-9281</t>
+          <t>314-13-072</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>Truist Bank Leonard J. McDonald</t>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -1194,26 +1201,26 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>20260359837</t>
+          <t>20260362801</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>Kyle Breeze</t>
+          <t>Moises Montes and Jeannette Montes</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>Truist Bank Leonard J. McDonald</t>
+          <t>Primary Residential Mortgage, Inc. Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>386190</v>
+        <v>207900</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
@@ -1227,7 +1234,7 @@
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>17833 W Country Club Ter</t>
+          <t>10918 W Adams St</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr"/>
@@ -1247,12 +1254,12 @@
       <c r="R7" s="3" t="inlineStr"/>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t>503-77-6576</t>
+          <t>101-01-8333</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>Truist Bank Leonard J. McDonald</t>
+          <t>Primary Residential Mortgage, Inc. Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -1287,26 +1294,26 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>20260359843</t>
+          <t>20260362812</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>Candelario Heras Jr</t>
+          <t>Albert L Miller</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo Bank, N.A. Leonard J. McDonald</t>
+          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>137600</v>
+        <v>184800</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
@@ -1320,7 +1327,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>1543 E Apollo Rd</t>
+          <t>8691 E Belleview PI</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr"/>
@@ -1340,12 +1347,12 @@
       <c r="R8" s="3" t="inlineStr"/>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t>114-22-5385</t>
+          <t>131-53-1911</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>Wells Fargo Bank, N.A. Leonard J. McDonald</t>
+          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
@@ -1365,368 +1372,320 @@
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
-      <c r="A9" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="A9" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>20260360018</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr"/>
-      <c r="G9" s="3" t="inlineStr"/>
-      <c r="H9" s="4" t="n">
-        <v>300000</v>
-      </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>20260361190</t>
+        </is>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="F9" s="7" t="inlineStr">
+        <is>
+          <t>AZ 85340</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>Waters Boulevard, Coppell, TX 75019.</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>314204</v>
+      </c>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Superior Court Building</t>
         </is>
       </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>8541 N. 112" Ave.</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>Peoria</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>85345</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr"/>
-      <c r="P9" s="3" t="inlineStr"/>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr"/>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>142-73-818</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr"/>
-      <c r="U9" s="3" t="inlineStr">
+      <c r="K9" s="7" t="inlineStr"/>
+      <c r="L9" s="7" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr"/>
+      <c r="O9" s="7" t="inlineStr"/>
+      <c r="P9" s="7" t="inlineStr"/>
+      <c r="Q9" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R9" s="7" t="inlineStr"/>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>508-12-3629</t>
+        </is>
+      </c>
+      <c r="T9" s="7" t="inlineStr">
+        <is>
+          <t>1253, Phoenix, AZ 85016, (602) 222-5711</t>
+        </is>
+      </c>
+      <c r="U9" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V9" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W9" s="5" t="inlineStr">
+      <c r="V9" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
       </c>
     </row>
     <row r="10" ht="26" customHeight="1">
-      <c r="A10" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="A10" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>20260360132</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
-        <is>
-          <t>Bobby Glass and Cynthia Glass</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>158725</v>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>1082 South 97th Street</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr"/>
-      <c r="O10" s="3" t="inlineStr"/>
-      <c r="P10" s="3" t="inlineStr"/>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr"/>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>220-70-7483</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="U10" s="3" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>20260361244</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee’s Sale Page 1 of 2</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>MO 64131.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="n">
+        <v>270019</v>
+      </c>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="inlineStr"/>
+      <c r="L10" s="7" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr"/>
+      <c r="O10" s="7" t="inlineStr"/>
+      <c r="P10" s="7" t="inlineStr"/>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr"/>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>502-46-3557</t>
+        </is>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
+        <is>
+          <t>1253, Phoenix, AZ 85016, (602) 222-5711</t>
+        </is>
+      </c>
+      <c r="U10" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+        </is>
+      </c>
+      <c r="V10" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>20260362290</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="8" t="n">
+        <v>254375</v>
+      </c>
+      <c r="I11" s="7" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="7" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr"/>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>301-55-7368</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr"/>
+      <c r="U11" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V10" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W10" s="5" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="26" customHeight="1">
-      <c r="A11" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Notice of Trustee Sale</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>NS</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
-        <is>
-          <t>20260360140</t>
-        </is>
-      </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>Maezz Khalid</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>Plains Commerce Bank Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>353600</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>22534 W Pima St</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr"/>
-      <c r="O11" s="3" t="inlineStr"/>
-      <c r="P11" s="3" t="inlineStr"/>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R11" s="3" t="inlineStr"/>
-      <c r="S11" s="3" t="inlineStr">
-        <is>
-          <t>504-21-3755</t>
-        </is>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
-        <is>
-          <t>Plains Commerce Bank Leonard J. McDonald</t>
-        </is>
-      </c>
-      <c r="U11" s="3" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>20260362300</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>C/O M&amp;T Bank</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>517500</v>
+      </c>
+      <c r="I12" s="7" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr"/>
+      <c r="P12" s="7" t="inlineStr"/>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr"/>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>309-23-5807</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr"/>
+      <c r="U12" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
-      <c r="V11" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W11" s="5" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="A12" s="2" t="n">
-        <v>73</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>NS</t>
-        </is>
-      </c>
-      <c r="D12" s="3" t="inlineStr">
-        <is>
-          <t>20260360142</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>JESSICA L ESPERTI AKA JESSICA ESPERTI</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>Lakeview Loan Servicing, LLC By LoanCare, LLC, as Attorney in Fact Under a Limited Power of Attorney</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>261249</v>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t>909 W LEAH LN</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr"/>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr"/>
-      <c r="O12" s="3" t="inlineStr"/>
-      <c r="P12" s="3" t="inlineStr"/>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr"/>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t>302-12-2454</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t>Erin K. Sweeney, a member of the State Bar of Arizona</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W12" s="5" t="inlineStr">
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>View ↗</t>
         </is>
@@ -1748,38 +1707,30 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>20260359281</t>
+          <t>20260362303</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F13" s="7" t="inlineStr">
-        <is>
-          <t>Douglas S. Bruner</t>
-        </is>
-      </c>
-      <c r="G13" s="7" t="inlineStr"/>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>C/O M&amp;T Bank</t>
+        </is>
+      </c>
       <c r="H13" s="8" t="n">
-        <v>78497</v>
-      </c>
-      <c r="I13" s="7" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
+        <v>604000</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr"/>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>Superior Court Building located at 201 West Jefferson</t>
-        </is>
-      </c>
-      <c r="K13" s="7" t="inlineStr">
-        <is>
-          <t>14099 W TWO GUNS TRL</t>
-        </is>
-      </c>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr"/>
       <c r="L13" s="7" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr">
         <is>
@@ -1795,7 +1746,11 @@
         </is>
       </c>
       <c r="R13" s="7" t="inlineStr"/>
-      <c r="S13" s="7" t="inlineStr"/>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>201-15-3442</t>
+        </is>
+      </c>
       <c r="T13" s="7" t="inlineStr"/>
       <c r="U13" s="7" t="inlineStr">
         <is>
@@ -1829,38 +1784,30 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>20260359694</t>
+          <t>20260362304</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>Narciso Gutierrez Lopez</t>
-        </is>
-      </c>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr"/>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>14001 N. 34" Street</t>
+          <t>C/O JPMorgan Chase Bank, N.A.</t>
         </is>
       </c>
       <c r="H14" s="8" t="n">
-        <v>73000</v>
+        <v>178000</v>
       </c>
       <c r="I14" s="7" t="inlineStr"/>
       <c r="J14" s="7" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
-        </is>
-      </c>
-      <c r="K14" s="7" t="inlineStr">
-        <is>
-          <t>3029 West Montebello Avenue</t>
-        </is>
-      </c>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr"/>
       <c r="L14" s="7" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr">
         <is>
@@ -1878,7 +1825,7 @@
       <c r="R14" s="7" t="inlineStr"/>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>153-14-014</t>
+          <t>160-06-0519</t>
         </is>
       </c>
       <c r="T14" s="7" t="inlineStr"/>
@@ -1914,42 +1861,30 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>20260359851</t>
+          <t>20260362307</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Paul G. Gagnon</t>
-        </is>
-      </c>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr"/>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>Johnson Bank Leonard J. McDonald</t>
+          <t>C/O MidFirst Bank</t>
         </is>
       </c>
       <c r="H15" s="8" t="n">
-        <v>99000</v>
-      </c>
-      <c r="I15" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
+        <v>250871</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr"/>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>Superior Court Building of the Maricopa County Courthouse</t>
-        </is>
-      </c>
-      <c r="K15" s="7" t="inlineStr">
-        <is>
-          <t>2623 N Jay St</t>
-        </is>
-      </c>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr"/>
       <c r="L15" s="7" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr">
         <is>
@@ -1967,14 +1902,10 @@
       <c r="R15" s="7" t="inlineStr"/>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>302-26-1219</t>
-        </is>
-      </c>
-      <c r="T15" s="7" t="inlineStr">
-        <is>
-          <t>Johnson Bank Leonard J. McDonald</t>
-        </is>
-      </c>
+          <t>104-77-7378</t>
+        </is>
+      </c>
+      <c r="T15" s="7" t="inlineStr"/>
       <c r="U15" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2007,27 +1938,27 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>20260359896</t>
+          <t>20260362675</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr"/>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>C/O Wells Fargo Bank, N.A.</t>
+          <t>C/O LoanCare, LLC</t>
         </is>
       </c>
       <c r="H16" s="8" t="n">
-        <v>900000</v>
+        <v>201286</v>
       </c>
       <c r="I16" s="7" t="inlineStr"/>
       <c r="J16" s="7" t="inlineStr">
         <is>
-          <t>Superior Courts Building. Maricopa County</t>
+          <t>Superior Courts Building</t>
         </is>
       </c>
       <c r="K16" s="7" t="inlineStr"/>
@@ -2048,7 +1979,7 @@
       <c r="R16" s="7" t="inlineStr"/>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>301-76-8746</t>
+          <t>145-27-329</t>
         </is>
       </c>
       <c r="T16" s="7" t="inlineStr"/>
@@ -2070,7 +2001,7 @@
     </row>
     <row r="17" ht="26" customHeight="1">
       <c r="A17" s="6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
@@ -2084,23 +2015,27 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>20260359119</t>
+          <t>20260363227</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>C/O Fay Servicing, LLC</t>
+        </is>
+      </c>
       <c r="H17" s="8" t="n">
-        <v>63574</v>
+        <v>416000</v>
       </c>
       <c r="I17" s="7" t="inlineStr"/>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>Superior Courts Building. Maricopa County</t>
+          <t>Superior Court Building</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr"/>
@@ -2121,7 +2056,7 @@
       <c r="R17" s="7" t="inlineStr"/>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>149-27-2291</t>
+          <t>200-62-154</t>
         </is>
       </c>
       <c r="T17" s="7" t="inlineStr"/>
@@ -2143,7 +2078,7 @@
     </row>
     <row r="18" ht="26" customHeight="1">
       <c r="A18" s="6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
@@ -2157,27 +2092,27 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>20260359892</t>
+          <t>20260363228</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr"/>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>C/O Bank of America, N.A.</t>
+          <t>C/O Freedom Mortgage Corporation</t>
         </is>
       </c>
       <c r="H18" s="8" t="n">
-        <v>71000</v>
+        <v>236408</v>
       </c>
       <c r="I18" s="7" t="inlineStr"/>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>Superior Courts Building</t>
         </is>
       </c>
       <c r="K18" s="7" t="inlineStr"/>
@@ -2198,7 +2133,7 @@
       <c r="R18" s="7" t="inlineStr"/>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>302-89-3667</t>
+          <t>148-19-171</t>
         </is>
       </c>
       <c r="T18" s="7" t="inlineStr"/>
@@ -2220,7 +2155,7 @@
     </row>
     <row r="19" ht="26" customHeight="1">
       <c r="A19" s="6" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
@@ -2234,23 +2169,27 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>20260360406</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr"/>
+          <t>20260363302</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
       <c r="F19" s="7" t="inlineStr"/>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>liability company, 11333 Moorpark Street, Suite 123, Studio City, CA 91602.</t>
         </is>
       </c>
       <c r="H19" s="8" t="n">
-        <v>306900</v>
+        <v>200000</v>
       </c>
       <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>SUPERIOR COURT BUILDING</t>
         </is>
       </c>
       <c r="K19" s="7" t="inlineStr"/>
@@ -2271,13 +2210,13 @@
       <c r="R19" s="7" t="inlineStr"/>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>200-92-150</t>
+          <t>301-29-550</t>
         </is>
       </c>
       <c r="T19" s="7" t="inlineStr"/>
       <c r="U19" s="7" t="inlineStr">
         <is>
-          <t>Pre-foreclosure; Trustee Sale</t>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
         </is>
       </c>
       <c r="V19" s="7" t="inlineStr">
@@ -2293,7 +2232,7 @@
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="6" t="n">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
@@ -2307,36 +2246,30 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>20260358192</t>
+          <t>20260363303</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>LYDIA R OUTRIDGE AND NIXON A BENJAMIN</t>
-        </is>
-      </c>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>LAKEVIEW LOAN SERVICING, LLC</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr"/>
+          <t>limited liability company, (by assignment), 14555 N. Scottsdale Rd. #200 Scottsdale, AZ</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>205000</v>
+      </c>
       <c r="I20" s="7" t="inlineStr"/>
       <c r="J20" s="7" t="inlineStr">
         <is>
           <t>SUPERIOR COURT BUILDING</t>
         </is>
       </c>
-      <c r="K20" s="7" t="inlineStr">
-        <is>
-          <t>4210 S 94TH DR</t>
-        </is>
-      </c>
+      <c r="K20" s="7" t="inlineStr"/>
       <c r="L20" s="7" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr">
         <is>
@@ -2354,14 +2287,10 @@
       <c r="R20" s="7" t="inlineStr"/>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>101-31-343</t>
-        </is>
-      </c>
-      <c r="T20" s="7" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
+          <t>108-19-087</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr"/>
       <c r="U20" s="7" t="inlineStr">
         <is>
           <t>Pre-foreclosure; Trustee Sale; New this week</t>
@@ -2380,57 +2309,57 @@
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="6" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Notice of Trustee Sale</t>
+          <t>Judgment</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>NS</t>
+          <t>JG</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>20260358216</t>
+          <t>20260362984</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>JOHANNA AYDEE LEDEZMA AND ANDREW DIAZ</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>PennyMac Loan Services, LLC</t>
-        </is>
-      </c>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
       <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="7" t="inlineStr"/>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>Superior Court Building</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K21" s="7" t="inlineStr">
         <is>
-          <t>18161 WEST RAYMOND ST</t>
-        </is>
-      </c>
-      <c r="L21" s="7" t="inlineStr"/>
+          <t>5215 West Western Star Boulevard</t>
+        </is>
+      </c>
+      <c r="L21" s="7" t="inlineStr">
+        <is>
+          <t>Laveen</t>
+        </is>
+      </c>
       <c r="M21" s="7" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="N21" s="7" t="inlineStr"/>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>85339</t>
+        </is>
+      </c>
       <c r="O21" s="7" t="inlineStr"/>
       <c r="P21" s="7" t="inlineStr"/>
       <c r="Q21" s="7" t="inlineStr">
@@ -2441,17 +2370,13 @@
       <c r="R21" s="7" t="inlineStr"/>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>502-45-383</t>
-        </is>
-      </c>
-      <c r="T21" s="7" t="inlineStr">
-        <is>
-          <t>Clear Recon Corp</t>
-        </is>
-      </c>
+          <t>300-06-38222</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr"/>
       <c r="U21" s="7" t="inlineStr">
         <is>
-          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+          <t>Judgment lien; New this week</t>
         </is>
       </c>
       <c r="V21" s="7" t="inlineStr">
@@ -2467,45 +2392,41 @@
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="6" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>20260359254</t>
+          <t>20260363182</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
       <c r="G22" s="7" t="inlineStr"/>
       <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr"/>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>Superior Court</t>
-        </is>
-      </c>
+      <c r="J22" s="7" t="inlineStr"/>
       <c r="K22" s="7" t="inlineStr">
         <is>
-          <t>12930 West Soledad Street</t>
+          <t>1654 E Draper Cir</t>
         </is>
       </c>
       <c r="L22" s="7" t="inlineStr">
         <is>
-          <t>El Mirage</t>
+          <t>Mesa</t>
         </is>
       </c>
       <c r="M22" s="7" t="inlineStr">
@@ -2515,7 +2436,7 @@
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>85335</t>
+          <t>85203</t>
         </is>
       </c>
       <c r="O22" s="7" t="inlineStr"/>
@@ -2526,15 +2447,11 @@
         </is>
       </c>
       <c r="R22" s="7" t="inlineStr"/>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>501-37-24917</t>
-        </is>
-      </c>
+      <c r="S22" s="7" t="inlineStr"/>
       <c r="T22" s="7" t="inlineStr"/>
       <c r="U22" s="7" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V22" s="7" t="inlineStr">
@@ -2550,38 +2467,38 @@
     </row>
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>Lien</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
         <is>
-          <t>LN</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>20260358237</t>
+          <t>20260361896</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F23" s="11" t="inlineStr"/>
       <c r="G23" s="11" t="inlineStr"/>
       <c r="H23" s="11" t="inlineStr"/>
       <c r="I23" s="11" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr">
-        <is>
-          <t>13011 W RAMPART DR</t>
-        </is>
-      </c>
+      <c r="J23" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr"/>
       <c r="L23" s="11" t="inlineStr"/>
       <c r="M23" s="11" t="inlineStr">
         <is>
@@ -2601,7 +2518,7 @@
       <c r="T23" s="11" t="inlineStr"/>
       <c r="U23" s="11" t="inlineStr">
         <is>
-          <t>Lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V23" s="11" t="inlineStr">
@@ -2621,22 +2538,22 @@
       </c>
       <c r="B24" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>20260357454</t>
+          <t>20260361897</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F24" s="11" t="inlineStr"/>
@@ -2668,7 +2585,7 @@
       <c r="T24" s="11" t="inlineStr"/>
       <c r="U24" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V24" s="11" t="inlineStr">
@@ -2688,22 +2605,22 @@
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D25" s="11" t="inlineStr">
         <is>
-          <t>20260357456</t>
+          <t>20260361900</t>
         </is>
       </c>
       <c r="E25" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F25" s="11" t="inlineStr"/>
@@ -2712,7 +2629,7 @@
       <c r="I25" s="11" t="inlineStr"/>
       <c r="J25" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr"/>
@@ -2731,15 +2648,11 @@
         </is>
       </c>
       <c r="R25" s="11" t="inlineStr"/>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>102-45-217217</t>
-        </is>
-      </c>
+      <c r="S25" s="11" t="inlineStr"/>
       <c r="T25" s="11" t="inlineStr"/>
       <c r="U25" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V25" s="11" t="inlineStr">
@@ -2759,22 +2672,22 @@
       </c>
       <c r="B26" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D26" s="11" t="inlineStr">
         <is>
-          <t>20260357458</t>
+          <t>20260361901</t>
         </is>
       </c>
       <c r="E26" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F26" s="11" t="inlineStr"/>
@@ -2783,7 +2696,7 @@
       <c r="I26" s="11" t="inlineStr"/>
       <c r="J26" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K26" s="11" t="inlineStr"/>
@@ -2802,15 +2715,11 @@
         </is>
       </c>
       <c r="R26" s="11" t="inlineStr"/>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>300-52-072177</t>
-        </is>
-      </c>
+      <c r="S26" s="11" t="inlineStr"/>
       <c r="T26" s="11" t="inlineStr"/>
       <c r="U26" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V26" s="11" t="inlineStr">
@@ -2830,22 +2739,22 @@
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D27" s="11" t="inlineStr">
         <is>
-          <t>20260357541</t>
+          <t>20260361906</t>
         </is>
       </c>
       <c r="E27" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F27" s="11" t="inlineStr"/>
@@ -2877,7 +2786,7 @@
       <c r="T27" s="11" t="inlineStr"/>
       <c r="U27" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V27" s="11" t="inlineStr">
@@ -2897,22 +2806,22 @@
       </c>
       <c r="B28" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D28" s="11" t="inlineStr">
         <is>
-          <t>20260357819</t>
+          <t>20260362144</t>
         </is>
       </c>
       <c r="E28" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F28" s="11" t="inlineStr"/>
@@ -2921,7 +2830,7 @@
       <c r="I28" s="11" t="inlineStr"/>
       <c r="J28" s="11" t="inlineStr">
         <is>
-          <t>Superior Court/Case No. CV2026-015633</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr"/>
@@ -2944,7 +2853,7 @@
       <c r="T28" s="11" t="inlineStr"/>
       <c r="U28" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V28" s="11" t="inlineStr">
@@ -2964,22 +2873,22 @@
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D29" s="11" t="inlineStr">
         <is>
-          <t>20260357856</t>
+          <t>20260362439</t>
         </is>
       </c>
       <c r="E29" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F29" s="11" t="inlineStr"/>
@@ -2988,7 +2897,7 @@
       <c r="I29" s="11" t="inlineStr"/>
       <c r="J29" s="11" t="inlineStr">
         <is>
-          <t>Superior Court/Case No. CV2025-064504</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr"/>
@@ -3011,7 +2920,7 @@
       <c r="T29" s="11" t="inlineStr"/>
       <c r="U29" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V29" s="11" t="inlineStr">
@@ -3031,22 +2940,22 @@
       </c>
       <c r="B30" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D30" s="11" t="inlineStr">
         <is>
-          <t>20260358046</t>
+          <t>20260363064</t>
         </is>
       </c>
       <c r="E30" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F30" s="11" t="inlineStr"/>
@@ -3055,7 +2964,7 @@
       <c r="I30" s="11" t="inlineStr"/>
       <c r="J30" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr"/>
@@ -3078,7 +2987,7 @@
       <c r="T30" s="11" t="inlineStr"/>
       <c r="U30" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V30" s="11" t="inlineStr">
@@ -3098,22 +3007,22 @@
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D31" s="11" t="inlineStr">
         <is>
-          <t>20260358460</t>
+          <t>20260363077</t>
         </is>
       </c>
       <c r="E31" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F31" s="11" t="inlineStr"/>
@@ -3122,7 +3031,7 @@
       <c r="I31" s="11" t="inlineStr"/>
       <c r="J31" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K31" s="11" t="inlineStr"/>
@@ -3145,7 +3054,7 @@
       <c r="T31" s="11" t="inlineStr"/>
       <c r="U31" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V31" s="11" t="inlineStr">
@@ -3165,22 +3074,22 @@
       </c>
       <c r="B32" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Lis Pendens</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>LP</t>
         </is>
       </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
-          <t>20260359021</t>
+          <t>20260363234</t>
         </is>
       </c>
       <c r="E32" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F32" s="11" t="inlineStr"/>
@@ -3189,7 +3098,7 @@
       <c r="I32" s="11" t="inlineStr"/>
       <c r="J32" s="11" t="inlineStr">
         <is>
-          <t>Superior Court</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr"/>
@@ -3212,7 +3121,7 @@
       <c r="T32" s="11" t="inlineStr"/>
       <c r="U32" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Lis pendens; New this week</t>
         </is>
       </c>
       <c r="V32" s="11" t="inlineStr">
@@ -3242,12 +3151,12 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>20260359593</t>
+          <t>20260360798</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F33" s="11" t="inlineStr"/>
@@ -3256,7 +3165,7 @@
       <c r="I33" s="11" t="inlineStr"/>
       <c r="J33" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>Superior Court Case No. CV2025-066546</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr"/>
@@ -3309,12 +3218,12 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>20260359594</t>
+          <t>20260361055</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F34" s="11" t="inlineStr"/>
@@ -3323,7 +3232,7 @@
       <c r="I34" s="11" t="inlineStr"/>
       <c r="J34" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+          <t>SUPERIOR COURT a</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr"/>
@@ -3376,12 +3285,12 @@
       </c>
       <c r="D35" s="11" t="inlineStr">
         <is>
-          <t>20260359611</t>
+          <t>20260361056</t>
         </is>
       </c>
       <c r="E35" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F35" s="11" t="inlineStr"/>
@@ -3443,23 +3352,19 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>20260359875</t>
+          <t>20260361348</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F36" s="11" t="inlineStr"/>
       <c r="G36" s="11" t="inlineStr"/>
       <c r="H36" s="11" t="inlineStr"/>
       <c r="I36" s="11" t="inlineStr"/>
-      <c r="J36" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J36" s="11" t="inlineStr"/>
       <c r="K36" s="11" t="inlineStr"/>
       <c r="L36" s="11" t="inlineStr"/>
       <c r="M36" s="11" t="inlineStr">
@@ -3510,12 +3415,12 @@
       </c>
       <c r="D37" s="11" t="inlineStr">
         <is>
-          <t>20260359909</t>
+          <t>20260361899</t>
         </is>
       </c>
       <c r="E37" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F37" s="11" t="inlineStr"/>
@@ -3524,7 +3429,7 @@
       <c r="I37" s="11" t="inlineStr"/>
       <c r="J37" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr"/>
@@ -3543,7 +3448,11 @@
         </is>
       </c>
       <c r="R37" s="11" t="inlineStr"/>
-      <c r="S37" s="11" t="inlineStr"/>
+      <c r="S37" s="11" t="inlineStr">
+        <is>
+          <t>102-45-217177</t>
+        </is>
+      </c>
       <c r="T37" s="11" t="inlineStr"/>
       <c r="U37" s="11" t="inlineStr">
         <is>
@@ -3577,12 +3486,12 @@
       </c>
       <c r="D38" s="11" t="inlineStr">
         <is>
-          <t>20260360151</t>
+          <t>20260362425</t>
         </is>
       </c>
       <c r="E38" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F38" s="11" t="inlineStr"/>
@@ -3591,7 +3500,7 @@
       <c r="I38" s="11" t="inlineStr"/>
       <c r="J38" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT</t>
+          <t>Superior Court of the State of Arizona</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr"/>
@@ -3644,12 +3553,12 @@
       </c>
       <c r="D39" s="11" t="inlineStr">
         <is>
-          <t>20260360280</t>
+          <t>20260362657</t>
         </is>
       </c>
       <c r="E39" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F39" s="11" t="inlineStr"/>
@@ -3658,7 +3567,7 @@
       <c r="I39" s="11" t="inlineStr"/>
       <c r="J39" s="11" t="inlineStr">
         <is>
-          <t>Superior Court in Maricopa County.</t>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr"/>
@@ -3711,12 +3620,12 @@
       </c>
       <c r="D40" s="11" t="inlineStr">
         <is>
-          <t>20260360329</t>
+          <t>20260362660</t>
         </is>
       </c>
       <c r="E40" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F40" s="11" t="inlineStr"/>
@@ -3778,12 +3687,12 @@
       </c>
       <c r="D41" s="11" t="inlineStr">
         <is>
-          <t>20260360367</t>
+          <t>20260362731</t>
         </is>
       </c>
       <c r="E41" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F41" s="11" t="inlineStr"/>
@@ -3792,7 +3701,7 @@
       <c r="I41" s="11" t="inlineStr"/>
       <c r="J41" s="11" t="inlineStr">
         <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
+          <t>Superior Court</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr"/>
@@ -3845,19 +3754,23 @@
       </c>
       <c r="D42" s="11" t="inlineStr">
         <is>
-          <t>20260360369</t>
+          <t>20260362732</t>
         </is>
       </c>
       <c r="E42" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F42" s="11" t="inlineStr"/>
       <c r="G42" s="11" t="inlineStr"/>
       <c r="H42" s="11" t="inlineStr"/>
       <c r="I42" s="11" t="inlineStr"/>
-      <c r="J42" s="11" t="inlineStr"/>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
       <c r="K42" s="11" t="inlineStr"/>
       <c r="L42" s="11" t="inlineStr"/>
       <c r="M42" s="11" t="inlineStr">
@@ -3908,19 +3821,23 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>20260360370</t>
+          <t>20260363076</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F43" s="11" t="inlineStr"/>
       <c r="G43" s="11" t="inlineStr"/>
       <c r="H43" s="11" t="inlineStr"/>
       <c r="I43" s="11" t="inlineStr"/>
-      <c r="J43" s="11" t="inlineStr"/>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K43" s="11" t="inlineStr"/>
       <c r="L43" s="11" t="inlineStr"/>
       <c r="M43" s="11" t="inlineStr">
@@ -3971,19 +3888,23 @@
       </c>
       <c r="D44" s="11" t="inlineStr">
         <is>
-          <t>20260360371</t>
+          <t>20260363259</t>
         </is>
       </c>
       <c r="E44" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F44" s="11" t="inlineStr"/>
       <c r="G44" s="11" t="inlineStr"/>
       <c r="H44" s="11" t="inlineStr"/>
       <c r="I44" s="11" t="inlineStr"/>
-      <c r="J44" s="11" t="inlineStr"/>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
       <c r="K44" s="11" t="inlineStr"/>
       <c r="L44" s="11" t="inlineStr"/>
       <c r="M44" s="11" t="inlineStr">
@@ -4020,26 +3941,26 @@
     </row>
     <row r="45" ht="26" customHeight="1">
       <c r="A45" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>20260360372</t>
+          <t>20260360869</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F45" s="11" t="inlineStr"/>
@@ -4063,11 +3984,15 @@
         </is>
       </c>
       <c r="R45" s="11" t="inlineStr"/>
-      <c r="S45" s="11" t="inlineStr"/>
+      <c r="S45" s="11" t="inlineStr">
+        <is>
+          <t>121-62-041</t>
+        </is>
+      </c>
       <c r="T45" s="11" t="inlineStr"/>
       <c r="U45" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V45" s="11" t="inlineStr">
@@ -4083,37 +4008,33 @@
     </row>
     <row r="46" ht="26" customHeight="1">
       <c r="A46" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C46" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>20260360375</t>
+          <t>20260361870</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F46" s="11" t="inlineStr"/>
       <c r="G46" s="11" t="inlineStr"/>
       <c r="H46" s="11" t="inlineStr"/>
       <c r="I46" s="11" t="inlineStr"/>
-      <c r="J46" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J46" s="11" t="inlineStr"/>
       <c r="K46" s="11" t="inlineStr"/>
       <c r="L46" s="11" t="inlineStr"/>
       <c r="M46" s="11" t="inlineStr">
@@ -4134,7 +4055,7 @@
       <c r="T46" s="11" t="inlineStr"/>
       <c r="U46" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V46" s="11" t="inlineStr">
@@ -4150,37 +4071,35 @@
     </row>
     <row r="47" ht="26" customHeight="1">
       <c r="A47" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C47" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>20260360376</t>
+          <t>20260361949</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F47" s="11" t="inlineStr"/>
       <c r="G47" s="11" t="inlineStr"/>
-      <c r="H47" s="11" t="inlineStr"/>
+      <c r="H47" s="13" t="n">
+        <v>17866.28</v>
+      </c>
       <c r="I47" s="11" t="inlineStr"/>
-      <c r="J47" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J47" s="11" t="inlineStr"/>
       <c r="K47" s="11" t="inlineStr"/>
       <c r="L47" s="11" t="inlineStr"/>
       <c r="M47" s="11" t="inlineStr">
@@ -4197,11 +4116,15 @@
         </is>
       </c>
       <c r="R47" s="11" t="inlineStr"/>
-      <c r="S47" s="11" t="inlineStr"/>
+      <c r="S47" s="11" t="inlineStr">
+        <is>
+          <t>140-67-003</t>
+        </is>
+      </c>
       <c r="T47" s="11" t="inlineStr"/>
       <c r="U47" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V47" s="11" t="inlineStr">
@@ -4217,37 +4140,33 @@
     </row>
     <row r="48" ht="26" customHeight="1">
       <c r="A48" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C48" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D48" s="11" t="inlineStr">
         <is>
-          <t>20260360377</t>
+          <t>20260361996</t>
         </is>
       </c>
       <c r="E48" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F48" s="11" t="inlineStr"/>
       <c r="G48" s="11" t="inlineStr"/>
       <c r="H48" s="11" t="inlineStr"/>
       <c r="I48" s="11" t="inlineStr"/>
-      <c r="J48" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J48" s="11" t="inlineStr"/>
       <c r="K48" s="11" t="inlineStr"/>
       <c r="L48" s="11" t="inlineStr"/>
       <c r="M48" s="11" t="inlineStr">
@@ -4268,7 +4187,7 @@
       <c r="T48" s="11" t="inlineStr"/>
       <c r="U48" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V48" s="11" t="inlineStr">
@@ -4284,37 +4203,33 @@
     </row>
     <row r="49" ht="26" customHeight="1">
       <c r="A49" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Judgment</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C49" s="11" t="inlineStr">
         <is>
-          <t>JG</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D49" s="11" t="inlineStr">
         <is>
-          <t>20260360379</t>
+          <t>20260363072</t>
         </is>
       </c>
       <c r="E49" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F49" s="11" t="inlineStr"/>
       <c r="G49" s="11" t="inlineStr"/>
       <c r="H49" s="11" t="inlineStr"/>
       <c r="I49" s="11" t="inlineStr"/>
-      <c r="J49" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J49" s="11" t="inlineStr"/>
       <c r="K49" s="11" t="inlineStr"/>
       <c r="L49" s="11" t="inlineStr"/>
       <c r="M49" s="11" t="inlineStr">
@@ -4335,7 +4250,7 @@
       <c r="T49" s="11" t="inlineStr"/>
       <c r="U49" s="11" t="inlineStr">
         <is>
-          <t>Judgment lien; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V49" s="11" t="inlineStr">
@@ -4351,37 +4266,33 @@
     </row>
     <row r="50" ht="26" customHeight="1">
       <c r="A50" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C50" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>20260358160</t>
+          <t>20260363190</t>
         </is>
       </c>
       <c r="E50" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F50" s="11" t="inlineStr"/>
       <c r="G50" s="11" t="inlineStr"/>
       <c r="H50" s="11" t="inlineStr"/>
       <c r="I50" s="11" t="inlineStr"/>
-      <c r="J50" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT</t>
-        </is>
-      </c>
+      <c r="J50" s="11" t="inlineStr"/>
       <c r="K50" s="11" t="inlineStr"/>
       <c r="L50" s="11" t="inlineStr"/>
       <c r="M50" s="11" t="inlineStr">
@@ -4402,7 +4313,7 @@
       <c r="T50" s="11" t="inlineStr"/>
       <c r="U50" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V50" s="11" t="inlineStr">
@@ -4418,37 +4329,33 @@
     </row>
     <row r="51" ht="26" customHeight="1">
       <c r="A51" s="10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Mechanic Lien</t>
         </is>
       </c>
       <c r="C51" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>ML</t>
         </is>
       </c>
       <c r="D51" s="11" t="inlineStr">
         <is>
-          <t>20260358298</t>
+          <t>20260363194</t>
         </is>
       </c>
       <c r="E51" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F51" s="11" t="inlineStr"/>
       <c r="G51" s="11" t="inlineStr"/>
       <c r="H51" s="11" t="inlineStr"/>
       <c r="I51" s="11" t="inlineStr"/>
-      <c r="J51" s="11" t="inlineStr">
-        <is>
-          <t>SUPERIOR COURT OF ARIZONA</t>
-        </is>
-      </c>
+      <c r="J51" s="11" t="inlineStr"/>
       <c r="K51" s="11" t="inlineStr"/>
       <c r="L51" s="11" t="inlineStr"/>
       <c r="M51" s="11" t="inlineStr">
@@ -4465,11 +4372,15 @@
         </is>
       </c>
       <c r="R51" s="11" t="inlineStr"/>
-      <c r="S51" s="11" t="inlineStr"/>
+      <c r="S51" s="11" t="inlineStr">
+        <is>
+          <t>167-12-204</t>
+        </is>
+      </c>
       <c r="T51" s="11" t="inlineStr"/>
       <c r="U51" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Mechanic lien; New this week</t>
         </is>
       </c>
       <c r="V51" s="11" t="inlineStr">
@@ -4489,22 +4400,22 @@
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C52" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D52" s="11" t="inlineStr">
         <is>
-          <t>20260357386</t>
+          <t>20260361849</t>
         </is>
       </c>
       <c r="E52" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F52" s="11" t="inlineStr"/>
@@ -4532,12 +4443,12 @@
       <c r="T52" s="11" t="inlineStr"/>
       <c r="U52" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V52" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W52" s="12" t="inlineStr">
@@ -4552,22 +4463,22 @@
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Tax Deed</t>
         </is>
       </c>
       <c r="C53" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D53" s="11" t="inlineStr">
         <is>
-          <t>20260357387</t>
+          <t>20260362746</t>
         </is>
       </c>
       <c r="E53" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F53" s="11" t="inlineStr"/>
@@ -4595,12 +4506,12 @@
       <c r="T53" s="11" t="inlineStr"/>
       <c r="U53" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Tax deed; New this week</t>
         </is>
       </c>
       <c r="V53" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W53" s="12" t="inlineStr">
@@ -4615,22 +4526,22 @@
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C54" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D54" s="11" t="inlineStr">
         <is>
-          <t>20260357388</t>
+          <t>20260361039</t>
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F54" s="11" t="inlineStr"/>
@@ -4658,12 +4569,12 @@
       <c r="T54" s="11" t="inlineStr"/>
       <c r="U54" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V54" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W54" s="12" t="inlineStr">
@@ -4678,22 +4589,22 @@
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C55" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D55" s="11" t="inlineStr">
         <is>
-          <t>20260357390</t>
+          <t>20260361659</t>
         </is>
       </c>
       <c r="E55" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F55" s="11" t="inlineStr"/>
@@ -4721,12 +4632,12 @@
       <c r="T55" s="11" t="inlineStr"/>
       <c r="U55" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V55" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W55" s="12" t="inlineStr">
@@ -4741,22 +4652,22 @@
       </c>
       <c r="B56" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C56" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D56" s="11" t="inlineStr">
         <is>
-          <t>20260357391</t>
+          <t>20260361883</t>
         </is>
       </c>
       <c r="E56" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F56" s="11" t="inlineStr"/>
@@ -4784,12 +4695,12 @@
       <c r="T56" s="11" t="inlineStr"/>
       <c r="U56" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V56" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W56" s="12" t="inlineStr">
@@ -4804,22 +4715,22 @@
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C57" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D57" s="11" t="inlineStr">
         <is>
-          <t>20260357392</t>
+          <t>20260362027</t>
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F57" s="11" t="inlineStr"/>
@@ -4847,12 +4758,12 @@
       <c r="T57" s="11" t="inlineStr"/>
       <c r="U57" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V57" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W57" s="12" t="inlineStr">
@@ -4867,22 +4778,22 @@
       </c>
       <c r="B58" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Probate Document</t>
         </is>
       </c>
       <c r="C58" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>PJ</t>
         </is>
       </c>
       <c r="D58" s="11" t="inlineStr">
         <is>
-          <t>20260357393</t>
+          <t>20260362699</t>
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F58" s="11" t="inlineStr"/>
@@ -4910,12 +4821,12 @@
       <c r="T58" s="11" t="inlineStr"/>
       <c r="U58" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Probate / estate; New this week</t>
         </is>
       </c>
       <c r="V58" s="11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W58" s="12" t="inlineStr">
@@ -4926,26 +4837,26 @@
     </row>
     <row r="59" ht="26" customHeight="1">
       <c r="A59" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C59" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D59" s="11" t="inlineStr">
         <is>
-          <t>20260357394</t>
+          <t>20260361166</t>
         </is>
       </c>
       <c r="E59" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F59" s="11" t="inlineStr"/>
@@ -4973,7 +4884,7 @@
       <c r="T59" s="11" t="inlineStr"/>
       <c r="U59" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V59" s="11" t="inlineStr">
@@ -4989,26 +4900,26 @@
     </row>
     <row r="60" ht="26" customHeight="1">
       <c r="A60" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C60" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D60" s="11" t="inlineStr">
         <is>
-          <t>20260357395</t>
+          <t>20260361207</t>
         </is>
       </c>
       <c r="E60" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F60" s="11" t="inlineStr"/>
@@ -5036,7 +4947,7 @@
       <c r="T60" s="11" t="inlineStr"/>
       <c r="U60" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V60" s="11" t="inlineStr">
@@ -5052,26 +4963,26 @@
     </row>
     <row r="61" ht="26" customHeight="1">
       <c r="A61" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C61" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D61" s="11" t="inlineStr">
         <is>
-          <t>20260357396</t>
+          <t>20260361306</t>
         </is>
       </c>
       <c r="E61" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F61" s="11" t="inlineStr"/>
@@ -5099,7 +5010,7 @@
       <c r="T61" s="11" t="inlineStr"/>
       <c r="U61" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V61" s="11" t="inlineStr">
@@ -5115,26 +5026,26 @@
     </row>
     <row r="62" ht="26" customHeight="1">
       <c r="A62" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B62" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C62" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D62" s="11" t="inlineStr">
         <is>
-          <t>20260357397</t>
+          <t>20260361483</t>
         </is>
       </c>
       <c r="E62" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F62" s="11" t="inlineStr"/>
@@ -5162,7 +5073,7 @@
       <c r="T62" s="11" t="inlineStr"/>
       <c r="U62" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V62" s="11" t="inlineStr">
@@ -5178,26 +5089,26 @@
     </row>
     <row r="63" ht="26" customHeight="1">
       <c r="A63" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C63" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D63" s="11" t="inlineStr">
         <is>
-          <t>20260357398</t>
+          <t>20260361487</t>
         </is>
       </c>
       <c r="E63" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F63" s="11" t="inlineStr"/>
@@ -5225,7 +5136,7 @@
       <c r="T63" s="11" t="inlineStr"/>
       <c r="U63" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V63" s="11" t="inlineStr">
@@ -5241,26 +5152,26 @@
     </row>
     <row r="64" ht="26" customHeight="1">
       <c r="A64" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B64" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C64" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D64" s="11" t="inlineStr">
         <is>
-          <t>20260357399</t>
+          <t>20260361488</t>
         </is>
       </c>
       <c r="E64" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F64" s="11" t="inlineStr"/>
@@ -5288,7 +5199,7 @@
       <c r="T64" s="11" t="inlineStr"/>
       <c r="U64" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V64" s="11" t="inlineStr">
@@ -5304,26 +5215,26 @@
     </row>
     <row r="65" ht="26" customHeight="1">
       <c r="A65" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C65" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D65" s="11" t="inlineStr">
         <is>
-          <t>20260357400</t>
+          <t>20260361489</t>
         </is>
       </c>
       <c r="E65" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F65" s="11" t="inlineStr"/>
@@ -5351,7 +5262,7 @@
       <c r="T65" s="11" t="inlineStr"/>
       <c r="U65" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V65" s="11" t="inlineStr">
@@ -5367,26 +5278,26 @@
     </row>
     <row r="66" ht="26" customHeight="1">
       <c r="A66" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B66" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C66" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D66" s="11" t="inlineStr">
         <is>
-          <t>20260357401</t>
+          <t>20260361490</t>
         </is>
       </c>
       <c r="E66" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F66" s="11" t="inlineStr"/>
@@ -5414,7 +5325,7 @@
       <c r="T66" s="11" t="inlineStr"/>
       <c r="U66" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V66" s="11" t="inlineStr">
@@ -5430,26 +5341,26 @@
     </row>
     <row r="67" ht="26" customHeight="1">
       <c r="A67" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C67" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D67" s="11" t="inlineStr">
         <is>
-          <t>20260357402</t>
+          <t>20260361491</t>
         </is>
       </c>
       <c r="E67" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F67" s="11" t="inlineStr"/>
@@ -5477,7 +5388,7 @@
       <c r="T67" s="11" t="inlineStr"/>
       <c r="U67" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V67" s="11" t="inlineStr">
@@ -5493,26 +5404,26 @@
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="A68" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C68" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D68" s="11" t="inlineStr">
         <is>
-          <t>20260357403</t>
+          <t>20260361492</t>
         </is>
       </c>
       <c r="E68" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F68" s="11" t="inlineStr"/>
@@ -5540,7 +5451,7 @@
       <c r="T68" s="11" t="inlineStr"/>
       <c r="U68" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V68" s="11" t="inlineStr">
@@ -5556,26 +5467,26 @@
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="A69" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C69" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D69" s="11" t="inlineStr">
         <is>
-          <t>20260357404</t>
+          <t>20260361495</t>
         </is>
       </c>
       <c r="E69" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F69" s="11" t="inlineStr"/>
@@ -5603,7 +5514,7 @@
       <c r="T69" s="11" t="inlineStr"/>
       <c r="U69" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V69" s="11" t="inlineStr">
@@ -5619,26 +5530,26 @@
     </row>
     <row r="70" ht="26" customHeight="1">
       <c r="A70" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C70" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D70" s="11" t="inlineStr">
         <is>
-          <t>20260357405</t>
+          <t>20260361498</t>
         </is>
       </c>
       <c r="E70" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F70" s="11" t="inlineStr"/>
@@ -5666,7 +5577,7 @@
       <c r="T70" s="11" t="inlineStr"/>
       <c r="U70" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V70" s="11" t="inlineStr">
@@ -5682,26 +5593,26 @@
     </row>
     <row r="71" ht="26" customHeight="1">
       <c r="A71" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B71" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C71" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D71" s="11" t="inlineStr">
         <is>
-          <t>20260357407</t>
+          <t>20260361500</t>
         </is>
       </c>
       <c r="E71" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F71" s="11" t="inlineStr"/>
@@ -5729,7 +5640,7 @@
       <c r="T71" s="11" t="inlineStr"/>
       <c r="U71" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V71" s="11" t="inlineStr">
@@ -5745,26 +5656,26 @@
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="A72" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C72" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D72" s="11" t="inlineStr">
         <is>
-          <t>20260357990</t>
+          <t>20260361501</t>
         </is>
       </c>
       <c r="E72" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F72" s="11" t="inlineStr"/>
@@ -5792,7 +5703,7 @@
       <c r="T72" s="11" t="inlineStr"/>
       <c r="U72" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V72" s="11" t="inlineStr">
@@ -5808,26 +5719,26 @@
     </row>
     <row r="73" ht="26" customHeight="1">
       <c r="A73" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C73" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D73" s="11" t="inlineStr">
         <is>
-          <t>20260358346</t>
+          <t>20260361502</t>
         </is>
       </c>
       <c r="E73" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F73" s="11" t="inlineStr"/>
@@ -5855,12 +5766,12 @@
       <c r="T73" s="11" t="inlineStr"/>
       <c r="U73" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V73" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W73" s="12" t="inlineStr">
@@ -5871,26 +5782,26 @@
     </row>
     <row r="74" ht="26" customHeight="1">
       <c r="A74" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B74" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C74" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D74" s="11" t="inlineStr">
         <is>
-          <t>20260358616</t>
+          <t>20260361503</t>
         </is>
       </c>
       <c r="E74" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F74" s="11" t="inlineStr"/>
@@ -5918,12 +5829,12 @@
       <c r="T74" s="11" t="inlineStr"/>
       <c r="U74" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V74" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W74" s="12" t="inlineStr">
@@ -5934,26 +5845,26 @@
     </row>
     <row r="75" ht="26" customHeight="1">
       <c r="A75" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B75" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C75" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D75" s="11" t="inlineStr">
         <is>
-          <t>20260358667</t>
+          <t>20260361504</t>
         </is>
       </c>
       <c r="E75" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F75" s="11" t="inlineStr"/>
@@ -5981,12 +5892,12 @@
       <c r="T75" s="11" t="inlineStr"/>
       <c r="U75" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V75" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W75" s="12" t="inlineStr">
@@ -5997,26 +5908,26 @@
     </row>
     <row r="76" ht="26" customHeight="1">
       <c r="A76" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B76" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C76" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D76" s="11" t="inlineStr">
         <is>
-          <t>20260358836</t>
+          <t>20260361505</t>
         </is>
       </c>
       <c r="E76" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F76" s="11" t="inlineStr"/>
@@ -6044,12 +5955,12 @@
       <c r="T76" s="11" t="inlineStr"/>
       <c r="U76" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V76" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W76" s="12" t="inlineStr">
@@ -6060,26 +5971,26 @@
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="A77" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B77" s="11" t="inlineStr">
         <is>
-          <t>Tax Deed</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C77" s="11" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D77" s="11" t="inlineStr">
         <is>
-          <t>20260359800</t>
+          <t>20260361506</t>
         </is>
       </c>
       <c r="E77" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F77" s="11" t="inlineStr"/>
@@ -6107,12 +6018,12 @@
       <c r="T77" s="11" t="inlineStr"/>
       <c r="U77" s="11" t="inlineStr">
         <is>
-          <t>Tax deed; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V77" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W77" s="12" t="inlineStr">
@@ -6123,26 +6034,26 @@
     </row>
     <row r="78" ht="26" customHeight="1">
       <c r="A78" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B78" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C78" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D78" s="11" t="inlineStr">
         <is>
-          <t>20260358477</t>
+          <t>20260361510</t>
         </is>
       </c>
       <c r="E78" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F78" s="11" t="inlineStr"/>
@@ -6170,12 +6081,12 @@
       <c r="T78" s="11" t="inlineStr"/>
       <c r="U78" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V78" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W78" s="12" t="inlineStr">
@@ -6186,26 +6097,26 @@
     </row>
     <row r="79" ht="26" customHeight="1">
       <c r="A79" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B79" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C79" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D79" s="11" t="inlineStr">
         <is>
-          <t>20260358557</t>
+          <t>20260361511</t>
         </is>
       </c>
       <c r="E79" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F79" s="11" t="inlineStr"/>
@@ -6233,12 +6144,12 @@
       <c r="T79" s="11" t="inlineStr"/>
       <c r="U79" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V79" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W79" s="12" t="inlineStr">
@@ -6249,26 +6160,26 @@
     </row>
     <row r="80" ht="26" customHeight="1">
       <c r="A80" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B80" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C80" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D80" s="11" t="inlineStr">
         <is>
-          <t>20260358747</t>
+          <t>20260361512</t>
         </is>
       </c>
       <c r="E80" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F80" s="11" t="inlineStr"/>
@@ -6296,12 +6207,12 @@
       <c r="T80" s="11" t="inlineStr"/>
       <c r="U80" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V80" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W80" s="12" t="inlineStr">
@@ -6312,26 +6223,26 @@
     </row>
     <row r="81" ht="26" customHeight="1">
       <c r="A81" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B81" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C81" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D81" s="11" t="inlineStr">
         <is>
-          <t>20260358761</t>
+          <t>20260361513</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F81" s="11" t="inlineStr"/>
@@ -6359,12 +6270,12 @@
       <c r="T81" s="11" t="inlineStr"/>
       <c r="U81" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V81" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W81" s="12" t="inlineStr">
@@ -6375,26 +6286,26 @@
     </row>
     <row r="82" ht="26" customHeight="1">
       <c r="A82" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B82" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C82" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D82" s="11" t="inlineStr">
         <is>
-          <t>20260358852</t>
+          <t>20260361514</t>
         </is>
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F82" s="11" t="inlineStr"/>
@@ -6422,12 +6333,12 @@
       <c r="T82" s="11" t="inlineStr"/>
       <c r="U82" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V82" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W82" s="12" t="inlineStr">
@@ -6438,26 +6349,26 @@
     </row>
     <row r="83" ht="26" customHeight="1">
       <c r="A83" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B83" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C83" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D83" s="11" t="inlineStr">
         <is>
-          <t>20260358883</t>
+          <t>20260361515</t>
         </is>
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F83" s="11" t="inlineStr"/>
@@ -6485,12 +6396,12 @@
       <c r="T83" s="11" t="inlineStr"/>
       <c r="U83" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V83" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W83" s="12" t="inlineStr">
@@ -6501,26 +6412,26 @@
     </row>
     <row r="84" ht="26" customHeight="1">
       <c r="A84" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B84" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C84" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D84" s="11" t="inlineStr">
         <is>
-          <t>20260359379</t>
+          <t>20260361516</t>
         </is>
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F84" s="11" t="inlineStr"/>
@@ -6548,12 +6459,12 @@
       <c r="T84" s="11" t="inlineStr"/>
       <c r="U84" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V84" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W84" s="12" t="inlineStr">
@@ -6564,26 +6475,26 @@
     </row>
     <row r="85" ht="26" customHeight="1">
       <c r="A85" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B85" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C85" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D85" s="11" t="inlineStr">
         <is>
-          <t>20260359629</t>
+          <t>20260361518</t>
         </is>
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F85" s="11" t="inlineStr"/>
@@ -6611,12 +6522,12 @@
       <c r="T85" s="11" t="inlineStr"/>
       <c r="U85" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V85" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W85" s="12" t="inlineStr">
@@ -6627,26 +6538,26 @@
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="A86" s="10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B86" s="11" t="inlineStr">
         <is>
-          <t>Probate Document</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C86" s="11" t="inlineStr">
         <is>
-          <t>PJ</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D86" s="11" t="inlineStr">
         <is>
-          <t>20260360274</t>
+          <t>20260361623</t>
         </is>
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F86" s="11" t="inlineStr"/>
@@ -6674,12 +6585,12 @@
       <c r="T86" s="11" t="inlineStr"/>
       <c r="U86" s="11" t="inlineStr">
         <is>
-          <t>Probate / estate; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V86" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W86" s="12" t="inlineStr">
@@ -6704,12 +6615,12 @@
       </c>
       <c r="D87" s="11" t="inlineStr">
         <is>
-          <t>20260357453</t>
+          <t>20260361624</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F87" s="11" t="inlineStr"/>
@@ -6767,12 +6678,12 @@
       </c>
       <c r="D88" s="11" t="inlineStr">
         <is>
-          <t>20260357466</t>
+          <t>20260361625</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F88" s="11" t="inlineStr"/>
@@ -6830,12 +6741,12 @@
       </c>
       <c r="D89" s="11" t="inlineStr">
         <is>
-          <t>20260357521</t>
+          <t>20260361627</t>
         </is>
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F89" s="11" t="inlineStr"/>
@@ -6893,12 +6804,12 @@
       </c>
       <c r="D90" s="11" t="inlineStr">
         <is>
-          <t>20260357953</t>
+          <t>20260361631</t>
         </is>
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F90" s="11" t="inlineStr"/>
@@ -6956,12 +6867,12 @@
       </c>
       <c r="D91" s="11" t="inlineStr">
         <is>
-          <t>20260357954</t>
+          <t>20260361632</t>
         </is>
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F91" s="11" t="inlineStr"/>
@@ -7019,12 +6930,12 @@
       </c>
       <c r="D92" s="11" t="inlineStr">
         <is>
-          <t>20260357955</t>
+          <t>20260361633</t>
         </is>
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F92" s="11" t="inlineStr"/>
@@ -7082,12 +6993,12 @@
       </c>
       <c r="D93" s="11" t="inlineStr">
         <is>
-          <t>20260357956</t>
+          <t>20260361634</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F93" s="11" t="inlineStr"/>
@@ -7145,12 +7056,12 @@
       </c>
       <c r="D94" s="11" t="inlineStr">
         <is>
-          <t>20260357957</t>
+          <t>20260361635</t>
         </is>
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F94" s="11" t="inlineStr"/>
@@ -7208,12 +7119,12 @@
       </c>
       <c r="D95" s="11" t="inlineStr">
         <is>
-          <t>20260358220</t>
+          <t>20260361636</t>
         </is>
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F95" s="11" t="inlineStr"/>
@@ -7271,12 +7182,12 @@
       </c>
       <c r="D96" s="11" t="inlineStr">
         <is>
-          <t>20260359139</t>
+          <t>20260361637</t>
         </is>
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F96" s="11" t="inlineStr"/>
@@ -7334,12 +7245,12 @@
       </c>
       <c r="D97" s="11" t="inlineStr">
         <is>
-          <t>20260359142</t>
+          <t>20260361639</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F97" s="11" t="inlineStr"/>
@@ -7397,12 +7308,12 @@
       </c>
       <c r="D98" s="11" t="inlineStr">
         <is>
-          <t>20260359293</t>
+          <t>20260361640</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F98" s="11" t="inlineStr"/>
@@ -7460,12 +7371,12 @@
       </c>
       <c r="D99" s="11" t="inlineStr">
         <is>
-          <t>20260359305</t>
+          <t>20260361641</t>
         </is>
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F99" s="11" t="inlineStr"/>
@@ -7523,12 +7434,12 @@
       </c>
       <c r="D100" s="11" t="inlineStr">
         <is>
-          <t>20260359306</t>
+          <t>20260361645</t>
         </is>
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F100" s="11" t="inlineStr"/>
@@ -7586,12 +7497,12 @@
       </c>
       <c r="D101" s="11" t="inlineStr">
         <is>
-          <t>20260359309</t>
+          <t>20260361936</t>
         </is>
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F101" s="11" t="inlineStr"/>
@@ -7649,12 +7560,12 @@
       </c>
       <c r="D102" s="11" t="inlineStr">
         <is>
-          <t>20260359321</t>
+          <t>20260361937</t>
         </is>
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F102" s="11" t="inlineStr"/>
@@ -7712,12 +7623,12 @@
       </c>
       <c r="D103" s="11" t="inlineStr">
         <is>
-          <t>20260359322</t>
+          <t>20260361970</t>
         </is>
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F103" s="11" t="inlineStr"/>
@@ -7775,12 +7686,12 @@
       </c>
       <c r="D104" s="11" t="inlineStr">
         <is>
-          <t>20260360246</t>
+          <t>20260361972</t>
         </is>
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F104" s="11" t="inlineStr"/>
@@ -7838,12 +7749,12 @@
       </c>
       <c r="D105" s="11" t="inlineStr">
         <is>
-          <t>20260360248</t>
+          <t>20260361973</t>
         </is>
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F105" s="11" t="inlineStr"/>
@@ -7901,12 +7812,12 @@
       </c>
       <c r="D106" s="11" t="inlineStr">
         <is>
-          <t>20260360249</t>
+          <t>20260361975</t>
         </is>
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F106" s="11" t="inlineStr"/>
@@ -7964,12 +7875,12 @@
       </c>
       <c r="D107" s="11" t="inlineStr">
         <is>
-          <t>20260360250</t>
+          <t>20260361976</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F107" s="11" t="inlineStr"/>
@@ -8027,12 +7938,12 @@
       </c>
       <c r="D108" s="11" t="inlineStr">
         <is>
-          <t>20260360252</t>
+          <t>20260361977</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F108" s="11" t="inlineStr"/>
@@ -8090,12 +8001,12 @@
       </c>
       <c r="D109" s="11" t="inlineStr">
         <is>
-          <t>20260360253</t>
+          <t>20260361978</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F109" s="11" t="inlineStr"/>
@@ -8153,12 +8064,12 @@
       </c>
       <c r="D110" s="11" t="inlineStr">
         <is>
-          <t>20260360254</t>
+          <t>20260361979</t>
         </is>
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F110" s="11" t="inlineStr"/>
@@ -8216,12 +8127,12 @@
       </c>
       <c r="D111" s="11" t="inlineStr">
         <is>
-          <t>20260360401</t>
+          <t>20260361980</t>
         </is>
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F111" s="11" t="inlineStr"/>
@@ -8279,12 +8190,12 @@
       </c>
       <c r="D112" s="11" t="inlineStr">
         <is>
-          <t>20260360403</t>
+          <t>20260361983</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F112" s="11" t="inlineStr"/>
@@ -8342,12 +8253,12 @@
       </c>
       <c r="D113" s="11" t="inlineStr">
         <is>
-          <t>20260360405</t>
+          <t>20260361985</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F113" s="11" t="inlineStr"/>
@@ -8405,12 +8316,12 @@
       </c>
       <c r="D114" s="11" t="inlineStr">
         <is>
-          <t>20260360416</t>
+          <t>20260362216</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F114" s="11" t="inlineStr"/>
@@ -8454,26 +8365,26 @@
     </row>
     <row r="115" ht="26" customHeight="1">
       <c r="A115" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B115" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C115" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D115" s="11" t="inlineStr">
         <is>
-          <t>20260358069</t>
+          <t>20260362237</t>
         </is>
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F115" s="11" t="inlineStr"/>
@@ -8501,12 +8412,12 @@
       <c r="T115" s="11" t="inlineStr"/>
       <c r="U115" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V115" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W115" s="12" t="inlineStr">
@@ -8517,26 +8428,26 @@
     </row>
     <row r="116" ht="26" customHeight="1">
       <c r="A116" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B116" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C116" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D116" s="11" t="inlineStr">
         <is>
-          <t>20260358190</t>
+          <t>20260362262</t>
         </is>
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F116" s="11" t="inlineStr"/>
@@ -8564,12 +8475,12 @@
       <c r="T116" s="11" t="inlineStr"/>
       <c r="U116" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V116" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W116" s="12" t="inlineStr">
@@ -8580,26 +8491,26 @@
     </row>
     <row r="117" ht="26" customHeight="1">
       <c r="A117" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B117" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C117" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D117" s="11" t="inlineStr">
         <is>
-          <t>20260358193</t>
+          <t>20260362289</t>
         </is>
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F117" s="11" t="inlineStr"/>
@@ -8627,12 +8538,12 @@
       <c r="T117" s="11" t="inlineStr"/>
       <c r="U117" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V117" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W117" s="12" t="inlineStr">
@@ -8643,26 +8554,26 @@
     </row>
     <row r="118" ht="26" customHeight="1">
       <c r="A118" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B118" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C118" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D118" s="11" t="inlineStr">
         <is>
-          <t>20260358194</t>
+          <t>20260362411</t>
         </is>
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F118" s="11" t="inlineStr"/>
@@ -8690,12 +8601,12 @@
       <c r="T118" s="11" t="inlineStr"/>
       <c r="U118" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V118" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W118" s="12" t="inlineStr">
@@ -8706,26 +8617,26 @@
     </row>
     <row r="119" ht="26" customHeight="1">
       <c r="A119" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B119" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C119" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D119" s="11" t="inlineStr">
         <is>
-          <t>20260358195</t>
+          <t>20260362782</t>
         </is>
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F119" s="11" t="inlineStr"/>
@@ -8753,12 +8664,12 @@
       <c r="T119" s="11" t="inlineStr"/>
       <c r="U119" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V119" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W119" s="12" t="inlineStr">
@@ -8769,26 +8680,26 @@
     </row>
     <row r="120" ht="26" customHeight="1">
       <c r="A120" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B120" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C120" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D120" s="11" t="inlineStr">
         <is>
-          <t>20260358197</t>
+          <t>20260362783</t>
         </is>
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F120" s="11" t="inlineStr"/>
@@ -8816,12 +8727,12 @@
       <c r="T120" s="11" t="inlineStr"/>
       <c r="U120" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V120" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W120" s="12" t="inlineStr">
@@ -8832,26 +8743,26 @@
     </row>
     <row r="121" ht="26" customHeight="1">
       <c r="A121" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B121" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C121" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D121" s="11" t="inlineStr">
         <is>
-          <t>20260358200</t>
+          <t>20260362785</t>
         </is>
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F121" s="11" t="inlineStr"/>
@@ -8879,12 +8790,12 @@
       <c r="T121" s="11" t="inlineStr"/>
       <c r="U121" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V121" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W121" s="12" t="inlineStr">
@@ -8895,26 +8806,26 @@
     </row>
     <row r="122" ht="26" customHeight="1">
       <c r="A122" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B122" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C122" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D122" s="11" t="inlineStr">
         <is>
-          <t>20260358524</t>
+          <t>20260362786</t>
         </is>
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F122" s="11" t="inlineStr"/>
@@ -8942,12 +8853,12 @@
       <c r="T122" s="11" t="inlineStr"/>
       <c r="U122" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V122" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W122" s="12" t="inlineStr">
@@ -8958,26 +8869,26 @@
     </row>
     <row r="123" ht="26" customHeight="1">
       <c r="A123" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B123" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C123" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D123" s="11" t="inlineStr">
         <is>
-          <t>20260358528</t>
+          <t>20260362787</t>
         </is>
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F123" s="11" t="inlineStr"/>
@@ -9005,12 +8916,12 @@
       <c r="T123" s="11" t="inlineStr"/>
       <c r="U123" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V123" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W123" s="12" t="inlineStr">
@@ -9021,26 +8932,26 @@
     </row>
     <row r="124" ht="26" customHeight="1">
       <c r="A124" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B124" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C124" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D124" s="11" t="inlineStr">
         <is>
-          <t>20260358630</t>
+          <t>20260362788</t>
         </is>
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F124" s="11" t="inlineStr"/>
@@ -9068,12 +8979,12 @@
       <c r="T124" s="11" t="inlineStr"/>
       <c r="U124" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V124" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W124" s="12" t="inlineStr">
@@ -9084,26 +8995,26 @@
     </row>
     <row r="125" ht="26" customHeight="1">
       <c r="A125" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B125" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C125" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D125" s="11" t="inlineStr">
         <is>
-          <t>20260358632</t>
+          <t>20260362826</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F125" s="11" t="inlineStr"/>
@@ -9131,12 +9042,12 @@
       <c r="T125" s="11" t="inlineStr"/>
       <c r="U125" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V125" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W125" s="12" t="inlineStr">
@@ -9147,26 +9058,26 @@
     </row>
     <row r="126" ht="26" customHeight="1">
       <c r="A126" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B126" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C126" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D126" s="11" t="inlineStr">
         <is>
-          <t>20260358633</t>
+          <t>20260362827</t>
         </is>
       </c>
       <c r="E126" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F126" s="11" t="inlineStr"/>
@@ -9194,12 +9105,12 @@
       <c r="T126" s="11" t="inlineStr"/>
       <c r="U126" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V126" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W126" s="12" t="inlineStr">
@@ -9210,26 +9121,26 @@
     </row>
     <row r="127" ht="26" customHeight="1">
       <c r="A127" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B127" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C127" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D127" s="11" t="inlineStr">
         <is>
-          <t>20260358634</t>
+          <t>20260362828</t>
         </is>
       </c>
       <c r="E127" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F127" s="11" t="inlineStr"/>
@@ -9257,12 +9168,12 @@
       <c r="T127" s="11" t="inlineStr"/>
       <c r="U127" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V127" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W127" s="12" t="inlineStr">
@@ -9273,26 +9184,26 @@
     </row>
     <row r="128" ht="26" customHeight="1">
       <c r="A128" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B128" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C128" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D128" s="11" t="inlineStr">
         <is>
-          <t>20260358635</t>
+          <t>20260362829</t>
         </is>
       </c>
       <c r="E128" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F128" s="11" t="inlineStr"/>
@@ -9320,12 +9231,12 @@
       <c r="T128" s="11" t="inlineStr"/>
       <c r="U128" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V128" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W128" s="12" t="inlineStr">
@@ -9336,26 +9247,26 @@
     </row>
     <row r="129" ht="26" customHeight="1">
       <c r="A129" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B129" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C129" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D129" s="11" t="inlineStr">
         <is>
-          <t>20260358636</t>
+          <t>20260362830</t>
         </is>
       </c>
       <c r="E129" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F129" s="11" t="inlineStr"/>
@@ -9383,12 +9294,12 @@
       <c r="T129" s="11" t="inlineStr"/>
       <c r="U129" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V129" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W129" s="12" t="inlineStr">
@@ -9399,26 +9310,26 @@
     </row>
     <row r="130" ht="26" customHeight="1">
       <c r="A130" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B130" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C130" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D130" s="11" t="inlineStr">
         <is>
-          <t>20260358637</t>
+          <t>20260362831</t>
         </is>
       </c>
       <c r="E130" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F130" s="11" t="inlineStr"/>
@@ -9446,12 +9357,12 @@
       <c r="T130" s="11" t="inlineStr"/>
       <c r="U130" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V130" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W130" s="12" t="inlineStr">
@@ -9462,26 +9373,26 @@
     </row>
     <row r="131" ht="26" customHeight="1">
       <c r="A131" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B131" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C131" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D131" s="11" t="inlineStr">
         <is>
-          <t>20260358638</t>
+          <t>20260362832</t>
         </is>
       </c>
       <c r="E131" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F131" s="11" t="inlineStr"/>
@@ -9509,12 +9420,12 @@
       <c r="T131" s="11" t="inlineStr"/>
       <c r="U131" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V131" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W131" s="12" t="inlineStr">
@@ -9525,26 +9436,26 @@
     </row>
     <row r="132" ht="26" customHeight="1">
       <c r="A132" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B132" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C132" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D132" s="11" t="inlineStr">
         <is>
-          <t>20260358640</t>
+          <t>20260362833</t>
         </is>
       </c>
       <c r="E132" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F132" s="11" t="inlineStr"/>
@@ -9572,12 +9483,12 @@
       <c r="T132" s="11" t="inlineStr"/>
       <c r="U132" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V132" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W132" s="12" t="inlineStr">
@@ -9588,26 +9499,26 @@
     </row>
     <row r="133" ht="26" customHeight="1">
       <c r="A133" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B133" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C133" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D133" s="11" t="inlineStr">
         <is>
-          <t>20260358641</t>
+          <t>20260362834</t>
         </is>
       </c>
       <c r="E133" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F133" s="11" t="inlineStr"/>
@@ -9635,12 +9546,12 @@
       <c r="T133" s="11" t="inlineStr"/>
       <c r="U133" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V133" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W133" s="12" t="inlineStr">
@@ -9651,26 +9562,26 @@
     </row>
     <row r="134" ht="26" customHeight="1">
       <c r="A134" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B134" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C134" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D134" s="11" t="inlineStr">
         <is>
-          <t>20260358642</t>
+          <t>20260362835</t>
         </is>
       </c>
       <c r="E134" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F134" s="11" t="inlineStr"/>
@@ -9698,12 +9609,12 @@
       <c r="T134" s="11" t="inlineStr"/>
       <c r="U134" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V134" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W134" s="12" t="inlineStr">
@@ -9714,26 +9625,26 @@
     </row>
     <row r="135" ht="26" customHeight="1">
       <c r="A135" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B135" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C135" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D135" s="11" t="inlineStr">
         <is>
-          <t>20260358643</t>
+          <t>20260362837</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F135" s="11" t="inlineStr"/>
@@ -9761,12 +9672,12 @@
       <c r="T135" s="11" t="inlineStr"/>
       <c r="U135" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V135" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W135" s="12" t="inlineStr">
@@ -9777,26 +9688,26 @@
     </row>
     <row r="136" ht="26" customHeight="1">
       <c r="A136" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B136" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C136" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D136" s="11" t="inlineStr">
         <is>
-          <t>20260358644</t>
+          <t>20260362838</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F136" s="11" t="inlineStr"/>
@@ -9824,12 +9735,12 @@
       <c r="T136" s="11" t="inlineStr"/>
       <c r="U136" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V136" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W136" s="12" t="inlineStr">
@@ -9840,26 +9751,26 @@
     </row>
     <row r="137" ht="26" customHeight="1">
       <c r="A137" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B137" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C137" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D137" s="11" t="inlineStr">
         <is>
-          <t>20260358645</t>
+          <t>20260362839</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F137" s="11" t="inlineStr"/>
@@ -9887,12 +9798,12 @@
       <c r="T137" s="11" t="inlineStr"/>
       <c r="U137" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V137" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W137" s="12" t="inlineStr">
@@ -9903,26 +9814,26 @@
     </row>
     <row r="138" ht="26" customHeight="1">
       <c r="A138" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B138" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C138" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D138" s="11" t="inlineStr">
         <is>
-          <t>20260358646</t>
+          <t>20260362840</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F138" s="11" t="inlineStr"/>
@@ -9950,12 +9861,12 @@
       <c r="T138" s="11" t="inlineStr"/>
       <c r="U138" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V138" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W138" s="12" t="inlineStr">
@@ -9966,26 +9877,26 @@
     </row>
     <row r="139" ht="26" customHeight="1">
       <c r="A139" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B139" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C139" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D139" s="11" t="inlineStr">
         <is>
-          <t>20260358726</t>
+          <t>20260362841</t>
         </is>
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F139" s="11" t="inlineStr"/>
@@ -10013,12 +9924,12 @@
       <c r="T139" s="11" t="inlineStr"/>
       <c r="U139" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V139" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W139" s="12" t="inlineStr">
@@ -10029,26 +9940,26 @@
     </row>
     <row r="140" ht="26" customHeight="1">
       <c r="A140" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B140" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C140" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D140" s="11" t="inlineStr">
         <is>
-          <t>20260358888</t>
+          <t>20260362843</t>
         </is>
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F140" s="11" t="inlineStr"/>
@@ -10076,12 +9987,12 @@
       <c r="T140" s="11" t="inlineStr"/>
       <c r="U140" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V140" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W140" s="12" t="inlineStr">
@@ -10092,26 +10003,26 @@
     </row>
     <row r="141" ht="26" customHeight="1">
       <c r="A141" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B141" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C141" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D141" s="11" t="inlineStr">
         <is>
-          <t>20260358938</t>
+          <t>20260362865</t>
         </is>
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F141" s="11" t="inlineStr"/>
@@ -10139,12 +10050,12 @@
       <c r="T141" s="11" t="inlineStr"/>
       <c r="U141" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V141" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W141" s="12" t="inlineStr">
@@ -10155,26 +10066,26 @@
     </row>
     <row r="142" ht="26" customHeight="1">
       <c r="A142" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B142" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C142" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D142" s="11" t="inlineStr">
         <is>
-          <t>20260358941</t>
+          <t>20260362969</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F142" s="11" t="inlineStr"/>
@@ -10202,12 +10113,12 @@
       <c r="T142" s="11" t="inlineStr"/>
       <c r="U142" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V142" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W142" s="12" t="inlineStr">
@@ -10218,26 +10129,26 @@
     </row>
     <row r="143" ht="26" customHeight="1">
       <c r="A143" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B143" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C143" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D143" s="11" t="inlineStr">
         <is>
-          <t>20260359035</t>
+          <t>20260363221</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F143" s="11" t="inlineStr"/>
@@ -10265,12 +10176,12 @@
       <c r="T143" s="11" t="inlineStr"/>
       <c r="U143" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V143" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W143" s="12" t="inlineStr">
@@ -10281,26 +10192,26 @@
     </row>
     <row r="144" ht="26" customHeight="1">
       <c r="A144" s="10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B144" s="11" t="inlineStr">
         <is>
-          <t>Medical Lien</t>
+          <t>Lien</t>
         </is>
       </c>
       <c r="C144" s="11" t="inlineStr">
         <is>
-          <t>HL</t>
+          <t>LN</t>
         </is>
       </c>
       <c r="D144" s="11" t="inlineStr">
         <is>
-          <t>20260359500</t>
+          <t>20260363222</t>
         </is>
       </c>
       <c r="E144" s="11" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="F144" s="11" t="inlineStr"/>
@@ -10328,12 +10239,12 @@
       <c r="T144" s="11" t="inlineStr"/>
       <c r="U144" s="11" t="inlineStr">
         <is>
-          <t>Medical lien; New this week</t>
+          <t>Lien; New this week</t>
         </is>
       </c>
       <c r="V144" s="11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="W144" s="12" t="inlineStr">
@@ -10342,2150 +10253,8 @@
         </is>
       </c>
     </row>
-    <row r="145" ht="26" customHeight="1">
-      <c r="A145" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B145" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C145" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D145" s="11" t="inlineStr">
-        <is>
-          <t>20260359753</t>
-        </is>
-      </c>
-      <c r="E145" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F145" s="11" t="inlineStr"/>
-      <c r="G145" s="11" t="inlineStr"/>
-      <c r="H145" s="11" t="inlineStr"/>
-      <c r="I145" s="11" t="inlineStr"/>
-      <c r="J145" s="11" t="inlineStr"/>
-      <c r="K145" s="11" t="inlineStr"/>
-      <c r="L145" s="11" t="inlineStr"/>
-      <c r="M145" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N145" s="11" t="inlineStr"/>
-      <c r="O145" s="11" t="inlineStr"/>
-      <c r="P145" s="11" t="inlineStr"/>
-      <c r="Q145" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R145" s="11" t="inlineStr"/>
-      <c r="S145" s="11" t="inlineStr"/>
-      <c r="T145" s="11" t="inlineStr"/>
-      <c r="U145" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V145" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W145" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="146" ht="26" customHeight="1">
-      <c r="A146" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B146" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C146" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D146" s="11" t="inlineStr">
-        <is>
-          <t>20260359754</t>
-        </is>
-      </c>
-      <c r="E146" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F146" s="11" t="inlineStr"/>
-      <c r="G146" s="11" t="inlineStr"/>
-      <c r="H146" s="11" t="inlineStr"/>
-      <c r="I146" s="11" t="inlineStr"/>
-      <c r="J146" s="11" t="inlineStr"/>
-      <c r="K146" s="11" t="inlineStr"/>
-      <c r="L146" s="11" t="inlineStr"/>
-      <c r="M146" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N146" s="11" t="inlineStr"/>
-      <c r="O146" s="11" t="inlineStr"/>
-      <c r="P146" s="11" t="inlineStr"/>
-      <c r="Q146" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R146" s="11" t="inlineStr"/>
-      <c r="S146" s="11" t="inlineStr"/>
-      <c r="T146" s="11" t="inlineStr"/>
-      <c r="U146" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V146" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W146" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="147" ht="26" customHeight="1">
-      <c r="A147" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B147" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C147" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D147" s="11" t="inlineStr">
-        <is>
-          <t>20260359755</t>
-        </is>
-      </c>
-      <c r="E147" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F147" s="11" t="inlineStr"/>
-      <c r="G147" s="11" t="inlineStr"/>
-      <c r="H147" s="11" t="inlineStr"/>
-      <c r="I147" s="11" t="inlineStr"/>
-      <c r="J147" s="11" t="inlineStr"/>
-      <c r="K147" s="11" t="inlineStr"/>
-      <c r="L147" s="11" t="inlineStr"/>
-      <c r="M147" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N147" s="11" t="inlineStr"/>
-      <c r="O147" s="11" t="inlineStr"/>
-      <c r="P147" s="11" t="inlineStr"/>
-      <c r="Q147" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R147" s="11" t="inlineStr"/>
-      <c r="S147" s="11" t="inlineStr"/>
-      <c r="T147" s="11" t="inlineStr"/>
-      <c r="U147" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V147" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W147" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="148" ht="26" customHeight="1">
-      <c r="A148" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B148" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C148" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D148" s="11" t="inlineStr">
-        <is>
-          <t>20260359770</t>
-        </is>
-      </c>
-      <c r="E148" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F148" s="11" t="inlineStr"/>
-      <c r="G148" s="11" t="inlineStr"/>
-      <c r="H148" s="11" t="inlineStr"/>
-      <c r="I148" s="11" t="inlineStr"/>
-      <c r="J148" s="11" t="inlineStr"/>
-      <c r="K148" s="11" t="inlineStr"/>
-      <c r="L148" s="11" t="inlineStr"/>
-      <c r="M148" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N148" s="11" t="inlineStr"/>
-      <c r="O148" s="11" t="inlineStr"/>
-      <c r="P148" s="11" t="inlineStr"/>
-      <c r="Q148" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R148" s="11" t="inlineStr"/>
-      <c r="S148" s="11" t="inlineStr"/>
-      <c r="T148" s="11" t="inlineStr"/>
-      <c r="U148" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V148" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W148" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="26" customHeight="1">
-      <c r="A149" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B149" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C149" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D149" s="11" t="inlineStr">
-        <is>
-          <t>20260359774</t>
-        </is>
-      </c>
-      <c r="E149" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F149" s="11" t="inlineStr"/>
-      <c r="G149" s="11" t="inlineStr"/>
-      <c r="H149" s="11" t="inlineStr"/>
-      <c r="I149" s="11" t="inlineStr"/>
-      <c r="J149" s="11" t="inlineStr"/>
-      <c r="K149" s="11" t="inlineStr"/>
-      <c r="L149" s="11" t="inlineStr"/>
-      <c r="M149" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N149" s="11" t="inlineStr"/>
-      <c r="O149" s="11" t="inlineStr"/>
-      <c r="P149" s="11" t="inlineStr"/>
-      <c r="Q149" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R149" s="11" t="inlineStr"/>
-      <c r="S149" s="11" t="inlineStr"/>
-      <c r="T149" s="11" t="inlineStr"/>
-      <c r="U149" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V149" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W149" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="26" customHeight="1">
-      <c r="A150" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B150" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C150" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D150" s="11" t="inlineStr">
-        <is>
-          <t>20260360003</t>
-        </is>
-      </c>
-      <c r="E150" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F150" s="11" t="inlineStr"/>
-      <c r="G150" s="11" t="inlineStr"/>
-      <c r="H150" s="11" t="inlineStr"/>
-      <c r="I150" s="11" t="inlineStr"/>
-      <c r="J150" s="11" t="inlineStr"/>
-      <c r="K150" s="11" t="inlineStr"/>
-      <c r="L150" s="11" t="inlineStr"/>
-      <c r="M150" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N150" s="11" t="inlineStr"/>
-      <c r="O150" s="11" t="inlineStr"/>
-      <c r="P150" s="11" t="inlineStr"/>
-      <c r="Q150" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R150" s="11" t="inlineStr"/>
-      <c r="S150" s="11" t="inlineStr"/>
-      <c r="T150" s="11" t="inlineStr"/>
-      <c r="U150" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V150" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W150" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="26" customHeight="1">
-      <c r="A151" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B151" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C151" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D151" s="11" t="inlineStr">
-        <is>
-          <t>20260360100</t>
-        </is>
-      </c>
-      <c r="E151" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F151" s="11" t="inlineStr"/>
-      <c r="G151" s="11" t="inlineStr"/>
-      <c r="H151" s="11" t="inlineStr"/>
-      <c r="I151" s="11" t="inlineStr"/>
-      <c r="J151" s="11" t="inlineStr"/>
-      <c r="K151" s="11" t="inlineStr"/>
-      <c r="L151" s="11" t="inlineStr"/>
-      <c r="M151" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N151" s="11" t="inlineStr"/>
-      <c r="O151" s="11" t="inlineStr"/>
-      <c r="P151" s="11" t="inlineStr"/>
-      <c r="Q151" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R151" s="11" t="inlineStr"/>
-      <c r="S151" s="11" t="inlineStr"/>
-      <c r="T151" s="11" t="inlineStr"/>
-      <c r="U151" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V151" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W151" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="26" customHeight="1">
-      <c r="A152" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B152" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C152" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D152" s="11" t="inlineStr">
-        <is>
-          <t>20260360111</t>
-        </is>
-      </c>
-      <c r="E152" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F152" s="11" t="inlineStr"/>
-      <c r="G152" s="11" t="inlineStr"/>
-      <c r="H152" s="11" t="inlineStr"/>
-      <c r="I152" s="11" t="inlineStr"/>
-      <c r="J152" s="11" t="inlineStr"/>
-      <c r="K152" s="11" t="inlineStr"/>
-      <c r="L152" s="11" t="inlineStr"/>
-      <c r="M152" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N152" s="11" t="inlineStr"/>
-      <c r="O152" s="11" t="inlineStr"/>
-      <c r="P152" s="11" t="inlineStr"/>
-      <c r="Q152" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R152" s="11" t="inlineStr"/>
-      <c r="S152" s="11" t="inlineStr"/>
-      <c r="T152" s="11" t="inlineStr"/>
-      <c r="U152" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V152" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W152" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="26" customHeight="1">
-      <c r="A153" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B153" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C153" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D153" s="11" t="inlineStr">
-        <is>
-          <t>20260360120</t>
-        </is>
-      </c>
-      <c r="E153" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F153" s="11" t="inlineStr"/>
-      <c r="G153" s="11" t="inlineStr"/>
-      <c r="H153" s="11" t="inlineStr"/>
-      <c r="I153" s="11" t="inlineStr"/>
-      <c r="J153" s="11" t="inlineStr"/>
-      <c r="K153" s="11" t="inlineStr"/>
-      <c r="L153" s="11" t="inlineStr"/>
-      <c r="M153" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N153" s="11" t="inlineStr"/>
-      <c r="O153" s="11" t="inlineStr"/>
-      <c r="P153" s="11" t="inlineStr"/>
-      <c r="Q153" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R153" s="11" t="inlineStr"/>
-      <c r="S153" s="11" t="inlineStr"/>
-      <c r="T153" s="11" t="inlineStr"/>
-      <c r="U153" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V153" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W153" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="26" customHeight="1">
-      <c r="A154" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B154" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C154" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D154" s="11" t="inlineStr">
-        <is>
-          <t>20260360130</t>
-        </is>
-      </c>
-      <c r="E154" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F154" s="11" t="inlineStr"/>
-      <c r="G154" s="11" t="inlineStr"/>
-      <c r="H154" s="11" t="inlineStr"/>
-      <c r="I154" s="11" t="inlineStr"/>
-      <c r="J154" s="11" t="inlineStr"/>
-      <c r="K154" s="11" t="inlineStr"/>
-      <c r="L154" s="11" t="inlineStr"/>
-      <c r="M154" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N154" s="11" t="inlineStr"/>
-      <c r="O154" s="11" t="inlineStr"/>
-      <c r="P154" s="11" t="inlineStr"/>
-      <c r="Q154" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R154" s="11" t="inlineStr"/>
-      <c r="S154" s="11" t="inlineStr"/>
-      <c r="T154" s="11" t="inlineStr"/>
-      <c r="U154" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V154" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W154" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="26" customHeight="1">
-      <c r="A155" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B155" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C155" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D155" s="11" t="inlineStr">
-        <is>
-          <t>20260360227</t>
-        </is>
-      </c>
-      <c r="E155" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F155" s="11" t="inlineStr"/>
-      <c r="G155" s="11" t="inlineStr"/>
-      <c r="H155" s="11" t="inlineStr"/>
-      <c r="I155" s="11" t="inlineStr"/>
-      <c r="J155" s="11" t="inlineStr"/>
-      <c r="K155" s="11" t="inlineStr"/>
-      <c r="L155" s="11" t="inlineStr"/>
-      <c r="M155" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N155" s="11" t="inlineStr"/>
-      <c r="O155" s="11" t="inlineStr"/>
-      <c r="P155" s="11" t="inlineStr"/>
-      <c r="Q155" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R155" s="11" t="inlineStr"/>
-      <c r="S155" s="11" t="inlineStr"/>
-      <c r="T155" s="11" t="inlineStr"/>
-      <c r="U155" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V155" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W155" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="26" customHeight="1">
-      <c r="A156" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B156" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C156" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D156" s="11" t="inlineStr">
-        <is>
-          <t>20260360228</t>
-        </is>
-      </c>
-      <c r="E156" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F156" s="11" t="inlineStr"/>
-      <c r="G156" s="11" t="inlineStr"/>
-      <c r="H156" s="11" t="inlineStr"/>
-      <c r="I156" s="11" t="inlineStr"/>
-      <c r="J156" s="11" t="inlineStr"/>
-      <c r="K156" s="11" t="inlineStr"/>
-      <c r="L156" s="11" t="inlineStr"/>
-      <c r="M156" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N156" s="11" t="inlineStr"/>
-      <c r="O156" s="11" t="inlineStr"/>
-      <c r="P156" s="11" t="inlineStr"/>
-      <c r="Q156" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R156" s="11" t="inlineStr"/>
-      <c r="S156" s="11" t="inlineStr"/>
-      <c r="T156" s="11" t="inlineStr"/>
-      <c r="U156" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V156" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W156" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="26" customHeight="1">
-      <c r="A157" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B157" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C157" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D157" s="11" t="inlineStr">
-        <is>
-          <t>20260360229</t>
-        </is>
-      </c>
-      <c r="E157" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F157" s="11" t="inlineStr"/>
-      <c r="G157" s="11" t="inlineStr"/>
-      <c r="H157" s="11" t="inlineStr"/>
-      <c r="I157" s="11" t="inlineStr"/>
-      <c r="J157" s="11" t="inlineStr"/>
-      <c r="K157" s="11" t="inlineStr"/>
-      <c r="L157" s="11" t="inlineStr"/>
-      <c r="M157" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N157" s="11" t="inlineStr"/>
-      <c r="O157" s="11" t="inlineStr"/>
-      <c r="P157" s="11" t="inlineStr"/>
-      <c r="Q157" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R157" s="11" t="inlineStr"/>
-      <c r="S157" s="11" t="inlineStr"/>
-      <c r="T157" s="11" t="inlineStr"/>
-      <c r="U157" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V157" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W157" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="26" customHeight="1">
-      <c r="A158" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B158" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C158" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D158" s="11" t="inlineStr">
-        <is>
-          <t>20260360230</t>
-        </is>
-      </c>
-      <c r="E158" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F158" s="11" t="inlineStr"/>
-      <c r="G158" s="11" t="inlineStr"/>
-      <c r="H158" s="11" t="inlineStr"/>
-      <c r="I158" s="11" t="inlineStr"/>
-      <c r="J158" s="11" t="inlineStr"/>
-      <c r="K158" s="11" t="inlineStr"/>
-      <c r="L158" s="11" t="inlineStr"/>
-      <c r="M158" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N158" s="11" t="inlineStr"/>
-      <c r="O158" s="11" t="inlineStr"/>
-      <c r="P158" s="11" t="inlineStr"/>
-      <c r="Q158" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R158" s="11" t="inlineStr"/>
-      <c r="S158" s="11" t="inlineStr"/>
-      <c r="T158" s="11" t="inlineStr"/>
-      <c r="U158" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V158" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W158" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="26" customHeight="1">
-      <c r="A159" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B159" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C159" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D159" s="11" t="inlineStr">
-        <is>
-          <t>20260360231</t>
-        </is>
-      </c>
-      <c r="E159" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F159" s="11" t="inlineStr"/>
-      <c r="G159" s="11" t="inlineStr"/>
-      <c r="H159" s="11" t="inlineStr"/>
-      <c r="I159" s="11" t="inlineStr"/>
-      <c r="J159" s="11" t="inlineStr"/>
-      <c r="K159" s="11" t="inlineStr"/>
-      <c r="L159" s="11" t="inlineStr"/>
-      <c r="M159" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N159" s="11" t="inlineStr"/>
-      <c r="O159" s="11" t="inlineStr"/>
-      <c r="P159" s="11" t="inlineStr"/>
-      <c r="Q159" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R159" s="11" t="inlineStr"/>
-      <c r="S159" s="11" t="inlineStr"/>
-      <c r="T159" s="11" t="inlineStr"/>
-      <c r="U159" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V159" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W159" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="26" customHeight="1">
-      <c r="A160" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B160" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C160" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D160" s="11" t="inlineStr">
-        <is>
-          <t>20260360232</t>
-        </is>
-      </c>
-      <c r="E160" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F160" s="11" t="inlineStr"/>
-      <c r="G160" s="11" t="inlineStr"/>
-      <c r="H160" s="11" t="inlineStr"/>
-      <c r="I160" s="11" t="inlineStr"/>
-      <c r="J160" s="11" t="inlineStr"/>
-      <c r="K160" s="11" t="inlineStr"/>
-      <c r="L160" s="11" t="inlineStr"/>
-      <c r="M160" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N160" s="11" t="inlineStr"/>
-      <c r="O160" s="11" t="inlineStr"/>
-      <c r="P160" s="11" t="inlineStr"/>
-      <c r="Q160" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R160" s="11" t="inlineStr"/>
-      <c r="S160" s="11" t="inlineStr"/>
-      <c r="T160" s="11" t="inlineStr"/>
-      <c r="U160" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V160" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W160" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="26" customHeight="1">
-      <c r="A161" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B161" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C161" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D161" s="11" t="inlineStr">
-        <is>
-          <t>20260360233</t>
-        </is>
-      </c>
-      <c r="E161" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F161" s="11" t="inlineStr"/>
-      <c r="G161" s="11" t="inlineStr"/>
-      <c r="H161" s="11" t="inlineStr"/>
-      <c r="I161" s="11" t="inlineStr"/>
-      <c r="J161" s="11" t="inlineStr"/>
-      <c r="K161" s="11" t="inlineStr"/>
-      <c r="L161" s="11" t="inlineStr"/>
-      <c r="M161" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N161" s="11" t="inlineStr"/>
-      <c r="O161" s="11" t="inlineStr"/>
-      <c r="P161" s="11" t="inlineStr"/>
-      <c r="Q161" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R161" s="11" t="inlineStr"/>
-      <c r="S161" s="11" t="inlineStr"/>
-      <c r="T161" s="11" t="inlineStr"/>
-      <c r="U161" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V161" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W161" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="162" ht="26" customHeight="1">
-      <c r="A162" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B162" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C162" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D162" s="11" t="inlineStr">
-        <is>
-          <t>20260360234</t>
-        </is>
-      </c>
-      <c r="E162" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F162" s="11" t="inlineStr"/>
-      <c r="G162" s="11" t="inlineStr"/>
-      <c r="H162" s="11" t="inlineStr"/>
-      <c r="I162" s="11" t="inlineStr"/>
-      <c r="J162" s="11" t="inlineStr"/>
-      <c r="K162" s="11" t="inlineStr"/>
-      <c r="L162" s="11" t="inlineStr"/>
-      <c r="M162" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N162" s="11" t="inlineStr"/>
-      <c r="O162" s="11" t="inlineStr"/>
-      <c r="P162" s="11" t="inlineStr"/>
-      <c r="Q162" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R162" s="11" t="inlineStr"/>
-      <c r="S162" s="11" t="inlineStr"/>
-      <c r="T162" s="11" t="inlineStr"/>
-      <c r="U162" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V162" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W162" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="163" ht="26" customHeight="1">
-      <c r="A163" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B163" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C163" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D163" s="11" t="inlineStr">
-        <is>
-          <t>20260360235</t>
-        </is>
-      </c>
-      <c r="E163" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F163" s="11" t="inlineStr"/>
-      <c r="G163" s="11" t="inlineStr"/>
-      <c r="H163" s="11" t="inlineStr"/>
-      <c r="I163" s="11" t="inlineStr"/>
-      <c r="J163" s="11" t="inlineStr"/>
-      <c r="K163" s="11" t="inlineStr"/>
-      <c r="L163" s="11" t="inlineStr"/>
-      <c r="M163" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N163" s="11" t="inlineStr"/>
-      <c r="O163" s="11" t="inlineStr"/>
-      <c r="P163" s="11" t="inlineStr"/>
-      <c r="Q163" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R163" s="11" t="inlineStr"/>
-      <c r="S163" s="11" t="inlineStr"/>
-      <c r="T163" s="11" t="inlineStr"/>
-      <c r="U163" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V163" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W163" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="164" ht="26" customHeight="1">
-      <c r="A164" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B164" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C164" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D164" s="11" t="inlineStr">
-        <is>
-          <t>20260360236</t>
-        </is>
-      </c>
-      <c r="E164" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F164" s="11" t="inlineStr"/>
-      <c r="G164" s="11" t="inlineStr"/>
-      <c r="H164" s="11" t="inlineStr"/>
-      <c r="I164" s="11" t="inlineStr"/>
-      <c r="J164" s="11" t="inlineStr"/>
-      <c r="K164" s="11" t="inlineStr"/>
-      <c r="L164" s="11" t="inlineStr"/>
-      <c r="M164" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N164" s="11" t="inlineStr"/>
-      <c r="O164" s="11" t="inlineStr"/>
-      <c r="P164" s="11" t="inlineStr"/>
-      <c r="Q164" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R164" s="11" t="inlineStr"/>
-      <c r="S164" s="11" t="inlineStr"/>
-      <c r="T164" s="11" t="inlineStr"/>
-      <c r="U164" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V164" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W164" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="165" ht="26" customHeight="1">
-      <c r="A165" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B165" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C165" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D165" s="11" t="inlineStr">
-        <is>
-          <t>20260360237</t>
-        </is>
-      </c>
-      <c r="E165" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F165" s="11" t="inlineStr"/>
-      <c r="G165" s="11" t="inlineStr"/>
-      <c r="H165" s="11" t="inlineStr"/>
-      <c r="I165" s="11" t="inlineStr"/>
-      <c r="J165" s="11" t="inlineStr"/>
-      <c r="K165" s="11" t="inlineStr"/>
-      <c r="L165" s="11" t="inlineStr"/>
-      <c r="M165" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N165" s="11" t="inlineStr"/>
-      <c r="O165" s="11" t="inlineStr"/>
-      <c r="P165" s="11" t="inlineStr"/>
-      <c r="Q165" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R165" s="11" t="inlineStr"/>
-      <c r="S165" s="11" t="inlineStr"/>
-      <c r="T165" s="11" t="inlineStr"/>
-      <c r="U165" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V165" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W165" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="166" ht="26" customHeight="1">
-      <c r="A166" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B166" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C166" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D166" s="11" t="inlineStr">
-        <is>
-          <t>20260360238</t>
-        </is>
-      </c>
-      <c r="E166" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F166" s="11" t="inlineStr"/>
-      <c r="G166" s="11" t="inlineStr"/>
-      <c r="H166" s="11" t="inlineStr"/>
-      <c r="I166" s="11" t="inlineStr"/>
-      <c r="J166" s="11" t="inlineStr"/>
-      <c r="K166" s="11" t="inlineStr"/>
-      <c r="L166" s="11" t="inlineStr"/>
-      <c r="M166" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N166" s="11" t="inlineStr"/>
-      <c r="O166" s="11" t="inlineStr"/>
-      <c r="P166" s="11" t="inlineStr"/>
-      <c r="Q166" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R166" s="11" t="inlineStr"/>
-      <c r="S166" s="11" t="inlineStr"/>
-      <c r="T166" s="11" t="inlineStr"/>
-      <c r="U166" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V166" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W166" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="167" ht="26" customHeight="1">
-      <c r="A167" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B167" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C167" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D167" s="11" t="inlineStr">
-        <is>
-          <t>20260360239</t>
-        </is>
-      </c>
-      <c r="E167" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F167" s="11" t="inlineStr"/>
-      <c r="G167" s="11" t="inlineStr"/>
-      <c r="H167" s="11" t="inlineStr"/>
-      <c r="I167" s="11" t="inlineStr"/>
-      <c r="J167" s="11" t="inlineStr"/>
-      <c r="K167" s="11" t="inlineStr"/>
-      <c r="L167" s="11" t="inlineStr"/>
-      <c r="M167" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N167" s="11" t="inlineStr"/>
-      <c r="O167" s="11" t="inlineStr"/>
-      <c r="P167" s="11" t="inlineStr"/>
-      <c r="Q167" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R167" s="11" t="inlineStr"/>
-      <c r="S167" s="11" t="inlineStr"/>
-      <c r="T167" s="11" t="inlineStr"/>
-      <c r="U167" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V167" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W167" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="168" ht="26" customHeight="1">
-      <c r="A168" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B168" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C168" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D168" s="11" t="inlineStr">
-        <is>
-          <t>20260360240</t>
-        </is>
-      </c>
-      <c r="E168" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F168" s="11" t="inlineStr"/>
-      <c r="G168" s="11" t="inlineStr"/>
-      <c r="H168" s="11" t="inlineStr"/>
-      <c r="I168" s="11" t="inlineStr"/>
-      <c r="J168" s="11" t="inlineStr"/>
-      <c r="K168" s="11" t="inlineStr"/>
-      <c r="L168" s="11" t="inlineStr"/>
-      <c r="M168" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N168" s="11" t="inlineStr"/>
-      <c r="O168" s="11" t="inlineStr"/>
-      <c r="P168" s="11" t="inlineStr"/>
-      <c r="Q168" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R168" s="11" t="inlineStr"/>
-      <c r="S168" s="11" t="inlineStr"/>
-      <c r="T168" s="11" t="inlineStr"/>
-      <c r="U168" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V168" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W168" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="169" ht="26" customHeight="1">
-      <c r="A169" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B169" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C169" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D169" s="11" t="inlineStr">
-        <is>
-          <t>20260360241</t>
-        </is>
-      </c>
-      <c r="E169" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F169" s="11" t="inlineStr"/>
-      <c r="G169" s="11" t="inlineStr"/>
-      <c r="H169" s="11" t="inlineStr"/>
-      <c r="I169" s="11" t="inlineStr"/>
-      <c r="J169" s="11" t="inlineStr"/>
-      <c r="K169" s="11" t="inlineStr"/>
-      <c r="L169" s="11" t="inlineStr"/>
-      <c r="M169" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N169" s="11" t="inlineStr"/>
-      <c r="O169" s="11" t="inlineStr"/>
-      <c r="P169" s="11" t="inlineStr"/>
-      <c r="Q169" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R169" s="11" t="inlineStr"/>
-      <c r="S169" s="11" t="inlineStr"/>
-      <c r="T169" s="11" t="inlineStr"/>
-      <c r="U169" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V169" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W169" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="170" ht="26" customHeight="1">
-      <c r="A170" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B170" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C170" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D170" s="11" t="inlineStr">
-        <is>
-          <t>20260360243</t>
-        </is>
-      </c>
-      <c r="E170" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F170" s="11" t="inlineStr"/>
-      <c r="G170" s="11" t="inlineStr"/>
-      <c r="H170" s="11" t="inlineStr"/>
-      <c r="I170" s="11" t="inlineStr"/>
-      <c r="J170" s="11" t="inlineStr"/>
-      <c r="K170" s="11" t="inlineStr"/>
-      <c r="L170" s="11" t="inlineStr"/>
-      <c r="M170" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N170" s="11" t="inlineStr"/>
-      <c r="O170" s="11" t="inlineStr"/>
-      <c r="P170" s="11" t="inlineStr"/>
-      <c r="Q170" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R170" s="11" t="inlineStr"/>
-      <c r="S170" s="11" t="inlineStr"/>
-      <c r="T170" s="11" t="inlineStr"/>
-      <c r="U170" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V170" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W170" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="171" ht="26" customHeight="1">
-      <c r="A171" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B171" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C171" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D171" s="11" t="inlineStr">
-        <is>
-          <t>20260360244</t>
-        </is>
-      </c>
-      <c r="E171" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F171" s="11" t="inlineStr"/>
-      <c r="G171" s="11" t="inlineStr"/>
-      <c r="H171" s="11" t="inlineStr"/>
-      <c r="I171" s="11" t="inlineStr"/>
-      <c r="J171" s="11" t="inlineStr"/>
-      <c r="K171" s="11" t="inlineStr"/>
-      <c r="L171" s="11" t="inlineStr"/>
-      <c r="M171" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N171" s="11" t="inlineStr"/>
-      <c r="O171" s="11" t="inlineStr"/>
-      <c r="P171" s="11" t="inlineStr"/>
-      <c r="Q171" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R171" s="11" t="inlineStr"/>
-      <c r="S171" s="11" t="inlineStr"/>
-      <c r="T171" s="11" t="inlineStr"/>
-      <c r="U171" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V171" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W171" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="172" ht="26" customHeight="1">
-      <c r="A172" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B172" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C172" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D172" s="11" t="inlineStr">
-        <is>
-          <t>20260360267</t>
-        </is>
-      </c>
-      <c r="E172" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F172" s="11" t="inlineStr"/>
-      <c r="G172" s="11" t="inlineStr"/>
-      <c r="H172" s="11" t="inlineStr"/>
-      <c r="I172" s="11" t="inlineStr"/>
-      <c r="J172" s="11" t="inlineStr"/>
-      <c r="K172" s="11" t="inlineStr"/>
-      <c r="L172" s="11" t="inlineStr"/>
-      <c r="M172" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N172" s="11" t="inlineStr"/>
-      <c r="O172" s="11" t="inlineStr"/>
-      <c r="P172" s="11" t="inlineStr"/>
-      <c r="Q172" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R172" s="11" t="inlineStr"/>
-      <c r="S172" s="11" t="inlineStr"/>
-      <c r="T172" s="11" t="inlineStr"/>
-      <c r="U172" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V172" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W172" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="173" ht="26" customHeight="1">
-      <c r="A173" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B173" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C173" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D173" s="11" t="inlineStr">
-        <is>
-          <t>20260360296</t>
-        </is>
-      </c>
-      <c r="E173" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F173" s="11" t="inlineStr"/>
-      <c r="G173" s="11" t="inlineStr"/>
-      <c r="H173" s="11" t="inlineStr"/>
-      <c r="I173" s="11" t="inlineStr"/>
-      <c r="J173" s="11" t="inlineStr"/>
-      <c r="K173" s="11" t="inlineStr"/>
-      <c r="L173" s="11" t="inlineStr"/>
-      <c r="M173" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N173" s="11" t="inlineStr"/>
-      <c r="O173" s="11" t="inlineStr"/>
-      <c r="P173" s="11" t="inlineStr"/>
-      <c r="Q173" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R173" s="11" t="inlineStr"/>
-      <c r="S173" s="11" t="inlineStr"/>
-      <c r="T173" s="11" t="inlineStr"/>
-      <c r="U173" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V173" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W173" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="174" ht="26" customHeight="1">
-      <c r="A174" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B174" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C174" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D174" s="11" t="inlineStr">
-        <is>
-          <t>20260360297</t>
-        </is>
-      </c>
-      <c r="E174" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F174" s="11" t="inlineStr"/>
-      <c r="G174" s="11" t="inlineStr"/>
-      <c r="H174" s="11" t="inlineStr"/>
-      <c r="I174" s="11" t="inlineStr"/>
-      <c r="J174" s="11" t="inlineStr"/>
-      <c r="K174" s="11" t="inlineStr"/>
-      <c r="L174" s="11" t="inlineStr"/>
-      <c r="M174" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N174" s="11" t="inlineStr"/>
-      <c r="O174" s="11" t="inlineStr"/>
-      <c r="P174" s="11" t="inlineStr"/>
-      <c r="Q174" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R174" s="11" t="inlineStr"/>
-      <c r="S174" s="11" t="inlineStr"/>
-      <c r="T174" s="11" t="inlineStr"/>
-      <c r="U174" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V174" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W174" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="175" ht="26" customHeight="1">
-      <c r="A175" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B175" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C175" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D175" s="11" t="inlineStr">
-        <is>
-          <t>20260360335</t>
-        </is>
-      </c>
-      <c r="E175" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F175" s="11" t="inlineStr"/>
-      <c r="G175" s="11" t="inlineStr"/>
-      <c r="H175" s="11" t="inlineStr"/>
-      <c r="I175" s="11" t="inlineStr"/>
-      <c r="J175" s="11" t="inlineStr"/>
-      <c r="K175" s="11" t="inlineStr"/>
-      <c r="L175" s="11" t="inlineStr"/>
-      <c r="M175" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N175" s="11" t="inlineStr"/>
-      <c r="O175" s="11" t="inlineStr"/>
-      <c r="P175" s="11" t="inlineStr"/>
-      <c r="Q175" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R175" s="11" t="inlineStr"/>
-      <c r="S175" s="11" t="inlineStr"/>
-      <c r="T175" s="11" t="inlineStr"/>
-      <c r="U175" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V175" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W175" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="176" ht="26" customHeight="1">
-      <c r="A176" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B176" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C176" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D176" s="11" t="inlineStr">
-        <is>
-          <t>20260360337</t>
-        </is>
-      </c>
-      <c r="E176" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F176" s="11" t="inlineStr"/>
-      <c r="G176" s="11" t="inlineStr"/>
-      <c r="H176" s="11" t="inlineStr"/>
-      <c r="I176" s="11" t="inlineStr"/>
-      <c r="J176" s="11" t="inlineStr"/>
-      <c r="K176" s="11" t="inlineStr"/>
-      <c r="L176" s="11" t="inlineStr"/>
-      <c r="M176" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N176" s="11" t="inlineStr"/>
-      <c r="O176" s="11" t="inlineStr"/>
-      <c r="P176" s="11" t="inlineStr"/>
-      <c r="Q176" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R176" s="11" t="inlineStr"/>
-      <c r="S176" s="11" t="inlineStr"/>
-      <c r="T176" s="11" t="inlineStr"/>
-      <c r="U176" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V176" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W176" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="177" ht="26" customHeight="1">
-      <c r="A177" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B177" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C177" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D177" s="11" t="inlineStr">
-        <is>
-          <t>20260360338</t>
-        </is>
-      </c>
-      <c r="E177" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F177" s="11" t="inlineStr"/>
-      <c r="G177" s="11" t="inlineStr"/>
-      <c r="H177" s="11" t="inlineStr"/>
-      <c r="I177" s="11" t="inlineStr"/>
-      <c r="J177" s="11" t="inlineStr"/>
-      <c r="K177" s="11" t="inlineStr"/>
-      <c r="L177" s="11" t="inlineStr"/>
-      <c r="M177" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N177" s="11" t="inlineStr"/>
-      <c r="O177" s="11" t="inlineStr"/>
-      <c r="P177" s="11" t="inlineStr"/>
-      <c r="Q177" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R177" s="11" t="inlineStr"/>
-      <c r="S177" s="11" t="inlineStr"/>
-      <c r="T177" s="11" t="inlineStr"/>
-      <c r="U177" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V177" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W177" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
-    <row r="178" ht="26" customHeight="1">
-      <c r="A178" s="10" t="n">
-        <v>42</v>
-      </c>
-      <c r="B178" s="11" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="C178" s="11" t="inlineStr">
-        <is>
-          <t>HL</t>
-        </is>
-      </c>
-      <c r="D178" s="11" t="inlineStr">
-        <is>
-          <t>20260360380</t>
-        </is>
-      </c>
-      <c r="E178" s="11" t="inlineStr">
-        <is>
-          <t>2026-06-15</t>
-        </is>
-      </c>
-      <c r="F178" s="11" t="inlineStr"/>
-      <c r="G178" s="11" t="inlineStr"/>
-      <c r="H178" s="11" t="inlineStr"/>
-      <c r="I178" s="11" t="inlineStr"/>
-      <c r="J178" s="11" t="inlineStr"/>
-      <c r="K178" s="11" t="inlineStr"/>
-      <c r="L178" s="11" t="inlineStr"/>
-      <c r="M178" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="N178" s="11" t="inlineStr"/>
-      <c r="O178" s="11" t="inlineStr"/>
-      <c r="P178" s="11" t="inlineStr"/>
-      <c r="Q178" s="11" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="R178" s="11" t="inlineStr"/>
-      <c r="S178" s="11" t="inlineStr"/>
-      <c r="T178" s="11" t="inlineStr"/>
-      <c r="U178" s="11" t="inlineStr">
-        <is>
-          <t>Medical lien; New this week</t>
-        </is>
-      </c>
-      <c r="V178" s="11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W178" s="12" t="inlineStr">
-        <is>
-          <t>View ↗</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W178"/>
+  <autoFilter ref="A1:W144"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
@@ -12630,40 +10399,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W142" r:id="rId141"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W143" r:id="rId142"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W144" r:id="rId143"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W145" r:id="rId144"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W146" r:id="rId145"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W147" r:id="rId146"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W148" r:id="rId147"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W149" r:id="rId148"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W150" r:id="rId149"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W151" r:id="rId150"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W152" r:id="rId151"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W153" r:id="rId152"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W154" r:id="rId153"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W155" r:id="rId154"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W156" r:id="rId155"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W157" r:id="rId156"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W158" r:id="rId157"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W159" r:id="rId158"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W160" r:id="rId159"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W161" r:id="rId160"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W162" r:id="rId161"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W163" r:id="rId162"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W164" r:id="rId163"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W165" r:id="rId164"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W166" r:id="rId165"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W167" r:id="rId166"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W168" r:id="rId167"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W169" r:id="rId168"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W170" r:id="rId169"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W171" r:id="rId170"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W172" r:id="rId171"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W173" r:id="rId172"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W174" r:id="rId173"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W175" r:id="rId174"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W176" r:id="rId175"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W177" r:id="rId176"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W178" r:id="rId177"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12675,7 +10410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -12683,7 +10418,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Maricopa County Motivated Seller Leads</t>
         </is>
@@ -12692,148 +10427,158 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-06-16 06:41</t>
+          <t>Run: 2026-06-17 06:18</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="inlineStr"/>
-      <c r="B3" s="14" t="inlineStr"/>
+      <c r="A3" s="15" t="inlineStr"/>
+      <c r="B3" s="15" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Total Leads</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
-        <v>177</v>
+      <c r="B4" s="15" t="n">
+        <v>143</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="inlineStr">
+      <c r="A5" s="16" t="inlineStr">
         <is>
           <t>With Property Address</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
-        <v>18</v>
+      <c r="B5" s="15" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="inlineStr">
+      <c r="A6" s="16" t="inlineStr">
         <is>
           <t>With Mailing Address</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="inlineStr">
+      <c r="A7" s="16" t="inlineStr">
         <is>
           <t>PDF Parsed</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
-        <v>99</v>
+      <c r="B7" s="15" t="n">
+        <v>136</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Score 70+ (Hot)</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n">
-        <v>11</v>
+      <c r="B8" s="15" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Score 50-69 (Warm)</t>
         </is>
       </c>
-      <c r="B9" s="14" t="n">
+      <c r="B9" s="15" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr"/>
+      <c r="B10" s="15" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>By Category</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="inlineStr">
+        <is>
+          <t>Lis Pendens</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="inlineStr"/>
-      <c r="B10" s="14" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="inlineStr">
-        <is>
-          <t>By Category</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="inlineStr">
-        <is>
-          <t>Medical Lien</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="inlineStr">
-        <is>
-          <t>Lien</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="inlineStr">
-        <is>
-          <t>Judgment</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="inlineStr">
-        <is>
-          <t>Notice of Trustee Sale</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="n">
-        <v>20</v>
-      </c>
-    </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
         <is>
           <t>Probate Document</t>
         </is>
       </c>
-      <c r="B16" s="14" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="inlineStr">
+      <c r="B17" s="15" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
         <is>
           <t>Tax Deed</t>
         </is>
       </c>
-      <c r="B17" s="14" t="n">
-        <v>5</v>
+      <c r="B18" s="15" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-06-21 06:00</t>
+          <t>Run: 2026-06-22 06:29</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$115</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +34,39 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00374151"/>
       <sz val="10"/>
     </font>
     <font>
@@ -49,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +94,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E2433"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,14 +138,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +544,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -606,8 +689,8058 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>20260371243</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>SHANE HEDIN AND STEPHANIE HEDIN</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>ROCKET MORTGAGE, LLC S/B/M TO NATIONSTAR MORTGAGE LLC</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>382936</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>18035 W GOLDEN LN</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>WADDELL</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>85355</t>
+        </is>
+      </c>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>502-10-532</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>America West Lender Services, LLC</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>20260371961</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Ivan F Lopez Ortega and Jessica Lopez</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Carrington Mortgage Services, LLC</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>157592</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>3206 E CAMPO BELLO DR</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr"/>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Vylla Solutions, LLC</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>20260373085</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Patrick Smith</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>University Credit Union Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>189438</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr"/>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2108 E Fawn Dr</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>301-30-2136</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>University Credit Union Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>20260373137</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Andrew Francis Young</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>775000</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>15035 N 49th St</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr"/>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr"/>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>215-67-3862</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>20260373148</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>Michael J Howes and Terry L Howes</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>341000</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>11243 N 44th Ct</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr"/>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>167-67-0432</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>JPMorgan Chase Bank, National Association Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>20260373219</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Minh B Nguyen and Mai L Tang</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>NewRez LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>317599</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>2949 E Flossmoor Ave</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>140-45-3454</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>NewRez LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>20260373224</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Dwayne Brewington and Lawanza Lett-Brewington</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>NewRez LLC d/b/a Shellpoint Mortgage Servicing Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>116000</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>6219 South 47th Place</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>123-17-6478</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>NewRez LLC d/b/a Shellpoint Mortgage Servicing Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>20260373232</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>Armando Avalos and Robin Avalos</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Truist Bank Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>517655</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>18462 W Brookwood Dr</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>400-63-4290</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>Truist Bank Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>20260373465</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>DAVID O. CAPLAN AND LESLIE W. CAPLAN</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="4" t="n">
+        <v>312444</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>25424 N 63RD LN PHOENIX, AZ 85083</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>201-10-447</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>Diane Weifenbach Esq.</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>20260371156</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>DAVID RAY CORDOVA</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>DEUTSCHE BANK NATIONAL TRUST COMPANY as Trustee for INDYMAC INDX MORTGAGE LOAN</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="n">
+        <v>370640</v>
+      </c>
+      <c r="I11" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="inlineStr"/>
+      <c r="L11" s="7" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr"/>
+      <c r="O11" s="7" t="inlineStr"/>
+      <c r="P11" s="7" t="inlineStr"/>
+      <c r="Q11" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R11" s="7" t="inlineStr"/>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>210-20-237</t>
+        </is>
+      </c>
+      <c r="T11" s="7" t="inlineStr">
+        <is>
+          <t>| Western Progressive — Arizona, Inc.</t>
+        </is>
+      </c>
+      <c r="U11" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V11" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>20260371468</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>Suzette Michelle Perez</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>254210</v>
+      </c>
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="inlineStr"/>
+      <c r="L12" s="7" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr"/>
+      <c r="O12" s="7" t="inlineStr"/>
+      <c r="P12" s="7" t="inlineStr"/>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr"/>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>501-74-3225</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
+        <is>
+          <t>Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U12" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V12" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>20260371719</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>ity Mi ion F/K/A PHH M e ion</t>
+        </is>
+      </c>
+      <c r="H13" s="8" t="n">
+        <v>221704</v>
+      </c>
+      <c r="I13" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K13" s="7" t="inlineStr"/>
+      <c r="L13" s="7" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr"/>
+      <c r="O13" s="7" t="inlineStr"/>
+      <c r="P13" s="7" t="inlineStr"/>
+      <c r="Q13" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R13" s="7" t="inlineStr"/>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>200-82-3523</t>
+        </is>
+      </c>
+      <c r="T13" s="7" t="inlineStr">
+        <is>
+          <t>Western Progressive — Arizona, Inc.</t>
+        </is>
+      </c>
+      <c r="U13" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V13" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>20260372597</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>AZTEX SOLUTIONS LLC, AN ARIZONA LIMITED LIABILITY COMPANY</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Wiknington Trust, National Association not in its individual capacity but solely as Trustee of Endea</t>
+        </is>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>342550</v>
+      </c>
+      <c r="I14" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K14" s="7" t="inlineStr"/>
+      <c r="L14" s="7" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr"/>
+      <c r="O14" s="7" t="inlineStr"/>
+      <c r="P14" s="7" t="inlineStr"/>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr"/>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>303-60-265</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
+        <is>
+          <t>Western Progressive — Arizona, Inc.</t>
+        </is>
+      </c>
+      <c r="U14" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+        </is>
+      </c>
+      <c r="V14" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C15" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>20260373141</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>C/O LoanCare, LLC</t>
+        </is>
+      </c>
+      <c r="H15" s="8" t="n">
+        <v>235653</v>
+      </c>
+      <c r="I15" s="7" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K15" s="7" t="inlineStr"/>
+      <c r="L15" s="7" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr"/>
+      <c r="O15" s="7" t="inlineStr"/>
+      <c r="P15" s="7" t="inlineStr"/>
+      <c r="Q15" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R15" s="7" t="inlineStr"/>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>141-86-324</t>
+        </is>
+      </c>
+      <c r="T15" s="7" t="inlineStr"/>
+      <c r="U15" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V15" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>20260373146</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>C/O Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H16" s="8" t="n">
+        <v>400000</v>
+      </c>
+      <c r="I16" s="7" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building</t>
+        </is>
+      </c>
+      <c r="K16" s="7" t="inlineStr"/>
+      <c r="L16" s="7" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr"/>
+      <c r="O16" s="7" t="inlineStr"/>
+      <c r="P16" s="7" t="inlineStr"/>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr"/>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>503-55-689</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr"/>
+      <c r="U16" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V16" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>20260373236</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>Gordan MacGregor</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H17" s="8" t="n">
+        <v>73500</v>
+      </c>
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="inlineStr">
+        <is>
+          <t>1207 East Minton Drive</t>
+        </is>
+      </c>
+      <c r="L17" s="7" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr"/>
+      <c r="O17" s="7" t="inlineStr"/>
+      <c r="P17" s="7" t="inlineStr"/>
+      <c r="Q17" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R17" s="7" t="inlineStr"/>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>133-38-2996</t>
+        </is>
+      </c>
+      <c r="T17" s="7" t="inlineStr">
+        <is>
+          <t>Desert Financial Credit Union Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U17" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V17" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>20260373408</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>LEONARD E COLEMAN AND ELAINE COLEMAN</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="8" t="n">
+        <v>63000</v>
+      </c>
+      <c r="I18" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>2255 E WIER AVE</t>
+        </is>
+      </c>
+      <c r="L18" s="7" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="M18" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>85040</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr"/>
+      <c r="P18" s="7" t="inlineStr"/>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr"/>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>122-07-026</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U18" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V18" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>20260373609</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>JOHN J. CLOW AND SHAUNA C. CLOW</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>The Bank of New York Mellon f/k/a The Bank of New York as Indenture trustee for CWHEQ Revolving Home</t>
+        </is>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>71500</v>
+      </c>
+      <c r="I19" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="inlineStr">
+        <is>
+          <t>28379 NORTH 113TH WAY</t>
+        </is>
+      </c>
+      <c r="L19" s="7" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr"/>
+      <c r="O19" s="7" t="inlineStr"/>
+      <c r="P19" s="7" t="inlineStr"/>
+      <c r="Q19" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R19" s="7" t="inlineStr"/>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>216-74-028</t>
+        </is>
+      </c>
+      <c r="T19" s="7" t="inlineStr">
+        <is>
+          <t>Michelle R. Ghidotti, Esq.</t>
+        </is>
+      </c>
+      <c r="U19" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V19" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>20260373682</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>C/O Bank of America, N.A.</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="n">
+        <v>54000</v>
+      </c>
+      <c r="I20" s="7" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K20" s="7" t="inlineStr"/>
+      <c r="L20" s="7" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr"/>
+      <c r="O20" s="7" t="inlineStr"/>
+      <c r="P20" s="7" t="inlineStr"/>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr"/>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>136-26-7643</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr"/>
+      <c r="U20" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V20" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>20260371809</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="8" t="n">
+        <v>171317</v>
+      </c>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr"/>
+      <c r="K21" s="7" t="inlineStr"/>
+      <c r="L21" s="7" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr"/>
+      <c r="O21" s="7" t="inlineStr"/>
+      <c r="P21" s="7" t="inlineStr"/>
+      <c r="Q21" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="7" t="inlineStr"/>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>304-34-016</t>
+        </is>
+      </c>
+      <c r="T21" s="7" t="inlineStr"/>
+      <c r="U21" s="7" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V21" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>20260372533</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>MOHAMMAD KHALIK</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>LAKEVIEW LOAN SERVICING, LLC</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr"/>
+      <c r="I22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K22" s="7" t="inlineStr">
+        <is>
+          <t>11248 E UPTON AVE</t>
+        </is>
+      </c>
+      <c r="L22" s="7" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr"/>
+      <c r="O22" s="7" t="inlineStr"/>
+      <c r="P22" s="7" t="inlineStr"/>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr"/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>304-37-462</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="U22" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V22" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>20260372542</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>DALE A. THOMAS AND ANN C. THOMAS</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>PNC BANK NATIONAL ASSOCIATION</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr"/>
+      <c r="I23" s="7" t="inlineStr"/>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K23" s="7" t="inlineStr">
+        <is>
+          <t>5930 S WHITE PL</t>
+        </is>
+      </c>
+      <c r="L23" s="7" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr"/>
+      <c r="O23" s="7" t="inlineStr"/>
+      <c r="P23" s="7" t="inlineStr"/>
+      <c r="Q23" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R23" s="7" t="inlineStr"/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>304-82-351</t>
+        </is>
+      </c>
+      <c r="T23" s="7" t="inlineStr">
+        <is>
+          <t>Clear Recon Corp</t>
+        </is>
+      </c>
+      <c r="U23" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V23" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="6" t="n">
+        <v>58</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>20260373592</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>TRACI DEAN</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>MEB Loan Trust VIII</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>25747.5</v>
+      </c>
+      <c r="I24" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J24" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
+        <is>
+          <t>8241 W RUE DE LAMOUR</t>
+        </is>
+      </c>
+      <c r="L24" s="7" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr"/>
+      <c r="O24" s="7" t="inlineStr"/>
+      <c r="P24" s="7" t="inlineStr"/>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R24" s="7" t="inlineStr"/>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>231-15-087</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr">
+        <is>
+          <t>Michelle R. Ghidotti, Esq.</t>
+        </is>
+      </c>
+      <c r="U24" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V24" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>20260372510</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
+      <c r="I25" s="7" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K25" s="7" t="inlineStr"/>
+      <c r="L25" s="7" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr"/>
+      <c r="O25" s="7" t="inlineStr"/>
+      <c r="P25" s="7" t="inlineStr"/>
+      <c r="Q25" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R25" s="7" t="inlineStr"/>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>200-81-15517</t>
+        </is>
+      </c>
+      <c r="T25" s="7" t="inlineStr"/>
+      <c r="U25" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V25" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>20260373348</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="7" t="inlineStr">
+        <is>
+          <t>6430 S. 37" St., Phoenix, AZ 85042</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>45475</v>
+      </c>
+      <c r="I26" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="J26" s="7" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K26" s="7" t="inlineStr"/>
+      <c r="L26" s="7" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr"/>
+      <c r="O26" s="7" t="inlineStr"/>
+      <c r="P26" s="7" t="inlineStr"/>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr"/>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>401-42-383</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr"/>
+      <c r="U26" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V26" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>20260370752</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr"/>
+      <c r="G27" s="11" t="inlineStr"/>
+      <c r="H27" s="11" t="inlineStr"/>
+      <c r="I27" s="11" t="inlineStr"/>
+      <c r="J27" s="11" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr"/>
+      <c r="L27" s="11" t="inlineStr"/>
+      <c r="M27" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N27" s="11" t="inlineStr"/>
+      <c r="O27" s="11" t="inlineStr"/>
+      <c r="P27" s="11" t="inlineStr"/>
+      <c r="Q27" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R27" s="11" t="inlineStr"/>
+      <c r="S27" s="11" t="inlineStr"/>
+      <c r="T27" s="11" t="inlineStr"/>
+      <c r="U27" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V27" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W27" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>20260370753</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr"/>
+      <c r="G28" s="11" t="inlineStr"/>
+      <c r="H28" s="11" t="inlineStr"/>
+      <c r="I28" s="11" t="inlineStr"/>
+      <c r="J28" s="11" t="inlineStr"/>
+      <c r="K28" s="11" t="inlineStr"/>
+      <c r="L28" s="11" t="inlineStr"/>
+      <c r="M28" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N28" s="11" t="inlineStr"/>
+      <c r="O28" s="11" t="inlineStr"/>
+      <c r="P28" s="11" t="inlineStr"/>
+      <c r="Q28" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R28" s="11" t="inlineStr"/>
+      <c r="S28" s="11" t="inlineStr"/>
+      <c r="T28" s="11" t="inlineStr"/>
+      <c r="U28" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V28" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W28" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>20260370754</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr"/>
+      <c r="G29" s="11" t="inlineStr"/>
+      <c r="H29" s="11" t="inlineStr"/>
+      <c r="I29" s="11" t="inlineStr"/>
+      <c r="J29" s="11" t="inlineStr"/>
+      <c r="K29" s="11" t="inlineStr"/>
+      <c r="L29" s="11" t="inlineStr"/>
+      <c r="M29" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N29" s="11" t="inlineStr"/>
+      <c r="O29" s="11" t="inlineStr"/>
+      <c r="P29" s="11" t="inlineStr"/>
+      <c r="Q29" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R29" s="11" t="inlineStr"/>
+      <c r="S29" s="11" t="inlineStr"/>
+      <c r="T29" s="11" t="inlineStr"/>
+      <c r="U29" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V29" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W29" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>20260370755</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr"/>
+      <c r="G30" s="11" t="inlineStr"/>
+      <c r="H30" s="11" t="inlineStr"/>
+      <c r="I30" s="11" t="inlineStr"/>
+      <c r="J30" s="11" t="inlineStr"/>
+      <c r="K30" s="11" t="inlineStr"/>
+      <c r="L30" s="11" t="inlineStr"/>
+      <c r="M30" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N30" s="11" t="inlineStr"/>
+      <c r="O30" s="11" t="inlineStr"/>
+      <c r="P30" s="11" t="inlineStr"/>
+      <c r="Q30" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R30" s="11" t="inlineStr"/>
+      <c r="S30" s="11" t="inlineStr"/>
+      <c r="T30" s="11" t="inlineStr"/>
+      <c r="U30" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V30" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W30" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>20260370756</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr"/>
+      <c r="G31" s="11" t="inlineStr"/>
+      <c r="H31" s="11" t="inlineStr"/>
+      <c r="I31" s="11" t="inlineStr"/>
+      <c r="J31" s="11" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr"/>
+      <c r="L31" s="11" t="inlineStr"/>
+      <c r="M31" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N31" s="11" t="inlineStr"/>
+      <c r="O31" s="11" t="inlineStr"/>
+      <c r="P31" s="11" t="inlineStr"/>
+      <c r="Q31" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R31" s="11" t="inlineStr"/>
+      <c r="S31" s="11" t="inlineStr"/>
+      <c r="T31" s="11" t="inlineStr"/>
+      <c r="U31" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V31" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W31" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>20260370759</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr"/>
+      <c r="G32" s="11" t="inlineStr"/>
+      <c r="H32" s="11" t="inlineStr"/>
+      <c r="I32" s="11" t="inlineStr"/>
+      <c r="J32" s="11" t="inlineStr"/>
+      <c r="K32" s="11" t="inlineStr"/>
+      <c r="L32" s="11" t="inlineStr"/>
+      <c r="M32" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N32" s="11" t="inlineStr"/>
+      <c r="O32" s="11" t="inlineStr"/>
+      <c r="P32" s="11" t="inlineStr"/>
+      <c r="Q32" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R32" s="11" t="inlineStr"/>
+      <c r="S32" s="11" t="inlineStr"/>
+      <c r="T32" s="11" t="inlineStr"/>
+      <c r="U32" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V32" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W32" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>20260370895</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr"/>
+      <c r="G33" s="11" t="inlineStr"/>
+      <c r="H33" s="11" t="inlineStr"/>
+      <c r="I33" s="11" t="inlineStr"/>
+      <c r="J33" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr"/>
+      <c r="L33" s="11" t="inlineStr"/>
+      <c r="M33" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N33" s="11" t="inlineStr"/>
+      <c r="O33" s="11" t="inlineStr"/>
+      <c r="P33" s="11" t="inlineStr"/>
+      <c r="Q33" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R33" s="11" t="inlineStr"/>
+      <c r="S33" s="11" t="inlineStr"/>
+      <c r="T33" s="11" t="inlineStr"/>
+      <c r="U33" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V33" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W33" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>20260371203</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr"/>
+      <c r="G34" s="11" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="11" t="inlineStr"/>
+      <c r="J34" s="11" t="inlineStr"/>
+      <c r="K34" s="11" t="inlineStr"/>
+      <c r="L34" s="11" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N34" s="11" t="inlineStr"/>
+      <c r="O34" s="11" t="inlineStr"/>
+      <c r="P34" s="11" t="inlineStr"/>
+      <c r="Q34" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R34" s="11" t="inlineStr"/>
+      <c r="S34" s="11" t="inlineStr"/>
+      <c r="T34" s="11" t="inlineStr"/>
+      <c r="U34" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V34" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>20260371220</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr"/>
+      <c r="G35" s="11" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr"/>
+      <c r="I35" s="11" t="inlineStr"/>
+      <c r="J35" s="11" t="inlineStr"/>
+      <c r="K35" s="11" t="inlineStr"/>
+      <c r="L35" s="11" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr"/>
+      <c r="O35" s="11" t="inlineStr"/>
+      <c r="P35" s="11" t="inlineStr"/>
+      <c r="Q35" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R35" s="11" t="inlineStr"/>
+      <c r="S35" s="11" t="inlineStr"/>
+      <c r="T35" s="11" t="inlineStr"/>
+      <c r="U35" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V35" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>20260371230</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr"/>
+      <c r="G36" s="11" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr"/>
+      <c r="I36" s="11" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr"/>
+      <c r="K36" s="11" t="inlineStr"/>
+      <c r="L36" s="11" t="inlineStr"/>
+      <c r="M36" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N36" s="11" t="inlineStr"/>
+      <c r="O36" s="11" t="inlineStr"/>
+      <c r="P36" s="11" t="inlineStr"/>
+      <c r="Q36" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R36" s="11" t="inlineStr"/>
+      <c r="S36" s="11" t="inlineStr"/>
+      <c r="T36" s="11" t="inlineStr"/>
+      <c r="U36" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V36" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W36" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>20260371249</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr"/>
+      <c r="G37" s="11" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr"/>
+      <c r="I37" s="11" t="inlineStr"/>
+      <c r="J37" s="11" t="inlineStr"/>
+      <c r="K37" s="11" t="inlineStr"/>
+      <c r="L37" s="11" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr"/>
+      <c r="O37" s="11" t="inlineStr"/>
+      <c r="P37" s="11" t="inlineStr"/>
+      <c r="Q37" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R37" s="11" t="inlineStr"/>
+      <c r="S37" s="11" t="inlineStr"/>
+      <c r="T37" s="11" t="inlineStr"/>
+      <c r="U37" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V37" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W37" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>20260371251</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr"/>
+      <c r="G38" s="11" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr"/>
+      <c r="I38" s="11" t="inlineStr"/>
+      <c r="J38" s="11" t="inlineStr"/>
+      <c r="K38" s="11" t="inlineStr"/>
+      <c r="L38" s="11" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N38" s="11" t="inlineStr"/>
+      <c r="O38" s="11" t="inlineStr"/>
+      <c r="P38" s="11" t="inlineStr"/>
+      <c r="Q38" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R38" s="11" t="inlineStr"/>
+      <c r="S38" s="11" t="inlineStr"/>
+      <c r="T38" s="11" t="inlineStr"/>
+      <c r="U38" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V38" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W38" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>20260371252</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr"/>
+      <c r="G39" s="11" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr"/>
+      <c r="I39" s="11" t="inlineStr"/>
+      <c r="J39" s="11" t="inlineStr"/>
+      <c r="K39" s="11" t="inlineStr"/>
+      <c r="L39" s="11" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr"/>
+      <c r="O39" s="11" t="inlineStr"/>
+      <c r="P39" s="11" t="inlineStr"/>
+      <c r="Q39" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R39" s="11" t="inlineStr"/>
+      <c r="S39" s="11" t="inlineStr"/>
+      <c r="T39" s="11" t="inlineStr"/>
+      <c r="U39" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V39" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W39" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>20260371253</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr"/>
+      <c r="G40" s="11" t="inlineStr"/>
+      <c r="H40" s="11" t="inlineStr"/>
+      <c r="I40" s="11" t="inlineStr"/>
+      <c r="J40" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="inlineStr"/>
+      <c r="L40" s="11" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N40" s="11" t="inlineStr"/>
+      <c r="O40" s="11" t="inlineStr"/>
+      <c r="P40" s="11" t="inlineStr"/>
+      <c r="Q40" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R40" s="11" t="inlineStr"/>
+      <c r="S40" s="11" t="inlineStr"/>
+      <c r="T40" s="11" t="inlineStr"/>
+      <c r="U40" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V40" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W40" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>20260371722</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr"/>
+      <c r="G41" s="11" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr"/>
+      <c r="I41" s="11" t="inlineStr"/>
+      <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr"/>
+      <c r="L41" s="11" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr"/>
+      <c r="O41" s="11" t="inlineStr"/>
+      <c r="P41" s="11" t="inlineStr"/>
+      <c r="Q41" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R41" s="11" t="inlineStr"/>
+      <c r="S41" s="11" t="inlineStr"/>
+      <c r="T41" s="11" t="inlineStr"/>
+      <c r="U41" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V41" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W41" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>20260372075</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr"/>
+      <c r="G42" s="11" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr"/>
+      <c r="I42" s="11" t="inlineStr"/>
+      <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr"/>
+      <c r="L42" s="11" t="inlineStr"/>
+      <c r="M42" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N42" s="11" t="inlineStr"/>
+      <c r="O42" s="11" t="inlineStr"/>
+      <c r="P42" s="11" t="inlineStr"/>
+      <c r="Q42" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R42" s="11" t="inlineStr"/>
+      <c r="S42" s="11" t="inlineStr"/>
+      <c r="T42" s="11" t="inlineStr"/>
+      <c r="U42" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V42" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W42" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>20260372279</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr"/>
+      <c r="G43" s="11" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr"/>
+      <c r="I43" s="11" t="inlineStr"/>
+      <c r="J43" s="11" t="inlineStr"/>
+      <c r="K43" s="11" t="inlineStr"/>
+      <c r="L43" s="11" t="inlineStr"/>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr"/>
+      <c r="O43" s="11" t="inlineStr"/>
+      <c r="P43" s="11" t="inlineStr"/>
+      <c r="Q43" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R43" s="11" t="inlineStr"/>
+      <c r="S43" s="11" t="inlineStr"/>
+      <c r="T43" s="11" t="inlineStr"/>
+      <c r="U43" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V43" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W43" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>20260372755</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr"/>
+      <c r="G44" s="11" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr"/>
+      <c r="I44" s="11" t="inlineStr"/>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court of the State of Arizona</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="inlineStr"/>
+      <c r="L44" s="11" t="inlineStr"/>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr"/>
+      <c r="O44" s="11" t="inlineStr"/>
+      <c r="P44" s="11" t="inlineStr"/>
+      <c r="Q44" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R44" s="11" t="inlineStr"/>
+      <c r="S44" s="11" t="inlineStr"/>
+      <c r="T44" s="11" t="inlineStr"/>
+      <c r="U44" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V44" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W44" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>20260373355</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr"/>
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr"/>
+      <c r="I45" s="11" t="inlineStr"/>
+      <c r="J45" s="11" t="inlineStr"/>
+      <c r="K45" s="11" t="inlineStr"/>
+      <c r="L45" s="11" t="inlineStr"/>
+      <c r="M45" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N45" s="11" t="inlineStr"/>
+      <c r="O45" s="11" t="inlineStr"/>
+      <c r="P45" s="11" t="inlineStr"/>
+      <c r="Q45" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R45" s="11" t="inlineStr"/>
+      <c r="S45" s="11" t="inlineStr"/>
+      <c r="T45" s="11" t="inlineStr"/>
+      <c r="U45" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V45" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W45" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>20260373563</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr"/>
+      <c r="G46" s="11" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr"/>
+      <c r="I46" s="11" t="inlineStr"/>
+      <c r="J46" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court of the State of Arizona</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr"/>
+      <c r="L46" s="11" t="inlineStr"/>
+      <c r="M46" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N46" s="11" t="inlineStr"/>
+      <c r="O46" s="11" t="inlineStr"/>
+      <c r="P46" s="11" t="inlineStr"/>
+      <c r="Q46" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R46" s="11" t="inlineStr"/>
+      <c r="S46" s="11" t="inlineStr"/>
+      <c r="T46" s="11" t="inlineStr"/>
+      <c r="U46" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V46" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W46" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>20260373765</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr"/>
+      <c r="G47" s="11" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr"/>
+      <c r="I47" s="11" t="inlineStr"/>
+      <c r="J47" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr"/>
+      <c r="L47" s="11" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N47" s="11" t="inlineStr"/>
+      <c r="O47" s="11" t="inlineStr"/>
+      <c r="P47" s="11" t="inlineStr"/>
+      <c r="Q47" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R47" s="11" t="inlineStr"/>
+      <c r="S47" s="11" t="inlineStr"/>
+      <c r="T47" s="11" t="inlineStr"/>
+      <c r="U47" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V47" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W47" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>20260373766</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr"/>
+      <c r="G48" s="11" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr"/>
+      <c r="I48" s="11" t="inlineStr"/>
+      <c r="J48" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="inlineStr"/>
+      <c r="L48" s="11" t="inlineStr"/>
+      <c r="M48" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N48" s="11" t="inlineStr"/>
+      <c r="O48" s="11" t="inlineStr"/>
+      <c r="P48" s="11" t="inlineStr"/>
+      <c r="Q48" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R48" s="11" t="inlineStr"/>
+      <c r="S48" s="11" t="inlineStr"/>
+      <c r="T48" s="11" t="inlineStr"/>
+      <c r="U48" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V48" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W48" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>20260373767</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr"/>
+      <c r="G49" s="11" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr"/>
+      <c r="I49" s="11" t="inlineStr"/>
+      <c r="J49" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="inlineStr"/>
+      <c r="L49" s="11" t="inlineStr"/>
+      <c r="M49" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N49" s="11" t="inlineStr"/>
+      <c r="O49" s="11" t="inlineStr"/>
+      <c r="P49" s="11" t="inlineStr"/>
+      <c r="Q49" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R49" s="11" t="inlineStr"/>
+      <c r="S49" s="11" t="inlineStr"/>
+      <c r="T49" s="11" t="inlineStr"/>
+      <c r="U49" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V49" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W49" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>20260373768</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr"/>
+      <c r="G50" s="11" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr"/>
+      <c r="I50" s="11" t="inlineStr"/>
+      <c r="J50" s="11" t="inlineStr"/>
+      <c r="K50" s="11" t="inlineStr"/>
+      <c r="L50" s="11" t="inlineStr"/>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N50" s="11" t="inlineStr"/>
+      <c r="O50" s="11" t="inlineStr"/>
+      <c r="P50" s="11" t="inlineStr"/>
+      <c r="Q50" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R50" s="11" t="inlineStr"/>
+      <c r="S50" s="11" t="inlineStr"/>
+      <c r="T50" s="11" t="inlineStr"/>
+      <c r="U50" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V50" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W50" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>20260373769</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr"/>
+      <c r="H51" s="11" t="inlineStr"/>
+      <c r="I51" s="11" t="inlineStr"/>
+      <c r="J51" s="11" t="inlineStr"/>
+      <c r="K51" s="11" t="inlineStr"/>
+      <c r="L51" s="11" t="inlineStr"/>
+      <c r="M51" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N51" s="11" t="inlineStr"/>
+      <c r="O51" s="11" t="inlineStr"/>
+      <c r="P51" s="11" t="inlineStr"/>
+      <c r="Q51" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R51" s="11" t="inlineStr"/>
+      <c r="S51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr"/>
+      <c r="U51" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W51" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>20260373770</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr"/>
+      <c r="G52" s="11" t="inlineStr"/>
+      <c r="H52" s="11" t="inlineStr"/>
+      <c r="I52" s="11" t="inlineStr"/>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
+      <c r="L52" s="11" t="inlineStr"/>
+      <c r="M52" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N52" s="11" t="inlineStr"/>
+      <c r="O52" s="11" t="inlineStr"/>
+      <c r="P52" s="11" t="inlineStr"/>
+      <c r="Q52" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R52" s="11" t="inlineStr"/>
+      <c r="S52" s="11" t="inlineStr"/>
+      <c r="T52" s="11" t="inlineStr"/>
+      <c r="U52" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V52" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W52" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>20260373771</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr"/>
+      <c r="G53" s="11" t="inlineStr"/>
+      <c r="H53" s="11" t="inlineStr"/>
+      <c r="I53" s="11" t="inlineStr"/>
+      <c r="J53" s="11" t="inlineStr"/>
+      <c r="K53" s="11" t="inlineStr"/>
+      <c r="L53" s="11" t="inlineStr"/>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N53" s="11" t="inlineStr"/>
+      <c r="O53" s="11" t="inlineStr"/>
+      <c r="P53" s="11" t="inlineStr"/>
+      <c r="Q53" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R53" s="11" t="inlineStr"/>
+      <c r="S53" s="11" t="inlineStr"/>
+      <c r="T53" s="11" t="inlineStr"/>
+      <c r="U53" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V53" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W53" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>20260373772</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr"/>
+      <c r="G54" s="11" t="inlineStr"/>
+      <c r="H54" s="11" t="inlineStr"/>
+      <c r="I54" s="11" t="inlineStr"/>
+      <c r="J54" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr"/>
+      <c r="L54" s="11" t="inlineStr"/>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N54" s="11" t="inlineStr"/>
+      <c r="O54" s="11" t="inlineStr"/>
+      <c r="P54" s="11" t="inlineStr"/>
+      <c r="Q54" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R54" s="11" t="inlineStr"/>
+      <c r="S54" s="11" t="inlineStr"/>
+      <c r="T54" s="11" t="inlineStr"/>
+      <c r="U54" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V54" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W54" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>20260373773</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr"/>
+      <c r="G55" s="11" t="inlineStr"/>
+      <c r="H55" s="11" t="inlineStr"/>
+      <c r="I55" s="11" t="inlineStr"/>
+      <c r="J55" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="inlineStr"/>
+      <c r="L55" s="11" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N55" s="11" t="inlineStr"/>
+      <c r="O55" s="11" t="inlineStr"/>
+      <c r="P55" s="11" t="inlineStr"/>
+      <c r="Q55" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R55" s="11" t="inlineStr"/>
+      <c r="S55" s="11" t="inlineStr"/>
+      <c r="T55" s="11" t="inlineStr"/>
+      <c r="U55" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V55" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W55" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>20260373774</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr"/>
+      <c r="G56" s="11" t="inlineStr"/>
+      <c r="H56" s="11" t="inlineStr"/>
+      <c r="I56" s="11" t="inlineStr"/>
+      <c r="J56" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr"/>
+      <c r="L56" s="11" t="inlineStr"/>
+      <c r="M56" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N56" s="11" t="inlineStr"/>
+      <c r="O56" s="11" t="inlineStr"/>
+      <c r="P56" s="11" t="inlineStr"/>
+      <c r="Q56" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R56" s="11" t="inlineStr"/>
+      <c r="S56" s="11" t="inlineStr"/>
+      <c r="T56" s="11" t="inlineStr"/>
+      <c r="U56" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V56" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W56" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>20260373810</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr"/>
+      <c r="G57" s="11" t="inlineStr"/>
+      <c r="H57" s="11" t="inlineStr"/>
+      <c r="I57" s="11" t="inlineStr"/>
+      <c r="J57" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court in Maricopa County.</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr"/>
+      <c r="L57" s="11" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N57" s="11" t="inlineStr"/>
+      <c r="O57" s="11" t="inlineStr"/>
+      <c r="P57" s="11" t="inlineStr"/>
+      <c r="Q57" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R57" s="11" t="inlineStr"/>
+      <c r="S57" s="11" t="inlineStr"/>
+      <c r="T57" s="11" t="inlineStr"/>
+      <c r="U57" s="11" t="inlineStr">
+        <is>
+          <t>Judgment lien; New this week</t>
+        </is>
+      </c>
+      <c r="V57" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W57" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>20260372257</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr"/>
+      <c r="G58" s="11" t="inlineStr"/>
+      <c r="H58" s="11" t="inlineStr"/>
+      <c r="I58" s="11" t="inlineStr"/>
+      <c r="J58" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr"/>
+      <c r="L58" s="11" t="inlineStr"/>
+      <c r="M58" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N58" s="11" t="inlineStr"/>
+      <c r="O58" s="11" t="inlineStr"/>
+      <c r="P58" s="11" t="inlineStr"/>
+      <c r="Q58" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R58" s="11" t="inlineStr"/>
+      <c r="S58" s="11" t="inlineStr"/>
+      <c r="T58" s="11" t="inlineStr"/>
+      <c r="U58" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V58" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W58" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>20260373072</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr"/>
+      <c r="G59" s="11" t="inlineStr"/>
+      <c r="H59" s="11" t="inlineStr"/>
+      <c r="I59" s="11" t="inlineStr"/>
+      <c r="J59" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K59" s="11" t="inlineStr"/>
+      <c r="L59" s="11" t="inlineStr"/>
+      <c r="M59" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N59" s="11" t="inlineStr"/>
+      <c r="O59" s="11" t="inlineStr"/>
+      <c r="P59" s="11" t="inlineStr"/>
+      <c r="Q59" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R59" s="11" t="inlineStr"/>
+      <c r="S59" s="11" t="inlineStr">
+        <is>
+          <t>113-14-011</t>
+        </is>
+      </c>
+      <c r="T59" s="11" t="inlineStr"/>
+      <c r="U59" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V59" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W59" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>20260372148</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr"/>
+      <c r="G60" s="11" t="inlineStr"/>
+      <c r="H60" s="11" t="inlineStr"/>
+      <c r="I60" s="11" t="inlineStr"/>
+      <c r="J60" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr"/>
+      <c r="L60" s="11" t="inlineStr"/>
+      <c r="M60" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N60" s="11" t="inlineStr"/>
+      <c r="O60" s="11" t="inlineStr"/>
+      <c r="P60" s="11" t="inlineStr"/>
+      <c r="Q60" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R60" s="11" t="inlineStr"/>
+      <c r="S60" s="11" t="inlineStr"/>
+      <c r="T60" s="11" t="inlineStr"/>
+      <c r="U60" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V60" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W60" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>20260372209</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr"/>
+      <c r="G61" s="11" t="inlineStr"/>
+      <c r="H61" s="11" t="inlineStr"/>
+      <c r="I61" s="11" t="inlineStr"/>
+      <c r="J61" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="inlineStr"/>
+      <c r="L61" s="11" t="inlineStr"/>
+      <c r="M61" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N61" s="11" t="inlineStr"/>
+      <c r="O61" s="11" t="inlineStr"/>
+      <c r="P61" s="11" t="inlineStr"/>
+      <c r="Q61" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R61" s="11" t="inlineStr"/>
+      <c r="S61" s="11" t="inlineStr"/>
+      <c r="T61" s="11" t="inlineStr"/>
+      <c r="U61" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V61" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W61" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>20260372216</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr"/>
+      <c r="G62" s="11" t="inlineStr"/>
+      <c r="H62" s="11" t="inlineStr"/>
+      <c r="I62" s="11" t="inlineStr"/>
+      <c r="J62" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K62" s="11" t="inlineStr"/>
+      <c r="L62" s="11" t="inlineStr"/>
+      <c r="M62" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N62" s="11" t="inlineStr"/>
+      <c r="O62" s="11" t="inlineStr"/>
+      <c r="P62" s="11" t="inlineStr"/>
+      <c r="Q62" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R62" s="11" t="inlineStr"/>
+      <c r="S62" s="11" t="inlineStr"/>
+      <c r="T62" s="11" t="inlineStr"/>
+      <c r="U62" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V62" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W62" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>20260372275</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr"/>
+      <c r="G63" s="11" t="inlineStr"/>
+      <c r="H63" s="11" t="inlineStr"/>
+      <c r="I63" s="11" t="inlineStr"/>
+      <c r="J63" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K63" s="11" t="inlineStr"/>
+      <c r="L63" s="11" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N63" s="11" t="inlineStr"/>
+      <c r="O63" s="11" t="inlineStr"/>
+      <c r="P63" s="11" t="inlineStr"/>
+      <c r="Q63" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R63" s="11" t="inlineStr"/>
+      <c r="S63" s="11" t="inlineStr"/>
+      <c r="T63" s="11" t="inlineStr"/>
+      <c r="U63" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V63" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W63" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>20260371532</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr"/>
+      <c r="G64" s="11" t="inlineStr"/>
+      <c r="H64" s="11" t="inlineStr"/>
+      <c r="I64" s="11" t="inlineStr"/>
+      <c r="J64" s="11" t="inlineStr"/>
+      <c r="K64" s="11" t="inlineStr"/>
+      <c r="L64" s="11" t="inlineStr"/>
+      <c r="M64" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N64" s="11" t="inlineStr"/>
+      <c r="O64" s="11" t="inlineStr"/>
+      <c r="P64" s="11" t="inlineStr"/>
+      <c r="Q64" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R64" s="11" t="inlineStr"/>
+      <c r="S64" s="11" t="inlineStr">
+        <is>
+          <t>502-35-845</t>
+        </is>
+      </c>
+      <c r="T64" s="11" t="inlineStr"/>
+      <c r="U64" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V64" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W64" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>20260372006</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr"/>
+      <c r="G65" s="11" t="inlineStr"/>
+      <c r="H65" s="11" t="inlineStr"/>
+      <c r="I65" s="11" t="inlineStr"/>
+      <c r="J65" s="11" t="inlineStr"/>
+      <c r="K65" s="11" t="inlineStr"/>
+      <c r="L65" s="11" t="inlineStr"/>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N65" s="11" t="inlineStr"/>
+      <c r="O65" s="11" t="inlineStr"/>
+      <c r="P65" s="11" t="inlineStr"/>
+      <c r="Q65" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R65" s="11" t="inlineStr"/>
+      <c r="S65" s="11" t="inlineStr">
+        <is>
+          <t>220-81-989</t>
+        </is>
+      </c>
+      <c r="T65" s="11" t="inlineStr"/>
+      <c r="U65" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V65" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W65" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>20260372196</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr"/>
+      <c r="G66" s="11" t="inlineStr"/>
+      <c r="H66" s="11" t="inlineStr"/>
+      <c r="I66" s="11" t="inlineStr"/>
+      <c r="J66" s="11" t="inlineStr"/>
+      <c r="K66" s="11" t="inlineStr"/>
+      <c r="L66" s="11" t="inlineStr"/>
+      <c r="M66" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N66" s="11" t="inlineStr"/>
+      <c r="O66" s="11" t="inlineStr"/>
+      <c r="P66" s="11" t="inlineStr"/>
+      <c r="Q66" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R66" s="11" t="inlineStr"/>
+      <c r="S66" s="11" t="inlineStr"/>
+      <c r="T66" s="11" t="inlineStr"/>
+      <c r="U66" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V66" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W66" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>20260372220</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr"/>
+      <c r="G67" s="11" t="inlineStr"/>
+      <c r="H67" s="11" t="inlineStr"/>
+      <c r="I67" s="11" t="inlineStr"/>
+      <c r="J67" s="11" t="inlineStr"/>
+      <c r="K67" s="11" t="inlineStr"/>
+      <c r="L67" s="11" t="inlineStr"/>
+      <c r="M67" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N67" s="11" t="inlineStr"/>
+      <c r="O67" s="11" t="inlineStr"/>
+      <c r="P67" s="11" t="inlineStr"/>
+      <c r="Q67" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R67" s="11" t="inlineStr"/>
+      <c r="S67" s="11" t="inlineStr">
+        <is>
+          <t>501-86-990</t>
+        </is>
+      </c>
+      <c r="T67" s="11" t="inlineStr"/>
+      <c r="U67" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V67" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W67" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>20260372686</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr"/>
+      <c r="G68" s="11" t="inlineStr"/>
+      <c r="H68" s="11" t="inlineStr"/>
+      <c r="I68" s="11" t="inlineStr"/>
+      <c r="J68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr"/>
+      <c r="L68" s="11" t="inlineStr"/>
+      <c r="M68" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N68" s="11" t="inlineStr"/>
+      <c r="O68" s="11" t="inlineStr"/>
+      <c r="P68" s="11" t="inlineStr"/>
+      <c r="Q68" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R68" s="11" t="inlineStr"/>
+      <c r="S68" s="11" t="inlineStr">
+        <is>
+          <t>118-37-021</t>
+        </is>
+      </c>
+      <c r="T68" s="11" t="inlineStr"/>
+      <c r="U68" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V68" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W68" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>20260372697</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr"/>
+      <c r="G69" s="11" t="inlineStr"/>
+      <c r="H69" s="11" t="inlineStr"/>
+      <c r="I69" s="11" t="inlineStr"/>
+      <c r="J69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr"/>
+      <c r="L69" s="11" t="inlineStr"/>
+      <c r="M69" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N69" s="11" t="inlineStr"/>
+      <c r="O69" s="11" t="inlineStr"/>
+      <c r="P69" s="11" t="inlineStr"/>
+      <c r="Q69" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R69" s="11" t="inlineStr"/>
+      <c r="S69" s="11" t="inlineStr">
+        <is>
+          <t>118-37-021</t>
+        </is>
+      </c>
+      <c r="T69" s="11" t="inlineStr"/>
+      <c r="U69" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V69" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W69" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>20260372699</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr"/>
+      <c r="G70" s="11" t="inlineStr"/>
+      <c r="H70" s="11" t="inlineStr"/>
+      <c r="I70" s="11" t="inlineStr"/>
+      <c r="J70" s="11" t="inlineStr"/>
+      <c r="K70" s="11" t="inlineStr"/>
+      <c r="L70" s="11" t="inlineStr"/>
+      <c r="M70" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N70" s="11" t="inlineStr"/>
+      <c r="O70" s="11" t="inlineStr"/>
+      <c r="P70" s="11" t="inlineStr"/>
+      <c r="Q70" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R70" s="11" t="inlineStr"/>
+      <c r="S70" s="11" t="inlineStr">
+        <is>
+          <t>118-37-021</t>
+        </is>
+      </c>
+      <c r="T70" s="11" t="inlineStr"/>
+      <c r="U70" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V70" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W70" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>20260372714</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr"/>
+      <c r="G71" s="11" t="inlineStr"/>
+      <c r="H71" s="11" t="inlineStr"/>
+      <c r="I71" s="11" t="inlineStr"/>
+      <c r="J71" s="11" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr"/>
+      <c r="L71" s="11" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N71" s="11" t="inlineStr"/>
+      <c r="O71" s="11" t="inlineStr"/>
+      <c r="P71" s="11" t="inlineStr"/>
+      <c r="Q71" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R71" s="11" t="inlineStr"/>
+      <c r="S71" s="11" t="inlineStr"/>
+      <c r="T71" s="11" t="inlineStr"/>
+      <c r="U71" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V71" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W71" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>20260372717</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr"/>
+      <c r="G72" s="11" t="inlineStr"/>
+      <c r="H72" s="11" t="inlineStr"/>
+      <c r="I72" s="11" t="inlineStr"/>
+      <c r="J72" s="11" t="inlineStr"/>
+      <c r="K72" s="11" t="inlineStr"/>
+      <c r="L72" s="11" t="inlineStr"/>
+      <c r="M72" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N72" s="11" t="inlineStr"/>
+      <c r="O72" s="11" t="inlineStr"/>
+      <c r="P72" s="11" t="inlineStr"/>
+      <c r="Q72" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R72" s="11" t="inlineStr"/>
+      <c r="S72" s="11" t="inlineStr"/>
+      <c r="T72" s="11" t="inlineStr"/>
+      <c r="U72" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V72" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W72" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>20260372813</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr"/>
+      <c r="G73" s="11" t="inlineStr"/>
+      <c r="H73" s="11" t="inlineStr"/>
+      <c r="I73" s="11" t="inlineStr"/>
+      <c r="J73" s="11" t="inlineStr"/>
+      <c r="K73" s="11" t="inlineStr"/>
+      <c r="L73" s="11" t="inlineStr"/>
+      <c r="M73" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N73" s="11" t="inlineStr"/>
+      <c r="O73" s="11" t="inlineStr"/>
+      <c r="P73" s="11" t="inlineStr"/>
+      <c r="Q73" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R73" s="11" t="inlineStr"/>
+      <c r="S73" s="11" t="inlineStr"/>
+      <c r="T73" s="11" t="inlineStr"/>
+      <c r="U73" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V73" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W73" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>20260372846</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr"/>
+      <c r="G74" s="11" t="inlineStr"/>
+      <c r="H74" s="11" t="inlineStr"/>
+      <c r="I74" s="11" t="inlineStr"/>
+      <c r="J74" s="11" t="inlineStr"/>
+      <c r="K74" s="11" t="inlineStr"/>
+      <c r="L74" s="11" t="inlineStr"/>
+      <c r="M74" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N74" s="11" t="inlineStr"/>
+      <c r="O74" s="11" t="inlineStr"/>
+      <c r="P74" s="11" t="inlineStr"/>
+      <c r="Q74" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R74" s="11" t="inlineStr"/>
+      <c r="S74" s="11" t="inlineStr">
+        <is>
+          <t>500-10-904</t>
+        </is>
+      </c>
+      <c r="T74" s="11" t="inlineStr"/>
+      <c r="U74" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V74" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W74" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
+      <c r="A75" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>20260372850</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr"/>
+      <c r="G75" s="11" t="inlineStr"/>
+      <c r="H75" s="11" t="inlineStr"/>
+      <c r="I75" s="11" t="inlineStr"/>
+      <c r="J75" s="11" t="inlineStr"/>
+      <c r="K75" s="11" t="inlineStr"/>
+      <c r="L75" s="11" t="inlineStr"/>
+      <c r="M75" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N75" s="11" t="inlineStr"/>
+      <c r="O75" s="11" t="inlineStr"/>
+      <c r="P75" s="11" t="inlineStr"/>
+      <c r="Q75" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R75" s="11" t="inlineStr"/>
+      <c r="S75" s="11" t="inlineStr"/>
+      <c r="T75" s="11" t="inlineStr"/>
+      <c r="U75" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V75" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W75" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>20260373225</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr"/>
+      <c r="G76" s="11" t="inlineStr"/>
+      <c r="H76" s="11" t="inlineStr"/>
+      <c r="I76" s="11" t="inlineStr"/>
+      <c r="J76" s="11" t="inlineStr"/>
+      <c r="K76" s="11" t="inlineStr"/>
+      <c r="L76" s="11" t="inlineStr"/>
+      <c r="M76" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N76" s="11" t="inlineStr"/>
+      <c r="O76" s="11" t="inlineStr"/>
+      <c r="P76" s="11" t="inlineStr"/>
+      <c r="Q76" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R76" s="11" t="inlineStr"/>
+      <c r="S76" s="11" t="inlineStr"/>
+      <c r="T76" s="11" t="inlineStr"/>
+      <c r="U76" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V76" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W76" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>20260373506</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr"/>
+      <c r="G77" s="11" t="inlineStr"/>
+      <c r="H77" s="11" t="inlineStr"/>
+      <c r="I77" s="11" t="inlineStr"/>
+      <c r="J77" s="11" t="inlineStr"/>
+      <c r="K77" s="11" t="inlineStr"/>
+      <c r="L77" s="11" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N77" s="11" t="inlineStr"/>
+      <c r="O77" s="11" t="inlineStr"/>
+      <c r="P77" s="11" t="inlineStr"/>
+      <c r="Q77" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R77" s="11" t="inlineStr"/>
+      <c r="S77" s="11" t="inlineStr">
+        <is>
+          <t>500-10-904</t>
+        </is>
+      </c>
+      <c r="T77" s="11" t="inlineStr"/>
+      <c r="U77" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V77" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W77" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B78" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D78" s="11" t="inlineStr">
+        <is>
+          <t>20260371483</t>
+        </is>
+      </c>
+      <c r="E78" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F78" s="11" t="inlineStr"/>
+      <c r="G78" s="11" t="inlineStr"/>
+      <c r="H78" s="11" t="inlineStr"/>
+      <c r="I78" s="11" t="inlineStr"/>
+      <c r="J78" s="11" t="inlineStr"/>
+      <c r="K78" s="11" t="inlineStr"/>
+      <c r="L78" s="11" t="inlineStr"/>
+      <c r="M78" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N78" s="11" t="inlineStr"/>
+      <c r="O78" s="11" t="inlineStr"/>
+      <c r="P78" s="11" t="inlineStr"/>
+      <c r="Q78" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R78" s="11" t="inlineStr"/>
+      <c r="S78" s="11" t="inlineStr"/>
+      <c r="T78" s="11" t="inlineStr"/>
+      <c r="U78" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V78" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W78" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="26" customHeight="1">
+      <c r="A79" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B79" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>20260371824</t>
+        </is>
+      </c>
+      <c r="E79" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F79" s="11" t="inlineStr"/>
+      <c r="G79" s="11" t="inlineStr"/>
+      <c r="H79" s="11" t="inlineStr"/>
+      <c r="I79" s="11" t="inlineStr"/>
+      <c r="J79" s="11" t="inlineStr"/>
+      <c r="K79" s="11" t="inlineStr"/>
+      <c r="L79" s="11" t="inlineStr"/>
+      <c r="M79" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N79" s="11" t="inlineStr"/>
+      <c r="O79" s="11" t="inlineStr"/>
+      <c r="P79" s="11" t="inlineStr"/>
+      <c r="Q79" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R79" s="11" t="inlineStr"/>
+      <c r="S79" s="11" t="inlineStr"/>
+      <c r="T79" s="11" t="inlineStr"/>
+      <c r="U79" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V79" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W79" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="26" customHeight="1">
+      <c r="A80" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B80" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>20260373018</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F80" s="11" t="inlineStr"/>
+      <c r="G80" s="11" t="inlineStr"/>
+      <c r="H80" s="11" t="inlineStr"/>
+      <c r="I80" s="11" t="inlineStr"/>
+      <c r="J80" s="11" t="inlineStr"/>
+      <c r="K80" s="11" t="inlineStr"/>
+      <c r="L80" s="11" t="inlineStr"/>
+      <c r="M80" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N80" s="11" t="inlineStr"/>
+      <c r="O80" s="11" t="inlineStr"/>
+      <c r="P80" s="11" t="inlineStr"/>
+      <c r="Q80" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R80" s="11" t="inlineStr"/>
+      <c r="S80" s="11" t="inlineStr"/>
+      <c r="T80" s="11" t="inlineStr"/>
+      <c r="U80" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V80" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W80" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B81" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D81" s="11" t="inlineStr">
+        <is>
+          <t>20260373418</t>
+        </is>
+      </c>
+      <c r="E81" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F81" s="11" t="inlineStr"/>
+      <c r="G81" s="11" t="inlineStr"/>
+      <c r="H81" s="11" t="inlineStr"/>
+      <c r="I81" s="11" t="inlineStr"/>
+      <c r="J81" s="11" t="inlineStr"/>
+      <c r="K81" s="11" t="inlineStr"/>
+      <c r="L81" s="11" t="inlineStr"/>
+      <c r="M81" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N81" s="11" t="inlineStr"/>
+      <c r="O81" s="11" t="inlineStr"/>
+      <c r="P81" s="11" t="inlineStr"/>
+      <c r="Q81" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R81" s="11" t="inlineStr"/>
+      <c r="S81" s="11" t="inlineStr"/>
+      <c r="T81" s="11" t="inlineStr"/>
+      <c r="U81" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V81" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W81" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="26" customHeight="1">
+      <c r="A82" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B82" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>20260373515</t>
+        </is>
+      </c>
+      <c r="E82" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F82" s="11" t="inlineStr"/>
+      <c r="G82" s="11" t="inlineStr"/>
+      <c r="H82" s="11" t="inlineStr"/>
+      <c r="I82" s="11" t="inlineStr"/>
+      <c r="J82" s="11" t="inlineStr"/>
+      <c r="K82" s="11" t="inlineStr"/>
+      <c r="L82" s="11" t="inlineStr"/>
+      <c r="M82" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N82" s="11" t="inlineStr"/>
+      <c r="O82" s="11" t="inlineStr"/>
+      <c r="P82" s="11" t="inlineStr"/>
+      <c r="Q82" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R82" s="11" t="inlineStr"/>
+      <c r="S82" s="11" t="inlineStr"/>
+      <c r="T82" s="11" t="inlineStr"/>
+      <c r="U82" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V82" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W82" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B83" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D83" s="11" t="inlineStr">
+        <is>
+          <t>20260373560</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F83" s="11" t="inlineStr"/>
+      <c r="G83" s="11" t="inlineStr"/>
+      <c r="H83" s="11" t="inlineStr"/>
+      <c r="I83" s="11" t="inlineStr"/>
+      <c r="J83" s="11" t="inlineStr"/>
+      <c r="K83" s="11" t="inlineStr"/>
+      <c r="L83" s="11" t="inlineStr"/>
+      <c r="M83" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N83" s="11" t="inlineStr"/>
+      <c r="O83" s="11" t="inlineStr"/>
+      <c r="P83" s="11" t="inlineStr"/>
+      <c r="Q83" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R83" s="11" t="inlineStr"/>
+      <c r="S83" s="11" t="inlineStr"/>
+      <c r="T83" s="11" t="inlineStr"/>
+      <c r="U83" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V83" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W83" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B84" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D84" s="11" t="inlineStr">
+        <is>
+          <t>20260373647</t>
+        </is>
+      </c>
+      <c r="E84" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F84" s="11" t="inlineStr"/>
+      <c r="G84" s="11" t="inlineStr"/>
+      <c r="H84" s="11" t="inlineStr"/>
+      <c r="I84" s="11" t="inlineStr"/>
+      <c r="J84" s="11" t="inlineStr"/>
+      <c r="K84" s="11" t="inlineStr"/>
+      <c r="L84" s="11" t="inlineStr"/>
+      <c r="M84" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N84" s="11" t="inlineStr"/>
+      <c r="O84" s="11" t="inlineStr"/>
+      <c r="P84" s="11" t="inlineStr"/>
+      <c r="Q84" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R84" s="11" t="inlineStr"/>
+      <c r="S84" s="11" t="inlineStr"/>
+      <c r="T84" s="11" t="inlineStr"/>
+      <c r="U84" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V84" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W84" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B85" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D85" s="11" t="inlineStr">
+        <is>
+          <t>20260372617</t>
+        </is>
+      </c>
+      <c r="E85" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F85" s="11" t="inlineStr"/>
+      <c r="G85" s="11" t="inlineStr"/>
+      <c r="H85" s="11" t="inlineStr"/>
+      <c r="I85" s="11" t="inlineStr"/>
+      <c r="J85" s="11" t="inlineStr"/>
+      <c r="K85" s="11" t="inlineStr"/>
+      <c r="L85" s="11" t="inlineStr"/>
+      <c r="M85" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N85" s="11" t="inlineStr"/>
+      <c r="O85" s="11" t="inlineStr"/>
+      <c r="P85" s="11" t="inlineStr"/>
+      <c r="Q85" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R85" s="11" t="inlineStr"/>
+      <c r="S85" s="11" t="inlineStr"/>
+      <c r="T85" s="11" t="inlineStr"/>
+      <c r="U85" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V85" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W85" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B86" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D86" s="11" t="inlineStr">
+        <is>
+          <t>20260372822</t>
+        </is>
+      </c>
+      <c r="E86" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F86" s="11" t="inlineStr"/>
+      <c r="G86" s="11" t="inlineStr"/>
+      <c r="H86" s="11" t="inlineStr"/>
+      <c r="I86" s="11" t="inlineStr"/>
+      <c r="J86" s="11" t="inlineStr"/>
+      <c r="K86" s="11" t="inlineStr"/>
+      <c r="L86" s="11" t="inlineStr"/>
+      <c r="M86" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N86" s="11" t="inlineStr"/>
+      <c r="O86" s="11" t="inlineStr"/>
+      <c r="P86" s="11" t="inlineStr"/>
+      <c r="Q86" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R86" s="11" t="inlineStr"/>
+      <c r="S86" s="11" t="inlineStr"/>
+      <c r="T86" s="11" t="inlineStr"/>
+      <c r="U86" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V86" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W86" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="26" customHeight="1">
+      <c r="A87" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B87" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D87" s="11" t="inlineStr">
+        <is>
+          <t>20260372893</t>
+        </is>
+      </c>
+      <c r="E87" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F87" s="11" t="inlineStr"/>
+      <c r="G87" s="11" t="inlineStr"/>
+      <c r="H87" s="11" t="inlineStr"/>
+      <c r="I87" s="11" t="inlineStr"/>
+      <c r="J87" s="11" t="inlineStr"/>
+      <c r="K87" s="11" t="inlineStr"/>
+      <c r="L87" s="11" t="inlineStr"/>
+      <c r="M87" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N87" s="11" t="inlineStr"/>
+      <c r="O87" s="11" t="inlineStr"/>
+      <c r="P87" s="11" t="inlineStr"/>
+      <c r="Q87" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R87" s="11" t="inlineStr"/>
+      <c r="S87" s="11" t="inlineStr"/>
+      <c r="T87" s="11" t="inlineStr"/>
+      <c r="U87" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V87" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W87" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="26" customHeight="1">
+      <c r="A88" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B88" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D88" s="11" t="inlineStr">
+        <is>
+          <t>20260373400</t>
+        </is>
+      </c>
+      <c r="E88" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F88" s="11" t="inlineStr"/>
+      <c r="G88" s="11" t="inlineStr"/>
+      <c r="H88" s="11" t="inlineStr"/>
+      <c r="I88" s="11" t="inlineStr"/>
+      <c r="J88" s="11" t="inlineStr"/>
+      <c r="K88" s="11" t="inlineStr"/>
+      <c r="L88" s="11" t="inlineStr"/>
+      <c r="M88" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N88" s="11" t="inlineStr"/>
+      <c r="O88" s="11" t="inlineStr"/>
+      <c r="P88" s="11" t="inlineStr"/>
+      <c r="Q88" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R88" s="11" t="inlineStr"/>
+      <c r="S88" s="11" t="inlineStr"/>
+      <c r="T88" s="11" t="inlineStr"/>
+      <c r="U88" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V88" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W88" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="26" customHeight="1">
+      <c r="A89" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B89" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C89" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D89" s="11" t="inlineStr">
+        <is>
+          <t>20260373611</t>
+        </is>
+      </c>
+      <c r="E89" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F89" s="11" t="inlineStr"/>
+      <c r="G89" s="11" t="inlineStr"/>
+      <c r="H89" s="11" t="inlineStr"/>
+      <c r="I89" s="11" t="inlineStr"/>
+      <c r="J89" s="11" t="inlineStr"/>
+      <c r="K89" s="11" t="inlineStr"/>
+      <c r="L89" s="11" t="inlineStr"/>
+      <c r="M89" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N89" s="11" t="inlineStr"/>
+      <c r="O89" s="11" t="inlineStr"/>
+      <c r="P89" s="11" t="inlineStr"/>
+      <c r="Q89" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R89" s="11" t="inlineStr"/>
+      <c r="S89" s="11" t="inlineStr"/>
+      <c r="T89" s="11" t="inlineStr"/>
+      <c r="U89" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V89" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W89" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="26" customHeight="1">
+      <c r="A90" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B90" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D90" s="11" t="inlineStr">
+        <is>
+          <t>20260373689</t>
+        </is>
+      </c>
+      <c r="E90" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F90" s="11" t="inlineStr"/>
+      <c r="G90" s="11" t="inlineStr"/>
+      <c r="H90" s="11" t="inlineStr"/>
+      <c r="I90" s="11" t="inlineStr"/>
+      <c r="J90" s="11" t="inlineStr"/>
+      <c r="K90" s="11" t="inlineStr"/>
+      <c r="L90" s="11" t="inlineStr"/>
+      <c r="M90" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N90" s="11" t="inlineStr"/>
+      <c r="O90" s="11" t="inlineStr"/>
+      <c r="P90" s="11" t="inlineStr"/>
+      <c r="Q90" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R90" s="11" t="inlineStr"/>
+      <c r="S90" s="11" t="inlineStr"/>
+      <c r="T90" s="11" t="inlineStr"/>
+      <c r="U90" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V90" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W90" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="26" customHeight="1">
+      <c r="A91" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B91" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D91" s="11" t="inlineStr">
+        <is>
+          <t>20260373695</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F91" s="11" t="inlineStr"/>
+      <c r="G91" s="11" t="inlineStr"/>
+      <c r="H91" s="11" t="inlineStr"/>
+      <c r="I91" s="11" t="inlineStr"/>
+      <c r="J91" s="11" t="inlineStr"/>
+      <c r="K91" s="11" t="inlineStr"/>
+      <c r="L91" s="11" t="inlineStr"/>
+      <c r="M91" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N91" s="11" t="inlineStr"/>
+      <c r="O91" s="11" t="inlineStr"/>
+      <c r="P91" s="11" t="inlineStr"/>
+      <c r="Q91" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R91" s="11" t="inlineStr"/>
+      <c r="S91" s="11" t="inlineStr"/>
+      <c r="T91" s="11" t="inlineStr"/>
+      <c r="U91" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V91" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W91" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="26" customHeight="1">
+      <c r="A92" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B92" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D92" s="11" t="inlineStr">
+        <is>
+          <t>20260370744</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F92" s="11" t="inlineStr"/>
+      <c r="G92" s="11" t="inlineStr"/>
+      <c r="H92" s="11" t="inlineStr"/>
+      <c r="I92" s="11" t="inlineStr"/>
+      <c r="J92" s="11" t="inlineStr"/>
+      <c r="K92" s="11" t="inlineStr"/>
+      <c r="L92" s="11" t="inlineStr"/>
+      <c r="M92" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N92" s="11" t="inlineStr"/>
+      <c r="O92" s="11" t="inlineStr"/>
+      <c r="P92" s="11" t="inlineStr"/>
+      <c r="Q92" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R92" s="11" t="inlineStr"/>
+      <c r="S92" s="11" t="inlineStr">
+        <is>
+          <t>169-20-059</t>
+        </is>
+      </c>
+      <c r="T92" s="11" t="inlineStr"/>
+      <c r="U92" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V92" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W92" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="26" customHeight="1">
+      <c r="A93" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B93" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D93" s="11" t="inlineStr">
+        <is>
+          <t>20260370745</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F93" s="11" t="inlineStr"/>
+      <c r="G93" s="11" t="inlineStr"/>
+      <c r="H93" s="11" t="inlineStr"/>
+      <c r="I93" s="11" t="inlineStr"/>
+      <c r="J93" s="11" t="inlineStr"/>
+      <c r="K93" s="11" t="inlineStr"/>
+      <c r="L93" s="11" t="inlineStr"/>
+      <c r="M93" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N93" s="11" t="inlineStr"/>
+      <c r="O93" s="11" t="inlineStr"/>
+      <c r="P93" s="11" t="inlineStr"/>
+      <c r="Q93" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R93" s="11" t="inlineStr"/>
+      <c r="S93" s="11" t="inlineStr">
+        <is>
+          <t>109-20-158</t>
+        </is>
+      </c>
+      <c r="T93" s="11" t="inlineStr"/>
+      <c r="U93" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V93" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W93" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="26" customHeight="1">
+      <c r="A94" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B94" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C94" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D94" s="11" t="inlineStr">
+        <is>
+          <t>20260370746</t>
+        </is>
+      </c>
+      <c r="E94" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F94" s="11" t="inlineStr"/>
+      <c r="G94" s="11" t="inlineStr"/>
+      <c r="H94" s="11" t="inlineStr"/>
+      <c r="I94" s="11" t="inlineStr"/>
+      <c r="J94" s="11" t="inlineStr"/>
+      <c r="K94" s="11" t="inlineStr"/>
+      <c r="L94" s="11" t="inlineStr"/>
+      <c r="M94" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N94" s="11" t="inlineStr"/>
+      <c r="O94" s="11" t="inlineStr"/>
+      <c r="P94" s="11" t="inlineStr"/>
+      <c r="Q94" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R94" s="11" t="inlineStr"/>
+      <c r="S94" s="11" t="inlineStr">
+        <is>
+          <t>103-17-146</t>
+        </is>
+      </c>
+      <c r="T94" s="11" t="inlineStr"/>
+      <c r="U94" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V94" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W94" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="26" customHeight="1">
+      <c r="A95" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B95" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C95" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D95" s="11" t="inlineStr">
+        <is>
+          <t>20260370747</t>
+        </is>
+      </c>
+      <c r="E95" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F95" s="11" t="inlineStr"/>
+      <c r="G95" s="11" t="inlineStr"/>
+      <c r="H95" s="11" t="inlineStr"/>
+      <c r="I95" s="11" t="inlineStr"/>
+      <c r="J95" s="11" t="inlineStr"/>
+      <c r="K95" s="11" t="inlineStr"/>
+      <c r="L95" s="11" t="inlineStr"/>
+      <c r="M95" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N95" s="11" t="inlineStr"/>
+      <c r="O95" s="11" t="inlineStr"/>
+      <c r="P95" s="11" t="inlineStr"/>
+      <c r="Q95" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R95" s="11" t="inlineStr"/>
+      <c r="S95" s="11" t="inlineStr">
+        <is>
+          <t>206-12-012</t>
+        </is>
+      </c>
+      <c r="T95" s="11" t="inlineStr"/>
+      <c r="U95" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V95" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W95" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="26" customHeight="1">
+      <c r="A96" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B96" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C96" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D96" s="11" t="inlineStr">
+        <is>
+          <t>20260370748</t>
+        </is>
+      </c>
+      <c r="E96" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F96" s="11" t="inlineStr"/>
+      <c r="G96" s="11" t="inlineStr"/>
+      <c r="H96" s="11" t="inlineStr"/>
+      <c r="I96" s="11" t="inlineStr"/>
+      <c r="J96" s="11" t="inlineStr"/>
+      <c r="K96" s="11" t="inlineStr"/>
+      <c r="L96" s="11" t="inlineStr"/>
+      <c r="M96" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N96" s="11" t="inlineStr"/>
+      <c r="O96" s="11" t="inlineStr"/>
+      <c r="P96" s="11" t="inlineStr"/>
+      <c r="Q96" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R96" s="11" t="inlineStr"/>
+      <c r="S96" s="11" t="inlineStr">
+        <is>
+          <t>109-25-082</t>
+        </is>
+      </c>
+      <c r="T96" s="11" t="inlineStr"/>
+      <c r="U96" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V96" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W96" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="26" customHeight="1">
+      <c r="A97" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B97" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D97" s="11" t="inlineStr">
+        <is>
+          <t>20260371593</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F97" s="11" t="inlineStr"/>
+      <c r="G97" s="11" t="inlineStr"/>
+      <c r="H97" s="11" t="inlineStr"/>
+      <c r="I97" s="11" t="inlineStr"/>
+      <c r="J97" s="11" t="inlineStr"/>
+      <c r="K97" s="11" t="inlineStr"/>
+      <c r="L97" s="11" t="inlineStr"/>
+      <c r="M97" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N97" s="11" t="inlineStr"/>
+      <c r="O97" s="11" t="inlineStr"/>
+      <c r="P97" s="11" t="inlineStr"/>
+      <c r="Q97" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R97" s="11" t="inlineStr"/>
+      <c r="S97" s="11" t="inlineStr"/>
+      <c r="T97" s="11" t="inlineStr"/>
+      <c r="U97" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V97" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W97" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="26" customHeight="1">
+      <c r="A98" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B98" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C98" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D98" s="11" t="inlineStr">
+        <is>
+          <t>20260372158</t>
+        </is>
+      </c>
+      <c r="E98" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F98" s="11" t="inlineStr"/>
+      <c r="G98" s="11" t="inlineStr"/>
+      <c r="H98" s="11" t="inlineStr"/>
+      <c r="I98" s="11" t="inlineStr"/>
+      <c r="J98" s="11" t="inlineStr"/>
+      <c r="K98" s="11" t="inlineStr"/>
+      <c r="L98" s="11" t="inlineStr"/>
+      <c r="M98" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N98" s="11" t="inlineStr"/>
+      <c r="O98" s="11" t="inlineStr"/>
+      <c r="P98" s="11" t="inlineStr"/>
+      <c r="Q98" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R98" s="11" t="inlineStr"/>
+      <c r="S98" s="11" t="inlineStr"/>
+      <c r="T98" s="11" t="inlineStr"/>
+      <c r="U98" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V98" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W98" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="26" customHeight="1">
+      <c r="A99" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B99" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C99" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D99" s="11" t="inlineStr">
+        <is>
+          <t>20260372299</t>
+        </is>
+      </c>
+      <c r="E99" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F99" s="11" t="inlineStr"/>
+      <c r="G99" s="11" t="inlineStr"/>
+      <c r="H99" s="11" t="inlineStr"/>
+      <c r="I99" s="11" t="inlineStr"/>
+      <c r="J99" s="11" t="inlineStr"/>
+      <c r="K99" s="11" t="inlineStr"/>
+      <c r="L99" s="11" t="inlineStr"/>
+      <c r="M99" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N99" s="11" t="inlineStr"/>
+      <c r="O99" s="11" t="inlineStr"/>
+      <c r="P99" s="11" t="inlineStr"/>
+      <c r="Q99" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R99" s="11" t="inlineStr"/>
+      <c r="S99" s="11" t="inlineStr"/>
+      <c r="T99" s="11" t="inlineStr"/>
+      <c r="U99" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V99" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W99" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="26" customHeight="1">
+      <c r="A100" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B100" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C100" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D100" s="11" t="inlineStr">
+        <is>
+          <t>20260372302</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F100" s="11" t="inlineStr"/>
+      <c r="G100" s="11" t="inlineStr"/>
+      <c r="H100" s="11" t="inlineStr"/>
+      <c r="I100" s="11" t="inlineStr"/>
+      <c r="J100" s="11" t="inlineStr"/>
+      <c r="K100" s="11" t="inlineStr"/>
+      <c r="L100" s="11" t="inlineStr"/>
+      <c r="M100" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N100" s="11" t="inlineStr"/>
+      <c r="O100" s="11" t="inlineStr"/>
+      <c r="P100" s="11" t="inlineStr"/>
+      <c r="Q100" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R100" s="11" t="inlineStr"/>
+      <c r="S100" s="11" t="inlineStr"/>
+      <c r="T100" s="11" t="inlineStr"/>
+      <c r="U100" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V100" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W100" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="26" customHeight="1">
+      <c r="A101" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B101" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C101" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D101" s="11" t="inlineStr">
+        <is>
+          <t>20260372452</t>
+        </is>
+      </c>
+      <c r="E101" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F101" s="11" t="inlineStr"/>
+      <c r="G101" s="11" t="inlineStr"/>
+      <c r="H101" s="11" t="inlineStr"/>
+      <c r="I101" s="11" t="inlineStr"/>
+      <c r="J101" s="11" t="inlineStr"/>
+      <c r="K101" s="11" t="inlineStr"/>
+      <c r="L101" s="11" t="inlineStr"/>
+      <c r="M101" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N101" s="11" t="inlineStr"/>
+      <c r="O101" s="11" t="inlineStr"/>
+      <c r="P101" s="11" t="inlineStr"/>
+      <c r="Q101" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R101" s="11" t="inlineStr"/>
+      <c r="S101" s="11" t="inlineStr"/>
+      <c r="T101" s="11" t="inlineStr"/>
+      <c r="U101" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V101" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W101" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="26" customHeight="1">
+      <c r="A102" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B102" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C102" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D102" s="11" t="inlineStr">
+        <is>
+          <t>20260372460</t>
+        </is>
+      </c>
+      <c r="E102" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F102" s="11" t="inlineStr"/>
+      <c r="G102" s="11" t="inlineStr"/>
+      <c r="H102" s="11" t="inlineStr"/>
+      <c r="I102" s="11" t="inlineStr"/>
+      <c r="J102" s="11" t="inlineStr"/>
+      <c r="K102" s="11" t="inlineStr"/>
+      <c r="L102" s="11" t="inlineStr"/>
+      <c r="M102" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N102" s="11" t="inlineStr"/>
+      <c r="O102" s="11" t="inlineStr"/>
+      <c r="P102" s="11" t="inlineStr"/>
+      <c r="Q102" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R102" s="11" t="inlineStr"/>
+      <c r="S102" s="11" t="inlineStr"/>
+      <c r="T102" s="11" t="inlineStr"/>
+      <c r="U102" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V102" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W102" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="26" customHeight="1">
+      <c r="A103" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B103" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C103" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D103" s="11" t="inlineStr">
+        <is>
+          <t>20260372634</t>
+        </is>
+      </c>
+      <c r="E103" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F103" s="11" t="inlineStr"/>
+      <c r="G103" s="11" t="inlineStr"/>
+      <c r="H103" s="11" t="inlineStr"/>
+      <c r="I103" s="11" t="inlineStr"/>
+      <c r="J103" s="11" t="inlineStr"/>
+      <c r="K103" s="11" t="inlineStr"/>
+      <c r="L103" s="11" t="inlineStr"/>
+      <c r="M103" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N103" s="11" t="inlineStr"/>
+      <c r="O103" s="11" t="inlineStr"/>
+      <c r="P103" s="11" t="inlineStr"/>
+      <c r="Q103" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R103" s="11" t="inlineStr"/>
+      <c r="S103" s="11" t="inlineStr"/>
+      <c r="T103" s="11" t="inlineStr"/>
+      <c r="U103" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V103" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W103" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="26" customHeight="1">
+      <c r="A104" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B104" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C104" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D104" s="11" t="inlineStr">
+        <is>
+          <t>20260372700</t>
+        </is>
+      </c>
+      <c r="E104" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F104" s="11" t="inlineStr"/>
+      <c r="G104" s="11" t="inlineStr"/>
+      <c r="H104" s="11" t="inlineStr"/>
+      <c r="I104" s="11" t="inlineStr"/>
+      <c r="J104" s="11" t="inlineStr"/>
+      <c r="K104" s="11" t="inlineStr"/>
+      <c r="L104" s="11" t="inlineStr"/>
+      <c r="M104" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N104" s="11" t="inlineStr"/>
+      <c r="O104" s="11" t="inlineStr"/>
+      <c r="P104" s="11" t="inlineStr"/>
+      <c r="Q104" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R104" s="11" t="inlineStr"/>
+      <c r="S104" s="11" t="inlineStr"/>
+      <c r="T104" s="11" t="inlineStr"/>
+      <c r="U104" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V104" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W104" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="26" customHeight="1">
+      <c r="A105" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B105" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C105" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D105" s="11" t="inlineStr">
+        <is>
+          <t>20260372707</t>
+        </is>
+      </c>
+      <c r="E105" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F105" s="11" t="inlineStr"/>
+      <c r="G105" s="11" t="inlineStr"/>
+      <c r="H105" s="11" t="inlineStr"/>
+      <c r="I105" s="11" t="inlineStr"/>
+      <c r="J105" s="11" t="inlineStr"/>
+      <c r="K105" s="11" t="inlineStr"/>
+      <c r="L105" s="11" t="inlineStr"/>
+      <c r="M105" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N105" s="11" t="inlineStr"/>
+      <c r="O105" s="11" t="inlineStr"/>
+      <c r="P105" s="11" t="inlineStr"/>
+      <c r="Q105" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R105" s="11" t="inlineStr"/>
+      <c r="S105" s="11" t="inlineStr"/>
+      <c r="T105" s="11" t="inlineStr"/>
+      <c r="U105" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V105" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W105" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="26" customHeight="1">
+      <c r="A106" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B106" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C106" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D106" s="11" t="inlineStr">
+        <is>
+          <t>20260372799</t>
+        </is>
+      </c>
+      <c r="E106" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F106" s="11" t="inlineStr"/>
+      <c r="G106" s="11" t="inlineStr"/>
+      <c r="H106" s="11" t="inlineStr"/>
+      <c r="I106" s="11" t="inlineStr"/>
+      <c r="J106" s="11" t="inlineStr"/>
+      <c r="K106" s="11" t="inlineStr"/>
+      <c r="L106" s="11" t="inlineStr"/>
+      <c r="M106" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N106" s="11" t="inlineStr"/>
+      <c r="O106" s="11" t="inlineStr"/>
+      <c r="P106" s="11" t="inlineStr"/>
+      <c r="Q106" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R106" s="11" t="inlineStr"/>
+      <c r="S106" s="11" t="inlineStr"/>
+      <c r="T106" s="11" t="inlineStr"/>
+      <c r="U106" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V106" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W106" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="26" customHeight="1">
+      <c r="A107" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B107" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C107" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D107" s="11" t="inlineStr">
+        <is>
+          <t>20260372826</t>
+        </is>
+      </c>
+      <c r="E107" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F107" s="11" t="inlineStr"/>
+      <c r="G107" s="11" t="inlineStr"/>
+      <c r="H107" s="11" t="inlineStr"/>
+      <c r="I107" s="11" t="inlineStr"/>
+      <c r="J107" s="11" t="inlineStr"/>
+      <c r="K107" s="11" t="inlineStr"/>
+      <c r="L107" s="11" t="inlineStr"/>
+      <c r="M107" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N107" s="11" t="inlineStr"/>
+      <c r="O107" s="11" t="inlineStr"/>
+      <c r="P107" s="11" t="inlineStr"/>
+      <c r="Q107" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R107" s="11" t="inlineStr"/>
+      <c r="S107" s="11" t="inlineStr">
+        <is>
+          <t>501-72-265202</t>
+        </is>
+      </c>
+      <c r="T107" s="11" t="inlineStr"/>
+      <c r="U107" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V107" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W107" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="26" customHeight="1">
+      <c r="A108" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B108" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C108" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D108" s="11" t="inlineStr">
+        <is>
+          <t>20260372828</t>
+        </is>
+      </c>
+      <c r="E108" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F108" s="11" t="inlineStr"/>
+      <c r="G108" s="11" t="inlineStr"/>
+      <c r="H108" s="11" t="inlineStr"/>
+      <c r="I108" s="11" t="inlineStr"/>
+      <c r="J108" s="11" t="inlineStr"/>
+      <c r="K108" s="11" t="inlineStr"/>
+      <c r="L108" s="11" t="inlineStr"/>
+      <c r="M108" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N108" s="11" t="inlineStr"/>
+      <c r="O108" s="11" t="inlineStr"/>
+      <c r="P108" s="11" t="inlineStr"/>
+      <c r="Q108" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R108" s="11" t="inlineStr"/>
+      <c r="S108" s="11" t="inlineStr">
+        <is>
+          <t>501-72-675202</t>
+        </is>
+      </c>
+      <c r="T108" s="11" t="inlineStr"/>
+      <c r="U108" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V108" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W108" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="26" customHeight="1">
+      <c r="A109" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B109" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C109" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D109" s="11" t="inlineStr">
+        <is>
+          <t>20260372829</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F109" s="11" t="inlineStr"/>
+      <c r="G109" s="11" t="inlineStr"/>
+      <c r="H109" s="11" t="inlineStr"/>
+      <c r="I109" s="11" t="inlineStr"/>
+      <c r="J109" s="11" t="inlineStr"/>
+      <c r="K109" s="11" t="inlineStr"/>
+      <c r="L109" s="11" t="inlineStr"/>
+      <c r="M109" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N109" s="11" t="inlineStr"/>
+      <c r="O109" s="11" t="inlineStr"/>
+      <c r="P109" s="11" t="inlineStr"/>
+      <c r="Q109" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R109" s="11" t="inlineStr"/>
+      <c r="S109" s="11" t="inlineStr">
+        <is>
+          <t>501-72-789202</t>
+        </is>
+      </c>
+      <c r="T109" s="11" t="inlineStr"/>
+      <c r="U109" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V109" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W109" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="26" customHeight="1">
+      <c r="A110" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B110" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C110" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D110" s="11" t="inlineStr">
+        <is>
+          <t>20260372858</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F110" s="11" t="inlineStr"/>
+      <c r="G110" s="11" t="inlineStr"/>
+      <c r="H110" s="11" t="inlineStr"/>
+      <c r="I110" s="11" t="inlineStr"/>
+      <c r="J110" s="11" t="inlineStr"/>
+      <c r="K110" s="11" t="inlineStr"/>
+      <c r="L110" s="11" t="inlineStr"/>
+      <c r="M110" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N110" s="11" t="inlineStr"/>
+      <c r="O110" s="11" t="inlineStr"/>
+      <c r="P110" s="11" t="inlineStr"/>
+      <c r="Q110" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R110" s="11" t="inlineStr"/>
+      <c r="S110" s="11" t="inlineStr"/>
+      <c r="T110" s="11" t="inlineStr"/>
+      <c r="U110" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V110" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W110" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="26" customHeight="1">
+      <c r="A111" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B111" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D111" s="11" t="inlineStr">
+        <is>
+          <t>20260372919</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F111" s="11" t="inlineStr"/>
+      <c r="G111" s="11" t="inlineStr"/>
+      <c r="H111" s="11" t="inlineStr"/>
+      <c r="I111" s="11" t="inlineStr"/>
+      <c r="J111" s="11" t="inlineStr"/>
+      <c r="K111" s="11" t="inlineStr"/>
+      <c r="L111" s="11" t="inlineStr"/>
+      <c r="M111" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N111" s="11" t="inlineStr"/>
+      <c r="O111" s="11" t="inlineStr"/>
+      <c r="P111" s="11" t="inlineStr"/>
+      <c r="Q111" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R111" s="11" t="inlineStr"/>
+      <c r="S111" s="11" t="inlineStr"/>
+      <c r="T111" s="11" t="inlineStr"/>
+      <c r="U111" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V111" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W111" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="26" customHeight="1">
+      <c r="A112" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B112" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C112" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D112" s="11" t="inlineStr">
+        <is>
+          <t>20260373405</t>
+        </is>
+      </c>
+      <c r="E112" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F112" s="11" t="inlineStr"/>
+      <c r="G112" s="11" t="inlineStr"/>
+      <c r="H112" s="11" t="inlineStr"/>
+      <c r="I112" s="11" t="inlineStr"/>
+      <c r="J112" s="11" t="inlineStr"/>
+      <c r="K112" s="11" t="inlineStr"/>
+      <c r="L112" s="11" t="inlineStr"/>
+      <c r="M112" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N112" s="11" t="inlineStr"/>
+      <c r="O112" s="11" t="inlineStr"/>
+      <c r="P112" s="11" t="inlineStr"/>
+      <c r="Q112" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R112" s="11" t="inlineStr"/>
+      <c r="S112" s="11" t="inlineStr"/>
+      <c r="T112" s="11" t="inlineStr"/>
+      <c r="U112" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V112" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W112" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="26" customHeight="1">
+      <c r="A113" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B113" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C113" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D113" s="11" t="inlineStr">
+        <is>
+          <t>20260373505</t>
+        </is>
+      </c>
+      <c r="E113" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F113" s="11" t="inlineStr"/>
+      <c r="G113" s="11" t="inlineStr"/>
+      <c r="H113" s="11" t="inlineStr"/>
+      <c r="I113" s="11" t="inlineStr"/>
+      <c r="J113" s="11" t="inlineStr"/>
+      <c r="K113" s="11" t="inlineStr"/>
+      <c r="L113" s="11" t="inlineStr"/>
+      <c r="M113" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N113" s="11" t="inlineStr"/>
+      <c r="O113" s="11" t="inlineStr"/>
+      <c r="P113" s="11" t="inlineStr"/>
+      <c r="Q113" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R113" s="11" t="inlineStr"/>
+      <c r="S113" s="11" t="inlineStr"/>
+      <c r="T113" s="11" t="inlineStr"/>
+      <c r="U113" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V113" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W113" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="26" customHeight="1">
+      <c r="A114" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B114" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C114" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D114" s="11" t="inlineStr">
+        <is>
+          <t>20260373763</t>
+        </is>
+      </c>
+      <c r="E114" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F114" s="11" t="inlineStr"/>
+      <c r="G114" s="11" t="inlineStr"/>
+      <c r="H114" s="11" t="inlineStr"/>
+      <c r="I114" s="11" t="inlineStr"/>
+      <c r="J114" s="11" t="inlineStr"/>
+      <c r="K114" s="11" t="inlineStr"/>
+      <c r="L114" s="11" t="inlineStr"/>
+      <c r="M114" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N114" s="11" t="inlineStr"/>
+      <c r="O114" s="11" t="inlineStr"/>
+      <c r="P114" s="11" t="inlineStr"/>
+      <c r="Q114" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R114" s="11" t="inlineStr"/>
+      <c r="S114" s="11" t="inlineStr"/>
+      <c r="T114" s="11" t="inlineStr"/>
+      <c r="U114" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V114" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W114" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="26" customHeight="1">
+      <c r="A115" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="B115" s="11" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="C115" s="11" t="inlineStr">
+        <is>
+          <t>LN</t>
+        </is>
+      </c>
+      <c r="D115" s="11" t="inlineStr">
+        <is>
+          <t>20260373826</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F115" s="11" t="inlineStr"/>
+      <c r="G115" s="11" t="inlineStr"/>
+      <c r="H115" s="11" t="inlineStr"/>
+      <c r="I115" s="11" t="inlineStr"/>
+      <c r="J115" s="11" t="inlineStr"/>
+      <c r="K115" s="11" t="inlineStr"/>
+      <c r="L115" s="11" t="inlineStr"/>
+      <c r="M115" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N115" s="11" t="inlineStr"/>
+      <c r="O115" s="11" t="inlineStr"/>
+      <c r="P115" s="11" t="inlineStr"/>
+      <c r="Q115" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R115" s="11" t="inlineStr"/>
+      <c r="S115" s="11" t="inlineStr"/>
+      <c r="T115" s="11" t="inlineStr"/>
+      <c r="U115" s="11" t="inlineStr">
+        <is>
+          <t>Lien; New this week</t>
+        </is>
+      </c>
+      <c r="V115" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W115" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W1"/>
+  <autoFilter ref="A1:W115"/>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="W115" r:id="rId114"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -618,7 +8751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -626,7 +8759,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Maricopa County Motivated Seller Leads</t>
         </is>
@@ -635,88 +8768,148 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-06-22 06:29</t>
+          <t>Run: 2026-06-23 05:07</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr"/>
-      <c r="B3" s="3" t="inlineStr"/>
+      <c r="A3" s="14" t="inlineStr"/>
+      <c r="B3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>Total Leads</t>
         </is>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="14" t="n">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>With Property Address</t>
+        </is>
+      </c>
+      <c r="B5" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>With Mailing Address</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>With Property Address</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>With Mailing Address</t>
-        </is>
-      </c>
-      <c r="B6" s="3" t="n">
-        <v>0</v>
-      </c>
-    </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>PDF Parsed</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
-        <v>0</v>
+      <c r="B7" s="14" t="n">
+        <v>100</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>Score 70+ (Hot)</t>
         </is>
       </c>
-      <c r="B8" s="3" t="n">
-        <v>0</v>
+      <c r="B8" s="14" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Score 50-69 (Warm)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="n">
-        <v>0</v>
+      <c r="B9" s="14" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr"/>
-      <c r="B10" s="3" t="inlineStr"/>
+      <c r="A10" s="14" t="inlineStr"/>
+      <c r="B10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>By Category</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>Judgment</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>Lien</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -635,7 +635,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Run: 2026-06-28 05:16</t>
+          <t>Run: 2026-06-29 05:27</t>
         </is>
       </c>
     </row>

--- a/data/leads.xlsx
+++ b/data/leads.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads'!$A$1:$W$126</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,8 +19,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="5">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
+  </numFmts>
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +34,39 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C0392B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00B45309"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00374151"/>
       <sz val="10"/>
     </font>
     <font>
@@ -49,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -59,6 +94,21 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E2433"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9C3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -88,14 +138,50 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -461,7 +547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W1"/>
+  <dimension ref="A1:W126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -606,8 +692,9064 @@
         </is>
       </c>
     </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>20260386135</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>PennyMac Loan Services, LLC Leonard J. McDonald |</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>417073</v>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>7116 N 81st Ln :</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr"/>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="inlineStr"/>
+      <c r="S2" s="3" t="inlineStr">
+        <is>
+          <t>142-27-1482</t>
+        </is>
+      </c>
+      <c r="T2" s="3" t="inlineStr">
+        <is>
+          <t>PennyMac Loan Services, LLC Leonard J. McDonald |</t>
+        </is>
+      </c>
+      <c r="U2" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V2" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="26" customHeight="1">
+      <c r="A3" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>20260386426</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>ELTON MULTIFAMILY HOLDINGS, LLC, a limited liability company organized and existing</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>U.S. Bank Trust Company, National Association, as Trustee for the</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>6583000</v>
+      </c>
+      <c r="I3" s="3" t="inlineStr"/>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>2420 N 24th Street</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr"/>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr"/>
+      <c r="O3" s="3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr"/>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R3" s="3" t="inlineStr"/>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>117-08-1591</t>
+        </is>
+      </c>
+      <c r="T3" s="3" t="inlineStr">
+        <is>
+          <t>Craig K. Williams, Attorney at Law</t>
+        </is>
+      </c>
+      <c r="U3" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+        </is>
+      </c>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>20260387066</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>ASPIRE CAMELBACK, LLC, a limited liability company organized and existing under the laws of Delaware</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>111577974.1</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>2978000</v>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>2201 and 2121 West Heatherbrae Drive</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr"/>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr"/>
+      <c r="O4" s="3" t="inlineStr"/>
+      <c r="P4" s="3" t="inlineStr"/>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R4" s="3" t="inlineStr"/>
+      <c r="S4" s="3" t="inlineStr">
+        <is>
+          <t>154-29-042</t>
+        </is>
+      </c>
+      <c r="T4" s="3" t="inlineStr">
+        <is>
+          <t>John Craiger</t>
+        </is>
+      </c>
+      <c r="U4" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+        </is>
+      </c>
+      <c r="V4" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>20260387443</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>MAHER SABRY ABDEEN</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>255290</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>1006 WEST DANBURY ROAD</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>85023</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr"/>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R5" s="3" t="inlineStr"/>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>208-18-28132</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>20260387499</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>LAURIE ATKINS</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>411070</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>8433 E GUADALUPE RD 170</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>85212</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr"/>
+      <c r="P6" s="3" t="inlineStr"/>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R6" s="3" t="inlineStr"/>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>141-83-12812</t>
+        </is>
+      </c>
+      <c r="T6" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
+      <c r="U6" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>20260387536</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>Douglas Paulsen II</t>
+        </is>
+      </c>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Selene Finance, LP Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>381728</v>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>1734 S Aaron</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr"/>
+      <c r="O7" s="3" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr"/>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R7" s="3" t="inlineStr"/>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>220-80-6201</t>
+        </is>
+      </c>
+      <c r="T7" s="3" t="inlineStr">
+        <is>
+          <t>Selene Finance, LP Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U7" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>20260387621</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>Alexis Jerrae Andrade</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>501424</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>7923 W Pasadena Ave</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr"/>
+      <c r="O8" s="3" t="inlineStr"/>
+      <c r="P8" s="3" t="inlineStr"/>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr"/>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t>102-09-3506</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t>Lakeview Loan Servicing, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>20260387630</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>CAROL LYNN BROOKS</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>DATA MORTGAGE INC., DBA ESSEX MORTGAGE</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>316904</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>19738 WEST VERDE LANE</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr"/>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr"/>
+      <c r="O9" s="3" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr"/>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R9" s="3" t="inlineStr"/>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>502-62-3307</t>
+        </is>
+      </c>
+      <c r="T9" s="3" t="inlineStr">
+        <is>
+          <t>Erin K. Sweeney, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
+      <c r="U9" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>20260387719</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>Brian L. Childress</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Rocket Mortgage, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>239760</v>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>13579 W Post Dr</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr"/>
+      <c r="O10" s="3" t="inlineStr"/>
+      <c r="P10" s="3" t="inlineStr"/>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R10" s="3" t="inlineStr"/>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>501-91-1609</t>
+        </is>
+      </c>
+      <c r="T10" s="3" t="inlineStr">
+        <is>
+          <t>Rocket Mortgage, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U10" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>20260387818</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>RAMON ALGANDAR</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>115862</v>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>4915 W. ELM STREET</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t>85031</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr"/>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R11" s="3" t="inlineStr"/>
+      <c r="S11" s="3" t="inlineStr">
+        <is>
+          <t>145-17-01822</t>
+        </is>
+      </c>
+      <c r="T11" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
+      <c r="U11" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V11" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>20260387890</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>THOMAS ANTHONY MARTINEZ AND NAYELY VANESSA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+      <c r="H12" s="4" t="n">
+        <v>348368</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>25214 N 142ND DR</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>SURPRISE</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>85387</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr"/>
+      <c r="P12" s="3" t="inlineStr"/>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr"/>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t>503-69-3917</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t>America West Lender Services, LLC</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>20260388048</t>
+        </is>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>RUBEN IVAN CRUZ MONTOYA AND ITZEL G COTA MARTINEZ</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>375070</v>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>3878 S 244TH AVE</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr"/>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr"/>
+      <c r="O13" s="3" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr"/>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr"/>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t>504-24-741</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t>(</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>20260388094</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>MATTHEW MIKE ZACZENIUK</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>407807</v>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>13415 W Ironwood St</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t>85374</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr"/>
+      <c r="P14" s="3" t="inlineStr"/>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr"/>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t>503-61-23002</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>20260388145</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>JOSE DANIEL ROMERO CONTRERAS AND PATRICIA JAQUELINE TORRES, HUSBAND</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>U.S. BANK NATIONAL ASSOCIATION</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>393263</v>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING MARICOPA COUNTY COURTHOUSE</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>2113 S 124TH DR</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>AVONDALE</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
+          <t>85323</t>
+        </is>
+      </c>
+      <c r="O15" s="3" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr"/>
+      <c r="Q15" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R15" s="3" t="inlineStr"/>
+      <c r="S15" s="3" t="inlineStr"/>
+      <c r="T15" s="3" t="inlineStr">
+        <is>
+          <t>Prime Recon LLC</t>
+        </is>
+      </c>
+      <c r="U15" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V15" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>20260388189</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>CHARLES M CHAVEZ AND BETSZABEL B CHAVEZ</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>368207</v>
+      </c>
+      <c r="I16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>17935 W ADAMS ST</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>GOODYEAR</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
+          <t>85338</t>
+        </is>
+      </c>
+      <c r="O16" s="3" t="inlineStr"/>
+      <c r="P16" s="3" t="inlineStr"/>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R16" s="3" t="inlineStr"/>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>504-28-6422</t>
+        </is>
+      </c>
+      <c r="T16" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
+      <c r="U16" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V16" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>20260388211</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Travis Allan Garber</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>440833</v>
+      </c>
+      <c r="I17" s="3" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building of the Maricopa County Courthouse</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>17657 W Buckhorn Trl</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr"/>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr"/>
+      <c r="O17" s="3" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr"/>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R17" s="3" t="inlineStr"/>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>503-57-3031</t>
+        </is>
+      </c>
+      <c r="T17" s="3" t="inlineStr">
+        <is>
+          <t>Guild Mortgage Company LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U17" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V17" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>20260388277</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>JARED DONALD JOHNSTON, UNMARRIED MAN</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>314204</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>2415 W SAINT JOHN RD</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>85023</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr"/>
+      <c r="P18" s="3" t="inlineStr"/>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr"/>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
+          <t>208-30-02222</t>
+        </is>
+      </c>
+      <c r="T18" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
+      <c r="U18" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V18" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>20260388394</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>MIASIA PASHA</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>Freedom Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>188236</v>
+      </c>
+      <c r="I19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>10752 W PEORIA AVE</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>SUN CITY</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr"/>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr"/>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>142-80-5872</t>
+        </is>
+      </c>
+      <c r="T19" s="3" t="inlineStr">
+        <is>
+          <t>Kim Quam, a member of the State Bar of Arizona</t>
+        </is>
+      </c>
+      <c r="U19" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>20260388686</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>LINDA K HARRIS, UNMARRIED WOMAN</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>PennyMac Loan Services, LLC</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="n">
+        <v>245471</v>
+      </c>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>13615 N 110TH AVE</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>SUN CITY</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
+      <c r="O20" s="3" t="inlineStr"/>
+      <c r="P20" s="3" t="inlineStr"/>
+      <c r="Q20" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R20" s="3" t="inlineStr"/>
+      <c r="S20" s="3" t="inlineStr">
+        <is>
+          <t>200-85-754</t>
+        </is>
+      </c>
+      <c r="T20" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U20" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V20" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W20" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>20260388715</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>Proferty LLC</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr"/>
+      <c r="H21" s="4" t="n">
+        <v>339000</v>
+      </c>
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr"/>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>1932 W. Whitton Ave</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr"/>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr"/>
+      <c r="O21" s="3" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr"/>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr"/>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t>110-17-083</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="inlineStr"/>
+      <c r="U21" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week; LLC / corp owner</t>
+        </is>
+      </c>
+      <c r="V21" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W21" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>20260388720</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>STACIA BLIER</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Lakeview Loan Servicing, LLC</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="n">
+        <v>200305</v>
+      </c>
+      <c r="I22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>2928 NORTH CASA TOMAS COURT</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>PHOENIX</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
+          <t>85016</t>
+        </is>
+      </c>
+      <c r="O22" s="3" t="inlineStr"/>
+      <c r="P22" s="3" t="inlineStr"/>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R22" s="3" t="inlineStr"/>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t>119-34-046</t>
+        </is>
+      </c>
+      <c r="T22" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U22" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V22" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W22" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>20260388732</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>TAYLOR BROWN</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t>U.S, Bank National Association</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="n">
+        <v>206196</v>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>4654 W TUCKEY LN</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>GLENDALE</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t>85301</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr"/>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R23" s="3" t="inlineStr"/>
+      <c r="S23" s="3" t="inlineStr">
+        <is>
+          <t>146-27-2158</t>
+        </is>
+      </c>
+      <c r="T23" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U23" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V23" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W23" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>20260388737</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>ROSE MARY CALVERT</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr">
+        <is>
+          <t>TH MSR Holdings LLC</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="n">
+        <v>260000</v>
+      </c>
+      <c r="I24" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>10320 W PINEAIRE DR</t>
+        </is>
+      </c>
+      <c r="L24" s="3" t="inlineStr">
+        <is>
+          <t>SUN CITY</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
+          <t>85351</t>
+        </is>
+      </c>
+      <c r="O24" s="3" t="inlineStr"/>
+      <c r="P24" s="3" t="inlineStr"/>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R24" s="3" t="inlineStr"/>
+      <c r="S24" s="3" t="inlineStr">
+        <is>
+          <t>230-01-1831</t>
+        </is>
+      </c>
+      <c r="T24" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U24" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V24" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W24" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>20260388741</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>MARGHERITA FRAY</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>Longbridge Financial, LLC</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="n">
+        <v>750000</v>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>201 West Jefferson</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>5046 N 82ND STREET</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>SCOTTSDALE</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>85250</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr"/>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr"/>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>173-26-4112</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W25" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>20260388754</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>JOSUE LINARES CORTEZ</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>U.S. Bank National Association</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="n">
+        <v>265109</v>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
+        <is>
+          <t>9309 W JEFFERSON STREET</t>
+        </is>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>TOLLESON</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>85353</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr"/>
+      <c r="P26" s="3" t="inlineStr"/>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr"/>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>101-10-0346</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. doa Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W26" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>20260388759</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>DENNIS J. BALZAN</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>Lakeview Loan Servicing, LLC</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>160115</v>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>1120 S 97TH ST</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>MESA</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>85208</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr"/>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr"/>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>220-70-7526</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="inlineStr"/>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V27" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W27" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>20260388770</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>ALEXANDRA GONZALEZ</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Rocket Mortgage, LLC</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>358900</v>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Superior Court Building</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>12725 W VOLTAIRE AVE</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>EL MIRAGE</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>85335</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr"/>
+      <c r="P28" s="3" t="inlineStr"/>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr"/>
+      <c r="S28" s="3" t="inlineStr">
+        <is>
+          <t>501-37-4059</t>
+        </is>
+      </c>
+      <c r="T28" s="3" t="inlineStr">
+        <is>
+          <t>MTC Financial Inc. dba Trustee Corps</t>
+        </is>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V28" s="3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W28" s="5" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C29" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>20260386072</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>LUCIEN T. PHOENIX AND JANE A. PHOENIX, HIS WIFE, AS JOINT TENANTS WITH RIGHT OF</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="inlineStr">
+        <is>
+          <t>Bank of New York Mellon Trust Company, N.A. as Owner Trustee for Mortgage Assets Management Series I</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>394725</v>
+      </c>
+      <c r="I29" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J29" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K29" s="7" t="inlineStr"/>
+      <c r="L29" s="7" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr"/>
+      <c r="O29" s="7" t="inlineStr"/>
+      <c r="P29" s="7" t="inlineStr"/>
+      <c r="Q29" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R29" s="7" t="inlineStr"/>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>135-18-080</t>
+        </is>
+      </c>
+      <c r="T29" s="7" t="inlineStr">
+        <is>
+          <t>Western Progressive — Arizona, Inc.</t>
+        </is>
+      </c>
+      <c r="U29" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V29" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>20260386086</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>DAVID MORROW AND OGREDA MORROW</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Onity Mortgage Corporation F/K/A PHH Mortgage Corporation</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>843000</v>
+      </c>
+      <c r="I30" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT BUILDING</t>
+        </is>
+      </c>
+      <c r="K30" s="7" t="inlineStr"/>
+      <c r="L30" s="7" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr"/>
+      <c r="O30" s="7" t="inlineStr"/>
+      <c r="P30" s="7" t="inlineStr"/>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R30" s="7" t="inlineStr"/>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>303-74-055</t>
+        </is>
+      </c>
+      <c r="T30" s="7" t="inlineStr">
+        <is>
+          <t>Western Progressive — Arizona, Inc.</t>
+        </is>
+      </c>
+      <c r="U30" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V30" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>20260386225</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>Adriano Rodrigues Da Costa and Carrie Beth Da Costa</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="inlineStr">
+        <is>
+          <t>PennyMac Loan Services, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>517994</v>
+      </c>
+      <c r="I31" s="7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="J31" s="7" t="inlineStr"/>
+      <c r="K31" s="7" t="inlineStr"/>
+      <c r="L31" s="7" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr"/>
+      <c r="O31" s="7" t="inlineStr"/>
+      <c r="P31" s="7" t="inlineStr"/>
+      <c r="Q31" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R31" s="7" t="inlineStr"/>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>503-77-25032</t>
+        </is>
+      </c>
+      <c r="T31" s="7" t="inlineStr">
+        <is>
+          <t>PennyMac Loan Services, LLC Leonard J. McDonald</t>
+        </is>
+      </c>
+      <c r="U31" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V31" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>20260388342</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr"/>
+      <c r="G32" s="7" t="inlineStr">
+        <is>
+          <t>C/O Mortgage Clearing Corp.</t>
+        </is>
+      </c>
+      <c r="H32" s="8" t="n">
+        <v>341910</v>
+      </c>
+      <c r="I32" s="7" t="inlineStr"/>
+      <c r="J32" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K32" s="7" t="inlineStr"/>
+      <c r="L32" s="7" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr"/>
+      <c r="O32" s="7" t="inlineStr"/>
+      <c r="P32" s="7" t="inlineStr"/>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R32" s="7" t="inlineStr"/>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>303-60-3501</t>
+        </is>
+      </c>
+      <c r="T32" s="7" t="inlineStr"/>
+      <c r="U32" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V32" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Notice of Trustee Sale</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="inlineStr">
+        <is>
+          <t>NS</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>20260388584</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr"/>
+      <c r="G33" s="7" t="inlineStr">
+        <is>
+          <t>C/O Onity Mortgage</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>652000</v>
+      </c>
+      <c r="I33" s="7" t="inlineStr"/>
+      <c r="J33" s="7" t="inlineStr">
+        <is>
+          <t>Superior Courts Building. Maricopa County</t>
+        </is>
+      </c>
+      <c r="K33" s="7" t="inlineStr"/>
+      <c r="L33" s="7" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr"/>
+      <c r="O33" s="7" t="inlineStr"/>
+      <c r="P33" s="7" t="inlineStr"/>
+      <c r="Q33" s="7" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R33" s="7" t="inlineStr"/>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>301-94-036</t>
+        </is>
+      </c>
+      <c r="T33" s="7" t="inlineStr"/>
+      <c r="U33" s="7" t="inlineStr">
+        <is>
+          <t>Pre-foreclosure; Trustee Sale; New this week</t>
+        </is>
+      </c>
+      <c r="V33" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W33" s="9" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>PD</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>20260388364</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr"/>
+      <c r="G34" s="11" t="inlineStr"/>
+      <c r="H34" s="11" t="inlineStr"/>
+      <c r="I34" s="11" t="inlineStr"/>
+      <c r="J34" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr"/>
+      <c r="L34" s="11" t="inlineStr"/>
+      <c r="M34" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N34" s="11" t="inlineStr"/>
+      <c r="O34" s="11" t="inlineStr"/>
+      <c r="P34" s="11" t="inlineStr"/>
+      <c r="Q34" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R34" s="11" t="inlineStr"/>
+      <c r="S34" s="11" t="inlineStr"/>
+      <c r="T34" s="11" t="inlineStr"/>
+      <c r="U34" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V34" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W34" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>20260386552</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr"/>
+      <c r="G35" s="11" t="inlineStr"/>
+      <c r="H35" s="11" t="inlineStr"/>
+      <c r="I35" s="11" t="inlineStr"/>
+      <c r="J35" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr"/>
+      <c r="L35" s="11" t="inlineStr"/>
+      <c r="M35" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N35" s="11" t="inlineStr"/>
+      <c r="O35" s="11" t="inlineStr"/>
+      <c r="P35" s="11" t="inlineStr"/>
+      <c r="Q35" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R35" s="11" t="inlineStr"/>
+      <c r="S35" s="11" t="inlineStr"/>
+      <c r="T35" s="11" t="inlineStr"/>
+      <c r="U35" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V35" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W35" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>20260387083</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr"/>
+      <c r="G36" s="11" t="inlineStr"/>
+      <c r="H36" s="11" t="inlineStr"/>
+      <c r="I36" s="11" t="inlineStr"/>
+      <c r="J36" s="11" t="inlineStr">
+        <is>
+          <t>Superior Court</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr"/>
+      <c r="L36" s="11" t="inlineStr"/>
+      <c r="M36" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N36" s="11" t="inlineStr"/>
+      <c r="O36" s="11" t="inlineStr"/>
+      <c r="P36" s="11" t="inlineStr"/>
+      <c r="Q36" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R36" s="11" t="inlineStr"/>
+      <c r="S36" s="11" t="inlineStr"/>
+      <c r="T36" s="11" t="inlineStr"/>
+      <c r="U36" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V36" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W36" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="10" t="n">
+        <v>48</v>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>Probate Document</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>PJ</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>20260387710</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr"/>
+      <c r="G37" s="11" t="inlineStr"/>
+      <c r="H37" s="11" t="inlineStr"/>
+      <c r="I37" s="11" t="inlineStr"/>
+      <c r="J37" s="11" t="inlineStr">
+        <is>
+          <t>SUPERIOR COURT OF THE STATE OF ARIZONA</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr"/>
+      <c r="L37" s="11" t="inlineStr"/>
+      <c r="M37" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N37" s="11" t="inlineStr"/>
+      <c r="O37" s="11" t="inlineStr"/>
+      <c r="P37" s="11" t="inlineStr"/>
+      <c r="Q37" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R37" s="11" t="inlineStr"/>
+      <c r="S37" s="11" t="inlineStr"/>
+      <c r="T37" s="11" t="inlineStr"/>
+      <c r="U37" s="11" t="inlineStr">
+        <is>
+          <t>Probate / estate; New this week</t>
+        </is>
+      </c>
+      <c r="V37" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W37" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>20260386486</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr"/>
+      <c r="G38" s="11" t="inlineStr"/>
+      <c r="H38" s="11" t="inlineStr"/>
+      <c r="I38" s="11" t="inlineStr"/>
+      <c r="J38" s="11" t="inlineStr"/>
+      <c r="K38" s="11" t="inlineStr"/>
+      <c r="L38" s="11" t="inlineStr"/>
+      <c r="M38" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N38" s="11" t="inlineStr"/>
+      <c r="O38" s="11" t="inlineStr"/>
+      <c r="P38" s="11" t="inlineStr"/>
+      <c r="Q38" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R38" s="11" t="inlineStr"/>
+      <c r="S38" s="11" t="inlineStr">
+        <is>
+          <t>148-10-078</t>
+        </is>
+      </c>
+      <c r="T38" s="11" t="inlineStr"/>
+      <c r="U38" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V38" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W38" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B39" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>20260386703</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F39" s="11" t="inlineStr"/>
+      <c r="G39" s="11" t="inlineStr"/>
+      <c r="H39" s="11" t="inlineStr"/>
+      <c r="I39" s="11" t="inlineStr"/>
+      <c r="J39" s="11" t="inlineStr"/>
+      <c r="K39" s="11" t="inlineStr"/>
+      <c r="L39" s="11" t="inlineStr"/>
+      <c r="M39" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N39" s="11" t="inlineStr"/>
+      <c r="O39" s="11" t="inlineStr"/>
+      <c r="P39" s="11" t="inlineStr"/>
+      <c r="Q39" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R39" s="11" t="inlineStr"/>
+      <c r="S39" s="11" t="inlineStr"/>
+      <c r="T39" s="11" t="inlineStr"/>
+      <c r="U39" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V39" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W39" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B40" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C40" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>20260387094</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F40" s="11" t="inlineStr"/>
+      <c r="G40" s="11" t="inlineStr"/>
+      <c r="H40" s="13" t="n">
+        <v>31753</v>
+      </c>
+      <c r="I40" s="11" t="inlineStr"/>
+      <c r="J40" s="11" t="inlineStr"/>
+      <c r="K40" s="11" t="inlineStr"/>
+      <c r="L40" s="11" t="inlineStr"/>
+      <c r="M40" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N40" s="11" t="inlineStr"/>
+      <c r="O40" s="11" t="inlineStr"/>
+      <c r="P40" s="11" t="inlineStr"/>
+      <c r="Q40" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R40" s="11" t="inlineStr"/>
+      <c r="S40" s="11" t="inlineStr">
+        <is>
+          <t>500-10-904</t>
+        </is>
+      </c>
+      <c r="T40" s="11" t="inlineStr"/>
+      <c r="U40" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V40" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W40" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B41" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D41" s="11" t="inlineStr">
+        <is>
+          <t>20260387243</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F41" s="11" t="inlineStr"/>
+      <c r="G41" s="11" t="inlineStr"/>
+      <c r="H41" s="11" t="inlineStr"/>
+      <c r="I41" s="11" t="inlineStr"/>
+      <c r="J41" s="11" t="inlineStr"/>
+      <c r="K41" s="11" t="inlineStr"/>
+      <c r="L41" s="11" t="inlineStr"/>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N41" s="11" t="inlineStr"/>
+      <c r="O41" s="11" t="inlineStr"/>
+      <c r="P41" s="11" t="inlineStr"/>
+      <c r="Q41" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R41" s="11" t="inlineStr"/>
+      <c r="S41" s="11" t="inlineStr"/>
+      <c r="T41" s="11" t="inlineStr"/>
+      <c r="U41" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V41" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W41" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B42" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C42" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>20260387249</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F42" s="11" t="inlineStr"/>
+      <c r="G42" s="11" t="inlineStr"/>
+      <c r="H42" s="11" t="inlineStr"/>
+      <c r="I42" s="11" t="inlineStr"/>
+      <c r="J42" s="11" t="inlineStr"/>
+      <c r="K42" s="11" t="inlineStr"/>
+      <c r="L42" s="11" t="inlineStr"/>
+      <c r="M42" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N42" s="11" t="inlineStr"/>
+      <c r="O42" s="11" t="inlineStr"/>
+      <c r="P42" s="11" t="inlineStr"/>
+      <c r="Q42" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R42" s="11" t="inlineStr"/>
+      <c r="S42" s="11" t="inlineStr">
+        <is>
+          <t>144-36-973</t>
+        </is>
+      </c>
+      <c r="T42" s="11" t="inlineStr"/>
+      <c r="U42" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V42" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W42" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B43" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C43" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>20260387256</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F43" s="11" t="inlineStr"/>
+      <c r="G43" s="11" t="inlineStr"/>
+      <c r="H43" s="11" t="inlineStr"/>
+      <c r="I43" s="11" t="inlineStr"/>
+      <c r="J43" s="11" t="inlineStr"/>
+      <c r="K43" s="11" t="inlineStr"/>
+      <c r="L43" s="11" t="inlineStr"/>
+      <c r="M43" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N43" s="11" t="inlineStr"/>
+      <c r="O43" s="11" t="inlineStr"/>
+      <c r="P43" s="11" t="inlineStr"/>
+      <c r="Q43" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R43" s="11" t="inlineStr"/>
+      <c r="S43" s="11" t="inlineStr">
+        <is>
+          <t>104-74-004</t>
+        </is>
+      </c>
+      <c r="T43" s="11" t="inlineStr"/>
+      <c r="U43" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V43" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W43" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="10" t="n">
+        <v>46</v>
+      </c>
+      <c r="B44" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic Lien</t>
+        </is>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>ML</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>20260387274</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F44" s="11" t="inlineStr"/>
+      <c r="G44" s="11" t="inlineStr"/>
+      <c r="H44" s="11" t="inlineStr"/>
+      <c r="I44" s="11" t="inlineStr"/>
+      <c r="J44" s="11" t="inlineStr"/>
+      <c r="K44" s="11" t="inlineStr"/>
+      <c r="L44" s="11" t="inlineStr"/>
+      <c r="M44" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N44" s="11" t="inlineStr"/>
+      <c r="O44" s="11" t="inlineStr"/>
+      <c r="P44" s="11" t="inlineStr"/>
+      <c r="Q44" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R44" s="11" t="inlineStr"/>
+      <c r="S44" s="11" t="inlineStr">
+        <is>
+          <t>303-65-7143</t>
+        </is>
+      </c>
+      <c r="T44" s="11" t="inlineStr"/>
+      <c r="U44" s="11" t="inlineStr">
+        <is>
+          <t>Mechanic lien; New this week</t>
+        </is>
+      </c>
+      <c r="V44" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W44" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B45" s="11" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C45" s="11" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>20260388404</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F45" s="11" t="inlineStr"/>
+      <c r="G45" s="11" t="inlineStr"/>
+      <c r="H45" s="11" t="inlineStr"/>
+      <c r="I45" s="11" t="inlineStr"/>
+      <c r="J45" s="11" t="inlineStr"/>
+      <c r="K45" s="11" t="inlineStr"/>
+      <c r="L45" s="11" t="inlineStr"/>
+      <c r="M45" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N45" s="11" t="inlineStr"/>
+      <c r="O45" s="11" t="inlineStr"/>
+      <c r="P45" s="11" t="inlineStr"/>
+      <c r="Q45" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R45" s="11" t="inlineStr"/>
+      <c r="S45" s="11" t="inlineStr"/>
+      <c r="T45" s="11" t="inlineStr"/>
+      <c r="U45" s="11" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V45" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W45" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="11" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>20260388405</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F46" s="11" t="inlineStr"/>
+      <c r="G46" s="11" t="inlineStr"/>
+      <c r="H46" s="11" t="inlineStr"/>
+      <c r="I46" s="11" t="inlineStr"/>
+      <c r="J46" s="11" t="inlineStr"/>
+      <c r="K46" s="11" t="inlineStr"/>
+      <c r="L46" s="11" t="inlineStr"/>
+      <c r="M46" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N46" s="11" t="inlineStr"/>
+      <c r="O46" s="11" t="inlineStr"/>
+      <c r="P46" s="11" t="inlineStr"/>
+      <c r="Q46" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R46" s="11" t="inlineStr"/>
+      <c r="S46" s="11" t="inlineStr"/>
+      <c r="T46" s="11" t="inlineStr"/>
+      <c r="U46" s="11" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V46" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W46" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>State Tax Lien</t>
+        </is>
+      </c>
+      <c r="C47" s="11" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>20260388406</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F47" s="11" t="inlineStr"/>
+      <c r="G47" s="11" t="inlineStr"/>
+      <c r="H47" s="11" t="inlineStr"/>
+      <c r="I47" s="11" t="inlineStr"/>
+      <c r="J47" s="11" t="inlineStr"/>
+      <c r="K47" s="11" t="inlineStr"/>
+      <c r="L47" s="11" t="inlineStr"/>
+      <c r="M47" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N47" s="11" t="inlineStr"/>
+      <c r="O47" s="11" t="inlineStr"/>
+      <c r="P47" s="11" t="inlineStr"/>
+      <c r="Q47" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R47" s="11" t="inlineStr"/>
+      <c r="S47" s="11" t="inlineStr"/>
+      <c r="T47" s="11" t="inlineStr"/>
+      <c r="U47" s="11" t="inlineStr">
+        <is>
+          <t>Gov/Tax lien; New this week</t>
+        </is>
+      </c>
+      <c r="V47" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W47" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>20260385707</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F48" s="11" t="inlineStr"/>
+      <c r="G48" s="11" t="inlineStr"/>
+      <c r="H48" s="11" t="inlineStr"/>
+      <c r="I48" s="11" t="inlineStr"/>
+      <c r="J48" s="11" t="inlineStr"/>
+      <c r="K48" s="11" t="inlineStr"/>
+      <c r="L48" s="11" t="inlineStr"/>
+      <c r="M48" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N48" s="11" t="inlineStr"/>
+      <c r="O48" s="11" t="inlineStr"/>
+      <c r="P48" s="11" t="inlineStr"/>
+      <c r="Q48" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R48" s="11" t="inlineStr"/>
+      <c r="S48" s="11" t="inlineStr"/>
+      <c r="T48" s="11" t="inlineStr"/>
+      <c r="U48" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V48" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W48" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C49" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>20260385708</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F49" s="11" t="inlineStr"/>
+      <c r="G49" s="11" t="inlineStr"/>
+      <c r="H49" s="11" t="inlineStr"/>
+      <c r="I49" s="11" t="inlineStr"/>
+      <c r="J49" s="11" t="inlineStr"/>
+      <c r="K49" s="11" t="inlineStr"/>
+      <c r="L49" s="11" t="inlineStr"/>
+      <c r="M49" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N49" s="11" t="inlineStr"/>
+      <c r="O49" s="11" t="inlineStr"/>
+      <c r="P49" s="11" t="inlineStr"/>
+      <c r="Q49" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R49" s="11" t="inlineStr"/>
+      <c r="S49" s="11" t="inlineStr"/>
+      <c r="T49" s="11" t="inlineStr"/>
+      <c r="U49" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V49" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W49" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B50" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C50" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>20260385709</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F50" s="11" t="inlineStr"/>
+      <c r="G50" s="11" t="inlineStr"/>
+      <c r="H50" s="11" t="inlineStr"/>
+      <c r="I50" s="11" t="inlineStr"/>
+      <c r="J50" s="11" t="inlineStr"/>
+      <c r="K50" s="11" t="inlineStr"/>
+      <c r="L50" s="11" t="inlineStr"/>
+      <c r="M50" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N50" s="11" t="inlineStr"/>
+      <c r="O50" s="11" t="inlineStr"/>
+      <c r="P50" s="11" t="inlineStr"/>
+      <c r="Q50" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R50" s="11" t="inlineStr"/>
+      <c r="S50" s="11" t="inlineStr"/>
+      <c r="T50" s="11" t="inlineStr"/>
+      <c r="U50" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V50" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W50" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="26" customHeight="1">
+      <c r="A51" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>20260385710</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F51" s="11" t="inlineStr"/>
+      <c r="G51" s="11" t="inlineStr"/>
+      <c r="H51" s="11" t="inlineStr"/>
+      <c r="I51" s="11" t="inlineStr"/>
+      <c r="J51" s="11" t="inlineStr"/>
+      <c r="K51" s="11" t="inlineStr"/>
+      <c r="L51" s="11" t="inlineStr"/>
+      <c r="M51" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N51" s="11" t="inlineStr"/>
+      <c r="O51" s="11" t="inlineStr"/>
+      <c r="P51" s="11" t="inlineStr"/>
+      <c r="Q51" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R51" s="11" t="inlineStr"/>
+      <c r="S51" s="11" t="inlineStr"/>
+      <c r="T51" s="11" t="inlineStr"/>
+      <c r="U51" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V51" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W51" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B52" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>20260385711</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F52" s="11" t="inlineStr"/>
+      <c r="G52" s="11" t="inlineStr"/>
+      <c r="H52" s="11" t="inlineStr"/>
+      <c r="I52" s="11" t="inlineStr"/>
+      <c r="J52" s="11" t="inlineStr"/>
+      <c r="K52" s="11" t="inlineStr"/>
+      <c r="L52" s="11" t="inlineStr"/>
+      <c r="M52" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N52" s="11" t="inlineStr"/>
+      <c r="O52" s="11" t="inlineStr"/>
+      <c r="P52" s="11" t="inlineStr"/>
+      <c r="Q52" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R52" s="11" t="inlineStr"/>
+      <c r="S52" s="11" t="inlineStr"/>
+      <c r="T52" s="11" t="inlineStr"/>
+      <c r="U52" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V52" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W52" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B53" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>20260385712</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F53" s="11" t="inlineStr"/>
+      <c r="G53" s="11" t="inlineStr"/>
+      <c r="H53" s="11" t="inlineStr"/>
+      <c r="I53" s="11" t="inlineStr"/>
+      <c r="J53" s="11" t="inlineStr"/>
+      <c r="K53" s="11" t="inlineStr"/>
+      <c r="L53" s="11" t="inlineStr"/>
+      <c r="M53" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N53" s="11" t="inlineStr"/>
+      <c r="O53" s="11" t="inlineStr"/>
+      <c r="P53" s="11" t="inlineStr"/>
+      <c r="Q53" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R53" s="11" t="inlineStr"/>
+      <c r="S53" s="11" t="inlineStr"/>
+      <c r="T53" s="11" t="inlineStr"/>
+      <c r="U53" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V53" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W53" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>20260385714</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F54" s="11" t="inlineStr"/>
+      <c r="G54" s="11" t="inlineStr"/>
+      <c r="H54" s="11" t="inlineStr"/>
+      <c r="I54" s="11" t="inlineStr"/>
+      <c r="J54" s="11" t="inlineStr"/>
+      <c r="K54" s="11" t="inlineStr"/>
+      <c r="L54" s="11" t="inlineStr"/>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N54" s="11" t="inlineStr"/>
+      <c r="O54" s="11" t="inlineStr"/>
+      <c r="P54" s="11" t="inlineStr"/>
+      <c r="Q54" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R54" s="11" t="inlineStr"/>
+      <c r="S54" s="11" t="inlineStr"/>
+      <c r="T54" s="11" t="inlineStr"/>
+      <c r="U54" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V54" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W54" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>20260385715</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F55" s="11" t="inlineStr"/>
+      <c r="G55" s="11" t="inlineStr"/>
+      <c r="H55" s="11" t="inlineStr"/>
+      <c r="I55" s="11" t="inlineStr"/>
+      <c r="J55" s="11" t="inlineStr"/>
+      <c r="K55" s="11" t="inlineStr"/>
+      <c r="L55" s="11" t="inlineStr"/>
+      <c r="M55" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N55" s="11" t="inlineStr"/>
+      <c r="O55" s="11" t="inlineStr"/>
+      <c r="P55" s="11" t="inlineStr"/>
+      <c r="Q55" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R55" s="11" t="inlineStr"/>
+      <c r="S55" s="11" t="inlineStr"/>
+      <c r="T55" s="11" t="inlineStr"/>
+      <c r="U55" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V55" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W55" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>20260385716</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F56" s="11" t="inlineStr"/>
+      <c r="G56" s="11" t="inlineStr"/>
+      <c r="H56" s="11" t="inlineStr"/>
+      <c r="I56" s="11" t="inlineStr"/>
+      <c r="J56" s="11" t="inlineStr"/>
+      <c r="K56" s="11" t="inlineStr"/>
+      <c r="L56" s="11" t="inlineStr"/>
+      <c r="M56" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N56" s="11" t="inlineStr"/>
+      <c r="O56" s="11" t="inlineStr"/>
+      <c r="P56" s="11" t="inlineStr"/>
+      <c r="Q56" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R56" s="11" t="inlineStr"/>
+      <c r="S56" s="11" t="inlineStr"/>
+      <c r="T56" s="11" t="inlineStr"/>
+      <c r="U56" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V56" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W56" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>20260385717</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F57" s="11" t="inlineStr"/>
+      <c r="G57" s="11" t="inlineStr"/>
+      <c r="H57" s="11" t="inlineStr"/>
+      <c r="I57" s="11" t="inlineStr"/>
+      <c r="J57" s="11" t="inlineStr"/>
+      <c r="K57" s="11" t="inlineStr"/>
+      <c r="L57" s="11" t="inlineStr"/>
+      <c r="M57" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N57" s="11" t="inlineStr"/>
+      <c r="O57" s="11" t="inlineStr"/>
+      <c r="P57" s="11" t="inlineStr"/>
+      <c r="Q57" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R57" s="11" t="inlineStr"/>
+      <c r="S57" s="11" t="inlineStr"/>
+      <c r="T57" s="11" t="inlineStr"/>
+      <c r="U57" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V57" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W57" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>20260385718</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F58" s="11" t="inlineStr"/>
+      <c r="G58" s="11" t="inlineStr"/>
+      <c r="H58" s="11" t="inlineStr"/>
+      <c r="I58" s="11" t="inlineStr"/>
+      <c r="J58" s="11" t="inlineStr"/>
+      <c r="K58" s="11" t="inlineStr"/>
+      <c r="L58" s="11" t="inlineStr"/>
+      <c r="M58" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N58" s="11" t="inlineStr"/>
+      <c r="O58" s="11" t="inlineStr"/>
+      <c r="P58" s="11" t="inlineStr"/>
+      <c r="Q58" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R58" s="11" t="inlineStr"/>
+      <c r="S58" s="11" t="inlineStr"/>
+      <c r="T58" s="11" t="inlineStr"/>
+      <c r="U58" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V58" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W58" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>20260385719</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F59" s="11" t="inlineStr"/>
+      <c r="G59" s="11" t="inlineStr"/>
+      <c r="H59" s="11" t="inlineStr"/>
+      <c r="I59" s="11" t="inlineStr"/>
+      <c r="J59" s="11" t="inlineStr"/>
+      <c r="K59" s="11" t="inlineStr"/>
+      <c r="L59" s="11" t="inlineStr"/>
+      <c r="M59" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N59" s="11" t="inlineStr"/>
+      <c r="O59" s="11" t="inlineStr"/>
+      <c r="P59" s="11" t="inlineStr"/>
+      <c r="Q59" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R59" s="11" t="inlineStr"/>
+      <c r="S59" s="11" t="inlineStr"/>
+      <c r="T59" s="11" t="inlineStr"/>
+      <c r="U59" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V59" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W59" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>20260385720</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F60" s="11" t="inlineStr"/>
+      <c r="G60" s="11" t="inlineStr"/>
+      <c r="H60" s="11" t="inlineStr"/>
+      <c r="I60" s="11" t="inlineStr"/>
+      <c r="J60" s="11" t="inlineStr"/>
+      <c r="K60" s="11" t="inlineStr"/>
+      <c r="L60" s="11" t="inlineStr"/>
+      <c r="M60" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N60" s="11" t="inlineStr"/>
+      <c r="O60" s="11" t="inlineStr"/>
+      <c r="P60" s="11" t="inlineStr"/>
+      <c r="Q60" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R60" s="11" t="inlineStr"/>
+      <c r="S60" s="11" t="inlineStr"/>
+      <c r="T60" s="11" t="inlineStr"/>
+      <c r="U60" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V60" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W60" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>20260385721</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F61" s="11" t="inlineStr"/>
+      <c r="G61" s="11" t="inlineStr"/>
+      <c r="H61" s="11" t="inlineStr"/>
+      <c r="I61" s="11" t="inlineStr"/>
+      <c r="J61" s="11" t="inlineStr"/>
+      <c r="K61" s="11" t="inlineStr"/>
+      <c r="L61" s="11" t="inlineStr"/>
+      <c r="M61" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N61" s="11" t="inlineStr"/>
+      <c r="O61" s="11" t="inlineStr"/>
+      <c r="P61" s="11" t="inlineStr"/>
+      <c r="Q61" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R61" s="11" t="inlineStr"/>
+      <c r="S61" s="11" t="inlineStr"/>
+      <c r="T61" s="11" t="inlineStr"/>
+      <c r="U61" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V61" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W61" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>20260385722</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F62" s="11" t="inlineStr"/>
+      <c r="G62" s="11" t="inlineStr"/>
+      <c r="H62" s="11" t="inlineStr"/>
+      <c r="I62" s="11" t="inlineStr"/>
+      <c r="J62" s="11" t="inlineStr"/>
+      <c r="K62" s="11" t="inlineStr"/>
+      <c r="L62" s="11" t="inlineStr"/>
+      <c r="M62" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N62" s="11" t="inlineStr"/>
+      <c r="O62" s="11" t="inlineStr"/>
+      <c r="P62" s="11" t="inlineStr"/>
+      <c r="Q62" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R62" s="11" t="inlineStr"/>
+      <c r="S62" s="11" t="inlineStr"/>
+      <c r="T62" s="11" t="inlineStr"/>
+      <c r="U62" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V62" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W62" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B63" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C63" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>20260385723</t>
+        </is>
+      </c>
+      <c r="E63" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F63" s="11" t="inlineStr"/>
+      <c r="G63" s="11" t="inlineStr"/>
+      <c r="H63" s="11" t="inlineStr"/>
+      <c r="I63" s="11" t="inlineStr"/>
+      <c r="J63" s="11" t="inlineStr"/>
+      <c r="K63" s="11" t="inlineStr"/>
+      <c r="L63" s="11" t="inlineStr"/>
+      <c r="M63" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N63" s="11" t="inlineStr"/>
+      <c r="O63" s="11" t="inlineStr"/>
+      <c r="P63" s="11" t="inlineStr"/>
+      <c r="Q63" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R63" s="11" t="inlineStr"/>
+      <c r="S63" s="11" t="inlineStr"/>
+      <c r="T63" s="11" t="inlineStr"/>
+      <c r="U63" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V63" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W63" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C64" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D64" s="11" t="inlineStr">
+        <is>
+          <t>20260385724</t>
+        </is>
+      </c>
+      <c r="E64" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F64" s="11" t="inlineStr"/>
+      <c r="G64" s="11" t="inlineStr"/>
+      <c r="H64" s="11" t="inlineStr"/>
+      <c r="I64" s="11" t="inlineStr"/>
+      <c r="J64" s="11" t="inlineStr"/>
+      <c r="K64" s="11" t="inlineStr"/>
+      <c r="L64" s="11" t="inlineStr"/>
+      <c r="M64" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N64" s="11" t="inlineStr"/>
+      <c r="O64" s="11" t="inlineStr"/>
+      <c r="P64" s="11" t="inlineStr"/>
+      <c r="Q64" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R64" s="11" t="inlineStr"/>
+      <c r="S64" s="11" t="inlineStr"/>
+      <c r="T64" s="11" t="inlineStr"/>
+      <c r="U64" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V64" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W64" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D65" s="11" t="inlineStr">
+        <is>
+          <t>20260385725</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F65" s="11" t="inlineStr"/>
+      <c r="G65" s="11" t="inlineStr"/>
+      <c r="H65" s="11" t="inlineStr"/>
+      <c r="I65" s="11" t="inlineStr"/>
+      <c r="J65" s="11" t="inlineStr"/>
+      <c r="K65" s="11" t="inlineStr"/>
+      <c r="L65" s="11" t="inlineStr"/>
+      <c r="M65" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N65" s="11" t="inlineStr"/>
+      <c r="O65" s="11" t="inlineStr"/>
+      <c r="P65" s="11" t="inlineStr"/>
+      <c r="Q65" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R65" s="11" t="inlineStr"/>
+      <c r="S65" s="11" t="inlineStr"/>
+      <c r="T65" s="11" t="inlineStr"/>
+      <c r="U65" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V65" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W65" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C66" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>20260385726</t>
+        </is>
+      </c>
+      <c r="E66" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F66" s="11" t="inlineStr"/>
+      <c r="G66" s="11" t="inlineStr"/>
+      <c r="H66" s="11" t="inlineStr"/>
+      <c r="I66" s="11" t="inlineStr"/>
+      <c r="J66" s="11" t="inlineStr"/>
+      <c r="K66" s="11" t="inlineStr"/>
+      <c r="L66" s="11" t="inlineStr"/>
+      <c r="M66" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N66" s="11" t="inlineStr"/>
+      <c r="O66" s="11" t="inlineStr"/>
+      <c r="P66" s="11" t="inlineStr"/>
+      <c r="Q66" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R66" s="11" t="inlineStr"/>
+      <c r="S66" s="11" t="inlineStr"/>
+      <c r="T66" s="11" t="inlineStr"/>
+      <c r="U66" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V66" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W66" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C67" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>20260385728</t>
+        </is>
+      </c>
+      <c r="E67" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F67" s="11" t="inlineStr"/>
+      <c r="G67" s="11" t="inlineStr"/>
+      <c r="H67" s="11" t="inlineStr"/>
+      <c r="I67" s="11" t="inlineStr"/>
+      <c r="J67" s="11" t="inlineStr"/>
+      <c r="K67" s="11" t="inlineStr"/>
+      <c r="L67" s="11" t="inlineStr"/>
+      <c r="M67" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N67" s="11" t="inlineStr"/>
+      <c r="O67" s="11" t="inlineStr"/>
+      <c r="P67" s="11" t="inlineStr"/>
+      <c r="Q67" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R67" s="11" t="inlineStr"/>
+      <c r="S67" s="11" t="inlineStr"/>
+      <c r="T67" s="11" t="inlineStr"/>
+      <c r="U67" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V67" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W67" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B68" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C68" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D68" s="11" t="inlineStr">
+        <is>
+          <t>20260385729</t>
+        </is>
+      </c>
+      <c r="E68" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F68" s="11" t="inlineStr"/>
+      <c r="G68" s="11" t="inlineStr"/>
+      <c r="H68" s="11" t="inlineStr"/>
+      <c r="I68" s="11" t="inlineStr"/>
+      <c r="J68" s="11" t="inlineStr"/>
+      <c r="K68" s="11" t="inlineStr"/>
+      <c r="L68" s="11" t="inlineStr"/>
+      <c r="M68" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N68" s="11" t="inlineStr"/>
+      <c r="O68" s="11" t="inlineStr"/>
+      <c r="P68" s="11" t="inlineStr"/>
+      <c r="Q68" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R68" s="11" t="inlineStr"/>
+      <c r="S68" s="11" t="inlineStr"/>
+      <c r="T68" s="11" t="inlineStr"/>
+      <c r="U68" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V68" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W68" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B69" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C69" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D69" s="11" t="inlineStr">
+        <is>
+          <t>20260385730</t>
+        </is>
+      </c>
+      <c r="E69" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F69" s="11" t="inlineStr"/>
+      <c r="G69" s="11" t="inlineStr"/>
+      <c r="H69" s="11" t="inlineStr"/>
+      <c r="I69" s="11" t="inlineStr"/>
+      <c r="J69" s="11" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr"/>
+      <c r="L69" s="11" t="inlineStr"/>
+      <c r="M69" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N69" s="11" t="inlineStr"/>
+      <c r="O69" s="11" t="inlineStr"/>
+      <c r="P69" s="11" t="inlineStr"/>
+      <c r="Q69" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R69" s="11" t="inlineStr"/>
+      <c r="S69" s="11" t="inlineStr"/>
+      <c r="T69" s="11" t="inlineStr"/>
+      <c r="U69" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V69" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W69" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B70" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C70" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D70" s="11" t="inlineStr">
+        <is>
+          <t>20260385731</t>
+        </is>
+      </c>
+      <c r="E70" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F70" s="11" t="inlineStr"/>
+      <c r="G70" s="11" t="inlineStr"/>
+      <c r="H70" s="11" t="inlineStr"/>
+      <c r="I70" s="11" t="inlineStr"/>
+      <c r="J70" s="11" t="inlineStr"/>
+      <c r="K70" s="11" t="inlineStr"/>
+      <c r="L70" s="11" t="inlineStr"/>
+      <c r="M70" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N70" s="11" t="inlineStr"/>
+      <c r="O70" s="11" t="inlineStr"/>
+      <c r="P70" s="11" t="inlineStr"/>
+      <c r="Q70" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R70" s="11" t="inlineStr"/>
+      <c r="S70" s="11" t="inlineStr"/>
+      <c r="T70" s="11" t="inlineStr"/>
+      <c r="U70" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V70" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W70" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>20260385732</t>
+        </is>
+      </c>
+      <c r="E71" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F71" s="11" t="inlineStr"/>
+      <c r="G71" s="11" t="inlineStr"/>
+      <c r="H71" s="11" t="inlineStr"/>
+      <c r="I71" s="11" t="inlineStr"/>
+      <c r="J71" s="11" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr"/>
+      <c r="L71" s="11" t="inlineStr"/>
+      <c r="M71" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N71" s="11" t="inlineStr"/>
+      <c r="O71" s="11" t="inlineStr"/>
+      <c r="P71" s="11" t="inlineStr"/>
+      <c r="Q71" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R71" s="11" t="inlineStr"/>
+      <c r="S71" s="11" t="inlineStr"/>
+      <c r="T71" s="11" t="inlineStr"/>
+      <c r="U71" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V71" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W71" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C72" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>20260385733</t>
+        </is>
+      </c>
+      <c r="E72" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F72" s="11" t="inlineStr"/>
+      <c r="G72" s="11" t="inlineStr"/>
+      <c r="H72" s="11" t="inlineStr"/>
+      <c r="I72" s="11" t="inlineStr"/>
+      <c r="J72" s="11" t="inlineStr"/>
+      <c r="K72" s="11" t="inlineStr"/>
+      <c r="L72" s="11" t="inlineStr"/>
+      <c r="M72" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N72" s="11" t="inlineStr"/>
+      <c r="O72" s="11" t="inlineStr"/>
+      <c r="P72" s="11" t="inlineStr"/>
+      <c r="Q72" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R72" s="11" t="inlineStr"/>
+      <c r="S72" s="11" t="inlineStr"/>
+      <c r="T72" s="11" t="inlineStr"/>
+      <c r="U72" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V72" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W72" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>Medical Lien</t>
+        </is>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>20260386323</t>
+        </is>
+      </c>
+      <c r="E73" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F73" s="11" t="inlineStr"/>
+      <c r="G73" s="11" t="inlineStr"/>
+      <c r="H73" s="11" t="inlineStr"/>
+      <c r="I73" s="11" t="inlineStr"/>
+      <c r="J73" s="11" t="inlineStr"/>
+      <c r="K73" s="11" t="inlineStr"/>
+      <c r="L73" s="11" t="inlineStr"/>
+      <c r="M73" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N73" s="11" t="inlineStr"/>
+      <c r="O73" s="11" t="inlineStr"/>
+      <c r="P73" s="11" t="inlineStr"/>
+      <c r="Q73" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R73" s="11" t="inlineStr"/>
+      <c r="S73" s="11" t="inlineStr"/>
+      <c r="T73" s="11" t="inlineStr"/>
+      <c r="U73" s="11" t="inlineStr">
+        <is>
+          <t>Medical lien; New this week</t>
+        </is>
+      </c>
+      <c r="V73" s="11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W73" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>20260386205</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F74" s="11" t="inlineStr"/>
+      <c r="G74" s="11" t="inlineStr"/>
+      <c r="H74" s="11" t="inlineStr"/>
+      <c r="I74" s="11" t="inlineStr"/>
+      <c r="J74" s="11" t="inlineStr"/>
+      <c r="K74" s="11" t="inlineStr"/>
+      <c r="L74" s="11" t="inlineStr"/>
+      <c r="M74" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N74" s="11" t="inlineStr"/>
+      <c r="O74" s="11" t="inlineStr"/>
+      <c r="P74" s="11" t="inlineStr"/>
+      <c r="Q74" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R74" s="11" t="inlineStr"/>
+      <c r="S74" s="11" t="inlineStr"/>
+      <c r="T74" s="11" t="inlineStr"/>
+      <c r="U74" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V74" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W74" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="26" customHeight="1">
+      <c r="A75" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B75" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D75" s="11" t="inlineStr">
+        <is>
+          <t>20260386490</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F75" s="11" t="inlineStr"/>
+      <c r="G75" s="11" t="inlineStr"/>
+      <c r="H75" s="11" t="inlineStr"/>
+      <c r="I75" s="11" t="inlineStr"/>
+      <c r="J75" s="11" t="inlineStr"/>
+      <c r="K75" s="11" t="inlineStr"/>
+      <c r="L75" s="11" t="inlineStr"/>
+      <c r="M75" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N75" s="11" t="inlineStr"/>
+      <c r="O75" s="11" t="inlineStr"/>
+      <c r="P75" s="11" t="inlineStr"/>
+      <c r="Q75" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R75" s="11" t="inlineStr"/>
+      <c r="S75" s="11" t="inlineStr"/>
+      <c r="T75" s="11" t="inlineStr"/>
+      <c r="U75" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V75" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W75" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B76" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D76" s="11" t="inlineStr">
+        <is>
+          <t>20260387793</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F76" s="11" t="inlineStr"/>
+      <c r="G76" s="11" t="inlineStr"/>
+      <c r="H76" s="11" t="inlineStr"/>
+      <c r="I76" s="11" t="inlineStr"/>
+      <c r="J76" s="11" t="inlineStr"/>
+      <c r="K76" s="11" t="inlineStr"/>
+      <c r="L76" s="11" t="inlineStr"/>
+      <c r="M76" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N76" s="11" t="inlineStr"/>
+      <c r="O76" s="11" t="inlineStr"/>
+      <c r="P76" s="11" t="inlineStr"/>
+      <c r="Q76" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R76" s="11" t="inlineStr"/>
+      <c r="S76" s="11" t="inlineStr"/>
+      <c r="T76" s="11" t="inlineStr"/>
+      <c r="U76" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V76" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W76" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="B77" s="11" t="inlineStr">
+        <is>
+          <t>Tax Deed</t>
+        </is>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D77" s="11" t="inlineStr">
+        <is>
+          <t>20260388150</t>
+        </is>
+      </c>
+      <c r="E77" s="11" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="F77" s="11" t="inlineStr"/>
+      <c r="G77" s="11" t="inlineStr"/>
+      <c r="H77" s="11" t="inlineStr"/>
+      <c r="I77" s="11" t="inlineStr"/>
+      <c r="J77" s="11" t="inlineStr"/>
+      <c r="K77" s="11" t="inlineStr"/>
+      <c r="L77" s="11" t="inlineStr"/>
+      <c r="M77" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="N77" s="11" t="inlineStr"/>
+      <c r="O77" s="11" t="inlineStr"/>
+      <c r="P77" s="11" t="inlineStr"/>
+      <c r="Q77" s="11" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="R77" s="11" t="inlineStr"/>
+      <c r="S77" s="11" t="inlineStr"/>
+      <c r="T77" s="11" t="inlineStr"/>
+      <c r="U77" s="11" t="inlineStr">
+        <is>
+          <t>Tax deed; New this week</t>
+        </is>
+      </c>
+      <c r="V77" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W77" s="12" t="inlineStr">
+        <is>
+          <t>View ↗</t>
+        </is>